--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -43084,7 +43084,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43917,7 +43917,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44459,7 +44459,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -5684,7 +5684,7 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="F1">
-            <v>6780</v>
+            <v>5111.25</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -5698,7 +5698,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -5719,28 +5719,28 @@
             <v>0</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>120</v>
           </cell>
           <cell r="Y1">
+            <v>157</v>
+          </cell>
+          <cell r="Z1">
+            <v>0</v>
+          </cell>
+          <cell r="AA1">
+            <v>135</v>
+          </cell>
+          <cell r="AB1">
+            <v>92</v>
+          </cell>
+          <cell r="AC1">
+            <v>602.25</v>
+          </cell>
+          <cell r="AD1">
+            <v>1440</v>
+          </cell>
+          <cell r="AE1">
             <v>180</v>
-          </cell>
-          <cell r="Z1">
-            <v>0</v>
-          </cell>
-          <cell r="AA1">
-            <v>60</v>
-          </cell>
-          <cell r="AB1">
-            <v>0</v>
-          </cell>
-          <cell r="AC1">
-            <v>1080</v>
-          </cell>
-          <cell r="AD1">
-            <v>960</v>
-          </cell>
-          <cell r="AE1">
-            <v>0</v>
           </cell>
           <cell r="AF1">
             <v>300</v>
@@ -5749,7 +5749,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>2400</v>
+            <v>0</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -5764,7 +5764,7 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="F1">
-            <v>5520</v>
+            <v>6375</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -5772,13 +5772,13 @@
         </row>
         <row r="1">
           <cell r="O1">
-            <v>0</v>
+            <v>720</v>
           </cell>
           <cell r="P1">
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>360</v>
+            <v>249</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -5793,28 +5793,28 @@
             <v>0</v>
           </cell>
           <cell r="V1">
-            <v>480</v>
+            <v>180</v>
           </cell>
           <cell r="W1">
-            <v>0</v>
+            <v>240</v>
           </cell>
           <cell r="X1">
             <v>0</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>115</v>
           </cell>
           <cell r="Z1">
-            <v>1200</v>
+            <v>600</v>
           </cell>
           <cell r="AA1">
-            <v>60</v>
+            <v>153</v>
           </cell>
           <cell r="AB1">
-            <v>0</v>
+            <v>152</v>
           </cell>
           <cell r="AC1">
-            <v>120</v>
+            <v>666</v>
           </cell>
           <cell r="AD1">
             <v>0</v>
@@ -5844,7 +5844,7 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="F1">
-            <v>6840</v>
+            <v>9057</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -5852,13 +5852,13 @@
         </row>
         <row r="1">
           <cell r="O1">
-            <v>0</v>
+            <v>360</v>
           </cell>
           <cell r="P1">
-            <v>3600</v>
+            <v>5000</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -5882,28 +5882,28 @@
             <v>0</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>145</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
           </cell>
           <cell r="AA1">
-            <v>180</v>
+            <v>231</v>
           </cell>
           <cell r="AB1">
-            <v>480</v>
+            <v>272</v>
           </cell>
           <cell r="AC1">
-            <v>0</v>
+            <v>654</v>
           </cell>
           <cell r="AD1">
             <v>0</v>
           </cell>
           <cell r="AE1">
-            <v>720</v>
+            <v>0</v>
           </cell>
           <cell r="AF1">
-            <v>300</v>
+            <v>550</v>
           </cell>
           <cell r="AG1">
             <v>0</v>
@@ -5924,7 +5924,7 @@
       <sheetData sheetId="4">
         <row r="1">
           <cell r="F1">
-            <v>22080</v>
+            <v>8759.25</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -5938,7 +5938,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>249</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -5953,46 +5953,46 @@
             <v>0</v>
           </cell>
           <cell r="V1">
-            <v>0</v>
+            <v>120</v>
           </cell>
           <cell r="W1">
-            <v>960</v>
+            <v>480</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>180</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>115</v>
           </cell>
           <cell r="Z1">
-            <v>0</v>
+            <v>480</v>
           </cell>
           <cell r="AA1">
-            <v>60</v>
+            <v>159</v>
           </cell>
           <cell r="AB1">
-            <v>0</v>
+            <v>92</v>
           </cell>
           <cell r="AC1">
-            <v>840</v>
+            <v>584.25</v>
           </cell>
           <cell r="AD1">
             <v>0</v>
           </cell>
           <cell r="AE1">
-            <v>0</v>
+            <v>180</v>
           </cell>
           <cell r="AF1">
-            <v>300</v>
+            <v>0</v>
           </cell>
           <cell r="AG1">
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>0</v>
+            <v>3000</v>
           </cell>
           <cell r="AI1">
-            <v>18000</v>
+            <v>1200</v>
           </cell>
         </row>
         <row r="1">
@@ -6004,7 +6004,7 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="F1">
-            <v>2480</v>
+            <v>4705.25</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -6012,13 +6012,13 @@
         </row>
         <row r="1">
           <cell r="O1">
-            <v>0</v>
+            <v>540</v>
           </cell>
           <cell r="P1">
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -6039,22 +6039,22 @@
             <v>0</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>240</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>163</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
           </cell>
           <cell r="AA1">
-            <v>60</v>
+            <v>135</v>
           </cell>
           <cell r="AB1">
-            <v>0</v>
+            <v>140</v>
           </cell>
           <cell r="AC1">
-            <v>120</v>
+            <v>602.25</v>
           </cell>
           <cell r="AD1">
             <v>0</v>
@@ -6063,7 +6063,7 @@
             <v>0</v>
           </cell>
           <cell r="AF1">
-            <v>300</v>
+            <v>600</v>
           </cell>
           <cell r="AG1">
             <v>0</v>
@@ -6084,7 +6084,7 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="F1">
-            <v>7920</v>
+            <v>4975</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -6092,13 +6092,13 @@
         </row>
         <row r="1">
           <cell r="O1">
-            <v>0</v>
+            <v>240</v>
           </cell>
           <cell r="P1">
-            <v>2400</v>
+            <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>249</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -6110,40 +6110,40 @@
             <v>1200</v>
           </cell>
           <cell r="U1">
+            <v>300</v>
+          </cell>
+          <cell r="V1">
+            <v>96</v>
+          </cell>
+          <cell r="W1">
             <v>360</v>
           </cell>
-          <cell r="V1">
-            <v>0</v>
-          </cell>
-          <cell r="W1">
-            <v>0</v>
-          </cell>
           <cell r="X1">
-            <v>480</v>
+            <v>0</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>115</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
           </cell>
           <cell r="AA1">
-            <v>60</v>
+            <v>147</v>
           </cell>
           <cell r="AB1">
-            <v>0</v>
+            <v>92</v>
           </cell>
           <cell r="AC1">
-            <v>0</v>
+            <v>708</v>
           </cell>
           <cell r="AD1">
             <v>0</v>
           </cell>
           <cell r="AE1">
-            <v>720</v>
+            <v>0</v>
           </cell>
           <cell r="AF1">
-            <v>300</v>
+            <v>1468</v>
           </cell>
           <cell r="AG1">
             <v>0</v>
@@ -6152,7 +6152,7 @@
             <v>0</v>
           </cell>
           <cell r="AI1">
-            <v>2400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="1">
@@ -6164,7 +6164,7 @@
       <sheetData sheetId="7">
         <row r="1">
           <cell r="F1">
-            <v>2184</v>
+            <v>43005.75</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -6178,7 +6178,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -6199,28 +6199,28 @@
             <v>0</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>96</v>
           </cell>
           <cell r="Y1">
-            <v>144</v>
+            <v>151</v>
           </cell>
           <cell r="Z1">
-            <v>0</v>
+            <v>3000</v>
           </cell>
           <cell r="AA1">
-            <v>60</v>
+            <v>135</v>
           </cell>
           <cell r="AB1">
-            <v>0</v>
+            <v>212</v>
           </cell>
           <cell r="AC1">
-            <v>0</v>
+            <v>606.75</v>
           </cell>
           <cell r="AD1">
-            <v>0</v>
+            <v>360</v>
           </cell>
           <cell r="AE1">
-            <v>0</v>
+            <v>180</v>
           </cell>
           <cell r="AF1">
             <v>300</v>
@@ -6232,7 +6232,7 @@
             <v>0</v>
           </cell>
           <cell r="AI1">
-            <v>0</v>
+            <v>36000</v>
           </cell>
         </row>
         <row r="1">
@@ -6244,7 +6244,7 @@
       <sheetData sheetId="8">
         <row r="1">
           <cell r="F1">
-            <v>2640</v>
+            <v>6918</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -6252,13 +6252,13 @@
         </row>
         <row r="1">
           <cell r="O1">
-            <v>0</v>
+            <v>840</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>3000</v>
           </cell>
           <cell r="Q1">
-            <v>360</v>
+            <v>249</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -6282,19 +6282,19 @@
             <v>0</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>115</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
           </cell>
           <cell r="AA1">
-            <v>60</v>
+            <v>165</v>
           </cell>
           <cell r="AB1">
-            <v>360</v>
+            <v>164</v>
           </cell>
           <cell r="AC1">
-            <v>120</v>
+            <v>645</v>
           </cell>
           <cell r="AD1">
             <v>0</v>
@@ -6324,7 +6324,7 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="F1">
-            <v>7900</v>
+            <v>3984.5</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -6332,16 +6332,16 @@
         </row>
         <row r="1">
           <cell r="O1">
-            <v>0</v>
+            <v>480</v>
           </cell>
           <cell r="P1">
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="R1">
-            <v>5000</v>
+            <v>0</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -6350,7 +6350,7 @@
             <v>1200</v>
           </cell>
           <cell r="U1">
-            <v>0</v>
+            <v>420</v>
           </cell>
           <cell r="V1">
             <v>0</v>
@@ -6362,28 +6362,28 @@
             <v>0</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>139</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
           </cell>
           <cell r="AA1">
-            <v>180</v>
+            <v>255</v>
           </cell>
           <cell r="AB1">
-            <v>0</v>
+            <v>92</v>
           </cell>
           <cell r="AC1">
-            <v>0</v>
+            <v>613.5</v>
           </cell>
           <cell r="AD1">
             <v>0</v>
           </cell>
           <cell r="AE1">
-            <v>720</v>
+            <v>0</v>
           </cell>
           <cell r="AF1">
-            <v>300</v>
+            <v>0</v>
           </cell>
           <cell r="AG1">
             <v>500</v>
@@ -6404,7 +6404,7 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="F1">
-            <v>3120</v>
+            <v>9978.25</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -6418,10 +6418,10 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>249</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>5000</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -6430,40 +6430,40 @@
             <v>1200</v>
           </cell>
           <cell r="U1">
-            <v>360</v>
+            <v>0</v>
           </cell>
           <cell r="V1">
-            <v>0</v>
+            <v>180</v>
           </cell>
           <cell r="W1">
-            <v>0</v>
+            <v>180</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>144</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>115</v>
           </cell>
           <cell r="Z1">
-            <v>600</v>
+            <v>480</v>
           </cell>
           <cell r="AA1">
-            <v>60</v>
+            <v>153</v>
           </cell>
           <cell r="AB1">
-            <v>0</v>
+            <v>92</v>
           </cell>
           <cell r="AC1">
-            <v>0</v>
+            <v>638.25</v>
           </cell>
           <cell r="AD1">
             <v>0</v>
           </cell>
           <cell r="AE1">
-            <v>0</v>
+            <v>180</v>
           </cell>
           <cell r="AF1">
-            <v>300</v>
+            <v>767</v>
           </cell>
           <cell r="AG1">
             <v>0</v>
@@ -6484,7 +6484,7 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="F1">
-            <v>2136</v>
+            <v>4396.5</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -6492,13 +6492,13 @@
         </row>
         <row r="1">
           <cell r="O1">
-            <v>0</v>
+            <v>660</v>
           </cell>
           <cell r="P1">
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -6516,25 +6516,25 @@
             <v>0</v>
           </cell>
           <cell r="W1">
-            <v>0</v>
+            <v>360</v>
           </cell>
           <cell r="X1">
             <v>360</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>133</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
           </cell>
           <cell r="AA1">
-            <v>60</v>
+            <v>135</v>
           </cell>
           <cell r="AB1">
-            <v>96</v>
+            <v>368</v>
           </cell>
           <cell r="AC1">
-            <v>120</v>
+            <v>595.5</v>
           </cell>
           <cell r="AD1">
             <v>0</v>
@@ -6564,7 +6564,7 @@
       <sheetData sheetId="12">
         <row r="1">
           <cell r="F1">
-            <v>4440</v>
+            <v>3726.5</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -6572,13 +6572,13 @@
         </row>
         <row r="1">
           <cell r="O1">
-            <v>0</v>
+            <v>300</v>
           </cell>
           <cell r="P1">
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>249</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -6593,7 +6593,7 @@
             <v>360</v>
           </cell>
           <cell r="V1">
-            <v>0</v>
+            <v>144</v>
           </cell>
           <cell r="W1">
             <v>0</v>
@@ -6602,28 +6602,28 @@
             <v>0</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>115</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
           </cell>
           <cell r="AA1">
-            <v>60</v>
+            <v>159</v>
           </cell>
           <cell r="AB1">
-            <v>0</v>
+            <v>92</v>
           </cell>
           <cell r="AC1">
-            <v>0</v>
+            <v>682.5</v>
           </cell>
           <cell r="AD1">
             <v>0</v>
           </cell>
           <cell r="AE1">
-            <v>720</v>
+            <v>0</v>
           </cell>
           <cell r="AF1">
-            <v>2100</v>
+            <v>425</v>
           </cell>
           <cell r="AG1">
             <v>0</v>
@@ -6671,24 +6671,24 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="F1">
-            <v>8200</v>
+            <v>16400</v>
           </cell>
           <cell r="G1">
-            <v>1366.66666666667</v>
+            <v>2733.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>5833.33333333333</v>
+            <v>11166.6666666667</v>
           </cell>
           <cell r="P1">
-            <v>1000</v>
+            <v>1800</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>700</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -6707,21 +6707,21 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="F1">
-            <v>7000</v>
+            <v>15920</v>
           </cell>
           <cell r="G1">
-            <v>1166.66666666667</v>
+            <v>2653.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>5833.33333333333</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -6743,18 +6743,18 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="F1">
-            <v>9400</v>
+            <v>18200</v>
           </cell>
           <cell r="G1">
-            <v>1566.66666666667</v>
+            <v>3033.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>5833.33333333333</v>
+            <v>12366.6666666667</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="Q1">
             <v>2000</v>
@@ -6779,24 +6779,24 @@
       <sheetData sheetId="4">
         <row r="1">
           <cell r="F1">
-            <v>8200</v>
+            <v>16760</v>
           </cell>
           <cell r="G1">
-            <v>1366.66666666667</v>
+            <v>2793.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>5833.33333333333</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="P1">
-            <v>1000</v>
+            <v>1800</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>700</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -6815,18 +6815,18 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="F1">
-            <v>9500</v>
+            <v>19020</v>
           </cell>
           <cell r="G1">
-            <v>1583.33333333333</v>
+            <v>3170</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>5833.33333333333</v>
+            <v>12966.6666666667</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -6851,21 +6851,21 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="F1">
-            <v>7600</v>
+            <v>16760</v>
           </cell>
           <cell r="G1">
-            <v>1266.66666666667</v>
+            <v>2793.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>5833.33333333333</v>
+            <v>10866.6666666667</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>1800</v>
           </cell>
           <cell r="R1">
             <v>500</v>
@@ -6887,24 +6887,24 @@
       <sheetData sheetId="7">
         <row r="1">
           <cell r="F1">
-            <v>14400</v>
+            <v>33560</v>
           </cell>
           <cell r="G1">
-            <v>2400</v>
+            <v>5593.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>7000</v>
+            <v>12966.6666666667</v>
           </cell>
           <cell r="P1">
-            <v>1000</v>
+            <v>1800</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>700</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -6913,7 +6913,7 @@
             <v>0</v>
           </cell>
           <cell r="U1">
-            <v>4000</v>
+            <v>12500</v>
           </cell>
           <cell r="V1">
             <v>0</v>
@@ -6923,18 +6923,18 @@
       <sheetData sheetId="8">
         <row r="1">
           <cell r="F1">
-            <v>12000</v>
+            <v>18320</v>
           </cell>
           <cell r="G1">
-            <v>2000</v>
+            <v>3053.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>7000</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="Q1">
             <v>3000</v>
@@ -6959,18 +6959,18 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="F1">
-            <v>8400</v>
+            <v>15800</v>
           </cell>
           <cell r="G1">
-            <v>1400</v>
+            <v>2633.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>7000</v>
+            <v>12366.6666666667</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -6995,24 +6995,24 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="F1">
-            <v>9600</v>
+            <v>18440</v>
           </cell>
           <cell r="G1">
-            <v>1600</v>
+            <v>3073.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>7000</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="P1">
+            <v>1800</v>
+          </cell>
+          <cell r="Q1">
             <v>1000</v>
           </cell>
-          <cell r="Q1">
-            <v>0</v>
-          </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>1100</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -7031,21 +7031,21 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="F1">
-            <v>8400</v>
+            <v>17360</v>
           </cell>
           <cell r="G1">
-            <v>1400</v>
+            <v>2893.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>7000</v>
+            <v>12166.6666666667</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>1500</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -7067,18 +7067,18 @@
       <sheetData sheetId="12">
         <row r="1">
           <cell r="F1">
-            <v>8760</v>
+            <v>14360</v>
           </cell>
           <cell r="G1">
-            <v>1460</v>
+            <v>2393.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>7000</v>
+            <v>10866.6666666667</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -15217,7 +15217,7 @@
       <c r="I8" s="78"/>
       <c r="J8" s="78" t="n">
         <f aca="false">[3]Jun!$O$1</f>
-        <v>5833.33333333333</v>
+        <v>11166.6666666667</v>
       </c>
       <c r="K8" s="78"/>
       <c r="L8" s="432" t="n">
@@ -15232,7 +15232,7 @@
       <c r="O8" s="78"/>
       <c r="P8" s="78" t="n">
         <f aca="false">[3]Jun!$P$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="Q8" s="78"/>
       <c r="R8" s="432" t="n">
@@ -15331,7 +15331,7 @@
       <c r="I10" s="78"/>
       <c r="J10" s="78" t="n">
         <f aca="false">[3]Jul!$O$1</f>
-        <v>5833.33333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K10" s="78"/>
       <c r="L10" s="432" t="n">
@@ -15346,7 +15346,7 @@
       <c r="O10" s="78"/>
       <c r="P10" s="78" t="n">
         <f aca="false">[3]Jul!$P$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q10" s="78"/>
       <c r="R10" s="432" t="n">
@@ -15361,7 +15361,7 @@
       <c r="U10" s="78"/>
       <c r="V10" s="78" t="n">
         <f aca="false">[3]Jul!$Q$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W10" s="78"/>
       <c r="X10" s="78" t="n">
@@ -15447,7 +15447,7 @@
       <c r="I12" s="78"/>
       <c r="J12" s="78" t="n">
         <f aca="false">[3]Aug!$O$1</f>
-        <v>5833.33333333333</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="K12" s="78"/>
       <c r="L12" s="432" t="n">
@@ -15462,7 +15462,7 @@
       <c r="O12" s="78"/>
       <c r="P12" s="78" t="n">
         <f aca="false">[3]Aug!$P$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q12" s="78"/>
       <c r="R12" s="432" t="n">
@@ -15561,7 +15561,7 @@
       <c r="I14" s="78"/>
       <c r="J14" s="78" t="n">
         <f aca="false">[3]Sep!$O$1</f>
-        <v>5833.33333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K14" s="78"/>
       <c r="L14" s="432" t="n">
@@ -15576,7 +15576,7 @@
       <c r="O14" s="78"/>
       <c r="P14" s="78" t="n">
         <f aca="false">[3]Sep!$P$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="Q14" s="78"/>
       <c r="R14" s="432" t="n">
@@ -15677,7 +15677,7 @@
       <c r="I16" s="78"/>
       <c r="J16" s="78" t="n">
         <f aca="false">[3]Oct!$O$1</f>
-        <v>5833.33333333333</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="K16" s="78"/>
       <c r="L16" s="432" t="n">
@@ -15692,7 +15692,7 @@
       <c r="O16" s="78"/>
       <c r="P16" s="78" t="n">
         <f aca="false">[3]Oct!$P$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q16" s="78"/>
       <c r="R16" s="432" t="n">
@@ -15791,7 +15791,7 @@
       <c r="I18" s="78"/>
       <c r="J18" s="78" t="n">
         <f aca="false">[3]Nov!$O$1</f>
-        <v>5833.33333333333</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="K18" s="78"/>
       <c r="L18" s="432" t="n">
@@ -15806,7 +15806,7 @@
       <c r="O18" s="78"/>
       <c r="P18" s="78" t="n">
         <f aca="false">[3]Nov!$P$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q18" s="78"/>
       <c r="R18" s="432" t="n">
@@ -15821,7 +15821,7 @@
       <c r="U18" s="78"/>
       <c r="V18" s="78" t="n">
         <f aca="false">[3]Nov!$Q$1</f>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="W18" s="78"/>
       <c r="X18" s="78" t="n">
@@ -15907,7 +15907,7 @@
       <c r="I20" s="78"/>
       <c r="J20" s="78" t="n">
         <f aca="false">[3]Dec!$O$1</f>
-        <v>7000</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="K20" s="78"/>
       <c r="L20" s="432" t="n">
@@ -15922,7 +15922,7 @@
       <c r="O20" s="78"/>
       <c r="P20" s="78" t="n">
         <f aca="false">[3]Dec!$P$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="Q20" s="78"/>
       <c r="R20" s="432" t="n">
@@ -16021,7 +16021,7 @@
       <c r="I22" s="78"/>
       <c r="J22" s="78" t="n">
         <f aca="false">[3]Jan!$O$1</f>
-        <v>7000</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K22" s="78"/>
       <c r="L22" s="432" t="n">
@@ -16036,7 +16036,7 @@
       <c r="O22" s="78"/>
       <c r="P22" s="78" t="n">
         <f aca="false">[3]Jan!$P$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q22" s="78"/>
       <c r="R22" s="432" t="n">
@@ -16137,7 +16137,7 @@
       <c r="I24" s="78"/>
       <c r="J24" s="78" t="n">
         <f aca="false">[3]Feb!$O$1</f>
-        <v>7000</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="K24" s="78"/>
       <c r="L24" s="432" t="n">
@@ -16152,7 +16152,7 @@
       <c r="O24" s="78"/>
       <c r="P24" s="78" t="n">
         <f aca="false">[3]Feb!$P$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q24" s="78"/>
       <c r="R24" s="432" t="n">
@@ -16251,7 +16251,7 @@
       <c r="I26" s="78"/>
       <c r="J26" s="78" t="n">
         <f aca="false">[3]Mar!$O$1</f>
-        <v>7000</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K26" s="78"/>
       <c r="L26" s="432" t="n">
@@ -16266,7 +16266,7 @@
       <c r="O26" s="78"/>
       <c r="P26" s="78" t="n">
         <f aca="false">[3]Mar!$P$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="Q26" s="78"/>
       <c r="R26" s="432" t="n">
@@ -16281,7 +16281,7 @@
       <c r="U26" s="78"/>
       <c r="V26" s="78" t="n">
         <f aca="false">[3]Mar!$Q$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W26" s="78"/>
       <c r="X26" s="78" t="n">
@@ -16365,7 +16365,7 @@
       <c r="I28" s="78"/>
       <c r="J28" s="78" t="n">
         <f aca="false">[3]Apr!$O$1</f>
-        <v>7000</v>
+        <v>12166.6666666667</v>
       </c>
       <c r="K28" s="78"/>
       <c r="L28" s="432" t="n">
@@ -16380,7 +16380,7 @@
       <c r="O28" s="78"/>
       <c r="P28" s="78" t="n">
         <f aca="false">[3]Apr!$P$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q28" s="78"/>
       <c r="R28" s="432" t="n">
@@ -16395,7 +16395,7 @@
       <c r="U28" s="78"/>
       <c r="V28" s="78" t="n">
         <f aca="false">[3]Apr!$Q$1</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="W28" s="78"/>
       <c r="X28" s="78" t="n">
@@ -16481,7 +16481,7 @@
       <c r="I30" s="78"/>
       <c r="J30" s="78" t="n">
         <f aca="false">[3]May!$O$1</f>
-        <v>7000</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="K30" s="78"/>
       <c r="L30" s="432" t="n">
@@ -16496,7 +16496,7 @@
       <c r="O30" s="78"/>
       <c r="P30" s="78" t="n">
         <f aca="false">[3]May!$P$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q30" s="78"/>
       <c r="R30" s="432" t="n">
@@ -20807,7 +20807,7 @@
       <c r="AM16" s="36"/>
       <c r="AN16" s="36" t="n">
         <f aca="false">[2]Sep!$AI$1</f>
-        <v>18000</v>
+        <v>1200</v>
       </c>
       <c r="AO16" s="36"/>
       <c r="AP16" s="36"/>
@@ -20818,7 +20818,7 @@
       <c r="AU16" s="54"/>
       <c r="AV16" s="36" t="n">
         <f aca="false">SUM(AK16:AU16)</f>
-        <v>19800</v>
+        <v>3000</v>
       </c>
       <c r="AW16" s="57"/>
       <c r="AX16" s="36"/>
@@ -20835,13 +20835,13 @@
       <c r="BF16" s="54"/>
       <c r="BG16" s="36" t="n">
         <f aca="false">SUM(AV16:BF16)</f>
-        <v>19800</v>
+        <v>3000</v>
       </c>
       <c r="BH16" s="57"/>
       <c r="BI16" s="36"/>
       <c r="BJ16" s="36" t="n">
         <f aca="false">[2]Nov!$AI$1</f>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="BK16" s="36"/>
       <c r="BL16" s="36"/>
@@ -20852,13 +20852,13 @@
       <c r="BQ16" s="54"/>
       <c r="BR16" s="36" t="n">
         <f aca="false">SUM(BG16:BQ16)</f>
-        <v>22200</v>
+        <v>3000</v>
       </c>
       <c r="BS16" s="57"/>
       <c r="BT16" s="36"/>
       <c r="BU16" s="36" t="n">
         <f aca="false">[2]Dec!$AI$1</f>
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="BV16" s="36"/>
       <c r="BW16" s="36"/>
@@ -20869,7 +20869,7 @@
       <c r="CB16" s="54"/>
       <c r="CC16" s="36" t="n">
         <f aca="false">SUM(BR16:CB16)</f>
-        <v>22200</v>
+        <v>39000</v>
       </c>
       <c r="CD16" s="57"/>
       <c r="CE16" s="36"/>
@@ -20886,7 +20886,7 @@
       <c r="CM16" s="54"/>
       <c r="CN16" s="36" t="n">
         <f aca="false">SUM(CC16:CM16)</f>
-        <v>22200</v>
+        <v>39000</v>
       </c>
       <c r="CO16" s="57"/>
       <c r="CP16" s="36"/>
@@ -20903,7 +20903,7 @@
       <c r="CX16" s="54"/>
       <c r="CY16" s="36" t="n">
         <f aca="false">SUM(CN16:CX16)</f>
-        <v>22200</v>
+        <v>39000</v>
       </c>
       <c r="CZ16" s="57"/>
       <c r="DA16" s="36"/>
@@ -20920,7 +20920,7 @@
       <c r="DI16" s="54"/>
       <c r="DJ16" s="36" t="n">
         <f aca="false">SUM(CY16:DI16)</f>
-        <v>22200</v>
+        <v>39000</v>
       </c>
       <c r="DK16" s="57"/>
       <c r="DL16" s="36"/>
@@ -20937,7 +20937,7 @@
       <c r="DT16" s="54"/>
       <c r="DU16" s="36" t="n">
         <f aca="false">SUM(DJ16:DT16)</f>
-        <v>22200</v>
+        <v>39000</v>
       </c>
       <c r="DV16" s="57"/>
       <c r="DW16" s="36"/>
@@ -20954,7 +20954,7 @@
       <c r="EE16" s="54"/>
       <c r="EF16" s="36" t="n">
         <f aca="false">SUM(DU16:EE16)</f>
-        <v>22200</v>
+        <v>39000</v>
       </c>
       <c r="EG16" s="54"/>
       <c r="EH16" s="36" t="n">
@@ -20964,7 +20964,7 @@
       <c r="EI16" s="54"/>
       <c r="EJ16" s="36" t="n">
         <f aca="false">SUM(EF16:EH16)</f>
-        <v>22200</v>
+        <v>39000</v>
       </c>
       <c r="EK16" s="54"/>
     </row>
@@ -21100,7 +21100,7 @@
       <c r="BS17" s="57"/>
       <c r="BT17" s="36" t="n">
         <f aca="false">-[3]Dec!$U$1</f>
-        <v>-4000</v>
+        <v>-12500</v>
       </c>
       <c r="BU17" s="36"/>
       <c r="BV17" s="36"/>
@@ -21115,7 +21115,7 @@
       <c r="CB17" s="54"/>
       <c r="CC17" s="36" t="n">
         <f aca="false">SUM(BR17:CB17)</f>
-        <v>-4000</v>
+        <v>-12500</v>
       </c>
       <c r="CD17" s="57"/>
       <c r="CE17" s="36" t="n">
@@ -21135,7 +21135,7 @@
       <c r="CM17" s="54"/>
       <c r="CN17" s="36" t="n">
         <f aca="false">SUM(CC17:CM17)</f>
-        <v>-4000</v>
+        <v>-12500</v>
       </c>
       <c r="CO17" s="57"/>
       <c r="CP17" s="36" t="n">
@@ -21155,7 +21155,7 @@
       <c r="CX17" s="54"/>
       <c r="CY17" s="36" t="n">
         <f aca="false">SUM(CN17:CX17)</f>
-        <v>-4000</v>
+        <v>-12500</v>
       </c>
       <c r="CZ17" s="57"/>
       <c r="DA17" s="36" t="n">
@@ -21175,7 +21175,7 @@
       <c r="DI17" s="54"/>
       <c r="DJ17" s="36" t="n">
         <f aca="false">SUM(CY17:DI17)</f>
-        <v>-4000</v>
+        <v>-12500</v>
       </c>
       <c r="DK17" s="57"/>
       <c r="DL17" s="36" t="n">
@@ -21195,7 +21195,7 @@
       <c r="DT17" s="54"/>
       <c r="DU17" s="36" t="n">
         <f aca="false">SUM(DJ17:DT17)</f>
-        <v>-4000</v>
+        <v>-12500</v>
       </c>
       <c r="DV17" s="57"/>
       <c r="DW17" s="36" t="n">
@@ -21215,7 +21215,7 @@
       <c r="EE17" s="54"/>
       <c r="EF17" s="36" t="n">
         <f aca="false">SUM(DU17:EE17)</f>
-        <v>-4000</v>
+        <v>-12500</v>
       </c>
       <c r="EG17" s="54"/>
       <c r="EH17" s="36" t="n">
@@ -21225,7 +21225,7 @@
       <c r="EI17" s="54"/>
       <c r="EJ17" s="36" t="n">
         <f aca="false">SUM(EF17:EH17)</f>
-        <v>-4000</v>
+        <v>-12500</v>
       </c>
       <c r="EK17" s="54"/>
     </row>
@@ -21602,7 +21602,7 @@
       <c r="E20" s="57"/>
       <c r="F20" s="36" t="n">
         <f aca="false">[3]Jun!$F$1-[3]Jun!$V$1</f>
-        <v>8200</v>
+        <v>16400</v>
       </c>
       <c r="G20" s="36"/>
       <c r="H20" s="36" t="n">
@@ -21625,12 +21625,12 @@
       <c r="N20" s="57"/>
       <c r="O20" s="36" t="n">
         <f aca="false">SUM(D20:N20)</f>
-        <v>8200</v>
+        <v>16400</v>
       </c>
       <c r="P20" s="57"/>
       <c r="Q20" s="36" t="n">
         <f aca="false">[3]Jul!$F$1-[3]Jul!$V$1</f>
-        <v>7000</v>
+        <v>15920</v>
       </c>
       <c r="R20" s="36"/>
       <c r="S20" s="36" t="n">
@@ -21656,12 +21656,12 @@
       <c r="Y20" s="54"/>
       <c r="Z20" s="36" t="n">
         <f aca="false">SUM(O20:Y20)</f>
-        <v>15200</v>
+        <v>32320</v>
       </c>
       <c r="AA20" s="57"/>
       <c r="AB20" s="36" t="n">
         <f aca="false">[3]Aug!$F$1-[3]Aug!$V$1</f>
-        <v>9400</v>
+        <v>18200</v>
       </c>
       <c r="AC20" s="36"/>
       <c r="AD20" s="36" t="n">
@@ -21685,12 +21685,12 @@
       <c r="AJ20" s="54"/>
       <c r="AK20" s="36" t="n">
         <f aca="false">SUM(Z20:AJ20)</f>
-        <v>24600</v>
+        <v>50520</v>
       </c>
       <c r="AL20" s="57"/>
       <c r="AM20" s="36" t="n">
         <f aca="false">[3]Sep!$F$1-[3]Sep!$V$1</f>
-        <v>8200</v>
+        <v>16760</v>
       </c>
       <c r="AN20" s="36"/>
       <c r="AO20" s="36" t="n">
@@ -21714,12 +21714,12 @@
       <c r="AU20" s="54"/>
       <c r="AV20" s="36" t="n">
         <f aca="false">SUM(AK20:AU20)</f>
-        <v>32800</v>
+        <v>67280</v>
       </c>
       <c r="AW20" s="57"/>
       <c r="AX20" s="36" t="n">
         <f aca="false">[3]Oct!$F$1-[3]Oct!$V$1</f>
-        <v>9500</v>
+        <v>19020</v>
       </c>
       <c r="AY20" s="36"/>
       <c r="AZ20" s="36" t="n">
@@ -21743,12 +21743,12 @@
       <c r="BF20" s="54"/>
       <c r="BG20" s="36" t="n">
         <f aca="false">SUM(AV20:BF20)</f>
-        <v>42300</v>
+        <v>86300</v>
       </c>
       <c r="BH20" s="57"/>
       <c r="BI20" s="36" t="n">
         <f aca="false">[3]Nov!$F$1-[3]Nov!$V$1</f>
-        <v>7600</v>
+        <v>16760</v>
       </c>
       <c r="BJ20" s="36"/>
       <c r="BK20" s="36" t="n">
@@ -21772,12 +21772,12 @@
       <c r="BQ20" s="54"/>
       <c r="BR20" s="36" t="n">
         <f aca="false">SUM(BG20:BQ20)</f>
-        <v>49900</v>
+        <v>103060</v>
       </c>
       <c r="BS20" s="57"/>
       <c r="BT20" s="36" t="n">
         <f aca="false">[3]Dec!$F$1-[3]Dec!$V$1</f>
-        <v>14400</v>
+        <v>33560</v>
       </c>
       <c r="BU20" s="36"/>
       <c r="BV20" s="36" t="n">
@@ -21801,12 +21801,12 @@
       <c r="CB20" s="54"/>
       <c r="CC20" s="36" t="n">
         <f aca="false">SUM(BR20:CB20)</f>
-        <v>64300</v>
+        <v>136620</v>
       </c>
       <c r="CD20" s="57"/>
       <c r="CE20" s="36" t="n">
         <f aca="false">[3]Jan!$F$1-[3]Jan!$V$1</f>
-        <v>12000</v>
+        <v>18320</v>
       </c>
       <c r="CF20" s="36"/>
       <c r="CG20" s="36" t="n">
@@ -21830,12 +21830,12 @@
       <c r="CM20" s="54"/>
       <c r="CN20" s="36" t="n">
         <f aca="false">SUM(CC20:CM20)</f>
-        <v>76300</v>
+        <v>154940</v>
       </c>
       <c r="CO20" s="57"/>
       <c r="CP20" s="36" t="n">
         <f aca="false">[3]Feb!$F$1-[3]Feb!$V$1</f>
-        <v>8400</v>
+        <v>15800</v>
       </c>
       <c r="CQ20" s="36"/>
       <c r="CR20" s="36" t="n">
@@ -21859,12 +21859,12 @@
       <c r="CX20" s="54"/>
       <c r="CY20" s="36" t="n">
         <f aca="false">SUM(CN20:CX20)</f>
-        <v>84700</v>
+        <v>170740</v>
       </c>
       <c r="CZ20" s="57"/>
       <c r="DA20" s="36" t="n">
         <f aca="false">[3]Mar!$F$1-[3]Mar!$V$1</f>
-        <v>9600</v>
+        <v>18440</v>
       </c>
       <c r="DB20" s="36"/>
       <c r="DC20" s="36" t="n">
@@ -21888,12 +21888,12 @@
       <c r="DI20" s="54"/>
       <c r="DJ20" s="36" t="n">
         <f aca="false">SUM(CY20:DI20)</f>
-        <v>94300</v>
+        <v>189180</v>
       </c>
       <c r="DK20" s="57"/>
       <c r="DL20" s="36" t="n">
         <f aca="false">[3]Apr!$F$1-[3]Apr!$V$1</f>
-        <v>8400</v>
+        <v>17360</v>
       </c>
       <c r="DM20" s="36"/>
       <c r="DN20" s="36" t="n">
@@ -21917,12 +21917,12 @@
       <c r="DT20" s="54"/>
       <c r="DU20" s="36" t="n">
         <f aca="false">SUM(DJ20:DT20)</f>
-        <v>102700</v>
+        <v>206540</v>
       </c>
       <c r="DV20" s="57"/>
       <c r="DW20" s="36" t="n">
         <f aca="false">[3]May!$F$1-[3]May!$V$1</f>
-        <v>8760</v>
+        <v>14360</v>
       </c>
       <c r="DX20" s="36"/>
       <c r="DY20" s="36" t="n">
@@ -21946,13 +21946,13 @@
       <c r="EE20" s="54"/>
       <c r="EF20" s="36" t="n">
         <f aca="false">SUM(DU20:EE20)</f>
-        <v>111460</v>
+        <v>220900</v>
       </c>
       <c r="EG20" s="54"/>
       <c r="EI20" s="54"/>
       <c r="EJ20" s="36" t="n">
         <f aca="false">SUM(EF20:EH20)</f>
-        <v>111460</v>
+        <v>220900</v>
       </c>
       <c r="EK20" s="54"/>
     </row>
@@ -23468,7 +23468,7 @@
       <c r="F28" s="36"/>
       <c r="G28" s="36" t="n">
         <f aca="false">-[2]Jun!$F$1+[2]Jun!$AK$1</f>
-        <v>-6780</v>
+        <v>-5111.25</v>
       </c>
       <c r="H28" s="36" t="n">
         <f aca="false">[4]Jun!$AB$1</f>
@@ -23490,13 +23490,13 @@
       <c r="N28" s="57"/>
       <c r="O28" s="36" t="n">
         <f aca="false">SUM(D28:N28)</f>
-        <v>-6780</v>
+        <v>-5111.25</v>
       </c>
       <c r="P28" s="57"/>
       <c r="Q28" s="36"/>
       <c r="R28" s="36" t="n">
         <f aca="false">-[2]Jul!$F$1+[2]Jul!$AK$1</f>
-        <v>-5520</v>
+        <v>-6375</v>
       </c>
       <c r="S28" s="36" t="n">
         <f aca="false">[4]Jul!$AB$1</f>
@@ -23519,13 +23519,13 @@
       <c r="Y28" s="54"/>
       <c r="Z28" s="36" t="n">
         <f aca="false">SUM(O28:Y28)</f>
-        <v>-12300</v>
+        <v>-11486.25</v>
       </c>
       <c r="AA28" s="57"/>
       <c r="AB28" s="36"/>
       <c r="AC28" s="36" t="n">
         <f aca="false">-[2]Aug!$F$1+[2]Aug!$AK$1</f>
-        <v>-6840</v>
+        <v>-9057</v>
       </c>
       <c r="AD28" s="36" t="n">
         <f aca="false">[4]Aug!$AB$1</f>
@@ -23548,13 +23548,13 @@
       <c r="AJ28" s="54"/>
       <c r="AK28" s="36" t="n">
         <f aca="false">SUM(Z28:AJ28)</f>
-        <v>-19140</v>
+        <v>-20543.25</v>
       </c>
       <c r="AL28" s="57"/>
       <c r="AM28" s="36"/>
       <c r="AN28" s="36" t="n">
         <f aca="false">-[2]Sep!$F$1+[2]Sep!$AK$1</f>
-        <v>-22080</v>
+        <v>-8759.25</v>
       </c>
       <c r="AO28" s="36" t="n">
         <f aca="false">[4]Sep!$AB$1</f>
@@ -23577,13 +23577,13 @@
       <c r="AU28" s="54"/>
       <c r="AV28" s="36" t="n">
         <f aca="false">SUM(AK28:AU28)</f>
-        <v>-41220</v>
+        <v>-29302.5</v>
       </c>
       <c r="AW28" s="57"/>
       <c r="AX28" s="36"/>
       <c r="AY28" s="36" t="n">
         <f aca="false">-[2]Oct!$F$1+[2]Oct!$AK$1</f>
-        <v>-2480</v>
+        <v>-4705.25</v>
       </c>
       <c r="AZ28" s="36" t="n">
         <f aca="false">[4]Oct!$AB$1</f>
@@ -23606,13 +23606,13 @@
       <c r="BF28" s="54"/>
       <c r="BG28" s="36" t="n">
         <f aca="false">SUM(AV28:BF28)</f>
-        <v>-43700</v>
+        <v>-34007.75</v>
       </c>
       <c r="BH28" s="57"/>
       <c r="BI28" s="36"/>
       <c r="BJ28" s="36" t="n">
         <f aca="false">-[2]Nov!$F$1+[2]Nov!$AK$1</f>
-        <v>-7920</v>
+        <v>-4975</v>
       </c>
       <c r="BK28" s="36" t="n">
         <f aca="false">[4]Nov!$AB$1</f>
@@ -23635,13 +23635,13 @@
       <c r="BQ28" s="54"/>
       <c r="BR28" s="36" t="n">
         <f aca="false">SUM(BG28:BQ28)</f>
-        <v>-51620</v>
+        <v>-38982.75</v>
       </c>
       <c r="BS28" s="57"/>
       <c r="BT28" s="36"/>
       <c r="BU28" s="36" t="n">
         <f aca="false">-[2]Dec!$F$1+[2]Dec!$AK$1</f>
-        <v>-2184</v>
+        <v>-43005.75</v>
       </c>
       <c r="BV28" s="36" t="n">
         <f aca="false">[4]Dec!$AB$1</f>
@@ -23664,13 +23664,13 @@
       <c r="CB28" s="54"/>
       <c r="CC28" s="36" t="n">
         <f aca="false">SUM(BR28:CB28)</f>
-        <v>-53804</v>
+        <v>-81988.5</v>
       </c>
       <c r="CD28" s="57"/>
       <c r="CE28" s="36"/>
       <c r="CF28" s="36" t="n">
         <f aca="false">-[2]Jan!$F$1+[2]Jan!$AK$1</f>
-        <v>-2640</v>
+        <v>-6918</v>
       </c>
       <c r="CG28" s="36" t="n">
         <f aca="false">[4]Jan!$AB$1</f>
@@ -23693,13 +23693,13 @@
       <c r="CM28" s="54"/>
       <c r="CN28" s="36" t="n">
         <f aca="false">SUM(CC28:CM28)</f>
-        <v>-56444</v>
+        <v>-88906.5</v>
       </c>
       <c r="CO28" s="57"/>
       <c r="CP28" s="36"/>
       <c r="CQ28" s="36" t="n">
         <f aca="false">-[2]Feb!$F$1+[2]Feb!$AK$1</f>
-        <v>-7900</v>
+        <v>-3984.5</v>
       </c>
       <c r="CR28" s="36" t="n">
         <f aca="false">[4]Feb!$AB$1</f>
@@ -23722,13 +23722,13 @@
       <c r="CX28" s="54"/>
       <c r="CY28" s="36" t="n">
         <f aca="false">SUM(CN28:CX28)</f>
-        <v>-64344</v>
+        <v>-92891</v>
       </c>
       <c r="CZ28" s="57"/>
       <c r="DA28" s="36"/>
       <c r="DB28" s="36" t="n">
         <f aca="false">-[2]Mar!$F$1+[2]Mar!$AK$1</f>
-        <v>-3120</v>
+        <v>-9978.25</v>
       </c>
       <c r="DC28" s="36" t="n">
         <f aca="false">[4]Mar!$AB$1</f>
@@ -23751,13 +23751,13 @@
       <c r="DI28" s="54"/>
       <c r="DJ28" s="36" t="n">
         <f aca="false">SUM(CY28:DI28)</f>
-        <v>-67464</v>
+        <v>-102869.25</v>
       </c>
       <c r="DK28" s="57"/>
       <c r="DL28" s="36"/>
       <c r="DM28" s="36" t="n">
         <f aca="false">-[2]Apr!$F$1+[2]Apr!$AK$1</f>
-        <v>-2136</v>
+        <v>-4396.5</v>
       </c>
       <c r="DN28" s="36" t="n">
         <f aca="false">[4]Apr!$AB$1</f>
@@ -23780,13 +23780,13 @@
       <c r="DT28" s="54"/>
       <c r="DU28" s="36" t="n">
         <f aca="false">SUM(DJ28:DT28)</f>
-        <v>-69600</v>
+        <v>-107265.75</v>
       </c>
       <c r="DV28" s="57"/>
       <c r="DW28" s="36"/>
       <c r="DX28" s="36" t="n">
         <f aca="false">-[2]May!$F$1+[2]May!$AK$1</f>
-        <v>-4440</v>
+        <v>-3726.5</v>
       </c>
       <c r="DY28" s="36" t="n">
         <f aca="false">[4]May!$AB$1</f>
@@ -23809,7 +23809,7 @@
       <c r="EE28" s="54"/>
       <c r="EF28" s="36" t="n">
         <f aca="false">SUM(DU28:EE28)</f>
-        <v>-74040</v>
+        <v>-110992.25</v>
       </c>
       <c r="EG28" s="54"/>
       <c r="EH28" s="36" t="n">
@@ -23819,7 +23819,7 @@
       <c r="EI28" s="54"/>
       <c r="EJ28" s="36" t="n">
         <f aca="false">SUM(EF28:EH28)</f>
-        <v>-74040</v>
+        <v>-110992.25</v>
       </c>
       <c r="EK28" s="54"/>
     </row>
@@ -25162,7 +25162,7 @@
       <c r="E33" s="57"/>
       <c r="F33" s="36" t="n">
         <f aca="false">-[3]Jun!$G$1</f>
-        <v>-1366.66666666667</v>
+        <v>-2733.33333333333</v>
       </c>
       <c r="G33" s="36" t="n">
         <f aca="false">[2]Jun!$G$1</f>
@@ -25188,12 +25188,12 @@
       <c r="N33" s="57"/>
       <c r="O33" s="36" t="n">
         <f aca="false">SUM(D33:N33)</f>
-        <v>-1366.66666666667</v>
+        <v>-2733.33333333333</v>
       </c>
       <c r="P33" s="57"/>
       <c r="Q33" s="36" t="n">
         <f aca="false">-[3]Jul!$G$1</f>
-        <v>-1166.66666666667</v>
+        <v>-2653.33333333333</v>
       </c>
       <c r="R33" s="36" t="n">
         <f aca="false">[2]Jul!$G$1</f>
@@ -25220,12 +25220,12 @@
       <c r="Y33" s="54"/>
       <c r="Z33" s="36" t="n">
         <f aca="false">SUM(O33:Y33)</f>
-        <v>-2533.33333333334</v>
+        <v>-5386.66666666666</v>
       </c>
       <c r="AA33" s="57"/>
       <c r="AB33" s="36" t="n">
         <f aca="false">-[3]Aug!$G$1</f>
-        <v>-1566.66666666667</v>
+        <v>-3033.33333333333</v>
       </c>
       <c r="AC33" s="36" t="n">
         <f aca="false">[2]Aug!$G$1</f>
@@ -25252,12 +25252,12 @@
       <c r="AJ33" s="54"/>
       <c r="AK33" s="36" t="n">
         <f aca="false">SUM(Z33:AJ33)</f>
-        <v>-4100.00000000001</v>
+        <v>-8419.99999999999</v>
       </c>
       <c r="AL33" s="57"/>
       <c r="AM33" s="36" t="n">
         <f aca="false">-[3]Sep!$G$1</f>
-        <v>-1366.66666666667</v>
+        <v>-2793.33333333333</v>
       </c>
       <c r="AN33" s="36" t="n">
         <f aca="false">[2]Sep!$G$1</f>
@@ -25284,12 +25284,12 @@
       <c r="AU33" s="54"/>
       <c r="AV33" s="36" t="n">
         <f aca="false">SUM(AK33:AU33)</f>
-        <v>-5466.66666666668</v>
+        <v>-11213.3333333333</v>
       </c>
       <c r="AW33" s="57"/>
       <c r="AX33" s="36" t="n">
         <f aca="false">-[3]Oct!$G$1</f>
-        <v>-1583.33333333333</v>
+        <v>-3170</v>
       </c>
       <c r="AY33" s="36" t="n">
         <f aca="false">[2]Oct!$G$1</f>
@@ -25316,12 +25316,12 @@
       <c r="BF33" s="54"/>
       <c r="BG33" s="36" t="n">
         <f aca="false">SUM(AV33:BF33)</f>
-        <v>-7050.00000000001</v>
+        <v>-14383.3333333333</v>
       </c>
       <c r="BH33" s="57"/>
       <c r="BI33" s="36" t="n">
         <f aca="false">-[3]Nov!$G$1</f>
-        <v>-1266.66666666667</v>
+        <v>-2793.33333333333</v>
       </c>
       <c r="BJ33" s="36" t="n">
         <f aca="false">[2]Nov!$G$1</f>
@@ -25348,12 +25348,12 @@
       <c r="BQ33" s="54"/>
       <c r="BR33" s="36" t="n">
         <f aca="false">SUM(BG33:BQ33)</f>
-        <v>-8316.66666666668</v>
+        <v>-17176.6666666667</v>
       </c>
       <c r="BS33" s="57"/>
       <c r="BT33" s="36" t="n">
         <f aca="false">-[3]Dec!$G$1</f>
-        <v>-2400</v>
+        <v>-5593.33333333333</v>
       </c>
       <c r="BU33" s="36" t="n">
         <f aca="false">[2]Dec!$G$1</f>
@@ -25380,12 +25380,12 @@
       <c r="CB33" s="54"/>
       <c r="CC33" s="36" t="n">
         <f aca="false">SUM(BR33:CB33)</f>
-        <v>-10716.6666666667</v>
+        <v>-22770</v>
       </c>
       <c r="CD33" s="57"/>
       <c r="CE33" s="36" t="n">
         <f aca="false">-[3]Jan!$G$1</f>
-        <v>-2000</v>
+        <v>-3053.33333333333</v>
       </c>
       <c r="CF33" s="36" t="n">
         <f aca="false">[2]Jan!$G$1</f>
@@ -25412,12 +25412,12 @@
       <c r="CM33" s="54"/>
       <c r="CN33" s="36" t="n">
         <f aca="false">SUM(CC33:CM33)</f>
-        <v>-12716.6666666667</v>
+        <v>-25823.3333333333</v>
       </c>
       <c r="CO33" s="57"/>
       <c r="CP33" s="36" t="n">
         <f aca="false">-[3]Feb!$G$1</f>
-        <v>-1400</v>
+        <v>-2633.33333333333</v>
       </c>
       <c r="CQ33" s="36" t="n">
         <f aca="false">[2]Feb!$G$1</f>
@@ -25444,12 +25444,12 @@
       <c r="CX33" s="54"/>
       <c r="CY33" s="36" t="n">
         <f aca="false">SUM(CN33:CX33)</f>
-        <v>-14116.6666666667</v>
+        <v>-28456.6666666666</v>
       </c>
       <c r="CZ33" s="57"/>
       <c r="DA33" s="36" t="n">
         <f aca="false">-[3]Mar!$G$1</f>
-        <v>-1600</v>
+        <v>-3073.33333333333</v>
       </c>
       <c r="DB33" s="36" t="n">
         <f aca="false">[2]Mar!$G$1</f>
@@ -25476,12 +25476,12 @@
       <c r="DI33" s="54"/>
       <c r="DJ33" s="36" t="n">
         <f aca="false">SUM(CY33:DI33)</f>
-        <v>-15716.6666666667</v>
+        <v>-31530</v>
       </c>
       <c r="DK33" s="57"/>
       <c r="DL33" s="36" t="n">
         <f aca="false">-[3]Apr!$G$1</f>
-        <v>-1400</v>
+        <v>-2893.33333333333</v>
       </c>
       <c r="DM33" s="36" t="n">
         <f aca="false">[2]Apr!$G$1</f>
@@ -25508,12 +25508,12 @@
       <c r="DT33" s="54"/>
       <c r="DU33" s="36" t="n">
         <f aca="false">SUM(DJ33:DT33)</f>
-        <v>-17116.6666666667</v>
+        <v>-34423.3333333333</v>
       </c>
       <c r="DV33" s="57"/>
       <c r="DW33" s="36" t="n">
         <f aca="false">-[3]May!$G$1</f>
-        <v>-1460</v>
+        <v>-2393.33333333333</v>
       </c>
       <c r="DX33" s="36" t="n">
         <f aca="false">[2]May!$G$1</f>
@@ -25540,13 +25540,13 @@
       <c r="EE33" s="54"/>
       <c r="EF33" s="36" t="n">
         <f aca="false">SUM(DU33:EE33)</f>
-        <v>-18576.6666666667</v>
+        <v>-36816.6666666666</v>
       </c>
       <c r="EG33" s="54"/>
       <c r="EI33" s="54"/>
       <c r="EJ33" s="36" t="n">
         <f aca="false">SUM(EF33:EH33)</f>
-        <v>-18576.6666666667</v>
+        <v>-36816.6666666666</v>
       </c>
       <c r="EK33" s="54"/>
     </row>
@@ -26236,12 +26236,12 @@
       <c r="EC35" s="36"/>
       <c r="ED35" s="36" t="n">
         <f aca="false">-CorporationTax!K35</f>
-        <v>-7494.23333333333</v>
+        <v>-19492.3058333334</v>
       </c>
       <c r="EE35" s="54"/>
       <c r="EF35" s="36" t="n">
         <f aca="false">SUM(DU35:EE35)</f>
-        <v>-7494.23333333333</v>
+        <v>-19492.3058333334</v>
       </c>
       <c r="EG35" s="54"/>
       <c r="EH35" s="36" t="n">
@@ -26251,7 +26251,7 @@
       <c r="EI35" s="54"/>
       <c r="EJ35" s="36" t="n">
         <f aca="false">SUM(EF35:EH35)</f>
-        <v>-7494.23333333333</v>
+        <v>-19492.3058333334</v>
       </c>
       <c r="EK35" s="54"/>
     </row>
@@ -28029,12 +28029,12 @@
       <c r="EG43" s="54"/>
       <c r="EH43" s="36" t="n">
         <f aca="false">-'PubP&amp;L'!F54</f>
-        <v>-29549.1</v>
+        <v>-80098.7775000004</v>
       </c>
       <c r="EI43" s="54"/>
       <c r="EJ43" s="36" t="n">
         <f aca="false">SUM(EF43:EH43)</f>
-        <v>-29549.1</v>
+        <v>-80098.7775000004</v>
       </c>
       <c r="EK43" s="54"/>
     </row>
@@ -28663,18 +28663,18 @@
       <c r="EC47" s="36"/>
       <c r="ED47" s="36" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>7494.23333333333</v>
+        <v>19492.3058333334</v>
       </c>
       <c r="EE47" s="54"/>
       <c r="EF47" s="36" t="n">
         <f aca="false">SUM(DU47:EE47)</f>
-        <v>7494.23333333333</v>
+        <v>19492.3058333334</v>
       </c>
       <c r="EG47" s="54"/>
       <c r="EI47" s="54"/>
       <c r="EJ47" s="36" t="n">
         <f aca="false">SUM(EF47:EH47)</f>
-        <v>7494.23333333333</v>
+        <v>19492.3058333334</v>
       </c>
       <c r="EK47" s="54"/>
     </row>
@@ -29043,12 +29043,12 @@
       <c r="EG49" s="54"/>
       <c r="EH49" s="36" t="n">
         <f aca="false">'PubP&amp;L'!F54</f>
-        <v>29549.1</v>
+        <v>80098.7775000004</v>
       </c>
       <c r="EI49" s="54"/>
       <c r="EJ49" s="36" t="n">
         <f aca="false">SUM(EF49:EH49)</f>
-        <v>29549.1</v>
+        <v>80098.7775000004</v>
       </c>
       <c r="EK49" s="54"/>
     </row>
@@ -29470,7 +29470,7 @@
       <c r="E53" s="57"/>
       <c r="F53" s="36" t="n">
         <f aca="false">-[3]Jun!$O$1</f>
-        <v>-5833.33333333333</v>
+        <v>-11166.6666666667</v>
       </c>
       <c r="G53" s="36"/>
       <c r="H53" s="36"/>
@@ -29481,12 +29481,12 @@
       <c r="N53" s="57"/>
       <c r="O53" s="36" t="n">
         <f aca="false">SUM(D53:N53)</f>
-        <v>-5833.33333333333</v>
+        <v>-11166.6666666667</v>
       </c>
       <c r="P53" s="57"/>
       <c r="Q53" s="36" t="n">
         <f aca="false">-[3]Jul!$O$1</f>
-        <v>-5833.33333333333</v>
+        <v>-11466.6666666667</v>
       </c>
       <c r="R53" s="36"/>
       <c r="S53" s="36"/>
@@ -29498,12 +29498,12 @@
       <c r="Y53" s="54"/>
       <c r="Z53" s="36" t="n">
         <f aca="false">SUM(O53:Y53)</f>
-        <v>-11666.6666666667</v>
+        <v>-22633.3333333334</v>
       </c>
       <c r="AA53" s="57"/>
       <c r="AB53" s="36" t="n">
         <f aca="false">-[3]Aug!$O$1</f>
-        <v>-5833.33333333333</v>
+        <v>-12366.6666666667</v>
       </c>
       <c r="AC53" s="36"/>
       <c r="AD53" s="36"/>
@@ -29515,12 +29515,12 @@
       <c r="AJ53" s="54"/>
       <c r="AK53" s="36" t="n">
         <f aca="false">SUM(Z53:AJ53)</f>
-        <v>-17500</v>
+        <v>-35000.0000000001</v>
       </c>
       <c r="AL53" s="57"/>
       <c r="AM53" s="36" t="n">
         <f aca="false">-[3]Sep!$O$1</f>
-        <v>-5833.33333333333</v>
+        <v>-11466.6666666667</v>
       </c>
       <c r="AN53" s="36"/>
       <c r="AO53" s="36"/>
@@ -29532,12 +29532,12 @@
       <c r="AU53" s="54"/>
       <c r="AV53" s="36" t="n">
         <f aca="false">SUM(AK53:AU53)</f>
-        <v>-23333.3333333333</v>
+        <v>-46466.6666666668</v>
       </c>
       <c r="AW53" s="57"/>
       <c r="AX53" s="36" t="n">
         <f aca="false">-[3]Oct!$O$1</f>
-        <v>-5833.33333333333</v>
+        <v>-12966.6666666667</v>
       </c>
       <c r="AY53" s="36"/>
       <c r="AZ53" s="36"/>
@@ -29549,12 +29549,12 @@
       <c r="BF53" s="54"/>
       <c r="BG53" s="36" t="n">
         <f aca="false">SUM(AV53:BF53)</f>
-        <v>-29166.6666666667</v>
+        <v>-59433.3333333335</v>
       </c>
       <c r="BH53" s="57"/>
       <c r="BI53" s="36" t="n">
         <f aca="false">-[3]Nov!$O$1</f>
-        <v>-5833.33333333333</v>
+        <v>-10866.6666666667</v>
       </c>
       <c r="BJ53" s="36"/>
       <c r="BK53" s="36"/>
@@ -29566,12 +29566,12 @@
       <c r="BQ53" s="54"/>
       <c r="BR53" s="36" t="n">
         <f aca="false">SUM(BG53:BQ53)</f>
-        <v>-35000</v>
+        <v>-70300.0000000002</v>
       </c>
       <c r="BS53" s="57"/>
       <c r="BT53" s="36" t="n">
         <f aca="false">-[3]Dec!$O$1</f>
-        <v>-7000</v>
+        <v>-12966.6666666667</v>
       </c>
       <c r="BU53" s="36"/>
       <c r="BV53" s="36"/>
@@ -29583,12 +29583,12 @@
       <c r="CB53" s="54"/>
       <c r="CC53" s="36" t="n">
         <f aca="false">SUM(BR53:CB53)</f>
-        <v>-42000</v>
+        <v>-83266.6666666669</v>
       </c>
       <c r="CD53" s="57"/>
       <c r="CE53" s="36" t="n">
         <f aca="false">-[3]Jan!$O$1</f>
-        <v>-7000</v>
+        <v>-11466.6666666667</v>
       </c>
       <c r="CF53" s="36"/>
       <c r="CG53" s="36"/>
@@ -29600,12 +29600,12 @@
       <c r="CM53" s="54"/>
       <c r="CN53" s="36" t="n">
         <f aca="false">SUM(CC53:CM53)</f>
-        <v>-49000</v>
+        <v>-94733.3333333336</v>
       </c>
       <c r="CO53" s="57"/>
       <c r="CP53" s="36" t="n">
         <f aca="false">-[3]Feb!$O$1</f>
-        <v>-7000</v>
+        <v>-12366.6666666667</v>
       </c>
       <c r="CQ53" s="36"/>
       <c r="CR53" s="36"/>
@@ -29617,12 +29617,12 @@
       <c r="CX53" s="54"/>
       <c r="CY53" s="36" t="n">
         <f aca="false">SUM(CN53:CX53)</f>
-        <v>-56000</v>
+        <v>-107100</v>
       </c>
       <c r="CZ53" s="57"/>
       <c r="DA53" s="36" t="n">
         <f aca="false">-[3]Mar!$O$1</f>
-        <v>-7000</v>
+        <v>-11466.6666666667</v>
       </c>
       <c r="DB53" s="36"/>
       <c r="DC53" s="36"/>
@@ -29634,12 +29634,12 @@
       <c r="DI53" s="54"/>
       <c r="DJ53" s="36" t="n">
         <f aca="false">SUM(CY53:DI53)</f>
-        <v>-63000</v>
+        <v>-118566.666666667</v>
       </c>
       <c r="DK53" s="57"/>
       <c r="DL53" s="36" t="n">
         <f aca="false">-[3]Apr!$O$1</f>
-        <v>-7000</v>
+        <v>-12166.6666666667</v>
       </c>
       <c r="DM53" s="36"/>
       <c r="DN53" s="36"/>
@@ -29651,12 +29651,12 @@
       <c r="DT53" s="54"/>
       <c r="DU53" s="36" t="n">
         <f aca="false">SUM(DJ53:DT53)</f>
-        <v>-70000</v>
+        <v>-130733.333333334</v>
       </c>
       <c r="DV53" s="57"/>
       <c r="DW53" s="36" t="n">
         <f aca="false">-[3]May!$O$1</f>
-        <v>-7000</v>
+        <v>-10866.6666666667</v>
       </c>
       <c r="DX53" s="36"/>
       <c r="DY53" s="36"/>
@@ -29668,13 +29668,13 @@
       <c r="EE53" s="54"/>
       <c r="EF53" s="36" t="n">
         <f aca="false">SUM(DU53:EE53)</f>
-        <v>-77000</v>
+        <v>-141600</v>
       </c>
       <c r="EG53" s="54"/>
       <c r="EI53" s="54"/>
       <c r="EJ53" s="36" t="n">
         <f aca="false">SUM(EF53:EH53)</f>
-        <v>-77000</v>
+        <v>-141600</v>
       </c>
       <c r="EK53" s="54"/>
     </row>
@@ -29690,7 +29690,7 @@
       <c r="E54" s="57"/>
       <c r="F54" s="36" t="n">
         <f aca="false">-[3]Jun!$P$1</f>
-        <v>-1000</v>
+        <v>-1800</v>
       </c>
       <c r="G54" s="36"/>
       <c r="H54" s="36"/>
@@ -29701,12 +29701,12 @@
       <c r="N54" s="57"/>
       <c r="O54" s="36" t="n">
         <f aca="false">SUM(D54:N54)</f>
-        <v>-1000</v>
+        <v>-1800</v>
       </c>
       <c r="P54" s="57"/>
       <c r="Q54" s="36" t="n">
         <f aca="false">-[3]Jul!$P$1</f>
-        <v>-0</v>
+        <v>-800</v>
       </c>
       <c r="R54" s="36"/>
       <c r="S54" s="36"/>
@@ -29718,12 +29718,12 @@
       <c r="Y54" s="54"/>
       <c r="Z54" s="36" t="n">
         <f aca="false">SUM(O54:Y54)</f>
-        <v>-1000</v>
+        <v>-2600</v>
       </c>
       <c r="AA54" s="57"/>
       <c r="AB54" s="36" t="n">
         <f aca="false">-[3]Aug!$P$1</f>
-        <v>-0</v>
+        <v>-800</v>
       </c>
       <c r="AC54" s="36"/>
       <c r="AD54" s="36"/>
@@ -29735,12 +29735,12 @@
       <c r="AJ54" s="54"/>
       <c r="AK54" s="36" t="n">
         <f aca="false">SUM(Z54:AJ54)</f>
-        <v>-1000</v>
+        <v>-3400</v>
       </c>
       <c r="AL54" s="57"/>
       <c r="AM54" s="36" t="n">
         <f aca="false">-[3]Sep!$P$1</f>
-        <v>-1000</v>
+        <v>-1800</v>
       </c>
       <c r="AN54" s="36"/>
       <c r="AO54" s="36"/>
@@ -29752,12 +29752,12 @@
       <c r="AU54" s="54"/>
       <c r="AV54" s="36" t="n">
         <f aca="false">SUM(AK54:AU54)</f>
-        <v>-2000</v>
+        <v>-5200</v>
       </c>
       <c r="AW54" s="57"/>
       <c r="AX54" s="36" t="n">
         <f aca="false">-[3]Oct!$P$1</f>
-        <v>-0</v>
+        <v>-800</v>
       </c>
       <c r="AY54" s="36"/>
       <c r="AZ54" s="36"/>
@@ -29769,12 +29769,12 @@
       <c r="BF54" s="54"/>
       <c r="BG54" s="36" t="n">
         <f aca="false">SUM(AV54:BF54)</f>
-        <v>-2000</v>
+        <v>-6000</v>
       </c>
       <c r="BH54" s="57"/>
       <c r="BI54" s="36" t="n">
         <f aca="false">-[3]Nov!$P$1</f>
-        <v>-0</v>
+        <v>-800</v>
       </c>
       <c r="BJ54" s="36"/>
       <c r="BK54" s="36"/>
@@ -29786,12 +29786,12 @@
       <c r="BQ54" s="54"/>
       <c r="BR54" s="36" t="n">
         <f aca="false">SUM(BG54:BQ54)</f>
-        <v>-2000</v>
+        <v>-6800</v>
       </c>
       <c r="BS54" s="57"/>
       <c r="BT54" s="36" t="n">
         <f aca="false">-[3]Dec!$P$1</f>
-        <v>-1000</v>
+        <v>-1800</v>
       </c>
       <c r="BU54" s="36"/>
       <c r="BV54" s="36"/>
@@ -29803,12 +29803,12 @@
       <c r="CB54" s="54"/>
       <c r="CC54" s="36" t="n">
         <f aca="false">SUM(BR54:CB54)</f>
-        <v>-3000</v>
+        <v>-8600</v>
       </c>
       <c r="CD54" s="57"/>
       <c r="CE54" s="36" t="n">
         <f aca="false">-[3]Jan!$P$1</f>
-        <v>-0</v>
+        <v>-800</v>
       </c>
       <c r="CF54" s="36"/>
       <c r="CG54" s="36"/>
@@ -29820,12 +29820,12 @@
       <c r="CM54" s="54"/>
       <c r="CN54" s="36" t="n">
         <f aca="false">SUM(CC54:CM54)</f>
-        <v>-3000</v>
+        <v>-9400</v>
       </c>
       <c r="CO54" s="57"/>
       <c r="CP54" s="36" t="n">
         <f aca="false">-[3]Feb!$P$1</f>
-        <v>-0</v>
+        <v>-800</v>
       </c>
       <c r="CQ54" s="36"/>
       <c r="CR54" s="36"/>
@@ -29837,12 +29837,12 @@
       <c r="CX54" s="54"/>
       <c r="CY54" s="36" t="n">
         <f aca="false">SUM(CN54:CX54)</f>
-        <v>-3000</v>
+        <v>-10200</v>
       </c>
       <c r="CZ54" s="57"/>
       <c r="DA54" s="36" t="n">
         <f aca="false">-[3]Mar!$P$1</f>
-        <v>-1000</v>
+        <v>-1800</v>
       </c>
       <c r="DB54" s="36"/>
       <c r="DC54" s="36"/>
@@ -29854,12 +29854,12 @@
       <c r="DI54" s="54"/>
       <c r="DJ54" s="36" t="n">
         <f aca="false">SUM(CY54:DI54)</f>
-        <v>-4000</v>
+        <v>-12000</v>
       </c>
       <c r="DK54" s="57"/>
       <c r="DL54" s="36" t="n">
         <f aca="false">-[3]Apr!$P$1</f>
-        <v>-0</v>
+        <v>-800</v>
       </c>
       <c r="DM54" s="36"/>
       <c r="DN54" s="36"/>
@@ -29871,12 +29871,12 @@
       <c r="DT54" s="54"/>
       <c r="DU54" s="36" t="n">
         <f aca="false">SUM(DJ54:DT54)</f>
-        <v>-4000</v>
+        <v>-12800</v>
       </c>
       <c r="DV54" s="57"/>
       <c r="DW54" s="36" t="n">
         <f aca="false">-[3]May!$P$1</f>
-        <v>-0</v>
+        <v>-800</v>
       </c>
       <c r="DX54" s="36"/>
       <c r="DY54" s="36"/>
@@ -29888,13 +29888,13 @@
       <c r="EE54" s="54"/>
       <c r="EF54" s="36" t="n">
         <f aca="false">SUM(DU54:EE54)</f>
-        <v>-4000</v>
+        <v>-13600</v>
       </c>
       <c r="EG54" s="54"/>
       <c r="EI54" s="54"/>
       <c r="EJ54" s="36" t="n">
         <f aca="false">SUM(EF54:EH54)</f>
-        <v>-4000</v>
+        <v>-13600</v>
       </c>
       <c r="EK54" s="54"/>
     </row>
@@ -29926,7 +29926,7 @@
       <c r="P55" s="57"/>
       <c r="Q55" s="36" t="n">
         <f aca="false">-[3]Jul!$Q$1</f>
-        <v>-0</v>
+        <v>-1000</v>
       </c>
       <c r="R55" s="36"/>
       <c r="S55" s="36"/>
@@ -29938,7 +29938,7 @@
       <c r="Y55" s="54"/>
       <c r="Z55" s="36" t="n">
         <f aca="false">SUM(O55:Y55)</f>
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AA55" s="57"/>
       <c r="AB55" s="36" t="n">
@@ -29955,7 +29955,7 @@
       <c r="AJ55" s="54"/>
       <c r="AK55" s="36" t="n">
         <f aca="false">SUM(Z55:AJ55)</f>
-        <v>-2000</v>
+        <v>-3000</v>
       </c>
       <c r="AL55" s="57"/>
       <c r="AM55" s="36" t="n">
@@ -29972,7 +29972,7 @@
       <c r="AU55" s="54"/>
       <c r="AV55" s="36" t="n">
         <f aca="false">SUM(AK55:AU55)</f>
-        <v>-2000</v>
+        <v>-3000</v>
       </c>
       <c r="AW55" s="57"/>
       <c r="AX55" s="36" t="n">
@@ -29989,12 +29989,12 @@
       <c r="BF55" s="54"/>
       <c r="BG55" s="36" t="n">
         <f aca="false">SUM(AV55:BF55)</f>
-        <v>-2000</v>
+        <v>-3000</v>
       </c>
       <c r="BH55" s="57"/>
       <c r="BI55" s="36" t="n">
         <f aca="false">-[3]Nov!$Q$1</f>
-        <v>-0</v>
+        <v>-1800</v>
       </c>
       <c r="BJ55" s="36"/>
       <c r="BK55" s="36"/>
@@ -30006,7 +30006,7 @@
       <c r="BQ55" s="54"/>
       <c r="BR55" s="36" t="n">
         <f aca="false">SUM(BG55:BQ55)</f>
-        <v>-2000</v>
+        <v>-4800</v>
       </c>
       <c r="BS55" s="57"/>
       <c r="BT55" s="36" t="n">
@@ -30023,7 +30023,7 @@
       <c r="CB55" s="54"/>
       <c r="CC55" s="36" t="n">
         <f aca="false">SUM(BR55:CB55)</f>
-        <v>-2000</v>
+        <v>-4800</v>
       </c>
       <c r="CD55" s="57"/>
       <c r="CE55" s="36" t="n">
@@ -30040,7 +30040,7 @@
       <c r="CM55" s="54"/>
       <c r="CN55" s="36" t="n">
         <f aca="false">SUM(CC55:CM55)</f>
-        <v>-5000</v>
+        <v>-7800</v>
       </c>
       <c r="CO55" s="57"/>
       <c r="CP55" s="36" t="n">
@@ -30057,12 +30057,12 @@
       <c r="CX55" s="54"/>
       <c r="CY55" s="36" t="n">
         <f aca="false">SUM(CN55:CX55)</f>
-        <v>-5000</v>
+        <v>-7800</v>
       </c>
       <c r="CZ55" s="57"/>
       <c r="DA55" s="36" t="n">
         <f aca="false">-[3]Mar!$Q$1</f>
-        <v>-0</v>
+        <v>-1000</v>
       </c>
       <c r="DB55" s="36"/>
       <c r="DC55" s="36"/>
@@ -30074,12 +30074,12 @@
       <c r="DI55" s="54"/>
       <c r="DJ55" s="36" t="n">
         <f aca="false">SUM(CY55:DI55)</f>
-        <v>-5000</v>
+        <v>-8800</v>
       </c>
       <c r="DK55" s="57"/>
       <c r="DL55" s="36" t="n">
         <f aca="false">-[3]Apr!$Q$1</f>
-        <v>-0</v>
+        <v>-1500</v>
       </c>
       <c r="DM55" s="36"/>
       <c r="DN55" s="36"/>
@@ -30091,7 +30091,7 @@
       <c r="DT55" s="54"/>
       <c r="DU55" s="36" t="n">
         <f aca="false">SUM(DJ55:DT55)</f>
-        <v>-5000</v>
+        <v>-10300</v>
       </c>
       <c r="DV55" s="57"/>
       <c r="DW55" s="36" t="n">
@@ -30108,13 +30108,13 @@
       <c r="EE55" s="54"/>
       <c r="EF55" s="36" t="n">
         <f aca="false">SUM(DU55:EE55)</f>
-        <v>-5000</v>
+        <v>-10300</v>
       </c>
       <c r="EG55" s="54"/>
       <c r="EI55" s="54"/>
       <c r="EJ55" s="36" t="n">
         <f aca="false">SUM(EF55:EH55)</f>
-        <v>-5000</v>
+        <v>-10300</v>
       </c>
       <c r="EK55" s="54"/>
     </row>
@@ -30130,7 +30130,7 @@
       <c r="E56" s="57"/>
       <c r="F56" s="36" t="n">
         <f aca="false">-[3]Jun!$R$1</f>
-        <v>-0</v>
+        <v>-700</v>
       </c>
       <c r="G56" s="36"/>
       <c r="H56" s="36"/>
@@ -30141,7 +30141,7 @@
       <c r="N56" s="57"/>
       <c r="O56" s="36" t="n">
         <f aca="false">SUM(D56:N56)</f>
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="P56" s="57"/>
       <c r="Q56" s="36" t="n">
@@ -30158,7 +30158,7 @@
       <c r="Y56" s="54"/>
       <c r="Z56" s="36" t="n">
         <f aca="false">SUM(O56:Y56)</f>
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="AA56" s="57"/>
       <c r="AB56" s="36" t="n">
@@ -30175,12 +30175,12 @@
       <c r="AJ56" s="54"/>
       <c r="AK56" s="36" t="n">
         <f aca="false">SUM(Z56:AJ56)</f>
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="AL56" s="57"/>
       <c r="AM56" s="36" t="n">
         <f aca="false">-[3]Sep!$R$1</f>
-        <v>-0</v>
+        <v>-700</v>
       </c>
       <c r="AN56" s="36"/>
       <c r="AO56" s="36"/>
@@ -30192,7 +30192,7 @@
       <c r="AU56" s="54"/>
       <c r="AV56" s="36" t="n">
         <f aca="false">SUM(AK56:AU56)</f>
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="AW56" s="57"/>
       <c r="AX56" s="36" t="n">
@@ -30209,7 +30209,7 @@
       <c r="BF56" s="54"/>
       <c r="BG56" s="36" t="n">
         <f aca="false">SUM(AV56:BF56)</f>
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="BH56" s="57"/>
       <c r="BI56" s="36" t="n">
@@ -30226,12 +30226,12 @@
       <c r="BQ56" s="54"/>
       <c r="BR56" s="36" t="n">
         <f aca="false">SUM(BG56:BQ56)</f>
-        <v>-500</v>
+        <v>-1900</v>
       </c>
       <c r="BS56" s="57"/>
       <c r="BT56" s="36" t="n">
         <f aca="false">-[3]Dec!$R$1</f>
-        <v>-0</v>
+        <v>-700</v>
       </c>
       <c r="BU56" s="36"/>
       <c r="BV56" s="36"/>
@@ -30243,7 +30243,7 @@
       <c r="CB56" s="54"/>
       <c r="CC56" s="36" t="n">
         <f aca="false">SUM(BR56:CB56)</f>
-        <v>-500</v>
+        <v>-2600</v>
       </c>
       <c r="CD56" s="57"/>
       <c r="CE56" s="36" t="n">
@@ -30260,7 +30260,7 @@
       <c r="CM56" s="54"/>
       <c r="CN56" s="36" t="n">
         <f aca="false">SUM(CC56:CM56)</f>
-        <v>-500</v>
+        <v>-2600</v>
       </c>
       <c r="CO56" s="57"/>
       <c r="CP56" s="36" t="n">
@@ -30277,12 +30277,12 @@
       <c r="CX56" s="54"/>
       <c r="CY56" s="36" t="n">
         <f aca="false">SUM(CN56:CX56)</f>
-        <v>-500</v>
+        <v>-2600</v>
       </c>
       <c r="CZ56" s="57"/>
       <c r="DA56" s="36" t="n">
         <f aca="false">-[3]Mar!$R$1</f>
-        <v>-0</v>
+        <v>-1100</v>
       </c>
       <c r="DB56" s="36"/>
       <c r="DC56" s="36"/>
@@ -30294,7 +30294,7 @@
       <c r="DI56" s="54"/>
       <c r="DJ56" s="36" t="n">
         <f aca="false">SUM(CY56:DI56)</f>
-        <v>-500</v>
+        <v>-3700</v>
       </c>
       <c r="DK56" s="57"/>
       <c r="DL56" s="36" t="n">
@@ -30311,7 +30311,7 @@
       <c r="DT56" s="54"/>
       <c r="DU56" s="36" t="n">
         <f aca="false">SUM(DJ56:DT56)</f>
-        <v>-500</v>
+        <v>-3700</v>
       </c>
       <c r="DV56" s="57"/>
       <c r="DW56" s="36" t="n">
@@ -30328,13 +30328,13 @@
       <c r="EE56" s="54"/>
       <c r="EF56" s="36" t="n">
         <f aca="false">SUM(DU56:EE56)</f>
-        <v>-500</v>
+        <v>-3700</v>
       </c>
       <c r="EG56" s="54"/>
       <c r="EI56" s="54"/>
       <c r="EJ56" s="36" t="n">
         <f aca="false">SUM(EF56:EH56)</f>
-        <v>-500</v>
+        <v>-3700</v>
       </c>
       <c r="EK56" s="54"/>
     </row>
@@ -31059,7 +31059,7 @@
       <c r="Q60" s="36"/>
       <c r="R60" s="36" t="n">
         <f aca="false">[2]Jul!$O$1</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="S60" s="36"/>
       <c r="T60" s="36"/>
@@ -31073,13 +31073,13 @@
       <c r="Y60" s="54"/>
       <c r="Z60" s="36" t="n">
         <f aca="false">SUM(O60:Y60)</f>
-        <v>600</v>
+        <v>1320</v>
       </c>
       <c r="AA60" s="57"/>
       <c r="AB60" s="36"/>
       <c r="AC60" s="36" t="n">
         <f aca="false">[2]Aug!$O$1</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="AD60" s="36"/>
       <c r="AE60" s="36"/>
@@ -31093,7 +31093,7 @@
       <c r="AJ60" s="54"/>
       <c r="AK60" s="36" t="n">
         <f aca="false">SUM(Z60:AJ60)</f>
-        <v>600</v>
+        <v>1680</v>
       </c>
       <c r="AL60" s="57"/>
       <c r="AM60" s="36"/>
@@ -31113,13 +31113,13 @@
       <c r="AU60" s="54"/>
       <c r="AV60" s="36" t="n">
         <f aca="false">SUM(AK60:AU60)</f>
-        <v>1320</v>
+        <v>2400</v>
       </c>
       <c r="AW60" s="57"/>
       <c r="AX60" s="36"/>
       <c r="AY60" s="36" t="n">
         <f aca="false">[2]Oct!$O$1</f>
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="AZ60" s="36"/>
       <c r="BA60" s="36"/>
@@ -31133,13 +31133,13 @@
       <c r="BF60" s="54"/>
       <c r="BG60" s="36" t="n">
         <f aca="false">SUM(AV60:BF60)</f>
-        <v>1320</v>
+        <v>2940</v>
       </c>
       <c r="BH60" s="57"/>
       <c r="BI60" s="36"/>
       <c r="BJ60" s="36" t="n">
         <f aca="false">[2]Nov!$O$1</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="BK60" s="36"/>
       <c r="BL60" s="36"/>
@@ -31153,7 +31153,7 @@
       <c r="BQ60" s="54"/>
       <c r="BR60" s="36" t="n">
         <f aca="false">SUM(BG60:BQ60)</f>
-        <v>1320</v>
+        <v>3180</v>
       </c>
       <c r="BS60" s="57"/>
       <c r="BT60" s="36"/>
@@ -31173,13 +31173,13 @@
       <c r="CB60" s="54"/>
       <c r="CC60" s="36" t="n">
         <f aca="false">SUM(BR60:CB60)</f>
-        <v>1800</v>
+        <v>3660</v>
       </c>
       <c r="CD60" s="57"/>
       <c r="CE60" s="36"/>
       <c r="CF60" s="36" t="n">
         <f aca="false">[2]Jan!$O$1</f>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="CG60" s="36"/>
       <c r="CH60" s="36"/>
@@ -31193,13 +31193,13 @@
       <c r="CM60" s="54"/>
       <c r="CN60" s="36" t="n">
         <f aca="false">SUM(CC60:CM60)</f>
-        <v>1800</v>
+        <v>4500</v>
       </c>
       <c r="CO60" s="57"/>
       <c r="CP60" s="36"/>
       <c r="CQ60" s="36" t="n">
         <f aca="false">[2]Feb!$O$1</f>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="CR60" s="36"/>
       <c r="CS60" s="36"/>
@@ -31213,7 +31213,7 @@
       <c r="CX60" s="54"/>
       <c r="CY60" s="36" t="n">
         <f aca="false">SUM(CN60:CX60)</f>
-        <v>1800</v>
+        <v>4980</v>
       </c>
       <c r="CZ60" s="57"/>
       <c r="DA60" s="36"/>
@@ -31233,13 +31233,13 @@
       <c r="DI60" s="54"/>
       <c r="DJ60" s="36" t="n">
         <f aca="false">SUM(CY60:DI60)</f>
-        <v>2400</v>
+        <v>5580</v>
       </c>
       <c r="DK60" s="57"/>
       <c r="DL60" s="36"/>
       <c r="DM60" s="36" t="n">
         <f aca="false">[2]Apr!$O$1</f>
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="DN60" s="36"/>
       <c r="DO60" s="36"/>
@@ -31253,13 +31253,13 @@
       <c r="DT60" s="54"/>
       <c r="DU60" s="36" t="n">
         <f aca="false">SUM(DJ60:DT60)</f>
-        <v>2400</v>
+        <v>6240</v>
       </c>
       <c r="DV60" s="57"/>
       <c r="DW60" s="36"/>
       <c r="DX60" s="36" t="n">
         <f aca="false">[2]May!$O$1</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="DY60" s="36"/>
       <c r="DZ60" s="36"/>
@@ -31273,13 +31273,13 @@
       <c r="EE60" s="54"/>
       <c r="EF60" s="36" t="n">
         <f aca="false">SUM(DU60:EE60)</f>
-        <v>2400</v>
+        <v>6540</v>
       </c>
       <c r="EG60" s="54"/>
       <c r="EI60" s="54"/>
       <c r="EJ60" s="36" t="n">
         <f aca="false">SUM(EF60:EH60)</f>
-        <v>2400</v>
+        <v>6540</v>
       </c>
       <c r="EK60" s="54"/>
     </row>
@@ -31329,7 +31329,7 @@
       <c r="AB61" s="36"/>
       <c r="AC61" s="36" t="n">
         <f aca="false">[2]Aug!$P$1</f>
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="AD61" s="36"/>
       <c r="AE61" s="36"/>
@@ -31340,7 +31340,7 @@
       <c r="AJ61" s="54"/>
       <c r="AK61" s="36" t="n">
         <f aca="false">SUM(Z61:AJ61)</f>
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="AL61" s="57"/>
       <c r="AM61" s="36"/>
@@ -31357,7 +31357,7 @@
       <c r="AU61" s="54"/>
       <c r="AV61" s="36" t="n">
         <f aca="false">SUM(AK61:AU61)</f>
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="AW61" s="57"/>
       <c r="AX61" s="36"/>
@@ -31374,13 +31374,13 @@
       <c r="BF61" s="54"/>
       <c r="BG61" s="36" t="n">
         <f aca="false">SUM(AV61:BF61)</f>
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="BH61" s="57"/>
       <c r="BI61" s="36"/>
       <c r="BJ61" s="36" t="n">
         <f aca="false">[2]Nov!$P$1</f>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="BK61" s="36"/>
       <c r="BL61" s="36"/>
@@ -31391,7 +31391,7 @@
       <c r="BQ61" s="54"/>
       <c r="BR61" s="36" t="n">
         <f aca="false">SUM(BG61:BQ61)</f>
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="BS61" s="57"/>
       <c r="BT61" s="36"/>
@@ -31408,13 +31408,13 @@
       <c r="CB61" s="54"/>
       <c r="CC61" s="36" t="n">
         <f aca="false">SUM(BR61:CB61)</f>
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="CD61" s="57"/>
       <c r="CE61" s="36"/>
       <c r="CF61" s="36" t="n">
         <f aca="false">[2]Jan!$P$1</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="CG61" s="36"/>
       <c r="CH61" s="36"/>
@@ -31425,7 +31425,7 @@
       <c r="CM61" s="54"/>
       <c r="CN61" s="36" t="n">
         <f aca="false">SUM(CC61:CM61)</f>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="CO61" s="57"/>
       <c r="CP61" s="36"/>
@@ -31442,7 +31442,7 @@
       <c r="CX61" s="54"/>
       <c r="CY61" s="36" t="n">
         <f aca="false">SUM(CN61:CX61)</f>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="CZ61" s="57"/>
       <c r="DA61" s="36"/>
@@ -31459,7 +31459,7 @@
       <c r="DI61" s="54"/>
       <c r="DJ61" s="36" t="n">
         <f aca="false">SUM(CY61:DI61)</f>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="DK61" s="57"/>
       <c r="DL61" s="36"/>
@@ -31476,7 +31476,7 @@
       <c r="DT61" s="54"/>
       <c r="DU61" s="36" t="n">
         <f aca="false">SUM(DJ61:DT61)</f>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="DV61" s="57"/>
       <c r="DW61" s="36"/>
@@ -31493,13 +31493,13 @@
       <c r="EE61" s="54"/>
       <c r="EF61" s="36" t="n">
         <f aca="false">SUM(DU61:EE61)</f>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="EG61" s="54"/>
       <c r="EI61" s="54"/>
       <c r="EJ61" s="36" t="n">
         <f aca="false">SUM(EF61:EH61)</f>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="EK61" s="54"/>
     </row>
@@ -31516,7 +31516,7 @@
       <c r="F62" s="36"/>
       <c r="G62" s="36" t="n">
         <f aca="false">[2]Jun!$Q$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="H62" s="36"/>
       <c r="I62" s="36"/>
@@ -31526,13 +31526,13 @@
       <c r="N62" s="57"/>
       <c r="O62" s="36" t="n">
         <f aca="false">SUM(D62:N62)</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="P62" s="57"/>
       <c r="Q62" s="36"/>
       <c r="R62" s="36" t="n">
         <f aca="false">[2]Jul!$Q$1</f>
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="S62" s="36"/>
       <c r="T62" s="36"/>
@@ -31543,13 +31543,13 @@
       <c r="Y62" s="54"/>
       <c r="Z62" s="36" t="n">
         <f aca="false">SUM(O62:Y62)</f>
-        <v>360</v>
+        <v>534</v>
       </c>
       <c r="AA62" s="57"/>
       <c r="AB62" s="36"/>
       <c r="AC62" s="36" t="n">
         <f aca="false">[2]Aug!$Q$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="AD62" s="36"/>
       <c r="AE62" s="36"/>
@@ -31560,13 +31560,13 @@
       <c r="AJ62" s="54"/>
       <c r="AK62" s="36" t="n">
         <f aca="false">SUM(Z62:AJ62)</f>
-        <v>360</v>
+        <v>819</v>
       </c>
       <c r="AL62" s="57"/>
       <c r="AM62" s="36"/>
       <c r="AN62" s="36" t="n">
         <f aca="false">[2]Sep!$Q$1</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="AO62" s="36"/>
       <c r="AP62" s="36"/>
@@ -31577,13 +31577,13 @@
       <c r="AU62" s="54"/>
       <c r="AV62" s="36" t="n">
         <f aca="false">SUM(AK62:AU62)</f>
-        <v>360</v>
+        <v>1068</v>
       </c>
       <c r="AW62" s="57"/>
       <c r="AX62" s="36"/>
       <c r="AY62" s="36" t="n">
         <f aca="false">[2]Oct!$Q$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="AZ62" s="36"/>
       <c r="BA62" s="36"/>
@@ -31594,13 +31594,13 @@
       <c r="BF62" s="54"/>
       <c r="BG62" s="36" t="n">
         <f aca="false">SUM(AV62:BF62)</f>
-        <v>360</v>
+        <v>1353</v>
       </c>
       <c r="BH62" s="57"/>
       <c r="BI62" s="36"/>
       <c r="BJ62" s="36" t="n">
         <f aca="false">[2]Nov!$Q$1</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="BK62" s="36"/>
       <c r="BL62" s="36"/>
@@ -31611,13 +31611,13 @@
       <c r="BQ62" s="54"/>
       <c r="BR62" s="36" t="n">
         <f aca="false">SUM(BG62:BQ62)</f>
-        <v>360</v>
+        <v>1602</v>
       </c>
       <c r="BS62" s="57"/>
       <c r="BT62" s="36"/>
       <c r="BU62" s="36" t="n">
         <f aca="false">[2]Dec!$Q$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="BV62" s="36"/>
       <c r="BW62" s="36"/>
@@ -31628,13 +31628,13 @@
       <c r="CB62" s="54"/>
       <c r="CC62" s="36" t="n">
         <f aca="false">SUM(BR62:CB62)</f>
-        <v>360</v>
+        <v>1887</v>
       </c>
       <c r="CD62" s="57"/>
       <c r="CE62" s="36"/>
       <c r="CF62" s="36" t="n">
         <f aca="false">[2]Jan!$Q$1</f>
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="CG62" s="36"/>
       <c r="CH62" s="36"/>
@@ -31645,13 +31645,13 @@
       <c r="CM62" s="54"/>
       <c r="CN62" s="36" t="n">
         <f aca="false">SUM(CC62:CM62)</f>
-        <v>720</v>
+        <v>2136</v>
       </c>
       <c r="CO62" s="57"/>
       <c r="CP62" s="36"/>
       <c r="CQ62" s="36" t="n">
         <f aca="false">[2]Feb!$Q$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="CR62" s="36"/>
       <c r="CS62" s="36"/>
@@ -31662,13 +31662,13 @@
       <c r="CX62" s="54"/>
       <c r="CY62" s="36" t="n">
         <f aca="false">SUM(CN62:CX62)</f>
-        <v>720</v>
+        <v>2421</v>
       </c>
       <c r="CZ62" s="57"/>
       <c r="DA62" s="36"/>
       <c r="DB62" s="36" t="n">
         <f aca="false">[2]Mar!$Q$1</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="DC62" s="36"/>
       <c r="DD62" s="36"/>
@@ -31679,13 +31679,13 @@
       <c r="DI62" s="54"/>
       <c r="DJ62" s="36" t="n">
         <f aca="false">SUM(CY62:DI62)</f>
-        <v>720</v>
+        <v>2670</v>
       </c>
       <c r="DK62" s="57"/>
       <c r="DL62" s="36"/>
       <c r="DM62" s="36" t="n">
         <f aca="false">[2]Apr!$Q$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="DN62" s="36"/>
       <c r="DO62" s="36"/>
@@ -31696,13 +31696,13 @@
       <c r="DT62" s="54"/>
       <c r="DU62" s="36" t="n">
         <f aca="false">SUM(DJ62:DT62)</f>
-        <v>720</v>
+        <v>2955</v>
       </c>
       <c r="DV62" s="57"/>
       <c r="DW62" s="36"/>
       <c r="DX62" s="36" t="n">
         <f aca="false">[2]May!$Q$1</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="DY62" s="36"/>
       <c r="DZ62" s="36"/>
@@ -31713,13 +31713,13 @@
       <c r="EE62" s="54"/>
       <c r="EF62" s="36" t="n">
         <f aca="false">SUM(DU62:EE62)</f>
-        <v>720</v>
+        <v>3204</v>
       </c>
       <c r="EG62" s="54"/>
       <c r="EI62" s="54"/>
       <c r="EJ62" s="36" t="n">
         <f aca="false">SUM(EF62:EH62)</f>
-        <v>720</v>
+        <v>3204</v>
       </c>
       <c r="EK62" s="54"/>
     </row>
@@ -32471,7 +32471,7 @@
       <c r="CP66" s="36"/>
       <c r="CQ66" s="36" t="n">
         <f aca="false">[2]Feb!$R$1</f>
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="CR66" s="36"/>
       <c r="CS66" s="36"/>
@@ -32485,13 +32485,13 @@
       <c r="CX66" s="54"/>
       <c r="CY66" s="36" t="n">
         <f aca="false">SUM(CN66:CX66)</f>
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="CZ66" s="57"/>
       <c r="DA66" s="36"/>
       <c r="DB66" s="36" t="n">
         <f aca="false">[2]Mar!$R$1</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="DC66" s="36"/>
       <c r="DD66" s="36"/>
@@ -33090,7 +33090,7 @@
       <c r="BI69" s="36"/>
       <c r="BJ69" s="36" t="n">
         <f aca="false">[2]Nov!$U$1</f>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="BK69" s="36"/>
       <c r="BL69" s="36"/>
@@ -33101,7 +33101,7 @@
       <c r="BQ69" s="54"/>
       <c r="BR69" s="36" t="n">
         <f aca="false">SUM(BG69:BQ69)</f>
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="BS69" s="57"/>
       <c r="BT69" s="36"/>
@@ -33118,7 +33118,7 @@
       <c r="CB69" s="54"/>
       <c r="CC69" s="36" t="n">
         <f aca="false">SUM(BR69:CB69)</f>
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="CD69" s="57"/>
       <c r="CE69" s="36"/>
@@ -33135,13 +33135,13 @@
       <c r="CM69" s="54"/>
       <c r="CN69" s="36" t="n">
         <f aca="false">SUM(CC69:CM69)</f>
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="CO69" s="57"/>
       <c r="CP69" s="36"/>
       <c r="CQ69" s="36" t="n">
         <f aca="false">[2]Feb!$U$1</f>
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="CR69" s="36"/>
       <c r="CS69" s="36"/>
@@ -33152,13 +33152,13 @@
       <c r="CX69" s="54"/>
       <c r="CY69" s="36" t="n">
         <f aca="false">SUM(CN69:CX69)</f>
-        <v>720</v>
+        <v>1080</v>
       </c>
       <c r="CZ69" s="57"/>
       <c r="DA69" s="36"/>
       <c r="DB69" s="36" t="n">
         <f aca="false">[2]Mar!$U$1</f>
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="DC69" s="36"/>
       <c r="DD69" s="36"/>
@@ -33242,7 +33242,7 @@
       <c r="Q70" s="36"/>
       <c r="R70" s="36" t="n">
         <f aca="false">[2]Jul!$V$1</f>
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="S70" s="36"/>
       <c r="T70" s="36"/>
@@ -33253,7 +33253,7 @@
       <c r="Y70" s="54"/>
       <c r="Z70" s="36" t="n">
         <f aca="false">SUM(O70:Y70)</f>
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="AA70" s="57"/>
       <c r="AB70" s="36"/>
@@ -33270,13 +33270,13 @@
       <c r="AJ70" s="54"/>
       <c r="AK70" s="36" t="n">
         <f aca="false">SUM(Z70:AJ70)</f>
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="AL70" s="57"/>
       <c r="AM70" s="36"/>
       <c r="AN70" s="36" t="n">
         <f aca="false">[2]Sep!$V$1</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AO70" s="36"/>
       <c r="AP70" s="36"/>
@@ -33287,7 +33287,7 @@
       <c r="AU70" s="54"/>
       <c r="AV70" s="36" t="n">
         <f aca="false">SUM(AK70:AU70)</f>
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="AW70" s="57"/>
       <c r="AX70" s="36"/>
@@ -33304,13 +33304,13 @@
       <c r="BF70" s="54"/>
       <c r="BG70" s="36" t="n">
         <f aca="false">SUM(AV70:BF70)</f>
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="BH70" s="57"/>
       <c r="BI70" s="36"/>
       <c r="BJ70" s="36" t="n">
         <f aca="false">[2]Nov!$V$1</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="BK70" s="36"/>
       <c r="BL70" s="36"/>
@@ -33321,7 +33321,7 @@
       <c r="BQ70" s="54"/>
       <c r="BR70" s="36" t="n">
         <f aca="false">SUM(BG70:BQ70)</f>
-        <v>480</v>
+        <v>396</v>
       </c>
       <c r="BS70" s="57"/>
       <c r="BT70" s="36"/>
@@ -33338,7 +33338,7 @@
       <c r="CB70" s="54"/>
       <c r="CC70" s="36" t="n">
         <f aca="false">SUM(BR70:CB70)</f>
-        <v>480</v>
+        <v>396</v>
       </c>
       <c r="CD70" s="57"/>
       <c r="CE70" s="36"/>
@@ -33355,7 +33355,7 @@
       <c r="CM70" s="54"/>
       <c r="CN70" s="36" t="n">
         <f aca="false">SUM(CC70:CM70)</f>
-        <v>720</v>
+        <v>636</v>
       </c>
       <c r="CO70" s="57"/>
       <c r="CP70" s="36"/>
@@ -33372,13 +33372,13 @@
       <c r="CX70" s="54"/>
       <c r="CY70" s="36" t="n">
         <f aca="false">SUM(CN70:CX70)</f>
-        <v>720</v>
+        <v>636</v>
       </c>
       <c r="CZ70" s="57"/>
       <c r="DA70" s="36"/>
       <c r="DB70" s="36" t="n">
         <f aca="false">[2]Mar!$V$1</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="DC70" s="36"/>
       <c r="DD70" s="36"/>
@@ -33389,7 +33389,7 @@
       <c r="DI70" s="54"/>
       <c r="DJ70" s="36" t="n">
         <f aca="false">SUM(CY70:DI70)</f>
-        <v>720</v>
+        <v>816</v>
       </c>
       <c r="DK70" s="57"/>
       <c r="DL70" s="36"/>
@@ -33406,13 +33406,13 @@
       <c r="DT70" s="54"/>
       <c r="DU70" s="36" t="n">
         <f aca="false">SUM(DJ70:DT70)</f>
-        <v>720</v>
+        <v>816</v>
       </c>
       <c r="DV70" s="57"/>
       <c r="DW70" s="36"/>
       <c r="DX70" s="36" t="n">
         <f aca="false">[2]May!$V$1</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="DY70" s="36"/>
       <c r="DZ70" s="36"/>
@@ -33423,13 +33423,13 @@
       <c r="EE70" s="54"/>
       <c r="EF70" s="36" t="n">
         <f aca="false">SUM(DU70:EE70)</f>
-        <v>720</v>
+        <v>960</v>
       </c>
       <c r="EG70" s="54"/>
       <c r="EI70" s="54"/>
       <c r="EJ70" s="36" t="n">
         <f aca="false">SUM(EF70:EH70)</f>
-        <v>720</v>
+        <v>960</v>
       </c>
       <c r="EK70" s="54"/>
     </row>
@@ -33462,7 +33462,7 @@
       <c r="Q71" s="36"/>
       <c r="R71" s="36" t="n">
         <f aca="false">[2]Jul!$W$1</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S71" s="36"/>
       <c r="T71" s="36"/>
@@ -33473,7 +33473,7 @@
       <c r="Y71" s="54"/>
       <c r="Z71" s="36" t="n">
         <f aca="false">SUM(O71:Y71)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AA71" s="57"/>
       <c r="AB71" s="36"/>
@@ -33490,13 +33490,13 @@
       <c r="AJ71" s="54"/>
       <c r="AK71" s="36" t="n">
         <f aca="false">SUM(Z71:AJ71)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AL71" s="57"/>
       <c r="AM71" s="36"/>
       <c r="AN71" s="36" t="n">
         <f aca="false">[2]Sep!$W$1</f>
-        <v>960</v>
+        <v>480</v>
       </c>
       <c r="AO71" s="36"/>
       <c r="AP71" s="36"/>
@@ -33507,7 +33507,7 @@
       <c r="AU71" s="54"/>
       <c r="AV71" s="36" t="n">
         <f aca="false">SUM(AK71:AU71)</f>
-        <v>960</v>
+        <v>720</v>
       </c>
       <c r="AW71" s="57"/>
       <c r="AX71" s="36"/>
@@ -33524,13 +33524,13 @@
       <c r="BF71" s="54"/>
       <c r="BG71" s="36" t="n">
         <f aca="false">SUM(AV71:BF71)</f>
-        <v>960</v>
+        <v>720</v>
       </c>
       <c r="BH71" s="57"/>
       <c r="BI71" s="36"/>
       <c r="BJ71" s="36" t="n">
         <f aca="false">[2]Nov!$W$1</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="BK71" s="36"/>
       <c r="BL71" s="36"/>
@@ -33541,7 +33541,7 @@
       <c r="BQ71" s="54"/>
       <c r="BR71" s="36" t="n">
         <f aca="false">SUM(BG71:BQ71)</f>
-        <v>960</v>
+        <v>1080</v>
       </c>
       <c r="BS71" s="57"/>
       <c r="BT71" s="36"/>
@@ -33558,7 +33558,7 @@
       <c r="CB71" s="54"/>
       <c r="CC71" s="36" t="n">
         <f aca="false">SUM(BR71:CB71)</f>
-        <v>960</v>
+        <v>1080</v>
       </c>
       <c r="CD71" s="57"/>
       <c r="CE71" s="36"/>
@@ -33575,7 +33575,7 @@
       <c r="CM71" s="54"/>
       <c r="CN71" s="36" t="n">
         <f aca="false">SUM(CC71:CM71)</f>
-        <v>960</v>
+        <v>1080</v>
       </c>
       <c r="CO71" s="57"/>
       <c r="CP71" s="36"/>
@@ -33592,13 +33592,13 @@
       <c r="CX71" s="54"/>
       <c r="CY71" s="36" t="n">
         <f aca="false">SUM(CN71:CX71)</f>
-        <v>960</v>
+        <v>1080</v>
       </c>
       <c r="CZ71" s="57"/>
       <c r="DA71" s="36"/>
       <c r="DB71" s="36" t="n">
         <f aca="false">[2]Mar!$W$1</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="DC71" s="36"/>
       <c r="DD71" s="36"/>
@@ -33609,13 +33609,13 @@
       <c r="DI71" s="54"/>
       <c r="DJ71" s="36" t="n">
         <f aca="false">SUM(CY71:DI71)</f>
-        <v>960</v>
+        <v>1260</v>
       </c>
       <c r="DK71" s="57"/>
       <c r="DL71" s="36"/>
       <c r="DM71" s="36" t="n">
         <f aca="false">[2]Apr!$W$1</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="DN71" s="36"/>
       <c r="DO71" s="36"/>
@@ -33626,7 +33626,7 @@
       <c r="DT71" s="54"/>
       <c r="DU71" s="36" t="n">
         <f aca="false">SUM(DJ71:DT71)</f>
-        <v>960</v>
+        <v>1620</v>
       </c>
       <c r="DV71" s="57"/>
       <c r="DW71" s="36"/>
@@ -33643,13 +33643,13 @@
       <c r="EE71" s="54"/>
       <c r="EF71" s="36" t="n">
         <f aca="false">SUM(DU71:EE71)</f>
-        <v>960</v>
+        <v>1620</v>
       </c>
       <c r="EG71" s="54"/>
       <c r="EI71" s="54"/>
       <c r="EJ71" s="36" t="n">
         <f aca="false">SUM(EF71:EH71)</f>
-        <v>960</v>
+        <v>1620</v>
       </c>
       <c r="EK71" s="54"/>
     </row>
@@ -33666,7 +33666,7 @@
       <c r="F72" s="36"/>
       <c r="G72" s="36" t="n">
         <f aca="false">[2]Jun!$X$1</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H72" s="36"/>
       <c r="I72" s="36"/>
@@ -33676,7 +33676,7 @@
       <c r="N72" s="57"/>
       <c r="O72" s="36" t="n">
         <f aca="false">SUM(D72:N72)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P72" s="57"/>
       <c r="Q72" s="36"/>
@@ -33693,7 +33693,7 @@
       <c r="Y72" s="54"/>
       <c r="Z72" s="36" t="n">
         <f aca="false">SUM(O72:Y72)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AA72" s="57"/>
       <c r="AB72" s="36"/>
@@ -33710,13 +33710,13 @@
       <c r="AJ72" s="54"/>
       <c r="AK72" s="36" t="n">
         <f aca="false">SUM(Z72:AJ72)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AL72" s="57"/>
       <c r="AM72" s="36"/>
       <c r="AN72" s="36" t="n">
         <f aca="false">[2]Sep!$X$1</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AO72" s="36"/>
       <c r="AP72" s="36"/>
@@ -33727,13 +33727,13 @@
       <c r="AU72" s="54"/>
       <c r="AV72" s="36" t="n">
         <f aca="false">SUM(AK72:AU72)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AW72" s="57"/>
       <c r="AX72" s="36"/>
       <c r="AY72" s="36" t="n">
         <f aca="false">[2]Oct!$X$1</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AZ72" s="36"/>
       <c r="BA72" s="36"/>
@@ -33744,13 +33744,13 @@
       <c r="BF72" s="54"/>
       <c r="BG72" s="36" t="n">
         <f aca="false">SUM(AV72:BF72)</f>
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="BH72" s="57"/>
       <c r="BI72" s="36"/>
       <c r="BJ72" s="36" t="n">
         <f aca="false">[2]Nov!$X$1</f>
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="BK72" s="36"/>
       <c r="BL72" s="36"/>
@@ -33761,13 +33761,13 @@
       <c r="BQ72" s="54"/>
       <c r="BR72" s="36" t="n">
         <f aca="false">SUM(BG72:BQ72)</f>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="BS72" s="57"/>
       <c r="BT72" s="36"/>
       <c r="BU72" s="36" t="n">
         <f aca="false">[2]Dec!$X$1</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="BV72" s="36"/>
       <c r="BW72" s="36"/>
@@ -33778,7 +33778,7 @@
       <c r="CB72" s="54"/>
       <c r="CC72" s="36" t="n">
         <f aca="false">SUM(BR72:CB72)</f>
-        <v>480</v>
+        <v>636</v>
       </c>
       <c r="CD72" s="57"/>
       <c r="CE72" s="36"/>
@@ -33795,7 +33795,7 @@
       <c r="CM72" s="54"/>
       <c r="CN72" s="36" t="n">
         <f aca="false">SUM(CC72:CM72)</f>
-        <v>480</v>
+        <v>636</v>
       </c>
       <c r="CO72" s="57"/>
       <c r="CP72" s="36"/>
@@ -33812,13 +33812,13 @@
       <c r="CX72" s="54"/>
       <c r="CY72" s="36" t="n">
         <f aca="false">SUM(CN72:CX72)</f>
-        <v>480</v>
+        <v>636</v>
       </c>
       <c r="CZ72" s="57"/>
       <c r="DA72" s="36"/>
       <c r="DB72" s="36" t="n">
         <f aca="false">[2]Mar!$X$1</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="DC72" s="36"/>
       <c r="DD72" s="36"/>
@@ -33829,7 +33829,7 @@
       <c r="DI72" s="54"/>
       <c r="DJ72" s="36" t="n">
         <f aca="false">SUM(CY72:DI72)</f>
-        <v>480</v>
+        <v>780</v>
       </c>
       <c r="DK72" s="57"/>
       <c r="DL72" s="36"/>
@@ -33846,7 +33846,7 @@
       <c r="DT72" s="54"/>
       <c r="DU72" s="36" t="n">
         <f aca="false">SUM(DJ72:DT72)</f>
-        <v>840</v>
+        <v>1140</v>
       </c>
       <c r="DV72" s="57"/>
       <c r="DW72" s="36"/>
@@ -33863,13 +33863,13 @@
       <c r="EE72" s="54"/>
       <c r="EF72" s="36" t="n">
         <f aca="false">SUM(DU72:EE72)</f>
-        <v>840</v>
+        <v>1140</v>
       </c>
       <c r="EG72" s="54"/>
       <c r="EI72" s="54"/>
       <c r="EJ72" s="36" t="n">
         <f aca="false">SUM(EF72:EH72)</f>
-        <v>840</v>
+        <v>1140</v>
       </c>
       <c r="EK72" s="54"/>
     </row>
@@ -33886,7 +33886,7 @@
       <c r="F73" s="36"/>
       <c r="G73" s="36" t="n">
         <f aca="false">[2]Jun!$Y$1</f>
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="H73" s="36"/>
       <c r="I73" s="36"/>
@@ -33896,13 +33896,13 @@
       <c r="N73" s="57"/>
       <c r="O73" s="36" t="n">
         <f aca="false">SUM(D73:N73)</f>
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="P73" s="57"/>
       <c r="Q73" s="36"/>
       <c r="R73" s="36" t="n">
         <f aca="false">[2]Jul!$Y$1</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="S73" s="36"/>
       <c r="T73" s="36"/>
@@ -33913,13 +33913,13 @@
       <c r="Y73" s="54"/>
       <c r="Z73" s="36" t="n">
         <f aca="false">SUM(O73:Y73)</f>
-        <v>180</v>
+        <v>272</v>
       </c>
       <c r="AA73" s="57"/>
       <c r="AB73" s="36"/>
       <c r="AC73" s="36" t="n">
         <f aca="false">[2]Aug!$Y$1</f>
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="AD73" s="36"/>
       <c r="AE73" s="36"/>
@@ -33930,13 +33930,13 @@
       <c r="AJ73" s="54"/>
       <c r="AK73" s="36" t="n">
         <f aca="false">SUM(Z73:AJ73)</f>
-        <v>180</v>
+        <v>417</v>
       </c>
       <c r="AL73" s="57"/>
       <c r="AM73" s="36"/>
       <c r="AN73" s="36" t="n">
         <f aca="false">[2]Sep!$Y$1</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="AO73" s="36"/>
       <c r="AP73" s="36"/>
@@ -33947,13 +33947,13 @@
       <c r="AU73" s="54"/>
       <c r="AV73" s="36" t="n">
         <f aca="false">SUM(AK73:AU73)</f>
-        <v>180</v>
+        <v>532</v>
       </c>
       <c r="AW73" s="57"/>
       <c r="AX73" s="36"/>
       <c r="AY73" s="36" t="n">
         <f aca="false">[2]Oct!$Y$1</f>
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="AZ73" s="36"/>
       <c r="BA73" s="36"/>
@@ -33964,13 +33964,13 @@
       <c r="BF73" s="54"/>
       <c r="BG73" s="36" t="n">
         <f aca="false">SUM(AV73:BF73)</f>
-        <v>180</v>
+        <v>695</v>
       </c>
       <c r="BH73" s="57"/>
       <c r="BI73" s="36"/>
       <c r="BJ73" s="36" t="n">
         <f aca="false">[2]Nov!$Y$1</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="BK73" s="36"/>
       <c r="BL73" s="36"/>
@@ -33981,13 +33981,13 @@
       <c r="BQ73" s="54"/>
       <c r="BR73" s="36" t="n">
         <f aca="false">SUM(BG73:BQ73)</f>
-        <v>180</v>
+        <v>810</v>
       </c>
       <c r="BS73" s="57"/>
       <c r="BT73" s="36"/>
       <c r="BU73" s="36" t="n">
         <f aca="false">[2]Dec!$Y$1</f>
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="BV73" s="36"/>
       <c r="BW73" s="36"/>
@@ -33998,13 +33998,13 @@
       <c r="CB73" s="54"/>
       <c r="CC73" s="36" t="n">
         <f aca="false">SUM(BR73:CB73)</f>
-        <v>324</v>
+        <v>961</v>
       </c>
       <c r="CD73" s="57"/>
       <c r="CE73" s="36"/>
       <c r="CF73" s="36" t="n">
         <f aca="false">[2]Jan!$Y$1</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="CG73" s="36"/>
       <c r="CH73" s="36"/>
@@ -34015,13 +34015,13 @@
       <c r="CM73" s="54"/>
       <c r="CN73" s="36" t="n">
         <f aca="false">SUM(CC73:CM73)</f>
-        <v>324</v>
+        <v>1076</v>
       </c>
       <c r="CO73" s="57"/>
       <c r="CP73" s="36"/>
       <c r="CQ73" s="36" t="n">
         <f aca="false">[2]Feb!$Y$1</f>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="CR73" s="36"/>
       <c r="CS73" s="36"/>
@@ -34032,13 +34032,13 @@
       <c r="CX73" s="54"/>
       <c r="CY73" s="36" t="n">
         <f aca="false">SUM(CN73:CX73)</f>
-        <v>324</v>
+        <v>1215</v>
       </c>
       <c r="CZ73" s="57"/>
       <c r="DA73" s="36"/>
       <c r="DB73" s="36" t="n">
         <f aca="false">[2]Mar!$Y$1</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="DC73" s="36"/>
       <c r="DD73" s="36"/>
@@ -34049,13 +34049,13 @@
       <c r="DI73" s="54"/>
       <c r="DJ73" s="36" t="n">
         <f aca="false">SUM(CY73:DI73)</f>
-        <v>324</v>
+        <v>1330</v>
       </c>
       <c r="DK73" s="57"/>
       <c r="DL73" s="36"/>
       <c r="DM73" s="36" t="n">
         <f aca="false">[2]Apr!$Y$1</f>
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="DN73" s="36"/>
       <c r="DO73" s="36"/>
@@ -34066,13 +34066,13 @@
       <c r="DT73" s="54"/>
       <c r="DU73" s="36" t="n">
         <f aca="false">SUM(DJ73:DT73)</f>
-        <v>324</v>
+        <v>1463</v>
       </c>
       <c r="DV73" s="57"/>
       <c r="DW73" s="36"/>
       <c r="DX73" s="36" t="n">
         <f aca="false">[2]May!$Y$1</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="DY73" s="36"/>
       <c r="DZ73" s="36"/>
@@ -34083,13 +34083,13 @@
       <c r="EE73" s="54"/>
       <c r="EF73" s="36" t="n">
         <f aca="false">SUM(DU73:EE73)</f>
-        <v>324</v>
+        <v>1578</v>
       </c>
       <c r="EG73" s="54"/>
       <c r="EI73" s="54"/>
       <c r="EJ73" s="36" t="n">
         <f aca="false">SUM(EF73:EH73)</f>
-        <v>324</v>
+        <v>1578</v>
       </c>
       <c r="EK73" s="54"/>
     </row>
@@ -34122,7 +34122,7 @@
       <c r="Q74" s="36"/>
       <c r="R74" s="36" t="n">
         <f aca="false">[2]Jul!$Z$1</f>
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="S74" s="36"/>
       <c r="T74" s="36"/>
@@ -34133,7 +34133,7 @@
       <c r="Y74" s="54"/>
       <c r="Z74" s="36" t="n">
         <f aca="false">SUM(O74:Y74)</f>
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="AA74" s="57"/>
       <c r="AB74" s="36"/>
@@ -34150,13 +34150,13 @@
       <c r="AJ74" s="54"/>
       <c r="AK74" s="36" t="n">
         <f aca="false">SUM(Z74:AJ74)</f>
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="AL74" s="57"/>
       <c r="AM74" s="36"/>
       <c r="AN74" s="36" t="n">
         <f aca="false">[2]Sep!$Z$1</f>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="AO74" s="36"/>
       <c r="AP74" s="36"/>
@@ -34167,7 +34167,7 @@
       <c r="AU74" s="54"/>
       <c r="AV74" s="36" t="n">
         <f aca="false">SUM(AK74:AU74)</f>
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="AW74" s="57"/>
       <c r="AX74" s="36"/>
@@ -34184,7 +34184,7 @@
       <c r="BF74" s="54"/>
       <c r="BG74" s="36" t="n">
         <f aca="false">SUM(AV74:BF74)</f>
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="BH74" s="57"/>
       <c r="BI74" s="36"/>
@@ -34201,13 +34201,13 @@
       <c r="BQ74" s="54"/>
       <c r="BR74" s="36" t="n">
         <f aca="false">SUM(BG74:BQ74)</f>
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="BS74" s="57"/>
       <c r="BT74" s="36"/>
       <c r="BU74" s="36" t="n">
         <f aca="false">[2]Dec!$Z$1</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="BV74" s="36"/>
       <c r="BW74" s="36"/>
@@ -34218,7 +34218,7 @@
       <c r="CB74" s="54"/>
       <c r="CC74" s="36" t="n">
         <f aca="false">SUM(BR74:CB74)</f>
-        <v>1200</v>
+        <v>4080</v>
       </c>
       <c r="CD74" s="57"/>
       <c r="CE74" s="36"/>
@@ -34235,7 +34235,7 @@
       <c r="CM74" s="54"/>
       <c r="CN74" s="36" t="n">
         <f aca="false">SUM(CC74:CM74)</f>
-        <v>1200</v>
+        <v>4080</v>
       </c>
       <c r="CO74" s="57"/>
       <c r="CP74" s="36"/>
@@ -34252,13 +34252,13 @@
       <c r="CX74" s="54"/>
       <c r="CY74" s="36" t="n">
         <f aca="false">SUM(CN74:CX74)</f>
-        <v>1200</v>
+        <v>4080</v>
       </c>
       <c r="CZ74" s="57"/>
       <c r="DA74" s="36"/>
       <c r="DB74" s="36" t="n">
         <f aca="false">[2]Mar!$Z$1</f>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="DC74" s="36"/>
       <c r="DD74" s="36"/>
@@ -34269,7 +34269,7 @@
       <c r="DI74" s="54"/>
       <c r="DJ74" s="36" t="n">
         <f aca="false">SUM(CY74:DI74)</f>
-        <v>1800</v>
+        <v>4560</v>
       </c>
       <c r="DK74" s="57"/>
       <c r="DL74" s="36"/>
@@ -34286,7 +34286,7 @@
       <c r="DT74" s="54"/>
       <c r="DU74" s="36" t="n">
         <f aca="false">SUM(DJ74:DT74)</f>
-        <v>1800</v>
+        <v>4560</v>
       </c>
       <c r="DV74" s="57"/>
       <c r="DW74" s="36"/>
@@ -34303,13 +34303,13 @@
       <c r="EE74" s="54"/>
       <c r="EF74" s="36" t="n">
         <f aca="false">SUM(DU74:EE74)</f>
-        <v>1800</v>
+        <v>4560</v>
       </c>
       <c r="EG74" s="54"/>
       <c r="EI74" s="54"/>
       <c r="EJ74" s="36" t="n">
         <f aca="false">SUM(EF74:EH74)</f>
-        <v>1800</v>
+        <v>4560</v>
       </c>
       <c r="EK74" s="54"/>
     </row>
@@ -34326,7 +34326,7 @@
       <c r="F75" s="36"/>
       <c r="G75" s="36" t="n">
         <f aca="false">[2]Jun!$AA$1</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="H75" s="36"/>
       <c r="I75" s="36"/>
@@ -34336,13 +34336,13 @@
       <c r="N75" s="57"/>
       <c r="O75" s="36" t="n">
         <f aca="false">SUM(D75:N75)</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="P75" s="57"/>
       <c r="Q75" s="36"/>
       <c r="R75" s="36" t="n">
         <f aca="false">[2]Jul!$AA$1</f>
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="S75" s="36"/>
       <c r="T75" s="36"/>
@@ -34353,13 +34353,13 @@
       <c r="Y75" s="54"/>
       <c r="Z75" s="36" t="n">
         <f aca="false">SUM(O75:Y75)</f>
-        <v>120</v>
+        <v>288</v>
       </c>
       <c r="AA75" s="57"/>
       <c r="AB75" s="36"/>
       <c r="AC75" s="36" t="n">
         <f aca="false">[2]Aug!$AA$1</f>
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="AD75" s="36"/>
       <c r="AE75" s="36"/>
@@ -34370,13 +34370,13 @@
       <c r="AJ75" s="54"/>
       <c r="AK75" s="36" t="n">
         <f aca="false">SUM(Z75:AJ75)</f>
-        <v>300</v>
+        <v>519</v>
       </c>
       <c r="AL75" s="57"/>
       <c r="AM75" s="36"/>
       <c r="AN75" s="36" t="n">
         <f aca="false">[2]Sep!$AA$1</f>
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="AO75" s="36"/>
       <c r="AP75" s="36"/>
@@ -34387,13 +34387,13 @@
       <c r="AU75" s="54"/>
       <c r="AV75" s="36" t="n">
         <f aca="false">SUM(AK75:AU75)</f>
-        <v>360</v>
+        <v>678</v>
       </c>
       <c r="AW75" s="57"/>
       <c r="AX75" s="36"/>
       <c r="AY75" s="36" t="n">
         <f aca="false">[2]Oct!$AA$1</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="AZ75" s="36"/>
       <c r="BA75" s="36"/>
@@ -34404,13 +34404,13 @@
       <c r="BF75" s="54"/>
       <c r="BG75" s="36" t="n">
         <f aca="false">SUM(AV75:BF75)</f>
-        <v>420</v>
+        <v>813</v>
       </c>
       <c r="BH75" s="57"/>
       <c r="BI75" s="36"/>
       <c r="BJ75" s="36" t="n">
         <f aca="false">[2]Nov!$AA$1</f>
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="BK75" s="36"/>
       <c r="BL75" s="36"/>
@@ -34421,13 +34421,13 @@
       <c r="BQ75" s="54"/>
       <c r="BR75" s="36" t="n">
         <f aca="false">SUM(BG75:BQ75)</f>
-        <v>480</v>
+        <v>960</v>
       </c>
       <c r="BS75" s="57"/>
       <c r="BT75" s="36"/>
       <c r="BU75" s="36" t="n">
         <f aca="false">[2]Dec!$AA$1</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="BV75" s="36"/>
       <c r="BW75" s="36"/>
@@ -34438,13 +34438,13 @@
       <c r="CB75" s="54"/>
       <c r="CC75" s="36" t="n">
         <f aca="false">SUM(BR75:CB75)</f>
-        <v>540</v>
+        <v>1095</v>
       </c>
       <c r="CD75" s="57"/>
       <c r="CE75" s="36"/>
       <c r="CF75" s="36" t="n">
         <f aca="false">[2]Jan!$AA$1</f>
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="CG75" s="36"/>
       <c r="CH75" s="36"/>
@@ -34455,13 +34455,13 @@
       <c r="CM75" s="54"/>
       <c r="CN75" s="36" t="n">
         <f aca="false">SUM(CC75:CM75)</f>
-        <v>600</v>
+        <v>1260</v>
       </c>
       <c r="CO75" s="57"/>
       <c r="CP75" s="36"/>
       <c r="CQ75" s="36" t="n">
         <f aca="false">[2]Feb!$AA$1</f>
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="CR75" s="36"/>
       <c r="CS75" s="36"/>
@@ -34472,13 +34472,13 @@
       <c r="CX75" s="54"/>
       <c r="CY75" s="36" t="n">
         <f aca="false">SUM(CN75:CX75)</f>
-        <v>780</v>
+        <v>1515</v>
       </c>
       <c r="CZ75" s="57"/>
       <c r="DA75" s="36"/>
       <c r="DB75" s="36" t="n">
         <f aca="false">[2]Mar!$AA$1</f>
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="DC75" s="36"/>
       <c r="DD75" s="36"/>
@@ -34489,13 +34489,13 @@
       <c r="DI75" s="54"/>
       <c r="DJ75" s="36" t="n">
         <f aca="false">SUM(CY75:DI75)</f>
-        <v>840</v>
+        <v>1668</v>
       </c>
       <c r="DK75" s="57"/>
       <c r="DL75" s="36"/>
       <c r="DM75" s="36" t="n">
         <f aca="false">[2]Apr!$AA$1</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="DN75" s="36"/>
       <c r="DO75" s="36"/>
@@ -34506,13 +34506,13 @@
       <c r="DT75" s="54"/>
       <c r="DU75" s="36" t="n">
         <f aca="false">SUM(DJ75:DT75)</f>
-        <v>900</v>
+        <v>1803</v>
       </c>
       <c r="DV75" s="57"/>
       <c r="DW75" s="36"/>
       <c r="DX75" s="36" t="n">
         <f aca="false">[2]May!$AA$1</f>
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="DY75" s="36"/>
       <c r="DZ75" s="36"/>
@@ -34523,13 +34523,13 @@
       <c r="EE75" s="54"/>
       <c r="EF75" s="36" t="n">
         <f aca="false">SUM(DU75:EE75)</f>
-        <v>960</v>
+        <v>1962</v>
       </c>
       <c r="EG75" s="54"/>
       <c r="EI75" s="54"/>
       <c r="EJ75" s="36" t="n">
         <f aca="false">SUM(EF75:EH75)</f>
-        <v>960</v>
+        <v>1962</v>
       </c>
       <c r="EK75" s="54"/>
     </row>
@@ -34546,7 +34546,7 @@
       <c r="F76" s="36"/>
       <c r="G76" s="36" t="n">
         <f aca="false">[2]Jun!$AB$1</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H76" s="36"/>
       <c r="I76" s="36"/>
@@ -34556,13 +34556,13 @@
       <c r="N76" s="57"/>
       <c r="O76" s="36" t="n">
         <f aca="false">SUM(D76:N76)</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="P76" s="57"/>
       <c r="Q76" s="36"/>
       <c r="R76" s="36" t="n">
         <f aca="false">[2]Jul!$AB$1</f>
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="S76" s="36"/>
       <c r="T76" s="36"/>
@@ -34573,13 +34573,13 @@
       <c r="Y76" s="54"/>
       <c r="Z76" s="36" t="n">
         <f aca="false">SUM(O76:Y76)</f>
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="AA76" s="57"/>
       <c r="AB76" s="36"/>
       <c r="AC76" s="36" t="n">
         <f aca="false">[2]Aug!$AB$1</f>
-        <v>480</v>
+        <v>272</v>
       </c>
       <c r="AD76" s="36"/>
       <c r="AE76" s="36"/>
@@ -34590,13 +34590,13 @@
       <c r="AJ76" s="54"/>
       <c r="AK76" s="36" t="n">
         <f aca="false">SUM(Z76:AJ76)</f>
-        <v>480</v>
+        <v>516</v>
       </c>
       <c r="AL76" s="57"/>
       <c r="AM76" s="36"/>
       <c r="AN76" s="36" t="n">
         <f aca="false">[2]Sep!$AB$1</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AO76" s="36"/>
       <c r="AP76" s="36"/>
@@ -34607,13 +34607,13 @@
       <c r="AU76" s="54"/>
       <c r="AV76" s="36" t="n">
         <f aca="false">SUM(AK76:AU76)</f>
-        <v>480</v>
+        <v>608</v>
       </c>
       <c r="AW76" s="57"/>
       <c r="AX76" s="36"/>
       <c r="AY76" s="36" t="n">
         <f aca="false">[2]Oct!$AB$1</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AZ76" s="36"/>
       <c r="BA76" s="36"/>
@@ -34624,13 +34624,13 @@
       <c r="BF76" s="54"/>
       <c r="BG76" s="36" t="n">
         <f aca="false">SUM(AV76:BF76)</f>
-        <v>480</v>
+        <v>748</v>
       </c>
       <c r="BH76" s="57"/>
       <c r="BI76" s="36"/>
       <c r="BJ76" s="36" t="n">
         <f aca="false">[2]Nov!$AB$1</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="BK76" s="36"/>
       <c r="BL76" s="36"/>
@@ -34641,13 +34641,13 @@
       <c r="BQ76" s="54"/>
       <c r="BR76" s="36" t="n">
         <f aca="false">SUM(BG76:BQ76)</f>
-        <v>480</v>
+        <v>840</v>
       </c>
       <c r="BS76" s="57"/>
       <c r="BT76" s="36"/>
       <c r="BU76" s="36" t="n">
         <f aca="false">[2]Dec!$AB$1</f>
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="BV76" s="36"/>
       <c r="BW76" s="36"/>
@@ -34658,13 +34658,13 @@
       <c r="CB76" s="54"/>
       <c r="CC76" s="36" t="n">
         <f aca="false">SUM(BR76:CB76)</f>
-        <v>480</v>
+        <v>1052</v>
       </c>
       <c r="CD76" s="57"/>
       <c r="CE76" s="36"/>
       <c r="CF76" s="36" t="n">
         <f aca="false">[2]Jan!$AB$1</f>
-        <v>360</v>
+        <v>164</v>
       </c>
       <c r="CG76" s="36"/>
       <c r="CH76" s="36"/>
@@ -34675,13 +34675,13 @@
       <c r="CM76" s="54"/>
       <c r="CN76" s="36" t="n">
         <f aca="false">SUM(CC76:CM76)</f>
-        <v>840</v>
+        <v>1216</v>
       </c>
       <c r="CO76" s="57"/>
       <c r="CP76" s="36"/>
       <c r="CQ76" s="36" t="n">
         <f aca="false">[2]Feb!$AB$1</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="CR76" s="36"/>
       <c r="CS76" s="36"/>
@@ -34692,13 +34692,13 @@
       <c r="CX76" s="54"/>
       <c r="CY76" s="36" t="n">
         <f aca="false">SUM(CN76:CX76)</f>
-        <v>840</v>
+        <v>1308</v>
       </c>
       <c r="CZ76" s="57"/>
       <c r="DA76" s="36"/>
       <c r="DB76" s="36" t="n">
         <f aca="false">[2]Mar!$AB$1</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="DC76" s="36"/>
       <c r="DD76" s="36"/>
@@ -34709,13 +34709,13 @@
       <c r="DI76" s="54"/>
       <c r="DJ76" s="36" t="n">
         <f aca="false">SUM(CY76:DI76)</f>
-        <v>840</v>
+        <v>1400</v>
       </c>
       <c r="DK76" s="57"/>
       <c r="DL76" s="36"/>
       <c r="DM76" s="36" t="n">
         <f aca="false">[2]Apr!$AB$1</f>
-        <v>96</v>
+        <v>368</v>
       </c>
       <c r="DN76" s="36"/>
       <c r="DO76" s="36"/>
@@ -34726,13 +34726,13 @@
       <c r="DT76" s="54"/>
       <c r="DU76" s="36" t="n">
         <f aca="false">SUM(DJ76:DT76)</f>
-        <v>936</v>
+        <v>1768</v>
       </c>
       <c r="DV76" s="57"/>
       <c r="DW76" s="36"/>
       <c r="DX76" s="36" t="n">
         <f aca="false">[2]May!$AB$1</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="DY76" s="36"/>
       <c r="DZ76" s="36"/>
@@ -34743,13 +34743,13 @@
       <c r="EE76" s="54"/>
       <c r="EF76" s="36" t="n">
         <f aca="false">SUM(DU76:EE76)</f>
-        <v>936</v>
+        <v>1860</v>
       </c>
       <c r="EG76" s="54"/>
       <c r="EI76" s="54"/>
       <c r="EJ76" s="36" t="n">
         <f aca="false">SUM(EF76:EH76)</f>
-        <v>936</v>
+        <v>1860</v>
       </c>
       <c r="EK76" s="54"/>
     </row>
@@ -34766,7 +34766,7 @@
       <c r="F77" s="36"/>
       <c r="G77" s="36" t="n">
         <f aca="false">[2]Jun!$AC$1</f>
-        <v>1080</v>
+        <v>602.25</v>
       </c>
       <c r="H77" s="36"/>
       <c r="I77" s="36"/>
@@ -34776,13 +34776,13 @@
       <c r="N77" s="57"/>
       <c r="O77" s="36" t="n">
         <f aca="false">SUM(D77:N77)</f>
-        <v>1080</v>
+        <v>602.25</v>
       </c>
       <c r="P77" s="57"/>
       <c r="Q77" s="36"/>
       <c r="R77" s="36" t="n">
         <f aca="false">[2]Jul!$AC$1</f>
-        <v>120</v>
+        <v>666</v>
       </c>
       <c r="S77" s="36"/>
       <c r="T77" s="36"/>
@@ -34793,13 +34793,13 @@
       <c r="Y77" s="54"/>
       <c r="Z77" s="36" t="n">
         <f aca="false">SUM(O77:Y77)</f>
-        <v>1200</v>
+        <v>1268.25</v>
       </c>
       <c r="AA77" s="57"/>
       <c r="AB77" s="36"/>
       <c r="AC77" s="36" t="n">
         <f aca="false">[2]Aug!$AC$1</f>
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="AD77" s="36"/>
       <c r="AE77" s="36"/>
@@ -34810,13 +34810,13 @@
       <c r="AJ77" s="54"/>
       <c r="AK77" s="36" t="n">
         <f aca="false">SUM(Z77:AJ77)</f>
-        <v>1200</v>
+        <v>1922.25</v>
       </c>
       <c r="AL77" s="57"/>
       <c r="AM77" s="36"/>
       <c r="AN77" s="36" t="n">
         <f aca="false">[2]Sep!$AC$1</f>
-        <v>840</v>
+        <v>584.25</v>
       </c>
       <c r="AO77" s="36"/>
       <c r="AP77" s="36"/>
@@ -34827,13 +34827,13 @@
       <c r="AU77" s="54"/>
       <c r="AV77" s="36" t="n">
         <f aca="false">SUM(AK77:AU77)</f>
-        <v>2040</v>
+        <v>2506.5</v>
       </c>
       <c r="AW77" s="57"/>
       <c r="AX77" s="36"/>
       <c r="AY77" s="36" t="n">
         <f aca="false">[2]Oct!$AC$1</f>
-        <v>120</v>
+        <v>602.25</v>
       </c>
       <c r="AZ77" s="36"/>
       <c r="BA77" s="36"/>
@@ -34844,13 +34844,13 @@
       <c r="BF77" s="54"/>
       <c r="BG77" s="36" t="n">
         <f aca="false">SUM(AV77:BF77)</f>
-        <v>2160</v>
+        <v>3108.75</v>
       </c>
       <c r="BH77" s="57"/>
       <c r="BI77" s="36"/>
       <c r="BJ77" s="36" t="n">
         <f aca="false">[2]Nov!$AC$1</f>
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="BK77" s="36"/>
       <c r="BL77" s="36"/>
@@ -34861,13 +34861,13 @@
       <c r="BQ77" s="54"/>
       <c r="BR77" s="36" t="n">
         <f aca="false">SUM(BG77:BQ77)</f>
-        <v>2160</v>
+        <v>3816.75</v>
       </c>
       <c r="BS77" s="57"/>
       <c r="BT77" s="36"/>
       <c r="BU77" s="36" t="n">
         <f aca="false">[2]Dec!$AC$1</f>
-        <v>0</v>
+        <v>606.75</v>
       </c>
       <c r="BV77" s="36"/>
       <c r="BW77" s="36"/>
@@ -34878,13 +34878,13 @@
       <c r="CB77" s="54"/>
       <c r="CC77" s="36" t="n">
         <f aca="false">SUM(BR77:CB77)</f>
-        <v>2160</v>
+        <v>4423.5</v>
       </c>
       <c r="CD77" s="57"/>
       <c r="CE77" s="36"/>
       <c r="CF77" s="36" t="n">
         <f aca="false">[2]Jan!$AC$1</f>
-        <v>120</v>
+        <v>645</v>
       </c>
       <c r="CG77" s="36"/>
       <c r="CH77" s="36"/>
@@ -34895,13 +34895,13 @@
       <c r="CM77" s="54"/>
       <c r="CN77" s="36" t="n">
         <f aca="false">SUM(CC77:CM77)</f>
-        <v>2280</v>
+        <v>5068.5</v>
       </c>
       <c r="CO77" s="57"/>
       <c r="CP77" s="36"/>
       <c r="CQ77" s="36" t="n">
         <f aca="false">[2]Feb!$AC$1</f>
-        <v>0</v>
+        <v>613.5</v>
       </c>
       <c r="CR77" s="36"/>
       <c r="CS77" s="36"/>
@@ -34912,13 +34912,13 @@
       <c r="CX77" s="54"/>
       <c r="CY77" s="36" t="n">
         <f aca="false">SUM(CN77:CX77)</f>
-        <v>2280</v>
+        <v>5682</v>
       </c>
       <c r="CZ77" s="57"/>
       <c r="DA77" s="36"/>
       <c r="DB77" s="36" t="n">
         <f aca="false">[2]Mar!$AC$1</f>
-        <v>0</v>
+        <v>638.25</v>
       </c>
       <c r="DC77" s="36"/>
       <c r="DD77" s="36"/>
@@ -34929,13 +34929,13 @@
       <c r="DI77" s="54"/>
       <c r="DJ77" s="36" t="n">
         <f aca="false">SUM(CY77:DI77)</f>
-        <v>2280</v>
+        <v>6320.25</v>
       </c>
       <c r="DK77" s="57"/>
       <c r="DL77" s="36"/>
       <c r="DM77" s="36" t="n">
         <f aca="false">[2]Apr!$AC$1</f>
-        <v>120</v>
+        <v>595.5</v>
       </c>
       <c r="DN77" s="36"/>
       <c r="DO77" s="36"/>
@@ -34946,13 +34946,13 @@
       <c r="DT77" s="54"/>
       <c r="DU77" s="36" t="n">
         <f aca="false">SUM(DJ77:DT77)</f>
-        <v>2400</v>
+        <v>6915.75</v>
       </c>
       <c r="DV77" s="57"/>
       <c r="DW77" s="36"/>
       <c r="DX77" s="36" t="n">
         <f aca="false">[2]May!$AC$1</f>
-        <v>0</v>
+        <v>682.5</v>
       </c>
       <c r="DY77" s="36"/>
       <c r="DZ77" s="36"/>
@@ -34963,13 +34963,13 @@
       <c r="EE77" s="54"/>
       <c r="EF77" s="36" t="n">
         <f aca="false">SUM(DU77:EE77)</f>
-        <v>2400</v>
+        <v>7598.25</v>
       </c>
       <c r="EG77" s="54"/>
       <c r="EI77" s="54"/>
       <c r="EJ77" s="36" t="n">
         <f aca="false">SUM(EF77:EH77)</f>
-        <v>2400</v>
+        <v>7598.25</v>
       </c>
       <c r="EK77" s="54"/>
     </row>
@@ -34986,7 +34986,7 @@
       <c r="F78" s="36"/>
       <c r="G78" s="36" t="n">
         <f aca="false">[2]Jun!$AD$1</f>
-        <v>960</v>
+        <v>1440</v>
       </c>
       <c r="H78" s="36"/>
       <c r="I78" s="36"/>
@@ -34996,7 +34996,7 @@
       <c r="N78" s="57"/>
       <c r="O78" s="36" t="n">
         <f aca="false">SUM(D78:N78)</f>
-        <v>960</v>
+        <v>1440</v>
       </c>
       <c r="P78" s="57"/>
       <c r="Q78" s="36"/>
@@ -35013,7 +35013,7 @@
       <c r="Y78" s="54"/>
       <c r="Z78" s="36" t="n">
         <f aca="false">SUM(O78:Y78)</f>
-        <v>960</v>
+        <v>1440</v>
       </c>
       <c r="AA78" s="57"/>
       <c r="AB78" s="36"/>
@@ -35030,7 +35030,7 @@
       <c r="AJ78" s="54"/>
       <c r="AK78" s="36" t="n">
         <f aca="false">SUM(Z78:AJ78)</f>
-        <v>960</v>
+        <v>1440</v>
       </c>
       <c r="AL78" s="57"/>
       <c r="AM78" s="36"/>
@@ -35047,7 +35047,7 @@
       <c r="AU78" s="54"/>
       <c r="AV78" s="36" t="n">
         <f aca="false">SUM(AK78:AU78)</f>
-        <v>960</v>
+        <v>1440</v>
       </c>
       <c r="AW78" s="57"/>
       <c r="AX78" s="36"/>
@@ -35064,7 +35064,7 @@
       <c r="BF78" s="54"/>
       <c r="BG78" s="36" t="n">
         <f aca="false">SUM(AV78:BF78)</f>
-        <v>960</v>
+        <v>1440</v>
       </c>
       <c r="BH78" s="57"/>
       <c r="BI78" s="36"/>
@@ -35081,13 +35081,13 @@
       <c r="BQ78" s="54"/>
       <c r="BR78" s="36" t="n">
         <f aca="false">SUM(BG78:BQ78)</f>
-        <v>960</v>
+        <v>1440</v>
       </c>
       <c r="BS78" s="57"/>
       <c r="BT78" s="36"/>
       <c r="BU78" s="36" t="n">
         <f aca="false">[2]Dec!$AD$1</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="BV78" s="36"/>
       <c r="BW78" s="36"/>
@@ -35098,7 +35098,7 @@
       <c r="CB78" s="54"/>
       <c r="CC78" s="36" t="n">
         <f aca="false">SUM(BR78:CB78)</f>
-        <v>960</v>
+        <v>1800</v>
       </c>
       <c r="CD78" s="57"/>
       <c r="CE78" s="36"/>
@@ -35115,7 +35115,7 @@
       <c r="CM78" s="54"/>
       <c r="CN78" s="36" t="n">
         <f aca="false">SUM(CC78:CM78)</f>
-        <v>960</v>
+        <v>1800</v>
       </c>
       <c r="CO78" s="57"/>
       <c r="CP78" s="36"/>
@@ -35132,7 +35132,7 @@
       <c r="CX78" s="54"/>
       <c r="CY78" s="36" t="n">
         <f aca="false">SUM(CN78:CX78)</f>
-        <v>960</v>
+        <v>1800</v>
       </c>
       <c r="CZ78" s="57"/>
       <c r="DA78" s="36"/>
@@ -35149,7 +35149,7 @@
       <c r="DI78" s="54"/>
       <c r="DJ78" s="36" t="n">
         <f aca="false">SUM(CY78:DI78)</f>
-        <v>960</v>
+        <v>1800</v>
       </c>
       <c r="DK78" s="57"/>
       <c r="DL78" s="36"/>
@@ -35166,7 +35166,7 @@
       <c r="DT78" s="54"/>
       <c r="DU78" s="36" t="n">
         <f aca="false">SUM(DJ78:DT78)</f>
-        <v>960</v>
+        <v>1800</v>
       </c>
       <c r="DV78" s="57"/>
       <c r="DW78" s="36"/>
@@ -35183,13 +35183,13 @@
       <c r="EE78" s="54"/>
       <c r="EF78" s="36" t="n">
         <f aca="false">SUM(DU78:EE78)</f>
-        <v>960</v>
+        <v>1800</v>
       </c>
       <c r="EG78" s="54"/>
       <c r="EI78" s="54"/>
       <c r="EJ78" s="36" t="n">
         <f aca="false">SUM(EF78:EH78)</f>
-        <v>960</v>
+        <v>1800</v>
       </c>
       <c r="EK78" s="54"/>
     </row>
@@ -35206,7 +35206,7 @@
       <c r="F79" s="36"/>
       <c r="G79" s="36" t="n">
         <f aca="false">[2]Jun!$AE$1</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H79" s="36"/>
       <c r="I79" s="36"/>
@@ -35216,7 +35216,7 @@
       <c r="N79" s="57"/>
       <c r="O79" s="36" t="n">
         <f aca="false">SUM(D79:N79)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="P79" s="57"/>
       <c r="Q79" s="36"/>
@@ -35233,13 +35233,13 @@
       <c r="Y79" s="54"/>
       <c r="Z79" s="36" t="n">
         <f aca="false">SUM(O79:Y79)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AA79" s="57"/>
       <c r="AB79" s="36"/>
       <c r="AC79" s="36" t="n">
         <f aca="false">[2]Aug!$AE$1</f>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="AD79" s="36"/>
       <c r="AE79" s="36"/>
@@ -35250,13 +35250,13 @@
       <c r="AJ79" s="54"/>
       <c r="AK79" s="36" t="n">
         <f aca="false">SUM(Z79:AJ79)</f>
-        <v>720</v>
+        <v>180</v>
       </c>
       <c r="AL79" s="57"/>
       <c r="AM79" s="36"/>
       <c r="AN79" s="36" t="n">
         <f aca="false">[2]Sep!$AE$1</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AO79" s="36"/>
       <c r="AP79" s="36"/>
@@ -35267,7 +35267,7 @@
       <c r="AU79" s="54"/>
       <c r="AV79" s="36" t="n">
         <f aca="false">SUM(AK79:AU79)</f>
-        <v>720</v>
+        <v>360</v>
       </c>
       <c r="AW79" s="57"/>
       <c r="AX79" s="36"/>
@@ -35284,13 +35284,13 @@
       <c r="BF79" s="54"/>
       <c r="BG79" s="36" t="n">
         <f aca="false">SUM(AV79:BF79)</f>
-        <v>720</v>
+        <v>360</v>
       </c>
       <c r="BH79" s="57"/>
       <c r="BI79" s="36"/>
       <c r="BJ79" s="36" t="n">
         <f aca="false">[2]Nov!$AE$1</f>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="BK79" s="36"/>
       <c r="BL79" s="36"/>
@@ -35301,13 +35301,13 @@
       <c r="BQ79" s="54"/>
       <c r="BR79" s="36" t="n">
         <f aca="false">SUM(BG79:BQ79)</f>
-        <v>1440</v>
+        <v>360</v>
       </c>
       <c r="BS79" s="57"/>
       <c r="BT79" s="36"/>
       <c r="BU79" s="36" t="n">
         <f aca="false">[2]Dec!$AE$1</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="BV79" s="36"/>
       <c r="BW79" s="36"/>
@@ -35318,7 +35318,7 @@
       <c r="CB79" s="54"/>
       <c r="CC79" s="36" t="n">
         <f aca="false">SUM(BR79:CB79)</f>
-        <v>1440</v>
+        <v>540</v>
       </c>
       <c r="CD79" s="57"/>
       <c r="CE79" s="36"/>
@@ -35335,13 +35335,13 @@
       <c r="CM79" s="54"/>
       <c r="CN79" s="36" t="n">
         <f aca="false">SUM(CC79:CM79)</f>
-        <v>1440</v>
+        <v>540</v>
       </c>
       <c r="CO79" s="57"/>
       <c r="CP79" s="36"/>
       <c r="CQ79" s="36" t="n">
         <f aca="false">[2]Feb!$AE$1</f>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="CR79" s="36"/>
       <c r="CS79" s="36"/>
@@ -35352,13 +35352,13 @@
       <c r="CX79" s="54"/>
       <c r="CY79" s="36" t="n">
         <f aca="false">SUM(CN79:CX79)</f>
-        <v>2160</v>
+        <v>540</v>
       </c>
       <c r="CZ79" s="57"/>
       <c r="DA79" s="36"/>
       <c r="DB79" s="36" t="n">
         <f aca="false">[2]Mar!$AE$1</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="DC79" s="36"/>
       <c r="DD79" s="36"/>
@@ -35369,7 +35369,7 @@
       <c r="DI79" s="54"/>
       <c r="DJ79" s="36" t="n">
         <f aca="false">SUM(CY79:DI79)</f>
-        <v>2160</v>
+        <v>720</v>
       </c>
       <c r="DK79" s="57"/>
       <c r="DL79" s="36"/>
@@ -35386,13 +35386,13 @@
       <c r="DT79" s="54"/>
       <c r="DU79" s="36" t="n">
         <f aca="false">SUM(DJ79:DT79)</f>
-        <v>2160</v>
+        <v>720</v>
       </c>
       <c r="DV79" s="57"/>
       <c r="DW79" s="36"/>
       <c r="DX79" s="36" t="n">
         <f aca="false">[2]May!$AE$1</f>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="DY79" s="36"/>
       <c r="DZ79" s="36"/>
@@ -35403,13 +35403,13 @@
       <c r="EE79" s="54"/>
       <c r="EF79" s="36" t="n">
         <f aca="false">SUM(DU79:EE79)</f>
-        <v>2880</v>
+        <v>720</v>
       </c>
       <c r="EG79" s="54"/>
       <c r="EI79" s="54"/>
       <c r="EJ79" s="36" t="n">
         <f aca="false">SUM(EF79:EH79)</f>
-        <v>2880</v>
+        <v>720</v>
       </c>
       <c r="EK79" s="54"/>
     </row>
@@ -35459,7 +35459,7 @@
       <c r="AB80" s="36"/>
       <c r="AC80" s="36" t="n">
         <f aca="false">[2]Aug!$AF$1</f>
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="AD80" s="36"/>
       <c r="AE80" s="36"/>
@@ -35470,13 +35470,13 @@
       <c r="AJ80" s="54"/>
       <c r="AK80" s="36" t="n">
         <f aca="false">SUM(Z80:AJ80)</f>
-        <v>900</v>
+        <v>1150</v>
       </c>
       <c r="AL80" s="57"/>
       <c r="AM80" s="36"/>
       <c r="AN80" s="36" t="n">
         <f aca="false">[2]Sep!$AF$1</f>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AO80" s="36"/>
       <c r="AP80" s="36"/>
@@ -35487,13 +35487,13 @@
       <c r="AU80" s="54"/>
       <c r="AV80" s="36" t="n">
         <f aca="false">SUM(AK80:AU80)</f>
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="AW80" s="57"/>
       <c r="AX80" s="36"/>
       <c r="AY80" s="36" t="n">
         <f aca="false">[2]Oct!$AF$1</f>
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AZ80" s="36"/>
       <c r="BA80" s="36"/>
@@ -35504,13 +35504,13 @@
       <c r="BF80" s="54"/>
       <c r="BG80" s="36" t="n">
         <f aca="false">SUM(AV80:BF80)</f>
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="BH80" s="57"/>
       <c r="BI80" s="36"/>
       <c r="BJ80" s="36" t="n">
         <f aca="false">[2]Nov!$AF$1</f>
-        <v>300</v>
+        <v>1468</v>
       </c>
       <c r="BK80" s="36"/>
       <c r="BL80" s="36"/>
@@ -35521,7 +35521,7 @@
       <c r="BQ80" s="54"/>
       <c r="BR80" s="36" t="n">
         <f aca="false">SUM(BG80:BQ80)</f>
-        <v>1800</v>
+        <v>3218</v>
       </c>
       <c r="BS80" s="57"/>
       <c r="BT80" s="36"/>
@@ -35538,7 +35538,7 @@
       <c r="CB80" s="54"/>
       <c r="CC80" s="36" t="n">
         <f aca="false">SUM(BR80:CB80)</f>
-        <v>2100</v>
+        <v>3518</v>
       </c>
       <c r="CD80" s="57"/>
       <c r="CE80" s="36"/>
@@ -35555,13 +35555,13 @@
       <c r="CM80" s="54"/>
       <c r="CN80" s="36" t="n">
         <f aca="false">SUM(CC80:CM80)</f>
-        <v>2400</v>
+        <v>3818</v>
       </c>
       <c r="CO80" s="57"/>
       <c r="CP80" s="36"/>
       <c r="CQ80" s="36" t="n">
         <f aca="false">[2]Feb!$AF$1</f>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="CR80" s="36"/>
       <c r="CS80" s="36"/>
@@ -35572,13 +35572,13 @@
       <c r="CX80" s="54"/>
       <c r="CY80" s="36" t="n">
         <f aca="false">SUM(CN80:CX80)</f>
-        <v>2700</v>
+        <v>3818</v>
       </c>
       <c r="CZ80" s="57"/>
       <c r="DA80" s="36"/>
       <c r="DB80" s="36" t="n">
         <f aca="false">[2]Mar!$AF$1</f>
-        <v>300</v>
+        <v>767</v>
       </c>
       <c r="DC80" s="36"/>
       <c r="DD80" s="36"/>
@@ -35589,7 +35589,7 @@
       <c r="DI80" s="54"/>
       <c r="DJ80" s="36" t="n">
         <f aca="false">SUM(CY80:DI80)</f>
-        <v>3000</v>
+        <v>4585</v>
       </c>
       <c r="DK80" s="57"/>
       <c r="DL80" s="36"/>
@@ -35606,13 +35606,13 @@
       <c r="DT80" s="54"/>
       <c r="DU80" s="36" t="n">
         <f aca="false">SUM(DJ80:DT80)</f>
-        <v>3300</v>
+        <v>4885</v>
       </c>
       <c r="DV80" s="57"/>
       <c r="DW80" s="36"/>
       <c r="DX80" s="36" t="n">
         <f aca="false">[2]May!$AF$1</f>
-        <v>2100</v>
+        <v>425</v>
       </c>
       <c r="DY80" s="36"/>
       <c r="DZ80" s="36"/>
@@ -35623,13 +35623,13 @@
       <c r="EE80" s="54"/>
       <c r="EF80" s="36" t="n">
         <f aca="false">SUM(DU80:EE80)</f>
-        <v>5400</v>
+        <v>5310</v>
       </c>
       <c r="EG80" s="54"/>
       <c r="EI80" s="54"/>
       <c r="EJ80" s="36" t="n">
         <f aca="false">SUM(EF80:EH80)</f>
-        <v>5400</v>
+        <v>5310</v>
       </c>
       <c r="EK80" s="54"/>
     </row>
@@ -36742,7 +36742,7 @@
       <c r="F85" s="36"/>
       <c r="G85" s="36" t="n">
         <f aca="false">[2]Jun!$AH$1</f>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="H85" s="36"/>
       <c r="I85" s="36"/>
@@ -36752,7 +36752,7 @@
       <c r="N85" s="57"/>
       <c r="O85" s="36" t="n">
         <f aca="false">SUM(D85:N85)</f>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="P85" s="57"/>
       <c r="Q85" s="36"/>
@@ -36769,7 +36769,7 @@
       <c r="Y85" s="54"/>
       <c r="Z85" s="36" t="n">
         <f aca="false">SUM(O85:Y85)</f>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="AA85" s="57"/>
       <c r="AB85" s="36"/>
@@ -36786,13 +36786,13 @@
       <c r="AJ85" s="54"/>
       <c r="AK85" s="36" t="n">
         <f aca="false">SUM(Z85:AJ85)</f>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="AL85" s="57"/>
       <c r="AM85" s="36"/>
       <c r="AN85" s="36" t="n">
         <f aca="false">[2]Sep!$AH$1</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AO85" s="36"/>
       <c r="AP85" s="36"/>
@@ -36803,7 +36803,7 @@
       <c r="AU85" s="54"/>
       <c r="AV85" s="36" t="n">
         <f aca="false">SUM(AK85:AU85)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="AW85" s="57"/>
       <c r="AX85" s="36"/>
@@ -36820,7 +36820,7 @@
       <c r="BF85" s="54"/>
       <c r="BG85" s="36" t="n">
         <f aca="false">SUM(AV85:BF85)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="BH85" s="57"/>
       <c r="BI85" s="36"/>
@@ -36837,7 +36837,7 @@
       <c r="BQ85" s="54"/>
       <c r="BR85" s="36" t="n">
         <f aca="false">SUM(BG85:BQ85)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="BS85" s="57"/>
       <c r="BT85" s="36"/>
@@ -36854,7 +36854,7 @@
       <c r="CB85" s="54"/>
       <c r="CC85" s="36" t="n">
         <f aca="false">SUM(BR85:CB85)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="CD85" s="57"/>
       <c r="CE85" s="36"/>
@@ -36871,7 +36871,7 @@
       <c r="CM85" s="54"/>
       <c r="CN85" s="36" t="n">
         <f aca="false">SUM(CC85:CM85)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="CO85" s="57"/>
       <c r="CP85" s="36"/>
@@ -36888,7 +36888,7 @@
       <c r="CX85" s="54"/>
       <c r="CY85" s="36" t="n">
         <f aca="false">SUM(CN85:CX85)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="CZ85" s="57"/>
       <c r="DA85" s="36"/>
@@ -36905,7 +36905,7 @@
       <c r="DI85" s="54"/>
       <c r="DJ85" s="36" t="n">
         <f aca="false">SUM(CY85:DI85)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="DK85" s="57"/>
       <c r="DL85" s="36"/>
@@ -36922,7 +36922,7 @@
       <c r="DT85" s="54"/>
       <c r="DU85" s="36" t="n">
         <f aca="false">SUM(DJ85:DT85)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="DV85" s="57"/>
       <c r="DW85" s="36"/>
@@ -36939,13 +36939,13 @@
       <c r="EE85" s="54"/>
       <c r="EF85" s="36" t="n">
         <f aca="false">SUM(DU85:EE85)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="EG85" s="54"/>
       <c r="EI85" s="54"/>
       <c r="EJ85" s="36" t="n">
         <f aca="false">SUM(EF85:EH85)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="EK85" s="54"/>
     </row>
@@ -38118,7 +38118,7 @@
       <c r="E91" s="54"/>
       <c r="F91" s="36" t="n">
         <f aca="false">SUM(F4:F90)</f>
-        <v>0</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="G91" s="36" t="n">
         <f aca="false">SUM(G4:G90)</f>
@@ -38151,12 +38151,12 @@
       <c r="N91" s="54"/>
       <c r="O91" s="36" t="n">
         <f aca="false">SUM(O4:O90)</f>
-        <v>0</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="P91" s="54"/>
       <c r="Q91" s="36" t="n">
         <f aca="false">SUM(Q4:Q90)</f>
-        <v>0</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="R91" s="36" t="n">
         <f aca="false">SUM(R4:R90)</f>
@@ -38189,12 +38189,12 @@
       <c r="Y91" s="54"/>
       <c r="Z91" s="36" t="n">
         <f aca="false">SUM(Z4:Z90)</f>
-        <v>0</v>
+        <v>-6.09361450187862E-011</v>
       </c>
       <c r="AA91" s="54"/>
       <c r="AB91" s="36" t="n">
         <f aca="false">SUM(AB4:AB90)</f>
-        <v>0</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="AC91" s="36" t="n">
         <f aca="false">SUM(AC4:AC90)</f>
@@ -38227,12 +38227,12 @@
       <c r="AJ91" s="54"/>
       <c r="AK91" s="36" t="n">
         <f aca="false">SUM(AK4:AK90)</f>
-        <v>0</v>
+        <v>-9.09494701772928E-011</v>
       </c>
       <c r="AL91" s="54"/>
       <c r="AM91" s="36" t="n">
         <f aca="false">SUM(AM4:AM90)</f>
-        <v>0</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="AN91" s="36" t="n">
         <f aca="false">SUM(AN4:AN90)</f>
@@ -38265,12 +38265,12 @@
       <c r="AU91" s="54"/>
       <c r="AV91" s="36" t="n">
         <f aca="false">SUM(AV4:AV90)</f>
-        <v>0</v>
+        <v>-1.21872290037572E-010</v>
       </c>
       <c r="AW91" s="54"/>
       <c r="AX91" s="36" t="n">
         <f aca="false">SUM(AX4:AX90)</f>
-        <v>9.54969436861575E-012</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="AY91" s="36" t="n">
         <f aca="false">SUM(AY4:AY90)</f>
@@ -38303,12 +38303,12 @@
       <c r="BF91" s="54"/>
       <c r="BG91" s="36" t="n">
         <f aca="false">SUM(BG4:BG90)</f>
-        <v>1.04591890703887E-011</v>
+        <v>-1.52340362546965E-010</v>
       </c>
       <c r="BH91" s="54"/>
       <c r="BI91" s="36" t="n">
         <f aca="false">SUM(BI4:BI90)</f>
-        <v>0</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="BJ91" s="36" t="n">
         <f aca="false">SUM(BJ4:BJ90)</f>
@@ -38341,12 +38341,12 @@
       <c r="BQ91" s="54"/>
       <c r="BR91" s="36" t="n">
         <f aca="false">SUM(BR4:BR90)</f>
-        <v>1.13686837721616E-011</v>
+        <v>-1.83263182407245E-010</v>
       </c>
       <c r="BS91" s="54"/>
       <c r="BT91" s="36" t="n">
         <f aca="false">SUM(BT4:BT90)</f>
-        <v>0</v>
+        <v>-3.09228198602796E-011</v>
       </c>
       <c r="BU91" s="36" t="n">
         <f aca="false">SUM(BU4:BU90)</f>
@@ -38379,12 +38379,12 @@
       <c r="CB91" s="54"/>
       <c r="CC91" s="36" t="n">
         <f aca="false">SUM(CC4:CC90)</f>
-        <v>1.13686837721616E-011</v>
+        <v>-2.12367012863979E-010</v>
       </c>
       <c r="CD91" s="54"/>
       <c r="CE91" s="36" t="n">
         <f aca="false">SUM(CE4:CE90)</f>
-        <v>0</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="CF91" s="36" t="n">
         <f aca="false">SUM(CF4:CF90)</f>
@@ -38417,12 +38417,12 @@
       <c r="CM91" s="54"/>
       <c r="CN91" s="36" t="n">
         <f aca="false">SUM(CN4:CN90)</f>
-        <v>1.13686837721616E-011</v>
+        <v>-2.41470843320712E-010</v>
       </c>
       <c r="CO91" s="54"/>
       <c r="CP91" s="36" t="n">
         <f aca="false">SUM(CP4:CP90)</f>
-        <v>0</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="CQ91" s="36" t="n">
         <f aca="false">SUM(CQ4:CQ90)</f>
@@ -38455,12 +38455,12 @@
       <c r="CX91" s="54"/>
       <c r="CY91" s="36" t="n">
         <f aca="false">SUM(CY4:CY90)</f>
-        <v>1.13686837721616E-011</v>
+        <v>-2.70574673777446E-010</v>
       </c>
       <c r="CZ91" s="54"/>
       <c r="DA91" s="36" t="n">
         <f aca="false">SUM(DA4:DA90)</f>
-        <v>0</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="DB91" s="36" t="n">
         <f aca="false">SUM(DB4:DB90)</f>
@@ -38493,12 +38493,12 @@
       <c r="DI91" s="54"/>
       <c r="DJ91" s="36" t="n">
         <f aca="false">SUM(DJ4:DJ90)</f>
-        <v>1.13686837721616E-011</v>
+        <v>-2.9967850423418E-010</v>
       </c>
       <c r="DK91" s="54"/>
       <c r="DL91" s="36" t="n">
         <f aca="false">SUM(DL4:DL90)</f>
-        <v>0</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="DM91" s="36" t="n">
         <f aca="false">SUM(DM4:DM90)</f>
@@ -38531,12 +38531,12 @@
       <c r="DT91" s="54"/>
       <c r="DU91" s="36" t="n">
         <f aca="false">SUM(DU4:DU90)</f>
-        <v>2.04636307898909E-011</v>
+        <v>-3.28782334690914E-010</v>
       </c>
       <c r="DV91" s="54"/>
       <c r="DW91" s="36" t="n">
         <f aca="false">SUM(DW4:DW90)</f>
-        <v>0</v>
+        <v>-3.04680725093931E-011</v>
       </c>
       <c r="DX91" s="36" t="n">
         <f aca="false">SUM(DX4:DX90)</f>
@@ -38569,7 +38569,7 @@
       <c r="EE91" s="54"/>
       <c r="EF91" s="36" t="n">
         <f aca="false">SUM(EF4:EF90)</f>
-        <v>2.04636307898909E-011</v>
+        <v>-3.57886165147647E-010</v>
       </c>
       <c r="EG91" s="54"/>
       <c r="EH91" s="36" t="n">
@@ -38579,7 +38579,7 @@
       <c r="EI91" s="54"/>
       <c r="EJ91" s="36" t="n">
         <f aca="false">SUM(EJ4:EJ90)</f>
-        <v>2.04636307898909E-011</v>
+        <v>-3.57886165147647E-010</v>
       </c>
       <c r="EK91" s="54"/>
     </row>
@@ -38960,55 +38960,55 @@
       </c>
       <c r="B4" s="71" t="n">
         <f aca="false">SUM(C4:N4)</f>
-        <v>77000</v>
+        <v>141600</v>
       </c>
       <c r="C4" s="72" t="n">
         <f aca="false">-TrialBalance!O53-0</f>
-        <v>5833.33333333333</v>
+        <v>11166.6666666667</v>
       </c>
       <c r="D4" s="72" t="n">
         <f aca="false">-TrialBalance!Z53-C4</f>
-        <v>5833.33333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="E4" s="72" t="n">
         <f aca="false">-TrialBalance!AK53-SUM(C4:D4)</f>
-        <v>5833.33333333333</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="F4" s="72" t="n">
         <f aca="false">-TrialBalance!AV53-SUM(C4:E4)</f>
-        <v>5833.33333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="G4" s="72" t="n">
         <f aca="false">-TrialBalance!BG53-SUM(C4:F4)</f>
-        <v>5833.33333333333</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="H4" s="72" t="n">
         <f aca="false">-TrialBalance!BR53-SUM(C4:G4)</f>
-        <v>5833.33333333333</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="I4" s="72" t="n">
         <f aca="false">-TrialBalance!CC53-SUM(C4:H4)</f>
-        <v>7000</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="J4" s="72" t="n">
         <f aca="false">-TrialBalance!CN53-SUM(C4:I4)</f>
-        <v>7000</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K4" s="72" t="n">
         <f aca="false">-TrialBalance!CY53-SUM(C4:J4)</f>
-        <v>7000</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="L4" s="72" t="n">
         <f aca="false">-TrialBalance!DJ53-SUM(C4:K4)</f>
-        <v>7000</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="M4" s="72" t="n">
         <f aca="false">-TrialBalance!DU53-SUM(C4:L4)</f>
-        <v>6999.99999999999</v>
+        <v>12166.6666666667</v>
       </c>
       <c r="N4" s="72" t="n">
         <f aca="false">-TrialBalance!EF53-SUM(C4:M4)</f>
-        <v>7000</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="O4" s="68"/>
     </row>
@@ -39018,55 +39018,55 @@
       </c>
       <c r="B5" s="71" t="n">
         <f aca="false">SUM(C5:N5)</f>
-        <v>4000</v>
+        <v>13600</v>
       </c>
       <c r="C5" s="72" t="n">
         <f aca="false">-TrialBalance!O54-0</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="D5" s="72" t="n">
         <f aca="false">-TrialBalance!Z54-C5</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E5" s="72" t="n">
         <f aca="false">-TrialBalance!AK54-SUM(C5:D5)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F5" s="72" t="n">
         <f aca="false">-TrialBalance!AV54-SUM(C5:E5)</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="G5" s="72" t="n">
         <f aca="false">-TrialBalance!BG54-SUM(C5:F5)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H5" s="72" t="n">
         <f aca="false">-TrialBalance!BR54-SUM(C5:G5)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I5" s="72" t="n">
         <f aca="false">-TrialBalance!CC54-SUM(C5:H5)</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="J5" s="72" t="n">
         <f aca="false">-TrialBalance!CN54-SUM(C5:I5)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K5" s="72" t="n">
         <f aca="false">-TrialBalance!CY54-SUM(C5:J5)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L5" s="72" t="n">
         <f aca="false">-TrialBalance!DJ54-SUM(C5:K5)</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="M5" s="72" t="n">
         <f aca="false">-TrialBalance!DU54-SUM(C5:L5)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N5" s="72" t="n">
         <f aca="false">-TrialBalance!EF54-SUM(C5:M5)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="O5" s="68"/>
     </row>
@@ -39076,7 +39076,7 @@
       </c>
       <c r="B6" s="71" t="n">
         <f aca="false">SUM(C6:N6)</f>
-        <v>5000</v>
+        <v>10300</v>
       </c>
       <c r="C6" s="72" t="n">
         <f aca="false">-TrialBalance!O55-0</f>
@@ -39084,7 +39084,7 @@
       </c>
       <c r="D6" s="72" t="n">
         <f aca="false">-TrialBalance!Z55-C6</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E6" s="72" t="n">
         <f aca="false">-TrialBalance!AK55-SUM(C6:D6)</f>
@@ -39100,7 +39100,7 @@
       </c>
       <c r="H6" s="72" t="n">
         <f aca="false">-TrialBalance!BR55-SUM(C6:G6)</f>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="I6" s="72" t="n">
         <f aca="false">-TrialBalance!CC55-SUM(C6:H6)</f>
@@ -39116,11 +39116,11 @@
       </c>
       <c r="L6" s="72" t="n">
         <f aca="false">-TrialBalance!DJ55-SUM(C6:K6)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M6" s="72" t="n">
         <f aca="false">-TrialBalance!DU55-SUM(C6:L6)</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="N6" s="72" t="n">
         <f aca="false">-TrialBalance!EF55-SUM(C6:M6)</f>
@@ -39134,11 +39134,11 @@
       </c>
       <c r="B7" s="71" t="n">
         <f aca="false">SUM(C7:N7)</f>
-        <v>500</v>
+        <v>3700</v>
       </c>
       <c r="C7" s="72" t="n">
         <f aca="false">-TrialBalance!O56</f>
-        <v>-0</v>
+        <v>700</v>
       </c>
       <c r="D7" s="72" t="n">
         <f aca="false">-TrialBalance!Z56-C7</f>
@@ -39146,15 +39146,15 @@
       </c>
       <c r="E7" s="72" t="n">
         <f aca="false">-TrialBalance!AK56-SUM(C7:D7)</f>
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F7" s="72" t="n">
         <f aca="false">-TrialBalance!AV56-SUM(C7:E7)</f>
-        <v>-0</v>
+        <v>700</v>
       </c>
       <c r="G7" s="72" t="n">
         <f aca="false">-TrialBalance!BG56-SUM(C7:F7)</f>
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H7" s="72" t="n">
         <f aca="false">-TrialBalance!BR56-SUM(C7:G7)</f>
@@ -39162,7 +39162,7 @@
       </c>
       <c r="I7" s="72" t="n">
         <f aca="false">-TrialBalance!CC56-SUM(C7:H7)</f>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J7" s="72" t="n">
         <f aca="false">-TrialBalance!CN56-SUM(C7:I7)</f>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="L7" s="72" t="n">
         <f aca="false">-TrialBalance!DJ56-SUM(C7:K7)</f>
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="M7" s="72" t="n">
         <f aca="false">-TrialBalance!DU56-SUM(C7:L7)</f>
@@ -39250,55 +39250,55 @@
       </c>
       <c r="B9" s="71" t="n">
         <f aca="false">SUM(B4:B8)</f>
-        <v>88583.3333333333</v>
+        <v>171283.333333334</v>
       </c>
       <c r="C9" s="74" t="n">
         <f aca="false">SUM(C4:C8)</f>
-        <v>6833.33333333333</v>
+        <v>13666.6666666667</v>
       </c>
       <c r="D9" s="71" t="n">
         <f aca="false">SUM(D4:D8)</f>
-        <v>5833.33333333333</v>
+        <v>13266.6666666667</v>
       </c>
       <c r="E9" s="71" t="n">
         <f aca="false">SUM(E4:E8)</f>
-        <v>7833.33333333333</v>
+        <v>15166.6666666667</v>
       </c>
       <c r="F9" s="71" t="n">
         <f aca="false">SUM(F4:F8)</f>
-        <v>6833.33333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="G9" s="71" t="n">
         <f aca="false">SUM(G4:G8)</f>
-        <v>7916.66666666666</v>
+        <v>15850</v>
       </c>
       <c r="H9" s="71" t="n">
         <f aca="false">SUM(H4:H8)</f>
-        <v>6333.33333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="I9" s="71" t="n">
         <f aca="false">SUM(I4:I8)</f>
-        <v>8000</v>
+        <v>15466.6666666667</v>
       </c>
       <c r="J9" s="71" t="n">
         <f aca="false">SUM(J4:J8)</f>
-        <v>10000</v>
+        <v>15266.6666666667</v>
       </c>
       <c r="K9" s="71" t="n">
         <f aca="false">SUM(K4:K8)</f>
-        <v>7000</v>
+        <v>13166.6666666667</v>
       </c>
       <c r="L9" s="71" t="n">
         <f aca="false">SUM(L4:L8)</f>
-        <v>8000</v>
+        <v>15366.6666666667</v>
       </c>
       <c r="M9" s="71" t="n">
         <f aca="false">SUM(M4:M8)</f>
-        <v>6999.99999999999</v>
+        <v>14466.6666666667</v>
       </c>
       <c r="N9" s="71" t="n">
         <f aca="false">SUM(N4:N8)</f>
-        <v>7000</v>
+        <v>11666.6666666667</v>
       </c>
       <c r="O9" s="75"/>
     </row>
@@ -39327,7 +39327,7 @@
       </c>
       <c r="B11" s="71" t="n">
         <f aca="false">SUM(C11:N11)</f>
-        <v>2400</v>
+        <v>6540</v>
       </c>
       <c r="C11" s="72" t="n">
         <f aca="false">TrialBalance!O60-0</f>
@@ -39335,11 +39335,11 @@
       </c>
       <c r="D11" s="72" t="n">
         <f aca="false">TrialBalance!Z60-C11</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="E11" s="72" t="n">
         <f aca="false">TrialBalance!AK60-SUM(C11:D11)</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="F11" s="72" t="n">
         <f aca="false">TrialBalance!AV60-SUM(C11:E11)</f>
@@ -39347,11 +39347,11 @@
       </c>
       <c r="G11" s="72" t="n">
         <f aca="false">TrialBalance!BG60-SUM(C11:F11)</f>
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H11" s="72" t="n">
         <f aca="false">TrialBalance!BR60-SUM(C11:G11)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="I11" s="72" t="n">
         <f aca="false">TrialBalance!CC60-SUM(C11:H11)</f>
@@ -39359,11 +39359,11 @@
       </c>
       <c r="J11" s="72" t="n">
         <f aca="false">TrialBalance!CN60-SUM(C11:I11)</f>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="K11" s="72" t="n">
         <f aca="false">TrialBalance!CY60-SUM(C11:J11)</f>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="L11" s="72" t="n">
         <f aca="false">TrialBalance!DJ60-SUM(C11:K11)</f>
@@ -39371,11 +39371,11 @@
       </c>
       <c r="M11" s="72" t="n">
         <f aca="false">TrialBalance!DU60-SUM(C11:L11)</f>
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="N11" s="72" t="n">
         <f aca="false">TrialBalance!EF60-SUM(C11:M11)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O11" s="68"/>
     </row>
@@ -39385,7 +39385,7 @@
       </c>
       <c r="B12" s="71" t="n">
         <f aca="false">SUM(C12:N12)</f>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="C12" s="72" t="n">
         <f aca="false">TrialBalance!O61-0</f>
@@ -39397,7 +39397,7 @@
       </c>
       <c r="E12" s="72" t="n">
         <f aca="false">TrialBalance!AK61-SUM(C12:D12)</f>
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="F12" s="72" t="n">
         <f aca="false">TrialBalance!AV61-SUM(C12:E12)</f>
@@ -39409,7 +39409,7 @@
       </c>
       <c r="H12" s="72" t="n">
         <f aca="false">TrialBalance!BR61-SUM(C12:G12)</f>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="I12" s="72" t="n">
         <f aca="false">TrialBalance!CC61-SUM(C12:H12)</f>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="J12" s="72" t="n">
         <f aca="false">TrialBalance!CN61-SUM(C12:I12)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="K12" s="72" t="n">
         <f aca="false">TrialBalance!CY61-SUM(C12:J12)</f>
@@ -39443,55 +39443,55 @@
       </c>
       <c r="B13" s="71" t="n">
         <f aca="false">SUM(C13:N13)</f>
-        <v>720</v>
+        <v>3204</v>
       </c>
       <c r="C13" s="79" t="n">
         <f aca="false">TrialBalance!O62-0</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="D13" s="72" t="n">
         <f aca="false">TrialBalance!Z62-C13</f>
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="E13" s="72" t="n">
         <f aca="false">TrialBalance!AK62-SUM(C13:D13)</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="F13" s="79" t="n">
         <f aca="false">TrialBalance!AV62-SUM(C13:E13)</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="G13" s="72" t="n">
         <f aca="false">TrialBalance!BG62-SUM(C13:F13)</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="H13" s="72" t="n">
         <f aca="false">TrialBalance!BR62-SUM(C13:G13)</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="I13" s="72" t="n">
         <f aca="false">TrialBalance!CC62-SUM(C13:H13)</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="J13" s="72" t="n">
         <f aca="false">TrialBalance!CN62-SUM(C13:I13)</f>
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="K13" s="72" t="n">
         <f aca="false">TrialBalance!CY62-SUM(C13:J13)</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="L13" s="72" t="n">
         <f aca="false">TrialBalance!DJ62-SUM(C13:K13)</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="M13" s="72" t="n">
         <f aca="false">TrialBalance!DU62-SUM(C13:L13)</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="N13" s="72" t="n">
         <f aca="false">TrialBalance!EF62-SUM(C13:M13)</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="O13" s="68"/>
     </row>
@@ -39501,55 +39501,55 @@
       </c>
       <c r="B14" s="71" t="n">
         <f aca="false">SUM(B11:B13)</f>
-        <v>9120</v>
+        <v>17744</v>
       </c>
       <c r="C14" s="74" t="n">
         <f aca="false">SUM(C11:C13)</f>
-        <v>600</v>
+        <v>885</v>
       </c>
       <c r="D14" s="71" t="n">
         <f aca="false">SUM(D11:D13)</f>
-        <v>360</v>
+        <v>969</v>
       </c>
       <c r="E14" s="71" t="n">
         <f aca="false">SUM(E11:E13)</f>
-        <v>3600</v>
+        <v>5645</v>
       </c>
       <c r="F14" s="71" t="n">
         <f aca="false">SUM(F11:F13)</f>
-        <v>720</v>
+        <v>969</v>
       </c>
       <c r="G14" s="71" t="n">
         <f aca="false">SUM(G11:G13)</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="H14" s="71" t="n">
         <f aca="false">SUM(H11:H13)</f>
-        <v>2400</v>
+        <v>489</v>
       </c>
       <c r="I14" s="71" t="n">
         <f aca="false">SUM(I11:I13)</f>
-        <v>480</v>
+        <v>765</v>
       </c>
       <c r="J14" s="71" t="n">
         <f aca="false">SUM(J11:J13)</f>
-        <v>360</v>
+        <v>4089</v>
       </c>
       <c r="K14" s="71" t="n">
         <f aca="false">SUM(K11:K13)</f>
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="L14" s="71" t="n">
         <f aca="false">SUM(L11:L13)</f>
-        <v>600</v>
+        <v>849</v>
       </c>
       <c r="M14" s="71" t="n">
         <f aca="false">SUM(M11:M13)</f>
-        <v>0</v>
+        <v>945</v>
       </c>
       <c r="N14" s="71" t="n">
         <f aca="false">SUM(N11:N13)</f>
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="O14" s="75"/>
     </row>
@@ -39576,55 +39576,55 @@
       </c>
       <c r="B16" s="71" t="n">
         <f aca="false">B9-B14</f>
-        <v>79463.3333333333</v>
+        <v>153539.333333334</v>
       </c>
       <c r="C16" s="71" t="n">
         <f aca="false">C9-C14</f>
-        <v>6233.33333333333</v>
+        <v>12781.6666666667</v>
       </c>
       <c r="D16" s="71" t="n">
         <f aca="false">D9-D14</f>
-        <v>5473.33333333333</v>
+        <v>12297.6666666667</v>
       </c>
       <c r="E16" s="71" t="n">
         <f aca="false">E9-E14</f>
-        <v>4233.33333333333</v>
+        <v>9521.6666666667</v>
       </c>
       <c r="F16" s="71" t="n">
         <f aca="false">F9-F14</f>
-        <v>6113.33333333333</v>
+        <v>12997.6666666667</v>
       </c>
       <c r="G16" s="71" t="n">
         <f aca="false">G9-G14</f>
-        <v>7916.66666666666</v>
+        <v>15025</v>
       </c>
       <c r="H16" s="71" t="n">
         <f aca="false">H9-H14</f>
-        <v>3933.33333333333</v>
+        <v>13477.6666666667</v>
       </c>
       <c r="I16" s="71" t="n">
         <f aca="false">I9-I14</f>
-        <v>7520</v>
+        <v>14701.6666666667</v>
       </c>
       <c r="J16" s="71" t="n">
         <f aca="false">J9-J14</f>
-        <v>9640</v>
+        <v>11177.6666666667</v>
       </c>
       <c r="K16" s="71" t="n">
         <f aca="false">K9-K14</f>
-        <v>7000</v>
+        <v>12401.6666666667</v>
       </c>
       <c r="L16" s="71" t="n">
         <f aca="false">L9-L14</f>
-        <v>7400</v>
+        <v>14517.6666666667</v>
       </c>
       <c r="M16" s="71" t="n">
         <f aca="false">M9-M14</f>
-        <v>6999.99999999999</v>
+        <v>13521.6666666667</v>
       </c>
       <c r="N16" s="71" t="n">
         <f aca="false">N9-N14</f>
-        <v>7000</v>
+        <v>11117.6666666667</v>
       </c>
       <c r="O16" s="75"/>
     </row>
@@ -39747,11 +39747,11 @@
       </c>
       <c r="K19" s="72" t="n">
         <f aca="false">TrialBalance!CY66-SUM(C19:J19)</f>
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="L19" s="72" t="n">
         <f aca="false">TrialBalance!DJ66-SUM(C19:K19)</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M19" s="72" t="n">
         <f aca="false">TrialBalance!DU66-SUM(C19:L19)</f>
@@ -39909,7 +39909,7 @@
       </c>
       <c r="H22" s="72" t="n">
         <f aca="false">TrialBalance!BR69-SUM(C22:G22)</f>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I22" s="72" t="n">
         <f aca="false">TrialBalance!CC69-SUM(C22:H22)</f>
@@ -39921,11 +39921,11 @@
       </c>
       <c r="K22" s="72" t="n">
         <f aca="false">TrialBalance!CY69-SUM(C22:J22)</f>
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="L22" s="72" t="n">
         <f aca="false">TrialBalance!DJ69-SUM(C22:K22)</f>
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="M22" s="72" t="n">
         <f aca="false">TrialBalance!DU69-SUM(C22:L22)</f>
@@ -39943,7 +39943,7 @@
       </c>
       <c r="B23" s="71" t="n">
         <f aca="false">SUM(C23:N23)</f>
-        <v>720</v>
+        <v>960</v>
       </c>
       <c r="C23" s="72" t="n">
         <f aca="false">TrialBalance!O70-0</f>
@@ -39951,7 +39951,7 @@
       </c>
       <c r="D23" s="72" t="n">
         <f aca="false">TrialBalance!Z70-C23</f>
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="E23" s="72" t="n">
         <f aca="false">TrialBalance!AK70-SUM(C23:D23)</f>
@@ -39959,7 +39959,7 @@
       </c>
       <c r="F23" s="72" t="n">
         <f aca="false">TrialBalance!AV70-SUM(C23:E23)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G23" s="72" t="n">
         <f aca="false">TrialBalance!BG70-SUM(C23:F23)</f>
@@ -39967,7 +39967,7 @@
       </c>
       <c r="H23" s="72" t="n">
         <f aca="false">TrialBalance!BR70-SUM(C23:G23)</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I23" s="72" t="n">
         <f aca="false">TrialBalance!CC70-SUM(C23:H23)</f>
@@ -39983,7 +39983,7 @@
       </c>
       <c r="L23" s="72" t="n">
         <f aca="false">TrialBalance!DJ70-SUM(C23:K23)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M23" s="72" t="n">
         <f aca="false">TrialBalance!DU70-SUM(C23:L23)</f>
@@ -39991,7 +39991,7 @@
       </c>
       <c r="N23" s="72" t="n">
         <f aca="false">TrialBalance!EF70-SUM(C23:M23)</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="O23" s="68"/>
     </row>
@@ -40001,7 +40001,7 @@
       </c>
       <c r="B24" s="71" t="n">
         <f aca="false">SUM(C24:N24)</f>
-        <v>960</v>
+        <v>1620</v>
       </c>
       <c r="C24" s="72" t="n">
         <f aca="false">TrialBalance!O71-0</f>
@@ -40009,7 +40009,7 @@
       </c>
       <c r="D24" s="72" t="n">
         <f aca="false">TrialBalance!Z71-C24</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E24" s="72" t="n">
         <f aca="false">TrialBalance!AK71-SUM(C24:D24)</f>
@@ -40017,7 +40017,7 @@
       </c>
       <c r="F24" s="72" t="n">
         <f aca="false">TrialBalance!AV71-SUM(C24:E24)</f>
-        <v>960</v>
+        <v>480</v>
       </c>
       <c r="G24" s="72" t="n">
         <f aca="false">TrialBalance!BG71-SUM(C24:F24)</f>
@@ -40025,7 +40025,7 @@
       </c>
       <c r="H24" s="72" t="n">
         <f aca="false">TrialBalance!BR71-SUM(C24:G24)</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="I24" s="72" t="n">
         <f aca="false">TrialBalance!CC71-SUM(C24:H24)</f>
@@ -40041,11 +40041,11 @@
       </c>
       <c r="L24" s="72" t="n">
         <f aca="false">TrialBalance!DJ71-SUM(C24:K24)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M24" s="72" t="n">
         <f aca="false">TrialBalance!DU71-SUM(C24:L24)</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="N24" s="72" t="n">
         <f aca="false">TrialBalance!EF71-SUM(C24:M24)</f>
@@ -40059,11 +40059,11 @@
       </c>
       <c r="B25" s="71" t="n">
         <f aca="false">SUM(C25:N25)</f>
-        <v>840</v>
+        <v>1140</v>
       </c>
       <c r="C25" s="72" t="n">
         <f aca="false">TrialBalance!O72-0</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D25" s="72" t="n">
         <f aca="false">TrialBalance!Z72-C25</f>
@@ -40075,19 +40075,19 @@
       </c>
       <c r="F25" s="72" t="n">
         <f aca="false">TrialBalance!AV72-SUM(C25:E25)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G25" s="72" t="n">
         <f aca="false">TrialBalance!BG72-SUM(C25:F25)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H25" s="72" t="n">
         <f aca="false">TrialBalance!BR72-SUM(C25:G25)</f>
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="I25" s="72" t="n">
         <f aca="false">TrialBalance!CC72-SUM(C25:H25)</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J25" s="72" t="n">
         <f aca="false">TrialBalance!CN72-SUM(C25:I25)</f>
@@ -40099,7 +40099,7 @@
       </c>
       <c r="L25" s="72" t="n">
         <f aca="false">TrialBalance!DJ72-SUM(C25:K25)</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M25" s="72" t="n">
         <f aca="false">TrialBalance!DU72-SUM(C25:L25)</f>
@@ -40117,55 +40117,55 @@
       </c>
       <c r="B26" s="71" t="n">
         <f aca="false">SUM(C26:N26)</f>
-        <v>324</v>
+        <v>1578</v>
       </c>
       <c r="C26" s="72" t="n">
         <f aca="false">TrialBalance!O73-0</f>
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="D26" s="72" t="n">
         <f aca="false">TrialBalance!Z73-C26</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E26" s="72" t="n">
         <f aca="false">TrialBalance!AK73-SUM(C26:D26)</f>
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="F26" s="72" t="n">
         <f aca="false">TrialBalance!AV73-SUM(C26:E26)</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="G26" s="72" t="n">
         <f aca="false">TrialBalance!BG73-SUM(C26:F26)</f>
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="H26" s="72" t="n">
         <f aca="false">TrialBalance!BR73-SUM(C26:G26)</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I26" s="72" t="n">
         <f aca="false">TrialBalance!CC73-SUM(C26:H26)</f>
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="J26" s="72" t="n">
         <f aca="false">TrialBalance!CN73-SUM(C26:I26)</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="K26" s="72" t="n">
         <f aca="false">TrialBalance!CY73-SUM(C26:J26)</f>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="L26" s="72" t="n">
         <f aca="false">TrialBalance!DJ73-SUM(C26:K26)</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M26" s="72" t="n">
         <f aca="false">TrialBalance!DU73-SUM(C26:L26)</f>
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="N26" s="72" t="n">
         <f aca="false">TrialBalance!EF73-SUM(C26:M26)</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="O26" s="68"/>
     </row>
@@ -40175,7 +40175,7 @@
       </c>
       <c r="B27" s="71" t="n">
         <f aca="false">SUM(C27:N27)</f>
-        <v>1800</v>
+        <v>4560</v>
       </c>
       <c r="C27" s="72" t="n">
         <f aca="false">TrialBalance!O74-0</f>
@@ -40183,7 +40183,7 @@
       </c>
       <c r="D27" s="72" t="n">
         <f aca="false">TrialBalance!Z74-C27</f>
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="E27" s="72" t="n">
         <f aca="false">TrialBalance!AK74-SUM(C27:D27)</f>
@@ -40191,7 +40191,7 @@
       </c>
       <c r="F27" s="72" t="n">
         <f aca="false">TrialBalance!AV74-SUM(C27:E27)</f>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G27" s="72" t="n">
         <f aca="false">TrialBalance!BG74-SUM(C27:F27)</f>
@@ -40203,7 +40203,7 @@
       </c>
       <c r="I27" s="72" t="n">
         <f aca="false">TrialBalance!CC74-SUM(C27:H27)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="J27" s="72" t="n">
         <f aca="false">TrialBalance!CN74-SUM(C27:I27)</f>
@@ -40215,7 +40215,7 @@
       </c>
       <c r="L27" s="72" t="n">
         <f aca="false">TrialBalance!DJ74-SUM(C27:K27)</f>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="M27" s="72" t="n">
         <f aca="false">TrialBalance!DU74-SUM(C27:L27)</f>
@@ -40233,55 +40233,55 @@
       </c>
       <c r="B28" s="71" t="n">
         <f aca="false">SUM(C28:N28)</f>
-        <v>960</v>
+        <v>1962</v>
       </c>
       <c r="C28" s="72" t="n">
         <f aca="false">TrialBalance!O75-0</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="D28" s="72" t="n">
         <f aca="false">TrialBalance!Z75-C28</f>
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="E28" s="72" t="n">
         <f aca="false">TrialBalance!AK75-SUM(C28:D28)</f>
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="F28" s="72" t="n">
         <f aca="false">TrialBalance!AV75-SUM(C28:E28)</f>
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="G28" s="72" t="n">
         <f aca="false">TrialBalance!BG75-SUM(C28:F28)</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="H28" s="72" t="n">
         <f aca="false">TrialBalance!BR75-SUM(C28:G28)</f>
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="I28" s="72" t="n">
         <f aca="false">TrialBalance!CC75-SUM(C28:H28)</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="J28" s="72" t="n">
         <f aca="false">TrialBalance!CN75-SUM(C28:I28)</f>
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="K28" s="72" t="n">
         <f aca="false">TrialBalance!CY75-SUM(C28:J28)</f>
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="L28" s="72" t="n">
         <f aca="false">TrialBalance!DJ75-SUM(C28:K28)</f>
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="M28" s="72" t="n">
         <f aca="false">TrialBalance!DU75-SUM(C28:L28)</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="N28" s="72" t="n">
         <f aca="false">TrialBalance!EF75-SUM(C28:M28)</f>
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="O28" s="68"/>
     </row>
@@ -40291,55 +40291,55 @@
       </c>
       <c r="B29" s="71" t="n">
         <f aca="false">SUM(C29:N29)</f>
-        <v>936</v>
+        <v>1860</v>
       </c>
       <c r="C29" s="72" t="n">
         <f aca="false">TrialBalance!O76-0</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D29" s="72" t="n">
         <f aca="false">TrialBalance!Z76-C29</f>
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="E29" s="72" t="n">
         <f aca="false">TrialBalance!AK76-SUM(C29:D29)</f>
-        <v>480</v>
+        <v>272</v>
       </c>
       <c r="F29" s="72" t="n">
         <f aca="false">TrialBalance!AV76-SUM(C29:E29)</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G29" s="72" t="n">
         <f aca="false">TrialBalance!BG76-SUM(C29:F29)</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="H29" s="72" t="n">
         <f aca="false">TrialBalance!BR76-SUM(C29:G29)</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="I29" s="72" t="n">
         <f aca="false">TrialBalance!CC76-SUM(C29:H29)</f>
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="J29" s="72" t="n">
         <f aca="false">TrialBalance!CN76-SUM(C29:I29)</f>
-        <v>360</v>
+        <v>164</v>
       </c>
       <c r="K29" s="72" t="n">
         <f aca="false">TrialBalance!CY76-SUM(C29:J29)</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L29" s="72" t="n">
         <f aca="false">TrialBalance!DJ76-SUM(C29:K29)</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M29" s="72" t="n">
         <f aca="false">TrialBalance!DU76-SUM(C29:L29)</f>
-        <v>96</v>
+        <v>368</v>
       </c>
       <c r="N29" s="72" t="n">
         <f aca="false">TrialBalance!EF76-SUM(C29:M29)</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="O29" s="68"/>
     </row>
@@ -40349,55 +40349,55 @@
       </c>
       <c r="B30" s="71" t="n">
         <f aca="false">SUM(C30:N30)</f>
-        <v>2400</v>
+        <v>7598.25</v>
       </c>
       <c r="C30" s="72" t="n">
         <f aca="false">TrialBalance!O77-0</f>
-        <v>1080</v>
+        <v>602.25</v>
       </c>
       <c r="D30" s="72" t="n">
         <f aca="false">TrialBalance!Z77-C30</f>
-        <v>120</v>
+        <v>666</v>
       </c>
       <c r="E30" s="72" t="n">
         <f aca="false">TrialBalance!AK77-SUM(C30:D30)</f>
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="F30" s="72" t="n">
         <f aca="false">TrialBalance!AV77-SUM(C30:E30)</f>
-        <v>840</v>
+        <v>584.25</v>
       </c>
       <c r="G30" s="72" t="n">
         <f aca="false">TrialBalance!BG77-SUM(C30:F30)</f>
-        <v>120</v>
+        <v>602.25</v>
       </c>
       <c r="H30" s="72" t="n">
         <f aca="false">TrialBalance!BR77-SUM(C30:G30)</f>
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="I30" s="72" t="n">
         <f aca="false">TrialBalance!CC77-SUM(C30:H30)</f>
-        <v>0</v>
+        <v>606.75</v>
       </c>
       <c r="J30" s="72" t="n">
         <f aca="false">TrialBalance!CN77-SUM(C30:I30)</f>
-        <v>120</v>
+        <v>645</v>
       </c>
       <c r="K30" s="72" t="n">
         <f aca="false">TrialBalance!CY77-SUM(C30:J30)</f>
-        <v>0</v>
+        <v>613.5</v>
       </c>
       <c r="L30" s="72" t="n">
         <f aca="false">TrialBalance!DJ77-SUM(C30:K30)</f>
-        <v>0</v>
+        <v>638.25</v>
       </c>
       <c r="M30" s="72" t="n">
         <f aca="false">TrialBalance!DU77-SUM(C30:L30)</f>
-        <v>120</v>
+        <v>595.5</v>
       </c>
       <c r="N30" s="72" t="n">
         <f aca="false">TrialBalance!EF77-SUM(C30:M30)</f>
-        <v>0</v>
+        <v>682.5</v>
       </c>
       <c r="O30" s="68"/>
     </row>
@@ -40407,11 +40407,11 @@
       </c>
       <c r="B31" s="71" t="n">
         <f aca="false">SUM(C31:N31)</f>
-        <v>960</v>
+        <v>1800</v>
       </c>
       <c r="C31" s="72" t="n">
         <f aca="false">TrialBalance!O78-0</f>
-        <v>960</v>
+        <v>1440</v>
       </c>
       <c r="D31" s="72" t="n">
         <f aca="false">TrialBalance!Z78-C31</f>
@@ -40435,7 +40435,7 @@
       </c>
       <c r="I31" s="72" t="n">
         <f aca="false">TrialBalance!CC78-SUM(C31:H31)</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="J31" s="72" t="n">
         <f aca="false">TrialBalance!CN78-SUM(C31:I31)</f>
@@ -40465,11 +40465,11 @@
       </c>
       <c r="B32" s="71" t="n">
         <f aca="false">SUM(C32:N32)</f>
-        <v>2880</v>
+        <v>720</v>
       </c>
       <c r="C32" s="72" t="n">
         <f aca="false">TrialBalance!O79-0</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D32" s="72" t="n">
         <f aca="false">TrialBalance!Z79-C32</f>
@@ -40477,11 +40477,11 @@
       </c>
       <c r="E32" s="72" t="n">
         <f aca="false">TrialBalance!AK79-SUM(C32:D32)</f>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="F32" s="72" t="n">
         <f aca="false">TrialBalance!AV79-SUM(C32:E32)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G32" s="72" t="n">
         <f aca="false">TrialBalance!BG79-SUM(C32:F32)</f>
@@ -40489,11 +40489,11 @@
       </c>
       <c r="H32" s="72" t="n">
         <f aca="false">TrialBalance!BR79-SUM(C32:G32)</f>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="I32" s="72" t="n">
         <f aca="false">TrialBalance!CC79-SUM(C32:H32)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J32" s="72" t="n">
         <f aca="false">TrialBalance!CN79-SUM(C32:I32)</f>
@@ -40501,11 +40501,11 @@
       </c>
       <c r="K32" s="72" t="n">
         <f aca="false">TrialBalance!CY79-SUM(C32:J32)</f>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="L32" s="72" t="n">
         <f aca="false">TrialBalance!DJ79-SUM(C32:K32)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M32" s="72" t="n">
         <f aca="false">TrialBalance!DU79-SUM(C32:L32)</f>
@@ -40513,7 +40513,7 @@
       </c>
       <c r="N32" s="72" t="n">
         <f aca="false">TrialBalance!EF79-SUM(C32:M32)</f>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="O32" s="68"/>
     </row>
@@ -40523,7 +40523,7 @@
       </c>
       <c r="B33" s="71" t="n">
         <f aca="false">SUM(C33:N33)</f>
-        <v>5400</v>
+        <v>5310</v>
       </c>
       <c r="C33" s="72" t="n">
         <f aca="false">TrialBalance!O80-0</f>
@@ -40535,19 +40535,19 @@
       </c>
       <c r="E33" s="72" t="n">
         <f aca="false">TrialBalance!AK80-SUM(C33:D33)</f>
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="F33" s="72" t="n">
         <f aca="false">TrialBalance!AV80-SUM(C33:E33)</f>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G33" s="72" t="n">
         <f aca="false">TrialBalance!BG80-SUM(C33:F33)</f>
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="H33" s="72" t="n">
         <f aca="false">TrialBalance!BR80-SUM(C33:G33)</f>
-        <v>300</v>
+        <v>1468</v>
       </c>
       <c r="I33" s="72" t="n">
         <f aca="false">TrialBalance!CC80-SUM(C33:H33)</f>
@@ -40559,11 +40559,11 @@
       </c>
       <c r="K33" s="72" t="n">
         <f aca="false">TrialBalance!CY80-SUM(C33:J33)</f>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L33" s="72" t="n">
         <f aca="false">TrialBalance!DJ80-SUM(C33:K33)</f>
-        <v>300</v>
+        <v>767</v>
       </c>
       <c r="M33" s="72" t="n">
         <f aca="false">TrialBalance!DU80-SUM(C33:L33)</f>
@@ -40571,7 +40571,7 @@
       </c>
       <c r="N33" s="72" t="n">
         <f aca="false">TrialBalance!EF80-SUM(C33:M33)</f>
-        <v>2100</v>
+        <v>425</v>
       </c>
       <c r="O33" s="68"/>
     </row>
@@ -40813,11 +40813,11 @@
       </c>
       <c r="B38" s="71" t="n">
         <f aca="false">SUM(C38:N38)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="C38" s="72" t="n">
         <f aca="false">TrialBalance!O85-0</f>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="D38" s="72" t="n">
         <f aca="false">TrialBalance!Z85-C38</f>
@@ -40829,7 +40829,7 @@
       </c>
       <c r="F38" s="72" t="n">
         <f aca="false">TrialBalance!AV85-SUM(C38:E38)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G38" s="72" t="n">
         <f aca="false">TrialBalance!BG85-SUM(C38:F38)</f>
@@ -40987,55 +40987,55 @@
       </c>
       <c r="B41" s="71" t="n">
         <f aca="false">SUM(B18:B40)</f>
-        <v>42420</v>
+        <v>53948.25</v>
       </c>
       <c r="C41" s="74" t="n">
         <f aca="false">SUM(C18:C40)</f>
-        <v>6180</v>
+        <v>4226.25</v>
       </c>
       <c r="D41" s="71" t="n">
         <f aca="false">SUM(D18:D40)</f>
-        <v>3360</v>
+        <v>3606</v>
       </c>
       <c r="E41" s="71" t="n">
         <f aca="false">SUM(E18:E40)</f>
-        <v>3240</v>
+        <v>3412</v>
       </c>
       <c r="F41" s="71" t="n">
         <f aca="false">SUM(F18:F40)</f>
-        <v>3360</v>
+        <v>6590.25</v>
       </c>
       <c r="G41" s="71" t="n">
         <f aca="false">SUM(G18:G40)</f>
-        <v>2480</v>
+        <v>3880.25</v>
       </c>
       <c r="H41" s="71" t="n">
         <f aca="false">SUM(H18:H40)</f>
-        <v>3120</v>
+        <v>4486</v>
       </c>
       <c r="I41" s="71" t="n">
         <f aca="false">SUM(I18:I40)</f>
-        <v>1704</v>
+        <v>6240.75</v>
       </c>
       <c r="J41" s="71" t="n">
         <f aca="false">SUM(J18:J40)</f>
-        <v>2280</v>
+        <v>2829</v>
       </c>
       <c r="K41" s="71" t="n">
         <f aca="false">SUM(K18:K40)</f>
-        <v>7900</v>
+        <v>3219.5</v>
       </c>
       <c r="L41" s="71" t="n">
         <f aca="false">SUM(L18:L40)</f>
-        <v>2520</v>
+        <v>9129.25</v>
       </c>
       <c r="M41" s="71" t="n">
         <f aca="false">SUM(M18:M40)</f>
-        <v>2136</v>
+        <v>3451.5</v>
       </c>
       <c r="N41" s="71" t="n">
         <f aca="false">SUM(N18:N40)</f>
-        <v>4140</v>
+        <v>2877.5</v>
       </c>
       <c r="O41" s="68"/>
     </row>
@@ -41062,55 +41062,55 @@
       </c>
       <c r="B43" s="71" t="n">
         <f aca="false">B16-B41</f>
-        <v>37043.3333333333</v>
+        <v>99591.0833333338</v>
       </c>
       <c r="C43" s="71" t="n">
         <f aca="false">C16-C41</f>
-        <v>53.3333333333303</v>
+        <v>8555.4166666667</v>
       </c>
       <c r="D43" s="71" t="n">
         <f aca="false">D16-D41</f>
-        <v>2113.33333333333</v>
+        <v>8691.6666666667</v>
       </c>
       <c r="E43" s="71" t="n">
         <f aca="false">E16-E41</f>
-        <v>993.333333333332</v>
+        <v>6109.6666666667</v>
       </c>
       <c r="F43" s="71" t="n">
         <f aca="false">F16-F41</f>
-        <v>2753.33333333333</v>
+        <v>6407.4166666667</v>
       </c>
       <c r="G43" s="71" t="n">
         <f aca="false">G16-G41</f>
-        <v>5436.66666666666</v>
+        <v>11144.75</v>
       </c>
       <c r="H43" s="71" t="n">
         <f aca="false">H16-H41</f>
-        <v>813.333333333329</v>
+        <v>8991.6666666667</v>
       </c>
       <c r="I43" s="71" t="n">
         <f aca="false">I16-I41</f>
-        <v>5816</v>
+        <v>8460.9166666667</v>
       </c>
       <c r="J43" s="71" t="n">
         <f aca="false">J16-J41</f>
-        <v>7360</v>
+        <v>8348.6666666667</v>
       </c>
       <c r="K43" s="71" t="n">
         <f aca="false">K16-K41</f>
-        <v>-900</v>
+        <v>9182.1666666667</v>
       </c>
       <c r="L43" s="71" t="n">
         <f aca="false">L16-L41</f>
-        <v>4880</v>
+        <v>5388.4166666667</v>
       </c>
       <c r="M43" s="71" t="n">
         <f aca="false">M16-M41</f>
-        <v>4863.99999999999</v>
+        <v>10070.1666666667</v>
       </c>
       <c r="N43" s="71" t="n">
         <f aca="false">N16-N41</f>
-        <v>2860</v>
+        <v>8240.1666666667</v>
       </c>
       <c r="O43" s="68"/>
     </row>
@@ -41178,55 +41178,55 @@
       </c>
       <c r="B45" s="71" t="n">
         <f aca="false">B43+B44</f>
-        <v>37043.3333333333</v>
+        <v>99591.0833333338</v>
       </c>
       <c r="C45" s="71" t="n">
         <f aca="false">C43+C44</f>
-        <v>53.3333333333303</v>
+        <v>8555.4166666667</v>
       </c>
       <c r="D45" s="71" t="n">
         <f aca="false">D43+D44</f>
-        <v>2113.33333333333</v>
+        <v>8691.6666666667</v>
       </c>
       <c r="E45" s="71" t="n">
         <f aca="false">E43+E44</f>
-        <v>993.333333333332</v>
+        <v>6109.6666666667</v>
       </c>
       <c r="F45" s="71" t="n">
         <f aca="false">F43+F44</f>
-        <v>2753.33333333333</v>
+        <v>6407.4166666667</v>
       </c>
       <c r="G45" s="71" t="n">
         <f aca="false">G43+G44</f>
-        <v>5436.66666666666</v>
+        <v>11144.75</v>
       </c>
       <c r="H45" s="71" t="n">
         <f aca="false">H43+H44</f>
-        <v>813.333333333329</v>
+        <v>8991.6666666667</v>
       </c>
       <c r="I45" s="71" t="n">
         <f aca="false">I43+I44</f>
-        <v>5816</v>
+        <v>8460.9166666667</v>
       </c>
       <c r="J45" s="71" t="n">
         <f aca="false">J43+J44</f>
-        <v>7360</v>
+        <v>8348.6666666667</v>
       </c>
       <c r="K45" s="71" t="n">
         <f aca="false">K43+K44</f>
-        <v>-900</v>
+        <v>9182.1666666667</v>
       </c>
       <c r="L45" s="71" t="n">
         <f aca="false">L43+L44</f>
-        <v>4880</v>
+        <v>5388.4166666667</v>
       </c>
       <c r="M45" s="71" t="n">
         <f aca="false">M43+M44</f>
-        <v>4863.99999999999</v>
+        <v>10070.1666666667</v>
       </c>
       <c r="N45" s="71" t="n">
         <f aca="false">N43+N44</f>
-        <v>2860</v>
+        <v>8240.1666666667</v>
       </c>
       <c r="O45" s="68"/>
     </row>
@@ -41400,7 +41400,7 @@
       <c r="D7" s="101"/>
       <c r="F7" s="86" t="n">
         <f aca="false">-(TrialBalance!EJ53+TrialBalance!EJ54+TrialBalance!EJ55+TrialBalance!EJ56)</f>
-        <v>86500</v>
+        <v>169200</v>
       </c>
       <c r="H7" s="89"/>
       <c r="I7" s="89"/>
@@ -41444,7 +41444,7 @@
       <c r="E9" s="103"/>
       <c r="F9" s="104" t="n">
         <f aca="false">SUM(F7:F8)</f>
-        <v>88583.3333333333</v>
+        <v>171283.333333334</v>
       </c>
       <c r="H9" s="89"/>
       <c r="I9" s="89"/>
@@ -41517,7 +41517,7 @@
       <c r="D13" s="101"/>
       <c r="E13" s="86" t="n">
         <f aca="false">F14-E12+E14</f>
-        <v>3120</v>
+        <v>9744</v>
       </c>
       <c r="H13" s="89"/>
       <c r="I13" s="89"/>
@@ -41549,7 +41549,7 @@
       </c>
       <c r="F14" s="86" t="n">
         <f aca="false">TrialBalance!EJ60+TrialBalance!EJ62</f>
-        <v>3120</v>
+        <v>9744</v>
       </c>
       <c r="H14" s="89"/>
       <c r="I14" s="86"/>
@@ -41570,7 +41570,7 @@
       <c r="D15" s="101"/>
       <c r="F15" s="102" t="n">
         <f aca="false">TrialBalance!EJ61</f>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="H15" s="89"/>
       <c r="I15" s="89"/>
@@ -41593,7 +41593,7 @@
       <c r="E16" s="103"/>
       <c r="F16" s="104" t="n">
         <f aca="false">SUM(F14:F15)</f>
-        <v>9120</v>
+        <v>17744</v>
       </c>
       <c r="H16" s="89"/>
       <c r="I16" s="89"/>
@@ -41627,7 +41627,7 @@
       <c r="E18" s="103"/>
       <c r="F18" s="104" t="n">
         <f aca="false">F9-F16</f>
-        <v>79463.3333333333</v>
+        <v>153539.333333334</v>
       </c>
       <c r="H18" s="89"/>
       <c r="I18" s="89"/>
@@ -41781,7 +41781,7 @@
       <c r="D26" s="88"/>
       <c r="E26" s="86" t="n">
         <f aca="false">TrialBalance!EJ70</f>
-        <v>720</v>
+        <v>960</v>
       </c>
       <c r="H26" s="89"/>
       <c r="I26" s="89"/>
@@ -41802,7 +41802,7 @@
       <c r="D27" s="88"/>
       <c r="E27" s="86" t="n">
         <f aca="false">TrialBalance!EJ71</f>
-        <v>960</v>
+        <v>1620</v>
       </c>
       <c r="H27" s="89"/>
       <c r="I27" s="89"/>
@@ -41823,7 +41823,7 @@
       <c r="D28" s="88"/>
       <c r="E28" s="86" t="n">
         <f aca="false">TrialBalance!EJ72</f>
-        <v>840</v>
+        <v>1140</v>
       </c>
       <c r="H28" s="89"/>
       <c r="I28" s="89"/>
@@ -41844,7 +41844,7 @@
       <c r="D29" s="88"/>
       <c r="E29" s="86" t="n">
         <f aca="false">TrialBalance!EJ73</f>
-        <v>324</v>
+        <v>1578</v>
       </c>
       <c r="H29" s="89"/>
       <c r="I29" s="89"/>
@@ -41865,7 +41865,7 @@
       <c r="D30" s="88"/>
       <c r="E30" s="86" t="n">
         <f aca="false">TrialBalance!EJ74</f>
-        <v>1800</v>
+        <v>4560</v>
       </c>
       <c r="H30" s="89"/>
       <c r="I30" s="89"/>
@@ -41886,7 +41886,7 @@
       <c r="D31" s="88"/>
       <c r="E31" s="86" t="n">
         <f aca="false">TrialBalance!EJ75</f>
-        <v>960</v>
+        <v>1962</v>
       </c>
       <c r="H31" s="89"/>
       <c r="I31" s="89"/>
@@ -41907,7 +41907,7 @@
       <c r="D32" s="88"/>
       <c r="E32" s="86" t="n">
         <f aca="false">TrialBalance!EJ76</f>
-        <v>936</v>
+        <v>1860</v>
       </c>
       <c r="H32" s="89"/>
       <c r="I32" s="89"/>
@@ -41928,7 +41928,7 @@
       <c r="D33" s="88"/>
       <c r="E33" s="86" t="n">
         <f aca="false">TrialBalance!EJ77</f>
-        <v>2400</v>
+        <v>7598.25</v>
       </c>
       <c r="H33" s="89"/>
       <c r="I33" s="89"/>
@@ -41949,7 +41949,7 @@
       <c r="D34" s="88"/>
       <c r="E34" s="86" t="n">
         <f aca="false">TrialBalance!EJ78</f>
-        <v>960</v>
+        <v>1800</v>
       </c>
       <c r="H34" s="89"/>
       <c r="I34" s="89"/>
@@ -41970,7 +41970,7 @@
       <c r="D35" s="88"/>
       <c r="E35" s="86" t="n">
         <f aca="false">TrialBalance!EJ79</f>
-        <v>2880</v>
+        <v>720</v>
       </c>
       <c r="H35" s="89"/>
       <c r="I35" s="89"/>
@@ -41991,7 +41991,7 @@
       <c r="D36" s="88"/>
       <c r="E36" s="86" t="n">
         <f aca="false">TrialBalance!EJ80</f>
-        <v>5400</v>
+        <v>5310</v>
       </c>
       <c r="H36" s="89"/>
       <c r="I36" s="89"/>
@@ -42096,7 +42096,7 @@
       <c r="D41" s="88"/>
       <c r="E41" s="86" t="n">
         <f aca="false">TrialBalance!EJ85</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="H41" s="89"/>
       <c r="I41" s="89"/>
@@ -42161,7 +42161,7 @@
       <c r="E44" s="103"/>
       <c r="F44" s="104" t="n">
         <f aca="false">SUM(E21:E43)</f>
-        <v>42420</v>
+        <v>53948.25</v>
       </c>
       <c r="H44" s="89"/>
       <c r="I44" s="89"/>
@@ -42197,7 +42197,7 @@
       <c r="E46" s="103"/>
       <c r="F46" s="104" t="n">
         <f aca="false">F18-F44</f>
-        <v>37043.3333333333</v>
+        <v>99591.0833333338</v>
       </c>
       <c r="H46" s="89"/>
       <c r="I46" s="89"/>
@@ -42252,7 +42252,7 @@
       <c r="E49" s="103"/>
       <c r="F49" s="104" t="n">
         <f aca="false">F46+F48</f>
-        <v>37043.3333333333</v>
+        <v>99591.0833333338</v>
       </c>
       <c r="H49" s="89"/>
       <c r="I49" s="89"/>
@@ -42273,7 +42273,7 @@
       <c r="D50" s="101"/>
       <c r="F50" s="86" t="n">
         <f aca="false">TrialBalance!EJ47</f>
-        <v>7494.23333333333</v>
+        <v>19492.3058333334</v>
       </c>
       <c r="H50" s="89"/>
       <c r="I50" s="89"/>
@@ -42296,7 +42296,7 @@
       <c r="E51" s="103"/>
       <c r="F51" s="104" t="n">
         <f aca="false">F49-F50</f>
-        <v>29549.1</v>
+        <v>80098.7775000004</v>
       </c>
       <c r="H51" s="89"/>
       <c r="I51" s="89"/>
@@ -42357,7 +42357,7 @@
       </c>
       <c r="F54" s="104" t="n">
         <f aca="false">F51-F52</f>
-        <v>29549.1</v>
+        <v>80098.7775000004</v>
       </c>
       <c r="H54" s="89"/>
       <c r="I54" s="89"/>
@@ -42480,7 +42480,7 @@
       <c r="E6" s="115"/>
       <c r="F6" s="116" t="n">
         <f aca="false">SUM(TrialBalance!EJ6:EJ17)</f>
-        <v>18200</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42534,7 +42534,7 @@
       </c>
       <c r="E11" s="115" t="n">
         <f aca="false">TrialBalance!EJ20</f>
-        <v>111460</v>
+        <v>220900</v>
       </c>
       <c r="F11" s="115"/>
     </row>
@@ -42565,7 +42565,7 @@
       <c r="D13" s="117"/>
       <c r="E13" s="116" t="n">
         <f aca="false">SUM(E10:E12)</f>
-        <v>111460</v>
+        <v>220900</v>
       </c>
       <c r="F13" s="118"/>
     </row>
@@ -42596,7 +42596,7 @@
       </c>
       <c r="E16" s="115" t="n">
         <f aca="false">-SUM(TrialBalance!EJ28:EJ31)</f>
-        <v>74040</v>
+        <v>110992.25</v>
       </c>
       <c r="F16" s="115"/>
     </row>
@@ -42611,7 +42611,7 @@
       </c>
       <c r="E17" s="115" t="n">
         <f aca="false">-TrialBalance!EJ35</f>
-        <v>7494.23333333333</v>
+        <v>19492.3058333334</v>
       </c>
       <c r="F17" s="115"/>
     </row>
@@ -42626,7 +42626,7 @@
       </c>
       <c r="E18" s="115" t="n">
         <f aca="false">-SUM(TrialBalance!EJ32:EJ34)</f>
-        <v>18576.6666666667</v>
+        <v>36816.6666666666</v>
       </c>
       <c r="F18" s="115"/>
     </row>
@@ -42659,7 +42659,7 @@
       <c r="D20" s="117"/>
       <c r="E20" s="116" t="n">
         <f aca="false">SUM(E16:E19)</f>
-        <v>100110.9</v>
+        <v>167301.2225</v>
       </c>
       <c r="F20" s="118"/>
       <c r="G20" s="120"/>
@@ -42686,7 +42686,7 @@
       <c r="E22" s="118"/>
       <c r="F22" s="116" t="n">
         <f aca="false">E13-E20</f>
-        <v>11349.1</v>
+        <v>53598.7775</v>
       </c>
       <c r="G22" s="120"/>
     </row>
@@ -42739,7 +42739,7 @@
       <c r="E26" s="118"/>
       <c r="F26" s="116" t="n">
         <f aca="false">SUM(F6:F25)</f>
-        <v>29549.1</v>
+        <v>80098.7775</v>
       </c>
       <c r="G26" s="120"/>
     </row>
@@ -42835,7 +42835,7 @@
       </c>
       <c r="F33" s="116" t="n">
         <f aca="false">F26-F31</f>
-        <v>29549.1</v>
+        <v>80098.7775</v>
       </c>
       <c r="G33" s="120"/>
     </row>
@@ -42885,7 +42885,7 @@
       <c r="E37" s="115"/>
       <c r="F37" s="115" t="n">
         <f aca="false">-TrialBalance!EJ43</f>
-        <v>29549.1</v>
+        <v>80098.7775000004</v>
       </c>
       <c r="G37" s="87"/>
       <c r="O37" s="87"/>
@@ -42925,7 +42925,7 @@
       </c>
       <c r="F39" s="116" t="n">
         <f aca="false">SUM(F36:F38)</f>
-        <v>29549.1</v>
+        <v>80098.7775000004</v>
       </c>
       <c r="G39" s="120"/>
     </row>
@@ -43687,7 +43687,7 @@
       <c r="C41" s="137"/>
       <c r="D41" s="136" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>7494.23333333333</v>
+        <v>19492.3058333334</v>
       </c>
       <c r="G41" s="89"/>
     </row>
@@ -44025,7 +44025,7 @@
       <c r="D87" s="160"/>
       <c r="E87" s="165" t="n">
         <f aca="false">'PubP&amp;L'!F9</f>
-        <v>88583.3333333333</v>
+        <v>171283.333333334</v>
       </c>
       <c r="F87" s="166" t="s">
         <v>289</v>
@@ -44060,7 +44060,7 @@
       <c r="C89" s="167"/>
       <c r="D89" s="168" t="n">
         <f aca="false">IF('PubP&amp;L'!F9&gt;0,'PubP&amp;L'!F18/'PubP&amp;L'!F9," ")</f>
-        <v>0.897046095954845</v>
+        <v>0.896405565826603</v>
       </c>
       <c r="E89" s="169" t="s">
         <v>293</v>
@@ -44658,7 +44658,7 @@
       <c r="J5" s="178"/>
       <c r="K5" s="191" t="n">
         <f aca="false">'PubP&amp;L'!F46</f>
-        <v>37043.3333333333</v>
+        <v>99591.0833333338</v>
       </c>
       <c r="L5" s="185"/>
     </row>
@@ -44689,7 +44689,7 @@
       <c r="H7" s="179"/>
       <c r="I7" s="194" t="n">
         <f aca="false">IF(TrialBalance!EJ85&gt;0,TrialBalance!EJ85," ")</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="J7" s="178"/>
       <c r="K7" s="192"/>
@@ -44743,7 +44743,7 @@
       <c r="J10" s="178"/>
       <c r="K10" s="191" t="n">
         <f aca="false">SUM(I6:I9)</f>
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="L10" s="177"/>
     </row>
@@ -44776,7 +44776,7 @@
       <c r="J12" s="178"/>
       <c r="K12" s="191" t="n">
         <f aca="false">K5+K10</f>
-        <v>39443.3333333333</v>
+        <v>102591.083333334</v>
       </c>
       <c r="L12" s="185"/>
     </row>
@@ -44986,7 +44986,7 @@
       <c r="J22" s="178"/>
       <c r="K22" s="209" t="n">
         <f aca="false">K12-K20</f>
-        <v>39443.3333333333</v>
+        <v>102591.083333334</v>
       </c>
       <c r="L22" s="185"/>
     </row>
@@ -45088,7 +45088,7 @@
       <c r="J28" s="178"/>
       <c r="K28" s="209" t="n">
         <f aca="false">K22+K24-K26</f>
-        <v>39443.3333333333</v>
+        <v>102591.083333334</v>
       </c>
       <c r="L28" s="185"/>
     </row>
@@ -45186,7 +45186,7 @@
       </c>
       <c r="F33" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A33/A35,0)</f>
-        <v>19694.6876424988</v>
+        <v>51225.3699270408</v>
       </c>
       <c r="G33" s="224" t="n">
         <f aca="false">Admin!P6</f>
@@ -45195,7 +45195,7 @@
       <c r="H33" s="224"/>
       <c r="I33" s="225" t="n">
         <f aca="false">F33*G33/100</f>
-        <v>3741.99065207478</v>
+        <v>9732.82028613775</v>
       </c>
       <c r="J33" s="226"/>
       <c r="K33" s="178"/>
@@ -45223,7 +45223,7 @@
       </c>
       <c r="F34" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A34/A35,0)</f>
-        <v>19748.6456908345</v>
+        <v>51365.713406293</v>
       </c>
       <c r="G34" s="224" t="n">
         <f aca="false">Admin!P7</f>
@@ -45232,7 +45232,7 @@
       <c r="H34" s="224"/>
       <c r="I34" s="225" t="n">
         <f aca="false">F34*G34/100</f>
-        <v>3752.24268125855</v>
+        <v>9759.48554719566</v>
       </c>
       <c r="J34" s="226"/>
       <c r="K34" s="178"/>
@@ -45256,7 +45256,7 @@
       <c r="J35" s="227"/>
       <c r="K35" s="228" t="n">
         <f aca="false">SUM(I33:I34)</f>
-        <v>7494.23333333333</v>
+        <v>19492.3058333334</v>
       </c>
       <c r="L35" s="185"/>
     </row>
@@ -45322,7 +45322,7 @@
       <c r="J39" s="178"/>
       <c r="K39" s="232" t="n">
         <f aca="false">K35-K37</f>
-        <v>7494.23333333333</v>
+        <v>19492.3058333334</v>
       </c>
       <c r="L39" s="185"/>
     </row>
@@ -49989,7 +49989,7 @@
       </c>
       <c r="AK66" s="300" t="n">
         <f aca="false">'PubP&amp;L'!F9</f>
-        <v>88583.3333333333</v>
+        <v>171283.333333334</v>
       </c>
       <c r="AL66" s="300"/>
       <c r="AM66" s="300"/>
@@ -50175,7 +50175,7 @@
       </c>
       <c r="Z70" s="302" t="n">
         <f aca="false">IF(CorporationTax!K22&gt;0,CorporationTax!K22," ")</f>
-        <v>39443.3333333333</v>
+        <v>102591.083333334</v>
       </c>
       <c r="AA70" s="302"/>
       <c r="AB70" s="302"/>
@@ -50393,7 +50393,7 @@
       </c>
       <c r="AJ74" s="302" t="n">
         <f aca="false">SUM(Z69:AF70)-SUM(Z72:AF73)</f>
-        <v>39443.3333333333</v>
+        <v>102591.083333334</v>
       </c>
       <c r="AK74" s="302"/>
       <c r="AL74" s="302"/>
@@ -51291,7 +51291,7 @@
       </c>
       <c r="AJ92" s="302" t="n">
         <f aca="false">IF(AJ74&gt;0,AJ74+SUM(AJ76:AJ80)+AJ88,0)</f>
-        <v>39443.3333333333</v>
+        <v>102591.083333334</v>
       </c>
       <c r="AK92" s="302"/>
       <c r="AL92" s="302"/>
@@ -52176,7 +52176,7 @@
       </c>
       <c r="AJ110" s="302" t="n">
         <f aca="false">AJ92-Z96-Z98-Z104-Z106</f>
-        <v>39443.3333333333</v>
+        <v>102591.083333334</v>
       </c>
       <c r="AK110" s="302"/>
       <c r="AL110" s="302"/>
@@ -52954,7 +52954,7 @@
       </c>
       <c r="N126" s="328" t="n">
         <f aca="false">CorporationTax!F33</f>
-        <v>19694.6876424988</v>
+        <v>51225.3699270408</v>
       </c>
       <c r="O126" s="328"/>
       <c r="P126" s="328"/>
@@ -52988,7 +52988,7 @@
       </c>
       <c r="AJ126" s="330" t="n">
         <f aca="false">CorporationTax!I33</f>
-        <v>3741.99065207478</v>
+        <v>9732.82028613775</v>
       </c>
       <c r="AK126" s="330"/>
       <c r="AL126" s="330"/>
@@ -53247,7 +53247,7 @@
       </c>
       <c r="AJ131" s="330" t="n">
         <f aca="false">AJ126+AJ128</f>
-        <v>3741.99065207478</v>
+        <v>9732.82028613775</v>
       </c>
       <c r="AK131" s="330"/>
       <c r="AL131" s="330"/>
@@ -53963,7 +53963,7 @@
       </c>
       <c r="AJ145" s="330" t="n">
         <f aca="false">AJ131</f>
-        <v>3741.99065207478</v>
+        <v>9732.82028613775</v>
       </c>
       <c r="AK145" s="330"/>
       <c r="AL145" s="330"/>
@@ -54665,7 +54665,7 @@
       </c>
       <c r="AJ159" s="330" t="n">
         <f aca="false">IF(AJ145&gt;0,AJ145+AJ149-AJ154,0)</f>
-        <v>3741.99065207478</v>
+        <v>9732.82028613775</v>
       </c>
       <c r="AK159" s="330"/>
       <c r="AL159" s="330"/>
@@ -55014,7 +55014,7 @@
       </c>
       <c r="AJ166" s="330" t="n">
         <f aca="false">IF(AJ159&gt;0,AJ159-AJ163,0)</f>
-        <v>3741.99065207478</v>
+        <v>9732.82028613775</v>
       </c>
       <c r="AK166" s="330"/>
       <c r="AL166" s="330"/>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -6662,15 +6662,15 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="F1">
-            <v>16400</v>
+            <v>33400</v>
           </cell>
           <cell r="G1">
-            <v>2733.33333333333</v>
+            <v>5566.66666666667</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>11166.6666666667</v>
+            <v>25333.3333333333</v>
           </cell>
           <cell r="P1">
             <v>1800</v>
@@ -6698,15 +6698,15 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="F1">
-            <v>15920</v>
+            <v>32920</v>
           </cell>
           <cell r="G1">
-            <v>2653.33333333333</v>
+            <v>5486.66666666667</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>11466.6666666667</v>
+            <v>25633.3333333333</v>
           </cell>
           <cell r="P1">
             <v>800</v>
@@ -6734,15 +6734,15 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="F1">
-            <v>18200</v>
+            <v>35200</v>
           </cell>
           <cell r="G1">
-            <v>3033.33333333333</v>
+            <v>5866.66666666667</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>12366.6666666667</v>
+            <v>26533.3333333333</v>
           </cell>
           <cell r="P1">
             <v>800</v>
@@ -6770,15 +6770,15 @@
       <sheetData sheetId="4">
         <row r="1">
           <cell r="F1">
-            <v>16760</v>
+            <v>33760</v>
           </cell>
           <cell r="G1">
-            <v>2793.33333333333</v>
+            <v>5626.66666666667</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>11466.6666666667</v>
+            <v>25633.3333333333</v>
           </cell>
           <cell r="P1">
             <v>1800</v>
@@ -6806,15 +6806,15 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="F1">
-            <v>19020</v>
+            <v>36020</v>
           </cell>
           <cell r="G1">
-            <v>3170</v>
+            <v>6003.33333333333</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>12966.6666666667</v>
+            <v>27133.3333333333</v>
           </cell>
           <cell r="P1">
             <v>800</v>
@@ -6842,15 +6842,15 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="F1">
-            <v>16760</v>
+            <v>33760</v>
           </cell>
           <cell r="G1">
-            <v>2793.33333333333</v>
+            <v>5626.66666666667</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>10866.6666666667</v>
+            <v>25033.3333333333</v>
           </cell>
           <cell r="P1">
             <v>800</v>
@@ -6878,15 +6878,15 @@
       <sheetData sheetId="7">
         <row r="1">
           <cell r="F1">
-            <v>33560</v>
+            <v>50560</v>
           </cell>
           <cell r="G1">
-            <v>5593.33333333333</v>
+            <v>8426.66666666667</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>12966.6666666667</v>
+            <v>27133.3333333333</v>
           </cell>
           <cell r="P1">
             <v>1800</v>
@@ -6914,15 +6914,15 @@
       <sheetData sheetId="8">
         <row r="1">
           <cell r="F1">
-            <v>18320</v>
+            <v>35320</v>
           </cell>
           <cell r="G1">
-            <v>3053.33333333333</v>
+            <v>5886.66666666667</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>11466.6666666667</v>
+            <v>25633.3333333333</v>
           </cell>
           <cell r="P1">
             <v>800</v>
@@ -6950,15 +6950,15 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="F1">
-            <v>15800</v>
+            <v>32800</v>
           </cell>
           <cell r="G1">
-            <v>2633.33333333333</v>
+            <v>5466.66666666667</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>12366.6666666667</v>
+            <v>26533.3333333333</v>
           </cell>
           <cell r="P1">
             <v>800</v>
@@ -6986,15 +6986,15 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="F1">
-            <v>18440</v>
+            <v>35440</v>
           </cell>
           <cell r="G1">
-            <v>3073.33333333333</v>
+            <v>5906.66666666667</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>11466.6666666667</v>
+            <v>25633.3333333333</v>
           </cell>
           <cell r="P1">
             <v>1800</v>
@@ -7022,15 +7022,15 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="F1">
-            <v>17360</v>
+            <v>34360</v>
           </cell>
           <cell r="G1">
-            <v>2893.33333333333</v>
+            <v>5726.66666666667</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>12166.6666666667</v>
+            <v>26333.3333333333</v>
           </cell>
           <cell r="P1">
             <v>800</v>
@@ -7058,15 +7058,15 @@
       <sheetData sheetId="12">
         <row r="1">
           <cell r="F1">
-            <v>14360</v>
+            <v>31360</v>
           </cell>
           <cell r="G1">
-            <v>2393.33333333333</v>
+            <v>5226.66666666667</v>
           </cell>
         </row>
         <row r="1">
           <cell r="O1">
-            <v>10866.6666666667</v>
+            <v>25033.3333333333</v>
           </cell>
           <cell r="P1">
             <v>800</v>
@@ -14996,7 +14996,7 @@
       <c r="I8" s="78"/>
       <c r="J8" s="78" t="n">
         <f aca="false">[3]Jun!$O$1</f>
-        <v>11166.6666666667</v>
+        <v>25333.3333333333</v>
       </c>
       <c r="K8" s="78"/>
       <c r="L8" s="434" t="n">
@@ -15110,7 +15110,7 @@
       <c r="I10" s="78"/>
       <c r="J10" s="78" t="n">
         <f aca="false">[3]Jul!$O$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="K10" s="78"/>
       <c r="L10" s="434" t="n">
@@ -15226,7 +15226,7 @@
       <c r="I12" s="78"/>
       <c r="J12" s="78" t="n">
         <f aca="false">[3]Aug!$O$1</f>
-        <v>12366.6666666667</v>
+        <v>26533.3333333333</v>
       </c>
       <c r="K12" s="78"/>
       <c r="L12" s="434" t="n">
@@ -15340,7 +15340,7 @@
       <c r="I14" s="78"/>
       <c r="J14" s="78" t="n">
         <f aca="false">[3]Sep!$O$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="K14" s="78"/>
       <c r="L14" s="434" t="n">
@@ -15456,7 +15456,7 @@
       <c r="I16" s="78"/>
       <c r="J16" s="78" t="n">
         <f aca="false">[3]Oct!$O$1</f>
-        <v>12966.6666666667</v>
+        <v>27133.3333333333</v>
       </c>
       <c r="K16" s="78"/>
       <c r="L16" s="434" t="n">
@@ -15570,7 +15570,7 @@
       <c r="I18" s="78"/>
       <c r="J18" s="78" t="n">
         <f aca="false">[3]Nov!$O$1</f>
-        <v>10866.6666666667</v>
+        <v>25033.3333333333</v>
       </c>
       <c r="K18" s="78"/>
       <c r="L18" s="434" t="n">
@@ -15686,7 +15686,7 @@
       <c r="I20" s="78"/>
       <c r="J20" s="78" t="n">
         <f aca="false">[3]Dec!$O$1</f>
-        <v>12966.6666666667</v>
+        <v>27133.3333333333</v>
       </c>
       <c r="K20" s="78"/>
       <c r="L20" s="434" t="n">
@@ -15800,7 +15800,7 @@
       <c r="I22" s="78"/>
       <c r="J22" s="78" t="n">
         <f aca="false">[3]Jan!$O$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="K22" s="78"/>
       <c r="L22" s="434" t="n">
@@ -15916,7 +15916,7 @@
       <c r="I24" s="78"/>
       <c r="J24" s="78" t="n">
         <f aca="false">[3]Feb!$O$1</f>
-        <v>12366.6666666667</v>
+        <v>26533.3333333333</v>
       </c>
       <c r="K24" s="78"/>
       <c r="L24" s="434" t="n">
@@ -16030,7 +16030,7 @@
       <c r="I26" s="78"/>
       <c r="J26" s="78" t="n">
         <f aca="false">[3]Mar!$O$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="K26" s="78"/>
       <c r="L26" s="434" t="n">
@@ -16144,7 +16144,7 @@
       <c r="I28" s="78"/>
       <c r="J28" s="78" t="n">
         <f aca="false">[3]Apr!$O$1</f>
-        <v>12166.6666666667</v>
+        <v>26333.3333333333</v>
       </c>
       <c r="K28" s="78"/>
       <c r="L28" s="434" t="n">
@@ -16260,7 +16260,7 @@
       <c r="I30" s="78"/>
       <c r="J30" s="78" t="n">
         <f aca="false">[3]May!$O$1</f>
-        <v>10866.6666666667</v>
+        <v>25033.3333333333</v>
       </c>
       <c r="K30" s="78"/>
       <c r="L30" s="434" t="n">
@@ -21381,7 +21381,7 @@
       <c r="E20" s="57"/>
       <c r="F20" s="36" t="n">
         <f aca="false">[3]Jun!$F$1-[3]Jun!$V$1</f>
-        <v>16400</v>
+        <v>33400</v>
       </c>
       <c r="G20" s="36"/>
       <c r="H20" s="36" t="n">
@@ -21404,12 +21404,12 @@
       <c r="N20" s="57"/>
       <c r="O20" s="36" t="n">
         <f aca="false">SUM(D20:N20)</f>
-        <v>16400</v>
+        <v>33400</v>
       </c>
       <c r="P20" s="57"/>
       <c r="Q20" s="36" t="n">
         <f aca="false">[3]Jul!$F$1-[3]Jul!$V$1</f>
-        <v>15920</v>
+        <v>32920</v>
       </c>
       <c r="R20" s="36"/>
       <c r="S20" s="36" t="n">
@@ -21435,12 +21435,12 @@
       <c r="Y20" s="54"/>
       <c r="Z20" s="36" t="n">
         <f aca="false">SUM(O20:Y20)</f>
-        <v>32320</v>
+        <v>66320</v>
       </c>
       <c r="AA20" s="57"/>
       <c r="AB20" s="36" t="n">
         <f aca="false">[3]Aug!$F$1-[3]Aug!$V$1</f>
-        <v>18200</v>
+        <v>35200</v>
       </c>
       <c r="AC20" s="36"/>
       <c r="AD20" s="36" t="n">
@@ -21464,12 +21464,12 @@
       <c r="AJ20" s="54"/>
       <c r="AK20" s="36" t="n">
         <f aca="false">SUM(Z20:AJ20)</f>
-        <v>50520</v>
+        <v>101520</v>
       </c>
       <c r="AL20" s="57"/>
       <c r="AM20" s="36" t="n">
         <f aca="false">[3]Sep!$F$1-[3]Sep!$V$1</f>
-        <v>16760</v>
+        <v>33760</v>
       </c>
       <c r="AN20" s="36"/>
       <c r="AO20" s="36" t="n">
@@ -21493,12 +21493,12 @@
       <c r="AU20" s="54"/>
       <c r="AV20" s="36" t="n">
         <f aca="false">SUM(AK20:AU20)</f>
-        <v>67280</v>
+        <v>135280</v>
       </c>
       <c r="AW20" s="57"/>
       <c r="AX20" s="36" t="n">
         <f aca="false">[3]Oct!$F$1-[3]Oct!$V$1</f>
-        <v>19020</v>
+        <v>36020</v>
       </c>
       <c r="AY20" s="36"/>
       <c r="AZ20" s="36" t="n">
@@ -21522,12 +21522,12 @@
       <c r="BF20" s="54"/>
       <c r="BG20" s="36" t="n">
         <f aca="false">SUM(AV20:BF20)</f>
-        <v>86300</v>
+        <v>171300</v>
       </c>
       <c r="BH20" s="57"/>
       <c r="BI20" s="36" t="n">
         <f aca="false">[3]Nov!$F$1-[3]Nov!$V$1</f>
-        <v>16760</v>
+        <v>33760</v>
       </c>
       <c r="BJ20" s="36"/>
       <c r="BK20" s="36" t="n">
@@ -21551,12 +21551,12 @@
       <c r="BQ20" s="54"/>
       <c r="BR20" s="36" t="n">
         <f aca="false">SUM(BG20:BQ20)</f>
-        <v>103060</v>
+        <v>205060</v>
       </c>
       <c r="BS20" s="57"/>
       <c r="BT20" s="36" t="n">
         <f aca="false">[3]Dec!$F$1-[3]Dec!$V$1</f>
-        <v>33560</v>
+        <v>50560</v>
       </c>
       <c r="BU20" s="36"/>
       <c r="BV20" s="36" t="n">
@@ -21580,12 +21580,12 @@
       <c r="CB20" s="54"/>
       <c r="CC20" s="36" t="n">
         <f aca="false">SUM(BR20:CB20)</f>
-        <v>136620</v>
+        <v>255620</v>
       </c>
       <c r="CD20" s="57"/>
       <c r="CE20" s="36" t="n">
         <f aca="false">[3]Jan!$F$1-[3]Jan!$V$1</f>
-        <v>18320</v>
+        <v>35320</v>
       </c>
       <c r="CF20" s="36"/>
       <c r="CG20" s="36" t="n">
@@ -21609,12 +21609,12 @@
       <c r="CM20" s="54"/>
       <c r="CN20" s="36" t="n">
         <f aca="false">SUM(CC20:CM20)</f>
-        <v>154940</v>
+        <v>290940</v>
       </c>
       <c r="CO20" s="57"/>
       <c r="CP20" s="36" t="n">
         <f aca="false">[3]Feb!$F$1-[3]Feb!$V$1</f>
-        <v>15800</v>
+        <v>32800</v>
       </c>
       <c r="CQ20" s="36"/>
       <c r="CR20" s="36" t="n">
@@ -21638,12 +21638,12 @@
       <c r="CX20" s="54"/>
       <c r="CY20" s="36" t="n">
         <f aca="false">SUM(CN20:CX20)</f>
-        <v>170740</v>
+        <v>323740</v>
       </c>
       <c r="CZ20" s="57"/>
       <c r="DA20" s="36" t="n">
         <f aca="false">[3]Mar!$F$1-[3]Mar!$V$1</f>
-        <v>18440</v>
+        <v>35440</v>
       </c>
       <c r="DB20" s="36"/>
       <c r="DC20" s="36" t="n">
@@ -21667,12 +21667,12 @@
       <c r="DI20" s="54"/>
       <c r="DJ20" s="36" t="n">
         <f aca="false">SUM(CY20:DI20)</f>
-        <v>189180</v>
+        <v>359180</v>
       </c>
       <c r="DK20" s="57"/>
       <c r="DL20" s="36" t="n">
         <f aca="false">[3]Apr!$F$1-[3]Apr!$V$1</f>
-        <v>17360</v>
+        <v>34360</v>
       </c>
       <c r="DM20" s="36"/>
       <c r="DN20" s="36" t="n">
@@ -21696,12 +21696,12 @@
       <c r="DT20" s="54"/>
       <c r="DU20" s="36" t="n">
         <f aca="false">SUM(DJ20:DT20)</f>
-        <v>206540</v>
+        <v>393540</v>
       </c>
       <c r="DV20" s="57"/>
       <c r="DW20" s="36" t="n">
         <f aca="false">[3]May!$F$1-[3]May!$V$1</f>
-        <v>14360</v>
+        <v>31360</v>
       </c>
       <c r="DX20" s="36"/>
       <c r="DY20" s="36" t="n">
@@ -21725,13 +21725,13 @@
       <c r="EE20" s="54"/>
       <c r="EF20" s="36" t="n">
         <f aca="false">SUM(DU20:EE20)</f>
-        <v>220900</v>
+        <v>424900</v>
       </c>
       <c r="EG20" s="54"/>
       <c r="EI20" s="54"/>
       <c r="EJ20" s="36" t="n">
         <f aca="false">SUM(EF20:EH20)</f>
-        <v>220900</v>
+        <v>424900</v>
       </c>
       <c r="EK20" s="54"/>
     </row>
@@ -24941,7 +24941,7 @@
       <c r="E33" s="57"/>
       <c r="F33" s="36" t="n">
         <f aca="false">-[3]Jun!$G$1</f>
-        <v>-2733.33333333333</v>
+        <v>-5566.66666666667</v>
       </c>
       <c r="G33" s="36" t="n">
         <f aca="false">[2]Jun!$G$1</f>
@@ -24967,12 +24967,12 @@
       <c r="N33" s="57"/>
       <c r="O33" s="36" t="n">
         <f aca="false">SUM(D33:N33)</f>
-        <v>-2733.33333333333</v>
+        <v>-5566.66666666667</v>
       </c>
       <c r="P33" s="57"/>
       <c r="Q33" s="36" t="n">
         <f aca="false">-[3]Jul!$G$1</f>
-        <v>-2653.33333333333</v>
+        <v>-5486.66666666667</v>
       </c>
       <c r="R33" s="36" t="n">
         <f aca="false">[2]Jul!$G$1</f>
@@ -24999,12 +24999,12 @@
       <c r="Y33" s="54"/>
       <c r="Z33" s="36" t="n">
         <f aca="false">SUM(O33:Y33)</f>
-        <v>-5386.66666666666</v>
+        <v>-11053.3333333333</v>
       </c>
       <c r="AA33" s="57"/>
       <c r="AB33" s="36" t="n">
         <f aca="false">-[3]Aug!$G$1</f>
-        <v>-3033.33333333333</v>
+        <v>-5866.66666666667</v>
       </c>
       <c r="AC33" s="36" t="n">
         <f aca="false">[2]Aug!$G$1</f>
@@ -25031,12 +25031,12 @@
       <c r="AJ33" s="54"/>
       <c r="AK33" s="36" t="n">
         <f aca="false">SUM(Z33:AJ33)</f>
-        <v>-8419.99999999999</v>
+        <v>-16920</v>
       </c>
       <c r="AL33" s="57"/>
       <c r="AM33" s="36" t="n">
         <f aca="false">-[3]Sep!$G$1</f>
-        <v>-2793.33333333333</v>
+        <v>-5626.66666666667</v>
       </c>
       <c r="AN33" s="36" t="n">
         <f aca="false">[2]Sep!$G$1</f>
@@ -25063,12 +25063,12 @@
       <c r="AU33" s="54"/>
       <c r="AV33" s="36" t="n">
         <f aca="false">SUM(AK33:AU33)</f>
-        <v>-11213.3333333333</v>
+        <v>-22546.6666666667</v>
       </c>
       <c r="AW33" s="57"/>
       <c r="AX33" s="36" t="n">
         <f aca="false">-[3]Oct!$G$1</f>
-        <v>-3170</v>
+        <v>-6003.33333333333</v>
       </c>
       <c r="AY33" s="36" t="n">
         <f aca="false">[2]Oct!$G$1</f>
@@ -25095,12 +25095,12 @@
       <c r="BF33" s="54"/>
       <c r="BG33" s="36" t="n">
         <f aca="false">SUM(AV33:BF33)</f>
-        <v>-14383.3333333333</v>
+        <v>-28550</v>
       </c>
       <c r="BH33" s="57"/>
       <c r="BI33" s="36" t="n">
         <f aca="false">-[3]Nov!$G$1</f>
-        <v>-2793.33333333333</v>
+        <v>-5626.66666666667</v>
       </c>
       <c r="BJ33" s="36" t="n">
         <f aca="false">[2]Nov!$G$1</f>
@@ -25127,12 +25127,12 @@
       <c r="BQ33" s="54"/>
       <c r="BR33" s="36" t="n">
         <f aca="false">SUM(BG33:BQ33)</f>
-        <v>-17176.6666666667</v>
+        <v>-34176.6666666667</v>
       </c>
       <c r="BS33" s="57"/>
       <c r="BT33" s="36" t="n">
         <f aca="false">-[3]Dec!$G$1</f>
-        <v>-5593.33333333333</v>
+        <v>-8426.66666666667</v>
       </c>
       <c r="BU33" s="36" t="n">
         <f aca="false">[2]Dec!$G$1</f>
@@ -25159,12 +25159,12 @@
       <c r="CB33" s="54"/>
       <c r="CC33" s="36" t="n">
         <f aca="false">SUM(BR33:CB33)</f>
-        <v>-22770</v>
+        <v>-42603.3333333334</v>
       </c>
       <c r="CD33" s="57"/>
       <c r="CE33" s="36" t="n">
         <f aca="false">-[3]Jan!$G$1</f>
-        <v>-3053.33333333333</v>
+        <v>-5886.66666666667</v>
       </c>
       <c r="CF33" s="36" t="n">
         <f aca="false">[2]Jan!$G$1</f>
@@ -25191,12 +25191,12 @@
       <c r="CM33" s="54"/>
       <c r="CN33" s="36" t="n">
         <f aca="false">SUM(CC33:CM33)</f>
-        <v>-25823.3333333333</v>
+        <v>-48490</v>
       </c>
       <c r="CO33" s="57"/>
       <c r="CP33" s="36" t="n">
         <f aca="false">-[3]Feb!$G$1</f>
-        <v>-2633.33333333333</v>
+        <v>-5466.66666666667</v>
       </c>
       <c r="CQ33" s="36" t="n">
         <f aca="false">[2]Feb!$G$1</f>
@@ -25223,12 +25223,12 @@
       <c r="CX33" s="54"/>
       <c r="CY33" s="36" t="n">
         <f aca="false">SUM(CN33:CX33)</f>
-        <v>-28456.6666666666</v>
+        <v>-53956.6666666667</v>
       </c>
       <c r="CZ33" s="57"/>
       <c r="DA33" s="36" t="n">
         <f aca="false">-[3]Mar!$G$1</f>
-        <v>-3073.33333333333</v>
+        <v>-5906.66666666667</v>
       </c>
       <c r="DB33" s="36" t="n">
         <f aca="false">[2]Mar!$G$1</f>
@@ -25255,12 +25255,12 @@
       <c r="DI33" s="54"/>
       <c r="DJ33" s="36" t="n">
         <f aca="false">SUM(CY33:DI33)</f>
-        <v>-31530</v>
+        <v>-59863.3333333334</v>
       </c>
       <c r="DK33" s="57"/>
       <c r="DL33" s="36" t="n">
         <f aca="false">-[3]Apr!$G$1</f>
-        <v>-2893.33333333333</v>
+        <v>-5726.66666666667</v>
       </c>
       <c r="DM33" s="36" t="n">
         <f aca="false">[2]Apr!$G$1</f>
@@ -25287,12 +25287,12 @@
       <c r="DT33" s="54"/>
       <c r="DU33" s="36" t="n">
         <f aca="false">SUM(DJ33:DT33)</f>
-        <v>-34423.3333333333</v>
+        <v>-65590</v>
       </c>
       <c r="DV33" s="57"/>
       <c r="DW33" s="36" t="n">
         <f aca="false">-[3]May!$G$1</f>
-        <v>-2393.33333333333</v>
+        <v>-5226.66666666667</v>
       </c>
       <c r="DX33" s="36" t="n">
         <f aca="false">[2]May!$G$1</f>
@@ -25319,13 +25319,13 @@
       <c r="EE33" s="54"/>
       <c r="EF33" s="36" t="n">
         <f aca="false">SUM(DU33:EE33)</f>
-        <v>-36816.6666666666</v>
+        <v>-70816.6666666667</v>
       </c>
       <c r="EG33" s="54"/>
       <c r="EI33" s="54"/>
       <c r="EJ33" s="36" t="n">
         <f aca="false">SUM(EF33:EH33)</f>
-        <v>-36816.6666666666</v>
+        <v>-70816.6666666667</v>
       </c>
       <c r="EK33" s="54"/>
     </row>
@@ -26015,12 +26015,12 @@
       <c r="EC35" s="36"/>
       <c r="ED35" s="36" t="n">
         <f aca="false">-CorporationTax!K35</f>
-        <v>-19492.3058333334</v>
+        <v>-51792.3058333333</v>
       </c>
       <c r="EE35" s="54"/>
       <c r="EF35" s="36" t="n">
         <f aca="false">SUM(DU35:EE35)</f>
-        <v>-19492.3058333334</v>
+        <v>-51792.3058333333</v>
       </c>
       <c r="EG35" s="54"/>
       <c r="EH35" s="36" t="n">
@@ -26030,7 +26030,7 @@
       <c r="EI35" s="54"/>
       <c r="EJ35" s="36" t="n">
         <f aca="false">SUM(EF35:EH35)</f>
-        <v>-19492.3058333334</v>
+        <v>-51792.3058333333</v>
       </c>
       <c r="EK35" s="54"/>
     </row>
@@ -27808,12 +27808,12 @@
       <c r="EG43" s="54"/>
       <c r="EH43" s="36" t="n">
         <f aca="false">-'PubP&amp;L'!F54</f>
-        <v>-80098.7775000004</v>
+        <v>-217798.7775</v>
       </c>
       <c r="EI43" s="54"/>
       <c r="EJ43" s="36" t="n">
         <f aca="false">SUM(EF43:EH43)</f>
-        <v>-80098.7775000004</v>
+        <v>-217798.7775</v>
       </c>
       <c r="EK43" s="54"/>
     </row>
@@ -28442,18 +28442,18 @@
       <c r="EC47" s="36"/>
       <c r="ED47" s="36" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>19492.3058333334</v>
+        <v>51792.3058333333</v>
       </c>
       <c r="EE47" s="54"/>
       <c r="EF47" s="36" t="n">
         <f aca="false">SUM(DU47:EE47)</f>
-        <v>19492.3058333334</v>
+        <v>51792.3058333333</v>
       </c>
       <c r="EG47" s="54"/>
       <c r="EI47" s="54"/>
       <c r="EJ47" s="36" t="n">
         <f aca="false">SUM(EF47:EH47)</f>
-        <v>19492.3058333334</v>
+        <v>51792.3058333333</v>
       </c>
       <c r="EK47" s="54"/>
     </row>
@@ -28822,12 +28822,12 @@
       <c r="EG49" s="54"/>
       <c r="EH49" s="36" t="n">
         <f aca="false">'PubP&amp;L'!F54</f>
-        <v>80098.7775000004</v>
+        <v>217798.7775</v>
       </c>
       <c r="EI49" s="54"/>
       <c r="EJ49" s="36" t="n">
         <f aca="false">SUM(EF49:EH49)</f>
-        <v>80098.7775000004</v>
+        <v>217798.7775</v>
       </c>
       <c r="EK49" s="54"/>
     </row>
@@ -29249,7 +29249,7 @@
       <c r="E53" s="57"/>
       <c r="F53" s="36" t="n">
         <f aca="false">-[3]Jun!$O$1</f>
-        <v>-11166.6666666667</v>
+        <v>-25333.3333333333</v>
       </c>
       <c r="G53" s="36"/>
       <c r="H53" s="36"/>
@@ -29260,12 +29260,12 @@
       <c r="N53" s="57"/>
       <c r="O53" s="36" t="n">
         <f aca="false">SUM(D53:N53)</f>
-        <v>-11166.6666666667</v>
+        <v>-25333.3333333333</v>
       </c>
       <c r="P53" s="57"/>
       <c r="Q53" s="36" t="n">
         <f aca="false">-[3]Jul!$O$1</f>
-        <v>-11466.6666666667</v>
+        <v>-25633.3333333333</v>
       </c>
       <c r="R53" s="36"/>
       <c r="S53" s="36"/>
@@ -29277,12 +29277,12 @@
       <c r="Y53" s="54"/>
       <c r="Z53" s="36" t="n">
         <f aca="false">SUM(O53:Y53)</f>
-        <v>-22633.3333333334</v>
+        <v>-50966.6666666666</v>
       </c>
       <c r="AA53" s="57"/>
       <c r="AB53" s="36" t="n">
         <f aca="false">-[3]Aug!$O$1</f>
-        <v>-12366.6666666667</v>
+        <v>-26533.3333333333</v>
       </c>
       <c r="AC53" s="36"/>
       <c r="AD53" s="36"/>
@@ -29294,12 +29294,12 @@
       <c r="AJ53" s="54"/>
       <c r="AK53" s="36" t="n">
         <f aca="false">SUM(Z53:AJ53)</f>
-        <v>-35000.0000000001</v>
+        <v>-77499.9999999999</v>
       </c>
       <c r="AL53" s="57"/>
       <c r="AM53" s="36" t="n">
         <f aca="false">-[3]Sep!$O$1</f>
-        <v>-11466.6666666667</v>
+        <v>-25633.3333333333</v>
       </c>
       <c r="AN53" s="36"/>
       <c r="AO53" s="36"/>
@@ -29311,12 +29311,12 @@
       <c r="AU53" s="54"/>
       <c r="AV53" s="36" t="n">
         <f aca="false">SUM(AK53:AU53)</f>
-        <v>-46466.6666666668</v>
+        <v>-103133.333333333</v>
       </c>
       <c r="AW53" s="57"/>
       <c r="AX53" s="36" t="n">
         <f aca="false">-[3]Oct!$O$1</f>
-        <v>-12966.6666666667</v>
+        <v>-27133.3333333333</v>
       </c>
       <c r="AY53" s="36"/>
       <c r="AZ53" s="36"/>
@@ -29328,12 +29328,12 @@
       <c r="BF53" s="54"/>
       <c r="BG53" s="36" t="n">
         <f aca="false">SUM(AV53:BF53)</f>
-        <v>-59433.3333333335</v>
+        <v>-130266.666666667</v>
       </c>
       <c r="BH53" s="57"/>
       <c r="BI53" s="36" t="n">
         <f aca="false">-[3]Nov!$O$1</f>
-        <v>-10866.6666666667</v>
+        <v>-25033.3333333333</v>
       </c>
       <c r="BJ53" s="36"/>
       <c r="BK53" s="36"/>
@@ -29345,12 +29345,12 @@
       <c r="BQ53" s="54"/>
       <c r="BR53" s="36" t="n">
         <f aca="false">SUM(BG53:BQ53)</f>
-        <v>-70300.0000000002</v>
+        <v>-155300</v>
       </c>
       <c r="BS53" s="57"/>
       <c r="BT53" s="36" t="n">
         <f aca="false">-[3]Dec!$O$1</f>
-        <v>-12966.6666666667</v>
+        <v>-27133.3333333333</v>
       </c>
       <c r="BU53" s="36"/>
       <c r="BV53" s="36"/>
@@ -29362,12 +29362,12 @@
       <c r="CB53" s="54"/>
       <c r="CC53" s="36" t="n">
         <f aca="false">SUM(BR53:CB53)</f>
-        <v>-83266.6666666669</v>
+        <v>-182433.333333333</v>
       </c>
       <c r="CD53" s="57"/>
       <c r="CE53" s="36" t="n">
         <f aca="false">-[3]Jan!$O$1</f>
-        <v>-11466.6666666667</v>
+        <v>-25633.3333333333</v>
       </c>
       <c r="CF53" s="36"/>
       <c r="CG53" s="36"/>
@@ -29379,12 +29379,12 @@
       <c r="CM53" s="54"/>
       <c r="CN53" s="36" t="n">
         <f aca="false">SUM(CC53:CM53)</f>
-        <v>-94733.3333333336</v>
+        <v>-208066.666666666</v>
       </c>
       <c r="CO53" s="57"/>
       <c r="CP53" s="36" t="n">
         <f aca="false">-[3]Feb!$O$1</f>
-        <v>-12366.6666666667</v>
+        <v>-26533.3333333333</v>
       </c>
       <c r="CQ53" s="36"/>
       <c r="CR53" s="36"/>
@@ -29396,12 +29396,12 @@
       <c r="CX53" s="54"/>
       <c r="CY53" s="36" t="n">
         <f aca="false">SUM(CN53:CX53)</f>
-        <v>-107100</v>
+        <v>-234600</v>
       </c>
       <c r="CZ53" s="57"/>
       <c r="DA53" s="36" t="n">
         <f aca="false">-[3]Mar!$O$1</f>
-        <v>-11466.6666666667</v>
+        <v>-25633.3333333333</v>
       </c>
       <c r="DB53" s="36"/>
       <c r="DC53" s="36"/>
@@ -29413,12 +29413,12 @@
       <c r="DI53" s="54"/>
       <c r="DJ53" s="36" t="n">
         <f aca="false">SUM(CY53:DI53)</f>
-        <v>-118566.666666667</v>
+        <v>-260233.333333333</v>
       </c>
       <c r="DK53" s="57"/>
       <c r="DL53" s="36" t="n">
         <f aca="false">-[3]Apr!$O$1</f>
-        <v>-12166.6666666667</v>
+        <v>-26333.3333333333</v>
       </c>
       <c r="DM53" s="36"/>
       <c r="DN53" s="36"/>
@@ -29430,12 +29430,12 @@
       <c r="DT53" s="54"/>
       <c r="DU53" s="36" t="n">
         <f aca="false">SUM(DJ53:DT53)</f>
-        <v>-130733.333333334</v>
+        <v>-286566.666666666</v>
       </c>
       <c r="DV53" s="57"/>
       <c r="DW53" s="36" t="n">
         <f aca="false">-[3]May!$O$1</f>
-        <v>-10866.6666666667</v>
+        <v>-25033.3333333333</v>
       </c>
       <c r="DX53" s="36"/>
       <c r="DY53" s="36"/>
@@ -29447,13 +29447,13 @@
       <c r="EE53" s="54"/>
       <c r="EF53" s="36" t="n">
         <f aca="false">SUM(DU53:EE53)</f>
-        <v>-141600</v>
+        <v>-311600</v>
       </c>
       <c r="EG53" s="54"/>
       <c r="EI53" s="54"/>
       <c r="EJ53" s="36" t="n">
         <f aca="false">SUM(EF53:EH53)</f>
-        <v>-141600</v>
+        <v>-311600</v>
       </c>
       <c r="EK53" s="54"/>
     </row>
@@ -37897,7 +37897,7 @@
       <c r="E91" s="54"/>
       <c r="F91" s="36" t="n">
         <f aca="false">SUM(F4:F90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="G91" s="36" t="n">
         <f aca="false">SUM(G4:G90)</f>
@@ -37930,12 +37930,12 @@
       <c r="N91" s="54"/>
       <c r="O91" s="36" t="n">
         <f aca="false">SUM(O4:O90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="P91" s="54"/>
       <c r="Q91" s="36" t="n">
         <f aca="false">SUM(Q4:Q90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="R91" s="36" t="n">
         <f aca="false">SUM(R4:R90)</f>
@@ -37968,12 +37968,12 @@
       <c r="Y91" s="54"/>
       <c r="Z91" s="36" t="n">
         <f aca="false">SUM(Z4:Z90)</f>
-        <v>-6.09361450187862E-011</v>
+        <v>6.18456397205591E-011</v>
       </c>
       <c r="AA91" s="54"/>
       <c r="AB91" s="36" t="n">
         <f aca="false">SUM(AB4:AB90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="AC91" s="36" t="n">
         <f aca="false">SUM(AC4:AC90)</f>
@@ -38006,12 +38006,12 @@
       <c r="AJ91" s="54"/>
       <c r="AK91" s="36" t="n">
         <f aca="false">SUM(AK4:AK90)</f>
-        <v>-9.09494701772928E-011</v>
+        <v>9.45874489843845E-011</v>
       </c>
       <c r="AL91" s="54"/>
       <c r="AM91" s="36" t="n">
         <f aca="false">SUM(AM4:AM90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="AN91" s="36" t="n">
         <f aca="false">SUM(AN4:AN90)</f>
@@ -38044,12 +38044,12 @@
       <c r="AU91" s="54"/>
       <c r="AV91" s="36" t="n">
         <f aca="false">SUM(AV4:AV90)</f>
-        <v>-1.21872290037572E-010</v>
+        <v>1.23691279441118E-010</v>
       </c>
       <c r="AW91" s="54"/>
       <c r="AX91" s="36" t="n">
         <f aca="false">SUM(AX4:AX90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>4.04725142288953E-011</v>
       </c>
       <c r="AY91" s="36" t="n">
         <f aca="false">SUM(AY4:AY90)</f>
@@ -38082,12 +38082,12 @@
       <c r="BF91" s="54"/>
       <c r="BG91" s="36" t="n">
         <f aca="false">SUM(BG4:BG90)</f>
-        <v>-1.52340362546965E-010</v>
+        <v>1.65982783073559E-010</v>
       </c>
       <c r="BH91" s="54"/>
       <c r="BI91" s="36" t="n">
         <f aca="false">SUM(BI4:BI90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="BJ91" s="36" t="n">
         <f aca="false">SUM(BJ4:BJ90)</f>
@@ -38120,12 +38120,12 @@
       <c r="BQ91" s="54"/>
       <c r="BR91" s="36" t="n">
         <f aca="false">SUM(BR4:BR90)</f>
-        <v>-1.83263182407245E-010</v>
+        <v>1.95086613530293E-010</v>
       </c>
       <c r="BS91" s="54"/>
       <c r="BT91" s="36" t="n">
         <f aca="false">SUM(BT4:BT90)</f>
-        <v>-3.09228198602796E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="BU91" s="36" t="n">
         <f aca="false">SUM(BU4:BU90)</f>
@@ -38158,12 +38158,12 @@
       <c r="CB91" s="54"/>
       <c r="CC91" s="36" t="n">
         <f aca="false">SUM(CC4:CC90)</f>
-        <v>-2.12367012863979E-010</v>
+        <v>2.38742359215394E-010</v>
       </c>
       <c r="CD91" s="54"/>
       <c r="CE91" s="36" t="n">
         <f aca="false">SUM(CE4:CE90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="CF91" s="36" t="n">
         <f aca="false">SUM(CF4:CF90)</f>
@@ -38196,12 +38196,12 @@
       <c r="CM91" s="54"/>
       <c r="CN91" s="36" t="n">
         <f aca="false">SUM(CN4:CN90)</f>
-        <v>-2.41470843320712E-010</v>
+        <v>2.53294274443761E-010</v>
       </c>
       <c r="CO91" s="54"/>
       <c r="CP91" s="36" t="n">
         <f aca="false">SUM(CP4:CP90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="CQ91" s="36" t="n">
         <f aca="false">SUM(CQ4:CQ90)</f>
@@ -38234,12 +38234,12 @@
       <c r="CX91" s="54"/>
       <c r="CY91" s="36" t="n">
         <f aca="false">SUM(CY4:CY90)</f>
-        <v>-2.70574673777446E-010</v>
+        <v>2.67846189672127E-010</v>
       </c>
       <c r="CZ91" s="54"/>
       <c r="DA91" s="36" t="n">
         <f aca="false">SUM(DA4:DA90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="DB91" s="36" t="n">
         <f aca="false">SUM(DB4:DB90)</f>
@@ -38272,12 +38272,12 @@
       <c r="DI91" s="54"/>
       <c r="DJ91" s="36" t="n">
         <f aca="false">SUM(DJ4:DJ90)</f>
-        <v>-2.9967850423418E-010</v>
+        <v>2.82398104900494E-010</v>
       </c>
       <c r="DK91" s="54"/>
       <c r="DL91" s="36" t="n">
         <f aca="false">SUM(DL4:DL90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="DM91" s="36" t="n">
         <f aca="false">SUM(DM4:DM90)</f>
@@ -38310,12 +38310,12 @@
       <c r="DT91" s="54"/>
       <c r="DU91" s="36" t="n">
         <f aca="false">SUM(DU4:DU90)</f>
-        <v>-3.28782334690914E-010</v>
+        <v>3.04225977743045E-010</v>
       </c>
       <c r="DV91" s="54"/>
       <c r="DW91" s="36" t="n">
         <f aca="false">SUM(DW4:DW90)</f>
-        <v>-3.04680725093931E-011</v>
+        <v>3.09228198602796E-011</v>
       </c>
       <c r="DX91" s="36" t="n">
         <f aca="false">SUM(DX4:DX90)</f>
@@ -38348,7 +38348,7 @@
       <c r="EE91" s="54"/>
       <c r="EF91" s="36" t="n">
         <f aca="false">SUM(EF4:EF90)</f>
-        <v>-3.57886165147647E-010</v>
+        <v>3.18777892971411E-010</v>
       </c>
       <c r="EG91" s="54"/>
       <c r="EH91" s="36" t="n">
@@ -38358,7 +38358,7 @@
       <c r="EI91" s="54"/>
       <c r="EJ91" s="36" t="n">
         <f aca="false">SUM(EJ4:EJ90)</f>
-        <v>-3.57886165147647E-010</v>
+        <v>3.18777892971411E-010</v>
       </c>
       <c r="EK91" s="54"/>
     </row>
@@ -38739,55 +38739,55 @@
       </c>
       <c r="B4" s="71" t="n">
         <f aca="false">SUM(C4:N4)</f>
-        <v>141600</v>
+        <v>311600</v>
       </c>
       <c r="C4" s="72" t="n">
         <f aca="false">-TrialBalance!O53-0</f>
-        <v>11166.6666666667</v>
+        <v>25333.3333333333</v>
       </c>
       <c r="D4" s="72" t="n">
         <f aca="false">-TrialBalance!Z53-C4</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="E4" s="72" t="n">
         <f aca="false">-TrialBalance!AK53-SUM(C4:D4)</f>
-        <v>12366.6666666667</v>
+        <v>26533.3333333333</v>
       </c>
       <c r="F4" s="72" t="n">
         <f aca="false">-TrialBalance!AV53-SUM(C4:E4)</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="G4" s="72" t="n">
         <f aca="false">-TrialBalance!BG53-SUM(C4:F4)</f>
-        <v>12966.6666666667</v>
+        <v>27133.3333333333</v>
       </c>
       <c r="H4" s="72" t="n">
         <f aca="false">-TrialBalance!BR53-SUM(C4:G4)</f>
-        <v>10866.6666666667</v>
+        <v>25033.3333333333</v>
       </c>
       <c r="I4" s="72" t="n">
         <f aca="false">-TrialBalance!CC53-SUM(C4:H4)</f>
-        <v>12966.6666666667</v>
+        <v>27133.3333333333</v>
       </c>
       <c r="J4" s="72" t="n">
         <f aca="false">-TrialBalance!CN53-SUM(C4:I4)</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="K4" s="72" t="n">
         <f aca="false">-TrialBalance!CY53-SUM(C4:J4)</f>
-        <v>12366.6666666667</v>
+        <v>26533.3333333333</v>
       </c>
       <c r="L4" s="72" t="n">
         <f aca="false">-TrialBalance!DJ53-SUM(C4:K4)</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="M4" s="72" t="n">
         <f aca="false">-TrialBalance!DU53-SUM(C4:L4)</f>
-        <v>12166.6666666667</v>
+        <v>26333.3333333333</v>
       </c>
       <c r="N4" s="72" t="n">
         <f aca="false">-TrialBalance!EF53-SUM(C4:M4)</f>
-        <v>10866.6666666667</v>
+        <v>25033.3333333333</v>
       </c>
       <c r="O4" s="68"/>
     </row>
@@ -39029,55 +39029,55 @@
       </c>
       <c r="B9" s="71" t="n">
         <f aca="false">SUM(B4:B8)</f>
-        <v>171283.333333334</v>
+        <v>341283.333333333</v>
       </c>
       <c r="C9" s="74" t="n">
         <f aca="false">SUM(C4:C8)</f>
-        <v>13666.6666666667</v>
+        <v>27833.3333333333</v>
       </c>
       <c r="D9" s="71" t="n">
         <f aca="false">SUM(D4:D8)</f>
-        <v>13266.6666666667</v>
+        <v>27433.3333333333</v>
       </c>
       <c r="E9" s="71" t="n">
         <f aca="false">SUM(E4:E8)</f>
-        <v>15166.6666666667</v>
+        <v>29333.3333333333</v>
       </c>
       <c r="F9" s="71" t="n">
         <f aca="false">SUM(F4:F8)</f>
-        <v>13966.6666666667</v>
+        <v>28133.3333333333</v>
       </c>
       <c r="G9" s="71" t="n">
         <f aca="false">SUM(G4:G8)</f>
-        <v>15850</v>
+        <v>30016.6666666666</v>
       </c>
       <c r="H9" s="71" t="n">
         <f aca="false">SUM(H4:H8)</f>
-        <v>13966.6666666667</v>
+        <v>28133.3333333333</v>
       </c>
       <c r="I9" s="71" t="n">
         <f aca="false">SUM(I4:I8)</f>
-        <v>15466.6666666667</v>
+        <v>29633.3333333333</v>
       </c>
       <c r="J9" s="71" t="n">
         <f aca="false">SUM(J4:J8)</f>
-        <v>15266.6666666667</v>
+        <v>29433.3333333333</v>
       </c>
       <c r="K9" s="71" t="n">
         <f aca="false">SUM(K4:K8)</f>
-        <v>13166.6666666667</v>
+        <v>27333.3333333333</v>
       </c>
       <c r="L9" s="71" t="n">
         <f aca="false">SUM(L4:L8)</f>
-        <v>15366.6666666667</v>
+        <v>29533.3333333333</v>
       </c>
       <c r="M9" s="71" t="n">
         <f aca="false">SUM(M4:M8)</f>
-        <v>14466.6666666667</v>
+        <v>28633.3333333333</v>
       </c>
       <c r="N9" s="71" t="n">
         <f aca="false">SUM(N4:N8)</f>
-        <v>11666.6666666667</v>
+        <v>25833.3333333333</v>
       </c>
       <c r="O9" s="75"/>
     </row>
@@ -39355,55 +39355,55 @@
       </c>
       <c r="B16" s="71" t="n">
         <f aca="false">B9-B14</f>
-        <v>153539.333333334</v>
+        <v>323539.333333333</v>
       </c>
       <c r="C16" s="71" t="n">
         <f aca="false">C9-C14</f>
-        <v>12781.6666666667</v>
+        <v>26948.3333333333</v>
       </c>
       <c r="D16" s="71" t="n">
         <f aca="false">D9-D14</f>
-        <v>12297.6666666667</v>
+        <v>26464.3333333333</v>
       </c>
       <c r="E16" s="71" t="n">
         <f aca="false">E9-E14</f>
-        <v>9521.6666666667</v>
+        <v>23688.3333333333</v>
       </c>
       <c r="F16" s="71" t="n">
         <f aca="false">F9-F14</f>
-        <v>12997.6666666667</v>
+        <v>27164.3333333333</v>
       </c>
       <c r="G16" s="71" t="n">
         <f aca="false">G9-G14</f>
-        <v>15025</v>
+        <v>29191.6666666666</v>
       </c>
       <c r="H16" s="71" t="n">
         <f aca="false">H9-H14</f>
-        <v>13477.6666666667</v>
+        <v>27644.3333333333</v>
       </c>
       <c r="I16" s="71" t="n">
         <f aca="false">I9-I14</f>
-        <v>14701.6666666667</v>
+        <v>28868.3333333333</v>
       </c>
       <c r="J16" s="71" t="n">
         <f aca="false">J9-J14</f>
-        <v>11177.6666666667</v>
+        <v>25344.3333333333</v>
       </c>
       <c r="K16" s="71" t="n">
         <f aca="false">K9-K14</f>
-        <v>12401.6666666667</v>
+        <v>26568.3333333333</v>
       </c>
       <c r="L16" s="71" t="n">
         <f aca="false">L9-L14</f>
-        <v>14517.6666666667</v>
+        <v>28684.3333333333</v>
       </c>
       <c r="M16" s="71" t="n">
         <f aca="false">M9-M14</f>
-        <v>13521.6666666667</v>
+        <v>27688.3333333333</v>
       </c>
       <c r="N16" s="71" t="n">
         <f aca="false">N9-N14</f>
-        <v>11117.6666666667</v>
+        <v>25284.3333333333</v>
       </c>
       <c r="O16" s="75"/>
     </row>
@@ -40841,55 +40841,55 @@
       </c>
       <c r="B43" s="71" t="n">
         <f aca="false">B16-B41</f>
-        <v>99591.0833333338</v>
+        <v>269591.083333333</v>
       </c>
       <c r="C43" s="71" t="n">
         <f aca="false">C16-C41</f>
-        <v>8555.4166666667</v>
+        <v>22722.0833333333</v>
       </c>
       <c r="D43" s="71" t="n">
         <f aca="false">D16-D41</f>
-        <v>8691.6666666667</v>
+        <v>22858.3333333333</v>
       </c>
       <c r="E43" s="71" t="n">
         <f aca="false">E16-E41</f>
-        <v>6109.6666666667</v>
+        <v>20276.3333333333</v>
       </c>
       <c r="F43" s="71" t="n">
         <f aca="false">F16-F41</f>
-        <v>6407.4166666667</v>
+        <v>20574.0833333333</v>
       </c>
       <c r="G43" s="71" t="n">
         <f aca="false">G16-G41</f>
-        <v>11144.75</v>
+        <v>25311.4166666666</v>
       </c>
       <c r="H43" s="71" t="n">
         <f aca="false">H16-H41</f>
-        <v>8991.6666666667</v>
+        <v>23158.3333333333</v>
       </c>
       <c r="I43" s="71" t="n">
         <f aca="false">I16-I41</f>
-        <v>8460.9166666667</v>
+        <v>22627.5833333333</v>
       </c>
       <c r="J43" s="71" t="n">
         <f aca="false">J16-J41</f>
-        <v>8348.6666666667</v>
+        <v>22515.3333333333</v>
       </c>
       <c r="K43" s="71" t="n">
         <f aca="false">K16-K41</f>
-        <v>9182.1666666667</v>
+        <v>23348.8333333333</v>
       </c>
       <c r="L43" s="71" t="n">
         <f aca="false">L16-L41</f>
-        <v>5388.4166666667</v>
+        <v>19555.0833333333</v>
       </c>
       <c r="M43" s="71" t="n">
         <f aca="false">M16-M41</f>
-        <v>10070.1666666667</v>
+        <v>24236.8333333333</v>
       </c>
       <c r="N43" s="71" t="n">
         <f aca="false">N16-N41</f>
-        <v>8240.1666666667</v>
+        <v>22406.8333333333</v>
       </c>
       <c r="O43" s="68"/>
     </row>
@@ -40957,55 +40957,55 @@
       </c>
       <c r="B45" s="71" t="n">
         <f aca="false">B43+B44</f>
-        <v>99591.0833333338</v>
+        <v>269591.083333333</v>
       </c>
       <c r="C45" s="71" t="n">
         <f aca="false">C43+C44</f>
-        <v>8555.4166666667</v>
+        <v>22722.0833333333</v>
       </c>
       <c r="D45" s="71" t="n">
         <f aca="false">D43+D44</f>
-        <v>8691.6666666667</v>
+        <v>22858.3333333333</v>
       </c>
       <c r="E45" s="71" t="n">
         <f aca="false">E43+E44</f>
-        <v>6109.6666666667</v>
+        <v>20276.3333333333</v>
       </c>
       <c r="F45" s="71" t="n">
         <f aca="false">F43+F44</f>
-        <v>6407.4166666667</v>
+        <v>20574.0833333333</v>
       </c>
       <c r="G45" s="71" t="n">
         <f aca="false">G43+G44</f>
-        <v>11144.75</v>
+        <v>25311.4166666666</v>
       </c>
       <c r="H45" s="71" t="n">
         <f aca="false">H43+H44</f>
-        <v>8991.6666666667</v>
+        <v>23158.3333333333</v>
       </c>
       <c r="I45" s="71" t="n">
         <f aca="false">I43+I44</f>
-        <v>8460.9166666667</v>
+        <v>22627.5833333333</v>
       </c>
       <c r="J45" s="71" t="n">
         <f aca="false">J43+J44</f>
-        <v>8348.6666666667</v>
+        <v>22515.3333333333</v>
       </c>
       <c r="K45" s="71" t="n">
         <f aca="false">K43+K44</f>
-        <v>9182.1666666667</v>
+        <v>23348.8333333333</v>
       </c>
       <c r="L45" s="71" t="n">
         <f aca="false">L43+L44</f>
-        <v>5388.4166666667</v>
+        <v>19555.0833333333</v>
       </c>
       <c r="M45" s="71" t="n">
         <f aca="false">M43+M44</f>
-        <v>10070.1666666667</v>
+        <v>24236.8333333333</v>
       </c>
       <c r="N45" s="71" t="n">
         <f aca="false">N43+N44</f>
-        <v>8240.1666666667</v>
+        <v>22406.8333333333</v>
       </c>
       <c r="O45" s="68"/>
     </row>
@@ -41179,7 +41179,7 @@
       <c r="D7" s="101"/>
       <c r="F7" s="86" t="n">
         <f aca="false">-(TrialBalance!EJ53+TrialBalance!EJ54+TrialBalance!EJ55+TrialBalance!EJ56)</f>
-        <v>169200</v>
+        <v>339200</v>
       </c>
       <c r="H7" s="89"/>
       <c r="I7" s="89"/>
@@ -41223,7 +41223,7 @@
       <c r="E9" s="103"/>
       <c r="F9" s="104" t="n">
         <f aca="false">SUM(F7:F8)</f>
-        <v>171283.333333334</v>
+        <v>341283.333333333</v>
       </c>
       <c r="H9" s="89"/>
       <c r="I9" s="89"/>
@@ -41406,7 +41406,7 @@
       <c r="E18" s="103"/>
       <c r="F18" s="104" t="n">
         <f aca="false">F9-F16</f>
-        <v>153539.333333334</v>
+        <v>323539.333333333</v>
       </c>
       <c r="H18" s="89"/>
       <c r="I18" s="89"/>
@@ -41976,7 +41976,7 @@
       <c r="E46" s="103"/>
       <c r="F46" s="104" t="n">
         <f aca="false">F18-F44</f>
-        <v>99591.0833333338</v>
+        <v>269591.083333333</v>
       </c>
       <c r="H46" s="89"/>
       <c r="I46" s="89"/>
@@ -42031,7 +42031,7 @@
       <c r="E49" s="103"/>
       <c r="F49" s="104" t="n">
         <f aca="false">F46+F48</f>
-        <v>99591.0833333338</v>
+        <v>269591.083333333</v>
       </c>
       <c r="H49" s="89"/>
       <c r="I49" s="89"/>
@@ -42052,7 +42052,7 @@
       <c r="D50" s="101"/>
       <c r="F50" s="86" t="n">
         <f aca="false">TrialBalance!EJ47</f>
-        <v>19492.3058333334</v>
+        <v>51792.3058333333</v>
       </c>
       <c r="H50" s="89"/>
       <c r="I50" s="89"/>
@@ -42075,7 +42075,7 @@
       <c r="E51" s="103"/>
       <c r="F51" s="104" t="n">
         <f aca="false">F49-F50</f>
-        <v>80098.7775000004</v>
+        <v>217798.7775</v>
       </c>
       <c r="H51" s="89"/>
       <c r="I51" s="89"/>
@@ -42136,7 +42136,7 @@
       </c>
       <c r="F54" s="104" t="n">
         <f aca="false">F51-F52</f>
-        <v>80098.7775000004</v>
+        <v>217798.7775</v>
       </c>
       <c r="H54" s="89"/>
       <c r="I54" s="89"/>
@@ -42313,7 +42313,7 @@
       </c>
       <c r="E11" s="115" t="n">
         <f aca="false">TrialBalance!EJ20</f>
-        <v>220900</v>
+        <v>424900</v>
       </c>
       <c r="F11" s="115"/>
     </row>
@@ -42344,7 +42344,7 @@
       <c r="D13" s="117"/>
       <c r="E13" s="116" t="n">
         <f aca="false">SUM(E10:E12)</f>
-        <v>220900</v>
+        <v>424900</v>
       </c>
       <c r="F13" s="118"/>
     </row>
@@ -42390,7 +42390,7 @@
       </c>
       <c r="E17" s="115" t="n">
         <f aca="false">-TrialBalance!EJ35</f>
-        <v>19492.3058333334</v>
+        <v>51792.3058333333</v>
       </c>
       <c r="F17" s="115"/>
     </row>
@@ -42405,7 +42405,7 @@
       </c>
       <c r="E18" s="115" t="n">
         <f aca="false">-SUM(TrialBalance!EJ32:EJ34)</f>
-        <v>36816.6666666666</v>
+        <v>70816.6666666667</v>
       </c>
       <c r="F18" s="115"/>
     </row>
@@ -42438,7 +42438,7 @@
       <c r="D20" s="117"/>
       <c r="E20" s="116" t="n">
         <f aca="false">SUM(E16:E19)</f>
-        <v>167301.2225</v>
+        <v>233601.2225</v>
       </c>
       <c r="F20" s="118"/>
       <c r="G20" s="120"/>
@@ -42465,7 +42465,7 @@
       <c r="E22" s="118"/>
       <c r="F22" s="116" t="n">
         <f aca="false">E13-E20</f>
-        <v>53598.7775</v>
+        <v>191298.7775</v>
       </c>
       <c r="G22" s="120"/>
     </row>
@@ -42518,7 +42518,7 @@
       <c r="E26" s="118"/>
       <c r="F26" s="116" t="n">
         <f aca="false">SUM(F6:F25)</f>
-        <v>80098.7775</v>
+        <v>217798.7775</v>
       </c>
       <c r="G26" s="120"/>
     </row>
@@ -42614,7 +42614,7 @@
       </c>
       <c r="F33" s="116" t="n">
         <f aca="false">F26-F31</f>
-        <v>80098.7775</v>
+        <v>217798.7775</v>
       </c>
       <c r="G33" s="120"/>
     </row>
@@ -42664,7 +42664,7 @@
       <c r="E37" s="115"/>
       <c r="F37" s="115" t="n">
         <f aca="false">-TrialBalance!EJ43</f>
-        <v>80098.7775000004</v>
+        <v>217798.7775</v>
       </c>
       <c r="G37" s="87"/>
       <c r="O37" s="87"/>
@@ -42704,7 +42704,7 @@
       </c>
       <c r="F39" s="116" t="n">
         <f aca="false">SUM(F36:F38)</f>
-        <v>80098.7775000004</v>
+        <v>217798.7775</v>
       </c>
       <c r="G39" s="120"/>
     </row>
@@ -43466,7 +43466,7 @@
       <c r="C41" s="137"/>
       <c r="D41" s="136" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>19492.3058333334</v>
+        <v>51792.3058333333</v>
       </c>
       <c r="G41" s="89"/>
     </row>
@@ -43804,7 +43804,7 @@
       <c r="D87" s="160"/>
       <c r="E87" s="165" t="n">
         <f aca="false">'PubP&amp;L'!F9</f>
-        <v>171283.333333334</v>
+        <v>341283.333333333</v>
       </c>
       <c r="F87" s="166" t="s">
         <v>285</v>
@@ -43839,7 +43839,7 @@
       <c r="C89" s="167"/>
       <c r="D89" s="168" t="n">
         <f aca="false">IF('PubP&amp;L'!F9&gt;0,'PubP&amp;L'!F18/'PubP&amp;L'!F9," ")</f>
-        <v>0.896405565826603</v>
+        <v>0.948008008985691</v>
       </c>
       <c r="E89" s="169" t="s">
         <v>289</v>
@@ -44437,7 +44437,7 @@
       <c r="J5" s="178"/>
       <c r="K5" s="191" t="n">
         <f aca="false">'PubP&amp;L'!F46</f>
-        <v>99591.0833333338</v>
+        <v>269591.083333333</v>
       </c>
       <c r="L5" s="185"/>
     </row>
@@ -44555,7 +44555,7 @@
       <c r="J12" s="178"/>
       <c r="K12" s="191" t="n">
         <f aca="false">K5+K10</f>
-        <v>102591.083333334</v>
+        <v>272591.083333333</v>
       </c>
       <c r="L12" s="185"/>
     </row>
@@ -44765,7 +44765,7 @@
       <c r="J22" s="178"/>
       <c r="K22" s="209" t="n">
         <f aca="false">K12-K20</f>
-        <v>102591.083333334</v>
+        <v>272591.083333333</v>
       </c>
       <c r="L22" s="185"/>
     </row>
@@ -44867,7 +44867,7 @@
       <c r="J28" s="178"/>
       <c r="K28" s="209" t="n">
         <f aca="false">K22+K24-K26</f>
-        <v>102591.083333334</v>
+        <v>272591.083333333</v>
       </c>
       <c r="L28" s="185"/>
     </row>
@@ -44965,7 +44965,7 @@
       </c>
       <c r="F33" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A33/A35,0)</f>
-        <v>51225.3699270408</v>
+        <v>136109.090857273</v>
       </c>
       <c r="G33" s="224" t="n">
         <f aca="false">Admin!P6</f>
@@ -44974,7 +44974,7 @@
       <c r="H33" s="224"/>
       <c r="I33" s="225" t="n">
         <f aca="false">F33*G33/100</f>
-        <v>9732.82028613775</v>
+        <v>25860.7272628819</v>
       </c>
       <c r="J33" s="226"/>
       <c r="K33" s="178"/>
@@ -45002,7 +45002,7 @@
       </c>
       <c r="F34" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A34/A35,0)</f>
-        <v>51365.713406293</v>
+        <v>136481.99247606</v>
       </c>
       <c r="G34" s="224" t="n">
         <f aca="false">Admin!P7</f>
@@ -45011,7 +45011,7 @@
       <c r="H34" s="224"/>
       <c r="I34" s="225" t="n">
         <f aca="false">F34*G34/100</f>
-        <v>9759.48554719566</v>
+        <v>25931.5785704514</v>
       </c>
       <c r="J34" s="226"/>
       <c r="K34" s="178"/>
@@ -45035,7 +45035,7 @@
       <c r="J35" s="227"/>
       <c r="K35" s="228" t="n">
         <f aca="false">SUM(I33:I34)</f>
-        <v>19492.3058333334</v>
+        <v>51792.3058333333</v>
       </c>
       <c r="L35" s="185"/>
     </row>
@@ -45101,7 +45101,7 @@
       <c r="J39" s="178"/>
       <c r="K39" s="232" t="n">
         <f aca="false">K35-K37</f>
-        <v>19492.3058333334</v>
+        <v>51792.3058333333</v>
       </c>
       <c r="L39" s="185"/>
     </row>
@@ -49768,7 +49768,7 @@
       </c>
       <c r="AK66" s="300" t="n">
         <f aca="false">'PubP&amp;L'!F9</f>
-        <v>171283.333333334</v>
+        <v>341283.333333333</v>
       </c>
       <c r="AL66" s="300"/>
       <c r="AM66" s="300"/>
@@ -49954,7 +49954,7 @@
       </c>
       <c r="Z70" s="302" t="n">
         <f aca="false">IF(CorporationTax!K22&gt;0,CorporationTax!K22," ")</f>
-        <v>102591.083333334</v>
+        <v>272591.083333333</v>
       </c>
       <c r="AA70" s="302"/>
       <c r="AB70" s="302"/>
@@ -50172,7 +50172,7 @@
       </c>
       <c r="AJ74" s="302" t="n">
         <f aca="false">SUM(Z69:AF70)-SUM(Z72:AF73)</f>
-        <v>102591.083333334</v>
+        <v>272591.083333333</v>
       </c>
       <c r="AK74" s="302"/>
       <c r="AL74" s="302"/>
@@ -51070,7 +51070,7 @@
       </c>
       <c r="AJ92" s="302" t="n">
         <f aca="false">IF(AJ74&gt;0,AJ74+SUM(AJ76:AJ80)+AJ88,0)</f>
-        <v>102591.083333334</v>
+        <v>272591.083333333</v>
       </c>
       <c r="AK92" s="302"/>
       <c r="AL92" s="302"/>
@@ -51955,7 +51955,7 @@
       </c>
       <c r="AJ110" s="302" t="n">
         <f aca="false">AJ92-Z96-Z98-Z104-Z106</f>
-        <v>102591.083333334</v>
+        <v>272591.083333333</v>
       </c>
       <c r="AK110" s="302"/>
       <c r="AL110" s="302"/>
@@ -52733,7 +52733,7 @@
       </c>
       <c r="N126" s="328" t="n">
         <f aca="false">CorporationTax!F33</f>
-        <v>51225.3699270408</v>
+        <v>136109.090857273</v>
       </c>
       <c r="O126" s="328"/>
       <c r="P126" s="328"/>
@@ -52767,7 +52767,7 @@
       </c>
       <c r="AJ126" s="330" t="n">
         <f aca="false">CorporationTax!I33</f>
-        <v>9732.82028613775</v>
+        <v>25860.7272628819</v>
       </c>
       <c r="AK126" s="330"/>
       <c r="AL126" s="330"/>
@@ -53026,7 +53026,7 @@
       </c>
       <c r="AJ131" s="330" t="n">
         <f aca="false">AJ126+AJ128</f>
-        <v>9732.82028613775</v>
+        <v>25860.7272628819</v>
       </c>
       <c r="AK131" s="330"/>
       <c r="AL131" s="330"/>
@@ -53742,7 +53742,7 @@
       </c>
       <c r="AJ145" s="330" t="n">
         <f aca="false">AJ131</f>
-        <v>9732.82028613775</v>
+        <v>25860.7272628819</v>
       </c>
       <c r="AK145" s="330"/>
       <c r="AL145" s="330"/>
@@ -54444,7 +54444,7 @@
       </c>
       <c r="AJ159" s="330" t="n">
         <f aca="false">IF(AJ145&gt;0,AJ145+AJ149-AJ154,0)</f>
-        <v>9732.82028613775</v>
+        <v>25860.7272628819</v>
       </c>
       <c r="AK159" s="330"/>
       <c r="AL159" s="330"/>
@@ -54793,7 +54793,7 @@
       </c>
       <c r="AJ166" s="330" t="n">
         <f aca="false">IF(AJ159&gt;0,AJ159-AJ163,0)</f>
-        <v>9732.82028613775</v>
+        <v>25860.7272628819</v>
       </c>
       <c r="AK166" s="330"/>
       <c r="AL166" s="330"/>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -42863,7 +42863,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43696,7 +43696,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44238,7 +44238,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -7118,7 +7118,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>29600</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7130,7 +7130,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>24400</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7148,7 +7148,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>137837</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7211,7 +7211,7 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19500</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7223,7 +7223,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14200</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7241,7 +7241,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>137586</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7304,7 +7304,7 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19900</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7316,7 +7316,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14900</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7334,7 +7334,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>137684</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7397,7 +7397,7 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19100</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7409,7 +7409,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14000</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7427,7 +7427,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>229588</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7490,7 +7490,7 @@
       <sheetData sheetId="4">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>22200</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7502,7 +7502,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14600</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7514,13 +7514,13 @@
             <v>0</v>
           </cell>
           <cell r="N1">
-            <v>0</v>
+            <v>2500</v>
           </cell>
           <cell r="O1">
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>91907</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7583,7 +7583,7 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>18000</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7595,7 +7595,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>13400</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7613,7 +7613,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>137960</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7676,7 +7676,7 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>72400</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7688,7 +7688,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>30400</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7706,7 +7706,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>230025</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7769,7 +7769,7 @@
       <sheetData sheetId="7">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19400</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7781,7 +7781,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14500</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7799,7 +7799,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>138138</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7862,7 +7862,7 @@
       <sheetData sheetId="8">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19100</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7874,7 +7874,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>13900</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7892,7 +7892,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>184309</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7955,7 +7955,7 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>27000</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7967,7 +7967,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>15200</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7979,13 +7979,13 @@
             <v>0</v>
           </cell>
           <cell r="N1">
-            <v>0</v>
+            <v>1500</v>
           </cell>
           <cell r="O1">
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>138305</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -8048,7 +8048,7 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19700</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -8060,7 +8060,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14300</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -8078,7 +8078,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>92271</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -8141,7 +8141,7 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>24600</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -8153,7 +8153,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14800</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -8171,7 +8171,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>184677</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -8722,7 +8722,7 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>125</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -8746,7 +8746,7 @@
             <v>0</v>
           </cell>
           <cell r="N1">
-            <v>0</v>
+            <v>125</v>
           </cell>
           <cell r="O1">
             <v>0</v>
@@ -9280,7 +9280,7 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>5150</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -9304,7 +9304,7 @@
             <v>0</v>
           </cell>
           <cell r="N1">
-            <v>0</v>
+            <v>150</v>
           </cell>
           <cell r="O1">
             <v>0</v>
@@ -9313,7 +9313,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="1">
@@ -9396,7 +9396,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>500</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -9429,7 +9429,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="1">
@@ -9519,7 +9519,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>45858</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -9582,7 +9582,7 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>180</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -9675,7 +9675,7 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>300</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -9708,7 +9708,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>300</v>
           </cell>
         </row>
         <row r="1">
@@ -9954,7 +9954,7 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>620</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -9987,7 +9987,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="1">
@@ -10233,7 +10233,7 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>300</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -10266,7 +10266,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>300</v>
           </cell>
         </row>
         <row r="1">
@@ -10326,7 +10326,7 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>240</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -10535,7 +10535,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>15</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -10697,7 +10697,7 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>125</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -10940,7 +10940,7 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>18</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -11183,7 +11183,7 @@
       <sheetData sheetId="8">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -11426,7 +11426,7 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>12</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -21386,7 +21386,7 @@
       <c r="G20" s="36"/>
       <c r="H20" s="36" t="n">
         <f aca="false">-[4]Jun!$J$1</f>
-        <v>-0</v>
+        <v>-24400</v>
       </c>
       <c r="I20" s="36" t="n">
         <f aca="false">-[5]Jun!$J$1</f>
@@ -21404,7 +21404,7 @@
       <c r="N20" s="57"/>
       <c r="O20" s="36" t="n">
         <f aca="false">SUM(D20:N20)</f>
-        <v>33400</v>
+        <v>9000</v>
       </c>
       <c r="P20" s="57"/>
       <c r="Q20" s="36" t="n">
@@ -21414,7 +21414,7 @@
       <c r="R20" s="36"/>
       <c r="S20" s="36" t="n">
         <f aca="false">-[4]Jul!$J$1</f>
-        <v>-0</v>
+        <v>-14200</v>
       </c>
       <c r="T20" s="36" t="n">
         <f aca="false">-[5]Jul!$J$1</f>
@@ -21435,7 +21435,7 @@
       <c r="Y20" s="54"/>
       <c r="Z20" s="36" t="n">
         <f aca="false">SUM(O20:Y20)</f>
-        <v>66320</v>
+        <v>27720</v>
       </c>
       <c r="AA20" s="57"/>
       <c r="AB20" s="36" t="n">
@@ -21445,7 +21445,7 @@
       <c r="AC20" s="36"/>
       <c r="AD20" s="36" t="n">
         <f aca="false">-[4]Aug!$J$1</f>
-        <v>-0</v>
+        <v>-14900</v>
       </c>
       <c r="AE20" s="36" t="n">
         <f aca="false">-[5]Aug!$J$1</f>
@@ -21464,7 +21464,7 @@
       <c r="AJ20" s="54"/>
       <c r="AK20" s="36" t="n">
         <f aca="false">SUM(Z20:AJ20)</f>
-        <v>101520</v>
+        <v>48020</v>
       </c>
       <c r="AL20" s="57"/>
       <c r="AM20" s="36" t="n">
@@ -21474,7 +21474,7 @@
       <c r="AN20" s="36"/>
       <c r="AO20" s="36" t="n">
         <f aca="false">-[4]Sep!$J$1</f>
-        <v>-0</v>
+        <v>-14000</v>
       </c>
       <c r="AP20" s="36" t="n">
         <f aca="false">-[5]Sep!$J$1</f>
@@ -21493,7 +21493,7 @@
       <c r="AU20" s="54"/>
       <c r="AV20" s="36" t="n">
         <f aca="false">SUM(AK20:AU20)</f>
-        <v>135280</v>
+        <v>67780</v>
       </c>
       <c r="AW20" s="57"/>
       <c r="AX20" s="36" t="n">
@@ -21503,7 +21503,7 @@
       <c r="AY20" s="36"/>
       <c r="AZ20" s="36" t="n">
         <f aca="false">-[4]Oct!$J$1</f>
-        <v>-0</v>
+        <v>-14600</v>
       </c>
       <c r="BA20" s="36" t="n">
         <f aca="false">-[5]Oct!$J$1</f>
@@ -21522,7 +21522,7 @@
       <c r="BF20" s="54"/>
       <c r="BG20" s="36" t="n">
         <f aca="false">SUM(AV20:BF20)</f>
-        <v>171300</v>
+        <v>89200</v>
       </c>
       <c r="BH20" s="57"/>
       <c r="BI20" s="36" t="n">
@@ -21532,7 +21532,7 @@
       <c r="BJ20" s="36"/>
       <c r="BK20" s="36" t="n">
         <f aca="false">-[4]Nov!$J$1</f>
-        <v>-0</v>
+        <v>-13400</v>
       </c>
       <c r="BL20" s="36" t="n">
         <f aca="false">-[5]Nov!$J$1</f>
@@ -21551,7 +21551,7 @@
       <c r="BQ20" s="54"/>
       <c r="BR20" s="36" t="n">
         <f aca="false">SUM(BG20:BQ20)</f>
-        <v>205060</v>
+        <v>109560</v>
       </c>
       <c r="BS20" s="57"/>
       <c r="BT20" s="36" t="n">
@@ -21561,7 +21561,7 @@
       <c r="BU20" s="36"/>
       <c r="BV20" s="36" t="n">
         <f aca="false">-[4]Dec!$J$1</f>
-        <v>-0</v>
+        <v>-30400</v>
       </c>
       <c r="BW20" s="36" t="n">
         <f aca="false">-[5]Dec!$J$1</f>
@@ -21580,7 +21580,7 @@
       <c r="CB20" s="54"/>
       <c r="CC20" s="36" t="n">
         <f aca="false">SUM(BR20:CB20)</f>
-        <v>255620</v>
+        <v>129720</v>
       </c>
       <c r="CD20" s="57"/>
       <c r="CE20" s="36" t="n">
@@ -21590,7 +21590,7 @@
       <c r="CF20" s="36"/>
       <c r="CG20" s="36" t="n">
         <f aca="false">-[4]Jan!$J$1</f>
-        <v>-0</v>
+        <v>-14500</v>
       </c>
       <c r="CH20" s="36" t="n">
         <f aca="false">-[5]Jan!$J$1</f>
@@ -21609,7 +21609,7 @@
       <c r="CM20" s="54"/>
       <c r="CN20" s="36" t="n">
         <f aca="false">SUM(CC20:CM20)</f>
-        <v>290940</v>
+        <v>150540</v>
       </c>
       <c r="CO20" s="57"/>
       <c r="CP20" s="36" t="n">
@@ -21619,7 +21619,7 @@
       <c r="CQ20" s="36"/>
       <c r="CR20" s="36" t="n">
         <f aca="false">-[4]Feb!$J$1</f>
-        <v>-0</v>
+        <v>-13900</v>
       </c>
       <c r="CS20" s="36" t="n">
         <f aca="false">-[5]Feb!$J$1</f>
@@ -21638,7 +21638,7 @@
       <c r="CX20" s="54"/>
       <c r="CY20" s="36" t="n">
         <f aca="false">SUM(CN20:CX20)</f>
-        <v>323740</v>
+        <v>169440</v>
       </c>
       <c r="CZ20" s="57"/>
       <c r="DA20" s="36" t="n">
@@ -21648,7 +21648,7 @@
       <c r="DB20" s="36"/>
       <c r="DC20" s="36" t="n">
         <f aca="false">-[4]Mar!$J$1</f>
-        <v>-0</v>
+        <v>-15200</v>
       </c>
       <c r="DD20" s="36" t="n">
         <f aca="false">-[5]Mar!$J$1</f>
@@ -21667,7 +21667,7 @@
       <c r="DI20" s="54"/>
       <c r="DJ20" s="36" t="n">
         <f aca="false">SUM(CY20:DI20)</f>
-        <v>359180</v>
+        <v>189680</v>
       </c>
       <c r="DK20" s="57"/>
       <c r="DL20" s="36" t="n">
@@ -21677,7 +21677,7 @@
       <c r="DM20" s="36"/>
       <c r="DN20" s="36" t="n">
         <f aca="false">-[4]Apr!$J$1</f>
-        <v>-0</v>
+        <v>-14300</v>
       </c>
       <c r="DO20" s="36" t="n">
         <f aca="false">-[5]Apr!$J$1</f>
@@ -21696,7 +21696,7 @@
       <c r="DT20" s="54"/>
       <c r="DU20" s="36" t="n">
         <f aca="false">SUM(DJ20:DT20)</f>
-        <v>393540</v>
+        <v>209740</v>
       </c>
       <c r="DV20" s="57"/>
       <c r="DW20" s="36" t="n">
@@ -21706,7 +21706,7 @@
       <c r="DX20" s="36"/>
       <c r="DY20" s="36" t="n">
         <f aca="false">-[4]May!$J$1</f>
-        <v>-0</v>
+        <v>-14800</v>
       </c>
       <c r="DZ20" s="36" t="n">
         <f aca="false">-[5]May!$J$1</f>
@@ -21725,13 +21725,13 @@
       <c r="EE20" s="54"/>
       <c r="EF20" s="36" t="n">
         <f aca="false">SUM(DU20:EE20)</f>
-        <v>424900</v>
+        <v>226300</v>
       </c>
       <c r="EG20" s="54"/>
       <c r="EI20" s="54"/>
       <c r="EJ20" s="36" t="n">
         <f aca="false">SUM(EF20:EH20)</f>
-        <v>424900</v>
+        <v>226300</v>
       </c>
       <c r="EK20" s="54"/>
     </row>
@@ -21888,7 +21888,7 @@
       <c r="G22" s="36"/>
       <c r="H22" s="36" t="n">
         <f aca="false">[4]Jun!$F$1-[4]Jun!$X$1</f>
-        <v>0</v>
+        <v>29600</v>
       </c>
       <c r="I22" s="36"/>
       <c r="J22" s="36"/>
@@ -21897,14 +21897,14 @@
       <c r="N22" s="57"/>
       <c r="O22" s="36" t="n">
         <f aca="false">SUM(D22:N22)</f>
-        <v>0</v>
+        <v>29600</v>
       </c>
       <c r="P22" s="57"/>
       <c r="Q22" s="36"/>
       <c r="R22" s="36"/>
       <c r="S22" s="36" t="n">
         <f aca="false">[4]Jul!$F$1-[4]Jul!$X$1</f>
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="T22" s="36"/>
       <c r="U22" s="36"/>
@@ -21914,14 +21914,14 @@
       <c r="Y22" s="54"/>
       <c r="Z22" s="36" t="n">
         <f aca="false">SUM(O22:Y22)</f>
-        <v>0</v>
+        <v>49100</v>
       </c>
       <c r="AA22" s="57"/>
       <c r="AB22" s="36"/>
       <c r="AC22" s="36"/>
       <c r="AD22" s="36" t="n">
         <f aca="false">[4]Aug!$F$1-[4]Aug!$X$1</f>
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="AE22" s="36"/>
       <c r="AF22" s="36"/>
@@ -21931,14 +21931,14 @@
       <c r="AJ22" s="54"/>
       <c r="AK22" s="36" t="n">
         <f aca="false">SUM(Z22:AJ22)</f>
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="AL22" s="57"/>
       <c r="AM22" s="36"/>
       <c r="AN22" s="36"/>
       <c r="AO22" s="36" t="n">
         <f aca="false">[4]Sep!$F$1-[4]Sep!$X$1</f>
-        <v>0</v>
+        <v>19100</v>
       </c>
       <c r="AP22" s="36"/>
       <c r="AQ22" s="36"/>
@@ -21948,14 +21948,14 @@
       <c r="AU22" s="54"/>
       <c r="AV22" s="36" t="n">
         <f aca="false">SUM(AK22:AU22)</f>
-        <v>0</v>
+        <v>88100</v>
       </c>
       <c r="AW22" s="57"/>
       <c r="AX22" s="36"/>
       <c r="AY22" s="36"/>
       <c r="AZ22" s="36" t="n">
         <f aca="false">[4]Oct!$F$1-[4]Oct!$X$1</f>
-        <v>0</v>
+        <v>22200</v>
       </c>
       <c r="BA22" s="36"/>
       <c r="BB22" s="36"/>
@@ -21965,14 +21965,14 @@
       <c r="BF22" s="54"/>
       <c r="BG22" s="36" t="n">
         <f aca="false">SUM(AV22:BF22)</f>
-        <v>0</v>
+        <v>110300</v>
       </c>
       <c r="BH22" s="57"/>
       <c r="BI22" s="36"/>
       <c r="BJ22" s="36"/>
       <c r="BK22" s="36" t="n">
         <f aca="false">[4]Nov!$F$1-[4]Nov!$X$1</f>
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="BL22" s="36"/>
       <c r="BM22" s="36"/>
@@ -21982,14 +21982,14 @@
       <c r="BQ22" s="54"/>
       <c r="BR22" s="36" t="n">
         <f aca="false">SUM(BG22:BQ22)</f>
-        <v>0</v>
+        <v>128300</v>
       </c>
       <c r="BS22" s="57"/>
       <c r="BT22" s="36"/>
       <c r="BU22" s="36"/>
       <c r="BV22" s="36" t="n">
         <f aca="false">[4]Dec!$F$1-[4]Dec!$X$1</f>
-        <v>0</v>
+        <v>72400</v>
       </c>
       <c r="BW22" s="36"/>
       <c r="BX22" s="36"/>
@@ -21999,14 +21999,14 @@
       <c r="CB22" s="54"/>
       <c r="CC22" s="36" t="n">
         <f aca="false">SUM(BR22:CB22)</f>
-        <v>0</v>
+        <v>200700</v>
       </c>
       <c r="CD22" s="57"/>
       <c r="CE22" s="36"/>
       <c r="CF22" s="36"/>
       <c r="CG22" s="36" t="n">
         <f aca="false">[4]Jan!$F$1-[4]Jan!$X$1</f>
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="CH22" s="36"/>
       <c r="CI22" s="36"/>
@@ -22016,14 +22016,14 @@
       <c r="CM22" s="54"/>
       <c r="CN22" s="36" t="n">
         <f aca="false">SUM(CC22:CM22)</f>
-        <v>0</v>
+        <v>220100</v>
       </c>
       <c r="CO22" s="57"/>
       <c r="CP22" s="36"/>
       <c r="CQ22" s="36"/>
       <c r="CR22" s="36" t="n">
         <f aca="false">[4]Feb!$F$1-[4]Feb!$X$1</f>
-        <v>0</v>
+        <v>19100</v>
       </c>
       <c r="CS22" s="36"/>
       <c r="CT22" s="36"/>
@@ -22033,14 +22033,14 @@
       <c r="CX22" s="54"/>
       <c r="CY22" s="36" t="n">
         <f aca="false">SUM(CN22:CX22)</f>
-        <v>0</v>
+        <v>239200</v>
       </c>
       <c r="CZ22" s="57"/>
       <c r="DA22" s="36"/>
       <c r="DB22" s="36"/>
       <c r="DC22" s="36" t="n">
         <f aca="false">[4]Mar!$F$1-[4]Mar!$X$1</f>
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="DD22" s="36"/>
       <c r="DE22" s="36"/>
@@ -22050,14 +22050,14 @@
       <c r="DI22" s="54"/>
       <c r="DJ22" s="36" t="n">
         <f aca="false">SUM(CY22:DI22)</f>
-        <v>0</v>
+        <v>266200</v>
       </c>
       <c r="DK22" s="57"/>
       <c r="DL22" s="36"/>
       <c r="DM22" s="36"/>
       <c r="DN22" s="36" t="n">
         <f aca="false">[4]Apr!$F$1-[4]Apr!$X$1</f>
-        <v>0</v>
+        <v>19700</v>
       </c>
       <c r="DO22" s="36"/>
       <c r="DP22" s="36"/>
@@ -22067,14 +22067,14 @@
       <c r="DT22" s="54"/>
       <c r="DU22" s="36" t="n">
         <f aca="false">SUM(DJ22:DT22)</f>
-        <v>0</v>
+        <v>285900</v>
       </c>
       <c r="DV22" s="57"/>
       <c r="DW22" s="36"/>
       <c r="DX22" s="36"/>
       <c r="DY22" s="36" t="n">
         <f aca="false">[4]May!$F$1-[4]May!$X$1</f>
-        <v>0</v>
+        <v>24600</v>
       </c>
       <c r="DZ22" s="36"/>
       <c r="EA22" s="36"/>
@@ -22084,13 +22084,13 @@
       <c r="EE22" s="54"/>
       <c r="EF22" s="36" t="n">
         <f aca="false">SUM(DU22:EE22)</f>
-        <v>0</v>
+        <v>310500</v>
       </c>
       <c r="EG22" s="54"/>
       <c r="EI22" s="54"/>
       <c r="EJ22" s="36" t="n">
         <f aca="false">SUM(EF22:EH22)</f>
-        <v>0</v>
+        <v>310500</v>
       </c>
       <c r="EK22" s="54"/>
     </row>
@@ -22196,7 +22196,7 @@
       <c r="BK23" s="36"/>
       <c r="BL23" s="36" t="n">
         <f aca="false">[5]Nov!$F$1-[5]Nov!$X$1</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="BM23" s="36"/>
       <c r="BN23" s="36"/>
@@ -22205,7 +22205,7 @@
       <c r="BQ23" s="54"/>
       <c r="BR23" s="36" t="n">
         <f aca="false">SUM(BG23:BQ23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="BS23" s="57"/>
       <c r="BT23" s="36"/>
@@ -22222,7 +22222,7 @@
       <c r="CB23" s="54"/>
       <c r="CC23" s="36" t="n">
         <f aca="false">SUM(BR23:CB23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="CD23" s="57"/>
       <c r="CE23" s="36"/>
@@ -22239,7 +22239,7 @@
       <c r="CM23" s="54"/>
       <c r="CN23" s="36" t="n">
         <f aca="false">SUM(CC23:CM23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="CO23" s="57"/>
       <c r="CP23" s="36"/>
@@ -22256,7 +22256,7 @@
       <c r="CX23" s="54"/>
       <c r="CY23" s="36" t="n">
         <f aca="false">SUM(CN23:CX23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="CZ23" s="57"/>
       <c r="DA23" s="36"/>
@@ -22273,7 +22273,7 @@
       <c r="DI23" s="54"/>
       <c r="DJ23" s="36" t="n">
         <f aca="false">SUM(CY23:DI23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="DK23" s="57"/>
       <c r="DL23" s="36"/>
@@ -22290,7 +22290,7 @@
       <c r="DT23" s="54"/>
       <c r="DU23" s="36" t="n">
         <f aca="false">SUM(DJ23:DT23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="DV23" s="57"/>
       <c r="DW23" s="36"/>
@@ -22298,7 +22298,7 @@
       <c r="DY23" s="36"/>
       <c r="DZ23" s="36" t="n">
         <f aca="false">[5]May!$F$1-[5]May!$X$1</f>
-        <v>0</v>
+        <v>5150</v>
       </c>
       <c r="EA23" s="36"/>
       <c r="EB23" s="36"/>
@@ -22307,13 +22307,13 @@
       <c r="EE23" s="54"/>
       <c r="EF23" s="36" t="n">
         <f aca="false">SUM(DU23:EE23)</f>
-        <v>0</v>
+        <v>5275</v>
       </c>
       <c r="EG23" s="54"/>
       <c r="EI23" s="54"/>
       <c r="EJ23" s="36" t="n">
         <f aca="false">SUM(EF23:EH23)</f>
-        <v>0</v>
+        <v>5275</v>
       </c>
       <c r="EK23" s="54"/>
     </row>
@@ -22336,14 +22336,14 @@
       <c r="I24" s="36"/>
       <c r="J24" s="36" t="n">
         <f aca="false">[6]Jun!$F$1-[6]Jun!$X$1</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K24" s="36"/>
       <c r="L24" s="36"/>
       <c r="N24" s="57"/>
       <c r="O24" s="36" t="n">
         <f aca="false">SUM(D24:N24)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P24" s="57"/>
       <c r="Q24" s="36"/>
@@ -22360,7 +22360,7 @@
       <c r="Y24" s="54"/>
       <c r="Z24" s="36" t="n">
         <f aca="false">SUM(O24:Y24)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AA24" s="57"/>
       <c r="AB24" s="36"/>
@@ -22369,7 +22369,7 @@
       <c r="AE24" s="36"/>
       <c r="AF24" s="36" t="n">
         <f aca="false">[6]Aug!$F$1-[6]Aug!$X$1</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG24" s="36"/>
       <c r="AH24" s="36"/>
@@ -22377,7 +22377,7 @@
       <c r="AJ24" s="54"/>
       <c r="AK24" s="36" t="n">
         <f aca="false">SUM(Z24:AJ24)</f>
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="AL24" s="57"/>
       <c r="AM24" s="36"/>
@@ -22386,7 +22386,7 @@
       <c r="AP24" s="36"/>
       <c r="AQ24" s="36" t="n">
         <f aca="false">[6]Sep!$F$1-[6]Sep!$X$1</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AR24" s="36"/>
       <c r="AS24" s="36"/>
@@ -22394,7 +22394,7 @@
       <c r="AU24" s="54"/>
       <c r="AV24" s="36" t="n">
         <f aca="false">SUM(AK24:AU24)</f>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AW24" s="57"/>
       <c r="AX24" s="36"/>
@@ -22411,7 +22411,7 @@
       <c r="BF24" s="54"/>
       <c r="BG24" s="36" t="n">
         <f aca="false">SUM(AV24:BF24)</f>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="BH24" s="57"/>
       <c r="BI24" s="36"/>
@@ -22428,7 +22428,7 @@
       <c r="BQ24" s="54"/>
       <c r="BR24" s="36" t="n">
         <f aca="false">SUM(BG24:BQ24)</f>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="BS24" s="57"/>
       <c r="BT24" s="36"/>
@@ -22437,7 +22437,7 @@
       <c r="BW24" s="36"/>
       <c r="BX24" s="36" t="n">
         <f aca="false">[6]Dec!$F$1-[6]Dec!$X$1</f>
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="BY24" s="36"/>
       <c r="BZ24" s="36"/>
@@ -22445,7 +22445,7 @@
       <c r="CB24" s="54"/>
       <c r="CC24" s="36" t="n">
         <f aca="false">SUM(BR24:CB24)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CD24" s="57"/>
       <c r="CE24" s="36"/>
@@ -22462,7 +22462,7 @@
       <c r="CM24" s="54"/>
       <c r="CN24" s="36" t="n">
         <f aca="false">SUM(CC24:CM24)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CO24" s="57"/>
       <c r="CP24" s="36"/>
@@ -22479,7 +22479,7 @@
       <c r="CX24" s="54"/>
       <c r="CY24" s="36" t="n">
         <f aca="false">SUM(CN24:CX24)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CZ24" s="57"/>
       <c r="DA24" s="36"/>
@@ -22488,7 +22488,7 @@
       <c r="DD24" s="36"/>
       <c r="DE24" s="36" t="n">
         <f aca="false">[6]Mar!$F$1-[6]Mar!$X$1</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="DF24" s="36"/>
       <c r="DG24" s="36"/>
@@ -22496,7 +22496,7 @@
       <c r="DI24" s="54"/>
       <c r="DJ24" s="36" t="n">
         <f aca="false">SUM(CY24:DI24)</f>
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="DK24" s="57"/>
       <c r="DL24" s="36"/>
@@ -22505,7 +22505,7 @@
       <c r="DO24" s="36"/>
       <c r="DP24" s="36" t="n">
         <f aca="false">[6]Apr!$F$1-[6]Apr!$X$1</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="DQ24" s="36"/>
       <c r="DR24" s="36"/>
@@ -22513,7 +22513,7 @@
       <c r="DT24" s="54"/>
       <c r="DU24" s="36" t="n">
         <f aca="false">SUM(DJ24:DT24)</f>
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="DV24" s="57"/>
       <c r="DW24" s="36"/>
@@ -22530,13 +22530,13 @@
       <c r="EE24" s="54"/>
       <c r="EF24" s="36" t="n">
         <f aca="false">SUM(DU24:EE24)</f>
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="EG24" s="54"/>
       <c r="EI24" s="54"/>
       <c r="EJ24" s="36" t="n">
         <f aca="false">SUM(EF24:EH24)</f>
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="EK24" s="54"/>
     </row>
@@ -22560,13 +22560,13 @@
       <c r="J25" s="36"/>
       <c r="K25" s="36" t="n">
         <f aca="false">[7]Jun!$F$1-[7]Jun!$U$1</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L25" s="36"/>
       <c r="N25" s="57"/>
       <c r="O25" s="36" t="n">
         <f aca="false">SUM(D25:N25)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P25" s="57"/>
       <c r="Q25" s="36"/>
@@ -22583,7 +22583,7 @@
       <c r="Y25" s="54"/>
       <c r="Z25" s="36" t="n">
         <f aca="false">SUM(O25:Y25)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA25" s="57"/>
       <c r="AB25" s="36"/>
@@ -22593,14 +22593,14 @@
       <c r="AF25" s="36"/>
       <c r="AG25" s="36" t="n">
         <f aca="false">[7]Aug!$F$1-[7]Aug!$U$1</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AH25" s="36"/>
       <c r="AI25" s="36"/>
       <c r="AJ25" s="54"/>
       <c r="AK25" s="36" t="n">
         <f aca="false">SUM(Z25:AJ25)</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AL25" s="57"/>
       <c r="AM25" s="36"/>
@@ -22617,7 +22617,7 @@
       <c r="AU25" s="54"/>
       <c r="AV25" s="36" t="n">
         <f aca="false">SUM(AK25:AU25)</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AW25" s="57"/>
       <c r="AX25" s="36"/>
@@ -22634,7 +22634,7 @@
       <c r="BF25" s="54"/>
       <c r="BG25" s="36" t="n">
         <f aca="false">SUM(AV25:BF25)</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BH25" s="57"/>
       <c r="BI25" s="36"/>
@@ -22644,14 +22644,14 @@
       <c r="BM25" s="36"/>
       <c r="BN25" s="36" t="n">
         <f aca="false">[7]Nov!$F$1-[7]Nov!$U$1</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BO25" s="36"/>
       <c r="BP25" s="36"/>
       <c r="BQ25" s="54"/>
       <c r="BR25" s="36" t="n">
         <f aca="false">SUM(BG25:BQ25)</f>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="BS25" s="57"/>
       <c r="BT25" s="36"/>
@@ -22668,7 +22668,7 @@
       <c r="CB25" s="54"/>
       <c r="CC25" s="36" t="n">
         <f aca="false">SUM(BR25:CB25)</f>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="CD25" s="57"/>
       <c r="CE25" s="36"/>
@@ -22685,7 +22685,7 @@
       <c r="CM25" s="54"/>
       <c r="CN25" s="36" t="n">
         <f aca="false">SUM(CC25:CM25)</f>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="CO25" s="57"/>
       <c r="CP25" s="36"/>
@@ -22695,14 +22695,14 @@
       <c r="CT25" s="36"/>
       <c r="CU25" s="36" t="n">
         <f aca="false">[7]Feb!$F$1-[7]Feb!$U$1</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CV25" s="36"/>
       <c r="CW25" s="36"/>
       <c r="CX25" s="54"/>
       <c r="CY25" s="36" t="n">
         <f aca="false">SUM(CN25:CX25)</f>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="CZ25" s="57"/>
       <c r="DA25" s="36"/>
@@ -22719,7 +22719,7 @@
       <c r="DI25" s="54"/>
       <c r="DJ25" s="36" t="n">
         <f aca="false">SUM(CY25:DI25)</f>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="DK25" s="57"/>
       <c r="DL25" s="36"/>
@@ -22736,7 +22736,7 @@
       <c r="DT25" s="54"/>
       <c r="DU25" s="36" t="n">
         <f aca="false">SUM(DJ25:DT25)</f>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="DV25" s="57"/>
       <c r="DW25" s="36"/>
@@ -22746,14 +22746,14 @@
       <c r="EA25" s="36"/>
       <c r="EB25" s="36" t="n">
         <f aca="false">[7]May!$F$1-[7]May!$U$1</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="EC25" s="36"/>
       <c r="ED25" s="36"/>
       <c r="EE25" s="54"/>
       <c r="EF25" s="36" t="n">
         <f aca="false">SUM(DU25:EE25)</f>
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="EG25" s="54"/>
       <c r="EH25" s="36" t="n">
@@ -22763,7 +22763,7 @@
       <c r="EI25" s="54"/>
       <c r="EJ25" s="36" t="n">
         <f aca="false">SUM(EF25:EH25)</f>
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="EK25" s="54"/>
     </row>
@@ -25076,7 +25076,7 @@
       </c>
       <c r="AZ33" s="36" t="n">
         <f aca="false">-[4]Oct!$N$1+[4]Oct!$AI$1</f>
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="BA33" s="36" t="n">
         <f aca="false">-[5]Oct!$N$1+[5]Oct!$AI$1</f>
@@ -25095,7 +25095,7 @@
       <c r="BF33" s="54"/>
       <c r="BG33" s="36" t="n">
         <f aca="false">SUM(AV33:BF33)</f>
-        <v>-28550</v>
+        <v>-31050</v>
       </c>
       <c r="BH33" s="57"/>
       <c r="BI33" s="36" t="n">
@@ -25112,7 +25112,7 @@
       </c>
       <c r="BL33" s="36" t="n">
         <f aca="false">-[5]Nov!$N$1+[5]Nov!$AI$1</f>
-        <v>0</v>
+        <v>-125</v>
       </c>
       <c r="BM33" s="36" t="n">
         <f aca="false">-[6]Nov!$N$1+[6]Nov!$AI$1</f>
@@ -25127,7 +25127,7 @@
       <c r="BQ33" s="54"/>
       <c r="BR33" s="36" t="n">
         <f aca="false">SUM(BG33:BQ33)</f>
-        <v>-34176.6666666667</v>
+        <v>-36801.6666666667</v>
       </c>
       <c r="BS33" s="57"/>
       <c r="BT33" s="36" t="n">
@@ -25159,7 +25159,7 @@
       <c r="CB33" s="54"/>
       <c r="CC33" s="36" t="n">
         <f aca="false">SUM(BR33:CB33)</f>
-        <v>-42603.3333333334</v>
+        <v>-45228.3333333334</v>
       </c>
       <c r="CD33" s="57"/>
       <c r="CE33" s="36" t="n">
@@ -25191,7 +25191,7 @@
       <c r="CM33" s="54"/>
       <c r="CN33" s="36" t="n">
         <f aca="false">SUM(CC33:CM33)</f>
-        <v>-48490</v>
+        <v>-51115</v>
       </c>
       <c r="CO33" s="57"/>
       <c r="CP33" s="36" t="n">
@@ -25223,7 +25223,7 @@
       <c r="CX33" s="54"/>
       <c r="CY33" s="36" t="n">
         <f aca="false">SUM(CN33:CX33)</f>
-        <v>-53956.6666666667</v>
+        <v>-56581.6666666667</v>
       </c>
       <c r="CZ33" s="57"/>
       <c r="DA33" s="36" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="DC33" s="36" t="n">
         <f aca="false">-[4]Mar!$N$1+[4]Mar!$AI$1</f>
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="DD33" s="36" t="n">
         <f aca="false">-[5]Mar!$N$1+[5]Mar!$AI$1</f>
@@ -25255,7 +25255,7 @@
       <c r="DI33" s="54"/>
       <c r="DJ33" s="36" t="n">
         <f aca="false">SUM(CY33:DI33)</f>
-        <v>-59863.3333333334</v>
+        <v>-63988.3333333334</v>
       </c>
       <c r="DK33" s="57"/>
       <c r="DL33" s="36" t="n">
@@ -25287,7 +25287,7 @@
       <c r="DT33" s="54"/>
       <c r="DU33" s="36" t="n">
         <f aca="false">SUM(DJ33:DT33)</f>
-        <v>-65590</v>
+        <v>-69715</v>
       </c>
       <c r="DV33" s="57"/>
       <c r="DW33" s="36" t="n">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="DZ33" s="36" t="n">
         <f aca="false">-[5]May!$N$1+[5]May!$AI$1</f>
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="EA33" s="36" t="n">
         <f aca="false">-[6]May!$N$1+[6]May!$AI$1</f>
@@ -25319,13 +25319,13 @@
       <c r="EE33" s="54"/>
       <c r="EF33" s="36" t="n">
         <f aca="false">SUM(DU33:EE33)</f>
-        <v>-70816.6666666667</v>
+        <v>-75091.6666666667</v>
       </c>
       <c r="EG33" s="54"/>
       <c r="EI33" s="54"/>
       <c r="EJ33" s="36" t="n">
         <f aca="false">SUM(EF33:EH33)</f>
-        <v>-70816.6666666667</v>
+        <v>-75091.6666666667</v>
       </c>
       <c r="EK33" s="54"/>
     </row>
@@ -26015,12 +26015,12 @@
       <c r="EC35" s="36"/>
       <c r="ED35" s="36" t="n">
         <f aca="false">-CorporationTax!K35</f>
-        <v>-51792.3058333333</v>
+        <v>-53046.3058333333</v>
       </c>
       <c r="EE35" s="54"/>
       <c r="EF35" s="36" t="n">
         <f aca="false">SUM(DU35:EE35)</f>
-        <v>-51792.3058333333</v>
+        <v>-53046.3058333333</v>
       </c>
       <c r="EG35" s="54"/>
       <c r="EH35" s="36" t="n">
@@ -26030,7 +26030,7 @@
       <c r="EI35" s="54"/>
       <c r="EJ35" s="36" t="n">
         <f aca="false">SUM(EF35:EH35)</f>
-        <v>-51792.3058333333</v>
+        <v>-53046.3058333333</v>
       </c>
       <c r="EK35" s="54"/>
     </row>
@@ -26654,7 +26654,7 @@
       <c r="G39" s="36"/>
       <c r="H39" s="36" t="n">
         <f aca="false">-[4]Jun!$P$1+[4]Jun!$AM$1</f>
-        <v>0</v>
+        <v>-137837</v>
       </c>
       <c r="I39" s="36" t="n">
         <f aca="false">-[5]Jun!$P$1+[5]Jun!$AM$1</f>
@@ -26672,14 +26672,14 @@
       <c r="N39" s="57"/>
       <c r="O39" s="36" t="n">
         <f aca="false">SUM(D39:N39)</f>
-        <v>0</v>
+        <v>-137837</v>
       </c>
       <c r="P39" s="57"/>
       <c r="Q39" s="36"/>
       <c r="R39" s="36"/>
       <c r="S39" s="36" t="n">
         <f aca="false">-[4]Jul!$P$1+[4]Jul!$AM$1</f>
-        <v>0</v>
+        <v>-137586</v>
       </c>
       <c r="T39" s="36" t="n">
         <f aca="false">-[5]Jul!$P$1+[5]Jul!$AM$1</f>
@@ -26687,7 +26687,7 @@
       </c>
       <c r="U39" s="36" t="n">
         <f aca="false">-[6]Jul!$P$1+[6]Jul!$AM$1</f>
-        <v>0</v>
+        <v>-45858</v>
       </c>
       <c r="V39" s="36" t="n">
         <f aca="false">-[7]Jul!$N$1+[7]Jul!$AJ$1</f>
@@ -26698,14 +26698,14 @@
       <c r="Y39" s="54"/>
       <c r="Z39" s="36" t="n">
         <f aca="false">SUM(O39:Y39)</f>
-        <v>0</v>
+        <v>-321281</v>
       </c>
       <c r="AA39" s="57"/>
       <c r="AB39" s="36"/>
       <c r="AC39" s="36"/>
       <c r="AD39" s="36" t="n">
         <f aca="false">-[4]Aug!$P$1+[4]Aug!$AM$1</f>
-        <v>0</v>
+        <v>-137684</v>
       </c>
       <c r="AE39" s="36" t="n">
         <f aca="false">-[5]Aug!$P$1+[5]Aug!$AM$1</f>
@@ -26724,14 +26724,14 @@
       <c r="AJ39" s="54"/>
       <c r="AK39" s="36" t="n">
         <f aca="false">SUM(Z39:AJ39)</f>
-        <v>0</v>
+        <v>-458965</v>
       </c>
       <c r="AL39" s="57"/>
       <c r="AM39" s="36"/>
       <c r="AN39" s="36"/>
       <c r="AO39" s="36" t="n">
         <f aca="false">-[4]Sep!$P$1+[4]Sep!$AM$1</f>
-        <v>0</v>
+        <v>-229588</v>
       </c>
       <c r="AP39" s="36" t="n">
         <f aca="false">-[5]Sep!$P$1+[5]Sep!$AM$1</f>
@@ -26750,14 +26750,14 @@
       <c r="AU39" s="54"/>
       <c r="AV39" s="36" t="n">
         <f aca="false">SUM(AK39:AU39)</f>
-        <v>0</v>
+        <v>-688553</v>
       </c>
       <c r="AW39" s="57"/>
       <c r="AX39" s="36"/>
       <c r="AY39" s="36"/>
       <c r="AZ39" s="36" t="n">
         <f aca="false">-[4]Oct!$P$1+[4]Oct!$AM$1</f>
-        <v>0</v>
+        <v>-91907</v>
       </c>
       <c r="BA39" s="36" t="n">
         <f aca="false">-[5]Oct!$P$1+[5]Oct!$AM$1</f>
@@ -26776,14 +26776,14 @@
       <c r="BF39" s="54"/>
       <c r="BG39" s="36" t="n">
         <f aca="false">SUM(AV39:BF39)</f>
-        <v>0</v>
+        <v>-780460</v>
       </c>
       <c r="BH39" s="57"/>
       <c r="BI39" s="36"/>
       <c r="BJ39" s="36"/>
       <c r="BK39" s="36" t="n">
         <f aca="false">-[4]Nov!$P$1+[4]Nov!$AM$1</f>
-        <v>0</v>
+        <v>-137960</v>
       </c>
       <c r="BL39" s="36" t="n">
         <f aca="false">-[5]Nov!$P$1+[5]Nov!$AM$1</f>
@@ -26802,14 +26802,14 @@
       <c r="BQ39" s="54"/>
       <c r="BR39" s="36" t="n">
         <f aca="false">SUM(BG39:BQ39)</f>
-        <v>0</v>
+        <v>-918420</v>
       </c>
       <c r="BS39" s="57"/>
       <c r="BT39" s="36"/>
       <c r="BU39" s="36"/>
       <c r="BV39" s="36" t="n">
         <f aca="false">-[4]Dec!$P$1+[4]Dec!$AM$1</f>
-        <v>0</v>
+        <v>-230025</v>
       </c>
       <c r="BW39" s="36" t="n">
         <f aca="false">-[5]Dec!$P$1+[5]Dec!$AM$1</f>
@@ -26828,14 +26828,14 @@
       <c r="CB39" s="54"/>
       <c r="CC39" s="36" t="n">
         <f aca="false">SUM(BR39:CB39)</f>
-        <v>0</v>
+        <v>-1148445</v>
       </c>
       <c r="CD39" s="57"/>
       <c r="CE39" s="36"/>
       <c r="CF39" s="36"/>
       <c r="CG39" s="36" t="n">
         <f aca="false">-[4]Jan!$P$1+[4]Jan!$AM$1</f>
-        <v>0</v>
+        <v>-138138</v>
       </c>
       <c r="CH39" s="36" t="n">
         <f aca="false">-[5]Jan!$P$1+[5]Jan!$AM$1</f>
@@ -26854,14 +26854,14 @@
       <c r="CM39" s="54"/>
       <c r="CN39" s="36" t="n">
         <f aca="false">SUM(CC39:CM39)</f>
-        <v>0</v>
+        <v>-1286583</v>
       </c>
       <c r="CO39" s="57"/>
       <c r="CP39" s="36"/>
       <c r="CQ39" s="36"/>
       <c r="CR39" s="36" t="n">
         <f aca="false">-[4]Feb!$P$1+[4]Feb!$AM$1</f>
-        <v>0</v>
+        <v>-184309</v>
       </c>
       <c r="CS39" s="36" t="n">
         <f aca="false">-[5]Feb!$P$1+[5]Feb!$AM$1</f>
@@ -26880,14 +26880,14 @@
       <c r="CX39" s="54"/>
       <c r="CY39" s="36" t="n">
         <f aca="false">SUM(CN39:CX39)</f>
-        <v>0</v>
+        <v>-1470892</v>
       </c>
       <c r="CZ39" s="57"/>
       <c r="DA39" s="36"/>
       <c r="DB39" s="36"/>
       <c r="DC39" s="36" t="n">
         <f aca="false">-[4]Mar!$P$1+[4]Mar!$AM$1</f>
-        <v>0</v>
+        <v>-138305</v>
       </c>
       <c r="DD39" s="36" t="n">
         <f aca="false">-[5]Mar!$P$1+[5]Mar!$AM$1</f>
@@ -26906,14 +26906,14 @@
       <c r="DI39" s="54"/>
       <c r="DJ39" s="36" t="n">
         <f aca="false">SUM(CY39:DI39)</f>
-        <v>0</v>
+        <v>-1609197</v>
       </c>
       <c r="DK39" s="57"/>
       <c r="DL39" s="36"/>
       <c r="DM39" s="36"/>
       <c r="DN39" s="36" t="n">
         <f aca="false">-[4]Apr!$P$1+[4]Apr!$AM$1</f>
-        <v>0</v>
+        <v>-92271</v>
       </c>
       <c r="DO39" s="36" t="n">
         <f aca="false">-[5]Apr!$P$1+[5]Apr!$AM$1</f>
@@ -26932,14 +26932,14 @@
       <c r="DT39" s="54"/>
       <c r="DU39" s="36" t="n">
         <f aca="false">SUM(DJ39:DT39)</f>
-        <v>0</v>
+        <v>-1701468</v>
       </c>
       <c r="DV39" s="57"/>
       <c r="DW39" s="36"/>
       <c r="DX39" s="36"/>
       <c r="DY39" s="36" t="n">
         <f aca="false">-[4]May!$P$1+[4]May!$AM$1</f>
-        <v>0</v>
+        <v>-184677</v>
       </c>
       <c r="DZ39" s="36" t="n">
         <f aca="false">-[5]May!$P$1+[5]May!$AM$1</f>
@@ -26958,13 +26958,13 @@
       <c r="EE39" s="54"/>
       <c r="EF39" s="36" t="n">
         <f aca="false">SUM(DU39:EE39)</f>
-        <v>0</v>
+        <v>-1886145</v>
       </c>
       <c r="EG39" s="54"/>
       <c r="EI39" s="54"/>
       <c r="EJ39" s="36" t="n">
         <f aca="false">SUM(EF39:EH39)</f>
-        <v>0</v>
+        <v>-1886145</v>
       </c>
       <c r="EK39" s="54"/>
     </row>
@@ -27808,12 +27808,12 @@
       <c r="EG43" s="54"/>
       <c r="EH43" s="36" t="n">
         <f aca="false">-'PubP&amp;L'!F54</f>
-        <v>-217798.7775</v>
+        <v>-223144.7775</v>
       </c>
       <c r="EI43" s="54"/>
       <c r="EJ43" s="36" t="n">
         <f aca="false">SUM(EF43:EH43)</f>
-        <v>-217798.7775</v>
+        <v>-223144.7775</v>
       </c>
       <c r="EK43" s="54"/>
     </row>
@@ -28442,18 +28442,18 @@
       <c r="EC47" s="36"/>
       <c r="ED47" s="36" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="EE47" s="54"/>
       <c r="EF47" s="36" t="n">
         <f aca="false">SUM(DU47:EE47)</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="EG47" s="54"/>
       <c r="EI47" s="54"/>
       <c r="EJ47" s="36" t="n">
         <f aca="false">SUM(EF47:EH47)</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="EK47" s="54"/>
     </row>
@@ -28822,12 +28822,12 @@
       <c r="EG49" s="54"/>
       <c r="EH49" s="36" t="n">
         <f aca="false">'PubP&amp;L'!F54</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="EI49" s="54"/>
       <c r="EJ49" s="36" t="n">
         <f aca="false">SUM(EF49:EH49)</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="EK49" s="54"/>
     </row>
@@ -37188,14 +37188,14 @@
       </c>
       <c r="J88" s="36" t="n">
         <f aca="false">-[6]Jun!$Q$1</f>
-        <v>-0</v>
+        <v>-500</v>
       </c>
       <c r="K88" s="36"/>
       <c r="L88" s="36"/>
       <c r="N88" s="57"/>
       <c r="O88" s="36" t="n">
         <f aca="false">SUM(D88:N88)</f>
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="P88" s="57"/>
       <c r="Q88" s="36"/>
@@ -37218,7 +37218,7 @@
       <c r="Y88" s="54"/>
       <c r="Z88" s="36" t="n">
         <f aca="false">SUM(O88:Y88)</f>
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="AA88" s="57"/>
       <c r="AB88" s="36"/>
@@ -37241,7 +37241,7 @@
       <c r="AJ88" s="54"/>
       <c r="AK88" s="36" t="n">
         <f aca="false">SUM(Z88:AJ88)</f>
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="AL88" s="57"/>
       <c r="AM88" s="36"/>
@@ -37256,7 +37256,7 @@
       </c>
       <c r="AQ88" s="36" t="n">
         <f aca="false">-[6]Sep!$Q$1</f>
-        <v>-0</v>
+        <v>-300</v>
       </c>
       <c r="AR88" s="36"/>
       <c r="AS88" s="36"/>
@@ -37264,7 +37264,7 @@
       <c r="AU88" s="54"/>
       <c r="AV88" s="36" t="n">
         <f aca="false">SUM(AK88:AU88)</f>
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="AW88" s="57"/>
       <c r="AX88" s="36"/>
@@ -37287,7 +37287,7 @@
       <c r="BF88" s="54"/>
       <c r="BG88" s="36" t="n">
         <f aca="false">SUM(AV88:BF88)</f>
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="BH88" s="57"/>
       <c r="BI88" s="36"/>
@@ -37310,7 +37310,7 @@
       <c r="BQ88" s="54"/>
       <c r="BR88" s="36" t="n">
         <f aca="false">SUM(BG88:BQ88)</f>
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="BS88" s="57"/>
       <c r="BT88" s="36"/>
@@ -37325,7 +37325,7 @@
       </c>
       <c r="BX88" s="36" t="n">
         <f aca="false">-[6]Dec!$Q$1</f>
-        <v>-0</v>
+        <v>-500</v>
       </c>
       <c r="BY88" s="36"/>
       <c r="BZ88" s="36"/>
@@ -37333,7 +37333,7 @@
       <c r="CB88" s="54"/>
       <c r="CC88" s="36" t="n">
         <f aca="false">SUM(BR88:CB88)</f>
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="CD88" s="57"/>
       <c r="CE88" s="36"/>
@@ -37356,7 +37356,7 @@
       <c r="CM88" s="54"/>
       <c r="CN88" s="36" t="n">
         <f aca="false">SUM(CC88:CM88)</f>
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="CO88" s="57"/>
       <c r="CP88" s="36"/>
@@ -37379,7 +37379,7 @@
       <c r="CX88" s="54"/>
       <c r="CY88" s="36" t="n">
         <f aca="false">SUM(CN88:CX88)</f>
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="CZ88" s="57"/>
       <c r="DA88" s="36"/>
@@ -37394,7 +37394,7 @@
       </c>
       <c r="DE88" s="36" t="n">
         <f aca="false">-[6]Mar!$Q$1</f>
-        <v>-0</v>
+        <v>-300</v>
       </c>
       <c r="DF88" s="36"/>
       <c r="DG88" s="36"/>
@@ -37402,7 +37402,7 @@
       <c r="DI88" s="54"/>
       <c r="DJ88" s="36" t="n">
         <f aca="false">SUM(CY88:DI88)</f>
-        <v>0</v>
+        <v>-1600</v>
       </c>
       <c r="DK88" s="57"/>
       <c r="DL88" s="36"/>
@@ -37425,7 +37425,7 @@
       <c r="DT88" s="54"/>
       <c r="DU88" s="36" t="n">
         <f aca="false">SUM(DJ88:DT88)</f>
-        <v>0</v>
+        <v>-1600</v>
       </c>
       <c r="DV88" s="57"/>
       <c r="DW88" s="36"/>
@@ -37436,7 +37436,7 @@
       </c>
       <c r="DZ88" s="36" t="n">
         <f aca="false">-[5]May!$Q$1</f>
-        <v>-0</v>
+        <v>-5000</v>
       </c>
       <c r="EA88" s="36" t="n">
         <f aca="false">-[6]May!$Q$1</f>
@@ -37448,13 +37448,13 @@
       <c r="EE88" s="54"/>
       <c r="EF88" s="36" t="n">
         <f aca="false">SUM(DU88:EE88)</f>
-        <v>0</v>
+        <v>-6600</v>
       </c>
       <c r="EG88" s="54"/>
       <c r="EI88" s="54"/>
       <c r="EJ88" s="36" t="n">
         <f aca="false">SUM(EF88:EH88)</f>
-        <v>0</v>
+        <v>-6600</v>
       </c>
       <c r="EK88" s="54"/>
     </row>
@@ -37905,7 +37905,7 @@
       </c>
       <c r="H91" s="36" t="n">
         <f aca="false">SUM(H4:H90)</f>
-        <v>0</v>
+        <v>-132637</v>
       </c>
       <c r="I91" s="36" t="n">
         <f aca="false">SUM(I4:I90)</f>
@@ -37917,7 +37917,7 @@
       </c>
       <c r="K91" s="36" t="n">
         <f aca="false">SUM(K4:K90)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L91" s="36" t="n">
         <f aca="false">SUM(L4:L90)</f>
@@ -37930,7 +37930,7 @@
       <c r="N91" s="54"/>
       <c r="O91" s="36" t="n">
         <f aca="false">SUM(O4:O90)</f>
-        <v>3.09228198602796E-011</v>
+        <v>-132622</v>
       </c>
       <c r="P91" s="54"/>
       <c r="Q91" s="36" t="n">
@@ -37943,7 +37943,7 @@
       </c>
       <c r="S91" s="36" t="n">
         <f aca="false">SUM(S4:S90)</f>
-        <v>0</v>
+        <v>-132286</v>
       </c>
       <c r="T91" s="36" t="n">
         <f aca="false">SUM(T4:T90)</f>
@@ -37951,7 +37951,7 @@
       </c>
       <c r="U91" s="36" t="n">
         <f aca="false">SUM(U4:U90)</f>
-        <v>0</v>
+        <v>-45858</v>
       </c>
       <c r="V91" s="36" t="n">
         <f aca="false">SUM(V4:V90)</f>
@@ -37968,7 +37968,7 @@
       <c r="Y91" s="54"/>
       <c r="Z91" s="36" t="n">
         <f aca="false">SUM(Z4:Z90)</f>
-        <v>6.18456397205591E-011</v>
+        <v>-310766</v>
       </c>
       <c r="AA91" s="54"/>
       <c r="AB91" s="36" t="n">
@@ -37981,7 +37981,7 @@
       </c>
       <c r="AD91" s="36" t="n">
         <f aca="false">SUM(AD4:AD90)</f>
-        <v>0</v>
+        <v>-132684</v>
       </c>
       <c r="AE91" s="36" t="n">
         <f aca="false">SUM(AE4:AE90)</f>
@@ -37989,11 +37989,11 @@
       </c>
       <c r="AF91" s="36" t="n">
         <f aca="false">SUM(AF4:AF90)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG91" s="36" t="n">
         <f aca="false">SUM(AG4:AG90)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AH91" s="36" t="n">
         <f aca="false">SUM(AH4:AH90)</f>
@@ -38006,7 +38006,7 @@
       <c r="AJ91" s="54"/>
       <c r="AK91" s="36" t="n">
         <f aca="false">SUM(AK4:AK90)</f>
-        <v>9.45874489843845E-011</v>
+        <v>-443145</v>
       </c>
       <c r="AL91" s="54"/>
       <c r="AM91" s="36" t="n">
@@ -38019,7 +38019,7 @@
       </c>
       <c r="AO91" s="36" t="n">
         <f aca="false">SUM(AO4:AO90)</f>
-        <v>0</v>
+        <v>-224488</v>
       </c>
       <c r="AP91" s="36" t="n">
         <f aca="false">SUM(AP4:AP90)</f>
@@ -38044,7 +38044,7 @@
       <c r="AU91" s="54"/>
       <c r="AV91" s="36" t="n">
         <f aca="false">SUM(AV4:AV90)</f>
-        <v>1.23691279441118E-010</v>
+        <v>-667633</v>
       </c>
       <c r="AW91" s="54"/>
       <c r="AX91" s="36" t="n">
@@ -38057,7 +38057,7 @@
       </c>
       <c r="AZ91" s="36" t="n">
         <f aca="false">SUM(AZ4:AZ90)</f>
-        <v>0</v>
+        <v>-86807</v>
       </c>
       <c r="BA91" s="36" t="n">
         <f aca="false">SUM(BA4:BA90)</f>
@@ -38082,7 +38082,7 @@
       <c r="BF91" s="54"/>
       <c r="BG91" s="36" t="n">
         <f aca="false">SUM(BG4:BG90)</f>
-        <v>1.65982783073559E-010</v>
+        <v>-754440</v>
       </c>
       <c r="BH91" s="54"/>
       <c r="BI91" s="36" t="n">
@@ -38095,7 +38095,7 @@
       </c>
       <c r="BK91" s="36" t="n">
         <f aca="false">SUM(BK4:BK90)</f>
-        <v>0</v>
+        <v>-133360</v>
       </c>
       <c r="BL91" s="36" t="n">
         <f aca="false">SUM(BL4:BL90)</f>
@@ -38107,7 +38107,7 @@
       </c>
       <c r="BN91" s="36" t="n">
         <f aca="false">SUM(BN4:BN90)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BO91" s="36" t="n">
         <f aca="false">SUM(BO4:BO90)</f>
@@ -38120,7 +38120,7 @@
       <c r="BQ91" s="54"/>
       <c r="BR91" s="36" t="n">
         <f aca="false">SUM(BR4:BR90)</f>
-        <v>1.95086613530293E-010</v>
+        <v>-887782</v>
       </c>
       <c r="BS91" s="54"/>
       <c r="BT91" s="36" t="n">
@@ -38133,7 +38133,7 @@
       </c>
       <c r="BV91" s="36" t="n">
         <f aca="false">SUM(BV4:BV90)</f>
-        <v>0</v>
+        <v>-188025</v>
       </c>
       <c r="BW91" s="36" t="n">
         <f aca="false">SUM(BW4:BW90)</f>
@@ -38141,7 +38141,7 @@
       </c>
       <c r="BX91" s="36" t="n">
         <f aca="false">SUM(BX4:BX90)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BY91" s="36" t="n">
         <f aca="false">SUM(BY4:BY90)</f>
@@ -38158,7 +38158,7 @@
       <c r="CB91" s="54"/>
       <c r="CC91" s="36" t="n">
         <f aca="false">SUM(CC4:CC90)</f>
-        <v>2.38742359215394E-010</v>
+        <v>-1075687</v>
       </c>
       <c r="CD91" s="54"/>
       <c r="CE91" s="36" t="n">
@@ -38171,7 +38171,7 @@
       </c>
       <c r="CG91" s="36" t="n">
         <f aca="false">SUM(CG4:CG90)</f>
-        <v>0</v>
+        <v>-133238</v>
       </c>
       <c r="CH91" s="36" t="n">
         <f aca="false">SUM(CH4:CH90)</f>
@@ -38196,7 +38196,7 @@
       <c r="CM91" s="54"/>
       <c r="CN91" s="36" t="n">
         <f aca="false">SUM(CN4:CN90)</f>
-        <v>2.53294274443761E-010</v>
+        <v>-1208925</v>
       </c>
       <c r="CO91" s="54"/>
       <c r="CP91" s="36" t="n">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="CR91" s="36" t="n">
         <f aca="false">SUM(CR4:CR90)</f>
-        <v>0</v>
+        <v>-179109</v>
       </c>
       <c r="CS91" s="36" t="n">
         <f aca="false">SUM(CS4:CS90)</f>
@@ -38221,7 +38221,7 @@
       </c>
       <c r="CU91" s="36" t="n">
         <f aca="false">SUM(CU4:CU90)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CV91" s="36" t="n">
         <f aca="false">SUM(CV4:CV90)</f>
@@ -38234,7 +38234,7 @@
       <c r="CX91" s="54"/>
       <c r="CY91" s="36" t="n">
         <f aca="false">SUM(CY4:CY90)</f>
-        <v>2.67846189672127E-010</v>
+        <v>-1387984</v>
       </c>
       <c r="CZ91" s="54"/>
       <c r="DA91" s="36" t="n">
@@ -38247,7 +38247,7 @@
       </c>
       <c r="DC91" s="36" t="n">
         <f aca="false">SUM(DC4:DC90)</f>
-        <v>0</v>
+        <v>-128005</v>
       </c>
       <c r="DD91" s="36" t="n">
         <f aca="false">SUM(DD4:DD90)</f>
@@ -38272,7 +38272,7 @@
       <c r="DI91" s="54"/>
       <c r="DJ91" s="36" t="n">
         <f aca="false">SUM(DJ4:DJ90)</f>
-        <v>2.82398104900494E-010</v>
+        <v>-1515989</v>
       </c>
       <c r="DK91" s="54"/>
       <c r="DL91" s="36" t="n">
@@ -38285,7 +38285,7 @@
       </c>
       <c r="DN91" s="36" t="n">
         <f aca="false">SUM(DN4:DN90)</f>
-        <v>0</v>
+        <v>-86871</v>
       </c>
       <c r="DO91" s="36" t="n">
         <f aca="false">SUM(DO4:DO90)</f>
@@ -38293,7 +38293,7 @@
       </c>
       <c r="DP91" s="36" t="n">
         <f aca="false">SUM(DP4:DP90)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="DQ91" s="36" t="n">
         <f aca="false">SUM(DQ4:DQ90)</f>
@@ -38310,7 +38310,7 @@
       <c r="DT91" s="54"/>
       <c r="DU91" s="36" t="n">
         <f aca="false">SUM(DU4:DU90)</f>
-        <v>3.04225977743045E-010</v>
+        <v>-1602620</v>
       </c>
       <c r="DV91" s="54"/>
       <c r="DW91" s="36" t="n">
@@ -38323,7 +38323,7 @@
       </c>
       <c r="DY91" s="36" t="n">
         <f aca="false">SUM(DY4:DY90)</f>
-        <v>0</v>
+        <v>-174877</v>
       </c>
       <c r="DZ91" s="36" t="n">
         <f aca="false">SUM(DZ4:DZ90)</f>
@@ -38335,7 +38335,7 @@
       </c>
       <c r="EB91" s="36" t="n">
         <f aca="false">SUM(EB4:EB90)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="EC91" s="36" t="n">
         <f aca="false">SUM(EC4:EC90)</f>
@@ -38348,7 +38348,7 @@
       <c r="EE91" s="54"/>
       <c r="EF91" s="36" t="n">
         <f aca="false">SUM(EF4:EF90)</f>
-        <v>3.18777892971411E-010</v>
+        <v>-1777485</v>
       </c>
       <c r="EG91" s="54"/>
       <c r="EH91" s="36" t="n">
@@ -38358,7 +38358,7 @@
       <c r="EI91" s="54"/>
       <c r="EJ91" s="36" t="n">
         <f aca="false">SUM(EJ4:EJ90)</f>
-        <v>3.18777892971411E-010</v>
+        <v>-1777485</v>
       </c>
       <c r="EK91" s="54"/>
     </row>
@@ -40476,11 +40476,11 @@
       </c>
       <c r="B36" s="71" t="n">
         <f aca="false">SUM(C36:N36)</f>
-        <v>0</v>
+        <v>-6600</v>
       </c>
       <c r="C36" s="72" t="n">
         <f aca="false">TrialBalance!O83+TrialBalance!O88+TrialBalance!O89-0</f>
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="D36" s="72" t="n">
         <f aca="false">TrialBalance!Z83+TrialBalance!Z88+TrialBalance!Z89-C36</f>
@@ -40492,7 +40492,7 @@
       </c>
       <c r="F36" s="72" t="n">
         <f aca="false">TrialBalance!AV83+TrialBalance!AV88+TrialBalance!AV89-SUM(C36:E36)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G36" s="72" t="n">
         <f aca="false">TrialBalance!BG83+TrialBalance!BG88+TrialBalance!BG89-SUM(C36:F36)</f>
@@ -40504,7 +40504,7 @@
       </c>
       <c r="I36" s="72" t="n">
         <f aca="false">TrialBalance!CC83+TrialBalance!CC88+TrialBalance!CC89-SUM(C36:H36)</f>
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="J36" s="72" t="n">
         <f aca="false">TrialBalance!CN83+TrialBalance!CN88+TrialBalance!CN89-SUM(C36:I36)</f>
@@ -40516,7 +40516,7 @@
       </c>
       <c r="L36" s="72" t="n">
         <f aca="false">TrialBalance!DJ83+TrialBalance!DJ88+TrialBalance!DJ89-SUM(C36:K36)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="M36" s="72" t="n">
         <f aca="false">TrialBalance!DU83+TrialBalance!DU88+TrialBalance!DU89-SUM(C36:L36)</f>
@@ -40524,7 +40524,7 @@
       </c>
       <c r="N36" s="72" t="n">
         <f aca="false">TrialBalance!EF83+TrialBalance!EF88+TrialBalance!EF89-SUM(C36:M36)</f>
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="O36" s="68"/>
     </row>
@@ -40766,11 +40766,11 @@
       </c>
       <c r="B41" s="71" t="n">
         <f aca="false">SUM(B18:B40)</f>
-        <v>53948.25</v>
+        <v>47348.25</v>
       </c>
       <c r="C41" s="74" t="n">
         <f aca="false">SUM(C18:C40)</f>
-        <v>4226.25</v>
+        <v>3726.25</v>
       </c>
       <c r="D41" s="71" t="n">
         <f aca="false">SUM(D18:D40)</f>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="F41" s="71" t="n">
         <f aca="false">SUM(F18:F40)</f>
-        <v>6590.25</v>
+        <v>6290.25</v>
       </c>
       <c r="G41" s="71" t="n">
         <f aca="false">SUM(G18:G40)</f>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="I41" s="71" t="n">
         <f aca="false">SUM(I18:I40)</f>
-        <v>6240.75</v>
+        <v>5740.75</v>
       </c>
       <c r="J41" s="71" t="n">
         <f aca="false">SUM(J18:J40)</f>
@@ -40806,7 +40806,7 @@
       </c>
       <c r="L41" s="71" t="n">
         <f aca="false">SUM(L18:L40)</f>
-        <v>9129.25</v>
+        <v>8829.25</v>
       </c>
       <c r="M41" s="71" t="n">
         <f aca="false">SUM(M18:M40)</f>
@@ -40814,7 +40814,7 @@
       </c>
       <c r="N41" s="71" t="n">
         <f aca="false">SUM(N18:N40)</f>
-        <v>2877.5</v>
+        <v>-2122.5</v>
       </c>
       <c r="O41" s="68"/>
     </row>
@@ -40841,11 +40841,11 @@
       </c>
       <c r="B43" s="71" t="n">
         <f aca="false">B16-B41</f>
-        <v>269591.083333333</v>
+        <v>276191.083333333</v>
       </c>
       <c r="C43" s="71" t="n">
         <f aca="false">C16-C41</f>
-        <v>22722.0833333333</v>
+        <v>23222.0833333333</v>
       </c>
       <c r="D43" s="71" t="n">
         <f aca="false">D16-D41</f>
@@ -40857,7 +40857,7 @@
       </c>
       <c r="F43" s="71" t="n">
         <f aca="false">F16-F41</f>
-        <v>20574.0833333333</v>
+        <v>20874.0833333333</v>
       </c>
       <c r="G43" s="71" t="n">
         <f aca="false">G16-G41</f>
@@ -40869,7 +40869,7 @@
       </c>
       <c r="I43" s="71" t="n">
         <f aca="false">I16-I41</f>
-        <v>22627.5833333333</v>
+        <v>23127.5833333333</v>
       </c>
       <c r="J43" s="71" t="n">
         <f aca="false">J16-J41</f>
@@ -40881,7 +40881,7 @@
       </c>
       <c r="L43" s="71" t="n">
         <f aca="false">L16-L41</f>
-        <v>19555.0833333333</v>
+        <v>19855.0833333333</v>
       </c>
       <c r="M43" s="71" t="n">
         <f aca="false">M16-M41</f>
@@ -40889,7 +40889,7 @@
       </c>
       <c r="N43" s="71" t="n">
         <f aca="false">N16-N41</f>
-        <v>22406.8333333333</v>
+        <v>27406.8333333333</v>
       </c>
       <c r="O43" s="68"/>
     </row>
@@ -40957,11 +40957,11 @@
       </c>
       <c r="B45" s="71" t="n">
         <f aca="false">B43+B44</f>
-        <v>269591.083333333</v>
+        <v>276191.083333333</v>
       </c>
       <c r="C45" s="71" t="n">
         <f aca="false">C43+C44</f>
-        <v>22722.0833333333</v>
+        <v>23222.0833333333</v>
       </c>
       <c r="D45" s="71" t="n">
         <f aca="false">D43+D44</f>
@@ -40973,7 +40973,7 @@
       </c>
       <c r="F45" s="71" t="n">
         <f aca="false">F43+F44</f>
-        <v>20574.0833333333</v>
+        <v>20874.0833333333</v>
       </c>
       <c r="G45" s="71" t="n">
         <f aca="false">G43+G44</f>
@@ -40985,7 +40985,7 @@
       </c>
       <c r="I45" s="71" t="n">
         <f aca="false">I43+I44</f>
-        <v>22627.5833333333</v>
+        <v>23127.5833333333</v>
       </c>
       <c r="J45" s="71" t="n">
         <f aca="false">J43+J44</f>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="L45" s="71" t="n">
         <f aca="false">L43+L44</f>
-        <v>19555.0833333333</v>
+        <v>19855.0833333333</v>
       </c>
       <c r="M45" s="71" t="n">
         <f aca="false">M43+M44</f>
@@ -41005,7 +41005,7 @@
       </c>
       <c r="N45" s="71" t="n">
         <f aca="false">N43+N44</f>
-        <v>22406.8333333333</v>
+        <v>27406.8333333333</v>
       </c>
       <c r="O45" s="68"/>
     </row>
@@ -41833,7 +41833,7 @@
       <c r="D39" s="88"/>
       <c r="E39" s="86" t="n">
         <f aca="false">TrialBalance!EJ83+TrialBalance!EJ88+TrialBalance!EJ89</f>
-        <v>0</v>
+        <v>-6600</v>
       </c>
       <c r="H39" s="89"/>
       <c r="I39" s="89"/>
@@ -41940,7 +41940,7 @@
       <c r="E44" s="103"/>
       <c r="F44" s="104" t="n">
         <f aca="false">SUM(E21:E43)</f>
-        <v>53948.25</v>
+        <v>47348.25</v>
       </c>
       <c r="H44" s="89"/>
       <c r="I44" s="89"/>
@@ -41976,7 +41976,7 @@
       <c r="E46" s="103"/>
       <c r="F46" s="104" t="n">
         <f aca="false">F18-F44</f>
-        <v>269591.083333333</v>
+        <v>276191.083333333</v>
       </c>
       <c r="H46" s="89"/>
       <c r="I46" s="89"/>
@@ -42031,7 +42031,7 @@
       <c r="E49" s="103"/>
       <c r="F49" s="104" t="n">
         <f aca="false">F46+F48</f>
-        <v>269591.083333333</v>
+        <v>276191.083333333</v>
       </c>
       <c r="H49" s="89"/>
       <c r="I49" s="89"/>
@@ -42052,7 +42052,7 @@
       <c r="D50" s="101"/>
       <c r="F50" s="86" t="n">
         <f aca="false">TrialBalance!EJ47</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="H50" s="89"/>
       <c r="I50" s="89"/>
@@ -42075,7 +42075,7 @@
       <c r="E51" s="103"/>
       <c r="F51" s="104" t="n">
         <f aca="false">F49-F50</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="H51" s="89"/>
       <c r="I51" s="89"/>
@@ -42136,7 +42136,7 @@
       </c>
       <c r="F54" s="104" t="n">
         <f aca="false">F51-F52</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="H54" s="89"/>
       <c r="I54" s="89"/>
@@ -42313,7 +42313,7 @@
       </c>
       <c r="E11" s="115" t="n">
         <f aca="false">TrialBalance!EJ20</f>
-        <v>424900</v>
+        <v>226300</v>
       </c>
       <c r="F11" s="115"/>
     </row>
@@ -42328,7 +42328,7 @@
       </c>
       <c r="E12" s="119" t="n">
         <f aca="false">IF(SUM(TrialBalance!EJ22:EJ24)&gt;0,SUM(TrialBalance!EJ22:EJ24)+TrialBalance!EJ25+TrialBalance!EJ26,TrialBalance!EJ25)</f>
-        <v>0</v>
+        <v>318135</v>
       </c>
       <c r="F12" s="115"/>
     </row>
@@ -42344,7 +42344,7 @@
       <c r="D13" s="117"/>
       <c r="E13" s="116" t="n">
         <f aca="false">SUM(E10:E12)</f>
-        <v>424900</v>
+        <v>544435</v>
       </c>
       <c r="F13" s="118"/>
     </row>
@@ -42390,7 +42390,7 @@
       </c>
       <c r="E17" s="115" t="n">
         <f aca="false">-TrialBalance!EJ35</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="F17" s="115"/>
     </row>
@@ -42405,7 +42405,7 @@
       </c>
       <c r="E18" s="115" t="n">
         <f aca="false">-SUM(TrialBalance!EJ32:EJ34)</f>
-        <v>70816.6666666667</v>
+        <v>75091.6666666667</v>
       </c>
       <c r="F18" s="115"/>
     </row>
@@ -42438,7 +42438,7 @@
       <c r="D20" s="117"/>
       <c r="E20" s="116" t="n">
         <f aca="false">SUM(E16:E19)</f>
-        <v>233601.2225</v>
+        <v>239130.2225</v>
       </c>
       <c r="F20" s="118"/>
       <c r="G20" s="120"/>
@@ -42465,7 +42465,7 @@
       <c r="E22" s="118"/>
       <c r="F22" s="116" t="n">
         <f aca="false">E13-E20</f>
-        <v>191298.7775</v>
+        <v>305304.7775</v>
       </c>
       <c r="G22" s="120"/>
     </row>
@@ -42518,7 +42518,7 @@
       <c r="E26" s="118"/>
       <c r="F26" s="116" t="n">
         <f aca="false">SUM(F6:F25)</f>
-        <v>217798.7775</v>
+        <v>331804.7775</v>
       </c>
       <c r="G26" s="120"/>
     </row>
@@ -42551,7 +42551,7 @@
       <c r="D29" s="88"/>
       <c r="E29" s="115" t="n">
         <f aca="false">-TrialBalance!EJ39</f>
-        <v>-0</v>
+        <v>1886145</v>
       </c>
       <c r="F29" s="115"/>
       <c r="G29" s="87"/>
@@ -42584,7 +42584,7 @@
       <c r="E31" s="115"/>
       <c r="F31" s="116" t="n">
         <f aca="false">SUM(E29:E30)</f>
-        <v>0</v>
+        <v>1886145</v>
       </c>
     </row>
     <row r="32" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42614,7 +42614,7 @@
       </c>
       <c r="F33" s="116" t="n">
         <f aca="false">F26-F31</f>
-        <v>217798.7775</v>
+        <v>-1554340.2225</v>
       </c>
       <c r="G33" s="120"/>
     </row>
@@ -42664,7 +42664,7 @@
       <c r="E37" s="115"/>
       <c r="F37" s="115" t="n">
         <f aca="false">-TrialBalance!EJ43</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="G37" s="87"/>
       <c r="O37" s="87"/>
@@ -42704,7 +42704,7 @@
       </c>
       <c r="F39" s="116" t="n">
         <f aca="false">SUM(F36:F38)</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="G39" s="120"/>
     </row>
@@ -42863,7 +42863,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43466,7 +43466,7 @@
       <c r="C41" s="137"/>
       <c r="D41" s="136" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="G41" s="89"/>
     </row>
@@ -43696,7 +43696,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44238,7 +44238,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="H119" s="159"/>
     </row>
@@ -44437,7 +44437,7 @@
       <c r="J5" s="178"/>
       <c r="K5" s="191" t="n">
         <f aca="false">'PubP&amp;L'!F46</f>
-        <v>269591.083333333</v>
+        <v>276191.083333333</v>
       </c>
       <c r="L5" s="185"/>
     </row>
@@ -44555,7 +44555,7 @@
       <c r="J12" s="178"/>
       <c r="K12" s="191" t="n">
         <f aca="false">K5+K10</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="L12" s="185"/>
     </row>
@@ -44765,7 +44765,7 @@
       <c r="J22" s="178"/>
       <c r="K22" s="209" t="n">
         <f aca="false">K12-K20</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="L22" s="185"/>
     </row>
@@ -44867,7 +44867,7 @@
       <c r="J28" s="178"/>
       <c r="K28" s="209" t="n">
         <f aca="false">K22+K24-K26</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="L28" s="185"/>
     </row>
@@ -44965,7 +44965,7 @@
       </c>
       <c r="F33" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A33/A35,0)</f>
-        <v>136109.090857273</v>
+        <v>139404.576493388</v>
       </c>
       <c r="G33" s="224" t="n">
         <f aca="false">Admin!P6</f>
@@ -44974,7 +44974,7 @@
       <c r="H33" s="224"/>
       <c r="I33" s="225" t="n">
         <f aca="false">F33*G33/100</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="J33" s="226"/>
       <c r="K33" s="178"/>
@@ -45002,7 +45002,7 @@
       </c>
       <c r="F34" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A34/A35,0)</f>
-        <v>136481.99247606</v>
+        <v>139786.506839945</v>
       </c>
       <c r="G34" s="224" t="n">
         <f aca="false">Admin!P7</f>
@@ -45011,7 +45011,7 @@
       <c r="H34" s="224"/>
       <c r="I34" s="225" t="n">
         <f aca="false">F34*G34/100</f>
-        <v>25931.5785704514</v>
+        <v>26559.4362995896</v>
       </c>
       <c r="J34" s="226"/>
       <c r="K34" s="178"/>
@@ -45035,7 +45035,7 @@
       <c r="J35" s="227"/>
       <c r="K35" s="228" t="n">
         <f aca="false">SUM(I33:I34)</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="L35" s="185"/>
     </row>
@@ -45101,7 +45101,7 @@
       <c r="J39" s="178"/>
       <c r="K39" s="232" t="n">
         <f aca="false">K35-K37</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="L39" s="185"/>
     </row>
@@ -49954,7 +49954,7 @@
       </c>
       <c r="Z70" s="302" t="n">
         <f aca="false">IF(CorporationTax!K22&gt;0,CorporationTax!K22," ")</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="AA70" s="302"/>
       <c r="AB70" s="302"/>
@@ -50172,7 +50172,7 @@
       </c>
       <c r="AJ74" s="302" t="n">
         <f aca="false">SUM(Z69:AF70)-SUM(Z72:AF73)</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="AK74" s="302"/>
       <c r="AL74" s="302"/>
@@ -51070,7 +51070,7 @@
       </c>
       <c r="AJ92" s="302" t="n">
         <f aca="false">IF(AJ74&gt;0,AJ74+SUM(AJ76:AJ80)+AJ88,0)</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="AK92" s="302"/>
       <c r="AL92" s="302"/>
@@ -51955,7 +51955,7 @@
       </c>
       <c r="AJ110" s="302" t="n">
         <f aca="false">AJ92-Z96-Z98-Z104-Z106</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="AK110" s="302"/>
       <c r="AL110" s="302"/>
@@ -52733,7 +52733,7 @@
       </c>
       <c r="N126" s="328" t="n">
         <f aca="false">CorporationTax!F33</f>
-        <v>136109.090857273</v>
+        <v>139404.576493388</v>
       </c>
       <c r="O126" s="328"/>
       <c r="P126" s="328"/>
@@ -52767,7 +52767,7 @@
       </c>
       <c r="AJ126" s="330" t="n">
         <f aca="false">CorporationTax!I33</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="AK126" s="330"/>
       <c r="AL126" s="330"/>
@@ -53026,7 +53026,7 @@
       </c>
       <c r="AJ131" s="330" t="n">
         <f aca="false">AJ126+AJ128</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="AK131" s="330"/>
       <c r="AL131" s="330"/>
@@ -53742,7 +53742,7 @@
       </c>
       <c r="AJ145" s="330" t="n">
         <f aca="false">AJ131</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="AK145" s="330"/>
       <c r="AL145" s="330"/>
@@ -54444,7 +54444,7 @@
       </c>
       <c r="AJ159" s="330" t="n">
         <f aca="false">IF(AJ145&gt;0,AJ145+AJ149-AJ154,0)</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="AK159" s="330"/>
       <c r="AL159" s="330"/>
@@ -54793,7 +54793,7 @@
       </c>
       <c r="AJ166" s="330" t="n">
         <f aca="false">IF(AJ159&gt;0,AJ159-AJ163,0)</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="AK166" s="330"/>
       <c r="AL166" s="330"/>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -42863,7 +42863,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43696,7 +43696,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44238,7 +44238,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -5335,7 +5335,7 @@
             <v>0</v>
           </cell>
           <cell r="F41">
-            <v>0</v>
+            <v>270</v>
           </cell>
         </row>
         <row r="41">
@@ -5366,7 +5366,7 @@
             <v>0</v>
           </cell>
           <cell r="F55">
-            <v>0</v>
+            <v>9828</v>
           </cell>
         </row>
         <row r="55">
@@ -7118,7 +7118,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>29600</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7130,7 +7130,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>24400</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7148,7 +7148,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>137837</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7211,7 +7211,7 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19500</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7223,7 +7223,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14200</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7241,7 +7241,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>137586</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7304,7 +7304,7 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19900</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7316,7 +7316,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14900</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7334,7 +7334,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>137684</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7397,7 +7397,7 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19100</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7409,7 +7409,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14000</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7427,7 +7427,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>229588</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7490,7 +7490,7 @@
       <sheetData sheetId="4">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>22200</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7502,7 +7502,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14600</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7514,13 +7514,13 @@
             <v>0</v>
           </cell>
           <cell r="N1">
-            <v>0</v>
+            <v>2500</v>
           </cell>
           <cell r="O1">
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>91907</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7583,7 +7583,7 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>18000</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7595,7 +7595,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>13400</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7613,7 +7613,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>137960</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7676,7 +7676,7 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>72400</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7688,7 +7688,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>30400</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7706,7 +7706,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>230025</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7769,7 +7769,7 @@
       <sheetData sheetId="7">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19400</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7781,7 +7781,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14500</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7799,7 +7799,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>138138</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7862,7 +7862,7 @@
       <sheetData sheetId="8">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19100</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7874,7 +7874,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>13900</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7892,7 +7892,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>184309</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -7955,7 +7955,7 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>27000</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7967,7 +7967,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>15200</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7979,13 +7979,13 @@
             <v>0</v>
           </cell>
           <cell r="N1">
-            <v>0</v>
+            <v>1500</v>
           </cell>
           <cell r="O1">
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>138305</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -8048,7 +8048,7 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>19700</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -8060,7 +8060,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14300</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -8078,7 +8078,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>92271</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -8141,7 +8141,7 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>24600</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -8153,7 +8153,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>0</v>
+            <v>14800</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -8171,7 +8171,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>184677</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -8722,7 +8722,7 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>125</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -8746,7 +8746,7 @@
             <v>0</v>
           </cell>
           <cell r="N1">
-            <v>0</v>
+            <v>125</v>
           </cell>
           <cell r="O1">
             <v>0</v>
@@ -9280,7 +9280,7 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>5150</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -9304,7 +9304,7 @@
             <v>0</v>
           </cell>
           <cell r="N1">
-            <v>0</v>
+            <v>150</v>
           </cell>
           <cell r="O1">
             <v>0</v>
@@ -9313,7 +9313,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="1">
@@ -9396,7 +9396,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>500</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -9429,7 +9429,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="1">
@@ -9519,7 +9519,7 @@
             <v>0</v>
           </cell>
           <cell r="P1">
-            <v>0</v>
+            <v>45858</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
@@ -9582,7 +9582,7 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>180</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -9675,7 +9675,7 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>300</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -9708,7 +9708,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>300</v>
           </cell>
         </row>
         <row r="1">
@@ -9954,7 +9954,7 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>620</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -9987,7 +9987,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>500</v>
           </cell>
         </row>
         <row r="1">
@@ -10233,7 +10233,7 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>300</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -10266,7 +10266,7 @@
             <v>0</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>300</v>
           </cell>
         </row>
         <row r="1">
@@ -10326,7 +10326,7 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>240</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -10535,7 +10535,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>15</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -10697,7 +10697,7 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>125</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -10940,7 +10940,7 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>18</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -11183,7 +11183,7 @@
       <sheetData sheetId="8">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -11426,7 +11426,7 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="F1">
-            <v>0</v>
+            <v>12</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -21386,7 +21386,7 @@
       <c r="G20" s="36"/>
       <c r="H20" s="36" t="n">
         <f aca="false">-[4]Jun!$J$1</f>
-        <v>-0</v>
+        <v>-24400</v>
       </c>
       <c r="I20" s="36" t="n">
         <f aca="false">-[5]Jun!$J$1</f>
@@ -21404,7 +21404,7 @@
       <c r="N20" s="57"/>
       <c r="O20" s="36" t="n">
         <f aca="false">SUM(D20:N20)</f>
-        <v>33400</v>
+        <v>9000</v>
       </c>
       <c r="P20" s="57"/>
       <c r="Q20" s="36" t="n">
@@ -21414,7 +21414,7 @@
       <c r="R20" s="36"/>
       <c r="S20" s="36" t="n">
         <f aca="false">-[4]Jul!$J$1</f>
-        <v>-0</v>
+        <v>-14200</v>
       </c>
       <c r="T20" s="36" t="n">
         <f aca="false">-[5]Jul!$J$1</f>
@@ -21435,7 +21435,7 @@
       <c r="Y20" s="54"/>
       <c r="Z20" s="36" t="n">
         <f aca="false">SUM(O20:Y20)</f>
-        <v>66320</v>
+        <v>27720</v>
       </c>
       <c r="AA20" s="57"/>
       <c r="AB20" s="36" t="n">
@@ -21445,7 +21445,7 @@
       <c r="AC20" s="36"/>
       <c r="AD20" s="36" t="n">
         <f aca="false">-[4]Aug!$J$1</f>
-        <v>-0</v>
+        <v>-14900</v>
       </c>
       <c r="AE20" s="36" t="n">
         <f aca="false">-[5]Aug!$J$1</f>
@@ -21464,7 +21464,7 @@
       <c r="AJ20" s="54"/>
       <c r="AK20" s="36" t="n">
         <f aca="false">SUM(Z20:AJ20)</f>
-        <v>101520</v>
+        <v>48020</v>
       </c>
       <c r="AL20" s="57"/>
       <c r="AM20" s="36" t="n">
@@ -21474,7 +21474,7 @@
       <c r="AN20" s="36"/>
       <c r="AO20" s="36" t="n">
         <f aca="false">-[4]Sep!$J$1</f>
-        <v>-0</v>
+        <v>-14000</v>
       </c>
       <c r="AP20" s="36" t="n">
         <f aca="false">-[5]Sep!$J$1</f>
@@ -21493,7 +21493,7 @@
       <c r="AU20" s="54"/>
       <c r="AV20" s="36" t="n">
         <f aca="false">SUM(AK20:AU20)</f>
-        <v>135280</v>
+        <v>67780</v>
       </c>
       <c r="AW20" s="57"/>
       <c r="AX20" s="36" t="n">
@@ -21503,7 +21503,7 @@
       <c r="AY20" s="36"/>
       <c r="AZ20" s="36" t="n">
         <f aca="false">-[4]Oct!$J$1</f>
-        <v>-0</v>
+        <v>-14600</v>
       </c>
       <c r="BA20" s="36" t="n">
         <f aca="false">-[5]Oct!$J$1</f>
@@ -21522,7 +21522,7 @@
       <c r="BF20" s="54"/>
       <c r="BG20" s="36" t="n">
         <f aca="false">SUM(AV20:BF20)</f>
-        <v>171300</v>
+        <v>89200</v>
       </c>
       <c r="BH20" s="57"/>
       <c r="BI20" s="36" t="n">
@@ -21532,7 +21532,7 @@
       <c r="BJ20" s="36"/>
       <c r="BK20" s="36" t="n">
         <f aca="false">-[4]Nov!$J$1</f>
-        <v>-0</v>
+        <v>-13400</v>
       </c>
       <c r="BL20" s="36" t="n">
         <f aca="false">-[5]Nov!$J$1</f>
@@ -21551,7 +21551,7 @@
       <c r="BQ20" s="54"/>
       <c r="BR20" s="36" t="n">
         <f aca="false">SUM(BG20:BQ20)</f>
-        <v>205060</v>
+        <v>109560</v>
       </c>
       <c r="BS20" s="57"/>
       <c r="BT20" s="36" t="n">
@@ -21561,7 +21561,7 @@
       <c r="BU20" s="36"/>
       <c r="BV20" s="36" t="n">
         <f aca="false">-[4]Dec!$J$1</f>
-        <v>-0</v>
+        <v>-30400</v>
       </c>
       <c r="BW20" s="36" t="n">
         <f aca="false">-[5]Dec!$J$1</f>
@@ -21580,7 +21580,7 @@
       <c r="CB20" s="54"/>
       <c r="CC20" s="36" t="n">
         <f aca="false">SUM(BR20:CB20)</f>
-        <v>255620</v>
+        <v>129720</v>
       </c>
       <c r="CD20" s="57"/>
       <c r="CE20" s="36" t="n">
@@ -21590,7 +21590,7 @@
       <c r="CF20" s="36"/>
       <c r="CG20" s="36" t="n">
         <f aca="false">-[4]Jan!$J$1</f>
-        <v>-0</v>
+        <v>-14500</v>
       </c>
       <c r="CH20" s="36" t="n">
         <f aca="false">-[5]Jan!$J$1</f>
@@ -21609,7 +21609,7 @@
       <c r="CM20" s="54"/>
       <c r="CN20" s="36" t="n">
         <f aca="false">SUM(CC20:CM20)</f>
-        <v>290940</v>
+        <v>150540</v>
       </c>
       <c r="CO20" s="57"/>
       <c r="CP20" s="36" t="n">
@@ -21619,7 +21619,7 @@
       <c r="CQ20" s="36"/>
       <c r="CR20" s="36" t="n">
         <f aca="false">-[4]Feb!$J$1</f>
-        <v>-0</v>
+        <v>-13900</v>
       </c>
       <c r="CS20" s="36" t="n">
         <f aca="false">-[5]Feb!$J$1</f>
@@ -21638,7 +21638,7 @@
       <c r="CX20" s="54"/>
       <c r="CY20" s="36" t="n">
         <f aca="false">SUM(CN20:CX20)</f>
-        <v>323740</v>
+        <v>169440</v>
       </c>
       <c r="CZ20" s="57"/>
       <c r="DA20" s="36" t="n">
@@ -21648,7 +21648,7 @@
       <c r="DB20" s="36"/>
       <c r="DC20" s="36" t="n">
         <f aca="false">-[4]Mar!$J$1</f>
-        <v>-0</v>
+        <v>-15200</v>
       </c>
       <c r="DD20" s="36" t="n">
         <f aca="false">-[5]Mar!$J$1</f>
@@ -21667,7 +21667,7 @@
       <c r="DI20" s="54"/>
       <c r="DJ20" s="36" t="n">
         <f aca="false">SUM(CY20:DI20)</f>
-        <v>359180</v>
+        <v>189680</v>
       </c>
       <c r="DK20" s="57"/>
       <c r="DL20" s="36" t="n">
@@ -21677,7 +21677,7 @@
       <c r="DM20" s="36"/>
       <c r="DN20" s="36" t="n">
         <f aca="false">-[4]Apr!$J$1</f>
-        <v>-0</v>
+        <v>-14300</v>
       </c>
       <c r="DO20" s="36" t="n">
         <f aca="false">-[5]Apr!$J$1</f>
@@ -21696,7 +21696,7 @@
       <c r="DT20" s="54"/>
       <c r="DU20" s="36" t="n">
         <f aca="false">SUM(DJ20:DT20)</f>
-        <v>393540</v>
+        <v>209740</v>
       </c>
       <c r="DV20" s="57"/>
       <c r="DW20" s="36" t="n">
@@ -21706,7 +21706,7 @@
       <c r="DX20" s="36"/>
       <c r="DY20" s="36" t="n">
         <f aca="false">-[4]May!$J$1</f>
-        <v>-0</v>
+        <v>-14800</v>
       </c>
       <c r="DZ20" s="36" t="n">
         <f aca="false">-[5]May!$J$1</f>
@@ -21725,13 +21725,13 @@
       <c r="EE20" s="54"/>
       <c r="EF20" s="36" t="n">
         <f aca="false">SUM(DU20:EE20)</f>
-        <v>424900</v>
+        <v>226300</v>
       </c>
       <c r="EG20" s="54"/>
       <c r="EI20" s="54"/>
       <c r="EJ20" s="36" t="n">
         <f aca="false">SUM(EF20:EH20)</f>
-        <v>424900</v>
+        <v>226300</v>
       </c>
       <c r="EK20" s="54"/>
     </row>
@@ -21888,7 +21888,7 @@
       <c r="G22" s="36"/>
       <c r="H22" s="36" t="n">
         <f aca="false">[4]Jun!$F$1-[4]Jun!$X$1</f>
-        <v>0</v>
+        <v>29600</v>
       </c>
       <c r="I22" s="36"/>
       <c r="J22" s="36"/>
@@ -21897,14 +21897,14 @@
       <c r="N22" s="57"/>
       <c r="O22" s="36" t="n">
         <f aca="false">SUM(D22:N22)</f>
-        <v>0</v>
+        <v>29600</v>
       </c>
       <c r="P22" s="57"/>
       <c r="Q22" s="36"/>
       <c r="R22" s="36"/>
       <c r="S22" s="36" t="n">
         <f aca="false">[4]Jul!$F$1-[4]Jul!$X$1</f>
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="T22" s="36"/>
       <c r="U22" s="36"/>
@@ -21914,14 +21914,14 @@
       <c r="Y22" s="54"/>
       <c r="Z22" s="36" t="n">
         <f aca="false">SUM(O22:Y22)</f>
-        <v>0</v>
+        <v>49100</v>
       </c>
       <c r="AA22" s="57"/>
       <c r="AB22" s="36"/>
       <c r="AC22" s="36"/>
       <c r="AD22" s="36" t="n">
         <f aca="false">[4]Aug!$F$1-[4]Aug!$X$1</f>
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="AE22" s="36"/>
       <c r="AF22" s="36"/>
@@ -21931,14 +21931,14 @@
       <c r="AJ22" s="54"/>
       <c r="AK22" s="36" t="n">
         <f aca="false">SUM(Z22:AJ22)</f>
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="AL22" s="57"/>
       <c r="AM22" s="36"/>
       <c r="AN22" s="36"/>
       <c r="AO22" s="36" t="n">
         <f aca="false">[4]Sep!$F$1-[4]Sep!$X$1</f>
-        <v>0</v>
+        <v>19100</v>
       </c>
       <c r="AP22" s="36"/>
       <c r="AQ22" s="36"/>
@@ -21948,14 +21948,14 @@
       <c r="AU22" s="54"/>
       <c r="AV22" s="36" t="n">
         <f aca="false">SUM(AK22:AU22)</f>
-        <v>0</v>
+        <v>88100</v>
       </c>
       <c r="AW22" s="57"/>
       <c r="AX22" s="36"/>
       <c r="AY22" s="36"/>
       <c r="AZ22" s="36" t="n">
         <f aca="false">[4]Oct!$F$1-[4]Oct!$X$1</f>
-        <v>0</v>
+        <v>22200</v>
       </c>
       <c r="BA22" s="36"/>
       <c r="BB22" s="36"/>
@@ -21965,14 +21965,14 @@
       <c r="BF22" s="54"/>
       <c r="BG22" s="36" t="n">
         <f aca="false">SUM(AV22:BF22)</f>
-        <v>0</v>
+        <v>110300</v>
       </c>
       <c r="BH22" s="57"/>
       <c r="BI22" s="36"/>
       <c r="BJ22" s="36"/>
       <c r="BK22" s="36" t="n">
         <f aca="false">[4]Nov!$F$1-[4]Nov!$X$1</f>
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="BL22" s="36"/>
       <c r="BM22" s="36"/>
@@ -21982,14 +21982,14 @@
       <c r="BQ22" s="54"/>
       <c r="BR22" s="36" t="n">
         <f aca="false">SUM(BG22:BQ22)</f>
-        <v>0</v>
+        <v>128300</v>
       </c>
       <c r="BS22" s="57"/>
       <c r="BT22" s="36"/>
       <c r="BU22" s="36"/>
       <c r="BV22" s="36" t="n">
         <f aca="false">[4]Dec!$F$1-[4]Dec!$X$1</f>
-        <v>0</v>
+        <v>72400</v>
       </c>
       <c r="BW22" s="36"/>
       <c r="BX22" s="36"/>
@@ -21999,14 +21999,14 @@
       <c r="CB22" s="54"/>
       <c r="CC22" s="36" t="n">
         <f aca="false">SUM(BR22:CB22)</f>
-        <v>0</v>
+        <v>200700</v>
       </c>
       <c r="CD22" s="57"/>
       <c r="CE22" s="36"/>
       <c r="CF22" s="36"/>
       <c r="CG22" s="36" t="n">
         <f aca="false">[4]Jan!$F$1-[4]Jan!$X$1</f>
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="CH22" s="36"/>
       <c r="CI22" s="36"/>
@@ -22016,14 +22016,14 @@
       <c r="CM22" s="54"/>
       <c r="CN22" s="36" t="n">
         <f aca="false">SUM(CC22:CM22)</f>
-        <v>0</v>
+        <v>220100</v>
       </c>
       <c r="CO22" s="57"/>
       <c r="CP22" s="36"/>
       <c r="CQ22" s="36"/>
       <c r="CR22" s="36" t="n">
         <f aca="false">[4]Feb!$F$1-[4]Feb!$X$1</f>
-        <v>0</v>
+        <v>19100</v>
       </c>
       <c r="CS22" s="36"/>
       <c r="CT22" s="36"/>
@@ -22033,14 +22033,14 @@
       <c r="CX22" s="54"/>
       <c r="CY22" s="36" t="n">
         <f aca="false">SUM(CN22:CX22)</f>
-        <v>0</v>
+        <v>239200</v>
       </c>
       <c r="CZ22" s="57"/>
       <c r="DA22" s="36"/>
       <c r="DB22" s="36"/>
       <c r="DC22" s="36" t="n">
         <f aca="false">[4]Mar!$F$1-[4]Mar!$X$1</f>
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="DD22" s="36"/>
       <c r="DE22" s="36"/>
@@ -22050,14 +22050,14 @@
       <c r="DI22" s="54"/>
       <c r="DJ22" s="36" t="n">
         <f aca="false">SUM(CY22:DI22)</f>
-        <v>0</v>
+        <v>266200</v>
       </c>
       <c r="DK22" s="57"/>
       <c r="DL22" s="36"/>
       <c r="DM22" s="36"/>
       <c r="DN22" s="36" t="n">
         <f aca="false">[4]Apr!$F$1-[4]Apr!$X$1</f>
-        <v>0</v>
+        <v>19700</v>
       </c>
       <c r="DO22" s="36"/>
       <c r="DP22" s="36"/>
@@ -22067,14 +22067,14 @@
       <c r="DT22" s="54"/>
       <c r="DU22" s="36" t="n">
         <f aca="false">SUM(DJ22:DT22)</f>
-        <v>0</v>
+        <v>285900</v>
       </c>
       <c r="DV22" s="57"/>
       <c r="DW22" s="36"/>
       <c r="DX22" s="36"/>
       <c r="DY22" s="36" t="n">
         <f aca="false">[4]May!$F$1-[4]May!$X$1</f>
-        <v>0</v>
+        <v>24600</v>
       </c>
       <c r="DZ22" s="36"/>
       <c r="EA22" s="36"/>
@@ -22084,13 +22084,13 @@
       <c r="EE22" s="54"/>
       <c r="EF22" s="36" t="n">
         <f aca="false">SUM(DU22:EE22)</f>
-        <v>0</v>
+        <v>310500</v>
       </c>
       <c r="EG22" s="54"/>
       <c r="EI22" s="54"/>
       <c r="EJ22" s="36" t="n">
         <f aca="false">SUM(EF22:EH22)</f>
-        <v>0</v>
+        <v>310500</v>
       </c>
       <c r="EK22" s="54"/>
     </row>
@@ -22196,7 +22196,7 @@
       <c r="BK23" s="36"/>
       <c r="BL23" s="36" t="n">
         <f aca="false">[5]Nov!$F$1-[5]Nov!$X$1</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="BM23" s="36"/>
       <c r="BN23" s="36"/>
@@ -22205,7 +22205,7 @@
       <c r="BQ23" s="54"/>
       <c r="BR23" s="36" t="n">
         <f aca="false">SUM(BG23:BQ23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="BS23" s="57"/>
       <c r="BT23" s="36"/>
@@ -22222,7 +22222,7 @@
       <c r="CB23" s="54"/>
       <c r="CC23" s="36" t="n">
         <f aca="false">SUM(BR23:CB23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="CD23" s="57"/>
       <c r="CE23" s="36"/>
@@ -22239,7 +22239,7 @@
       <c r="CM23" s="54"/>
       <c r="CN23" s="36" t="n">
         <f aca="false">SUM(CC23:CM23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="CO23" s="57"/>
       <c r="CP23" s="36"/>
@@ -22256,7 +22256,7 @@
       <c r="CX23" s="54"/>
       <c r="CY23" s="36" t="n">
         <f aca="false">SUM(CN23:CX23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="CZ23" s="57"/>
       <c r="DA23" s="36"/>
@@ -22273,7 +22273,7 @@
       <c r="DI23" s="54"/>
       <c r="DJ23" s="36" t="n">
         <f aca="false">SUM(CY23:DI23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="DK23" s="57"/>
       <c r="DL23" s="36"/>
@@ -22290,7 +22290,7 @@
       <c r="DT23" s="54"/>
       <c r="DU23" s="36" t="n">
         <f aca="false">SUM(DJ23:DT23)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="DV23" s="57"/>
       <c r="DW23" s="36"/>
@@ -22298,7 +22298,7 @@
       <c r="DY23" s="36"/>
       <c r="DZ23" s="36" t="n">
         <f aca="false">[5]May!$F$1-[5]May!$X$1</f>
-        <v>0</v>
+        <v>5150</v>
       </c>
       <c r="EA23" s="36"/>
       <c r="EB23" s="36"/>
@@ -22307,13 +22307,13 @@
       <c r="EE23" s="54"/>
       <c r="EF23" s="36" t="n">
         <f aca="false">SUM(DU23:EE23)</f>
-        <v>0</v>
+        <v>5275</v>
       </c>
       <c r="EG23" s="54"/>
       <c r="EI23" s="54"/>
       <c r="EJ23" s="36" t="n">
         <f aca="false">SUM(EF23:EH23)</f>
-        <v>0</v>
+        <v>5275</v>
       </c>
       <c r="EK23" s="54"/>
     </row>
@@ -22336,14 +22336,14 @@
       <c r="I24" s="36"/>
       <c r="J24" s="36" t="n">
         <f aca="false">[6]Jun!$F$1-[6]Jun!$X$1</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K24" s="36"/>
       <c r="L24" s="36"/>
       <c r="N24" s="57"/>
       <c r="O24" s="36" t="n">
         <f aca="false">SUM(D24:N24)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P24" s="57"/>
       <c r="Q24" s="36"/>
@@ -22360,7 +22360,7 @@
       <c r="Y24" s="54"/>
       <c r="Z24" s="36" t="n">
         <f aca="false">SUM(O24:Y24)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AA24" s="57"/>
       <c r="AB24" s="36"/>
@@ -22369,7 +22369,7 @@
       <c r="AE24" s="36"/>
       <c r="AF24" s="36" t="n">
         <f aca="false">[6]Aug!$F$1-[6]Aug!$X$1</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG24" s="36"/>
       <c r="AH24" s="36"/>
@@ -22377,7 +22377,7 @@
       <c r="AJ24" s="54"/>
       <c r="AK24" s="36" t="n">
         <f aca="false">SUM(Z24:AJ24)</f>
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="AL24" s="57"/>
       <c r="AM24" s="36"/>
@@ -22386,7 +22386,7 @@
       <c r="AP24" s="36"/>
       <c r="AQ24" s="36" t="n">
         <f aca="false">[6]Sep!$F$1-[6]Sep!$X$1</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AR24" s="36"/>
       <c r="AS24" s="36"/>
@@ -22394,7 +22394,7 @@
       <c r="AU24" s="54"/>
       <c r="AV24" s="36" t="n">
         <f aca="false">SUM(AK24:AU24)</f>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AW24" s="57"/>
       <c r="AX24" s="36"/>
@@ -22411,7 +22411,7 @@
       <c r="BF24" s="54"/>
       <c r="BG24" s="36" t="n">
         <f aca="false">SUM(AV24:BF24)</f>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="BH24" s="57"/>
       <c r="BI24" s="36"/>
@@ -22428,7 +22428,7 @@
       <c r="BQ24" s="54"/>
       <c r="BR24" s="36" t="n">
         <f aca="false">SUM(BG24:BQ24)</f>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="BS24" s="57"/>
       <c r="BT24" s="36"/>
@@ -22437,7 +22437,7 @@
       <c r="BW24" s="36"/>
       <c r="BX24" s="36" t="n">
         <f aca="false">[6]Dec!$F$1-[6]Dec!$X$1</f>
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="BY24" s="36"/>
       <c r="BZ24" s="36"/>
@@ -22445,7 +22445,7 @@
       <c r="CB24" s="54"/>
       <c r="CC24" s="36" t="n">
         <f aca="false">SUM(BR24:CB24)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CD24" s="57"/>
       <c r="CE24" s="36"/>
@@ -22462,7 +22462,7 @@
       <c r="CM24" s="54"/>
       <c r="CN24" s="36" t="n">
         <f aca="false">SUM(CC24:CM24)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CO24" s="57"/>
       <c r="CP24" s="36"/>
@@ -22479,7 +22479,7 @@
       <c r="CX24" s="54"/>
       <c r="CY24" s="36" t="n">
         <f aca="false">SUM(CN24:CX24)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CZ24" s="57"/>
       <c r="DA24" s="36"/>
@@ -22488,7 +22488,7 @@
       <c r="DD24" s="36"/>
       <c r="DE24" s="36" t="n">
         <f aca="false">[6]Mar!$F$1-[6]Mar!$X$1</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="DF24" s="36"/>
       <c r="DG24" s="36"/>
@@ -22496,7 +22496,7 @@
       <c r="DI24" s="54"/>
       <c r="DJ24" s="36" t="n">
         <f aca="false">SUM(CY24:DI24)</f>
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="DK24" s="57"/>
       <c r="DL24" s="36"/>
@@ -22505,7 +22505,7 @@
       <c r="DO24" s="36"/>
       <c r="DP24" s="36" t="n">
         <f aca="false">[6]Apr!$F$1-[6]Apr!$X$1</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="DQ24" s="36"/>
       <c r="DR24" s="36"/>
@@ -22513,7 +22513,7 @@
       <c r="DT24" s="54"/>
       <c r="DU24" s="36" t="n">
         <f aca="false">SUM(DJ24:DT24)</f>
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="DV24" s="57"/>
       <c r="DW24" s="36"/>
@@ -22530,13 +22530,13 @@
       <c r="EE24" s="54"/>
       <c r="EF24" s="36" t="n">
         <f aca="false">SUM(DU24:EE24)</f>
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="EG24" s="54"/>
       <c r="EI24" s="54"/>
       <c r="EJ24" s="36" t="n">
         <f aca="false">SUM(EF24:EH24)</f>
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="EK24" s="54"/>
     </row>
@@ -22560,13 +22560,13 @@
       <c r="J25" s="36"/>
       <c r="K25" s="36" t="n">
         <f aca="false">[7]Jun!$F$1-[7]Jun!$U$1</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L25" s="36"/>
       <c r="N25" s="57"/>
       <c r="O25" s="36" t="n">
         <f aca="false">SUM(D25:N25)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P25" s="57"/>
       <c r="Q25" s="36"/>
@@ -22583,7 +22583,7 @@
       <c r="Y25" s="54"/>
       <c r="Z25" s="36" t="n">
         <f aca="false">SUM(O25:Y25)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA25" s="57"/>
       <c r="AB25" s="36"/>
@@ -22593,14 +22593,14 @@
       <c r="AF25" s="36"/>
       <c r="AG25" s="36" t="n">
         <f aca="false">[7]Aug!$F$1-[7]Aug!$U$1</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AH25" s="36"/>
       <c r="AI25" s="36"/>
       <c r="AJ25" s="54"/>
       <c r="AK25" s="36" t="n">
         <f aca="false">SUM(Z25:AJ25)</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AL25" s="57"/>
       <c r="AM25" s="36"/>
@@ -22617,7 +22617,7 @@
       <c r="AU25" s="54"/>
       <c r="AV25" s="36" t="n">
         <f aca="false">SUM(AK25:AU25)</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AW25" s="57"/>
       <c r="AX25" s="36"/>
@@ -22634,7 +22634,7 @@
       <c r="BF25" s="54"/>
       <c r="BG25" s="36" t="n">
         <f aca="false">SUM(AV25:BF25)</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BH25" s="57"/>
       <c r="BI25" s="36"/>
@@ -22644,14 +22644,14 @@
       <c r="BM25" s="36"/>
       <c r="BN25" s="36" t="n">
         <f aca="false">[7]Nov!$F$1-[7]Nov!$U$1</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BO25" s="36"/>
       <c r="BP25" s="36"/>
       <c r="BQ25" s="54"/>
       <c r="BR25" s="36" t="n">
         <f aca="false">SUM(BG25:BQ25)</f>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="BS25" s="57"/>
       <c r="BT25" s="36"/>
@@ -22668,7 +22668,7 @@
       <c r="CB25" s="54"/>
       <c r="CC25" s="36" t="n">
         <f aca="false">SUM(BR25:CB25)</f>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="CD25" s="57"/>
       <c r="CE25" s="36"/>
@@ -22685,7 +22685,7 @@
       <c r="CM25" s="54"/>
       <c r="CN25" s="36" t="n">
         <f aca="false">SUM(CC25:CM25)</f>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="CO25" s="57"/>
       <c r="CP25" s="36"/>
@@ -22695,14 +22695,14 @@
       <c r="CT25" s="36"/>
       <c r="CU25" s="36" t="n">
         <f aca="false">[7]Feb!$F$1-[7]Feb!$U$1</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CV25" s="36"/>
       <c r="CW25" s="36"/>
       <c r="CX25" s="54"/>
       <c r="CY25" s="36" t="n">
         <f aca="false">SUM(CN25:CX25)</f>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="CZ25" s="57"/>
       <c r="DA25" s="36"/>
@@ -22719,7 +22719,7 @@
       <c r="DI25" s="54"/>
       <c r="DJ25" s="36" t="n">
         <f aca="false">SUM(CY25:DI25)</f>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="DK25" s="57"/>
       <c r="DL25" s="36"/>
@@ -22736,7 +22736,7 @@
       <c r="DT25" s="54"/>
       <c r="DU25" s="36" t="n">
         <f aca="false">SUM(DJ25:DT25)</f>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="DV25" s="57"/>
       <c r="DW25" s="36"/>
@@ -22746,14 +22746,14 @@
       <c r="EA25" s="36"/>
       <c r="EB25" s="36" t="n">
         <f aca="false">[7]May!$F$1-[7]May!$U$1</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="EC25" s="36"/>
       <c r="ED25" s="36"/>
       <c r="EE25" s="54"/>
       <c r="EF25" s="36" t="n">
         <f aca="false">SUM(DU25:EE25)</f>
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="EG25" s="54"/>
       <c r="EH25" s="36" t="n">
@@ -22763,7 +22763,7 @@
       <c r="EI25" s="54"/>
       <c r="EJ25" s="36" t="n">
         <f aca="false">SUM(EF25:EH25)</f>
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="EK25" s="54"/>
     </row>
@@ -25076,7 +25076,7 @@
       </c>
       <c r="AZ33" s="36" t="n">
         <f aca="false">-[4]Oct!$N$1+[4]Oct!$AI$1</f>
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="BA33" s="36" t="n">
         <f aca="false">-[5]Oct!$N$1+[5]Oct!$AI$1</f>
@@ -25095,7 +25095,7 @@
       <c r="BF33" s="54"/>
       <c r="BG33" s="36" t="n">
         <f aca="false">SUM(AV33:BF33)</f>
-        <v>-28550</v>
+        <v>-31050</v>
       </c>
       <c r="BH33" s="57"/>
       <c r="BI33" s="36" t="n">
@@ -25112,7 +25112,7 @@
       </c>
       <c r="BL33" s="36" t="n">
         <f aca="false">-[5]Nov!$N$1+[5]Nov!$AI$1</f>
-        <v>0</v>
+        <v>-125</v>
       </c>
       <c r="BM33" s="36" t="n">
         <f aca="false">-[6]Nov!$N$1+[6]Nov!$AI$1</f>
@@ -25127,7 +25127,7 @@
       <c r="BQ33" s="54"/>
       <c r="BR33" s="36" t="n">
         <f aca="false">SUM(BG33:BQ33)</f>
-        <v>-34176.6666666667</v>
+        <v>-36801.6666666667</v>
       </c>
       <c r="BS33" s="57"/>
       <c r="BT33" s="36" t="n">
@@ -25159,7 +25159,7 @@
       <c r="CB33" s="54"/>
       <c r="CC33" s="36" t="n">
         <f aca="false">SUM(BR33:CB33)</f>
-        <v>-42603.3333333334</v>
+        <v>-45228.3333333334</v>
       </c>
       <c r="CD33" s="57"/>
       <c r="CE33" s="36" t="n">
@@ -25191,7 +25191,7 @@
       <c r="CM33" s="54"/>
       <c r="CN33" s="36" t="n">
         <f aca="false">SUM(CC33:CM33)</f>
-        <v>-48490</v>
+        <v>-51115</v>
       </c>
       <c r="CO33" s="57"/>
       <c r="CP33" s="36" t="n">
@@ -25223,7 +25223,7 @@
       <c r="CX33" s="54"/>
       <c r="CY33" s="36" t="n">
         <f aca="false">SUM(CN33:CX33)</f>
-        <v>-53956.6666666667</v>
+        <v>-56581.6666666667</v>
       </c>
       <c r="CZ33" s="57"/>
       <c r="DA33" s="36" t="n">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="DC33" s="36" t="n">
         <f aca="false">-[4]Mar!$N$1+[4]Mar!$AI$1</f>
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="DD33" s="36" t="n">
         <f aca="false">-[5]Mar!$N$1+[5]Mar!$AI$1</f>
@@ -25255,7 +25255,7 @@
       <c r="DI33" s="54"/>
       <c r="DJ33" s="36" t="n">
         <f aca="false">SUM(CY33:DI33)</f>
-        <v>-59863.3333333334</v>
+        <v>-63988.3333333334</v>
       </c>
       <c r="DK33" s="57"/>
       <c r="DL33" s="36" t="n">
@@ -25287,7 +25287,7 @@
       <c r="DT33" s="54"/>
       <c r="DU33" s="36" t="n">
         <f aca="false">SUM(DJ33:DT33)</f>
-        <v>-65590</v>
+        <v>-69715</v>
       </c>
       <c r="DV33" s="57"/>
       <c r="DW33" s="36" t="n">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="DZ33" s="36" t="n">
         <f aca="false">-[5]May!$N$1+[5]May!$AI$1</f>
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="EA33" s="36" t="n">
         <f aca="false">-[6]May!$N$1+[6]May!$AI$1</f>
@@ -25319,13 +25319,13 @@
       <c r="EE33" s="54"/>
       <c r="EF33" s="36" t="n">
         <f aca="false">SUM(DU33:EE33)</f>
-        <v>-70816.6666666667</v>
+        <v>-75091.6666666667</v>
       </c>
       <c r="EG33" s="54"/>
       <c r="EI33" s="54"/>
       <c r="EJ33" s="36" t="n">
         <f aca="false">SUM(EF33:EH33)</f>
-        <v>-70816.6666666667</v>
+        <v>-75091.6666666667</v>
       </c>
       <c r="EK33" s="54"/>
     </row>
@@ -26015,12 +26015,12 @@
       <c r="EC35" s="36"/>
       <c r="ED35" s="36" t="n">
         <f aca="false">-CorporationTax!K35</f>
-        <v>-51792.3058333333</v>
+        <v>-53046.3058333333</v>
       </c>
       <c r="EE35" s="54"/>
       <c r="EF35" s="36" t="n">
         <f aca="false">SUM(DU35:EE35)</f>
-        <v>-51792.3058333333</v>
+        <v>-53046.3058333333</v>
       </c>
       <c r="EG35" s="54"/>
       <c r="EH35" s="36" t="n">
@@ -26030,7 +26030,7 @@
       <c r="EI35" s="54"/>
       <c r="EJ35" s="36" t="n">
         <f aca="false">SUM(EF35:EH35)</f>
-        <v>-51792.3058333333</v>
+        <v>-53046.3058333333</v>
       </c>
       <c r="EK35" s="54"/>
     </row>
@@ -26654,7 +26654,7 @@
       <c r="G39" s="36"/>
       <c r="H39" s="36" t="n">
         <f aca="false">-[4]Jun!$P$1+[4]Jun!$AM$1</f>
-        <v>0</v>
+        <v>-137837</v>
       </c>
       <c r="I39" s="36" t="n">
         <f aca="false">-[5]Jun!$P$1+[5]Jun!$AM$1</f>
@@ -26672,14 +26672,14 @@
       <c r="N39" s="57"/>
       <c r="O39" s="36" t="n">
         <f aca="false">SUM(D39:N39)</f>
-        <v>0</v>
+        <v>-137837</v>
       </c>
       <c r="P39" s="57"/>
       <c r="Q39" s="36"/>
       <c r="R39" s="36"/>
       <c r="S39" s="36" t="n">
         <f aca="false">-[4]Jul!$P$1+[4]Jul!$AM$1</f>
-        <v>0</v>
+        <v>-137586</v>
       </c>
       <c r="T39" s="36" t="n">
         <f aca="false">-[5]Jul!$P$1+[5]Jul!$AM$1</f>
@@ -26687,7 +26687,7 @@
       </c>
       <c r="U39" s="36" t="n">
         <f aca="false">-[6]Jul!$P$1+[6]Jul!$AM$1</f>
-        <v>0</v>
+        <v>-45858</v>
       </c>
       <c r="V39" s="36" t="n">
         <f aca="false">-[7]Jul!$N$1+[7]Jul!$AJ$1</f>
@@ -26698,14 +26698,14 @@
       <c r="Y39" s="54"/>
       <c r="Z39" s="36" t="n">
         <f aca="false">SUM(O39:Y39)</f>
-        <v>0</v>
+        <v>-321281</v>
       </c>
       <c r="AA39" s="57"/>
       <c r="AB39" s="36"/>
       <c r="AC39" s="36"/>
       <c r="AD39" s="36" t="n">
         <f aca="false">-[4]Aug!$P$1+[4]Aug!$AM$1</f>
-        <v>0</v>
+        <v>-137684</v>
       </c>
       <c r="AE39" s="36" t="n">
         <f aca="false">-[5]Aug!$P$1+[5]Aug!$AM$1</f>
@@ -26724,14 +26724,14 @@
       <c r="AJ39" s="54"/>
       <c r="AK39" s="36" t="n">
         <f aca="false">SUM(Z39:AJ39)</f>
-        <v>0</v>
+        <v>-458965</v>
       </c>
       <c r="AL39" s="57"/>
       <c r="AM39" s="36"/>
       <c r="AN39" s="36"/>
       <c r="AO39" s="36" t="n">
         <f aca="false">-[4]Sep!$P$1+[4]Sep!$AM$1</f>
-        <v>0</v>
+        <v>-229588</v>
       </c>
       <c r="AP39" s="36" t="n">
         <f aca="false">-[5]Sep!$P$1+[5]Sep!$AM$1</f>
@@ -26750,14 +26750,14 @@
       <c r="AU39" s="54"/>
       <c r="AV39" s="36" t="n">
         <f aca="false">SUM(AK39:AU39)</f>
-        <v>0</v>
+        <v>-688553</v>
       </c>
       <c r="AW39" s="57"/>
       <c r="AX39" s="36"/>
       <c r="AY39" s="36"/>
       <c r="AZ39" s="36" t="n">
         <f aca="false">-[4]Oct!$P$1+[4]Oct!$AM$1</f>
-        <v>0</v>
+        <v>-91907</v>
       </c>
       <c r="BA39" s="36" t="n">
         <f aca="false">-[5]Oct!$P$1+[5]Oct!$AM$1</f>
@@ -26776,14 +26776,14 @@
       <c r="BF39" s="54"/>
       <c r="BG39" s="36" t="n">
         <f aca="false">SUM(AV39:BF39)</f>
-        <v>0</v>
+        <v>-780460</v>
       </c>
       <c r="BH39" s="57"/>
       <c r="BI39" s="36"/>
       <c r="BJ39" s="36"/>
       <c r="BK39" s="36" t="n">
         <f aca="false">-[4]Nov!$P$1+[4]Nov!$AM$1</f>
-        <v>0</v>
+        <v>-137960</v>
       </c>
       <c r="BL39" s="36" t="n">
         <f aca="false">-[5]Nov!$P$1+[5]Nov!$AM$1</f>
@@ -26802,14 +26802,14 @@
       <c r="BQ39" s="54"/>
       <c r="BR39" s="36" t="n">
         <f aca="false">SUM(BG39:BQ39)</f>
-        <v>0</v>
+        <v>-918420</v>
       </c>
       <c r="BS39" s="57"/>
       <c r="BT39" s="36"/>
       <c r="BU39" s="36"/>
       <c r="BV39" s="36" t="n">
         <f aca="false">-[4]Dec!$P$1+[4]Dec!$AM$1</f>
-        <v>0</v>
+        <v>-230025</v>
       </c>
       <c r="BW39" s="36" t="n">
         <f aca="false">-[5]Dec!$P$1+[5]Dec!$AM$1</f>
@@ -26828,14 +26828,14 @@
       <c r="CB39" s="54"/>
       <c r="CC39" s="36" t="n">
         <f aca="false">SUM(BR39:CB39)</f>
-        <v>0</v>
+        <v>-1148445</v>
       </c>
       <c r="CD39" s="57"/>
       <c r="CE39" s="36"/>
       <c r="CF39" s="36"/>
       <c r="CG39" s="36" t="n">
         <f aca="false">-[4]Jan!$P$1+[4]Jan!$AM$1</f>
-        <v>0</v>
+        <v>-138138</v>
       </c>
       <c r="CH39" s="36" t="n">
         <f aca="false">-[5]Jan!$P$1+[5]Jan!$AM$1</f>
@@ -26854,14 +26854,14 @@
       <c r="CM39" s="54"/>
       <c r="CN39" s="36" t="n">
         <f aca="false">SUM(CC39:CM39)</f>
-        <v>0</v>
+        <v>-1286583</v>
       </c>
       <c r="CO39" s="57"/>
       <c r="CP39" s="36"/>
       <c r="CQ39" s="36"/>
       <c r="CR39" s="36" t="n">
         <f aca="false">-[4]Feb!$P$1+[4]Feb!$AM$1</f>
-        <v>0</v>
+        <v>-184309</v>
       </c>
       <c r="CS39" s="36" t="n">
         <f aca="false">-[5]Feb!$P$1+[5]Feb!$AM$1</f>
@@ -26880,14 +26880,14 @@
       <c r="CX39" s="54"/>
       <c r="CY39" s="36" t="n">
         <f aca="false">SUM(CN39:CX39)</f>
-        <v>0</v>
+        <v>-1470892</v>
       </c>
       <c r="CZ39" s="57"/>
       <c r="DA39" s="36"/>
       <c r="DB39" s="36"/>
       <c r="DC39" s="36" t="n">
         <f aca="false">-[4]Mar!$P$1+[4]Mar!$AM$1</f>
-        <v>0</v>
+        <v>-138305</v>
       </c>
       <c r="DD39" s="36" t="n">
         <f aca="false">-[5]Mar!$P$1+[5]Mar!$AM$1</f>
@@ -26906,14 +26906,14 @@
       <c r="DI39" s="54"/>
       <c r="DJ39" s="36" t="n">
         <f aca="false">SUM(CY39:DI39)</f>
-        <v>0</v>
+        <v>-1609197</v>
       </c>
       <c r="DK39" s="57"/>
       <c r="DL39" s="36"/>
       <c r="DM39" s="36"/>
       <c r="DN39" s="36" t="n">
         <f aca="false">-[4]Apr!$P$1+[4]Apr!$AM$1</f>
-        <v>0</v>
+        <v>-92271</v>
       </c>
       <c r="DO39" s="36" t="n">
         <f aca="false">-[5]Apr!$P$1+[5]Apr!$AM$1</f>
@@ -26932,14 +26932,14 @@
       <c r="DT39" s="54"/>
       <c r="DU39" s="36" t="n">
         <f aca="false">SUM(DJ39:DT39)</f>
-        <v>0</v>
+        <v>-1701468</v>
       </c>
       <c r="DV39" s="57"/>
       <c r="DW39" s="36"/>
       <c r="DX39" s="36"/>
       <c r="DY39" s="36" t="n">
         <f aca="false">-[4]May!$P$1+[4]May!$AM$1</f>
-        <v>0</v>
+        <v>-184677</v>
       </c>
       <c r="DZ39" s="36" t="n">
         <f aca="false">-[5]May!$P$1+[5]May!$AM$1</f>
@@ -26958,13 +26958,13 @@
       <c r="EE39" s="54"/>
       <c r="EF39" s="36" t="n">
         <f aca="false">SUM(DU39:EE39)</f>
-        <v>0</v>
+        <v>-1886145</v>
       </c>
       <c r="EG39" s="54"/>
       <c r="EI39" s="54"/>
       <c r="EJ39" s="36" t="n">
         <f aca="false">SUM(EF39:EH39)</f>
-        <v>0</v>
+        <v>-1886145</v>
       </c>
       <c r="EK39" s="54"/>
     </row>
@@ -27808,12 +27808,12 @@
       <c r="EG43" s="54"/>
       <c r="EH43" s="36" t="n">
         <f aca="false">-'PubP&amp;L'!F54</f>
-        <v>-217798.7775</v>
+        <v>-223144.7775</v>
       </c>
       <c r="EI43" s="54"/>
       <c r="EJ43" s="36" t="n">
         <f aca="false">SUM(EF43:EH43)</f>
-        <v>-217798.7775</v>
+        <v>-223144.7775</v>
       </c>
       <c r="EK43" s="54"/>
     </row>
@@ -28442,18 +28442,18 @@
       <c r="EC47" s="36"/>
       <c r="ED47" s="36" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="EE47" s="54"/>
       <c r="EF47" s="36" t="n">
         <f aca="false">SUM(DU47:EE47)</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="EG47" s="54"/>
       <c r="EI47" s="54"/>
       <c r="EJ47" s="36" t="n">
         <f aca="false">SUM(EF47:EH47)</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="EK47" s="54"/>
     </row>
@@ -28822,12 +28822,12 @@
       <c r="EG49" s="54"/>
       <c r="EH49" s="36" t="n">
         <f aca="false">'PubP&amp;L'!F54</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="EI49" s="54"/>
       <c r="EJ49" s="36" t="n">
         <f aca="false">SUM(EF49:EH49)</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="EK49" s="54"/>
     </row>
@@ -37188,14 +37188,14 @@
       </c>
       <c r="J88" s="36" t="n">
         <f aca="false">-[6]Jun!$Q$1</f>
-        <v>-0</v>
+        <v>-500</v>
       </c>
       <c r="K88" s="36"/>
       <c r="L88" s="36"/>
       <c r="N88" s="57"/>
       <c r="O88" s="36" t="n">
         <f aca="false">SUM(D88:N88)</f>
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="P88" s="57"/>
       <c r="Q88" s="36"/>
@@ -37218,7 +37218,7 @@
       <c r="Y88" s="54"/>
       <c r="Z88" s="36" t="n">
         <f aca="false">SUM(O88:Y88)</f>
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="AA88" s="57"/>
       <c r="AB88" s="36"/>
@@ -37241,7 +37241,7 @@
       <c r="AJ88" s="54"/>
       <c r="AK88" s="36" t="n">
         <f aca="false">SUM(Z88:AJ88)</f>
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="AL88" s="57"/>
       <c r="AM88" s="36"/>
@@ -37256,7 +37256,7 @@
       </c>
       <c r="AQ88" s="36" t="n">
         <f aca="false">-[6]Sep!$Q$1</f>
-        <v>-0</v>
+        <v>-300</v>
       </c>
       <c r="AR88" s="36"/>
       <c r="AS88" s="36"/>
@@ -37264,7 +37264,7 @@
       <c r="AU88" s="54"/>
       <c r="AV88" s="36" t="n">
         <f aca="false">SUM(AK88:AU88)</f>
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="AW88" s="57"/>
       <c r="AX88" s="36"/>
@@ -37287,7 +37287,7 @@
       <c r="BF88" s="54"/>
       <c r="BG88" s="36" t="n">
         <f aca="false">SUM(AV88:BF88)</f>
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="BH88" s="57"/>
       <c r="BI88" s="36"/>
@@ -37310,7 +37310,7 @@
       <c r="BQ88" s="54"/>
       <c r="BR88" s="36" t="n">
         <f aca="false">SUM(BG88:BQ88)</f>
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="BS88" s="57"/>
       <c r="BT88" s="36"/>
@@ -37325,7 +37325,7 @@
       </c>
       <c r="BX88" s="36" t="n">
         <f aca="false">-[6]Dec!$Q$1</f>
-        <v>-0</v>
+        <v>-500</v>
       </c>
       <c r="BY88" s="36"/>
       <c r="BZ88" s="36"/>
@@ -37333,7 +37333,7 @@
       <c r="CB88" s="54"/>
       <c r="CC88" s="36" t="n">
         <f aca="false">SUM(BR88:CB88)</f>
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="CD88" s="57"/>
       <c r="CE88" s="36"/>
@@ -37356,7 +37356,7 @@
       <c r="CM88" s="54"/>
       <c r="CN88" s="36" t="n">
         <f aca="false">SUM(CC88:CM88)</f>
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="CO88" s="57"/>
       <c r="CP88" s="36"/>
@@ -37379,7 +37379,7 @@
       <c r="CX88" s="54"/>
       <c r="CY88" s="36" t="n">
         <f aca="false">SUM(CN88:CX88)</f>
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="CZ88" s="57"/>
       <c r="DA88" s="36"/>
@@ -37394,7 +37394,7 @@
       </c>
       <c r="DE88" s="36" t="n">
         <f aca="false">-[6]Mar!$Q$1</f>
-        <v>-0</v>
+        <v>-300</v>
       </c>
       <c r="DF88" s="36"/>
       <c r="DG88" s="36"/>
@@ -37402,7 +37402,7 @@
       <c r="DI88" s="54"/>
       <c r="DJ88" s="36" t="n">
         <f aca="false">SUM(CY88:DI88)</f>
-        <v>0</v>
+        <v>-1600</v>
       </c>
       <c r="DK88" s="57"/>
       <c r="DL88" s="36"/>
@@ -37425,7 +37425,7 @@
       <c r="DT88" s="54"/>
       <c r="DU88" s="36" t="n">
         <f aca="false">SUM(DJ88:DT88)</f>
-        <v>0</v>
+        <v>-1600</v>
       </c>
       <c r="DV88" s="57"/>
       <c r="DW88" s="36"/>
@@ -37436,7 +37436,7 @@
       </c>
       <c r="DZ88" s="36" t="n">
         <f aca="false">-[5]May!$Q$1</f>
-        <v>-0</v>
+        <v>-5000</v>
       </c>
       <c r="EA88" s="36" t="n">
         <f aca="false">-[6]May!$Q$1</f>
@@ -37448,13 +37448,13 @@
       <c r="EE88" s="54"/>
       <c r="EF88" s="36" t="n">
         <f aca="false">SUM(DU88:EE88)</f>
-        <v>0</v>
+        <v>-6600</v>
       </c>
       <c r="EG88" s="54"/>
       <c r="EI88" s="54"/>
       <c r="EJ88" s="36" t="n">
         <f aca="false">SUM(EF88:EH88)</f>
-        <v>0</v>
+        <v>-6600</v>
       </c>
       <c r="EK88" s="54"/>
     </row>
@@ -37905,7 +37905,7 @@
       </c>
       <c r="H91" s="36" t="n">
         <f aca="false">SUM(H4:H90)</f>
-        <v>0</v>
+        <v>-132637</v>
       </c>
       <c r="I91" s="36" t="n">
         <f aca="false">SUM(I4:I90)</f>
@@ -37917,7 +37917,7 @@
       </c>
       <c r="K91" s="36" t="n">
         <f aca="false">SUM(K4:K90)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L91" s="36" t="n">
         <f aca="false">SUM(L4:L90)</f>
@@ -37930,7 +37930,7 @@
       <c r="N91" s="54"/>
       <c r="O91" s="36" t="n">
         <f aca="false">SUM(O4:O90)</f>
-        <v>3.09228198602796E-011</v>
+        <v>-132622</v>
       </c>
       <c r="P91" s="54"/>
       <c r="Q91" s="36" t="n">
@@ -37943,7 +37943,7 @@
       </c>
       <c r="S91" s="36" t="n">
         <f aca="false">SUM(S4:S90)</f>
-        <v>0</v>
+        <v>-132286</v>
       </c>
       <c r="T91" s="36" t="n">
         <f aca="false">SUM(T4:T90)</f>
@@ -37951,7 +37951,7 @@
       </c>
       <c r="U91" s="36" t="n">
         <f aca="false">SUM(U4:U90)</f>
-        <v>0</v>
+        <v>-45858</v>
       </c>
       <c r="V91" s="36" t="n">
         <f aca="false">SUM(V4:V90)</f>
@@ -37968,7 +37968,7 @@
       <c r="Y91" s="54"/>
       <c r="Z91" s="36" t="n">
         <f aca="false">SUM(Z4:Z90)</f>
-        <v>6.18456397205591E-011</v>
+        <v>-310766</v>
       </c>
       <c r="AA91" s="54"/>
       <c r="AB91" s="36" t="n">
@@ -37981,7 +37981,7 @@
       </c>
       <c r="AD91" s="36" t="n">
         <f aca="false">SUM(AD4:AD90)</f>
-        <v>0</v>
+        <v>-132684</v>
       </c>
       <c r="AE91" s="36" t="n">
         <f aca="false">SUM(AE4:AE90)</f>
@@ -37989,11 +37989,11 @@
       </c>
       <c r="AF91" s="36" t="n">
         <f aca="false">SUM(AF4:AF90)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG91" s="36" t="n">
         <f aca="false">SUM(AG4:AG90)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AH91" s="36" t="n">
         <f aca="false">SUM(AH4:AH90)</f>
@@ -38006,7 +38006,7 @@
       <c r="AJ91" s="54"/>
       <c r="AK91" s="36" t="n">
         <f aca="false">SUM(AK4:AK90)</f>
-        <v>9.45874489843845E-011</v>
+        <v>-443145</v>
       </c>
       <c r="AL91" s="54"/>
       <c r="AM91" s="36" t="n">
@@ -38019,7 +38019,7 @@
       </c>
       <c r="AO91" s="36" t="n">
         <f aca="false">SUM(AO4:AO90)</f>
-        <v>0</v>
+        <v>-224488</v>
       </c>
       <c r="AP91" s="36" t="n">
         <f aca="false">SUM(AP4:AP90)</f>
@@ -38044,7 +38044,7 @@
       <c r="AU91" s="54"/>
       <c r="AV91" s="36" t="n">
         <f aca="false">SUM(AV4:AV90)</f>
-        <v>1.23691279441118E-010</v>
+        <v>-667633</v>
       </c>
       <c r="AW91" s="54"/>
       <c r="AX91" s="36" t="n">
@@ -38057,7 +38057,7 @@
       </c>
       <c r="AZ91" s="36" t="n">
         <f aca="false">SUM(AZ4:AZ90)</f>
-        <v>0</v>
+        <v>-86807</v>
       </c>
       <c r="BA91" s="36" t="n">
         <f aca="false">SUM(BA4:BA90)</f>
@@ -38082,7 +38082,7 @@
       <c r="BF91" s="54"/>
       <c r="BG91" s="36" t="n">
         <f aca="false">SUM(BG4:BG90)</f>
-        <v>1.65982783073559E-010</v>
+        <v>-754440</v>
       </c>
       <c r="BH91" s="54"/>
       <c r="BI91" s="36" t="n">
@@ -38095,7 +38095,7 @@
       </c>
       <c r="BK91" s="36" t="n">
         <f aca="false">SUM(BK4:BK90)</f>
-        <v>0</v>
+        <v>-133360</v>
       </c>
       <c r="BL91" s="36" t="n">
         <f aca="false">SUM(BL4:BL90)</f>
@@ -38107,7 +38107,7 @@
       </c>
       <c r="BN91" s="36" t="n">
         <f aca="false">SUM(BN4:BN90)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BO91" s="36" t="n">
         <f aca="false">SUM(BO4:BO90)</f>
@@ -38120,7 +38120,7 @@
       <c r="BQ91" s="54"/>
       <c r="BR91" s="36" t="n">
         <f aca="false">SUM(BR4:BR90)</f>
-        <v>1.95086613530293E-010</v>
+        <v>-887782</v>
       </c>
       <c r="BS91" s="54"/>
       <c r="BT91" s="36" t="n">
@@ -38133,7 +38133,7 @@
       </c>
       <c r="BV91" s="36" t="n">
         <f aca="false">SUM(BV4:BV90)</f>
-        <v>0</v>
+        <v>-188025</v>
       </c>
       <c r="BW91" s="36" t="n">
         <f aca="false">SUM(BW4:BW90)</f>
@@ -38141,7 +38141,7 @@
       </c>
       <c r="BX91" s="36" t="n">
         <f aca="false">SUM(BX4:BX90)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BY91" s="36" t="n">
         <f aca="false">SUM(BY4:BY90)</f>
@@ -38158,7 +38158,7 @@
       <c r="CB91" s="54"/>
       <c r="CC91" s="36" t="n">
         <f aca="false">SUM(CC4:CC90)</f>
-        <v>2.38742359215394E-010</v>
+        <v>-1075687</v>
       </c>
       <c r="CD91" s="54"/>
       <c r="CE91" s="36" t="n">
@@ -38171,7 +38171,7 @@
       </c>
       <c r="CG91" s="36" t="n">
         <f aca="false">SUM(CG4:CG90)</f>
-        <v>0</v>
+        <v>-133238</v>
       </c>
       <c r="CH91" s="36" t="n">
         <f aca="false">SUM(CH4:CH90)</f>
@@ -38196,7 +38196,7 @@
       <c r="CM91" s="54"/>
       <c r="CN91" s="36" t="n">
         <f aca="false">SUM(CN4:CN90)</f>
-        <v>2.53294274443761E-010</v>
+        <v>-1208925</v>
       </c>
       <c r="CO91" s="54"/>
       <c r="CP91" s="36" t="n">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="CR91" s="36" t="n">
         <f aca="false">SUM(CR4:CR90)</f>
-        <v>0</v>
+        <v>-179109</v>
       </c>
       <c r="CS91" s="36" t="n">
         <f aca="false">SUM(CS4:CS90)</f>
@@ -38221,7 +38221,7 @@
       </c>
       <c r="CU91" s="36" t="n">
         <f aca="false">SUM(CU4:CU90)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CV91" s="36" t="n">
         <f aca="false">SUM(CV4:CV90)</f>
@@ -38234,7 +38234,7 @@
       <c r="CX91" s="54"/>
       <c r="CY91" s="36" t="n">
         <f aca="false">SUM(CY4:CY90)</f>
-        <v>2.67846189672127E-010</v>
+        <v>-1387984</v>
       </c>
       <c r="CZ91" s="54"/>
       <c r="DA91" s="36" t="n">
@@ -38247,7 +38247,7 @@
       </c>
       <c r="DC91" s="36" t="n">
         <f aca="false">SUM(DC4:DC90)</f>
-        <v>0</v>
+        <v>-128005</v>
       </c>
       <c r="DD91" s="36" t="n">
         <f aca="false">SUM(DD4:DD90)</f>
@@ -38272,7 +38272,7 @@
       <c r="DI91" s="54"/>
       <c r="DJ91" s="36" t="n">
         <f aca="false">SUM(DJ4:DJ90)</f>
-        <v>2.82398104900494E-010</v>
+        <v>-1515989</v>
       </c>
       <c r="DK91" s="54"/>
       <c r="DL91" s="36" t="n">
@@ -38285,7 +38285,7 @@
       </c>
       <c r="DN91" s="36" t="n">
         <f aca="false">SUM(DN4:DN90)</f>
-        <v>0</v>
+        <v>-86871</v>
       </c>
       <c r="DO91" s="36" t="n">
         <f aca="false">SUM(DO4:DO90)</f>
@@ -38293,7 +38293,7 @@
       </c>
       <c r="DP91" s="36" t="n">
         <f aca="false">SUM(DP4:DP90)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="DQ91" s="36" t="n">
         <f aca="false">SUM(DQ4:DQ90)</f>
@@ -38310,7 +38310,7 @@
       <c r="DT91" s="54"/>
       <c r="DU91" s="36" t="n">
         <f aca="false">SUM(DU4:DU90)</f>
-        <v>3.04225977743045E-010</v>
+        <v>-1602620</v>
       </c>
       <c r="DV91" s="54"/>
       <c r="DW91" s="36" t="n">
@@ -38323,7 +38323,7 @@
       </c>
       <c r="DY91" s="36" t="n">
         <f aca="false">SUM(DY4:DY90)</f>
-        <v>0</v>
+        <v>-174877</v>
       </c>
       <c r="DZ91" s="36" t="n">
         <f aca="false">SUM(DZ4:DZ90)</f>
@@ -38335,7 +38335,7 @@
       </c>
       <c r="EB91" s="36" t="n">
         <f aca="false">SUM(EB4:EB90)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="EC91" s="36" t="n">
         <f aca="false">SUM(EC4:EC90)</f>
@@ -38348,7 +38348,7 @@
       <c r="EE91" s="54"/>
       <c r="EF91" s="36" t="n">
         <f aca="false">SUM(EF4:EF90)</f>
-        <v>3.18777892971411E-010</v>
+        <v>-1777485</v>
       </c>
       <c r="EG91" s="54"/>
       <c r="EH91" s="36" t="n">
@@ -38358,7 +38358,7 @@
       <c r="EI91" s="54"/>
       <c r="EJ91" s="36" t="n">
         <f aca="false">SUM(EJ4:EJ90)</f>
-        <v>3.18777892971411E-010</v>
+        <v>-1777485</v>
       </c>
       <c r="EK91" s="54"/>
     </row>
@@ -40476,11 +40476,11 @@
       </c>
       <c r="B36" s="71" t="n">
         <f aca="false">SUM(C36:N36)</f>
-        <v>0</v>
+        <v>-6600</v>
       </c>
       <c r="C36" s="72" t="n">
         <f aca="false">TrialBalance!O83+TrialBalance!O88+TrialBalance!O89-0</f>
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="D36" s="72" t="n">
         <f aca="false">TrialBalance!Z83+TrialBalance!Z88+TrialBalance!Z89-C36</f>
@@ -40492,7 +40492,7 @@
       </c>
       <c r="F36" s="72" t="n">
         <f aca="false">TrialBalance!AV83+TrialBalance!AV88+TrialBalance!AV89-SUM(C36:E36)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G36" s="72" t="n">
         <f aca="false">TrialBalance!BG83+TrialBalance!BG88+TrialBalance!BG89-SUM(C36:F36)</f>
@@ -40504,7 +40504,7 @@
       </c>
       <c r="I36" s="72" t="n">
         <f aca="false">TrialBalance!CC83+TrialBalance!CC88+TrialBalance!CC89-SUM(C36:H36)</f>
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="J36" s="72" t="n">
         <f aca="false">TrialBalance!CN83+TrialBalance!CN88+TrialBalance!CN89-SUM(C36:I36)</f>
@@ -40516,7 +40516,7 @@
       </c>
       <c r="L36" s="72" t="n">
         <f aca="false">TrialBalance!DJ83+TrialBalance!DJ88+TrialBalance!DJ89-SUM(C36:K36)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="M36" s="72" t="n">
         <f aca="false">TrialBalance!DU83+TrialBalance!DU88+TrialBalance!DU89-SUM(C36:L36)</f>
@@ -40524,7 +40524,7 @@
       </c>
       <c r="N36" s="72" t="n">
         <f aca="false">TrialBalance!EF83+TrialBalance!EF88+TrialBalance!EF89-SUM(C36:M36)</f>
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="O36" s="68"/>
     </row>
@@ -40766,11 +40766,11 @@
       </c>
       <c r="B41" s="71" t="n">
         <f aca="false">SUM(B18:B40)</f>
-        <v>53948.25</v>
+        <v>47348.25</v>
       </c>
       <c r="C41" s="74" t="n">
         <f aca="false">SUM(C18:C40)</f>
-        <v>4226.25</v>
+        <v>3726.25</v>
       </c>
       <c r="D41" s="71" t="n">
         <f aca="false">SUM(D18:D40)</f>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="F41" s="71" t="n">
         <f aca="false">SUM(F18:F40)</f>
-        <v>6590.25</v>
+        <v>6290.25</v>
       </c>
       <c r="G41" s="71" t="n">
         <f aca="false">SUM(G18:G40)</f>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="I41" s="71" t="n">
         <f aca="false">SUM(I18:I40)</f>
-        <v>6240.75</v>
+        <v>5740.75</v>
       </c>
       <c r="J41" s="71" t="n">
         <f aca="false">SUM(J18:J40)</f>
@@ -40806,7 +40806,7 @@
       </c>
       <c r="L41" s="71" t="n">
         <f aca="false">SUM(L18:L40)</f>
-        <v>9129.25</v>
+        <v>8829.25</v>
       </c>
       <c r="M41" s="71" t="n">
         <f aca="false">SUM(M18:M40)</f>
@@ -40814,7 +40814,7 @@
       </c>
       <c r="N41" s="71" t="n">
         <f aca="false">SUM(N18:N40)</f>
-        <v>2877.5</v>
+        <v>-2122.5</v>
       </c>
       <c r="O41" s="68"/>
     </row>
@@ -40841,11 +40841,11 @@
       </c>
       <c r="B43" s="71" t="n">
         <f aca="false">B16-B41</f>
-        <v>269591.083333333</v>
+        <v>276191.083333333</v>
       </c>
       <c r="C43" s="71" t="n">
         <f aca="false">C16-C41</f>
-        <v>22722.0833333333</v>
+        <v>23222.0833333333</v>
       </c>
       <c r="D43" s="71" t="n">
         <f aca="false">D16-D41</f>
@@ -40857,7 +40857,7 @@
       </c>
       <c r="F43" s="71" t="n">
         <f aca="false">F16-F41</f>
-        <v>20574.0833333333</v>
+        <v>20874.0833333333</v>
       </c>
       <c r="G43" s="71" t="n">
         <f aca="false">G16-G41</f>
@@ -40869,7 +40869,7 @@
       </c>
       <c r="I43" s="71" t="n">
         <f aca="false">I16-I41</f>
-        <v>22627.5833333333</v>
+        <v>23127.5833333333</v>
       </c>
       <c r="J43" s="71" t="n">
         <f aca="false">J16-J41</f>
@@ -40881,7 +40881,7 @@
       </c>
       <c r="L43" s="71" t="n">
         <f aca="false">L16-L41</f>
-        <v>19555.0833333333</v>
+        <v>19855.0833333333</v>
       </c>
       <c r="M43" s="71" t="n">
         <f aca="false">M16-M41</f>
@@ -40889,7 +40889,7 @@
       </c>
       <c r="N43" s="71" t="n">
         <f aca="false">N16-N41</f>
-        <v>22406.8333333333</v>
+        <v>27406.8333333333</v>
       </c>
       <c r="O43" s="68"/>
     </row>
@@ -40957,11 +40957,11 @@
       </c>
       <c r="B45" s="71" t="n">
         <f aca="false">B43+B44</f>
-        <v>269591.083333333</v>
+        <v>276191.083333333</v>
       </c>
       <c r="C45" s="71" t="n">
         <f aca="false">C43+C44</f>
-        <v>22722.0833333333</v>
+        <v>23222.0833333333</v>
       </c>
       <c r="D45" s="71" t="n">
         <f aca="false">D43+D44</f>
@@ -40973,7 +40973,7 @@
       </c>
       <c r="F45" s="71" t="n">
         <f aca="false">F43+F44</f>
-        <v>20574.0833333333</v>
+        <v>20874.0833333333</v>
       </c>
       <c r="G45" s="71" t="n">
         <f aca="false">G43+G44</f>
@@ -40985,7 +40985,7 @@
       </c>
       <c r="I45" s="71" t="n">
         <f aca="false">I43+I44</f>
-        <v>22627.5833333333</v>
+        <v>23127.5833333333</v>
       </c>
       <c r="J45" s="71" t="n">
         <f aca="false">J43+J44</f>
@@ -40997,7 +40997,7 @@
       </c>
       <c r="L45" s="71" t="n">
         <f aca="false">L43+L44</f>
-        <v>19555.0833333333</v>
+        <v>19855.0833333333</v>
       </c>
       <c r="M45" s="71" t="n">
         <f aca="false">M43+M44</f>
@@ -41005,7 +41005,7 @@
       </c>
       <c r="N45" s="71" t="n">
         <f aca="false">N43+N44</f>
-        <v>22406.8333333333</v>
+        <v>27406.8333333333</v>
       </c>
       <c r="O45" s="68"/>
     </row>
@@ -41833,7 +41833,7 @@
       <c r="D39" s="88"/>
       <c r="E39" s="86" t="n">
         <f aca="false">TrialBalance!EJ83+TrialBalance!EJ88+TrialBalance!EJ89</f>
-        <v>0</v>
+        <v>-6600</v>
       </c>
       <c r="H39" s="89"/>
       <c r="I39" s="89"/>
@@ -41940,7 +41940,7 @@
       <c r="E44" s="103"/>
       <c r="F44" s="104" t="n">
         <f aca="false">SUM(E21:E43)</f>
-        <v>53948.25</v>
+        <v>47348.25</v>
       </c>
       <c r="H44" s="89"/>
       <c r="I44" s="89"/>
@@ -41976,7 +41976,7 @@
       <c r="E46" s="103"/>
       <c r="F46" s="104" t="n">
         <f aca="false">F18-F44</f>
-        <v>269591.083333333</v>
+        <v>276191.083333333</v>
       </c>
       <c r="H46" s="89"/>
       <c r="I46" s="89"/>
@@ -42031,7 +42031,7 @@
       <c r="E49" s="103"/>
       <c r="F49" s="104" t="n">
         <f aca="false">F46+F48</f>
-        <v>269591.083333333</v>
+        <v>276191.083333333</v>
       </c>
       <c r="H49" s="89"/>
       <c r="I49" s="89"/>
@@ -42052,7 +42052,7 @@
       <c r="D50" s="101"/>
       <c r="F50" s="86" t="n">
         <f aca="false">TrialBalance!EJ47</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="H50" s="89"/>
       <c r="I50" s="89"/>
@@ -42075,7 +42075,7 @@
       <c r="E51" s="103"/>
       <c r="F51" s="104" t="n">
         <f aca="false">F49-F50</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="H51" s="89"/>
       <c r="I51" s="89"/>
@@ -42136,7 +42136,7 @@
       </c>
       <c r="F54" s="104" t="n">
         <f aca="false">F51-F52</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="H54" s="89"/>
       <c r="I54" s="89"/>
@@ -42313,7 +42313,7 @@
       </c>
       <c r="E11" s="115" t="n">
         <f aca="false">TrialBalance!EJ20</f>
-        <v>424900</v>
+        <v>226300</v>
       </c>
       <c r="F11" s="115"/>
     </row>
@@ -42328,7 +42328,7 @@
       </c>
       <c r="E12" s="119" t="n">
         <f aca="false">IF(SUM(TrialBalance!EJ22:EJ24)&gt;0,SUM(TrialBalance!EJ22:EJ24)+TrialBalance!EJ25+TrialBalance!EJ26,TrialBalance!EJ25)</f>
-        <v>0</v>
+        <v>318135</v>
       </c>
       <c r="F12" s="115"/>
     </row>
@@ -42344,7 +42344,7 @@
       <c r="D13" s="117"/>
       <c r="E13" s="116" t="n">
         <f aca="false">SUM(E10:E12)</f>
-        <v>424900</v>
+        <v>544435</v>
       </c>
       <c r="F13" s="118"/>
     </row>
@@ -42390,7 +42390,7 @@
       </c>
       <c r="E17" s="115" t="n">
         <f aca="false">-TrialBalance!EJ35</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="F17" s="115"/>
     </row>
@@ -42405,7 +42405,7 @@
       </c>
       <c r="E18" s="115" t="n">
         <f aca="false">-SUM(TrialBalance!EJ32:EJ34)</f>
-        <v>70816.6666666667</v>
+        <v>75091.6666666667</v>
       </c>
       <c r="F18" s="115"/>
     </row>
@@ -42438,7 +42438,7 @@
       <c r="D20" s="117"/>
       <c r="E20" s="116" t="n">
         <f aca="false">SUM(E16:E19)</f>
-        <v>233601.2225</v>
+        <v>239130.2225</v>
       </c>
       <c r="F20" s="118"/>
       <c r="G20" s="120"/>
@@ -42465,7 +42465,7 @@
       <c r="E22" s="118"/>
       <c r="F22" s="116" t="n">
         <f aca="false">E13-E20</f>
-        <v>191298.7775</v>
+        <v>305304.7775</v>
       </c>
       <c r="G22" s="120"/>
     </row>
@@ -42518,7 +42518,7 @@
       <c r="E26" s="118"/>
       <c r="F26" s="116" t="n">
         <f aca="false">SUM(F6:F25)</f>
-        <v>217798.7775</v>
+        <v>331804.7775</v>
       </c>
       <c r="G26" s="120"/>
     </row>
@@ -42551,7 +42551,7 @@
       <c r="D29" s="88"/>
       <c r="E29" s="115" t="n">
         <f aca="false">-TrialBalance!EJ39</f>
-        <v>-0</v>
+        <v>1886145</v>
       </c>
       <c r="F29" s="115"/>
       <c r="G29" s="87"/>
@@ -42584,7 +42584,7 @@
       <c r="E31" s="115"/>
       <c r="F31" s="116" t="n">
         <f aca="false">SUM(E29:E30)</f>
-        <v>0</v>
+        <v>1886145</v>
       </c>
     </row>
     <row r="32" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42614,7 +42614,7 @@
       </c>
       <c r="F33" s="116" t="n">
         <f aca="false">F26-F31</f>
-        <v>217798.7775</v>
+        <v>-1554340.2225</v>
       </c>
       <c r="G33" s="120"/>
     </row>
@@ -42664,7 +42664,7 @@
       <c r="E37" s="115"/>
       <c r="F37" s="115" t="n">
         <f aca="false">-TrialBalance!EJ43</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="G37" s="87"/>
       <c r="O37" s="87"/>
@@ -42704,7 +42704,7 @@
       </c>
       <c r="F39" s="116" t="n">
         <f aca="false">SUM(F36:F38)</f>
-        <v>217798.7775</v>
+        <v>223144.7775</v>
       </c>
       <c r="G39" s="120"/>
     </row>
@@ -43190,15 +43190,15 @@
       </c>
       <c r="E14" s="108" t="n">
         <f aca="false">IF([1]Schedule!$F$41&gt;0,[1]Schedule!$F$41,0)</f>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="F14" s="108" t="n">
         <f aca="false">IF([1]Schedule!$F$55&gt;0,[1]Schedule!$F$55,0)</f>
-        <v>0</v>
+        <v>9828</v>
       </c>
       <c r="G14" s="108" t="n">
         <f aca="false">SUM(B14:F14)</f>
-        <v>0</v>
+        <v>10098</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43278,15 +43278,15 @@
       </c>
       <c r="E17" s="108" t="n">
         <f aca="false">E14-E16+E15</f>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="F17" s="108" t="n">
         <f aca="false">F14-F16+F15</f>
-        <v>0</v>
+        <v>9828</v>
       </c>
       <c r="G17" s="108" t="n">
         <f aca="false">SUM(B17:F17)</f>
-        <v>0</v>
+        <v>10098</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43327,15 +43327,15 @@
       </c>
       <c r="E20" s="134" t="n">
         <f aca="false">E11-E17</f>
-        <v>0</v>
+        <v>-270</v>
       </c>
       <c r="F20" s="134" t="n">
         <f aca="false">F11-F17</f>
-        <v>0</v>
+        <v>-9828</v>
       </c>
       <c r="G20" s="134" t="n">
         <f aca="false">G11-G17</f>
-        <v>0</v>
+        <v>-10098</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43466,7 +43466,7 @@
       <c r="C41" s="137"/>
       <c r="D41" s="136" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="G41" s="89"/>
     </row>
@@ -44437,7 +44437,7 @@
       <c r="J5" s="178"/>
       <c r="K5" s="191" t="n">
         <f aca="false">'PubP&amp;L'!F46</f>
-        <v>269591.083333333</v>
+        <v>276191.083333333</v>
       </c>
       <c r="L5" s="185"/>
     </row>
@@ -44555,7 +44555,7 @@
       <c r="J12" s="178"/>
       <c r="K12" s="191" t="n">
         <f aca="false">K5+K10</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="L12" s="185"/>
     </row>
@@ -44765,7 +44765,7 @@
       <c r="J22" s="178"/>
       <c r="K22" s="209" t="n">
         <f aca="false">K12-K20</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="L22" s="185"/>
     </row>
@@ -44867,7 +44867,7 @@
       <c r="J28" s="178"/>
       <c r="K28" s="209" t="n">
         <f aca="false">K22+K24-K26</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="L28" s="185"/>
     </row>
@@ -44965,7 +44965,7 @@
       </c>
       <c r="F33" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A33/A35,0)</f>
-        <v>136109.090857273</v>
+        <v>139404.576493388</v>
       </c>
       <c r="G33" s="224" t="n">
         <f aca="false">Admin!P6</f>
@@ -44974,7 +44974,7 @@
       <c r="H33" s="224"/>
       <c r="I33" s="225" t="n">
         <f aca="false">F33*G33/100</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="J33" s="226"/>
       <c r="K33" s="178"/>
@@ -45002,7 +45002,7 @@
       </c>
       <c r="F34" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A34/A35,0)</f>
-        <v>136481.99247606</v>
+        <v>139786.506839945</v>
       </c>
       <c r="G34" s="224" t="n">
         <f aca="false">Admin!P7</f>
@@ -45011,7 +45011,7 @@
       <c r="H34" s="224"/>
       <c r="I34" s="225" t="n">
         <f aca="false">F34*G34/100</f>
-        <v>25931.5785704514</v>
+        <v>26559.4362995896</v>
       </c>
       <c r="J34" s="226"/>
       <c r="K34" s="178"/>
@@ -45035,7 +45035,7 @@
       <c r="J35" s="227"/>
       <c r="K35" s="228" t="n">
         <f aca="false">SUM(I33:I34)</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="L35" s="185"/>
     </row>
@@ -45101,7 +45101,7 @@
       <c r="J39" s="178"/>
       <c r="K39" s="232" t="n">
         <f aca="false">K35-K37</f>
-        <v>51792.3058333333</v>
+        <v>53046.3058333333</v>
       </c>
       <c r="L39" s="185"/>
     </row>
@@ -49954,7 +49954,7 @@
       </c>
       <c r="Z70" s="302" t="n">
         <f aca="false">IF(CorporationTax!K22&gt;0,CorporationTax!K22," ")</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="AA70" s="302"/>
       <c r="AB70" s="302"/>
@@ -50172,7 +50172,7 @@
       </c>
       <c r="AJ74" s="302" t="n">
         <f aca="false">SUM(Z69:AF70)-SUM(Z72:AF73)</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="AK74" s="302"/>
       <c r="AL74" s="302"/>
@@ -51070,7 +51070,7 @@
       </c>
       <c r="AJ92" s="302" t="n">
         <f aca="false">IF(AJ74&gt;0,AJ74+SUM(AJ76:AJ80)+AJ88,0)</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="AK92" s="302"/>
       <c r="AL92" s="302"/>
@@ -51955,7 +51955,7 @@
       </c>
       <c r="AJ110" s="302" t="n">
         <f aca="false">AJ92-Z96-Z98-Z104-Z106</f>
-        <v>272591.083333333</v>
+        <v>279191.083333333</v>
       </c>
       <c r="AK110" s="302"/>
       <c r="AL110" s="302"/>
@@ -52733,7 +52733,7 @@
       </c>
       <c r="N126" s="328" t="n">
         <f aca="false">CorporationTax!F33</f>
-        <v>136109.090857273</v>
+        <v>139404.576493388</v>
       </c>
       <c r="O126" s="328"/>
       <c r="P126" s="328"/>
@@ -52767,7 +52767,7 @@
       </c>
       <c r="AJ126" s="330" t="n">
         <f aca="false">CorporationTax!I33</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="AK126" s="330"/>
       <c r="AL126" s="330"/>
@@ -53026,7 +53026,7 @@
       </c>
       <c r="AJ131" s="330" t="n">
         <f aca="false">AJ126+AJ128</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="AK131" s="330"/>
       <c r="AL131" s="330"/>
@@ -53742,7 +53742,7 @@
       </c>
       <c r="AJ145" s="330" t="n">
         <f aca="false">AJ131</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="AK145" s="330"/>
       <c r="AL145" s="330"/>
@@ -54444,7 +54444,7 @@
       </c>
       <c r="AJ159" s="330" t="n">
         <f aca="false">IF(AJ145&gt;0,AJ145+AJ149-AJ154,0)</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="AK159" s="330"/>
       <c r="AL159" s="330"/>
@@ -54793,7 +54793,7 @@
       </c>
       <c r="AJ166" s="330" t="n">
         <f aca="false">IF(AJ159&gt;0,AJ159-AJ163,0)</f>
-        <v>25860.7272628819</v>
+        <v>26486.8695337437</v>
       </c>
       <c r="AK166" s="330"/>
       <c r="AL166" s="330"/>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -42863,7 +42863,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43696,7 +43696,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44238,7 +44238,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -42863,7 +42863,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43696,7 +43696,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44238,7 +44238,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -42863,7 +42863,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43696,7 +43696,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44238,7 +44238,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -42863,7 +42863,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43696,7 +43696,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44238,7 +44238,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -43063,7 +43063,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43896,7 +43896,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44438,7 +44438,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="637">
   <si>
     <t xml:space="preserve">Company Name (including Limited)</t>
   </si>
@@ -2251,6 +2251,12 @@
     <t xml:space="preserve">Writing down allowance</t>
   </si>
   <si>
+    <t xml:space="preserve">Corporation Tax main rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marginal relief fraction</t>
+  </si>
+  <si>
     <t xml:space="preserve">Number</t>
   </si>
   <si>
@@ -2266,7 +2272,13 @@
     <t xml:space="preserve">Restricted to</t>
   </si>
   <si>
+    <t xml:space="preserve">Marginal relief lower limit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Depreciation Rates Applied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marginal relief upper limit</t>
   </si>
   <si>
     <t xml:space="preserve">Mileage Allowances</t>
@@ -3279,7 +3291,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="487">
+  <cellXfs count="486">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5164,10 +5176,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="true"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
@@ -5577,7 +5585,7 @@
       <sheetData sheetId="2">
         <row r="2">
           <cell r="E2">
-            <v>0</v>
+            <v>20000</v>
           </cell>
         </row>
       </sheetData>
@@ -7091,7 +7099,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>15153</v>
+            <v>12525.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7121,7 +7129,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>4301</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -7184,7 +7192,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>12478</v>
+            <v>14150.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7214,7 +7222,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>1501</v>
+            <v>3173.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -7277,7 +7285,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>12403</v>
+            <v>12575.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7307,7 +7315,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>1501</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -7370,7 +7378,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>20053</v>
+            <v>16425.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7400,7 +7408,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>6301</v>
+            <v>2673.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -7463,7 +7471,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>12253</v>
+            <v>26233.37</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7493,7 +7501,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>1501</v>
+            <v>15481.37</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -7556,7 +7564,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>11961</v>
+            <v>12133.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7586,7 +7594,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>1501</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -7649,7 +7657,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>59853</v>
+            <v>56825.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7679,7 +7687,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>9201</v>
+            <v>6173.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -7742,7 +7750,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>12078</v>
+            <v>26706.7</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7772,7 +7780,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>1501</v>
+            <v>16129.7</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -7835,7 +7843,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>13120</v>
+            <v>13292.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7865,7 +7873,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>2101</v>
+            <v>2273.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -7890,7 +7898,7 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="F1">
-            <v>41940</v>
+            <v>40440</v>
           </cell>
           <cell r="G1">
             <v>0</v>
@@ -7914,7 +7922,7 @@
             <v>0</v>
           </cell>
           <cell r="N1">
-            <v>1500</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
             <v>0</v>
@@ -7928,7 +7936,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>15453</v>
+            <v>15625.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7958,7 +7966,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>1501</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -8021,7 +8029,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>12553</v>
+            <v>23642.7</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -8051,7 +8059,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>1501</v>
+            <v>12590.7</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -8114,7 +8122,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>23078</v>
+            <v>23250.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -8144,7 +8152,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>1501</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -8416,7 +8424,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>0</v>
+            <v>15000</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -8428,13 +8436,13 @@
             <v>0</v>
           </cell>
           <cell r="AB1">
-            <v>0</v>
+            <v>13000</v>
           </cell>
           <cell r="AC1">
             <v>0</v>
           </cell>
           <cell r="AD1">
-            <v>0</v>
+            <v>2000</v>
           </cell>
           <cell r="AE1">
             <v>0</v>
@@ -8695,7 +8703,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>0</v>
+            <v>8100</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -8707,13 +8715,13 @@
             <v>0</v>
           </cell>
           <cell r="AB1">
-            <v>0</v>
+            <v>7000</v>
           </cell>
           <cell r="AC1">
             <v>0</v>
           </cell>
           <cell r="AD1">
-            <v>0</v>
+            <v>1100</v>
           </cell>
           <cell r="AE1">
             <v>0</v>
@@ -11455,7 +11463,13 @@
       <sheetName val="Charges&amp;Debentures"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="E4">
+            <v>15000</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="1">
@@ -11464,13 +11478,23 @@
           </cell>
         </row>
         <row r="3">
+          <cell r="A3" t="str">
+            <v>Carol Smith</v>
+          </cell>
+        </row>
+        <row r="3">
           <cell r="G3">
-            <v>100</v>
+            <v>60</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>David Brown</v>
           </cell>
         </row>
         <row r="4">
           <cell r="G4">
-            <v>0</v>
+            <v>25</v>
           </cell>
         </row>
       </sheetData>
@@ -13017,7 +13041,9 @@
         <v>54</v>
       </c>
       <c r="D31" s="22"/>
-      <c r="E31" s="8"/>
+      <c r="E31" s="8" t="n">
+        <v>25000</v>
+      </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -13086,7 +13112,7 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="8" t="n">
-        <v>45702</v>
+        <v>20702</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -13311,8 +13337,8 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="8" t="n">
-        <f aca="false">E15</f>
-        <v>10000</v>
+        <f aca="false">IF(COUNT(E43:E47,E49:E76,E80:E85)=0,0,E15)</f>
+        <v>0</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -13341,7 +13367,7 @@
       <c r="F50" s="2"/>
       <c r="G50" s="24" t="n">
         <f aca="false">E46+E47-E48+E49</f>
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="H50" s="2"/>
     </row>
@@ -13366,7 +13392,7 @@
       <c r="F52" s="2"/>
       <c r="G52" s="24" t="n">
         <f aca="false">G45-G50</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H52" s="2"/>
     </row>
@@ -13693,7 +13719,7 @@
       <c r="F79" s="2"/>
       <c r="G79" s="24" t="n">
         <f aca="false">G52-G77</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H79" s="2"/>
     </row>
@@ -13718,7 +13744,7 @@
       <c r="F81" s="2"/>
       <c r="G81" s="24" t="n">
         <f aca="false">G79+E80</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H81" s="2"/>
     </row>
@@ -13743,7 +13769,7 @@
       <c r="F83" s="2"/>
       <c r="G83" s="24" t="n">
         <f aca="false">G81-E82</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H83" s="2"/>
     </row>
@@ -13768,7 +13794,7 @@
       <c r="F85" s="2"/>
       <c r="G85" s="24" t="n">
         <f aca="false">G83-E84</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H85" s="2"/>
     </row>
@@ -15023,7 +15049,7 @@
       <c r="F4" s="428"/>
       <c r="G4" s="423"/>
       <c r="H4" s="429" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I4" s="423"/>
       <c r="J4" s="423"/>
@@ -15182,17 +15208,17 @@
       <c r="C8" s="435"/>
       <c r="D8" s="436" t="n">
         <f aca="false">D6+F8-L8-R8-X8+Z6</f>
-        <v>10000</v>
+        <v>9740</v>
       </c>
       <c r="E8" s="78"/>
       <c r="F8" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]Oct!O$1)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G8" s="78"/>
       <c r="H8" s="437" t="n">
         <f aca="false">H4</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I8" s="78"/>
       <c r="J8" s="78" t="n">
@@ -15202,7 +15228,7 @@
       <c r="K8" s="78"/>
       <c r="L8" s="432" t="n">
         <f aca="false">J8*H8</f>
-        <v>0</v>
+        <v>759.999999999999</v>
       </c>
       <c r="M8" s="78"/>
       <c r="N8" s="437" t="n">
@@ -15242,7 +15268,7 @@
       <c r="AA8" s="78"/>
       <c r="AB8" s="71" t="n">
         <f aca="false">AB6+F8-L8-R8-X8</f>
-        <v>10000</v>
+        <v>9740</v>
       </c>
       <c r="AC8" s="68"/>
       <c r="AD8" s="427"/>
@@ -15296,17 +15322,17 @@
       <c r="C10" s="435"/>
       <c r="D10" s="436" t="n">
         <f aca="false">D8+F10-L10-R10-X10+Z8</f>
-        <v>10000</v>
+        <v>9571</v>
       </c>
       <c r="E10" s="78"/>
       <c r="F10" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]Nov!O$1)</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G10" s="78"/>
       <c r="H10" s="437" t="n">
         <f aca="false">H8</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I10" s="78"/>
       <c r="J10" s="78" t="n">
@@ -15316,7 +15342,7 @@
       <c r="K10" s="78"/>
       <c r="L10" s="432" t="n">
         <f aca="false">J10*H10</f>
-        <v>0</v>
+        <v>768.999999999999</v>
       </c>
       <c r="M10" s="78"/>
       <c r="N10" s="437" t="n">
@@ -15356,7 +15382,7 @@
       <c r="AA10" s="78"/>
       <c r="AB10" s="71" t="n">
         <f aca="false">AB8+F10-L10-R10-X10</f>
-        <v>10000</v>
+        <v>9571</v>
       </c>
       <c r="AC10" s="68"/>
       <c r="AD10" s="438"/>
@@ -15412,17 +15438,17 @@
       <c r="C12" s="435"/>
       <c r="D12" s="436" t="n">
         <f aca="false">D10+F12-L12-R12-X12+Z10</f>
-        <v>10000</v>
+        <v>9075.00000000001</v>
       </c>
       <c r="E12" s="78"/>
       <c r="F12" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]Dec!O$1)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G12" s="78"/>
       <c r="H12" s="437" t="n">
         <f aca="false">H10</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I12" s="78"/>
       <c r="J12" s="78" t="n">
@@ -15432,7 +15458,7 @@
       <c r="K12" s="78"/>
       <c r="L12" s="432" t="n">
         <f aca="false">J12*H12</f>
-        <v>0</v>
+        <v>795.999999999999</v>
       </c>
       <c r="M12" s="78"/>
       <c r="N12" s="437" t="n">
@@ -15472,7 +15498,7 @@
       <c r="AA12" s="78"/>
       <c r="AB12" s="71" t="n">
         <f aca="false">AB10+F12-L12-R12-X12</f>
-        <v>10000</v>
+        <v>9075.00000000001</v>
       </c>
       <c r="AC12" s="68"/>
       <c r="AD12" s="427"/>
@@ -15526,17 +15552,17 @@
       <c r="C14" s="435"/>
       <c r="D14" s="436" t="n">
         <f aca="false">D12+F14-L14-R14-X14+Z12</f>
-        <v>10000</v>
+        <v>8906.00000000001</v>
       </c>
       <c r="E14" s="78"/>
       <c r="F14" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]Jan!O$1)</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G14" s="78"/>
       <c r="H14" s="437" t="n">
         <f aca="false">H12</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I14" s="78"/>
       <c r="J14" s="78" t="n">
@@ -15546,7 +15572,7 @@
       <c r="K14" s="78"/>
       <c r="L14" s="432" t="n">
         <f aca="false">J14*H14</f>
-        <v>0</v>
+        <v>768.999999999999</v>
       </c>
       <c r="M14" s="78"/>
       <c r="N14" s="437" t="n">
@@ -15586,7 +15612,7 @@
       <c r="AA14" s="78"/>
       <c r="AB14" s="71" t="n">
         <f aca="false">AB12+F14-L14-R14-X14</f>
-        <v>10000</v>
+        <v>8906.00000000001</v>
       </c>
       <c r="AC14" s="68"/>
       <c r="AD14" s="440"/>
@@ -15642,17 +15668,17 @@
       <c r="C16" s="435"/>
       <c r="D16" s="436" t="n">
         <f aca="false">D14+F16-L16-R16-X16+Z14</f>
-        <v>10000</v>
+        <v>8542.00000000001</v>
       </c>
       <c r="E16" s="78"/>
       <c r="F16" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]Feb!O$1)</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="G16" s="78"/>
       <c r="H16" s="437" t="n">
         <f aca="false">H14</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I16" s="78"/>
       <c r="J16" s="78" t="n">
@@ -15662,7 +15688,7 @@
       <c r="K16" s="78"/>
       <c r="L16" s="432" t="n">
         <f aca="false">J16*H16</f>
-        <v>0</v>
+        <v>813.999999999999</v>
       </c>
       <c r="M16" s="78"/>
       <c r="N16" s="437" t="n">
@@ -15702,7 +15728,7 @@
       <c r="AA16" s="78"/>
       <c r="AB16" s="71" t="n">
         <f aca="false">AB14+F16-L16-R16-X16</f>
-        <v>10000</v>
+        <v>8542.00000000001</v>
       </c>
       <c r="AC16" s="68"/>
       <c r="AD16" s="427"/>
@@ -15756,17 +15782,17 @@
       <c r="C18" s="435"/>
       <c r="D18" s="436" t="n">
         <f aca="false">D16+F18-L18-R18-X18+Z16</f>
-        <v>10000</v>
+        <v>7991.00000000001</v>
       </c>
       <c r="E18" s="78"/>
       <c r="F18" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]Mar!O$1)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G18" s="78"/>
       <c r="H18" s="437" t="n">
         <f aca="false">H16</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I18" s="78"/>
       <c r="J18" s="78" t="n">
@@ -15776,7 +15802,7 @@
       <c r="K18" s="78"/>
       <c r="L18" s="432" t="n">
         <f aca="false">J18*H18</f>
-        <v>0</v>
+        <v>750.999999999999</v>
       </c>
       <c r="M18" s="78"/>
       <c r="N18" s="437" t="n">
@@ -15816,7 +15842,7 @@
       <c r="AA18" s="78"/>
       <c r="AB18" s="71" t="n">
         <f aca="false">AB16+F18-L18-R18-X18</f>
-        <v>10000</v>
+        <v>7991.00000000001</v>
       </c>
       <c r="AC18" s="68"/>
       <c r="AD18" s="440"/>
@@ -15872,17 +15898,17 @@
       <c r="C20" s="435"/>
       <c r="D20" s="436" t="n">
         <f aca="false">D18+F20-L20-R20-X20+Z18</f>
-        <v>10000</v>
+        <v>7577.00000000001</v>
       </c>
       <c r="E20" s="78"/>
       <c r="F20" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]Apr!O$1)</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G20" s="78"/>
       <c r="H20" s="437" t="n">
         <f aca="false">H18</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I20" s="78"/>
       <c r="J20" s="78" t="n">
@@ -15892,7 +15918,7 @@
       <c r="K20" s="78"/>
       <c r="L20" s="432" t="n">
         <f aca="false">J20*H20</f>
-        <v>0</v>
+        <v>813.999999999999</v>
       </c>
       <c r="M20" s="78"/>
       <c r="N20" s="437" t="n">
@@ -15932,7 +15958,7 @@
       <c r="AA20" s="78"/>
       <c r="AB20" s="71" t="n">
         <f aca="false">AB18+F20-L20-R20-X20</f>
-        <v>10000</v>
+        <v>7577.00000000001</v>
       </c>
       <c r="AC20" s="68"/>
       <c r="AD20" s="427"/>
@@ -15986,17 +16012,17 @@
       <c r="C22" s="435"/>
       <c r="D22" s="436" t="n">
         <f aca="false">D20+F22-L22-R22-X22+Z20</f>
-        <v>10000</v>
+        <v>7508.00000000001</v>
       </c>
       <c r="E22" s="78"/>
       <c r="F22" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]May!O$1)</f>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G22" s="78"/>
       <c r="H22" s="437" t="n">
         <f aca="false">H20</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I22" s="78"/>
       <c r="J22" s="78" t="n">
@@ -16006,7 +16032,7 @@
       <c r="K22" s="78"/>
       <c r="L22" s="432" t="n">
         <f aca="false">J22*H22</f>
-        <v>0</v>
+        <v>768.999999999999</v>
       </c>
       <c r="M22" s="78"/>
       <c r="N22" s="437" t="n">
@@ -16046,7 +16072,7 @@
       <c r="AA22" s="78"/>
       <c r="AB22" s="71" t="n">
         <f aca="false">AB20+F22-L22-R22-X22</f>
-        <v>10000</v>
+        <v>7508.00000000001</v>
       </c>
       <c r="AC22" s="68"/>
       <c r="AD22" s="440"/>
@@ -16102,17 +16128,17 @@
       <c r="C24" s="435"/>
       <c r="D24" s="436" t="n">
         <f aca="false">D22+F24-L24-R24-X24+Z22</f>
-        <v>10000</v>
+        <v>7112.00000000001</v>
       </c>
       <c r="E24" s="78"/>
       <c r="F24" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]Jun!O$1)</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G24" s="78"/>
       <c r="H24" s="437" t="n">
         <f aca="false">H22</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I24" s="78"/>
       <c r="J24" s="78" t="n">
@@ -16122,7 +16148,7 @@
       <c r="K24" s="78"/>
       <c r="L24" s="432" t="n">
         <f aca="false">J24*H24</f>
-        <v>0</v>
+        <v>795.999999999999</v>
       </c>
       <c r="M24" s="78"/>
       <c r="N24" s="437" t="n">
@@ -16162,7 +16188,7 @@
       <c r="AA24" s="78"/>
       <c r="AB24" s="71" t="n">
         <f aca="false">AB22+F24-L24-R24-X24</f>
-        <v>10000</v>
+        <v>7112.00000000001</v>
       </c>
       <c r="AC24" s="68"/>
       <c r="AD24" s="427"/>
@@ -16216,17 +16242,17 @@
       <c r="C26" s="435"/>
       <c r="D26" s="436" t="n">
         <f aca="false">D24+F26-L26-R26-X26+Z24</f>
-        <v>10000</v>
+        <v>6843.00000000001</v>
       </c>
       <c r="E26" s="78"/>
       <c r="F26" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]Jul!O$1)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G26" s="78"/>
       <c r="H26" s="437" t="n">
         <f aca="false">H24</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I26" s="78"/>
       <c r="J26" s="78" t="n">
@@ -16236,7 +16262,7 @@
       <c r="K26" s="78"/>
       <c r="L26" s="432" t="n">
         <f aca="false">J26*H26</f>
-        <v>0</v>
+        <v>768.999999999999</v>
       </c>
       <c r="M26" s="78"/>
       <c r="N26" s="437" t="n">
@@ -16276,7 +16302,7 @@
       <c r="AA26" s="78"/>
       <c r="AB26" s="71" t="n">
         <f aca="false">AB24+F26-L26-R26-X26</f>
-        <v>10000</v>
+        <v>6843.00000000001</v>
       </c>
       <c r="AC26" s="68"/>
       <c r="AD26" s="427"/>
@@ -16330,17 +16356,17 @@
       <c r="C28" s="435"/>
       <c r="D28" s="436" t="n">
         <f aca="false">D26+F28-L28-R28-X28+Z26</f>
-        <v>10000</v>
+        <v>6603.00000000002</v>
       </c>
       <c r="E28" s="78"/>
       <c r="F28" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]Aug!O$1)</f>
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="G28" s="78"/>
       <c r="H28" s="437" t="n">
         <f aca="false">H26</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I28" s="78"/>
       <c r="J28" s="78" t="n">
@@ -16350,7 +16376,7 @@
       <c r="K28" s="78"/>
       <c r="L28" s="432" t="n">
         <f aca="false">J28*H28</f>
-        <v>0</v>
+        <v>789.999999999999</v>
       </c>
       <c r="M28" s="78"/>
       <c r="N28" s="437" t="n">
@@ -16390,7 +16416,7 @@
       <c r="AA28" s="78"/>
       <c r="AB28" s="71" t="n">
         <f aca="false">AB26+F28-L28-R28-X28</f>
-        <v>10000</v>
+        <v>6603.00000000002</v>
       </c>
       <c r="AC28" s="68"/>
       <c r="AD28" s="427" t="s">
@@ -16446,17 +16472,17 @@
       <c r="C30" s="435"/>
       <c r="D30" s="436" t="n">
         <f aca="false">D28+F30-L30-R30-X30+Z28</f>
-        <v>10000</v>
+        <v>6102.00000000002</v>
       </c>
       <c r="E30" s="78"/>
       <c r="F30" s="78" t="n">
         <f aca="false">IF((H$4+N$4+T$4)=0,0,[2]Sep!O$1)</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G30" s="78"/>
       <c r="H30" s="437" t="n">
         <f aca="false">H28</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I30" s="78"/>
       <c r="J30" s="78" t="n">
@@ -16466,7 +16492,7 @@
       <c r="K30" s="78"/>
       <c r="L30" s="432" t="n">
         <f aca="false">J30*H30</f>
-        <v>0</v>
+        <v>750.999999999999</v>
       </c>
       <c r="M30" s="78"/>
       <c r="N30" s="437" t="n">
@@ -16501,7 +16527,7 @@
       <c r="Y30" s="433"/>
       <c r="Z30" s="78" t="n">
         <f aca="false">IF(AB30&lt;&gt;D30,AB30-D30,0)</f>
-        <v>-4000</v>
+        <v>-102.000000000015</v>
       </c>
       <c r="AA30" s="78"/>
       <c r="AB30" s="71" t="n">
@@ -16758,7 +16784,7 @@
       </c>
       <c r="J6" s="465"/>
       <c r="K6" s="465" t="n">
-        <f aca="false">YEAR(L6)</f>
+        <f aca="false">YEAR(L6)-IF(MONTH(L6)&lt;4,1,0)</f>
         <v>2026</v>
       </c>
       <c r="L6" s="466" t="n">
@@ -16767,8 +16793,8 @@
       </c>
       <c r="M6" s="466"/>
       <c r="N6" s="467" t="n">
-        <f aca="false">B32</f>
-        <v>46660</v>
+        <f aca="false">MIN(IF(DATE(YEAR(L6),3,31)&gt;=L6,DATE(YEAR(L6),3,31),DATE(YEAR(L6)+1,3,31)),F21)</f>
+        <v>46477</v>
       </c>
       <c r="O6" s="467"/>
       <c r="P6" s="464" t="n">
@@ -16802,17 +16828,17 @@
       </c>
       <c r="J7" s="465"/>
       <c r="K7" s="465" t="n">
-        <f aca="false">YEAR(L7)</f>
+        <f aca="false">YEAR(L7)-IF(MONTH(L7)&lt;4,1,0)</f>
         <v>2027</v>
       </c>
       <c r="L7" s="466" t="n">
-        <f aca="false">B33</f>
-        <v>46661</v>
+        <f aca="false">N6+1</f>
+        <v>46478</v>
       </c>
       <c r="M7" s="466"/>
       <c r="N7" s="467" t="n">
-        <f aca="false">B56</f>
-        <v>47026</v>
+        <f aca="false">F21</f>
+        <v>46660</v>
       </c>
       <c r="O7" s="467"/>
       <c r="P7" s="464" t="n">
@@ -16841,15 +16867,21 @@
         <v>14</v>
       </c>
       <c r="H8" s="451"/>
-      <c r="I8" s="451"/>
+      <c r="I8" s="465" t="s">
+        <v>620</v>
+      </c>
       <c r="J8" s="451"/>
       <c r="K8" s="451"/>
       <c r="L8" s="451"/>
       <c r="M8" s="451"/>
       <c r="N8" s="451"/>
       <c r="O8" s="451"/>
-      <c r="P8" s="453"/>
-      <c r="Q8" s="453"/>
+      <c r="P8" s="464" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="453" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="451"/>
@@ -16863,7 +16895,9 @@
       <c r="F9" s="451"/>
       <c r="G9" s="453"/>
       <c r="H9" s="451"/>
-      <c r="I9" s="451"/>
+      <c r="I9" s="465" t="s">
+        <v>621</v>
+      </c>
       <c r="J9" s="451"/>
       <c r="K9" s="451"/>
       <c r="L9" s="468" t="s">
@@ -16871,10 +16905,12 @@
       </c>
       <c r="M9" s="451"/>
       <c r="N9" s="469" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="O9" s="470"/>
-      <c r="P9" s="471"/>
+      <c r="P9" s="468" t="n">
+        <v>0.015</v>
+      </c>
       <c r="Q9" s="453"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16884,11 +16920,11 @@
         <v>46326</v>
       </c>
       <c r="C10" s="451"/>
-      <c r="D10" s="472" t="s">
-        <v>621</v>
-      </c>
-      <c r="E10" s="472"/>
-      <c r="F10" s="472"/>
+      <c r="D10" s="471" t="s">
+        <v>623</v>
+      </c>
+      <c r="E10" s="471"/>
+      <c r="F10" s="471"/>
       <c r="G10" s="453"/>
       <c r="H10" s="451"/>
       <c r="I10" s="451"/>
@@ -16899,9 +16935,9 @@
         <v>46295</v>
       </c>
       <c r="M10" s="453" t="s">
-        <v>622</v>
-      </c>
-      <c r="N10" s="473" t="n">
+        <v>624</v>
+      </c>
+      <c r="N10" s="472" t="n">
         <f aca="false">B8</f>
         <v>46295</v>
       </c>
@@ -16917,13 +16953,13 @@
       </c>
       <c r="C11" s="451"/>
       <c r="D11" s="451" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E11" s="468" t="n">
         <v>12000</v>
       </c>
       <c r="F11" s="451" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G11" s="468" t="n">
         <v>3000</v>
@@ -16936,10 +16972,10 @@
         <f aca="false">B32</f>
         <v>46660</v>
       </c>
-      <c r="M11" s="474" t="s">
-        <v>622</v>
-      </c>
-      <c r="N11" s="473" t="n">
+      <c r="M11" s="473" t="s">
+        <v>624</v>
+      </c>
+      <c r="N11" s="472" t="n">
         <f aca="false">B32</f>
         <v>46660</v>
       </c>
@@ -16959,14 +16995,18 @@
       <c r="F12" s="451"/>
       <c r="G12" s="453"/>
       <c r="H12" s="451"/>
-      <c r="I12" s="451"/>
+      <c r="I12" s="465" t="s">
+        <v>627</v>
+      </c>
       <c r="J12" s="451"/>
       <c r="K12" s="451"/>
       <c r="L12" s="451"/>
-      <c r="M12" s="474"/>
+      <c r="M12" s="473"/>
       <c r="N12" s="453"/>
       <c r="O12" s="451"/>
-      <c r="P12" s="453"/>
+      <c r="P12" s="468" t="n">
+        <v>50000</v>
+      </c>
       <c r="Q12" s="453"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16977,7 +17017,7 @@
       </c>
       <c r="C13" s="451"/>
       <c r="D13" s="458" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E13" s="458"/>
       <c r="F13" s="458"/>
@@ -16985,14 +17025,18 @@
         <v>355</v>
       </c>
       <c r="H13" s="451"/>
-      <c r="I13" s="451"/>
+      <c r="I13" s="465" t="s">
+        <v>629</v>
+      </c>
       <c r="J13" s="451"/>
       <c r="K13" s="451"/>
       <c r="L13" s="451"/>
       <c r="M13" s="451"/>
       <c r="N13" s="451"/>
       <c r="O13" s="451"/>
-      <c r="P13" s="451"/>
+      <c r="P13" s="468" t="n">
+        <v>250000</v>
+      </c>
       <c r="Q13" s="451"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17008,17 +17052,17 @@
       <c r="G14" s="453"/>
       <c r="H14" s="451"/>
       <c r="I14" s="458" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="J14" s="458"/>
       <c r="K14" s="458"/>
       <c r="L14" s="456"/>
       <c r="M14" s="451"/>
       <c r="N14" s="453" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="O14" s="453" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="P14" s="451"/>
       <c r="Q14" s="451"/>
@@ -17030,12 +17074,12 @@
         <v>46388</v>
       </c>
       <c r="C15" s="451"/>
-      <c r="D15" s="472" t="s">
-        <v>629</v>
-      </c>
-      <c r="E15" s="472"/>
-      <c r="F15" s="472"/>
-      <c r="G15" s="475" t="n">
+      <c r="D15" s="471" t="s">
+        <v>633</v>
+      </c>
+      <c r="E15" s="471"/>
+      <c r="F15" s="471"/>
+      <c r="G15" s="474" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="451"/>
@@ -17056,26 +17100,26 @@
         <v>46418</v>
       </c>
       <c r="C16" s="451"/>
-      <c r="D16" s="472" t="s">
+      <c r="D16" s="471" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="472"/>
-      <c r="F16" s="472"/>
-      <c r="G16" s="475" t="n">
+      <c r="E16" s="471"/>
+      <c r="F16" s="471"/>
+      <c r="G16" s="474" t="n">
         <v>0.1</v>
       </c>
       <c r="H16" s="451"/>
-      <c r="I16" s="476" t="s">
-        <v>630</v>
-      </c>
-      <c r="J16" s="476"/>
-      <c r="K16" s="476"/>
-      <c r="L16" s="476"/>
-      <c r="M16" s="476"/>
+      <c r="I16" s="475" t="s">
+        <v>634</v>
+      </c>
+      <c r="J16" s="475"/>
+      <c r="K16" s="475"/>
+      <c r="L16" s="475"/>
+      <c r="M16" s="475"/>
       <c r="N16" s="468" t="n">
         <v>10000</v>
       </c>
-      <c r="O16" s="477" t="n">
+      <c r="O16" s="476" t="n">
         <v>0.45</v>
       </c>
       <c r="P16" s="451"/>
@@ -17088,26 +17132,26 @@
         <v>46419</v>
       </c>
       <c r="C17" s="451"/>
-      <c r="D17" s="472" t="s">
+      <c r="D17" s="471" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="472"/>
-      <c r="F17" s="472"/>
-      <c r="G17" s="475" t="n">
+      <c r="E17" s="471"/>
+      <c r="F17" s="471"/>
+      <c r="G17" s="474" t="n">
         <v>0.2</v>
       </c>
       <c r="H17" s="451"/>
-      <c r="I17" s="476" t="s">
-        <v>631</v>
-      </c>
-      <c r="J17" s="476"/>
-      <c r="K17" s="476"/>
-      <c r="L17" s="476"/>
-      <c r="M17" s="476"/>
+      <c r="I17" s="475" t="s">
+        <v>635</v>
+      </c>
+      <c r="J17" s="475"/>
+      <c r="K17" s="475"/>
+      <c r="L17" s="475"/>
+      <c r="M17" s="475"/>
       <c r="N17" s="468" t="n">
         <v>10001</v>
       </c>
-      <c r="O17" s="477" t="n">
+      <c r="O17" s="476" t="n">
         <v>0.25</v>
       </c>
       <c r="P17" s="451"/>
@@ -17120,12 +17164,12 @@
         <v>46446</v>
       </c>
       <c r="C18" s="451"/>
-      <c r="D18" s="472" t="s">
+      <c r="D18" s="471" t="s">
         <v>260</v>
       </c>
-      <c r="E18" s="472"/>
-      <c r="F18" s="472"/>
-      <c r="G18" s="475" t="n">
+      <c r="E18" s="471"/>
+      <c r="F18" s="471"/>
+      <c r="G18" s="474" t="n">
         <v>0.33</v>
       </c>
       <c r="H18" s="451"/>
@@ -17146,29 +17190,29 @@
         <v>46447</v>
       </c>
       <c r="C19" s="451"/>
-      <c r="D19" s="472" t="s">
+      <c r="D19" s="471" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="472"/>
-      <c r="F19" s="472"/>
-      <c r="G19" s="475" t="n">
+      <c r="E19" s="471"/>
+      <c r="F19" s="471"/>
+      <c r="G19" s="474" t="n">
         <v>0.25</v>
       </c>
       <c r="H19" s="451"/>
       <c r="I19" s="458" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="J19" s="458"/>
       <c r="K19" s="458"/>
       <c r="L19" s="451"/>
-      <c r="M19" s="478" t="n">
+      <c r="M19" s="477" t="n">
         <v>20</v>
       </c>
       <c r="N19" s="452" t="n">
         <f aca="false">B9</f>
         <v>46296</v>
       </c>
-      <c r="O19" s="479" t="n">
+      <c r="O19" s="478" t="n">
         <f aca="false">B26</f>
         <v>46568</v>
       </c>
@@ -17192,8 +17236,8 @@
       <c r="K20" s="451"/>
       <c r="L20" s="451"/>
       <c r="M20" s="451"/>
-      <c r="N20" s="480"/>
-      <c r="O20" s="481"/>
+      <c r="N20" s="479"/>
+      <c r="O20" s="480"/>
       <c r="P20" s="451"/>
       <c r="Q20" s="451"/>
     </row>
@@ -17208,13 +17252,13 @@
         <v>616</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="482" t="n">
+      <c r="F21" s="481" t="n">
         <v>46660</v>
       </c>
       <c r="G21" s="453"/>
       <c r="H21" s="451"/>
       <c r="I21" s="458" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="J21" s="458"/>
       <c r="K21" s="458"/>
@@ -17226,7 +17270,7 @@
         <f aca="false">B27</f>
         <v>46569</v>
       </c>
-      <c r="O21" s="481"/>
+      <c r="O21" s="480"/>
       <c r="P21" s="451"/>
       <c r="Q21" s="451"/>
     </row>
@@ -17247,7 +17291,7 @@
       <c r="K22" s="451"/>
       <c r="L22" s="451"/>
       <c r="M22" s="451"/>
-      <c r="N22" s="474"/>
+      <c r="N22" s="473"/>
       <c r="O22" s="451"/>
       <c r="P22" s="451"/>
       <c r="Q22" s="451"/>
@@ -17259,7 +17303,7 @@
         <v>46508</v>
       </c>
       <c r="C23" s="451"/>
-      <c r="F23" s="483"/>
+      <c r="F23" s="482"/>
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="451"/>
@@ -17277,7 +17321,7 @@
       </c>
       <c r="C25" s="451"/>
       <c r="F25" s="450"/>
-      <c r="G25" s="484"/>
+      <c r="G25" s="483"/>
     </row>
     <row r="26" s="448" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="451"/>
@@ -17329,7 +17373,7 @@
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="451"/>
-      <c r="B32" s="485" t="n">
+      <c r="B32" s="484" t="n">
         <f aca="false">F21</f>
         <v>46660</v>
       </c>
@@ -17521,7 +17565,7 @@
     </row>
     <row r="56" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="451"/>
-      <c r="B56" s="486" t="n">
+      <c r="B56" s="485" t="n">
         <f aca="false">DATE(IF(MONTH(B54)&lt;11,YEAR(B54),YEAR(B54)+1),IF(MONTH(B54)&lt;11,MONTH(B54)+2,IF(MONTH(B54)=11,1,2)),1)-1</f>
         <v>47026</v>
       </c>
@@ -21364,12 +21408,12 @@
       <c r="L19" s="36"/>
       <c r="M19" s="36" t="n">
         <f aca="false">Stock!$F$8-Stock!$L$8-Stock!$R$8-Stock!$X$8+Stock!$Z$8</f>
-        <v>0</v>
+        <v>-259.999999999999</v>
       </c>
       <c r="N19" s="57"/>
       <c r="O19" s="36" t="n">
         <f aca="false">SUM(D19:N19)</f>
-        <v>10000</v>
+        <v>9740</v>
       </c>
       <c r="P19" s="57"/>
       <c r="Q19" s="36"/>
@@ -21381,12 +21425,12 @@
       <c r="W19" s="36"/>
       <c r="X19" s="36" t="n">
         <f aca="false">Stock!$F$10-Stock!$L$10-Stock!$R$10-Stock!$X$10+Stock!$Z$10</f>
-        <v>0</v>
+        <v>-168.999999999999</v>
       </c>
       <c r="Y19" s="54"/>
       <c r="Z19" s="36" t="n">
         <f aca="false">SUM(O19:Y19)</f>
-        <v>10000</v>
+        <v>9571</v>
       </c>
       <c r="AA19" s="57"/>
       <c r="AB19" s="36"/>
@@ -21398,12 +21442,12 @@
       <c r="AH19" s="36"/>
       <c r="AI19" s="36" t="n">
         <f aca="false">Stock!$F$12-Stock!$L$12-Stock!$R$12-Stock!$X$12+Stock!$Z$12</f>
-        <v>0</v>
+        <v>-495.999999999999</v>
       </c>
       <c r="AJ19" s="54"/>
       <c r="AK19" s="36" t="n">
         <f aca="false">SUM(Z19:AJ19)</f>
-        <v>10000</v>
+        <v>9075.00000000001</v>
       </c>
       <c r="AL19" s="57"/>
       <c r="AM19" s="36"/>
@@ -21415,12 +21459,12 @@
       <c r="AS19" s="36"/>
       <c r="AT19" s="36" t="n">
         <f aca="false">Stock!$F$14-Stock!$L$14-Stock!$R$14-Stock!$X$14+Stock!$Z$14</f>
-        <v>0</v>
+        <v>-168.999999999999</v>
       </c>
       <c r="AU19" s="54"/>
       <c r="AV19" s="36" t="n">
         <f aca="false">SUM(AK19:AU19)</f>
-        <v>10000</v>
+        <v>8906.00000000001</v>
       </c>
       <c r="AW19" s="57"/>
       <c r="AX19" s="36"/>
@@ -21432,12 +21476,12 @@
       <c r="BD19" s="36"/>
       <c r="BE19" s="36" t="n">
         <f aca="false">Stock!$F$16-Stock!$L$16-Stock!$R$16-Stock!$X$16+Stock!$Z$16</f>
-        <v>0</v>
+        <v>-363.999999999999</v>
       </c>
       <c r="BF19" s="54"/>
       <c r="BG19" s="36" t="n">
         <f aca="false">SUM(AV19:BF19)</f>
-        <v>10000</v>
+        <v>8542.00000000001</v>
       </c>
       <c r="BH19" s="57"/>
       <c r="BI19" s="36"/>
@@ -21449,12 +21493,12 @@
       <c r="BO19" s="36"/>
       <c r="BP19" s="36" t="n">
         <f aca="false">Stock!$F$18-Stock!$L$18-Stock!$R$18-Stock!$X$18+Stock!$Z$18</f>
-        <v>0</v>
+        <v>-550.999999999999</v>
       </c>
       <c r="BQ19" s="54"/>
       <c r="BR19" s="36" t="n">
         <f aca="false">SUM(BG19:BQ19)</f>
-        <v>10000</v>
+        <v>7991.00000000001</v>
       </c>
       <c r="BS19" s="57"/>
       <c r="BT19" s="36"/>
@@ -21466,12 +21510,12 @@
       <c r="BZ19" s="36"/>
       <c r="CA19" s="36" t="n">
         <f aca="false">Stock!$F$20-Stock!$L$20-Stock!$R$20-Stock!$X$20+Stock!$Z$20</f>
-        <v>0</v>
+        <v>-413.999999999999</v>
       </c>
       <c r="CB19" s="54"/>
       <c r="CC19" s="36" t="n">
         <f aca="false">SUM(BR19:CB19)</f>
-        <v>10000</v>
+        <v>7577.00000000001</v>
       </c>
       <c r="CD19" s="57"/>
       <c r="CE19" s="36"/>
@@ -21483,12 +21527,12 @@
       <c r="CK19" s="36"/>
       <c r="CL19" s="36" t="n">
         <f aca="false">Stock!$F$22-Stock!$L$22-Stock!$R$22-Stock!$X$22+Stock!$Z$22</f>
-        <v>0</v>
+        <v>-68.999999999999</v>
       </c>
       <c r="CM19" s="54"/>
       <c r="CN19" s="36" t="n">
         <f aca="false">SUM(CC19:CM19)</f>
-        <v>10000</v>
+        <v>7508.00000000001</v>
       </c>
       <c r="CO19" s="57"/>
       <c r="CP19" s="36"/>
@@ -21500,12 +21544,12 @@
       <c r="CV19" s="36"/>
       <c r="CW19" s="36" t="n">
         <f aca="false">Stock!$F$24-Stock!$L$24-Stock!$R$24-Stock!$X$24+Stock!$Z$24</f>
-        <v>0</v>
+        <v>-395.999999999999</v>
       </c>
       <c r="CX19" s="54"/>
       <c r="CY19" s="36" t="n">
         <f aca="false">SUM(CN19:CX19)</f>
-        <v>10000</v>
+        <v>7112.00000000001</v>
       </c>
       <c r="CZ19" s="57"/>
       <c r="DA19" s="36"/>
@@ -21517,12 +21561,12 @@
       <c r="DG19" s="36"/>
       <c r="DH19" s="36" t="n">
         <f aca="false">Stock!$F$26-Stock!$L$26-Stock!$R$26-Stock!$X$26+Stock!$Z$26</f>
-        <v>0</v>
+        <v>-268.999999999999</v>
       </c>
       <c r="DI19" s="54"/>
       <c r="DJ19" s="36" t="n">
         <f aca="false">SUM(CY19:DI19)</f>
-        <v>10000</v>
+        <v>6843.00000000001</v>
       </c>
       <c r="DK19" s="57"/>
       <c r="DL19" s="36"/>
@@ -21534,12 +21578,12 @@
       <c r="DR19" s="36"/>
       <c r="DS19" s="36" t="n">
         <f aca="false">Stock!$F$28-Stock!$L$28-Stock!$R$28-Stock!$X$28+Stock!$Z$28</f>
-        <v>0</v>
+        <v>-239.999999999999</v>
       </c>
       <c r="DT19" s="54"/>
       <c r="DU19" s="36" t="n">
         <f aca="false">SUM(DJ19:DT19)</f>
-        <v>10000</v>
+        <v>6603.00000000002</v>
       </c>
       <c r="DV19" s="57"/>
       <c r="DW19" s="36"/>
@@ -21551,7 +21595,7 @@
       <c r="EC19" s="36"/>
       <c r="ED19" s="36" t="n">
         <f aca="false">Stock!$F$30-Stock!$L$30-Stock!$R$30-Stock!$X$30+Stock!$Z$30</f>
-        <v>-4000</v>
+        <v>-603.000000000014</v>
       </c>
       <c r="EE19" s="54"/>
       <c r="EF19" s="36" t="n">
@@ -22088,7 +22132,7 @@
       <c r="G22" s="36"/>
       <c r="H22" s="36" t="n">
         <f aca="false">[4]Oct!$F$1-[4]Oct!$X$1</f>
-        <v>29047</v>
+        <v>31674.8</v>
       </c>
       <c r="I22" s="36"/>
       <c r="J22" s="36"/>
@@ -22097,14 +22141,14 @@
       <c r="N22" s="57"/>
       <c r="O22" s="36" t="n">
         <f aca="false">SUM(D22:N22)</f>
-        <v>54047</v>
+        <v>56674.8</v>
       </c>
       <c r="P22" s="57"/>
       <c r="Q22" s="36"/>
       <c r="R22" s="36"/>
       <c r="S22" s="36" t="n">
         <f aca="false">[4]Nov!$F$1-[4]Nov!$X$1</f>
-        <v>20442</v>
+        <v>18769.8</v>
       </c>
       <c r="T22" s="36"/>
       <c r="U22" s="36"/>
@@ -22114,14 +22158,14 @@
       <c r="Y22" s="54"/>
       <c r="Z22" s="36" t="n">
         <f aca="false">SUM(O22:Y22)</f>
-        <v>74489</v>
+        <v>75444.6</v>
       </c>
       <c r="AA22" s="57"/>
       <c r="AB22" s="36"/>
       <c r="AC22" s="36"/>
       <c r="AD22" s="36" t="n">
         <f aca="false">[4]Dec!$F$1-[4]Dec!$X$1</f>
-        <v>22797</v>
+        <v>22624.8</v>
       </c>
       <c r="AE22" s="36"/>
       <c r="AF22" s="36"/>
@@ -22131,14 +22175,14 @@
       <c r="AJ22" s="54"/>
       <c r="AK22" s="36" t="n">
         <f aca="false">SUM(Z22:AJ22)</f>
-        <v>97286</v>
+        <v>98069.4</v>
       </c>
       <c r="AL22" s="57"/>
       <c r="AM22" s="36"/>
       <c r="AN22" s="36"/>
       <c r="AO22" s="36" t="n">
         <f aca="false">[4]Jan!$F$1-[4]Jan!$X$1</f>
-        <v>13707</v>
+        <v>17334.8</v>
       </c>
       <c r="AP22" s="36"/>
       <c r="AQ22" s="36"/>
@@ -22148,14 +22192,14 @@
       <c r="AU22" s="54"/>
       <c r="AV22" s="36" t="n">
         <f aca="false">SUM(AK22:AU22)</f>
-        <v>110993</v>
+        <v>115404.2</v>
       </c>
       <c r="AW22" s="57"/>
       <c r="AX22" s="36"/>
       <c r="AY22" s="36"/>
       <c r="AZ22" s="36" t="n">
         <f aca="false">[4]Feb!$F$1-[4]Feb!$X$1</f>
-        <v>26267</v>
+        <v>12286.63</v>
       </c>
       <c r="BA22" s="36"/>
       <c r="BB22" s="36"/>
@@ -22165,14 +22209,14 @@
       <c r="BF22" s="54"/>
       <c r="BG22" s="36" t="n">
         <f aca="false">SUM(AV22:BF22)</f>
-        <v>137260</v>
+        <v>127690.83</v>
       </c>
       <c r="BH22" s="57"/>
       <c r="BI22" s="36"/>
       <c r="BJ22" s="36"/>
       <c r="BK22" s="36" t="n">
         <f aca="false">[4]Mar!$F$1-[4]Mar!$X$1</f>
-        <v>21799</v>
+        <v>21626.8</v>
       </c>
       <c r="BL22" s="36"/>
       <c r="BM22" s="36"/>
@@ -22182,14 +22226,14 @@
       <c r="BQ22" s="54"/>
       <c r="BR22" s="36" t="n">
         <f aca="false">SUM(BG22:BQ22)</f>
-        <v>159059</v>
+        <v>149317.63</v>
       </c>
       <c r="BS22" s="57"/>
       <c r="BT22" s="36"/>
       <c r="BU22" s="36"/>
       <c r="BV22" s="36" t="n">
         <f aca="false">[4]Apr!$F$1-[4]Apr!$X$1</f>
-        <v>-9293</v>
+        <v>-6265.2</v>
       </c>
       <c r="BW22" s="36"/>
       <c r="BX22" s="36"/>
@@ -22199,14 +22243,14 @@
       <c r="CB22" s="54"/>
       <c r="CC22" s="36" t="n">
         <f aca="false">SUM(BR22:CB22)</f>
-        <v>149766</v>
+        <v>143052.43</v>
       </c>
       <c r="CD22" s="57"/>
       <c r="CE22" s="36"/>
       <c r="CF22" s="36"/>
       <c r="CG22" s="36" t="n">
         <f aca="false">[4]May!$F$1-[4]May!$X$1</f>
-        <v>23242</v>
+        <v>8613.3</v>
       </c>
       <c r="CH22" s="36"/>
       <c r="CI22" s="36"/>
@@ -22216,14 +22260,14 @@
       <c r="CM22" s="54"/>
       <c r="CN22" s="36" t="n">
         <f aca="false">SUM(CC22:CM22)</f>
-        <v>173008</v>
+        <v>151665.73</v>
       </c>
       <c r="CO22" s="57"/>
       <c r="CP22" s="36"/>
       <c r="CQ22" s="36"/>
       <c r="CR22" s="36" t="n">
         <f aca="false">[4]Jun!$F$1-[4]Jun!$X$1</f>
-        <v>19680</v>
+        <v>19507.8</v>
       </c>
       <c r="CS22" s="36"/>
       <c r="CT22" s="36"/>
@@ -22233,14 +22277,14 @@
       <c r="CX22" s="54"/>
       <c r="CY22" s="36" t="n">
         <f aca="false">SUM(CN22:CX22)</f>
-        <v>192688</v>
+        <v>171173.53</v>
       </c>
       <c r="CZ22" s="57"/>
       <c r="DA22" s="36"/>
       <c r="DB22" s="36"/>
       <c r="DC22" s="36" t="n">
         <f aca="false">[4]Jul!$F$1-[4]Jul!$X$1</f>
-        <v>26487</v>
+        <v>24814.8</v>
       </c>
       <c r="DD22" s="36"/>
       <c r="DE22" s="36"/>
@@ -22250,14 +22294,14 @@
       <c r="DI22" s="54"/>
       <c r="DJ22" s="36" t="n">
         <f aca="false">SUM(CY22:DI22)</f>
-        <v>219175</v>
+        <v>195988.33</v>
       </c>
       <c r="DK22" s="57"/>
       <c r="DL22" s="36"/>
       <c r="DM22" s="36"/>
       <c r="DN22" s="36" t="n">
         <f aca="false">[4]Aug!$F$1-[4]Aug!$X$1</f>
-        <v>21807</v>
+        <v>10717.3</v>
       </c>
       <c r="DO22" s="36"/>
       <c r="DP22" s="36"/>
@@ -22267,14 +22311,14 @@
       <c r="DT22" s="54"/>
       <c r="DU22" s="36" t="n">
         <f aca="false">SUM(DJ22:DT22)</f>
-        <v>240982</v>
+        <v>206705.63</v>
       </c>
       <c r="DV22" s="57"/>
       <c r="DW22" s="36"/>
       <c r="DX22" s="36"/>
       <c r="DY22" s="36" t="n">
         <f aca="false">[4]Sep!$F$1-[4]Sep!$X$1</f>
-        <v>-2118</v>
+        <v>-2290.2</v>
       </c>
       <c r="DZ22" s="36"/>
       <c r="EA22" s="36"/>
@@ -22284,13 +22328,13 @@
       <c r="EE22" s="54"/>
       <c r="EF22" s="36" t="n">
         <f aca="false">SUM(DU22:EE22)</f>
-        <v>238864</v>
+        <v>204415.43</v>
       </c>
       <c r="EG22" s="54"/>
       <c r="EI22" s="54"/>
       <c r="EJ22" s="36" t="n">
         <f aca="false">SUM(EF22:EH22)</f>
-        <v>238864</v>
+        <v>204415.43</v>
       </c>
       <c r="EK22" s="54"/>
     </row>
@@ -22345,7 +22389,7 @@
       <c r="AD23" s="36"/>
       <c r="AE23" s="36" t="n">
         <f aca="false">[5]Dec!$F$1-[5]Dec!$X$1</f>
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="AF23" s="36"/>
       <c r="AG23" s="36"/>
@@ -22354,7 +22398,7 @@
       <c r="AJ23" s="54"/>
       <c r="AK23" s="36" t="n">
         <f aca="false">SUM(Z23:AJ23)</f>
-        <v>5000</v>
+        <v>-10000</v>
       </c>
       <c r="AL23" s="57"/>
       <c r="AM23" s="36"/>
@@ -22371,7 +22415,7 @@
       <c r="AU23" s="54"/>
       <c r="AV23" s="36" t="n">
         <f aca="false">SUM(AK23:AU23)</f>
-        <v>5000</v>
+        <v>-10000</v>
       </c>
       <c r="AW23" s="57"/>
       <c r="AX23" s="36"/>
@@ -22388,7 +22432,7 @@
       <c r="BF23" s="54"/>
       <c r="BG23" s="36" t="n">
         <f aca="false">SUM(AV23:BF23)</f>
-        <v>5000</v>
+        <v>-10000</v>
       </c>
       <c r="BH23" s="57"/>
       <c r="BI23" s="36"/>
@@ -22396,7 +22440,7 @@
       <c r="BK23" s="36"/>
       <c r="BL23" s="36" t="n">
         <f aca="false">[5]Mar!$F$1-[5]Mar!$X$1</f>
-        <v>125</v>
+        <v>-7975</v>
       </c>
       <c r="BM23" s="36"/>
       <c r="BN23" s="36"/>
@@ -22405,7 +22449,7 @@
       <c r="BQ23" s="54"/>
       <c r="BR23" s="36" t="n">
         <f aca="false">SUM(BG23:BQ23)</f>
-        <v>5125</v>
+        <v>-17975</v>
       </c>
       <c r="BS23" s="57"/>
       <c r="BT23" s="36"/>
@@ -22422,7 +22466,7 @@
       <c r="CB23" s="54"/>
       <c r="CC23" s="36" t="n">
         <f aca="false">SUM(BR23:CB23)</f>
-        <v>5125</v>
+        <v>-17975</v>
       </c>
       <c r="CD23" s="57"/>
       <c r="CE23" s="36"/>
@@ -22439,7 +22483,7 @@
       <c r="CM23" s="54"/>
       <c r="CN23" s="36" t="n">
         <f aca="false">SUM(CC23:CM23)</f>
-        <v>5125</v>
+        <v>-17975</v>
       </c>
       <c r="CO23" s="57"/>
       <c r="CP23" s="36"/>
@@ -22456,7 +22500,7 @@
       <c r="CX23" s="54"/>
       <c r="CY23" s="36" t="n">
         <f aca="false">SUM(CN23:CX23)</f>
-        <v>5125</v>
+        <v>-17975</v>
       </c>
       <c r="CZ23" s="57"/>
       <c r="DA23" s="36"/>
@@ -22473,7 +22517,7 @@
       <c r="DI23" s="54"/>
       <c r="DJ23" s="36" t="n">
         <f aca="false">SUM(CY23:DI23)</f>
-        <v>5125</v>
+        <v>-17975</v>
       </c>
       <c r="DK23" s="57"/>
       <c r="DL23" s="36"/>
@@ -22490,7 +22534,7 @@
       <c r="DT23" s="54"/>
       <c r="DU23" s="36" t="n">
         <f aca="false">SUM(DJ23:DT23)</f>
-        <v>5125</v>
+        <v>-17975</v>
       </c>
       <c r="DV23" s="57"/>
       <c r="DW23" s="36"/>
@@ -22507,13 +22551,13 @@
       <c r="EE23" s="54"/>
       <c r="EF23" s="36" t="n">
         <f aca="false">SUM(DU23:EE23)</f>
-        <v>10275</v>
+        <v>-12825</v>
       </c>
       <c r="EG23" s="54"/>
       <c r="EI23" s="54"/>
       <c r="EJ23" s="36" t="n">
         <f aca="false">SUM(EF23:EH23)</f>
-        <v>10275</v>
+        <v>-12825</v>
       </c>
       <c r="EK23" s="54"/>
     </row>
@@ -23512,7 +23556,7 @@
       </c>
       <c r="AE28" s="36" t="n">
         <f aca="false">[5]Dec!$AB$1</f>
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="AF28" s="36" t="n">
         <f aca="false">[6]Dec!$AB$1</f>
@@ -23527,7 +23571,7 @@
       <c r="AJ28" s="54"/>
       <c r="AK28" s="36" t="n">
         <f aca="false">SUM(Z28:AJ28)</f>
-        <v>-10723.25</v>
+        <v>2276.75</v>
       </c>
       <c r="AL28" s="57"/>
       <c r="AM28" s="36"/>
@@ -23556,7 +23600,7 @@
       <c r="AU28" s="54"/>
       <c r="AV28" s="36" t="n">
         <f aca="false">SUM(AK28:AU28)</f>
-        <v>-15982.5</v>
+        <v>-2982.5</v>
       </c>
       <c r="AW28" s="57"/>
       <c r="AX28" s="36"/>
@@ -23585,7 +23629,7 @@
       <c r="BF28" s="54"/>
       <c r="BG28" s="36" t="n">
         <f aca="false">SUM(AV28:BF28)</f>
-        <v>-16287.75</v>
+        <v>-3287.75</v>
       </c>
       <c r="BH28" s="57"/>
       <c r="BI28" s="36"/>
@@ -23599,7 +23643,7 @@
       </c>
       <c r="BL28" s="36" t="n">
         <f aca="false">[5]Mar!$AB$1</f>
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="BM28" s="36" t="n">
         <f aca="false">[6]Mar!$AB$1</f>
@@ -23614,7 +23658,7 @@
       <c r="BQ28" s="54"/>
       <c r="BR28" s="36" t="n">
         <f aca="false">SUM(BG28:BQ28)</f>
-        <v>-17644.75</v>
+        <v>2355.25</v>
       </c>
       <c r="BS28" s="57"/>
       <c r="BT28" s="36"/>
@@ -23643,7 +23687,7 @@
       <c r="CB28" s="54"/>
       <c r="CC28" s="36" t="n">
         <f aca="false">SUM(BR28:CB28)</f>
-        <v>-20030.5</v>
+        <v>-30.5</v>
       </c>
       <c r="CD28" s="57"/>
       <c r="CE28" s="36"/>
@@ -23672,7 +23716,7 @@
       <c r="CM28" s="54"/>
       <c r="CN28" s="36" t="n">
         <f aca="false">SUM(CC28:CM28)</f>
-        <v>-23048.5</v>
+        <v>-3048.5</v>
       </c>
       <c r="CO28" s="57"/>
       <c r="CP28" s="36"/>
@@ -23701,7 +23745,7 @@
       <c r="CX28" s="54"/>
       <c r="CY28" s="36" t="n">
         <f aca="false">SUM(CN28:CX28)</f>
-        <v>-28250</v>
+        <v>-8250</v>
       </c>
       <c r="CZ28" s="57"/>
       <c r="DA28" s="36"/>
@@ -23730,7 +23774,7 @@
       <c r="DI28" s="54"/>
       <c r="DJ28" s="36" t="n">
         <f aca="false">SUM(CY28:DI28)</f>
-        <v>-28761.25</v>
+        <v>-8761.25</v>
       </c>
       <c r="DK28" s="57"/>
       <c r="DL28" s="36"/>
@@ -23759,7 +23803,7 @@
       <c r="DT28" s="54"/>
       <c r="DU28" s="36" t="n">
         <f aca="false">SUM(DJ28:DT28)</f>
-        <v>-28517.75</v>
+        <v>-8517.75</v>
       </c>
       <c r="DV28" s="57"/>
       <c r="DW28" s="36"/>
@@ -23788,17 +23832,17 @@
       <c r="EE28" s="54"/>
       <c r="EF28" s="36" t="n">
         <f aca="false">SUM(DU28:EE28)</f>
-        <v>-28432.25</v>
+        <v>-8432.25</v>
       </c>
       <c r="EG28" s="54"/>
       <c r="EH28" s="36" t="n">
         <f aca="false">[1]HPfinance!$E$2</f>
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="EI28" s="54"/>
       <c r="EJ28" s="36" t="n">
         <f aca="false">SUM(EF28:EH28)</f>
-        <v>-28432.25</v>
+        <v>11567.75</v>
       </c>
       <c r="EK28" s="54"/>
     </row>
@@ -24714,12 +24758,12 @@
       <c r="EG31" s="54"/>
       <c r="EH31" s="36" t="n">
         <f aca="false">-[8]Boardmeeting!$E$4</f>
-        <v>-0</v>
+        <v>-15000</v>
       </c>
       <c r="EI31" s="54"/>
       <c r="EJ31" s="36" t="n">
         <f aca="false">SUM(EF31:EH31)</f>
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="EK31" s="54"/>
     </row>
@@ -25436,7 +25480,7 @@
       </c>
       <c r="DC33" s="36" t="n">
         <f aca="false">-[4]Jul!$N$1+[4]Jul!$AI$1</f>
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="DD33" s="36" t="n">
         <f aca="false">-[5]Jul!$N$1+[5]Jul!$AI$1</f>
@@ -25455,7 +25499,7 @@
       <c r="DI33" s="54"/>
       <c r="DJ33" s="36" t="n">
         <f aca="false">SUM(CY33:DI33)</f>
-        <v>-48218.4583333334</v>
+        <v>-46718.4583333334</v>
       </c>
       <c r="DK33" s="57"/>
       <c r="DL33" s="36" t="n">
@@ -25487,7 +25531,7 @@
       <c r="DT33" s="54"/>
       <c r="DU33" s="36" t="n">
         <f aca="false">SUM(DJ33:DT33)</f>
-        <v>-53212.375</v>
+        <v>-51712.375</v>
       </c>
       <c r="DV33" s="57"/>
       <c r="DW33" s="36" t="n">
@@ -25519,13 +25563,13 @@
       <c r="EE33" s="54"/>
       <c r="EF33" s="36" t="n">
         <f aca="false">SUM(DU33:EE33)</f>
-        <v>-57817.9583333334</v>
+        <v>-56317.9583333334</v>
       </c>
       <c r="EG33" s="54"/>
       <c r="EI33" s="54"/>
       <c r="EJ33" s="36" t="n">
         <f aca="false">SUM(EF33:EH33)</f>
-        <v>-57817.9583333334</v>
+        <v>-56317.9583333334</v>
       </c>
       <c r="EK33" s="54"/>
     </row>
@@ -25546,7 +25590,7 @@
       <c r="G34" s="36"/>
       <c r="H34" s="36" t="n">
         <f aca="false">[4]Oct!$AH$1</f>
-        <v>4301</v>
+        <v>1673.2</v>
       </c>
       <c r="I34" s="36" t="n">
         <f aca="false">[5]Oct!$AH$1</f>
@@ -25567,14 +25611,14 @@
       <c r="N34" s="57"/>
       <c r="O34" s="36" t="n">
         <f aca="false">SUM(D34:N34)</f>
-        <v>2627.8</v>
+        <v>0</v>
       </c>
       <c r="P34" s="57"/>
       <c r="Q34" s="36"/>
       <c r="R34" s="36"/>
       <c r="S34" s="36" t="n">
         <f aca="false">[4]Nov!$AH$1</f>
-        <v>1501</v>
+        <v>3173.2</v>
       </c>
       <c r="T34" s="36" t="n">
         <f aca="false">[5]Nov!$AH$1</f>
@@ -25596,14 +25640,14 @@
       <c r="Y34" s="54"/>
       <c r="Z34" s="36" t="n">
         <f aca="false">SUM(O34:Y34)</f>
-        <v>2455.6</v>
+        <v>1500</v>
       </c>
       <c r="AA34" s="57"/>
       <c r="AB34" s="36"/>
       <c r="AC34" s="36"/>
       <c r="AD34" s="36" t="n">
         <f aca="false">[4]Dec!$AH$1</f>
-        <v>1501</v>
+        <v>1673.2</v>
       </c>
       <c r="AE34" s="36" t="n">
         <f aca="false">[5]Dec!$AH$1</f>
@@ -25625,14 +25669,14 @@
       <c r="AJ34" s="54"/>
       <c r="AK34" s="36" t="n">
         <f aca="false">SUM(Z34:AJ34)</f>
-        <v>2283.4</v>
+        <v>1500</v>
       </c>
       <c r="AL34" s="57"/>
       <c r="AM34" s="36"/>
       <c r="AN34" s="36"/>
       <c r="AO34" s="36" t="n">
         <f aca="false">[4]Jan!$AH$1</f>
-        <v>6301</v>
+        <v>2673.2</v>
       </c>
       <c r="AP34" s="36" t="n">
         <f aca="false">[5]Jan!$AH$1</f>
@@ -25654,14 +25698,14 @@
       <c r="AU34" s="54"/>
       <c r="AV34" s="36" t="n">
         <f aca="false">SUM(AK34:AU34)</f>
-        <v>6911.2</v>
+        <v>2500</v>
       </c>
       <c r="AW34" s="57"/>
       <c r="AX34" s="36"/>
       <c r="AY34" s="36"/>
       <c r="AZ34" s="36" t="n">
         <f aca="false">[4]Feb!$AH$1</f>
-        <v>1501</v>
+        <v>15481.37</v>
       </c>
       <c r="BA34" s="36" t="n">
         <f aca="false">[5]Feb!$AH$1</f>
@@ -25683,14 +25727,14 @@
       <c r="BF34" s="54"/>
       <c r="BG34" s="36" t="n">
         <f aca="false">SUM(AV34:BF34)</f>
-        <v>6739</v>
+        <v>16308.17</v>
       </c>
       <c r="BH34" s="57"/>
       <c r="BI34" s="36"/>
       <c r="BJ34" s="36"/>
       <c r="BK34" s="36" t="n">
         <f aca="false">[4]Mar!$AH$1</f>
-        <v>1501</v>
+        <v>1673.2</v>
       </c>
       <c r="BL34" s="36" t="n">
         <f aca="false">[5]Mar!$AH$1</f>
@@ -25712,14 +25756,14 @@
       <c r="BQ34" s="54"/>
       <c r="BR34" s="36" t="n">
         <f aca="false">SUM(BG34:BQ34)</f>
-        <v>6566.8</v>
+        <v>16308.17</v>
       </c>
       <c r="BS34" s="57"/>
       <c r="BT34" s="36"/>
       <c r="BU34" s="36"/>
       <c r="BV34" s="36" t="n">
         <f aca="false">[4]Apr!$AH$1</f>
-        <v>9201</v>
+        <v>6173.2</v>
       </c>
       <c r="BW34" s="36" t="n">
         <f aca="false">[5]Apr!$AH$1</f>
@@ -25741,14 +25785,14 @@
       <c r="CB34" s="54"/>
       <c r="CC34" s="36" t="n">
         <f aca="false">SUM(BR34:CB34)</f>
-        <v>14094.6</v>
+        <v>20808.17</v>
       </c>
       <c r="CD34" s="57"/>
       <c r="CE34" s="36"/>
       <c r="CF34" s="36"/>
       <c r="CG34" s="36" t="n">
         <f aca="false">[4]May!$AH$1</f>
-        <v>1501</v>
+        <v>16129.7</v>
       </c>
       <c r="CH34" s="36" t="n">
         <f aca="false">[5]May!$AH$1</f>
@@ -25770,14 +25814,14 @@
       <c r="CM34" s="54"/>
       <c r="CN34" s="36" t="n">
         <f aca="false">SUM(CC34:CM34)</f>
-        <v>13922.4</v>
+        <v>35264.67</v>
       </c>
       <c r="CO34" s="57"/>
       <c r="CP34" s="36"/>
       <c r="CQ34" s="36"/>
       <c r="CR34" s="36" t="n">
         <f aca="false">[4]Jun!$AH$1</f>
-        <v>2101</v>
+        <v>2273.2</v>
       </c>
       <c r="CS34" s="36" t="n">
         <f aca="false">[5]Jun!$AH$1</f>
@@ -25799,14 +25843,14 @@
       <c r="CX34" s="54"/>
       <c r="CY34" s="36" t="n">
         <f aca="false">SUM(CN34:CX34)</f>
-        <v>14350.2</v>
+        <v>35864.67</v>
       </c>
       <c r="CZ34" s="57"/>
       <c r="DA34" s="36"/>
       <c r="DB34" s="36"/>
       <c r="DC34" s="36" t="n">
         <f aca="false">[4]Jul!$AH$1</f>
-        <v>1501</v>
+        <v>1673.2</v>
       </c>
       <c r="DD34" s="36" t="n">
         <f aca="false">[5]Jul!$AH$1</f>
@@ -25828,14 +25872,14 @@
       <c r="DI34" s="54"/>
       <c r="DJ34" s="36" t="n">
         <f aca="false">SUM(CY34:DI34)</f>
-        <v>14178</v>
+        <v>35864.67</v>
       </c>
       <c r="DK34" s="57"/>
       <c r="DL34" s="36"/>
       <c r="DM34" s="36"/>
       <c r="DN34" s="36" t="n">
         <f aca="false">[4]Aug!$AH$1</f>
-        <v>1501</v>
+        <v>12590.7</v>
       </c>
       <c r="DO34" s="36" t="n">
         <f aca="false">[5]Aug!$AH$1</f>
@@ -25857,14 +25901,14 @@
       <c r="DT34" s="54"/>
       <c r="DU34" s="36" t="n">
         <f aca="false">SUM(DJ34:DT34)</f>
-        <v>14005.8</v>
+        <v>46782.17</v>
       </c>
       <c r="DV34" s="57"/>
       <c r="DW34" s="36"/>
       <c r="DX34" s="36"/>
       <c r="DY34" s="36" t="n">
         <f aca="false">[4]Sep!$AH$1</f>
-        <v>1501</v>
+        <v>1673.2</v>
       </c>
       <c r="DZ34" s="36" t="n">
         <f aca="false">[5]Sep!$AH$1</f>
@@ -25886,13 +25930,13 @@
       <c r="EE34" s="54"/>
       <c r="EF34" s="36" t="n">
         <f aca="false">SUM(DU34:EE34)</f>
-        <v>13833.6</v>
+        <v>46782.17</v>
       </c>
       <c r="EG34" s="54"/>
       <c r="EI34" s="54"/>
       <c r="EJ34" s="36" t="n">
         <f aca="false">SUM(EF34:EH34)</f>
-        <v>13833.6</v>
+        <v>46782.17</v>
       </c>
       <c r="EK34" s="54"/>
     </row>
@@ -26215,12 +26259,12 @@
       <c r="EC35" s="36"/>
       <c r="ED35" s="36" t="n">
         <f aca="false">-CorporationTax!K35</f>
-        <v>-28028.7805895061</v>
+        <v>-34521.272927469</v>
       </c>
       <c r="EE35" s="54"/>
       <c r="EF35" s="36" t="n">
         <f aca="false">SUM(DU35:EE35)</f>
-        <v>-32528.7805895061</v>
+        <v>-39021.272927469</v>
       </c>
       <c r="EG35" s="54"/>
       <c r="EH35" s="36" t="n">
@@ -26230,7 +26274,7 @@
       <c r="EI35" s="54"/>
       <c r="EJ35" s="36" t="n">
         <f aca="false">SUM(EF35:EH35)</f>
-        <v>-32464.2744166666</v>
+        <v>-38956.7667546295</v>
       </c>
       <c r="EK35" s="54"/>
     </row>
@@ -27178,7 +27222,7 @@
       </c>
       <c r="D40" s="36" t="n">
         <f aca="false">-OpenAccounts!E31</f>
-        <v>-0</v>
+        <v>-25000</v>
       </c>
       <c r="E40" s="57"/>
       <c r="F40" s="36"/>
@@ -27203,7 +27247,7 @@
       <c r="N40" s="57"/>
       <c r="O40" s="36" t="n">
         <f aca="false">SUM(D40:N40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="P40" s="57"/>
       <c r="Q40" s="36"/>
@@ -27229,7 +27273,7 @@
       <c r="Y40" s="54"/>
       <c r="Z40" s="36" t="n">
         <f aca="false">SUM(O40:Y40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="AA40" s="57"/>
       <c r="AB40" s="36"/>
@@ -27255,7 +27299,7 @@
       <c r="AJ40" s="54"/>
       <c r="AK40" s="36" t="n">
         <f aca="false">SUM(Z40:AJ40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="AL40" s="57"/>
       <c r="AM40" s="36"/>
@@ -27281,7 +27325,7 @@
       <c r="AU40" s="54"/>
       <c r="AV40" s="36" t="n">
         <f aca="false">SUM(AK40:AU40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="AW40" s="57"/>
       <c r="AX40" s="36"/>
@@ -27307,7 +27351,7 @@
       <c r="BF40" s="54"/>
       <c r="BG40" s="36" t="n">
         <f aca="false">SUM(AV40:BF40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="BH40" s="57"/>
       <c r="BI40" s="36"/>
@@ -27333,7 +27377,7 @@
       <c r="BQ40" s="54"/>
       <c r="BR40" s="36" t="n">
         <f aca="false">SUM(BG40:BQ40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="BS40" s="57"/>
       <c r="BT40" s="36"/>
@@ -27359,7 +27403,7 @@
       <c r="CB40" s="54"/>
       <c r="CC40" s="36" t="n">
         <f aca="false">SUM(BR40:CB40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="CD40" s="57"/>
       <c r="CE40" s="36"/>
@@ -27385,7 +27429,7 @@
       <c r="CM40" s="54"/>
       <c r="CN40" s="36" t="n">
         <f aca="false">SUM(CC40:CM40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="CO40" s="57"/>
       <c r="CP40" s="36"/>
@@ -27411,7 +27455,7 @@
       <c r="CX40" s="54"/>
       <c r="CY40" s="36" t="n">
         <f aca="false">SUM(CN40:CX40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="CZ40" s="57"/>
       <c r="DA40" s="36"/>
@@ -27437,7 +27481,7 @@
       <c r="DI40" s="54"/>
       <c r="DJ40" s="36" t="n">
         <f aca="false">SUM(CY40:DI40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="DK40" s="57"/>
       <c r="DL40" s="36"/>
@@ -27463,7 +27507,7 @@
       <c r="DT40" s="54"/>
       <c r="DU40" s="36" t="n">
         <f aca="false">SUM(DJ40:DT40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="DV40" s="57"/>
       <c r="DW40" s="36"/>
@@ -27489,17 +27533,17 @@
       <c r="EE40" s="54"/>
       <c r="EF40" s="36" t="n">
         <f aca="false">SUM(DU40:EE40)</f>
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="EG40" s="54"/>
       <c r="EH40" s="36" t="n">
         <f aca="false">-[1]HPfinance!$E$2</f>
-        <v>-0</v>
+        <v>-20000</v>
       </c>
       <c r="EI40" s="54"/>
       <c r="EJ40" s="36" t="n">
         <f aca="false">SUM(EF40:EH40)</f>
-        <v>0</v>
+        <v>-45000</v>
       </c>
       <c r="EK40" s="54"/>
     </row>
@@ -27836,7 +27880,7 @@
       <c r="C43" s="56"/>
       <c r="D43" s="36" t="n">
         <f aca="false">-OpenAccounts!E34</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="E43" s="57"/>
       <c r="F43" s="36"/>
@@ -27849,7 +27893,7 @@
       <c r="N43" s="57"/>
       <c r="O43" s="36" t="n">
         <f aca="false">SUM(D43:N43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="P43" s="57"/>
       <c r="Q43" s="36"/>
@@ -27863,7 +27907,7 @@
       <c r="Y43" s="54"/>
       <c r="Z43" s="36" t="n">
         <f aca="false">SUM(O43:Y43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="AA43" s="57"/>
       <c r="AB43" s="36"/>
@@ -27877,7 +27921,7 @@
       <c r="AJ43" s="54"/>
       <c r="AK43" s="36" t="n">
         <f aca="false">SUM(Z43:AJ43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="AL43" s="57"/>
       <c r="AM43" s="36"/>
@@ -27891,7 +27935,7 @@
       <c r="AU43" s="54"/>
       <c r="AV43" s="36" t="n">
         <f aca="false">SUM(AK43:AU43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="AW43" s="57"/>
       <c r="AX43" s="36"/>
@@ -27905,7 +27949,7 @@
       <c r="BF43" s="54"/>
       <c r="BG43" s="36" t="n">
         <f aca="false">SUM(AV43:BF43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="BH43" s="57"/>
       <c r="BI43" s="36"/>
@@ -27919,7 +27963,7 @@
       <c r="BQ43" s="54"/>
       <c r="BR43" s="36" t="n">
         <f aca="false">SUM(BG43:BQ43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="BS43" s="57"/>
       <c r="BT43" s="36"/>
@@ -27933,7 +27977,7 @@
       <c r="CB43" s="54"/>
       <c r="CC43" s="36" t="n">
         <f aca="false">SUM(BR43:CB43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="CD43" s="57"/>
       <c r="CE43" s="36"/>
@@ -27947,7 +27991,7 @@
       <c r="CM43" s="54"/>
       <c r="CN43" s="36" t="n">
         <f aca="false">SUM(CC43:CM43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="CO43" s="57"/>
       <c r="CP43" s="36"/>
@@ -27961,7 +28005,7 @@
       <c r="CX43" s="54"/>
       <c r="CY43" s="36" t="n">
         <f aca="false">SUM(CN43:CX43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="CZ43" s="57"/>
       <c r="DA43" s="36"/>
@@ -27975,7 +28019,7 @@
       <c r="DI43" s="54"/>
       <c r="DJ43" s="36" t="n">
         <f aca="false">SUM(CY43:DI43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="DK43" s="57"/>
       <c r="DL43" s="36"/>
@@ -27989,7 +28033,7 @@
       <c r="DT43" s="54"/>
       <c r="DU43" s="36" t="n">
         <f aca="false">SUM(DJ43:DT43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="DV43" s="57"/>
       <c r="DW43" s="36"/>
@@ -28003,17 +28047,17 @@
       <c r="EE43" s="54"/>
       <c r="EF43" s="36" t="n">
         <f aca="false">SUM(DU43:EE43)</f>
-        <v>-45702</v>
+        <v>-20702</v>
       </c>
       <c r="EG43" s="54"/>
       <c r="EH43" s="36" t="n">
         <f aca="false">-'PubP&amp;L'!F54</f>
-        <v>-149251.11725</v>
+        <v>-124658.624912037</v>
       </c>
       <c r="EI43" s="54"/>
       <c r="EJ43" s="36" t="n">
         <f aca="false">SUM(EF43:EH43)</f>
-        <v>-194953.11725</v>
+        <v>-145360.624912037</v>
       </c>
       <c r="EK43" s="54"/>
     </row>
@@ -28642,18 +28686,18 @@
       <c r="EC47" s="36"/>
       <c r="ED47" s="36" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>28028.7805895061</v>
+        <v>34521.272927469</v>
       </c>
       <c r="EE47" s="54"/>
       <c r="EF47" s="36" t="n">
         <f aca="false">SUM(DU47:EE47)</f>
-        <v>28028.7805895061</v>
+        <v>34521.272927469</v>
       </c>
       <c r="EG47" s="54"/>
       <c r="EI47" s="54"/>
       <c r="EJ47" s="36" t="n">
         <f aca="false">SUM(EF47:EH47)</f>
-        <v>28028.7805895061</v>
+        <v>34521.272927469</v>
       </c>
       <c r="EK47" s="54"/>
     </row>
@@ -28836,12 +28880,12 @@
       <c r="EG48" s="54"/>
       <c r="EH48" s="36" t="n">
         <f aca="false">[8]Boardmeeting!$E$4</f>
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="EI48" s="54"/>
       <c r="EJ48" s="36" t="n">
         <f aca="false">SUM(EF48:EH48)</f>
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="EK48" s="54"/>
     </row>
@@ -29022,12 +29066,12 @@
       <c r="EG49" s="54"/>
       <c r="EH49" s="36" t="n">
         <f aca="false">'PubP&amp;L'!F54</f>
-        <v>149251.11725</v>
+        <v>124658.624912037</v>
       </c>
       <c r="EI49" s="54"/>
       <c r="EJ49" s="36" t="n">
         <f aca="false">SUM(EF49:EH49)</f>
-        <v>149251.11725</v>
+        <v>124658.624912037</v>
       </c>
       <c r="EK49" s="54"/>
     </row>
@@ -31027,12 +31071,12 @@
       <c r="L60" s="36"/>
       <c r="M60" s="36" t="n">
         <f aca="false">-(Stock!$F$8-Stock!$L$8-Stock!$R$8-Stock!$X$8+Stock!$Z$8)</f>
-        <v>-0</v>
+        <v>259.999999999999</v>
       </c>
       <c r="N60" s="57"/>
       <c r="O60" s="36" t="n">
         <f aca="false">SUM(D60:N60)</f>
-        <v>500</v>
+        <v>759.999999999999</v>
       </c>
       <c r="P60" s="57"/>
       <c r="Q60" s="36"/>
@@ -31047,12 +31091,12 @@
       <c r="W60" s="36"/>
       <c r="X60" s="36" t="n">
         <f aca="false">-(Stock!$F$10-Stock!$L$10-Stock!$R$10-Stock!$X$10+Stock!$Z$10)</f>
-        <v>-0</v>
+        <v>168.999999999999</v>
       </c>
       <c r="Y60" s="54"/>
       <c r="Z60" s="36" t="n">
         <f aca="false">SUM(O60:Y60)</f>
-        <v>1100</v>
+        <v>1529</v>
       </c>
       <c r="AA60" s="57"/>
       <c r="AB60" s="36"/>
@@ -31067,12 +31111,12 @@
       <c r="AH60" s="36"/>
       <c r="AI60" s="36" t="n">
         <f aca="false">-(Stock!$F$12-Stock!$L$12-Stock!$R$12-Stock!$X$12+Stock!$Z$12)</f>
-        <v>-0</v>
+        <v>495.999999999999</v>
       </c>
       <c r="AJ60" s="54"/>
       <c r="AK60" s="36" t="n">
         <f aca="false">SUM(Z60:AJ60)</f>
-        <v>1400</v>
+        <v>2325</v>
       </c>
       <c r="AL60" s="57"/>
       <c r="AM60" s="36"/>
@@ -31087,12 +31131,12 @@
       <c r="AS60" s="36"/>
       <c r="AT60" s="36" t="n">
         <f aca="false">-(Stock!$F$14-Stock!$L$14-Stock!$R$14-Stock!$X$14+Stock!$Z$14)</f>
-        <v>-0</v>
+        <v>168.999999999999</v>
       </c>
       <c r="AU60" s="54"/>
       <c r="AV60" s="36" t="n">
         <f aca="false">SUM(AK60:AU60)</f>
-        <v>2000</v>
+        <v>3094</v>
       </c>
       <c r="AW60" s="57"/>
       <c r="AX60" s="36"/>
@@ -31107,12 +31151,12 @@
       <c r="BD60" s="36"/>
       <c r="BE60" s="36" t="n">
         <f aca="false">-(Stock!$F$16-Stock!$L$16-Stock!$R$16-Stock!$X$16+Stock!$Z$16)</f>
-        <v>-0</v>
+        <v>363.999999999999</v>
       </c>
       <c r="BF60" s="54"/>
       <c r="BG60" s="36" t="n">
         <f aca="false">SUM(AV60:BF60)</f>
-        <v>2450</v>
+        <v>3908</v>
       </c>
       <c r="BH60" s="57"/>
       <c r="BI60" s="36"/>
@@ -31127,12 +31171,12 @@
       <c r="BO60" s="36"/>
       <c r="BP60" s="36" t="n">
         <f aca="false">-(Stock!$F$18-Stock!$L$18-Stock!$R$18-Stock!$X$18+Stock!$Z$18)</f>
-        <v>-0</v>
+        <v>550.999999999999</v>
       </c>
       <c r="BQ60" s="54"/>
       <c r="BR60" s="36" t="n">
         <f aca="false">SUM(BG60:BQ60)</f>
-        <v>2650</v>
+        <v>4658.99999999999</v>
       </c>
       <c r="BS60" s="57"/>
       <c r="BT60" s="36"/>
@@ -31147,12 +31191,12 @@
       <c r="BZ60" s="36"/>
       <c r="CA60" s="36" t="n">
         <f aca="false">-(Stock!$F$20-Stock!$L$20-Stock!$R$20-Stock!$X$20+Stock!$Z$20)</f>
-        <v>-0</v>
+        <v>413.999999999999</v>
       </c>
       <c r="CB60" s="54"/>
       <c r="CC60" s="36" t="n">
         <f aca="false">SUM(BR60:CB60)</f>
-        <v>3050</v>
+        <v>5472.99999999999</v>
       </c>
       <c r="CD60" s="57"/>
       <c r="CE60" s="36"/>
@@ -31167,12 +31211,12 @@
       <c r="CK60" s="36"/>
       <c r="CL60" s="36" t="n">
         <f aca="false">-(Stock!$F$22-Stock!$L$22-Stock!$R$22-Stock!$X$22+Stock!$Z$22)</f>
-        <v>-0</v>
+        <v>68.999999999999</v>
       </c>
       <c r="CM60" s="54"/>
       <c r="CN60" s="36" t="n">
         <f aca="false">SUM(CC60:CM60)</f>
-        <v>3750</v>
+        <v>6241.99999999999</v>
       </c>
       <c r="CO60" s="57"/>
       <c r="CP60" s="36"/>
@@ -31187,12 +31231,12 @@
       <c r="CV60" s="36"/>
       <c r="CW60" s="36" t="n">
         <f aca="false">-(Stock!$F$24-Stock!$L$24-Stock!$R$24-Stock!$X$24+Stock!$Z$24)</f>
-        <v>-0</v>
+        <v>395.999999999999</v>
       </c>
       <c r="CX60" s="54"/>
       <c r="CY60" s="36" t="n">
         <f aca="false">SUM(CN60:CX60)</f>
-        <v>4150</v>
+        <v>7037.99999999999</v>
       </c>
       <c r="CZ60" s="57"/>
       <c r="DA60" s="36"/>
@@ -31207,12 +31251,12 @@
       <c r="DG60" s="36"/>
       <c r="DH60" s="36" t="n">
         <f aca="false">-(Stock!$F$26-Stock!$L$26-Stock!$R$26-Stock!$X$26+Stock!$Z$26)</f>
-        <v>-0</v>
+        <v>268.999999999999</v>
       </c>
       <c r="DI60" s="54"/>
       <c r="DJ60" s="36" t="n">
         <f aca="false">SUM(CY60:DI60)</f>
-        <v>4650</v>
+        <v>7806.99999999999</v>
       </c>
       <c r="DK60" s="57"/>
       <c r="DL60" s="36"/>
@@ -31227,12 +31271,12 @@
       <c r="DR60" s="36"/>
       <c r="DS60" s="36" t="n">
         <f aca="false">-(Stock!$F$28-Stock!$L$28-Stock!$R$28-Stock!$X$28+Stock!$Z$28)</f>
-        <v>-0</v>
+        <v>239.999999999999</v>
       </c>
       <c r="DT60" s="54"/>
       <c r="DU60" s="36" t="n">
         <f aca="false">SUM(DJ60:DT60)</f>
-        <v>5200</v>
+        <v>8596.99999999999</v>
       </c>
       <c r="DV60" s="57"/>
       <c r="DW60" s="36"/>
@@ -31247,7 +31291,7 @@
       <c r="EC60" s="36"/>
       <c r="ED60" s="36" t="n">
         <f aca="false">-(Stock!$F$30-Stock!$L$30-Stock!$R$30-Stock!$X$30+Stock!$Z$30)</f>
-        <v>4000</v>
+        <v>603.000000000014</v>
       </c>
       <c r="EE60" s="54"/>
       <c r="EF60" s="36" t="n">
@@ -36229,7 +36273,7 @@
       </c>
       <c r="AE83" s="36" t="n">
         <f aca="false">[5]Dec!$AD$1</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AF83" s="36" t="n">
         <f aca="false">[6]Dec!$AD$1</f>
@@ -36244,7 +36288,7 @@
       <c r="AJ83" s="54"/>
       <c r="AK83" s="36" t="n">
         <f aca="false">SUM(Z83:AJ83)</f>
-        <v>310</v>
+        <v>2310</v>
       </c>
       <c r="AL83" s="57"/>
       <c r="AM83" s="36"/>
@@ -36270,7 +36314,7 @@
       <c r="AU83" s="54"/>
       <c r="AV83" s="36" t="n">
         <f aca="false">SUM(AK83:AU83)</f>
-        <v>310</v>
+        <v>2310</v>
       </c>
       <c r="AW83" s="57"/>
       <c r="AX83" s="36"/>
@@ -36296,7 +36340,7 @@
       <c r="BF83" s="54"/>
       <c r="BG83" s="36" t="n">
         <f aca="false">SUM(AV83:BF83)</f>
-        <v>310</v>
+        <v>2310</v>
       </c>
       <c r="BH83" s="57"/>
       <c r="BI83" s="36"/>
@@ -36307,7 +36351,7 @@
       </c>
       <c r="BL83" s="36" t="n">
         <f aca="false">[5]Mar!$AD$1</f>
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="BM83" s="36" t="n">
         <f aca="false">[6]Mar!$AD$1</f>
@@ -36322,7 +36366,7 @@
       <c r="BQ83" s="54"/>
       <c r="BR83" s="36" t="n">
         <f aca="false">SUM(BG83:BQ83)</f>
-        <v>518</v>
+        <v>3618</v>
       </c>
       <c r="BS83" s="57"/>
       <c r="BT83" s="36"/>
@@ -36348,7 +36392,7 @@
       <c r="CB83" s="54"/>
       <c r="CC83" s="36" t="n">
         <f aca="false">SUM(BR83:CB83)</f>
-        <v>518</v>
+        <v>3618</v>
       </c>
       <c r="CD83" s="57"/>
       <c r="CE83" s="36"/>
@@ -36374,7 +36418,7 @@
       <c r="CM83" s="54"/>
       <c r="CN83" s="36" t="n">
         <f aca="false">SUM(CC83:CM83)</f>
-        <v>543</v>
+        <v>3643</v>
       </c>
       <c r="CO83" s="57"/>
       <c r="CP83" s="36"/>
@@ -36400,7 +36444,7 @@
       <c r="CX83" s="54"/>
       <c r="CY83" s="36" t="n">
         <f aca="false">SUM(CN83:CX83)</f>
-        <v>710</v>
+        <v>3810</v>
       </c>
       <c r="CZ83" s="57"/>
       <c r="DA83" s="36"/>
@@ -36426,7 +36470,7 @@
       <c r="DI83" s="54"/>
       <c r="DJ83" s="36" t="n">
         <f aca="false">SUM(CY83:DI83)</f>
-        <v>710</v>
+        <v>3810</v>
       </c>
       <c r="DK83" s="57"/>
       <c r="DL83" s="36"/>
@@ -36452,7 +36496,7 @@
       <c r="DT83" s="54"/>
       <c r="DU83" s="36" t="n">
         <f aca="false">SUM(DJ83:DT83)</f>
-        <v>710</v>
+        <v>3810</v>
       </c>
       <c r="DV83" s="57"/>
       <c r="DW83" s="36"/>
@@ -36478,13 +36522,13 @@
       <c r="EE83" s="54"/>
       <c r="EF83" s="36" t="n">
         <f aca="false">SUM(DU83:EE83)</f>
-        <v>835</v>
+        <v>3935</v>
       </c>
       <c r="EG83" s="54"/>
       <c r="EI83" s="54"/>
       <c r="EJ83" s="36" t="n">
         <f aca="false">SUM(EF83:EH83)</f>
-        <v>835</v>
+        <v>3935</v>
       </c>
       <c r="EK83" s="54"/>
     </row>
@@ -38130,7 +38174,7 @@
       <c r="N91" s="54"/>
       <c r="O91" s="36" t="n">
         <f aca="false">SUM(O4:O90)</f>
-        <v>3.09228198602796E-011</v>
+        <v>3.44471118296497E-011</v>
       </c>
       <c r="P91" s="54"/>
       <c r="Q91" s="36" t="n">
@@ -38143,7 +38187,7 @@
       </c>
       <c r="S91" s="36" t="n">
         <f aca="false">SUM(S4:S90)</f>
-        <v>0</v>
+        <v>-9.09494701772928E-013</v>
       </c>
       <c r="T91" s="36" t="n">
         <f aca="false">SUM(T4:T90)</f>
@@ -38168,7 +38212,7 @@
       <c r="Y91" s="54"/>
       <c r="Z91" s="36" t="n">
         <f aca="false">SUM(Z4:Z90)</f>
-        <v>6.24140739091672E-011</v>
+        <v>6.94626578479074E-011</v>
       </c>
       <c r="AA91" s="54"/>
       <c r="AB91" s="36" t="n">
@@ -38206,7 +38250,7 @@
       <c r="AJ91" s="54"/>
       <c r="AK91" s="36" t="n">
         <f aca="false">SUM(AK4:AK90)</f>
-        <v>9.7998054116033E-011</v>
+        <v>1.08684616861865E-010</v>
       </c>
       <c r="AL91" s="54"/>
       <c r="AM91" s="36" t="n">
@@ -38244,7 +38288,7 @@
       <c r="AU91" s="54"/>
       <c r="AV91" s="36" t="n">
         <f aca="false">SUM(AV4:AV90)</f>
-        <v>1.28466126625426E-010</v>
+        <v>1.4210854715202E-010</v>
       </c>
       <c r="AW91" s="54"/>
       <c r="AX91" s="36" t="n">
@@ -38282,7 +38326,7 @@
       <c r="BF91" s="54"/>
       <c r="BG91" s="36" t="n">
         <f aca="false">SUM(BG4:BG90)</f>
-        <v>1.69166014529765E-010</v>
+        <v>1.90993887372315E-010</v>
       </c>
       <c r="BH91" s="54"/>
       <c r="BI91" s="36" t="n">
@@ -38320,7 +38364,7 @@
       <c r="BQ91" s="54"/>
       <c r="BR91" s="36" t="n">
         <f aca="false">SUM(BR4:BR90)</f>
-        <v>1.98951966012828E-010</v>
+        <v>2.09865902434103E-010</v>
       </c>
       <c r="BS91" s="54"/>
       <c r="BT91" s="36" t="n">
@@ -38333,7 +38377,7 @@
       </c>
       <c r="BV91" s="36" t="n">
         <f aca="false">SUM(BV4:BV90)</f>
-        <v>0</v>
+        <v>2.72848410531878E-012</v>
       </c>
       <c r="BW91" s="36" t="n">
         <f aca="false">SUM(BW4:BW90)</f>
@@ -38358,7 +38402,7 @@
       <c r="CB91" s="54"/>
       <c r="CC91" s="36" t="n">
         <f aca="false">SUM(CC4:CC90)</f>
-        <v>2.43517206399702E-010</v>
+        <v>2.44426701101474E-010</v>
       </c>
       <c r="CD91" s="54"/>
       <c r="CE91" s="36" t="n">
@@ -38396,7 +38440,7 @@
       <c r="CM91" s="54"/>
       <c r="CN91" s="36" t="n">
         <f aca="false">SUM(CN4:CN90)</f>
-        <v>2.56477505899966E-010</v>
+        <v>2.50111042987555E-010</v>
       </c>
       <c r="CO91" s="54"/>
       <c r="CP91" s="36" t="n">
@@ -38409,7 +38453,7 @@
       </c>
       <c r="CR91" s="36" t="n">
         <f aca="false">SUM(CR4:CR90)</f>
-        <v>0</v>
+        <v>-9.09494701772928E-013</v>
       </c>
       <c r="CS91" s="36" t="n">
         <f aca="false">SUM(CS4:CS90)</f>
@@ -38434,7 +38478,7 @@
       <c r="CX91" s="54"/>
       <c r="CY91" s="36" t="n">
         <f aca="false">SUM(CY4:CY90)</f>
-        <v>2.73303157882765E-010</v>
+        <v>2.56022758549079E-010</v>
       </c>
       <c r="CZ91" s="54"/>
       <c r="DA91" s="36" t="n">
@@ -38472,7 +38516,7 @@
       <c r="DI91" s="54"/>
       <c r="DJ91" s="36" t="n">
         <f aca="false">SUM(DJ4:DJ90)</f>
-        <v>2.86945578409359E-010</v>
+        <v>2.58751242654398E-010</v>
       </c>
       <c r="DK91" s="54"/>
       <c r="DL91" s="36" t="n">
@@ -38510,7 +38554,7 @@
       <c r="DT91" s="54"/>
       <c r="DU91" s="36" t="n">
         <f aca="false">SUM(DU4:DU90)</f>
-        <v>3.0036062526051E-010</v>
+        <v>2.67618815996684E-010</v>
       </c>
       <c r="DV91" s="54"/>
       <c r="DW91" s="36" t="n">
@@ -38548,7 +38592,7 @@
       <c r="EE91" s="54"/>
       <c r="EF91" s="36" t="n">
         <f aca="false">SUM(EF4:EF90)</f>
-        <v>3.16504156216979E-010</v>
+        <v>2.72848410531878E-010</v>
       </c>
       <c r="EG91" s="54"/>
       <c r="EH91" s="36" t="n">
@@ -38558,7 +38602,7 @@
       <c r="EI91" s="54"/>
       <c r="EJ91" s="36" t="n">
         <f aca="false">SUM(EJ4:EJ90)</f>
-        <v>3.19232640322298E-010</v>
+        <v>2.79214873444289E-010</v>
       </c>
       <c r="EK91" s="54"/>
     </row>
@@ -39310,51 +39354,51 @@
       </c>
       <c r="C11" s="72" t="n">
         <f aca="false">TrialBalance!O60-0</f>
-        <v>500</v>
+        <v>759.999999999999</v>
       </c>
       <c r="D11" s="72" t="n">
         <f aca="false">TrialBalance!Z60-C11</f>
-        <v>600</v>
+        <v>768.999999999999</v>
       </c>
       <c r="E11" s="72" t="n">
         <f aca="false">TrialBalance!AK60-SUM(C11:D11)</f>
-        <v>300</v>
+        <v>795.999999999999</v>
       </c>
       <c r="F11" s="72" t="n">
         <f aca="false">TrialBalance!AV60-SUM(C11:E11)</f>
-        <v>600</v>
+        <v>768.999999999999</v>
       </c>
       <c r="G11" s="72" t="n">
         <f aca="false">TrialBalance!BG60-SUM(C11:F11)</f>
-        <v>450</v>
+        <v>813.999999999999</v>
       </c>
       <c r="H11" s="72" t="n">
         <f aca="false">TrialBalance!BR60-SUM(C11:G11)</f>
-        <v>200</v>
+        <v>750.999999999999</v>
       </c>
       <c r="I11" s="72" t="n">
         <f aca="false">TrialBalance!CC60-SUM(C11:H11)</f>
-        <v>400</v>
+        <v>813.999999999999</v>
       </c>
       <c r="J11" s="72" t="n">
         <f aca="false">TrialBalance!CN60-SUM(C11:I11)</f>
-        <v>700</v>
+        <v>768.999999999999</v>
       </c>
       <c r="K11" s="72" t="n">
         <f aca="false">TrialBalance!CY60-SUM(C11:J11)</f>
-        <v>400</v>
+        <v>795.999999999999</v>
       </c>
       <c r="L11" s="72" t="n">
         <f aca="false">TrialBalance!DJ60-SUM(C11:K11)</f>
-        <v>500</v>
+        <v>768.999999999999</v>
       </c>
       <c r="M11" s="72" t="n">
         <f aca="false">TrialBalance!DU60-SUM(C11:L11)</f>
-        <v>550</v>
+        <v>789.999999999998</v>
       </c>
       <c r="N11" s="72" t="n">
         <f aca="false">TrialBalance!EF60-SUM(C11:M11)</f>
-        <v>4250</v>
+        <v>853.000000000015</v>
       </c>
       <c r="O11" s="68"/>
     </row>
@@ -39484,51 +39528,51 @@
       </c>
       <c r="C14" s="74" t="n">
         <f aca="false">SUM(C11:C13)</f>
-        <v>737.5</v>
+        <v>997.499999999999</v>
       </c>
       <c r="D14" s="71" t="n">
         <f aca="false">SUM(D11:D13)</f>
-        <v>807.5</v>
+        <v>976.499999999999</v>
       </c>
       <c r="E14" s="71" t="n">
         <f aca="false">SUM(E11:E13)</f>
-        <v>4704.16666666667</v>
+        <v>5200.16666666667</v>
       </c>
       <c r="F14" s="71" t="n">
         <f aca="false">SUM(F11:F13)</f>
-        <v>807.5</v>
+        <v>976.499999999999</v>
       </c>
       <c r="G14" s="71" t="n">
         <f aca="false">SUM(G11:G13)</f>
-        <v>687.5</v>
+        <v>1051.5</v>
       </c>
       <c r="H14" s="71" t="n">
         <f aca="false">SUM(H11:H13)</f>
-        <v>407.5</v>
+        <v>958.499999999999</v>
       </c>
       <c r="I14" s="71" t="n">
         <f aca="false">SUM(I11:I13)</f>
-        <v>637.5</v>
+        <v>1051.5</v>
       </c>
       <c r="J14" s="71" t="n">
         <f aca="false">SUM(J11:J13)</f>
-        <v>3407.5</v>
+        <v>3476.5</v>
       </c>
       <c r="K14" s="71" t="n">
         <f aca="false">SUM(K11:K13)</f>
-        <v>637.5</v>
+        <v>1033.5</v>
       </c>
       <c r="L14" s="71" t="n">
         <f aca="false">SUM(L11:L13)</f>
-        <v>707.5</v>
+        <v>976.499999999999</v>
       </c>
       <c r="M14" s="71" t="n">
         <f aca="false">SUM(M11:M13)</f>
-        <v>787.5</v>
+        <v>1027.5</v>
       </c>
       <c r="N14" s="71" t="n">
         <f aca="false">SUM(N11:N13)</f>
-        <v>4457.5</v>
+        <v>1060.50000000001</v>
       </c>
       <c r="O14" s="75"/>
     </row>
@@ -39559,51 +39603,51 @@
       </c>
       <c r="C16" s="71" t="n">
         <f aca="false">C9-C14</f>
-        <v>27095.8333333333</v>
+        <v>26835.8333333333</v>
       </c>
       <c r="D16" s="71" t="n">
         <f aca="false">D9-D14</f>
-        <v>26625.8333333333</v>
+        <v>26456.8333333333</v>
       </c>
       <c r="E16" s="71" t="n">
         <f aca="false">E9-E14</f>
-        <v>24629.1666666666</v>
+        <v>24133.1666666666</v>
       </c>
       <c r="F16" s="71" t="n">
         <f aca="false">F9-F14</f>
-        <v>27325.8333333333</v>
+        <v>27156.8333333333</v>
       </c>
       <c r="G16" s="71" t="n">
         <f aca="false">G9-G14</f>
-        <v>29329.1666666666</v>
+        <v>28965.1666666666</v>
       </c>
       <c r="H16" s="71" t="n">
         <f aca="false">H9-H14</f>
-        <v>27725.8333333333</v>
+        <v>27174.8333333333</v>
       </c>
       <c r="I16" s="71" t="n">
         <f aca="false">I9-I14</f>
-        <v>28995.8333333333</v>
+        <v>28581.8333333333</v>
       </c>
       <c r="J16" s="71" t="n">
         <f aca="false">J9-J14</f>
-        <v>26025.8333333333</v>
+        <v>25956.8333333333</v>
       </c>
       <c r="K16" s="71" t="n">
         <f aca="false">K9-K14</f>
-        <v>26695.8333333333</v>
+        <v>26299.8333333333</v>
       </c>
       <c r="L16" s="71" t="n">
         <f aca="false">L9-L14</f>
-        <v>28825.8333333333</v>
+        <v>28556.8333333333</v>
       </c>
       <c r="M16" s="71" t="n">
         <f aca="false">M9-M14</f>
-        <v>27845.8333333333</v>
+        <v>27605.8333333333</v>
       </c>
       <c r="N16" s="71" t="n">
         <f aca="false">N9-N14</f>
-        <v>21375.8333333333</v>
+        <v>24772.8333333333</v>
       </c>
       <c r="O16" s="75"/>
     </row>
@@ -40676,7 +40720,7 @@
       </c>
       <c r="B36" s="71" t="n">
         <f aca="false">SUM(C36:N36)</f>
-        <v>835</v>
+        <v>3935</v>
       </c>
       <c r="C36" s="72" t="n">
         <f aca="false">TrialBalance!O83+TrialBalance!O88+TrialBalance!O89-0</f>
@@ -40688,7 +40732,7 @@
       </c>
       <c r="E36" s="72" t="n">
         <f aca="false">TrialBalance!AK83+TrialBalance!AK88+TrialBalance!AK89-SUM(C36:D36)</f>
-        <v>250</v>
+        <v>2250</v>
       </c>
       <c r="F36" s="72" t="n">
         <f aca="false">TrialBalance!AV83+TrialBalance!AV88+TrialBalance!AV89-SUM(C36:E36)</f>
@@ -40700,7 +40744,7 @@
       </c>
       <c r="H36" s="72" t="n">
         <f aca="false">TrialBalance!BR83+TrialBalance!BR88+TrialBalance!BR89-SUM(C36:G36)</f>
-        <v>208</v>
+        <v>1308</v>
       </c>
       <c r="I36" s="72" t="n">
         <f aca="false">TrialBalance!CC83+TrialBalance!CC88+TrialBalance!CC89-SUM(C36:H36)</f>
@@ -40966,7 +41010,7 @@
       </c>
       <c r="B41" s="71" t="n">
         <f aca="false">SUM(B18:B40)</f>
-        <v>145556.275</v>
+        <v>148656.275</v>
       </c>
       <c r="C41" s="74" t="n">
         <f aca="false">SUM(C18:C40)</f>
@@ -40978,7 +41022,7 @@
       </c>
       <c r="E41" s="71" t="n">
         <f aca="false">SUM(E18:E40)</f>
-        <v>11411.2</v>
+        <v>13411.2</v>
       </c>
       <c r="F41" s="71" t="n">
         <f aca="false">SUM(F18:F40)</f>
@@ -40990,7 +41034,7 @@
       </c>
       <c r="H41" s="71" t="n">
         <f aca="false">SUM(H18:H40)</f>
-        <v>12264.2</v>
+        <v>13364.2</v>
       </c>
       <c r="I41" s="71" t="n">
         <f aca="false">SUM(I18:I40)</f>
@@ -41041,55 +41085,55 @@
       </c>
       <c r="B43" s="71" t="n">
         <f aca="false">B16-B41</f>
-        <v>176940.391666666</v>
+        <v>173840.391666666</v>
       </c>
       <c r="C43" s="71" t="n">
         <f aca="false">C16-C41</f>
-        <v>15256.0916666666</v>
+        <v>14996.0916666666</v>
       </c>
       <c r="D43" s="71" t="n">
         <f aca="false">D16-D41</f>
-        <v>15242.9666666666</v>
+        <v>15073.9666666666</v>
       </c>
       <c r="E43" s="71" t="n">
         <f aca="false">E16-E41</f>
-        <v>13217.9666666666</v>
+        <v>10721.9666666666</v>
       </c>
       <c r="F43" s="71" t="n">
         <f aca="false">F16-F41</f>
-        <v>13266.0916666666</v>
+        <v>13097.0916666666</v>
       </c>
       <c r="G43" s="71" t="n">
         <f aca="false">G16-G41</f>
-        <v>18027.7583333333</v>
+        <v>17663.7583333333</v>
       </c>
       <c r="H43" s="71" t="n">
         <f aca="false">H16-H41</f>
-        <v>15461.6333333333</v>
+        <v>13810.6333333333</v>
       </c>
       <c r="I43" s="71" t="n">
         <f aca="false">I16-I41</f>
-        <v>15477.3416666666</v>
+        <v>15063.3416666666</v>
       </c>
       <c r="J43" s="71" t="n">
         <f aca="false">J16-J41</f>
-        <v>15325.4666666666</v>
+        <v>15256.4666666666</v>
       </c>
       <c r="K43" s="71" t="n">
         <f aca="false">K16-K41</f>
-        <v>10972.2166666666</v>
+        <v>10576.2166666666</v>
       </c>
       <c r="L43" s="71" t="n">
         <f aca="false">L16-L41</f>
-        <v>17456.0916666666</v>
+        <v>17187.0916666666</v>
       </c>
       <c r="M43" s="71" t="n">
         <f aca="false">M16-M41</f>
-        <v>16651.7166666666</v>
+        <v>16411.7166666666</v>
       </c>
       <c r="N43" s="71" t="n">
         <f aca="false">N16-N41</f>
-        <v>10585.05</v>
+        <v>13982.05</v>
       </c>
       <c r="O43" s="68"/>
     </row>
@@ -41157,55 +41201,55 @@
       </c>
       <c r="B45" s="71" t="n">
         <f aca="false">B43+B44</f>
-        <v>177215.391666666</v>
+        <v>174115.391666666</v>
       </c>
       <c r="C45" s="71" t="n">
         <f aca="false">C43+C44</f>
-        <v>15256.0916666666</v>
+        <v>14996.0916666666</v>
       </c>
       <c r="D45" s="71" t="n">
         <f aca="false">D43+D44</f>
-        <v>15242.9666666666</v>
+        <v>15073.9666666666</v>
       </c>
       <c r="E45" s="71" t="n">
         <f aca="false">E43+E44</f>
-        <v>13217.9666666666</v>
+        <v>10721.9666666666</v>
       </c>
       <c r="F45" s="71" t="n">
         <f aca="false">F43+F44</f>
-        <v>13266.0916666666</v>
+        <v>13097.0916666666</v>
       </c>
       <c r="G45" s="71" t="n">
         <f aca="false">G43+G44</f>
-        <v>18027.7583333333</v>
+        <v>17663.7583333333</v>
       </c>
       <c r="H45" s="71" t="n">
         <f aca="false">H43+H44</f>
-        <v>15586.6333333333</v>
+        <v>13935.6333333333</v>
       </c>
       <c r="I45" s="71" t="n">
         <f aca="false">I43+I44</f>
-        <v>15477.3416666666</v>
+        <v>15063.3416666666</v>
       </c>
       <c r="J45" s="71" t="n">
         <f aca="false">J43+J44</f>
-        <v>15325.4666666666</v>
+        <v>15256.4666666666</v>
       </c>
       <c r="K45" s="71" t="n">
         <f aca="false">K43+K44</f>
-        <v>10972.2166666666</v>
+        <v>10576.2166666666</v>
       </c>
       <c r="L45" s="71" t="n">
         <f aca="false">L43+L44</f>
-        <v>17456.0916666666</v>
+        <v>17187.0916666666</v>
       </c>
       <c r="M45" s="71" t="n">
         <f aca="false">M43+M44</f>
-        <v>16651.7166666666</v>
+        <v>16411.7166666666</v>
       </c>
       <c r="N45" s="71" t="n">
         <f aca="false">N43+N44</f>
-        <v>10735.05</v>
+        <v>14132.05</v>
       </c>
       <c r="O45" s="68"/>
     </row>
@@ -41509,11 +41553,11 @@
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="86" t="n">
         <f aca="false">OpenAccounts!E48</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="B14" s="86" t="n">
         <f aca="false">A12+A13-A14</f>
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="C14" s="101" t="s">
         <v>224</v>
@@ -41563,7 +41607,7 @@
       <c r="A16" s="103"/>
       <c r="B16" s="104" t="n">
         <f aca="false">SUM(B14:B15)</f>
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="C16" s="105" t="s">
         <v>67</v>
@@ -41597,7 +41641,7 @@
       <c r="A18" s="103"/>
       <c r="B18" s="104" t="n">
         <f aca="false">B9-B16</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="C18" s="105" t="s">
         <v>68</v>
@@ -42033,7 +42077,7 @@
       <c r="D39" s="88"/>
       <c r="E39" s="86" t="n">
         <f aca="false">TrialBalance!EJ83+TrialBalance!EJ88+TrialBalance!EJ89</f>
-        <v>835</v>
+        <v>3935</v>
       </c>
       <c r="H39" s="89"/>
       <c r="I39" s="89"/>
@@ -42140,7 +42184,7 @@
       <c r="E44" s="103"/>
       <c r="F44" s="104" t="n">
         <f aca="false">SUM(E21:E43)</f>
-        <v>145556.275</v>
+        <v>148656.275</v>
       </c>
       <c r="H44" s="89"/>
       <c r="I44" s="89"/>
@@ -42167,7 +42211,7 @@
       <c r="A46" s="103"/>
       <c r="B46" s="104" t="n">
         <f aca="false">B18-B44</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="C46" s="109" t="s">
         <v>93</v>
@@ -42176,7 +42220,7 @@
       <c r="E46" s="103"/>
       <c r="F46" s="104" t="n">
         <f aca="false">F18-F44</f>
-        <v>176940.391666666</v>
+        <v>173840.391666666</v>
       </c>
       <c r="H46" s="89"/>
       <c r="I46" s="89"/>
@@ -42222,7 +42266,7 @@
       <c r="A49" s="103"/>
       <c r="B49" s="104" t="n">
         <f aca="false">B46+B48</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="C49" s="106" t="s">
         <v>95</v>
@@ -42231,7 +42275,7 @@
       <c r="E49" s="103"/>
       <c r="F49" s="104" t="n">
         <f aca="false">F46+F48</f>
-        <v>177279.897839506</v>
+        <v>174179.897839506</v>
       </c>
       <c r="H49" s="89"/>
       <c r="I49" s="89"/>
@@ -42252,7 +42296,7 @@
       <c r="D50" s="101"/>
       <c r="F50" s="86" t="n">
         <f aca="false">TrialBalance!EJ47</f>
-        <v>28028.7805895061</v>
+        <v>34521.272927469</v>
       </c>
       <c r="H50" s="89"/>
       <c r="I50" s="89"/>
@@ -42266,7 +42310,7 @@
       <c r="A51" s="103"/>
       <c r="B51" s="104" t="n">
         <f aca="false">B49-B50</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="C51" s="106" t="s">
         <v>97</v>
@@ -42275,7 +42319,7 @@
       <c r="E51" s="103"/>
       <c r="F51" s="104" t="n">
         <f aca="false">F49-F50</f>
-        <v>149251.11725</v>
+        <v>139658.624912037</v>
       </c>
       <c r="H51" s="89"/>
       <c r="I51" s="89"/>
@@ -42296,7 +42340,7 @@
       <c r="D52" s="101"/>
       <c r="F52" s="86" t="n">
         <f aca="false">TrialBalance!EJ48</f>
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H52" s="89"/>
       <c r="I52" s="89"/>
@@ -42325,7 +42369,7 @@
       </c>
       <c r="B54" s="104" t="n">
         <f aca="false">B51-B52</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="C54" s="106" t="s">
         <v>99</v>
@@ -42336,7 +42380,7 @@
       </c>
       <c r="F54" s="104" t="n">
         <f aca="false">F51-F52</f>
-        <v>149251.11725</v>
+        <v>124658.624912037</v>
       </c>
       <c r="H54" s="89"/>
       <c r="I54" s="89"/>
@@ -42528,7 +42572,7 @@
       </c>
       <c r="E12" s="119" t="n">
         <f aca="false">IF(SUM(TrialBalance!EJ22:EJ24)&gt;0,SUM(TrialBalance!EJ22:EJ24)+TrialBalance!EJ25+TrialBalance!EJ26,TrialBalance!EJ25)</f>
-        <v>250544</v>
+        <v>192995.43</v>
       </c>
       <c r="F12" s="115"/>
     </row>
@@ -42544,7 +42588,7 @@
       <c r="D13" s="117"/>
       <c r="E13" s="116" t="n">
         <f aca="false">SUM(E10:E12)</f>
-        <v>266944</v>
+        <v>209395.43</v>
       </c>
       <c r="F13" s="118"/>
     </row>
@@ -42575,7 +42619,7 @@
       </c>
       <c r="E16" s="115" t="n">
         <f aca="false">-SUM(TrialBalance!EJ28:EJ31)</f>
-        <v>13432.25</v>
+        <v>-11567.75</v>
       </c>
       <c r="F16" s="115"/>
     </row>
@@ -42590,7 +42634,7 @@
       </c>
       <c r="E17" s="115" t="n">
         <f aca="false">-TrialBalance!EJ35</f>
-        <v>32464.2744166666</v>
+        <v>38956.7667546295</v>
       </c>
       <c r="F17" s="115"/>
     </row>
@@ -42605,7 +42649,7 @@
       </c>
       <c r="E18" s="115" t="n">
         <f aca="false">-SUM(TrialBalance!EJ32:EJ34)</f>
-        <v>43984.3583333334</v>
+        <v>9535.78833333335</v>
       </c>
       <c r="F18" s="115"/>
     </row>
@@ -42638,7 +42682,7 @@
       <c r="D20" s="117"/>
       <c r="E20" s="116" t="n">
         <f aca="false">SUM(E16:E19)</f>
-        <v>89880.88275</v>
+        <v>36924.8050879629</v>
       </c>
       <c r="F20" s="118"/>
       <c r="G20" s="120"/>
@@ -42665,7 +42709,7 @@
       <c r="E22" s="118"/>
       <c r="F22" s="116" t="n">
         <f aca="false">E13-E20</f>
-        <v>177063.11725</v>
+        <v>172470.624912037</v>
       </c>
       <c r="G22" s="120"/>
     </row>
@@ -42718,7 +42762,7 @@
       <c r="E26" s="118"/>
       <c r="F26" s="116" t="n">
         <f aca="false">SUM(F6:F25)</f>
-        <v>208053.11725</v>
+        <v>203460.624912037</v>
       </c>
       <c r="G26" s="120"/>
     </row>
@@ -42760,7 +42804,7 @@
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="115" t="n">
         <f aca="false">-TrialBalance!D40</f>
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="B30" s="118"/>
       <c r="C30" s="117" t="s">
@@ -42769,7 +42813,7 @@
       <c r="D30" s="117"/>
       <c r="E30" s="115" t="n">
         <f aca="false">-TrialBalance!EJ40</f>
-        <v>-0</v>
+        <v>45000</v>
       </c>
       <c r="F30" s="118"/>
       <c r="G30" s="120"/>
@@ -42779,12 +42823,12 @@
       <c r="A31" s="115"/>
       <c r="B31" s="116" t="n">
         <f aca="false">SUM(A29:A30)</f>
-        <v>20000</v>
+        <v>45000</v>
       </c>
       <c r="E31" s="115"/>
       <c r="F31" s="116" t="n">
         <f aca="false">SUM(E29:E30)</f>
-        <v>13000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="32" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42803,7 +42847,7 @@
       </c>
       <c r="B33" s="116" t="n">
         <f aca="false">B26-B31</f>
-        <v>45802</v>
+        <v>20802</v>
       </c>
       <c r="C33" s="117" t="s">
         <v>234</v>
@@ -42814,7 +42858,7 @@
       </c>
       <c r="F33" s="116" t="n">
         <f aca="false">F26-F31</f>
-        <v>195053.11725</v>
+        <v>145460.624912037</v>
       </c>
       <c r="G33" s="120"/>
     </row>
@@ -42855,7 +42899,7 @@
       <c r="A37" s="115"/>
       <c r="B37" s="115" t="n">
         <f aca="false">-TrialBalance!D43</f>
-        <v>45702</v>
+        <v>20702</v>
       </c>
       <c r="C37" s="88" t="s">
         <v>57</v>
@@ -42864,7 +42908,7 @@
       <c r="E37" s="115"/>
       <c r="F37" s="115" t="n">
         <f aca="false">-TrialBalance!EJ43</f>
-        <v>194953.11725</v>
+        <v>145360.624912037</v>
       </c>
       <c r="G37" s="87"/>
       <c r="O37" s="87"/>
@@ -42893,7 +42937,7 @@
       </c>
       <c r="B39" s="116" t="n">
         <f aca="false">SUM(B36:B38)</f>
-        <v>45802</v>
+        <v>20802</v>
       </c>
       <c r="C39" s="117" t="s">
         <v>236</v>
@@ -42904,7 +42948,7 @@
       </c>
       <c r="F39" s="116" t="n">
         <f aca="false">SUM(F36:F38)</f>
-        <v>195053.11725</v>
+        <v>145460.624912037</v>
       </c>
       <c r="G39" s="120"/>
     </row>
@@ -43646,7 +43690,7 @@
       <c r="E38" s="137"/>
       <c r="F38" s="136" t="n">
         <f aca="false">[8]Boardmeeting!$E$4</f>
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="G38" s="138"/>
     </row>
@@ -43666,7 +43710,7 @@
       <c r="C41" s="137"/>
       <c r="D41" s="136" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>28028.7805895061</v>
+        <v>34521.272927469</v>
       </c>
       <c r="G41" s="89"/>
     </row>
@@ -44110,7 +44154,7 @@
       <c r="C94" s="160"/>
       <c r="D94" s="165" t="n">
         <f aca="false">[8]Boardmeeting!$E$4</f>
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E94" s="170" t="s">
         <v>307</v>
@@ -44152,7 +44196,7 @@
     <row r="97" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="172" t="str">
         <f aca="false">IF([8]RegisterofMembers!$A$3&gt;0,[8]RegisterofMembers!$A$3," ")</f>
-        <v> </v>
+        <v>Carol Smith</v>
       </c>
       <c r="B97" s="172"/>
       <c r="C97" s="172"/>
@@ -44162,7 +44206,7 @@
       <c r="E97" s="147"/>
       <c r="F97" s="173" t="n">
         <f aca="false">[8]RegisterofMembers!$G$3</f>
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G97" s="174" t="s">
         <v>311</v>
@@ -44176,7 +44220,7 @@
     <row r="98" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="172" t="str">
         <f aca="false">IF([8]RegisterofMembers!$A$4&gt;0,[8]RegisterofMembers!$A$4," ")</f>
-        <v> </v>
+        <v>David Brown</v>
       </c>
       <c r="B98" s="172"/>
       <c r="C98" s="172"/>
@@ -44186,7 +44230,7 @@
       <c r="E98" s="147"/>
       <c r="F98" s="173" t="n">
         <f aca="false">[8]RegisterofMembers!$G$4</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G98" s="174" t="s">
         <v>311</v>
@@ -44631,13 +44675,13 @@
       </c>
       <c r="H5" s="189" t="n">
         <f aca="false">Admin!N7</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="I5" s="189"/>
       <c r="J5" s="178"/>
       <c r="K5" s="191" t="n">
         <f aca="false">'PubP&amp;L'!F46</f>
-        <v>176940.391666666</v>
+        <v>173840.391666666</v>
       </c>
       <c r="L5" s="185"/>
     </row>
@@ -44755,7 +44799,7 @@
       <c r="J12" s="178"/>
       <c r="K12" s="191" t="n">
         <f aca="false">K5+K10</f>
-        <v>191180.391666666</v>
+        <v>188080.391666666</v>
       </c>
       <c r="L12" s="185"/>
     </row>
@@ -44802,7 +44846,7 @@
       </c>
       <c r="F15" s="198" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="G15" s="199" t="n">
         <f aca="false">Admin!G5</f>
@@ -44832,7 +44876,7 @@
       </c>
       <c r="F16" s="198" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="G16" s="199" t="n">
         <f aca="false">Admin!G6</f>
@@ -44889,7 +44933,7 @@
       </c>
       <c r="F18" s="198" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="G18" s="204"/>
       <c r="H18" s="205"/>
@@ -44965,7 +45009,7 @@
       <c r="J22" s="178"/>
       <c r="K22" s="209" t="n">
         <f aca="false">K12-K20</f>
-        <v>147180.391666666</v>
+        <v>144080.391666666</v>
       </c>
       <c r="L22" s="185"/>
     </row>
@@ -45058,7 +45102,7 @@
       <c r="D28" s="188"/>
       <c r="E28" s="213" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="F28" s="213"/>
       <c r="G28" s="178"/>
@@ -45067,7 +45111,7 @@
       <c r="J28" s="178"/>
       <c r="K28" s="209" t="n">
         <f aca="false">K22+K24-K26</f>
-        <v>147519.897839506</v>
+        <v>144419.897839506</v>
       </c>
       <c r="L28" s="185"/>
     </row>
@@ -45146,7 +45190,7 @@
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="221" t="n">
         <f aca="false">D33-C33+1</f>
-        <v>365</v>
+        <v>182</v>
       </c>
       <c r="B33" s="204" t="s">
         <v>46</v>
@@ -45157,7 +45201,7 @@
       </c>
       <c r="D33" s="222" t="n">
         <f aca="false">Admin!N6</f>
-        <v>46660</v>
+        <v>46477</v>
       </c>
       <c r="E33" s="223" t="n">
         <f aca="false">Admin!K6</f>
@@ -45165,36 +45209,42 @@
       </c>
       <c r="F33" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A33/A35,0)</f>
-        <v>73659.0461168531</v>
+        <v>72012.1134432604</v>
       </c>
       <c r="G33" s="224" t="n">
-        <f aca="false">Admin!P6</f>
-        <v>19</v>
+        <f aca="false">IF(F33&lt;=Admin!$P$12*A33/A35,Admin!P6,Admin!$P$8)</f>
+        <v>25</v>
       </c>
       <c r="H33" s="224"/>
       <c r="I33" s="225" t="n">
+        <f aca="false">J33-L33</f>
+        <v>17213.3470487654</v>
+      </c>
+      <c r="J33" s="226" t="n">
         <f aca="false">F33*G33/100</f>
-        <v>13995.2187622021</v>
-      </c>
-      <c r="J33" s="226"/>
+        <v>18003.0283608151</v>
+      </c>
       <c r="K33" s="178"/>
-      <c r="L33" s="177"/>
+      <c r="L33" s="177" t="n">
+        <f aca="false">IF(AND(F33&gt;Admin!$P$12*A33/A35,F33&lt;Admin!$P$13*A33/A35),(Admin!$P$13*A33/A35-F33)*Admin!$P$9,0)</f>
+        <v>789.681312049724</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="221" t="n">
-        <f aca="false">D34-C34+1</f>
-        <v>366</v>
+        <f aca="false">MAX(0,D34-C34+1)</f>
+        <v>183</v>
       </c>
       <c r="B34" s="204" t="s">
         <v>46</v>
       </c>
       <c r="C34" s="222" t="n">
         <f aca="false">Admin!L7</f>
-        <v>46661</v>
+        <v>46478</v>
       </c>
       <c r="D34" s="222" t="n">
         <f aca="false">Admin!N7</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="E34" s="223" t="n">
         <f aca="false">Admin!K7</f>
@@ -45202,25 +45252,31 @@
       </c>
       <c r="F34" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A34/A35,0)</f>
-        <v>73860.8517226527</v>
+        <v>72407.7843962454</v>
       </c>
       <c r="G34" s="224" t="n">
-        <f aca="false">Admin!P7</f>
-        <v>19</v>
+        <f aca="false">IF(F34&lt;=Admin!$P$12*A34/A35,Admin!P7,Admin!$P$8)</f>
+        <v>25</v>
       </c>
       <c r="H34" s="224"/>
       <c r="I34" s="225" t="n">
+        <f aca="false">J34-L34</f>
+        <v>17307.9258787037</v>
+      </c>
+      <c r="J34" s="226" t="n">
         <f aca="false">F34*G34/100</f>
-        <v>14033.561827304</v>
-      </c>
-      <c r="J34" s="226"/>
+        <v>18101.9460990613</v>
+      </c>
       <c r="K34" s="178"/>
-      <c r="L34" s="177"/>
+      <c r="L34" s="177" t="n">
+        <f aca="false">IF(AND(F34&gt;Admin!$P$12*A34/A35,F34&lt;Admin!$P$13*A34/A35),(Admin!$P$13*A34/A35-F34)*Admin!$P$9,0)</f>
+        <v>794.020220357689</v>
+      </c>
     </row>
     <row r="35" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="221" t="n">
         <f aca="false">D34-C33+1</f>
-        <v>731</v>
+        <v>365</v>
       </c>
       <c r="B35" s="214"/>
       <c r="C35" s="196" t="s">
@@ -45235,7 +45291,7 @@
       <c r="J35" s="227"/>
       <c r="K35" s="228" t="n">
         <f aca="false">SUM(I33:I34)</f>
-        <v>28028.7805895061</v>
+        <v>34521.272927469</v>
       </c>
       <c r="L35" s="185"/>
     </row>
@@ -45301,7 +45357,7 @@
       <c r="J39" s="178"/>
       <c r="K39" s="232" t="n">
         <f aca="false">K35-K37</f>
-        <v>27964.2744166666</v>
+        <v>34456.7667546295</v>
       </c>
       <c r="L39" s="185"/>
     </row>
@@ -45417,7 +45473,7 @@
       </c>
       <c r="E48" s="240" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="F48" s="178"/>
       <c r="G48" s="178"/>
@@ -45631,7 +45687,7 @@
       </c>
       <c r="E57" s="240" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="F57" s="178"/>
       <c r="G57" s="178"/>
@@ -45773,7 +45829,7 @@
       </c>
       <c r="E63" s="240" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="F63" s="178"/>
       <c r="G63" s="178"/>
@@ -45987,7 +46043,7 @@
       </c>
       <c r="E72" s="240" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="F72" s="178"/>
       <c r="G72" s="178"/>
@@ -46143,7 +46199,7 @@
       </c>
       <c r="E79" s="245" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="F79" s="246" t="n">
         <f aca="false">SUM(F48:F78)</f>
@@ -46242,7 +46298,7 @@
       </c>
       <c r="E84" s="248" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="F84" s="178"/>
       <c r="G84" s="178"/>
@@ -46398,7 +46454,7 @@
       </c>
       <c r="E91" s="250" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="F91" s="251" t="s">
         <v>374</v>
@@ -46624,7 +46680,7 @@
       </c>
       <c r="F102" s="253" t="n">
         <f aca="false">H5</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="G102" s="257"/>
       <c r="H102" s="257"/>
@@ -48355,7 +48411,7 @@
       <c r="L33" s="272"/>
       <c r="M33" s="290" t="n">
         <f aca="false">Admin!N7</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="N33" s="290"/>
       <c r="O33" s="290"/>
@@ -50154,7 +50210,7 @@
       </c>
       <c r="Z70" s="302" t="n">
         <f aca="false">IF(CorporationTax!K22&gt;0,CorporationTax!K22," ")</f>
-        <v>147180.391666666</v>
+        <v>144080.391666666</v>
       </c>
       <c r="AA70" s="302"/>
       <c r="AB70" s="302"/>
@@ -50372,7 +50428,7 @@
       </c>
       <c r="AJ74" s="302" t="n">
         <f aca="false">SUM(Z69:AF70)-SUM(Z72:AF73)</f>
-        <v>147180.391666666</v>
+        <v>144080.391666666</v>
       </c>
       <c r="AK74" s="302"/>
       <c r="AL74" s="302"/>
@@ -51270,7 +51326,7 @@
       </c>
       <c r="AJ92" s="302" t="n">
         <f aca="false">IF(AJ74&gt;0,AJ74+SUM(AJ76:AJ80)+AJ88,0)</f>
-        <v>147519.897839506</v>
+        <v>144419.897839506</v>
       </c>
       <c r="AK92" s="302"/>
       <c r="AL92" s="302"/>
@@ -52155,7 +52211,7 @@
       </c>
       <c r="AJ110" s="302" t="n">
         <f aca="false">AJ92-Z96-Z98-Z104-Z106</f>
-        <v>147519.897839506</v>
+        <v>144419.897839506</v>
       </c>
       <c r="AK110" s="302"/>
       <c r="AL110" s="302"/>
@@ -52933,7 +52989,7 @@
       </c>
       <c r="N126" s="328" t="n">
         <f aca="false">CorporationTax!F33</f>
-        <v>73659.0461168531</v>
+        <v>72012.1134432604</v>
       </c>
       <c r="O126" s="328"/>
       <c r="P126" s="328"/>
@@ -52951,7 +53007,7 @@
       <c r="Z126" s="315"/>
       <c r="AA126" s="329" t="n">
         <f aca="false">CorporationTax!G33</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AB126" s="329"/>
       <c r="AC126" s="272"/>
@@ -52966,8 +53022,8 @@
         <v>218</v>
       </c>
       <c r="AJ126" s="330" t="n">
-        <f aca="false">CorporationTax!I33</f>
-        <v>13995.2187622021</v>
+        <f aca="false">CorporationTax!J33</f>
+        <v>18003.0283608151</v>
       </c>
       <c r="AK126" s="330"/>
       <c r="AL126" s="330"/>
@@ -53031,12 +53087,15 @@
       <c r="B128" s="298" t="n">
         <v>53</v>
       </c>
-      <c r="C128" s="311"/>
-      <c r="D128" s="311"/>
-      <c r="E128" s="311"/>
-      <c r="F128" s="311"/>
-      <c r="G128" s="311"/>
-      <c r="H128" s="311"/>
+      <c r="C128" s="278" t="n">
+        <f aca="false">IF(CorporationTax!A34&gt;0,CorporationTax!E34," ")</f>
+        <v>2027</v>
+      </c>
+      <c r="D128" s="278"/>
+      <c r="E128" s="278"/>
+      <c r="F128" s="278"/>
+      <c r="G128" s="278"/>
+      <c r="H128" s="278"/>
       <c r="I128" s="272"/>
       <c r="J128" s="272"/>
       <c r="K128" s="272"/>
@@ -53046,13 +53105,16 @@
       <c r="M128" s="299" t="s">
         <v>218</v>
       </c>
-      <c r="N128" s="311"/>
-      <c r="O128" s="311"/>
-      <c r="P128" s="311"/>
-      <c r="Q128" s="311"/>
-      <c r="R128" s="311"/>
-      <c r="S128" s="311"/>
-      <c r="T128" s="311"/>
+      <c r="N128" s="328" t="n">
+        <f aca="false">IF(CorporationTax!A34&gt;0,CorporationTax!F34," ")</f>
+        <v>72407.7843962454</v>
+      </c>
+      <c r="O128" s="328"/>
+      <c r="P128" s="328"/>
+      <c r="Q128" s="328"/>
+      <c r="R128" s="328"/>
+      <c r="S128" s="328"/>
+      <c r="T128" s="328"/>
       <c r="U128" s="272"/>
       <c r="V128" s="272"/>
       <c r="W128" s="272"/>
@@ -53061,8 +53123,11 @@
         <v>55</v>
       </c>
       <c r="Z128" s="315"/>
-      <c r="AA128" s="311"/>
-      <c r="AB128" s="311"/>
+      <c r="AA128" s="329" t="n">
+        <f aca="false">IF(CorporationTax!A34&gt;0,CorporationTax!G34," ")</f>
+        <v>25</v>
+      </c>
+      <c r="AB128" s="329"/>
       <c r="AC128" s="272"/>
       <c r="AD128" s="272"/>
       <c r="AE128" s="272"/>
@@ -53074,7 +53139,10 @@
       <c r="AI128" s="305" t="s">
         <v>218</v>
       </c>
-      <c r="AJ128" s="330"/>
+      <c r="AJ128" s="330" t="n">
+        <f aca="false">CorporationTax!J34</f>
+        <v>18101.9460990613</v>
+      </c>
       <c r="AK128" s="330"/>
       <c r="AL128" s="330"/>
       <c r="AM128" s="330"/>
@@ -53226,7 +53294,7 @@
       </c>
       <c r="AJ131" s="330" t="n">
         <f aca="false">AJ126+AJ128</f>
-        <v>13995.2187622021</v>
+        <v>36104.9744598764</v>
       </c>
       <c r="AK131" s="330"/>
       <c r="AL131" s="330"/>
@@ -53318,11 +53386,14 @@
         <v>218</v>
       </c>
       <c r="X133" s="333"/>
-      <c r="Y133" s="333"/>
-      <c r="Z133" s="333"/>
-      <c r="AA133" s="333"/>
-      <c r="AB133" s="333"/>
-      <c r="AC133" s="333"/>
+      <c r="Y133" s="330" t="n">
+        <f aca="false">CorporationTax!L33+CorporationTax!L34</f>
+        <v>1583.70153240741</v>
+      </c>
+      <c r="Z133" s="330"/>
+      <c r="AA133" s="330"/>
+      <c r="AB133" s="330"/>
+      <c r="AC133" s="330"/>
       <c r="AD133" s="333"/>
       <c r="AE133" s="331" t="s">
         <v>475</v>
@@ -53420,11 +53491,14 @@
         <v>218</v>
       </c>
       <c r="X135" s="333"/>
-      <c r="Y135" s="333"/>
-      <c r="Z135" s="333"/>
-      <c r="AA135" s="333"/>
-      <c r="AB135" s="333"/>
-      <c r="AC135" s="333"/>
+      <c r="Y135" s="330" t="n">
+        <f aca="false">AJ131-Y133</f>
+        <v>34521.272927469</v>
+      </c>
+      <c r="Z135" s="330"/>
+      <c r="AA135" s="330"/>
+      <c r="AB135" s="330"/>
+      <c r="AC135" s="330"/>
       <c r="AD135" s="333"/>
       <c r="AE135" s="331" t="s">
         <v>475</v>
@@ -53519,8 +53593,8 @@
         <v>66</v>
       </c>
       <c r="W137" s="334" t="n">
-        <f aca="false">IF(AJ131&gt;0,AJ131*100/AJ110," ")</f>
-        <v>9.48700410396717</v>
+        <f aca="false">IF(Y135&gt;0,Y135*100/AJ110," ")</f>
+        <v>23.9034048935782</v>
       </c>
       <c r="X137" s="334"/>
       <c r="Y137" s="334"/>
@@ -53941,8 +54015,8 @@
         <v>218</v>
       </c>
       <c r="AJ145" s="330" t="n">
-        <f aca="false">AJ131</f>
-        <v>13995.2187622021</v>
+        <f aca="false">Y135</f>
+        <v>34521.272927469</v>
       </c>
       <c r="AK145" s="330"/>
       <c r="AL145" s="330"/>
@@ -54644,7 +54718,7 @@
       </c>
       <c r="AJ159" s="330" t="n">
         <f aca="false">IF(AJ145&gt;0,AJ145+AJ149-AJ154,0)</f>
-        <v>13930.7125893626</v>
+        <v>34456.7667546295</v>
       </c>
       <c r="AK159" s="330"/>
       <c r="AL159" s="330"/>
@@ -54993,7 +55067,7 @@
       </c>
       <c r="AJ166" s="330" t="n">
         <f aca="false">IF(AJ159&gt;0,AJ159-AJ163,0)</f>
-        <v>13930.7125893626</v>
+        <v>34456.7667546295</v>
       </c>
       <c r="AK166" s="330"/>
       <c r="AL166" s="330"/>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -5261,7 +5261,7 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="I1">
-            <v>11740</v>
+            <v>13740</v>
           </cell>
         </row>
         <row r="1">
@@ -5469,48 +5469,84 @@
         </row>
         <row r="68">
           <cell r="B68">
-            <v>46037</v>
+            <v>45992</v>
           </cell>
           <cell r="C68" t="str">
-            <v>IKEA</v>
+            <v>Precision Tooling Supplies</v>
           </cell>
         </row>
         <row r="68">
           <cell r="E68">
-            <v>1000</v>
+            <v>13000</v>
           </cell>
         </row>
         <row r="68">
           <cell r="Q68">
-            <v>1000</v>
+            <v>13000</v>
           </cell>
         </row>
         <row r="69">
           <cell r="B69">
-            <v>46137</v>
+            <v>46037</v>
           </cell>
           <cell r="C69" t="str">
-            <v>Ford</v>
+            <v>IKEA</v>
           </cell>
         </row>
         <row r="69">
           <cell r="E69">
-            <v>30000</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="69">
           <cell r="Q69">
+            <v>1000</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="B70">
+            <v>46082</v>
+          </cell>
+          <cell r="C70" t="str">
+            <v>Precision Tooling Supplies</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="E70">
+            <v>7000</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="Q70">
+            <v>7000</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="B71">
+            <v>46137</v>
+          </cell>
+          <cell r="C71" t="str">
+            <v>Ford</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="E71">
+            <v>30000</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="Q71">
             <v>30000</v>
           </cell>
         </row>
         <row r="75">
           <cell r="E75">
-            <v>32500</v>
+            <v>52500</v>
           </cell>
         </row>
         <row r="75">
           <cell r="I75">
-            <v>3250</v>
+            <v>5250</v>
           </cell>
         </row>
         <row r="75">
@@ -5577,7 +5613,7 @@
         </row>
         <row r="110">
           <cell r="E110">
-            <v>32500</v>
+            <v>52500</v>
           </cell>
         </row>
       </sheetData>
@@ -5778,10 +5814,10 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="F1">
-            <v>9057</v>
+            <v>24657</v>
           </cell>
           <cell r="G1">
-            <v>1509.5</v>
+            <v>4109.5</v>
           </cell>
         </row>
         <row r="1">
@@ -5846,7 +5882,7 @@
             <v>0</v>
           </cell>
           <cell r="AI1">
-            <v>0</v>
+            <v>13000</v>
           </cell>
         </row>
         <row r="1">
@@ -6018,10 +6054,10 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="F1">
-            <v>4975</v>
+            <v>13375</v>
           </cell>
           <cell r="G1">
-            <v>829.166666666667</v>
+            <v>2229.16666666667</v>
           </cell>
         </row>
         <row r="1">
@@ -6086,7 +6122,7 @@
             <v>0</v>
           </cell>
           <cell r="AI1">
-            <v>0</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="1">
@@ -7285,7 +7321,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>12575.2</v>
+            <v>27575.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7297,13 +7333,13 @@
             <v>0</v>
           </cell>
           <cell r="AB1">
-            <v>4000</v>
+            <v>17000</v>
           </cell>
           <cell r="AC1">
             <v>5652</v>
           </cell>
           <cell r="AD1">
-            <v>250</v>
+            <v>2250</v>
           </cell>
           <cell r="AE1">
             <v>0</v>
@@ -7408,13 +7444,13 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>2673.2</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
           </cell>
           <cell r="AJ1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
           <cell r="AK1">
             <v>0</v>
@@ -7445,7 +7481,7 @@
             <v>0</v>
           </cell>
           <cell r="J1">
-            <v>36020</v>
+            <v>38520</v>
           </cell>
           <cell r="K1">
             <v>0</v>
@@ -7457,7 +7493,7 @@
             <v>0</v>
           </cell>
           <cell r="N1">
-            <v>2500</v>
+            <v>0</v>
           </cell>
           <cell r="O1">
             <v>0</v>
@@ -7564,7 +7600,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>12133.2</v>
+            <v>20233.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7576,13 +7612,13 @@
             <v>0</v>
           </cell>
           <cell r="AB1">
-            <v>3600</v>
+            <v>10600</v>
           </cell>
           <cell r="AC1">
             <v>5652</v>
           </cell>
           <cell r="AD1">
-            <v>208</v>
+            <v>1308</v>
           </cell>
           <cell r="AE1">
             <v>0</v>
@@ -7687,7 +7723,7 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>6173.2</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
@@ -7696,7 +7732,7 @@
             <v>0</v>
           </cell>
           <cell r="AK1">
-            <v>0</v>
+            <v>4500</v>
           </cell>
           <cell r="AL1">
             <v>3000</v>
@@ -7873,13 +7909,13 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>2273.2</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
             <v>0</v>
           </cell>
           <cell r="AJ1">
-            <v>0</v>
+            <v>600</v>
           </cell>
           <cell r="AK1">
             <v>0</v>
@@ -8424,7 +8460,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>15000</v>
+            <v>0</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -8436,13 +8472,13 @@
             <v>0</v>
           </cell>
           <cell r="AB1">
-            <v>13000</v>
+            <v>0</v>
           </cell>
           <cell r="AC1">
             <v>0</v>
           </cell>
           <cell r="AD1">
-            <v>2000</v>
+            <v>0</v>
           </cell>
           <cell r="AE1">
             <v>0</v>
@@ -8703,7 +8739,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>8100</v>
+            <v>0</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -8715,13 +8751,13 @@
             <v>0</v>
           </cell>
           <cell r="AB1">
-            <v>7000</v>
+            <v>0</v>
           </cell>
           <cell r="AC1">
             <v>0</v>
           </cell>
           <cell r="AD1">
-            <v>1100</v>
+            <v>0</v>
           </cell>
           <cell r="AE1">
             <v>0</v>
@@ -19057,12 +19093,12 @@
       <c r="EG7" s="54"/>
       <c r="EH7" s="36" t="n">
         <f aca="false">[1]Schedule!$E$75-([1]Schedule!$W$22+[1]Schedule!$W$75)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="EI7" s="54"/>
       <c r="EJ7" s="36" t="n">
         <f aca="false">SUM(EF7:EH7)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="EK7" s="54"/>
     </row>
@@ -19885,12 +19921,12 @@
       <c r="L12" s="36"/>
       <c r="M12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="N12" s="57"/>
       <c r="O12" s="36" t="n">
         <f aca="false">SUM(D12:N12)</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="P12" s="57"/>
       <c r="Q12" s="36"/>
@@ -19902,12 +19938,12 @@
       <c r="W12" s="36"/>
       <c r="X12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="Y12" s="54"/>
       <c r="Z12" s="36" t="n">
         <f aca="false">SUM(O12:Y12)</f>
-        <v>-541.666666666667</v>
+        <v>-875</v>
       </c>
       <c r="AA12" s="57"/>
       <c r="AB12" s="36"/>
@@ -19919,12 +19955,12 @@
       <c r="AH12" s="36"/>
       <c r="AI12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="AJ12" s="54"/>
       <c r="AK12" s="36" t="n">
         <f aca="false">SUM(Z12:AJ12)</f>
-        <v>-812.5</v>
+        <v>-1312.5</v>
       </c>
       <c r="AL12" s="57"/>
       <c r="AM12" s="36"/>
@@ -19936,12 +19972,12 @@
       <c r="AS12" s="36"/>
       <c r="AT12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="AU12" s="54"/>
       <c r="AV12" s="36" t="n">
         <f aca="false">SUM(AK12:AU12)</f>
-        <v>-1083.33333333333</v>
+        <v>-1750</v>
       </c>
       <c r="AW12" s="57"/>
       <c r="AX12" s="36"/>
@@ -19953,12 +19989,12 @@
       <c r="BD12" s="36"/>
       <c r="BE12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="BF12" s="54"/>
       <c r="BG12" s="36" t="n">
         <f aca="false">SUM(AV12:BF12)</f>
-        <v>-1354.16666666667</v>
+        <v>-2187.5</v>
       </c>
       <c r="BH12" s="57"/>
       <c r="BI12" s="36"/>
@@ -19970,12 +20006,12 @@
       <c r="BO12" s="36"/>
       <c r="BP12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="BQ12" s="54"/>
       <c r="BR12" s="36" t="n">
         <f aca="false">SUM(BG12:BQ12)</f>
-        <v>-1625</v>
+        <v>-2625</v>
       </c>
       <c r="BS12" s="57"/>
       <c r="BT12" s="36"/>
@@ -19987,12 +20023,12 @@
       <c r="BZ12" s="36"/>
       <c r="CA12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="CB12" s="54"/>
       <c r="CC12" s="36" t="n">
         <f aca="false">SUM(BR12:CB12)</f>
-        <v>-1895.83333333333</v>
+        <v>-3062.5</v>
       </c>
       <c r="CD12" s="57"/>
       <c r="CE12" s="36"/>
@@ -20004,12 +20040,12 @@
       <c r="CK12" s="36"/>
       <c r="CL12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="CM12" s="54"/>
       <c r="CN12" s="36" t="n">
         <f aca="false">SUM(CC12:CM12)</f>
-        <v>-2166.66666666667</v>
+        <v>-3500</v>
       </c>
       <c r="CO12" s="57"/>
       <c r="CP12" s="36"/>
@@ -20021,12 +20057,12 @@
       <c r="CV12" s="36"/>
       <c r="CW12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="CX12" s="54"/>
       <c r="CY12" s="36" t="n">
         <f aca="false">SUM(CN12:CX12)</f>
-        <v>-2437.5</v>
+        <v>-3937.5</v>
       </c>
       <c r="CZ12" s="57"/>
       <c r="DA12" s="36"/>
@@ -20038,12 +20074,12 @@
       <c r="DG12" s="36"/>
       <c r="DH12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="DI12" s="54"/>
       <c r="DJ12" s="36" t="n">
         <f aca="false">SUM(CY12:DI12)</f>
-        <v>-2708.33333333333</v>
+        <v>-4375</v>
       </c>
       <c r="DK12" s="57"/>
       <c r="DL12" s="36"/>
@@ -20055,12 +20091,12 @@
       <c r="DR12" s="36"/>
       <c r="DS12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="DT12" s="54"/>
       <c r="DU12" s="36" t="n">
         <f aca="false">SUM(DJ12:DT12)</f>
-        <v>-2979.16666666667</v>
+        <v>-4812.5</v>
       </c>
       <c r="DV12" s="57"/>
       <c r="DW12" s="36"/>
@@ -20072,12 +20108,12 @@
       <c r="EC12" s="36"/>
       <c r="ED12" s="36" t="n">
         <f aca="false">-([1]Schedule!$I$22+[1]Schedule!$I$75)/12</f>
-        <v>-270.833333333333</v>
+        <v>-437.5</v>
       </c>
       <c r="EE12" s="54"/>
       <c r="EF12" s="36" t="n">
         <f aca="false">SUM(DU12:EE12)</f>
-        <v>-3250</v>
+        <v>-5250</v>
       </c>
       <c r="EG12" s="54"/>
       <c r="EH12" s="36" t="n">
@@ -20087,7 +20123,7 @@
       <c r="EI12" s="54"/>
       <c r="EJ12" s="36" t="n">
         <f aca="false">SUM(EF12:EH12)</f>
-        <v>-3250</v>
+        <v>-5250</v>
       </c>
       <c r="EK12" s="54"/>
     </row>
@@ -20813,7 +20849,7 @@
       <c r="AB16" s="36"/>
       <c r="AC16" s="36" t="n">
         <f aca="false">[2]Dec!$AI$1</f>
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="AD16" s="36"/>
       <c r="AE16" s="36"/>
@@ -20824,7 +20860,7 @@
       <c r="AJ16" s="54"/>
       <c r="AK16" s="36" t="n">
         <f aca="false">SUM(Z16:AJ16)</f>
-        <v>1500</v>
+        <v>14500</v>
       </c>
       <c r="AL16" s="57"/>
       <c r="AM16" s="36"/>
@@ -20841,7 +20877,7 @@
       <c r="AU16" s="54"/>
       <c r="AV16" s="36" t="n">
         <f aca="false">SUM(AK16:AU16)</f>
-        <v>2500</v>
+        <v>15500</v>
       </c>
       <c r="AW16" s="57"/>
       <c r="AX16" s="36"/>
@@ -20858,13 +20894,13 @@
       <c r="BF16" s="54"/>
       <c r="BG16" s="36" t="n">
         <f aca="false">SUM(AV16:BF16)</f>
-        <v>2500</v>
+        <v>15500</v>
       </c>
       <c r="BH16" s="57"/>
       <c r="BI16" s="36"/>
       <c r="BJ16" s="36" t="n">
         <f aca="false">[2]Mar!$AI$1</f>
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="BK16" s="36"/>
       <c r="BL16" s="36"/>
@@ -20875,7 +20911,7 @@
       <c r="BQ16" s="54"/>
       <c r="BR16" s="36" t="n">
         <f aca="false">SUM(BG16:BQ16)</f>
-        <v>2500</v>
+        <v>22500</v>
       </c>
       <c r="BS16" s="57"/>
       <c r="BT16" s="36"/>
@@ -20892,7 +20928,7 @@
       <c r="CB16" s="54"/>
       <c r="CC16" s="36" t="n">
         <f aca="false">SUM(BR16:CB16)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="CD16" s="57"/>
       <c r="CE16" s="36"/>
@@ -20909,7 +20945,7 @@
       <c r="CM16" s="54"/>
       <c r="CN16" s="36" t="n">
         <f aca="false">SUM(CC16:CM16)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="CO16" s="57"/>
       <c r="CP16" s="36"/>
@@ -20926,7 +20962,7 @@
       <c r="CX16" s="54"/>
       <c r="CY16" s="36" t="n">
         <f aca="false">SUM(CN16:CX16)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="CZ16" s="57"/>
       <c r="DA16" s="36"/>
@@ -20943,7 +20979,7 @@
       <c r="DI16" s="54"/>
       <c r="DJ16" s="36" t="n">
         <f aca="false">SUM(CY16:DI16)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="DK16" s="57"/>
       <c r="DL16" s="36"/>
@@ -20960,7 +20996,7 @@
       <c r="DT16" s="54"/>
       <c r="DU16" s="36" t="n">
         <f aca="false">SUM(DJ16:DT16)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="DV16" s="57"/>
       <c r="DW16" s="36"/>
@@ -20977,12 +21013,12 @@
       <c r="EE16" s="54"/>
       <c r="EF16" s="36" t="n">
         <f aca="false">SUM(DU16:EE16)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="EG16" s="54"/>
       <c r="EH16" s="36" t="n">
         <f aca="false">-[1]Schedule!$E$110</f>
-        <v>-32500</v>
+        <v>-52500</v>
       </c>
       <c r="EI16" s="54"/>
       <c r="EJ16" s="36" t="n">
@@ -21747,7 +21783,7 @@
       <c r="AY20" s="36"/>
       <c r="AZ20" s="36" t="n">
         <f aca="false">-[4]Feb!$J$1</f>
-        <v>-36020</v>
+        <v>-38520</v>
       </c>
       <c r="BA20" s="36" t="n">
         <f aca="false">-[5]Feb!$J$1</f>
@@ -21766,7 +21802,7 @@
       <c r="BF20" s="54"/>
       <c r="BG20" s="36" t="n">
         <f aca="false">SUM(AV20:BF20)</f>
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="BH20" s="57"/>
       <c r="BI20" s="36" t="n">
@@ -21795,7 +21831,7 @@
       <c r="BQ20" s="54"/>
       <c r="BR20" s="36" t="n">
         <f aca="false">SUM(BG20:BQ20)</f>
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="BS20" s="57"/>
       <c r="BT20" s="36" t="n">
@@ -21824,7 +21860,7 @@
       <c r="CB20" s="54"/>
       <c r="CC20" s="36" t="n">
         <f aca="false">SUM(BR20:CB20)</f>
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="CD20" s="57"/>
       <c r="CE20" s="36" t="n">
@@ -21853,7 +21889,7 @@
       <c r="CM20" s="54"/>
       <c r="CN20" s="36" t="n">
         <f aca="false">SUM(CC20:CM20)</f>
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="CO20" s="57"/>
       <c r="CP20" s="36" t="n">
@@ -21882,7 +21918,7 @@
       <c r="CX20" s="54"/>
       <c r="CY20" s="36" t="n">
         <f aca="false">SUM(CN20:CX20)</f>
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="CZ20" s="57"/>
       <c r="DA20" s="36" t="n">
@@ -21911,7 +21947,7 @@
       <c r="DI20" s="54"/>
       <c r="DJ20" s="36" t="n">
         <f aca="false">SUM(CY20:DI20)</f>
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="DK20" s="57"/>
       <c r="DL20" s="36" t="n">
@@ -21940,7 +21976,7 @@
       <c r="DT20" s="54"/>
       <c r="DU20" s="36" t="n">
         <f aca="false">SUM(DJ20:DT20)</f>
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="DV20" s="57"/>
       <c r="DW20" s="36" t="n">
@@ -21969,13 +22005,13 @@
       <c r="EE20" s="54"/>
       <c r="EF20" s="36" t="n">
         <f aca="false">SUM(DU20:EE20)</f>
-        <v>10400</v>
+        <v>7900</v>
       </c>
       <c r="EG20" s="54"/>
       <c r="EI20" s="54"/>
       <c r="EJ20" s="36" t="n">
         <f aca="false">SUM(EF20:EH20)</f>
-        <v>10400</v>
+        <v>7900</v>
       </c>
       <c r="EK20" s="54"/>
     </row>
@@ -22165,7 +22201,7 @@
       <c r="AC22" s="36"/>
       <c r="AD22" s="36" t="n">
         <f aca="false">[4]Dec!$F$1-[4]Dec!$X$1</f>
-        <v>22624.8</v>
+        <v>7624.8</v>
       </c>
       <c r="AE22" s="36"/>
       <c r="AF22" s="36"/>
@@ -22175,7 +22211,7 @@
       <c r="AJ22" s="54"/>
       <c r="AK22" s="36" t="n">
         <f aca="false">SUM(Z22:AJ22)</f>
-        <v>98069.4</v>
+        <v>83069.4</v>
       </c>
       <c r="AL22" s="57"/>
       <c r="AM22" s="36"/>
@@ -22192,7 +22228,7 @@
       <c r="AU22" s="54"/>
       <c r="AV22" s="36" t="n">
         <f aca="false">SUM(AK22:AU22)</f>
-        <v>115404.2</v>
+        <v>100404.2</v>
       </c>
       <c r="AW22" s="57"/>
       <c r="AX22" s="36"/>
@@ -22209,14 +22245,14 @@
       <c r="BF22" s="54"/>
       <c r="BG22" s="36" t="n">
         <f aca="false">SUM(AV22:BF22)</f>
-        <v>127690.83</v>
+        <v>112690.83</v>
       </c>
       <c r="BH22" s="57"/>
       <c r="BI22" s="36"/>
       <c r="BJ22" s="36"/>
       <c r="BK22" s="36" t="n">
         <f aca="false">[4]Mar!$F$1-[4]Mar!$X$1</f>
-        <v>21626.8</v>
+        <v>13526.8</v>
       </c>
       <c r="BL22" s="36"/>
       <c r="BM22" s="36"/>
@@ -22226,7 +22262,7 @@
       <c r="BQ22" s="54"/>
       <c r="BR22" s="36" t="n">
         <f aca="false">SUM(BG22:BQ22)</f>
-        <v>149317.63</v>
+        <v>126217.63</v>
       </c>
       <c r="BS22" s="57"/>
       <c r="BT22" s="36"/>
@@ -22243,7 +22279,7 @@
       <c r="CB22" s="54"/>
       <c r="CC22" s="36" t="n">
         <f aca="false">SUM(BR22:CB22)</f>
-        <v>143052.43</v>
+        <v>119952.43</v>
       </c>
       <c r="CD22" s="57"/>
       <c r="CE22" s="36"/>
@@ -22260,7 +22296,7 @@
       <c r="CM22" s="54"/>
       <c r="CN22" s="36" t="n">
         <f aca="false">SUM(CC22:CM22)</f>
-        <v>151665.73</v>
+        <v>128565.73</v>
       </c>
       <c r="CO22" s="57"/>
       <c r="CP22" s="36"/>
@@ -22277,7 +22313,7 @@
       <c r="CX22" s="54"/>
       <c r="CY22" s="36" t="n">
         <f aca="false">SUM(CN22:CX22)</f>
-        <v>171173.53</v>
+        <v>148073.53</v>
       </c>
       <c r="CZ22" s="57"/>
       <c r="DA22" s="36"/>
@@ -22294,7 +22330,7 @@
       <c r="DI22" s="54"/>
       <c r="DJ22" s="36" t="n">
         <f aca="false">SUM(CY22:DI22)</f>
-        <v>195988.33</v>
+        <v>172888.33</v>
       </c>
       <c r="DK22" s="57"/>
       <c r="DL22" s="36"/>
@@ -22311,7 +22347,7 @@
       <c r="DT22" s="54"/>
       <c r="DU22" s="36" t="n">
         <f aca="false">SUM(DJ22:DT22)</f>
-        <v>206705.63</v>
+        <v>183605.63</v>
       </c>
       <c r="DV22" s="57"/>
       <c r="DW22" s="36"/>
@@ -22328,13 +22364,13 @@
       <c r="EE22" s="54"/>
       <c r="EF22" s="36" t="n">
         <f aca="false">SUM(DU22:EE22)</f>
-        <v>204415.43</v>
+        <v>181315.43</v>
       </c>
       <c r="EG22" s="54"/>
       <c r="EI22" s="54"/>
       <c r="EJ22" s="36" t="n">
         <f aca="false">SUM(EF22:EH22)</f>
-        <v>204415.43</v>
+        <v>181315.43</v>
       </c>
       <c r="EK22" s="54"/>
     </row>
@@ -22389,7 +22425,7 @@
       <c r="AD23" s="36"/>
       <c r="AE23" s="36" t="n">
         <f aca="false">[5]Dec!$F$1-[5]Dec!$X$1</f>
-        <v>-15000</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="36"/>
       <c r="AG23" s="36"/>
@@ -22398,7 +22434,7 @@
       <c r="AJ23" s="54"/>
       <c r="AK23" s="36" t="n">
         <f aca="false">SUM(Z23:AJ23)</f>
-        <v>-10000</v>
+        <v>5000</v>
       </c>
       <c r="AL23" s="57"/>
       <c r="AM23" s="36"/>
@@ -22415,7 +22451,7 @@
       <c r="AU23" s="54"/>
       <c r="AV23" s="36" t="n">
         <f aca="false">SUM(AK23:AU23)</f>
-        <v>-10000</v>
+        <v>5000</v>
       </c>
       <c r="AW23" s="57"/>
       <c r="AX23" s="36"/>
@@ -22432,7 +22468,7 @@
       <c r="BF23" s="54"/>
       <c r="BG23" s="36" t="n">
         <f aca="false">SUM(AV23:BF23)</f>
-        <v>-10000</v>
+        <v>5000</v>
       </c>
       <c r="BH23" s="57"/>
       <c r="BI23" s="36"/>
@@ -22440,7 +22476,7 @@
       <c r="BK23" s="36"/>
       <c r="BL23" s="36" t="n">
         <f aca="false">[5]Mar!$F$1-[5]Mar!$X$1</f>
-        <v>-7975</v>
+        <v>125</v>
       </c>
       <c r="BM23" s="36"/>
       <c r="BN23" s="36"/>
@@ -22449,7 +22485,7 @@
       <c r="BQ23" s="54"/>
       <c r="BR23" s="36" t="n">
         <f aca="false">SUM(BG23:BQ23)</f>
-        <v>-17975</v>
+        <v>5125</v>
       </c>
       <c r="BS23" s="57"/>
       <c r="BT23" s="36"/>
@@ -22466,7 +22502,7 @@
       <c r="CB23" s="54"/>
       <c r="CC23" s="36" t="n">
         <f aca="false">SUM(BR23:CB23)</f>
-        <v>-17975</v>
+        <v>5125</v>
       </c>
       <c r="CD23" s="57"/>
       <c r="CE23" s="36"/>
@@ -22483,7 +22519,7 @@
       <c r="CM23" s="54"/>
       <c r="CN23" s="36" t="n">
         <f aca="false">SUM(CC23:CM23)</f>
-        <v>-17975</v>
+        <v>5125</v>
       </c>
       <c r="CO23" s="57"/>
       <c r="CP23" s="36"/>
@@ -22500,7 +22536,7 @@
       <c r="CX23" s="54"/>
       <c r="CY23" s="36" t="n">
         <f aca="false">SUM(CN23:CX23)</f>
-        <v>-17975</v>
+        <v>5125</v>
       </c>
       <c r="CZ23" s="57"/>
       <c r="DA23" s="36"/>
@@ -22517,7 +22553,7 @@
       <c r="DI23" s="54"/>
       <c r="DJ23" s="36" t="n">
         <f aca="false">SUM(CY23:DI23)</f>
-        <v>-17975</v>
+        <v>5125</v>
       </c>
       <c r="DK23" s="57"/>
       <c r="DL23" s="36"/>
@@ -22534,7 +22570,7 @@
       <c r="DT23" s="54"/>
       <c r="DU23" s="36" t="n">
         <f aca="false">SUM(DJ23:DT23)</f>
-        <v>-17975</v>
+        <v>5125</v>
       </c>
       <c r="DV23" s="57"/>
       <c r="DW23" s="36"/>
@@ -22551,13 +22587,13 @@
       <c r="EE23" s="54"/>
       <c r="EF23" s="36" t="n">
         <f aca="false">SUM(DU23:EE23)</f>
-        <v>-12825</v>
+        <v>10275</v>
       </c>
       <c r="EG23" s="54"/>
       <c r="EI23" s="54"/>
       <c r="EJ23" s="36" t="n">
         <f aca="false">SUM(EF23:EH23)</f>
-        <v>-12825</v>
+        <v>10275</v>
       </c>
       <c r="EK23" s="54"/>
     </row>
@@ -23548,15 +23584,15 @@
       <c r="AB28" s="36"/>
       <c r="AC28" s="36" t="n">
         <f aca="false">-[2]Dec!$F$1+[2]Dec!$AK$1</f>
-        <v>-9057</v>
+        <v>-24657</v>
       </c>
       <c r="AD28" s="36" t="n">
         <f aca="false">[4]Dec!$AB$1</f>
-        <v>4000</v>
+        <v>17000</v>
       </c>
       <c r="AE28" s="36" t="n">
         <f aca="false">[5]Dec!$AB$1</f>
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="AF28" s="36" t="n">
         <f aca="false">[6]Dec!$AB$1</f>
@@ -23571,7 +23607,7 @@
       <c r="AJ28" s="54"/>
       <c r="AK28" s="36" t="n">
         <f aca="false">SUM(Z28:AJ28)</f>
-        <v>2276.75</v>
+        <v>-13323.25</v>
       </c>
       <c r="AL28" s="57"/>
       <c r="AM28" s="36"/>
@@ -23600,7 +23636,7 @@
       <c r="AU28" s="54"/>
       <c r="AV28" s="36" t="n">
         <f aca="false">SUM(AK28:AU28)</f>
-        <v>-2982.5</v>
+        <v>-18582.5</v>
       </c>
       <c r="AW28" s="57"/>
       <c r="AX28" s="36"/>
@@ -23629,21 +23665,21 @@
       <c r="BF28" s="54"/>
       <c r="BG28" s="36" t="n">
         <f aca="false">SUM(AV28:BF28)</f>
-        <v>-3287.75</v>
+        <v>-18887.75</v>
       </c>
       <c r="BH28" s="57"/>
       <c r="BI28" s="36"/>
       <c r="BJ28" s="36" t="n">
         <f aca="false">-[2]Mar!$F$1+[2]Mar!$AK$1</f>
-        <v>-4975</v>
+        <v>-13375</v>
       </c>
       <c r="BK28" s="36" t="n">
         <f aca="false">[4]Mar!$AB$1</f>
-        <v>3600</v>
+        <v>10600</v>
       </c>
       <c r="BL28" s="36" t="n">
         <f aca="false">[5]Mar!$AB$1</f>
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="BM28" s="36" t="n">
         <f aca="false">[6]Mar!$AB$1</f>
@@ -23658,7 +23694,7 @@
       <c r="BQ28" s="54"/>
       <c r="BR28" s="36" t="n">
         <f aca="false">SUM(BG28:BQ28)</f>
-        <v>2355.25</v>
+        <v>-21644.75</v>
       </c>
       <c r="BS28" s="57"/>
       <c r="BT28" s="36"/>
@@ -23687,7 +23723,7 @@
       <c r="CB28" s="54"/>
       <c r="CC28" s="36" t="n">
         <f aca="false">SUM(BR28:CB28)</f>
-        <v>-30.5</v>
+        <v>-24030.5</v>
       </c>
       <c r="CD28" s="57"/>
       <c r="CE28" s="36"/>
@@ -23716,7 +23752,7 @@
       <c r="CM28" s="54"/>
       <c r="CN28" s="36" t="n">
         <f aca="false">SUM(CC28:CM28)</f>
-        <v>-3048.5</v>
+        <v>-27048.5</v>
       </c>
       <c r="CO28" s="57"/>
       <c r="CP28" s="36"/>
@@ -23745,7 +23781,7 @@
       <c r="CX28" s="54"/>
       <c r="CY28" s="36" t="n">
         <f aca="false">SUM(CN28:CX28)</f>
-        <v>-8250</v>
+        <v>-32250</v>
       </c>
       <c r="CZ28" s="57"/>
       <c r="DA28" s="36"/>
@@ -23774,7 +23810,7 @@
       <c r="DI28" s="54"/>
       <c r="DJ28" s="36" t="n">
         <f aca="false">SUM(CY28:DI28)</f>
-        <v>-8761.25</v>
+        <v>-32761.25</v>
       </c>
       <c r="DK28" s="57"/>
       <c r="DL28" s="36"/>
@@ -23803,7 +23839,7 @@
       <c r="DT28" s="54"/>
       <c r="DU28" s="36" t="n">
         <f aca="false">SUM(DJ28:DT28)</f>
-        <v>-8517.75</v>
+        <v>-32517.75</v>
       </c>
       <c r="DV28" s="57"/>
       <c r="DW28" s="36"/>
@@ -23832,7 +23868,7 @@
       <c r="EE28" s="54"/>
       <c r="EF28" s="36" t="n">
         <f aca="false">SUM(DU28:EE28)</f>
-        <v>-8432.25</v>
+        <v>-32432.25</v>
       </c>
       <c r="EG28" s="54"/>
       <c r="EH28" s="36" t="n">
@@ -23842,7 +23878,7 @@
       <c r="EI28" s="54"/>
       <c r="EJ28" s="36" t="n">
         <f aca="false">SUM(EF28:EH28)</f>
-        <v>11567.75</v>
+        <v>-12432.25</v>
       </c>
       <c r="EK28" s="54"/>
     </row>
@@ -24885,7 +24921,7 @@
       </c>
       <c r="AO32" s="36" t="n">
         <f aca="false">-[4]Jan!$O$1+[4]Jan!$AJ$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32" s="36" t="n">
         <f aca="false">-[5]Jan!$O$1+[5]Jan!$AJ$1</f>
@@ -24904,7 +24940,7 @@
       <c r="AU32" s="54"/>
       <c r="AV32" s="36" t="n">
         <f aca="false">SUM(AK32:AU32)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AW32" s="57"/>
       <c r="AX32" s="36" t="n">
@@ -24936,7 +24972,7 @@
       <c r="BF32" s="54"/>
       <c r="BG32" s="36" t="n">
         <f aca="false">SUM(AV32:BF32)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BH32" s="57"/>
       <c r="BI32" s="36" t="n">
@@ -24968,7 +25004,7 @@
       <c r="BQ32" s="54"/>
       <c r="BR32" s="36" t="n">
         <f aca="false">SUM(BG32:BQ32)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32" s="57"/>
       <c r="BT32" s="36" t="n">
@@ -25000,7 +25036,7 @@
       <c r="CB32" s="54"/>
       <c r="CC32" s="36" t="n">
         <f aca="false">SUM(BR32:CB32)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CD32" s="57"/>
       <c r="CE32" s="36" t="n">
@@ -25032,7 +25068,7 @@
       <c r="CM32" s="54"/>
       <c r="CN32" s="36" t="n">
         <f aca="false">SUM(CC32:CM32)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CO32" s="57"/>
       <c r="CP32" s="36" t="n">
@@ -25045,7 +25081,7 @@
       </c>
       <c r="CR32" s="36" t="n">
         <f aca="false">-[4]Jun!$O$1+[4]Jun!$AJ$1</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="CS32" s="36" t="n">
         <f aca="false">-[5]Jun!$O$1+[5]Jun!$AJ$1</f>
@@ -25064,7 +25100,7 @@
       <c r="CX32" s="54"/>
       <c r="CY32" s="36" t="n">
         <f aca="false">SUM(CN32:CX32)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="CZ32" s="57"/>
       <c r="DA32" s="36" t="n">
@@ -25096,7 +25132,7 @@
       <c r="DI32" s="54"/>
       <c r="DJ32" s="36" t="n">
         <f aca="false">SUM(CY32:DI32)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="DK32" s="57"/>
       <c r="DL32" s="36" t="n">
@@ -25128,7 +25164,7 @@
       <c r="DT32" s="54"/>
       <c r="DU32" s="36" t="n">
         <f aca="false">SUM(DJ32:DT32)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="DV32" s="57"/>
       <c r="DW32" s="36" t="n">
@@ -25160,13 +25196,13 @@
       <c r="EE32" s="54"/>
       <c r="EF32" s="36" t="n">
         <f aca="false">SUM(DU32:EE32)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="EG32" s="54"/>
       <c r="EI32" s="54"/>
       <c r="EJ32" s="36" t="n">
         <f aca="false">SUM(EF32:EH32)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="EK32" s="54"/>
     </row>
@@ -25252,7 +25288,7 @@
       </c>
       <c r="AC33" s="36" t="n">
         <f aca="false">[2]Dec!$G$1</f>
-        <v>1509.5</v>
+        <v>4109.5</v>
       </c>
       <c r="AD33" s="36" t="n">
         <f aca="false">-[4]Dec!$N$1+[4]Dec!$AI$1</f>
@@ -25275,7 +25311,7 @@
       <c r="AJ33" s="54"/>
       <c r="AK33" s="36" t="n">
         <f aca="false">SUM(Z33:AJ33)</f>
-        <v>-14996.125</v>
+        <v>-12396.125</v>
       </c>
       <c r="AL33" s="57"/>
       <c r="AM33" s="36" t="n">
@@ -25307,7 +25343,7 @@
       <c r="AU33" s="54"/>
       <c r="AV33" s="36" t="n">
         <f aca="false">SUM(AK33:AU33)</f>
-        <v>-19112.9166666667</v>
+        <v>-16512.9166666667</v>
       </c>
       <c r="AW33" s="57"/>
       <c r="AX33" s="36" t="n">
@@ -25320,7 +25356,7 @@
       </c>
       <c r="AZ33" s="36" t="n">
         <f aca="false">-[4]Feb!$N$1+[4]Feb!$AI$1</f>
-        <v>-2500</v>
+        <v>0</v>
       </c>
       <c r="BA33" s="36" t="n">
         <f aca="false">-[5]Feb!$N$1+[5]Feb!$AI$1</f>
@@ -25339,7 +25375,7 @@
       <c r="BF33" s="54"/>
       <c r="BG33" s="36" t="n">
         <f aca="false">SUM(AV33:BF33)</f>
-        <v>-26882.0416666667</v>
+        <v>-21782.0416666667</v>
       </c>
       <c r="BH33" s="57"/>
       <c r="BI33" s="36" t="n">
@@ -25348,7 +25384,7 @@
       </c>
       <c r="BJ33" s="36" t="n">
         <f aca="false">[2]Mar!$G$1</f>
-        <v>829.166666666667</v>
+        <v>2229.16666666667</v>
       </c>
       <c r="BK33" s="36" t="n">
         <f aca="false">-[4]Mar!$N$1+[4]Mar!$AI$1</f>
@@ -25371,7 +25407,7 @@
       <c r="BQ33" s="54"/>
       <c r="BR33" s="36" t="n">
         <f aca="false">SUM(BG33:BQ33)</f>
-        <v>-31679.5416666667</v>
+        <v>-25179.5416666667</v>
       </c>
       <c r="BS33" s="57"/>
       <c r="BT33" s="36" t="n">
@@ -25403,7 +25439,7 @@
       <c r="CB33" s="54"/>
       <c r="CC33" s="36" t="n">
         <f aca="false">SUM(BR33:CB33)</f>
-        <v>-32938.5833333333</v>
+        <v>-26438.5833333333</v>
       </c>
       <c r="CD33" s="57"/>
       <c r="CE33" s="36" t="n">
@@ -25435,7 +25471,7 @@
       <c r="CM33" s="54"/>
       <c r="CN33" s="36" t="n">
         <f aca="false">SUM(CC33:CM33)</f>
-        <v>-37672.25</v>
+        <v>-31172.25</v>
       </c>
       <c r="CO33" s="57"/>
       <c r="CP33" s="36" t="n">
@@ -25467,7 +25503,7 @@
       <c r="CX33" s="54"/>
       <c r="CY33" s="36" t="n">
         <f aca="false">SUM(CN33:CX33)</f>
-        <v>-41563.6666666667</v>
+        <v>-35063.6666666667</v>
       </c>
       <c r="CZ33" s="57"/>
       <c r="DA33" s="36" t="n">
@@ -25499,7 +25535,7 @@
       <c r="DI33" s="54"/>
       <c r="DJ33" s="36" t="n">
         <f aca="false">SUM(CY33:DI33)</f>
-        <v>-46718.4583333334</v>
+        <v>-40218.4583333334</v>
       </c>
       <c r="DK33" s="57"/>
       <c r="DL33" s="36" t="n">
@@ -25531,7 +25567,7 @@
       <c r="DT33" s="54"/>
       <c r="DU33" s="36" t="n">
         <f aca="false">SUM(DJ33:DT33)</f>
-        <v>-51712.375</v>
+        <v>-45212.375</v>
       </c>
       <c r="DV33" s="57"/>
       <c r="DW33" s="36" t="n">
@@ -25563,13 +25599,13 @@
       <c r="EE33" s="54"/>
       <c r="EF33" s="36" t="n">
         <f aca="false">SUM(DU33:EE33)</f>
-        <v>-56317.9583333334</v>
+        <v>-49817.9583333334</v>
       </c>
       <c r="EG33" s="54"/>
       <c r="EI33" s="54"/>
       <c r="EJ33" s="36" t="n">
         <f aca="false">SUM(EF33:EH33)</f>
-        <v>-56317.9583333334</v>
+        <v>-49817.9583333334</v>
       </c>
       <c r="EK33" s="54"/>
     </row>
@@ -25676,7 +25712,7 @@
       <c r="AN34" s="36"/>
       <c r="AO34" s="36" t="n">
         <f aca="false">[4]Jan!$AH$1</f>
-        <v>2673.2</v>
+        <v>1673.2</v>
       </c>
       <c r="AP34" s="36" t="n">
         <f aca="false">[5]Jan!$AH$1</f>
@@ -25698,7 +25734,7 @@
       <c r="AU34" s="54"/>
       <c r="AV34" s="36" t="n">
         <f aca="false">SUM(AK34:AU34)</f>
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="AW34" s="57"/>
       <c r="AX34" s="36"/>
@@ -25727,7 +25763,7 @@
       <c r="BF34" s="54"/>
       <c r="BG34" s="36" t="n">
         <f aca="false">SUM(AV34:BF34)</f>
-        <v>16308.17</v>
+        <v>15308.17</v>
       </c>
       <c r="BH34" s="57"/>
       <c r="BI34" s="36"/>
@@ -25756,14 +25792,14 @@
       <c r="BQ34" s="54"/>
       <c r="BR34" s="36" t="n">
         <f aca="false">SUM(BG34:BQ34)</f>
-        <v>16308.17</v>
+        <v>15308.17</v>
       </c>
       <c r="BS34" s="57"/>
       <c r="BT34" s="36"/>
       <c r="BU34" s="36"/>
       <c r="BV34" s="36" t="n">
         <f aca="false">[4]Apr!$AH$1</f>
-        <v>6173.2</v>
+        <v>1673.2</v>
       </c>
       <c r="BW34" s="36" t="n">
         <f aca="false">[5]Apr!$AH$1</f>
@@ -25785,7 +25821,7 @@
       <c r="CB34" s="54"/>
       <c r="CC34" s="36" t="n">
         <f aca="false">SUM(BR34:CB34)</f>
-        <v>20808.17</v>
+        <v>15308.17</v>
       </c>
       <c r="CD34" s="57"/>
       <c r="CE34" s="36"/>
@@ -25814,14 +25850,14 @@
       <c r="CM34" s="54"/>
       <c r="CN34" s="36" t="n">
         <f aca="false">SUM(CC34:CM34)</f>
-        <v>35264.67</v>
+        <v>29764.67</v>
       </c>
       <c r="CO34" s="57"/>
       <c r="CP34" s="36"/>
       <c r="CQ34" s="36"/>
       <c r="CR34" s="36" t="n">
         <f aca="false">[4]Jun!$AH$1</f>
-        <v>2273.2</v>
+        <v>1673.2</v>
       </c>
       <c r="CS34" s="36" t="n">
         <f aca="false">[5]Jun!$AH$1</f>
@@ -25843,7 +25879,7 @@
       <c r="CX34" s="54"/>
       <c r="CY34" s="36" t="n">
         <f aca="false">SUM(CN34:CX34)</f>
-        <v>35864.67</v>
+        <v>29764.67</v>
       </c>
       <c r="CZ34" s="57"/>
       <c r="DA34" s="36"/>
@@ -25872,7 +25908,7 @@
       <c r="DI34" s="54"/>
       <c r="DJ34" s="36" t="n">
         <f aca="false">SUM(CY34:DI34)</f>
-        <v>35864.67</v>
+        <v>29764.67</v>
       </c>
       <c r="DK34" s="57"/>
       <c r="DL34" s="36"/>
@@ -25901,7 +25937,7 @@
       <c r="DT34" s="54"/>
       <c r="DU34" s="36" t="n">
         <f aca="false">SUM(DJ34:DT34)</f>
-        <v>46782.17</v>
+        <v>40682.17</v>
       </c>
       <c r="DV34" s="57"/>
       <c r="DW34" s="36"/>
@@ -25930,13 +25966,13 @@
       <c r="EE34" s="54"/>
       <c r="EF34" s="36" t="n">
         <f aca="false">SUM(DU34:EE34)</f>
-        <v>46782.17</v>
+        <v>40682.17</v>
       </c>
       <c r="EG34" s="54"/>
       <c r="EI34" s="54"/>
       <c r="EJ34" s="36" t="n">
         <f aca="false">SUM(EF34:EH34)</f>
-        <v>46782.17</v>
+        <v>40682.17</v>
       </c>
       <c r="EK34" s="54"/>
     </row>
@@ -26112,7 +26148,7 @@
       <c r="BU35" s="36"/>
       <c r="BV35" s="36" t="n">
         <f aca="false">[4]Apr!$AK$1</f>
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="BW35" s="36" t="n">
         <f aca="false">[5]Apr!$AK$1</f>
@@ -26131,7 +26167,7 @@
       <c r="CB35" s="54"/>
       <c r="CC35" s="36" t="n">
         <f aca="false">SUM(BR35:CB35)</f>
-        <v>-4500</v>
+        <v>0</v>
       </c>
       <c r="CD35" s="57"/>
       <c r="CE35" s="36"/>
@@ -26157,7 +26193,7 @@
       <c r="CM35" s="54"/>
       <c r="CN35" s="36" t="n">
         <f aca="false">SUM(CC35:CM35)</f>
-        <v>-4500</v>
+        <v>0</v>
       </c>
       <c r="CO35" s="57"/>
       <c r="CP35" s="36"/>
@@ -26183,7 +26219,7 @@
       <c r="CX35" s="54"/>
       <c r="CY35" s="36" t="n">
         <f aca="false">SUM(CN35:CX35)</f>
-        <v>-4500</v>
+        <v>0</v>
       </c>
       <c r="CZ35" s="57"/>
       <c r="DA35" s="36"/>
@@ -26209,7 +26245,7 @@
       <c r="DI35" s="54"/>
       <c r="DJ35" s="36" t="n">
         <f aca="false">SUM(CY35:DI35)</f>
-        <v>-4500</v>
+        <v>0</v>
       </c>
       <c r="DK35" s="57"/>
       <c r="DL35" s="36"/>
@@ -26235,7 +26271,7 @@
       <c r="DT35" s="54"/>
       <c r="DU35" s="36" t="n">
         <f aca="false">SUM(DJ35:DT35)</f>
-        <v>-4500</v>
+        <v>0</v>
       </c>
       <c r="DV35" s="57"/>
       <c r="DW35" s="36"/>
@@ -26259,12 +26295,12 @@
       <c r="EC35" s="36"/>
       <c r="ED35" s="36" t="n">
         <f aca="false">-CorporationTax!K35</f>
-        <v>-34521.272927469</v>
+        <v>-29221.272927469</v>
       </c>
       <c r="EE35" s="54"/>
       <c r="EF35" s="36" t="n">
         <f aca="false">SUM(DU35:EE35)</f>
-        <v>-39021.272927469</v>
+        <v>-29221.272927469</v>
       </c>
       <c r="EG35" s="54"/>
       <c r="EH35" s="36" t="n">
@@ -26274,7 +26310,7 @@
       <c r="EI35" s="54"/>
       <c r="EJ35" s="36" t="n">
         <f aca="false">SUM(EF35:EH35)</f>
-        <v>-38956.7667546295</v>
+        <v>-29156.7667546295</v>
       </c>
       <c r="EK35" s="54"/>
     </row>
@@ -28052,12 +28088,12 @@
       <c r="EG43" s="54"/>
       <c r="EH43" s="36" t="n">
         <f aca="false">-'PubP&amp;L'!F54</f>
-        <v>-124658.624912037</v>
+        <v>-127958.624912037</v>
       </c>
       <c r="EI43" s="54"/>
       <c r="EJ43" s="36" t="n">
         <f aca="false">SUM(EF43:EH43)</f>
-        <v>-145360.624912037</v>
+        <v>-148660.624912037</v>
       </c>
       <c r="EK43" s="54"/>
     </row>
@@ -28686,18 +28722,18 @@
       <c r="EC47" s="36"/>
       <c r="ED47" s="36" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>34521.272927469</v>
+        <v>29221.272927469</v>
       </c>
       <c r="EE47" s="54"/>
       <c r="EF47" s="36" t="n">
         <f aca="false">SUM(DU47:EE47)</f>
-        <v>34521.272927469</v>
+        <v>29221.272927469</v>
       </c>
       <c r="EG47" s="54"/>
       <c r="EI47" s="54"/>
       <c r="EJ47" s="36" t="n">
         <f aca="false">SUM(EF47:EH47)</f>
-        <v>34521.272927469</v>
+        <v>29221.272927469</v>
       </c>
       <c r="EK47" s="54"/>
     </row>
@@ -29066,12 +29102,12 @@
       <c r="EG49" s="54"/>
       <c r="EH49" s="36" t="n">
         <f aca="false">'PubP&amp;L'!F54</f>
-        <v>124658.624912037</v>
+        <v>127958.624912037</v>
       </c>
       <c r="EI49" s="54"/>
       <c r="EJ49" s="36" t="n">
         <f aca="false">SUM(EF49:EH49)</f>
-        <v>124658.624912037</v>
+        <v>127958.624912037</v>
       </c>
       <c r="EK49" s="54"/>
     </row>
@@ -36269,11 +36305,11 @@
       <c r="AC83" s="36"/>
       <c r="AD83" s="36" t="n">
         <f aca="false">[4]Dec!$AD$1</f>
-        <v>250</v>
+        <v>2250</v>
       </c>
       <c r="AE83" s="36" t="n">
         <f aca="false">[5]Dec!$AD$1</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AF83" s="36" t="n">
         <f aca="false">[6]Dec!$AD$1</f>
@@ -36347,11 +36383,11 @@
       <c r="BJ83" s="36"/>
       <c r="BK83" s="36" t="n">
         <f aca="false">[4]Mar!$AD$1</f>
-        <v>208</v>
+        <v>1308</v>
       </c>
       <c r="BL83" s="36" t="n">
         <f aca="false">[5]Mar!$AD$1</f>
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="BM83" s="36" t="n">
         <f aca="false">[6]Mar!$AD$1</f>
@@ -37208,12 +37244,12 @@
       <c r="L87" s="36"/>
       <c r="M87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="N87" s="57"/>
       <c r="O87" s="36" t="n">
         <f aca="false">SUM(D87:N87)</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="P87" s="57"/>
       <c r="Q87" s="36"/>
@@ -37225,12 +37261,12 @@
       <c r="W87" s="36"/>
       <c r="X87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="Y87" s="54"/>
       <c r="Z87" s="36" t="n">
         <f aca="false">SUM(O87:Y87)</f>
-        <v>1956.66666666667</v>
+        <v>2290</v>
       </c>
       <c r="AA87" s="57"/>
       <c r="AB87" s="36"/>
@@ -37242,12 +37278,12 @@
       <c r="AH87" s="36"/>
       <c r="AI87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="AJ87" s="54"/>
       <c r="AK87" s="36" t="n">
         <f aca="false">SUM(Z87:AJ87)</f>
-        <v>2935</v>
+        <v>3435</v>
       </c>
       <c r="AL87" s="57"/>
       <c r="AM87" s="36"/>
@@ -37259,12 +37295,12 @@
       <c r="AS87" s="36"/>
       <c r="AT87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="AU87" s="54"/>
       <c r="AV87" s="36" t="n">
         <f aca="false">SUM(AK87:AU87)</f>
-        <v>3913.33333333333</v>
+        <v>4580</v>
       </c>
       <c r="AW87" s="57"/>
       <c r="AX87" s="36"/>
@@ -37276,12 +37312,12 @@
       <c r="BD87" s="36"/>
       <c r="BE87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="BF87" s="54"/>
       <c r="BG87" s="36" t="n">
         <f aca="false">SUM(AV87:BF87)</f>
-        <v>4891.66666666667</v>
+        <v>5725</v>
       </c>
       <c r="BH87" s="57"/>
       <c r="BI87" s="36"/>
@@ -37293,12 +37329,12 @@
       <c r="BO87" s="36"/>
       <c r="BP87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="BQ87" s="54"/>
       <c r="BR87" s="36" t="n">
         <f aca="false">SUM(BG87:BQ87)</f>
-        <v>5870</v>
+        <v>6870</v>
       </c>
       <c r="BS87" s="57"/>
       <c r="BT87" s="36"/>
@@ -37310,12 +37346,12 @@
       <c r="BZ87" s="36"/>
       <c r="CA87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="CB87" s="54"/>
       <c r="CC87" s="36" t="n">
         <f aca="false">SUM(BR87:CB87)</f>
-        <v>6848.33333333333</v>
+        <v>8015</v>
       </c>
       <c r="CD87" s="57"/>
       <c r="CE87" s="36"/>
@@ -37327,12 +37363,12 @@
       <c r="CK87" s="36"/>
       <c r="CL87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="CM87" s="54"/>
       <c r="CN87" s="36" t="n">
         <f aca="false">SUM(CC87:CM87)</f>
-        <v>7826.66666666667</v>
+        <v>9160</v>
       </c>
       <c r="CO87" s="57"/>
       <c r="CP87" s="36"/>
@@ -37344,12 +37380,12 @@
       <c r="CV87" s="36"/>
       <c r="CW87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="CX87" s="54"/>
       <c r="CY87" s="36" t="n">
         <f aca="false">SUM(CN87:CX87)</f>
-        <v>8805</v>
+        <v>10305</v>
       </c>
       <c r="CZ87" s="57"/>
       <c r="DA87" s="36"/>
@@ -37361,12 +37397,12 @@
       <c r="DG87" s="36"/>
       <c r="DH87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="DI87" s="54"/>
       <c r="DJ87" s="36" t="n">
         <f aca="false">SUM(CY87:DI87)</f>
-        <v>9783.33333333333</v>
+        <v>11450</v>
       </c>
       <c r="DK87" s="57"/>
       <c r="DL87" s="36"/>
@@ -37378,12 +37414,12 @@
       <c r="DR87" s="36"/>
       <c r="DS87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="DT87" s="54"/>
       <c r="DU87" s="36" t="n">
         <f aca="false">SUM(DJ87:DT87)</f>
-        <v>10761.6666666667</v>
+        <v>12595</v>
       </c>
       <c r="DV87" s="57"/>
       <c r="DW87" s="36"/>
@@ -37395,18 +37431,18 @@
       <c r="EC87" s="36"/>
       <c r="ED87" s="36" t="n">
         <f aca="false">[1]Schedule!$I$1/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="EE87" s="54"/>
       <c r="EF87" s="36" t="n">
         <f aca="false">SUM(DU87:EE87)</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
       <c r="EG87" s="54"/>
       <c r="EI87" s="54"/>
       <c r="EJ87" s="36" t="n">
         <f aca="false">SUM(EF87:EH87)</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
       <c r="EK87" s="54"/>
     </row>
@@ -38174,7 +38210,7 @@
       <c r="N91" s="54"/>
       <c r="O91" s="36" t="n">
         <f aca="false">SUM(O4:O90)</f>
-        <v>3.44471118296497E-011</v>
+        <v>3.43902684107889E-011</v>
       </c>
       <c r="P91" s="54"/>
       <c r="Q91" s="36" t="n">
@@ -38212,7 +38248,7 @@
       <c r="Y91" s="54"/>
       <c r="Z91" s="36" t="n">
         <f aca="false">SUM(Z4:Z90)</f>
-        <v>6.94626578479074E-011</v>
+        <v>6.93489710101858E-011</v>
       </c>
       <c r="AA91" s="54"/>
       <c r="AB91" s="36" t="n">
@@ -38288,7 +38324,7 @@
       <c r="AU91" s="54"/>
       <c r="AV91" s="36" t="n">
         <f aca="false">SUM(AV4:AV90)</f>
-        <v>1.4210854715202E-010</v>
+        <v>1.41653799801134E-010</v>
       </c>
       <c r="AW91" s="54"/>
       <c r="AX91" s="36" t="n">
@@ -38326,7 +38362,7 @@
       <c r="BF91" s="54"/>
       <c r="BG91" s="36" t="n">
         <f aca="false">SUM(BG4:BG90)</f>
-        <v>1.90993887372315E-010</v>
+        <v>1.86901161214337E-010</v>
       </c>
       <c r="BH91" s="54"/>
       <c r="BI91" s="36" t="n">
@@ -38364,7 +38400,7 @@
       <c r="BQ91" s="54"/>
       <c r="BR91" s="36" t="n">
         <f aca="false">SUM(BR4:BR90)</f>
-        <v>2.09865902434103E-010</v>
+        <v>2.24190443987027E-010</v>
       </c>
       <c r="BS91" s="54"/>
       <c r="BT91" s="36" t="n">
@@ -38377,7 +38413,7 @@
       </c>
       <c r="BV91" s="36" t="n">
         <f aca="false">SUM(BV4:BV90)</f>
-        <v>2.72848410531878E-012</v>
+        <v>2.95585778076202E-012</v>
       </c>
       <c r="BW91" s="36" t="n">
         <f aca="false">SUM(BW4:BW90)</f>
@@ -38402,7 +38438,7 @@
       <c r="CB91" s="54"/>
       <c r="CC91" s="36" t="n">
         <f aca="false">SUM(CC4:CC90)</f>
-        <v>2.44426701101474E-010</v>
+        <v>2.69892552751116E-010</v>
       </c>
       <c r="CD91" s="54"/>
       <c r="CE91" s="36" t="n">
@@ -38440,7 +38476,7 @@
       <c r="CM91" s="54"/>
       <c r="CN91" s="36" t="n">
         <f aca="false">SUM(CN4:CN90)</f>
-        <v>2.50111042987555E-010</v>
+        <v>2.86945578409359E-010</v>
       </c>
       <c r="CO91" s="54"/>
       <c r="CP91" s="36" t="n">
@@ -38453,7 +38489,7 @@
       </c>
       <c r="CR91" s="36" t="n">
         <f aca="false">SUM(CR4:CR90)</f>
-        <v>-9.09494701772928E-013</v>
+        <v>-6.82121026329696E-013</v>
       </c>
       <c r="CS91" s="36" t="n">
         <f aca="false">SUM(CS4:CS90)</f>
@@ -38478,7 +38514,7 @@
       <c r="CX91" s="54"/>
       <c r="CY91" s="36" t="n">
         <f aca="false">SUM(CY4:CY90)</f>
-        <v>2.56022758549079E-010</v>
+        <v>3.06954461848363E-010</v>
       </c>
       <c r="CZ91" s="54"/>
       <c r="DA91" s="36" t="n">
@@ -38516,7 +38552,7 @@
       <c r="DI91" s="54"/>
       <c r="DJ91" s="36" t="n">
         <f aca="false">SUM(DJ4:DJ90)</f>
-        <v>2.58751242654398E-010</v>
+        <v>3.09228198602796E-010</v>
       </c>
       <c r="DK91" s="54"/>
       <c r="DL91" s="36" t="n">
@@ -38554,7 +38590,7 @@
       <c r="DT91" s="54"/>
       <c r="DU91" s="36" t="n">
         <f aca="false">SUM(DU4:DU90)</f>
-        <v>2.67618815996684E-010</v>
+        <v>3.10365066980012E-010</v>
       </c>
       <c r="DV91" s="54"/>
       <c r="DW91" s="36" t="n">
@@ -38592,7 +38628,7 @@
       <c r="EE91" s="54"/>
       <c r="EF91" s="36" t="n">
         <f aca="false">SUM(EF4:EF90)</f>
-        <v>2.72848410531878E-010</v>
+        <v>3.15594661515206E-010</v>
       </c>
       <c r="EG91" s="54"/>
       <c r="EH91" s="36" t="n">
@@ -38602,7 +38638,7 @@
       <c r="EI91" s="54"/>
       <c r="EJ91" s="36" t="n">
         <f aca="false">SUM(EJ4:EJ90)</f>
-        <v>2.79214873444289E-010</v>
+        <v>3.17413650918752E-010</v>
       </c>
       <c r="EK91" s="54"/>
     </row>
@@ -40952,55 +40988,55 @@
       </c>
       <c r="B40" s="71" t="n">
         <f aca="false">SUM(C40:N40)</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
       <c r="C40" s="79" t="n">
         <f aca="false">TrialBalance!O87-0</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="D40" s="72" t="n">
         <f aca="false">TrialBalance!Z87-C40</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="E40" s="72" t="n">
         <f aca="false">TrialBalance!AK87-SUM(C40:D40)</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="F40" s="72" t="n">
         <f aca="false">TrialBalance!AV87-SUM(C40:E40)</f>
-        <v>978.333333333334</v>
+        <v>1145</v>
       </c>
       <c r="G40" s="72" t="n">
         <f aca="false">TrialBalance!BG87-SUM(C40:F40)</f>
-        <v>978.333333333334</v>
+        <v>1145</v>
       </c>
       <c r="H40" s="72" t="n">
         <f aca="false">TrialBalance!BR87-SUM(C40:G40)</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="I40" s="72" t="n">
         <f aca="false">TrialBalance!CC87-SUM(C40:H40)</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="J40" s="72" t="n">
         <f aca="false">TrialBalance!CN87-SUM(C40:I40)</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="K40" s="72" t="n">
         <f aca="false">TrialBalance!CY87-SUM(C40:J40)</f>
-        <v>978.333333333334</v>
+        <v>1145</v>
       </c>
       <c r="L40" s="72" t="n">
         <f aca="false">TrialBalance!DJ87-SUM(C40:K40)</f>
-        <v>978.333333333334</v>
+        <v>1145</v>
       </c>
       <c r="M40" s="72" t="n">
         <f aca="false">TrialBalance!DU87-SUM(C40:L40)</f>
-        <v>978.333333333334</v>
+        <v>1145</v>
       </c>
       <c r="N40" s="72" t="n">
         <f aca="false">TrialBalance!EF87-SUM(C40:M40)</f>
-        <v>978.333333333334</v>
+        <v>1145</v>
       </c>
       <c r="O40" s="68"/>
     </row>
@@ -41010,55 +41046,55 @@
       </c>
       <c r="B41" s="71" t="n">
         <f aca="false">SUM(B18:B40)</f>
-        <v>148656.275</v>
+        <v>150656.275</v>
       </c>
       <c r="C41" s="74" t="n">
         <f aca="false">SUM(C18:C40)</f>
-        <v>11839.7416666667</v>
+        <v>12006.4083333333</v>
       </c>
       <c r="D41" s="71" t="n">
         <f aca="false">SUM(D18:D40)</f>
-        <v>11382.8666666667</v>
+        <v>11549.5333333333</v>
       </c>
       <c r="E41" s="71" t="n">
         <f aca="false">SUM(E18:E40)</f>
-        <v>13411.2</v>
+        <v>13577.8666666667</v>
       </c>
       <c r="F41" s="71" t="n">
         <f aca="false">SUM(F18:F40)</f>
-        <v>14059.7416666667</v>
+        <v>14226.4083333333</v>
       </c>
       <c r="G41" s="71" t="n">
         <f aca="false">SUM(G18:G40)</f>
-        <v>11301.4083333333</v>
+        <v>11468.075</v>
       </c>
       <c r="H41" s="71" t="n">
         <f aca="false">SUM(H18:H40)</f>
-        <v>13364.2</v>
+        <v>13530.8666666667</v>
       </c>
       <c r="I41" s="71" t="n">
         <f aca="false">SUM(I18:I40)</f>
-        <v>13518.4916666667</v>
+        <v>13685.1583333333</v>
       </c>
       <c r="J41" s="71" t="n">
         <f aca="false">SUM(J18:J40)</f>
-        <v>10700.3666666667</v>
+        <v>10867.0333333333</v>
       </c>
       <c r="K41" s="71" t="n">
         <f aca="false">SUM(K18:K40)</f>
-        <v>15723.6166666667</v>
+        <v>15890.2833333333</v>
       </c>
       <c r="L41" s="71" t="n">
         <f aca="false">SUM(L18:L40)</f>
-        <v>11369.7416666667</v>
+        <v>11536.4083333333</v>
       </c>
       <c r="M41" s="71" t="n">
         <f aca="false">SUM(M18:M40)</f>
-        <v>11194.1166666667</v>
+        <v>11360.7833333333</v>
       </c>
       <c r="N41" s="71" t="n">
         <f aca="false">SUM(N18:N40)</f>
-        <v>10790.7833333333</v>
+        <v>10957.45</v>
       </c>
       <c r="O41" s="68"/>
     </row>
@@ -41085,55 +41121,55 @@
       </c>
       <c r="B43" s="71" t="n">
         <f aca="false">B16-B41</f>
-        <v>173840.391666666</v>
+        <v>171840.391666666</v>
       </c>
       <c r="C43" s="71" t="n">
         <f aca="false">C16-C41</f>
-        <v>14996.0916666666</v>
+        <v>14829.425</v>
       </c>
       <c r="D43" s="71" t="n">
         <f aca="false">D16-D41</f>
-        <v>15073.9666666666</v>
+        <v>14907.3</v>
       </c>
       <c r="E43" s="71" t="n">
         <f aca="false">E16-E41</f>
-        <v>10721.9666666666</v>
+        <v>10555.3</v>
       </c>
       <c r="F43" s="71" t="n">
         <f aca="false">F16-F41</f>
-        <v>13097.0916666666</v>
+        <v>12930.425</v>
       </c>
       <c r="G43" s="71" t="n">
         <f aca="false">G16-G41</f>
-        <v>17663.7583333333</v>
+        <v>17497.0916666666</v>
       </c>
       <c r="H43" s="71" t="n">
         <f aca="false">H16-H41</f>
-        <v>13810.6333333333</v>
+        <v>13643.9666666666</v>
       </c>
       <c r="I43" s="71" t="n">
         <f aca="false">I16-I41</f>
-        <v>15063.3416666666</v>
+        <v>14896.675</v>
       </c>
       <c r="J43" s="71" t="n">
         <f aca="false">J16-J41</f>
-        <v>15256.4666666666</v>
+        <v>15089.8</v>
       </c>
       <c r="K43" s="71" t="n">
         <f aca="false">K16-K41</f>
-        <v>10576.2166666666</v>
+        <v>10409.55</v>
       </c>
       <c r="L43" s="71" t="n">
         <f aca="false">L16-L41</f>
-        <v>17187.0916666666</v>
+        <v>17020.425</v>
       </c>
       <c r="M43" s="71" t="n">
         <f aca="false">M16-M41</f>
-        <v>16411.7166666666</v>
+        <v>16245.05</v>
       </c>
       <c r="N43" s="71" t="n">
         <f aca="false">N16-N41</f>
-        <v>13982.05</v>
+        <v>13815.3833333333</v>
       </c>
       <c r="O43" s="68"/>
     </row>
@@ -41201,55 +41237,55 @@
       </c>
       <c r="B45" s="71" t="n">
         <f aca="false">B43+B44</f>
-        <v>174115.391666666</v>
+        <v>172115.391666666</v>
       </c>
       <c r="C45" s="71" t="n">
         <f aca="false">C43+C44</f>
-        <v>14996.0916666666</v>
+        <v>14829.425</v>
       </c>
       <c r="D45" s="71" t="n">
         <f aca="false">D43+D44</f>
-        <v>15073.9666666666</v>
+        <v>14907.3</v>
       </c>
       <c r="E45" s="71" t="n">
         <f aca="false">E43+E44</f>
-        <v>10721.9666666666</v>
+        <v>10555.3</v>
       </c>
       <c r="F45" s="71" t="n">
         <f aca="false">F43+F44</f>
-        <v>13097.0916666666</v>
+        <v>12930.425</v>
       </c>
       <c r="G45" s="71" t="n">
         <f aca="false">G43+G44</f>
-        <v>17663.7583333333</v>
+        <v>17497.0916666666</v>
       </c>
       <c r="H45" s="71" t="n">
         <f aca="false">H43+H44</f>
-        <v>13935.6333333333</v>
+        <v>13768.9666666666</v>
       </c>
       <c r="I45" s="71" t="n">
         <f aca="false">I43+I44</f>
-        <v>15063.3416666666</v>
+        <v>14896.675</v>
       </c>
       <c r="J45" s="71" t="n">
         <f aca="false">J43+J44</f>
-        <v>15256.4666666666</v>
+        <v>15089.8</v>
       </c>
       <c r="K45" s="71" t="n">
         <f aca="false">K43+K44</f>
-        <v>10576.2166666666</v>
+        <v>10409.55</v>
       </c>
       <c r="L45" s="71" t="n">
         <f aca="false">L43+L44</f>
-        <v>17187.0916666666</v>
+        <v>17020.425</v>
       </c>
       <c r="M45" s="71" t="n">
         <f aca="false">M43+M44</f>
-        <v>16411.7166666666</v>
+        <v>16245.05</v>
       </c>
       <c r="N45" s="71" t="n">
         <f aca="false">N43+N44</f>
-        <v>14132.05</v>
+        <v>13965.3833333333</v>
       </c>
       <c r="O45" s="68"/>
     </row>
@@ -42161,7 +42197,7 @@
       <c r="D43" s="101"/>
       <c r="E43" s="86" t="n">
         <f aca="false">TrialBalance!EJ87</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
       <c r="H43" s="89"/>
       <c r="I43" s="89"/>
@@ -42184,7 +42220,7 @@
       <c r="E44" s="103"/>
       <c r="F44" s="104" t="n">
         <f aca="false">SUM(E21:E43)</f>
-        <v>148656.275</v>
+        <v>150656.275</v>
       </c>
       <c r="H44" s="89"/>
       <c r="I44" s="89"/>
@@ -42220,7 +42256,7 @@
       <c r="E46" s="103"/>
       <c r="F46" s="104" t="n">
         <f aca="false">F18-F44</f>
-        <v>173840.391666666</v>
+        <v>171840.391666666</v>
       </c>
       <c r="H46" s="89"/>
       <c r="I46" s="89"/>
@@ -42275,7 +42311,7 @@
       <c r="E49" s="103"/>
       <c r="F49" s="104" t="n">
         <f aca="false">F46+F48</f>
-        <v>174179.897839506</v>
+        <v>172179.897839506</v>
       </c>
       <c r="H49" s="89"/>
       <c r="I49" s="89"/>
@@ -42296,7 +42332,7 @@
       <c r="D50" s="101"/>
       <c r="F50" s="86" t="n">
         <f aca="false">TrialBalance!EJ47</f>
-        <v>34521.272927469</v>
+        <v>29221.272927469</v>
       </c>
       <c r="H50" s="89"/>
       <c r="I50" s="89"/>
@@ -42319,7 +42355,7 @@
       <c r="E51" s="103"/>
       <c r="F51" s="104" t="n">
         <f aca="false">F49-F50</f>
-        <v>139658.624912037</v>
+        <v>142958.624912037</v>
       </c>
       <c r="H51" s="89"/>
       <c r="I51" s="89"/>
@@ -42380,7 +42416,7 @@
       </c>
       <c r="F54" s="104" t="n">
         <f aca="false">F51-F52</f>
-        <v>124658.624912037</v>
+        <v>127958.624912037</v>
       </c>
       <c r="H54" s="89"/>
       <c r="I54" s="89"/>
@@ -42503,7 +42539,7 @@
       <c r="E6" s="115"/>
       <c r="F6" s="116" t="n">
         <f aca="false">SUM(TrialBalance!EJ6:EJ17)</f>
-        <v>30990</v>
+        <v>48990</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42557,7 +42593,7 @@
       </c>
       <c r="E11" s="115" t="n">
         <f aca="false">TrialBalance!EJ20</f>
-        <v>10400</v>
+        <v>7900</v>
       </c>
       <c r="F11" s="115"/>
     </row>
@@ -42588,7 +42624,7 @@
       <c r="D13" s="117"/>
       <c r="E13" s="116" t="n">
         <f aca="false">SUM(E10:E12)</f>
-        <v>209395.43</v>
+        <v>206895.43</v>
       </c>
       <c r="F13" s="118"/>
     </row>
@@ -42619,7 +42655,7 @@
       </c>
       <c r="E16" s="115" t="n">
         <f aca="false">-SUM(TrialBalance!EJ28:EJ31)</f>
-        <v>-11567.75</v>
+        <v>12432.25</v>
       </c>
       <c r="F16" s="115"/>
     </row>
@@ -42634,7 +42670,7 @@
       </c>
       <c r="E17" s="115" t="n">
         <f aca="false">-TrialBalance!EJ35</f>
-        <v>38956.7667546295</v>
+        <v>29156.7667546295</v>
       </c>
       <c r="F17" s="115"/>
     </row>
@@ -42649,7 +42685,7 @@
       </c>
       <c r="E18" s="115" t="n">
         <f aca="false">-SUM(TrialBalance!EJ32:EJ34)</f>
-        <v>9535.78833333335</v>
+        <v>7535.78833333337</v>
       </c>
       <c r="F18" s="115"/>
     </row>
@@ -42682,7 +42718,7 @@
       <c r="D20" s="117"/>
       <c r="E20" s="116" t="n">
         <f aca="false">SUM(E16:E19)</f>
-        <v>36924.8050879629</v>
+        <v>49124.8050879629</v>
       </c>
       <c r="F20" s="118"/>
       <c r="G20" s="120"/>
@@ -42709,7 +42745,7 @@
       <c r="E22" s="118"/>
       <c r="F22" s="116" t="n">
         <f aca="false">E13-E20</f>
-        <v>172470.624912037</v>
+        <v>157770.624912037</v>
       </c>
       <c r="G22" s="120"/>
     </row>
@@ -42762,7 +42798,7 @@
       <c r="E26" s="118"/>
       <c r="F26" s="116" t="n">
         <f aca="false">SUM(F6:F25)</f>
-        <v>203460.624912037</v>
+        <v>206760.624912037</v>
       </c>
       <c r="G26" s="120"/>
     </row>
@@ -42858,7 +42894,7 @@
       </c>
       <c r="F33" s="116" t="n">
         <f aca="false">F26-F31</f>
-        <v>145460.624912037</v>
+        <v>148760.624912037</v>
       </c>
       <c r="G33" s="120"/>
     </row>
@@ -42908,7 +42944,7 @@
       <c r="E37" s="115"/>
       <c r="F37" s="115" t="n">
         <f aca="false">-TrialBalance!EJ43</f>
-        <v>145360.624912037</v>
+        <v>148660.624912037</v>
       </c>
       <c r="G37" s="87"/>
       <c r="O37" s="87"/>
@@ -42948,7 +42984,7 @@
       </c>
       <c r="F39" s="116" t="n">
         <f aca="false">SUM(F36:F38)</f>
-        <v>145460.624912037</v>
+        <v>148760.624912037</v>
       </c>
       <c r="G39" s="120"/>
     </row>
@@ -43318,7 +43354,7 @@
       </c>
       <c r="C9" s="108" t="n">
         <f aca="false">IF([1]Schedule!$E$75&gt;0,[1]Schedule!$E$75,0)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="D9" s="108" t="n">
         <f aca="false">IF([1]Schedule!$E$83&gt;0,[1]Schedule!$E$83,0)</f>
@@ -43334,7 +43370,7 @@
       </c>
       <c r="G9" s="108" t="n">
         <f aca="false">SUM(B9:F9)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43377,7 +43413,7 @@
       </c>
       <c r="C11" s="108" t="n">
         <f aca="false">C8+C9-C10</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="D11" s="108" t="n">
         <f aca="false">D8+D9-D10</f>
@@ -43393,7 +43429,7 @@
       </c>
       <c r="G11" s="108" t="n">
         <f aca="false">G8+G9-G10</f>
-        <v>35500</v>
+        <v>55500</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43455,7 +43491,7 @@
       </c>
       <c r="C15" s="108" t="n">
         <f aca="false">IF(([1]Schedule!$I$22+[1]Schedule!$I$75)&gt;0,[1]Schedule!$I$22+[1]Schedule!$I$75,0)</f>
-        <v>3250</v>
+        <v>5250</v>
       </c>
       <c r="D15" s="108" t="n">
         <f aca="false">IF(([1]Schedule!$I$30+[1]Schedule!$I$83)&gt;0,[1]Schedule!$I$30+[1]Schedule!$I$83,0)</f>
@@ -43471,7 +43507,7 @@
       </c>
       <c r="G15" s="108" t="n">
         <f aca="false">SUM(B15:F15)</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43514,7 +43550,7 @@
       </c>
       <c r="C17" s="108" t="n">
         <f aca="false">C14-C16+C15</f>
-        <v>3250</v>
+        <v>5250</v>
       </c>
       <c r="D17" s="108" t="n">
         <f aca="false">D14-D16+D15</f>
@@ -43530,7 +43566,7 @@
       </c>
       <c r="G17" s="108" t="n">
         <f aca="false">SUM(B17:F17)</f>
-        <v>4510</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43563,7 +43599,7 @@
       </c>
       <c r="C20" s="134" t="n">
         <f aca="false">C11-C17</f>
-        <v>29250</v>
+        <v>47250</v>
       </c>
       <c r="D20" s="134" t="n">
         <f aca="false">D11-D17</f>
@@ -43579,7 +43615,7 @@
       </c>
       <c r="G20" s="134" t="n">
         <f aca="false">G11-G17</f>
-        <v>30990</v>
+        <v>48990</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43710,7 +43746,7 @@
       <c r="C41" s="137"/>
       <c r="D41" s="136" t="n">
         <f aca="false">CorporationTax!K35</f>
-        <v>34521.272927469</v>
+        <v>29221.272927469</v>
       </c>
       <c r="G41" s="89"/>
     </row>
@@ -44681,7 +44717,7 @@
       <c r="J5" s="178"/>
       <c r="K5" s="191" t="n">
         <f aca="false">'PubP&amp;L'!F46</f>
-        <v>173840.391666666</v>
+        <v>171840.391666666</v>
       </c>
       <c r="L5" s="185"/>
     </row>
@@ -44731,7 +44767,7 @@
       <c r="H8" s="179"/>
       <c r="I8" s="194" t="n">
         <f aca="false">IF(TrialBalance!EJ87&gt;0,TrialBalance!EJ87," ")</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
       <c r="J8" s="178"/>
       <c r="K8" s="192"/>
@@ -44766,7 +44802,7 @@
       <c r="J10" s="178"/>
       <c r="K10" s="191" t="n">
         <f aca="false">SUM(I6:I9)</f>
-        <v>14240</v>
+        <v>16240</v>
       </c>
       <c r="L10" s="177"/>
     </row>
@@ -44855,7 +44891,7 @@
       <c r="H15" s="199"/>
       <c r="I15" s="200" t="n">
         <f aca="false">IF(K79&gt;0,K79,0)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="J15" s="178"/>
       <c r="K15" s="201" t="s">
@@ -44976,7 +45012,7 @@
       <c r="J20" s="178"/>
       <c r="K20" s="191" t="n">
         <f aca="false">SUM(I14:I19)</f>
-        <v>44000</v>
+        <v>64000</v>
       </c>
       <c r="L20" s="185"/>
     </row>
@@ -45009,7 +45045,7 @@
       <c r="J22" s="178"/>
       <c r="K22" s="209" t="n">
         <f aca="false">K12-K20</f>
-        <v>144080.391666666</v>
+        <v>124080.391666666</v>
       </c>
       <c r="L22" s="185"/>
     </row>
@@ -45111,7 +45147,7 @@
       <c r="J28" s="178"/>
       <c r="K28" s="209" t="n">
         <f aca="false">K22+K24-K26</f>
-        <v>144419.897839506</v>
+        <v>124419.897839506</v>
       </c>
       <c r="L28" s="185"/>
     </row>
@@ -45209,7 +45245,7 @@
       </c>
       <c r="F33" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A33/A35,0)</f>
-        <v>72012.1134432604</v>
+        <v>62039.5107035344</v>
       </c>
       <c r="G33" s="224" t="n">
         <f aca="false">IF(F33&lt;=Admin!$P$12*A33/A35,Admin!P6,Admin!$P$8)</f>
@@ -45218,16 +45254,16 @@
       <c r="H33" s="224"/>
       <c r="I33" s="225" t="n">
         <f aca="false">J33-L33</f>
-        <v>17213.3470487654</v>
+        <v>14570.607322738</v>
       </c>
       <c r="J33" s="226" t="n">
         <f aca="false">F33*G33/100</f>
-        <v>18003.0283608151</v>
+        <v>15509.8776758836</v>
       </c>
       <c r="K33" s="178"/>
       <c r="L33" s="177" t="n">
         <f aca="false">IF(AND(F33&gt;Admin!$P$12*A33/A35,F33&lt;Admin!$P$13*A33/A35),(Admin!$P$13*A33/A35-F33)*Admin!$P$9,0)</f>
-        <v>789.681312049724</v>
+        <v>939.270353145614</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45252,7 +45288,7 @@
       </c>
       <c r="F34" s="186" t="n">
         <f aca="false">IF(K28&gt;0,K28*A34/A35,0)</f>
-        <v>72407.7843962454</v>
+        <v>62380.3871359714</v>
       </c>
       <c r="G34" s="224" t="n">
         <f aca="false">IF(F34&lt;=Admin!$P$12*A34/A35,Admin!P7,Admin!$P$8)</f>
@@ -45261,16 +45297,16 @@
       <c r="H34" s="224"/>
       <c r="I34" s="225" t="n">
         <f aca="false">J34-L34</f>
-        <v>17307.9258787037</v>
+        <v>14650.6656047311</v>
       </c>
       <c r="J34" s="226" t="n">
         <f aca="false">F34*G34/100</f>
-        <v>18101.9460990613</v>
+        <v>15595.0967839928</v>
       </c>
       <c r="K34" s="178"/>
       <c r="L34" s="177" t="n">
         <f aca="false">IF(AND(F34&gt;Admin!$P$12*A34/A35,F34&lt;Admin!$P$13*A34/A35),(Admin!$P$13*A34/A35-F34)*Admin!$P$9,0)</f>
-        <v>794.020220357689</v>
+        <v>944.431179261799</v>
       </c>
     </row>
     <row r="35" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45291,7 +45327,7 @@
       <c r="J35" s="227"/>
       <c r="K35" s="228" t="n">
         <f aca="false">SUM(I33:I34)</f>
-        <v>34521.272927469</v>
+        <v>29221.272927469</v>
       </c>
       <c r="L35" s="185"/>
     </row>
@@ -45357,7 +45393,7 @@
       <c r="J39" s="178"/>
       <c r="K39" s="232" t="n">
         <f aca="false">K35-K37</f>
-        <v>34456.7667546295</v>
+        <v>29156.7667546295</v>
       </c>
       <c r="L39" s="185"/>
     </row>
@@ -45510,22 +45546,22 @@
     <row r="50" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="241" t="n">
         <f aca="false">IF([1]Schedule!$E$68&gt;0,[1]Schedule!$B$68," ")</f>
-        <v>46037</v>
+        <v>45992</v>
       </c>
       <c r="B50" s="87" t="str">
         <f aca="false">IF([1]Schedule!$E$68&gt;0,[1]Schedule!$C$68," ")</f>
-        <v>IKEA</v>
+        <v>Precision Tooling Supplies</v>
       </c>
       <c r="E50" s="242"/>
       <c r="F50" s="194" t="n">
         <f aca="false">IF([1]Schedule!$E$68&gt;0,[1]Schedule!$E$68," ")</f>
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="G50" s="178"/>
       <c r="H50" s="179"/>
       <c r="I50" s="89" t="n">
         <f aca="false">IF([1]Schedule!$E$68&gt;0,[1]Schedule!$Q$68," ")</f>
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="J50" s="178"/>
       <c r="K50" s="178"/>
@@ -45534,70 +45570,70 @@
     <row r="51" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="241" t="n">
         <f aca="false">IF([1]Schedule!$E$69&gt;0,[1]Schedule!$B$69," ")</f>
-        <v>46137</v>
+        <v>46037</v>
       </c>
       <c r="B51" s="87" t="str">
         <f aca="false">IF([1]Schedule!$E$69&gt;0,[1]Schedule!$C$69," ")</f>
-        <v>Ford</v>
+        <v>IKEA</v>
       </c>
       <c r="E51" s="242"/>
       <c r="F51" s="194" t="n">
         <f aca="false">IF([1]Schedule!$E$69&gt;0,[1]Schedule!$E$69," ")</f>
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="G51" s="178"/>
       <c r="H51" s="179"/>
       <c r="I51" s="89" t="n">
         <f aca="false">IF([1]Schedule!$E$69&gt;0,[1]Schedule!$Q$69," ")</f>
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="J51" s="178"/>
       <c r="K51" s="178"/>
       <c r="L51" s="185"/>
     </row>
     <row r="52" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="241" t="str">
+      <c r="A52" s="241" t="n">
         <f aca="false">IF([1]Schedule!$E$70&gt;0,[1]Schedule!$B$70," ")</f>
-        <v> </v>
+        <v>46082</v>
       </c>
       <c r="B52" s="87" t="str">
         <f aca="false">IF([1]Schedule!$E$70&gt;0,[1]Schedule!$C$70," ")</f>
-        <v> </v>
+        <v>Precision Tooling Supplies</v>
       </c>
       <c r="E52" s="242"/>
-      <c r="F52" s="194" t="str">
+      <c r="F52" s="194" t="n">
         <f aca="false">IF([1]Schedule!$E$70&gt;0,[1]Schedule!$E$70," ")</f>
-        <v> </v>
+        <v>7000</v>
       </c>
       <c r="G52" s="178"/>
       <c r="H52" s="179"/>
-      <c r="I52" s="89" t="str">
+      <c r="I52" s="89" t="n">
         <f aca="false">IF([1]Schedule!$E$70&gt;0,[1]Schedule!$Q$70," ")</f>
-        <v> </v>
+        <v>7000</v>
       </c>
       <c r="J52" s="178"/>
       <c r="K52" s="178"/>
       <c r="L52" s="185"/>
     </row>
     <row r="53" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="241" t="str">
+      <c r="A53" s="241" t="n">
         <f aca="false">IF([1]Schedule!$E$71&gt;0,[1]Schedule!$B$71," ")</f>
-        <v> </v>
+        <v>46137</v>
       </c>
       <c r="B53" s="87" t="str">
         <f aca="false">IF([1]Schedule!$E$71&gt;0,[1]Schedule!$C$71," ")</f>
-        <v> </v>
+        <v>Ford</v>
       </c>
       <c r="E53" s="242"/>
-      <c r="F53" s="194" t="str">
+      <c r="F53" s="194" t="n">
         <f aca="false">IF([1]Schedule!$E$71&gt;0,[1]Schedule!$E$71," ")</f>
-        <v> </v>
+        <v>30000</v>
       </c>
       <c r="G53" s="178"/>
       <c r="H53" s="179"/>
-      <c r="I53" s="89" t="str">
+      <c r="I53" s="89" t="n">
         <f aca="false">IF([1]Schedule!$E$71&gt;0,[1]Schedule!$Q$71," ")</f>
-        <v> </v>
+        <v>30000</v>
       </c>
       <c r="J53" s="178"/>
       <c r="K53" s="178"/>
@@ -46203,18 +46239,18 @@
       </c>
       <c r="F79" s="246" t="n">
         <f aca="false">SUM(F48:F78)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="G79" s="178"/>
       <c r="H79" s="179"/>
       <c r="I79" s="194" t="n">
         <f aca="false">SUM(I48:I78)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="J79" s="178"/>
       <c r="K79" s="194" t="n">
         <f aca="false">I79</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="L79" s="185"/>
     </row>
@@ -46721,7 +46757,7 @@
       <c r="J104" s="178"/>
       <c r="K104" s="259" t="n">
         <f aca="false">K79+K99+K91-K102</f>
-        <v>44000</v>
+        <v>64000</v>
       </c>
       <c r="L104" s="177"/>
     </row>
@@ -50210,7 +50246,7 @@
       </c>
       <c r="Z70" s="302" t="n">
         <f aca="false">IF(CorporationTax!K22&gt;0,CorporationTax!K22," ")</f>
-        <v>144080.391666666</v>
+        <v>124080.391666666</v>
       </c>
       <c r="AA70" s="302"/>
       <c r="AB70" s="302"/>
@@ -50428,7 +50464,7 @@
       </c>
       <c r="AJ74" s="302" t="n">
         <f aca="false">SUM(Z69:AF70)-SUM(Z72:AF73)</f>
-        <v>144080.391666666</v>
+        <v>124080.391666666</v>
       </c>
       <c r="AK74" s="302"/>
       <c r="AL74" s="302"/>
@@ -51326,7 +51362,7 @@
       </c>
       <c r="AJ92" s="302" t="n">
         <f aca="false">IF(AJ74&gt;0,AJ74+SUM(AJ76:AJ80)+AJ88,0)</f>
-        <v>144419.897839506</v>
+        <v>124419.897839506</v>
       </c>
       <c r="AK92" s="302"/>
       <c r="AL92" s="302"/>
@@ -52211,7 +52247,7 @@
       </c>
       <c r="AJ110" s="302" t="n">
         <f aca="false">AJ92-Z96-Z98-Z104-Z106</f>
-        <v>144419.897839506</v>
+        <v>124419.897839506</v>
       </c>
       <c r="AK110" s="302"/>
       <c r="AL110" s="302"/>
@@ -52989,7 +53025,7 @@
       </c>
       <c r="N126" s="328" t="n">
         <f aca="false">CorporationTax!F33</f>
-        <v>72012.1134432604</v>
+        <v>62039.5107035344</v>
       </c>
       <c r="O126" s="328"/>
       <c r="P126" s="328"/>
@@ -53023,7 +53059,7 @@
       </c>
       <c r="AJ126" s="330" t="n">
         <f aca="false">CorporationTax!J33</f>
-        <v>18003.0283608151</v>
+        <v>15509.8776758836</v>
       </c>
       <c r="AK126" s="330"/>
       <c r="AL126" s="330"/>
@@ -53107,7 +53143,7 @@
       </c>
       <c r="N128" s="328" t="n">
         <f aca="false">IF(CorporationTax!A34&gt;0,CorporationTax!F34," ")</f>
-        <v>72407.7843962454</v>
+        <v>62380.3871359714</v>
       </c>
       <c r="O128" s="328"/>
       <c r="P128" s="328"/>
@@ -53141,7 +53177,7 @@
       </c>
       <c r="AJ128" s="330" t="n">
         <f aca="false">CorporationTax!J34</f>
-        <v>18101.9460990613</v>
+        <v>15595.0967839928</v>
       </c>
       <c r="AK128" s="330"/>
       <c r="AL128" s="330"/>
@@ -53294,7 +53330,7 @@
       </c>
       <c r="AJ131" s="330" t="n">
         <f aca="false">AJ126+AJ128</f>
-        <v>36104.9744598764</v>
+        <v>31104.9744598765</v>
       </c>
       <c r="AK131" s="330"/>
       <c r="AL131" s="330"/>
@@ -53388,7 +53424,7 @@
       <c r="X133" s="333"/>
       <c r="Y133" s="330" t="n">
         <f aca="false">CorporationTax!L33+CorporationTax!L34</f>
-        <v>1583.70153240741</v>
+        <v>1883.70153240741</v>
       </c>
       <c r="Z133" s="330"/>
       <c r="AA133" s="330"/>
@@ -53493,7 +53529,7 @@
       <c r="X135" s="333"/>
       <c r="Y135" s="330" t="n">
         <f aca="false">AJ131-Y133</f>
-        <v>34521.272927469</v>
+        <v>29221.272927469</v>
       </c>
       <c r="Z135" s="330"/>
       <c r="AA135" s="330"/>
@@ -53594,7 +53630,7 @@
       </c>
       <c r="W137" s="334" t="n">
         <f aca="false">IF(Y135&gt;0,Y135*100/AJ110," ")</f>
-        <v>23.9034048935782</v>
+        <v>23.4860126353445</v>
       </c>
       <c r="X137" s="334"/>
       <c r="Y137" s="334"/>
@@ -54016,7 +54052,7 @@
       </c>
       <c r="AJ145" s="330" t="n">
         <f aca="false">Y135</f>
-        <v>34521.272927469</v>
+        <v>29221.272927469</v>
       </c>
       <c r="AK145" s="330"/>
       <c r="AL145" s="330"/>
@@ -54718,7 +54754,7 @@
       </c>
       <c r="AJ159" s="330" t="n">
         <f aca="false">IF(AJ145&gt;0,AJ145+AJ149-AJ154,0)</f>
-        <v>34456.7667546295</v>
+        <v>29156.7667546295</v>
       </c>
       <c r="AK159" s="330"/>
       <c r="AL159" s="330"/>
@@ -55067,7 +55103,7 @@
       </c>
       <c r="AJ166" s="330" t="n">
         <f aca="false">IF(AJ159&gt;0,AJ159-AJ163,0)</f>
-        <v>34456.7667546295</v>
+        <v>29156.7667546295</v>
       </c>
       <c r="AK166" s="330"/>
       <c r="AL166" s="330"/>
@@ -56490,7 +56526,7 @@
       </c>
       <c r="AL194" s="328" t="n">
         <f aca="false">IF(CorporationTax!F79&gt;0,CorporationTax!F79," ")</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="AM194" s="328"/>
       <c r="AN194" s="328"/>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -5887,7 +5887,7 @@
         </row>
         <row r="1">
           <cell r="AK1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
       </sheetData>
@@ -6287,7 +6287,7 @@
         </row>
         <row r="1">
           <cell r="AK1">
-            <v>0</v>
+            <v>600</v>
           </cell>
         </row>
       </sheetData>
@@ -7258,10 +7258,10 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>3173.2</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
-            <v>0</v>
+            <v>1500</v>
           </cell>
           <cell r="AJ1">
             <v>0</v>
@@ -7537,10 +7537,10 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>15481.37</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
-            <v>0</v>
+            <v>13808.17</v>
           </cell>
           <cell r="AJ1">
             <v>0</v>
@@ -7816,10 +7816,10 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>16129.7</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
-            <v>0</v>
+            <v>14456.5</v>
           </cell>
           <cell r="AJ1">
             <v>0</v>
@@ -8095,10 +8095,10 @@
             <v>0</v>
           </cell>
           <cell r="AH1">
-            <v>12590.7</v>
+            <v>1673.2</v>
           </cell>
           <cell r="AI1">
-            <v>0</v>
+            <v>10917.5</v>
           </cell>
           <cell r="AJ1">
             <v>0</v>
@@ -23584,7 +23584,7 @@
       <c r="AB28" s="36"/>
       <c r="AC28" s="36" t="n">
         <f aca="false">-[2]Dec!$F$1+[2]Dec!$AK$1</f>
-        <v>-24657</v>
+        <v>-23657</v>
       </c>
       <c r="AD28" s="36" t="n">
         <f aca="false">[4]Dec!$AB$1</f>
@@ -23607,7 +23607,7 @@
       <c r="AJ28" s="54"/>
       <c r="AK28" s="36" t="n">
         <f aca="false">SUM(Z28:AJ28)</f>
-        <v>-13323.25</v>
+        <v>-12323.25</v>
       </c>
       <c r="AL28" s="57"/>
       <c r="AM28" s="36"/>
@@ -23636,7 +23636,7 @@
       <c r="AU28" s="54"/>
       <c r="AV28" s="36" t="n">
         <f aca="false">SUM(AK28:AU28)</f>
-        <v>-18582.5</v>
+        <v>-17582.5</v>
       </c>
       <c r="AW28" s="57"/>
       <c r="AX28" s="36"/>
@@ -23665,7 +23665,7 @@
       <c r="BF28" s="54"/>
       <c r="BG28" s="36" t="n">
         <f aca="false">SUM(AV28:BF28)</f>
-        <v>-18887.75</v>
+        <v>-17887.75</v>
       </c>
       <c r="BH28" s="57"/>
       <c r="BI28" s="36"/>
@@ -23694,7 +23694,7 @@
       <c r="BQ28" s="54"/>
       <c r="BR28" s="36" t="n">
         <f aca="false">SUM(BG28:BQ28)</f>
-        <v>-21644.75</v>
+        <v>-20644.75</v>
       </c>
       <c r="BS28" s="57"/>
       <c r="BT28" s="36"/>
@@ -23723,13 +23723,13 @@
       <c r="CB28" s="54"/>
       <c r="CC28" s="36" t="n">
         <f aca="false">SUM(BR28:CB28)</f>
-        <v>-24030.5</v>
+        <v>-23030.5</v>
       </c>
       <c r="CD28" s="57"/>
       <c r="CE28" s="36"/>
       <c r="CF28" s="36" t="n">
         <f aca="false">-[2]May!$F$1+[2]May!$AK$1</f>
-        <v>-6918</v>
+        <v>-6318</v>
       </c>
       <c r="CG28" s="36" t="n">
         <f aca="false">[4]May!$AB$1</f>
@@ -23752,7 +23752,7 @@
       <c r="CM28" s="54"/>
       <c r="CN28" s="36" t="n">
         <f aca="false">SUM(CC28:CM28)</f>
-        <v>-27048.5</v>
+        <v>-25448.5</v>
       </c>
       <c r="CO28" s="57"/>
       <c r="CP28" s="36"/>
@@ -23781,7 +23781,7 @@
       <c r="CX28" s="54"/>
       <c r="CY28" s="36" t="n">
         <f aca="false">SUM(CN28:CX28)</f>
-        <v>-32250</v>
+        <v>-30650</v>
       </c>
       <c r="CZ28" s="57"/>
       <c r="DA28" s="36"/>
@@ -23810,7 +23810,7 @@
       <c r="DI28" s="54"/>
       <c r="DJ28" s="36" t="n">
         <f aca="false">SUM(CY28:DI28)</f>
-        <v>-32761.25</v>
+        <v>-31161.25</v>
       </c>
       <c r="DK28" s="57"/>
       <c r="DL28" s="36"/>
@@ -23839,7 +23839,7 @@
       <c r="DT28" s="54"/>
       <c r="DU28" s="36" t="n">
         <f aca="false">SUM(DJ28:DT28)</f>
-        <v>-32517.75</v>
+        <v>-30917.75</v>
       </c>
       <c r="DV28" s="57"/>
       <c r="DW28" s="36"/>
@@ -23868,7 +23868,7 @@
       <c r="EE28" s="54"/>
       <c r="EF28" s="36" t="n">
         <f aca="false">SUM(DU28:EE28)</f>
-        <v>-32432.25</v>
+        <v>-30832.25</v>
       </c>
       <c r="EG28" s="54"/>
       <c r="EH28" s="36" t="n">
@@ -23878,7 +23878,7 @@
       <c r="EI28" s="54"/>
       <c r="EJ28" s="36" t="n">
         <f aca="false">SUM(EF28:EH28)</f>
-        <v>-12432.25</v>
+        <v>-10832.25</v>
       </c>
       <c r="EK28" s="54"/>
     </row>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="AC32" s="36" t="n">
         <f aca="false">-[2]Dec!$AK$1</f>
-        <v>-0</v>
+        <v>-1000</v>
       </c>
       <c r="AD32" s="36" t="n">
         <f aca="false">-[4]Dec!$O$1+[4]Dec!$AJ$1</f>
@@ -24908,7 +24908,7 @@
       <c r="AJ32" s="54"/>
       <c r="AK32" s="36" t="n">
         <f aca="false">SUM(Z32:AJ32)</f>
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AL32" s="57"/>
       <c r="AM32" s="36" t="n">
@@ -24940,7 +24940,7 @@
       <c r="AU32" s="54"/>
       <c r="AV32" s="36" t="n">
         <f aca="false">SUM(AK32:AU32)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AW32" s="57"/>
       <c r="AX32" s="36" t="n">
@@ -24972,7 +24972,7 @@
       <c r="BF32" s="54"/>
       <c r="BG32" s="36" t="n">
         <f aca="false">SUM(AV32:BF32)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BH32" s="57"/>
       <c r="BI32" s="36" t="n">
@@ -25004,7 +25004,7 @@
       <c r="BQ32" s="54"/>
       <c r="BR32" s="36" t="n">
         <f aca="false">SUM(BG32:BQ32)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS32" s="57"/>
       <c r="BT32" s="36" t="n">
@@ -25036,7 +25036,7 @@
       <c r="CB32" s="54"/>
       <c r="CC32" s="36" t="n">
         <f aca="false">SUM(BR32:CB32)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CD32" s="57"/>
       <c r="CE32" s="36" t="n">
@@ -25045,7 +25045,7 @@
       </c>
       <c r="CF32" s="36" t="n">
         <f aca="false">-[2]May!$AK$1</f>
-        <v>-0</v>
+        <v>-600</v>
       </c>
       <c r="CG32" s="36" t="n">
         <f aca="false">-[4]May!$O$1+[4]May!$AJ$1</f>
@@ -25068,7 +25068,7 @@
       <c r="CM32" s="54"/>
       <c r="CN32" s="36" t="n">
         <f aca="false">SUM(CC32:CM32)</f>
-        <v>1000</v>
+        <v>-600</v>
       </c>
       <c r="CO32" s="57"/>
       <c r="CP32" s="36" t="n">
@@ -25100,7 +25100,7 @@
       <c r="CX32" s="54"/>
       <c r="CY32" s="36" t="n">
         <f aca="false">SUM(CN32:CX32)</f>
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="CZ32" s="57"/>
       <c r="DA32" s="36" t="n">
@@ -25132,7 +25132,7 @@
       <c r="DI32" s="54"/>
       <c r="DJ32" s="36" t="n">
         <f aca="false">SUM(CY32:DI32)</f>
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="DK32" s="57"/>
       <c r="DL32" s="36" t="n">
@@ -25164,7 +25164,7 @@
       <c r="DT32" s="54"/>
       <c r="DU32" s="36" t="n">
         <f aca="false">SUM(DJ32:DT32)</f>
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="DV32" s="57"/>
       <c r="DW32" s="36" t="n">
@@ -25196,13 +25196,13 @@
       <c r="EE32" s="54"/>
       <c r="EF32" s="36" t="n">
         <f aca="false">SUM(DU32:EE32)</f>
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="EG32" s="54"/>
       <c r="EI32" s="54"/>
       <c r="EJ32" s="36" t="n">
         <f aca="false">SUM(EF32:EH32)</f>
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="EK32" s="54"/>
     </row>
@@ -25260,7 +25260,7 @@
       </c>
       <c r="S33" s="36" t="n">
         <f aca="false">-[4]Nov!$N$1+[4]Nov!$AI$1</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="T33" s="36" t="n">
         <f aca="false">-[5]Nov!$N$1+[5]Nov!$AI$1</f>
@@ -25279,7 +25279,7 @@
       <c r="Y33" s="54"/>
       <c r="Z33" s="36" t="n">
         <f aca="false">SUM(O33:Y33)</f>
-        <v>-10638.9583333333</v>
+        <v>-9138.95833333334</v>
       </c>
       <c r="AA33" s="57"/>
       <c r="AB33" s="36" t="n">
@@ -25311,7 +25311,7 @@
       <c r="AJ33" s="54"/>
       <c r="AK33" s="36" t="n">
         <f aca="false">SUM(Z33:AJ33)</f>
-        <v>-12396.125</v>
+        <v>-10896.125</v>
       </c>
       <c r="AL33" s="57"/>
       <c r="AM33" s="36" t="n">
@@ -25343,7 +25343,7 @@
       <c r="AU33" s="54"/>
       <c r="AV33" s="36" t="n">
         <f aca="false">SUM(AK33:AU33)</f>
-        <v>-16512.9166666667</v>
+        <v>-15012.9166666667</v>
       </c>
       <c r="AW33" s="57"/>
       <c r="AX33" s="36" t="n">
@@ -25356,7 +25356,7 @@
       </c>
       <c r="AZ33" s="36" t="n">
         <f aca="false">-[4]Feb!$N$1+[4]Feb!$AI$1</f>
-        <v>0</v>
+        <v>13808.17</v>
       </c>
       <c r="BA33" s="36" t="n">
         <f aca="false">-[5]Feb!$N$1+[5]Feb!$AI$1</f>
@@ -25375,7 +25375,7 @@
       <c r="BF33" s="54"/>
       <c r="BG33" s="36" t="n">
         <f aca="false">SUM(AV33:BF33)</f>
-        <v>-21782.0416666667</v>
+        <v>-6473.87166666668</v>
       </c>
       <c r="BH33" s="57"/>
       <c r="BI33" s="36" t="n">
@@ -25407,7 +25407,7 @@
       <c r="BQ33" s="54"/>
       <c r="BR33" s="36" t="n">
         <f aca="false">SUM(BG33:BQ33)</f>
-        <v>-25179.5416666667</v>
+        <v>-9871.37166666668</v>
       </c>
       <c r="BS33" s="57"/>
       <c r="BT33" s="36" t="n">
@@ -25439,7 +25439,7 @@
       <c r="CB33" s="54"/>
       <c r="CC33" s="36" t="n">
         <f aca="false">SUM(BR33:CB33)</f>
-        <v>-26438.5833333333</v>
+        <v>-11130.4133333333</v>
       </c>
       <c r="CD33" s="57"/>
       <c r="CE33" s="36" t="n">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="CG33" s="36" t="n">
         <f aca="false">-[4]May!$N$1+[4]May!$AI$1</f>
-        <v>0</v>
+        <v>14456.5</v>
       </c>
       <c r="CH33" s="36" t="n">
         <f aca="false">-[5]May!$N$1+[5]May!$AI$1</f>
@@ -25471,7 +25471,7 @@
       <c r="CM33" s="54"/>
       <c r="CN33" s="36" t="n">
         <f aca="false">SUM(CC33:CM33)</f>
-        <v>-31172.25</v>
+        <v>-1407.58000000001</v>
       </c>
       <c r="CO33" s="57"/>
       <c r="CP33" s="36" t="n">
@@ -25503,7 +25503,7 @@
       <c r="CX33" s="54"/>
       <c r="CY33" s="36" t="n">
         <f aca="false">SUM(CN33:CX33)</f>
-        <v>-35063.6666666667</v>
+        <v>-5298.99666666668</v>
       </c>
       <c r="CZ33" s="57"/>
       <c r="DA33" s="36" t="n">
@@ -25535,7 +25535,7 @@
       <c r="DI33" s="54"/>
       <c r="DJ33" s="36" t="n">
         <f aca="false">SUM(CY33:DI33)</f>
-        <v>-40218.4583333334</v>
+        <v>-10453.7883333334</v>
       </c>
       <c r="DK33" s="57"/>
       <c r="DL33" s="36" t="n">
@@ -25548,7 +25548,7 @@
       </c>
       <c r="DN33" s="36" t="n">
         <f aca="false">-[4]Aug!$N$1+[4]Aug!$AI$1</f>
-        <v>0</v>
+        <v>10917.5</v>
       </c>
       <c r="DO33" s="36" t="n">
         <f aca="false">-[5]Aug!$N$1+[5]Aug!$AI$1</f>
@@ -25567,7 +25567,7 @@
       <c r="DT33" s="54"/>
       <c r="DU33" s="36" t="n">
         <f aca="false">SUM(DJ33:DT33)</f>
-        <v>-45212.375</v>
+        <v>-4530.20500000002</v>
       </c>
       <c r="DV33" s="57"/>
       <c r="DW33" s="36" t="n">
@@ -25599,13 +25599,13 @@
       <c r="EE33" s="54"/>
       <c r="EF33" s="36" t="n">
         <f aca="false">SUM(DU33:EE33)</f>
-        <v>-49817.9583333334</v>
+        <v>-9135.78833333336</v>
       </c>
       <c r="EG33" s="54"/>
       <c r="EI33" s="54"/>
       <c r="EJ33" s="36" t="n">
         <f aca="false">SUM(EF33:EH33)</f>
-        <v>-49817.9583333334</v>
+        <v>-9135.78833333336</v>
       </c>
       <c r="EK33" s="54"/>
     </row>
@@ -25654,7 +25654,7 @@
       <c r="R34" s="36"/>
       <c r="S34" s="36" t="n">
         <f aca="false">[4]Nov!$AH$1</f>
-        <v>3173.2</v>
+        <v>1673.2</v>
       </c>
       <c r="T34" s="36" t="n">
         <f aca="false">[5]Nov!$AH$1</f>
@@ -25676,7 +25676,7 @@
       <c r="Y34" s="54"/>
       <c r="Z34" s="36" t="n">
         <f aca="false">SUM(O34:Y34)</f>
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="AA34" s="57"/>
       <c r="AB34" s="36"/>
@@ -25705,7 +25705,7 @@
       <c r="AJ34" s="54"/>
       <c r="AK34" s="36" t="n">
         <f aca="false">SUM(Z34:AJ34)</f>
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="AL34" s="57"/>
       <c r="AM34" s="36"/>
@@ -25734,14 +25734,14 @@
       <c r="AU34" s="54"/>
       <c r="AV34" s="36" t="n">
         <f aca="false">SUM(AK34:AU34)</f>
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="AW34" s="57"/>
       <c r="AX34" s="36"/>
       <c r="AY34" s="36"/>
       <c r="AZ34" s="36" t="n">
         <f aca="false">[4]Feb!$AH$1</f>
-        <v>15481.37</v>
+        <v>1673.2</v>
       </c>
       <c r="BA34" s="36" t="n">
         <f aca="false">[5]Feb!$AH$1</f>
@@ -25763,7 +25763,7 @@
       <c r="BF34" s="54"/>
       <c r="BG34" s="36" t="n">
         <f aca="false">SUM(AV34:BF34)</f>
-        <v>15308.17</v>
+        <v>0</v>
       </c>
       <c r="BH34" s="57"/>
       <c r="BI34" s="36"/>
@@ -25792,7 +25792,7 @@
       <c r="BQ34" s="54"/>
       <c r="BR34" s="36" t="n">
         <f aca="false">SUM(BG34:BQ34)</f>
-        <v>15308.17</v>
+        <v>0</v>
       </c>
       <c r="BS34" s="57"/>
       <c r="BT34" s="36"/>
@@ -25821,14 +25821,14 @@
       <c r="CB34" s="54"/>
       <c r="CC34" s="36" t="n">
         <f aca="false">SUM(BR34:CB34)</f>
-        <v>15308.17</v>
+        <v>0</v>
       </c>
       <c r="CD34" s="57"/>
       <c r="CE34" s="36"/>
       <c r="CF34" s="36"/>
       <c r="CG34" s="36" t="n">
         <f aca="false">[4]May!$AH$1</f>
-        <v>16129.7</v>
+        <v>1673.2</v>
       </c>
       <c r="CH34" s="36" t="n">
         <f aca="false">[5]May!$AH$1</f>
@@ -25850,7 +25850,7 @@
       <c r="CM34" s="54"/>
       <c r="CN34" s="36" t="n">
         <f aca="false">SUM(CC34:CM34)</f>
-        <v>29764.67</v>
+        <v>0</v>
       </c>
       <c r="CO34" s="57"/>
       <c r="CP34" s="36"/>
@@ -25879,7 +25879,7 @@
       <c r="CX34" s="54"/>
       <c r="CY34" s="36" t="n">
         <f aca="false">SUM(CN34:CX34)</f>
-        <v>29764.67</v>
+        <v>0</v>
       </c>
       <c r="CZ34" s="57"/>
       <c r="DA34" s="36"/>
@@ -25908,14 +25908,14 @@
       <c r="DI34" s="54"/>
       <c r="DJ34" s="36" t="n">
         <f aca="false">SUM(CY34:DI34)</f>
-        <v>29764.67</v>
+        <v>0</v>
       </c>
       <c r="DK34" s="57"/>
       <c r="DL34" s="36"/>
       <c r="DM34" s="36"/>
       <c r="DN34" s="36" t="n">
         <f aca="false">[4]Aug!$AH$1</f>
-        <v>12590.7</v>
+        <v>1673.2</v>
       </c>
       <c r="DO34" s="36" t="n">
         <f aca="false">[5]Aug!$AH$1</f>
@@ -25937,7 +25937,7 @@
       <c r="DT34" s="54"/>
       <c r="DU34" s="36" t="n">
         <f aca="false">SUM(DJ34:DT34)</f>
-        <v>40682.17</v>
+        <v>0</v>
       </c>
       <c r="DV34" s="57"/>
       <c r="DW34" s="36"/>
@@ -25966,13 +25966,13 @@
       <c r="EE34" s="54"/>
       <c r="EF34" s="36" t="n">
         <f aca="false">SUM(DU34:EE34)</f>
-        <v>40682.17</v>
+        <v>0</v>
       </c>
       <c r="EG34" s="54"/>
       <c r="EI34" s="54"/>
       <c r="EJ34" s="36" t="n">
         <f aca="false">SUM(EF34:EH34)</f>
-        <v>40682.17</v>
+        <v>0</v>
       </c>
       <c r="EK34" s="54"/>
     </row>
@@ -38223,7 +38223,7 @@
       </c>
       <c r="S91" s="36" t="n">
         <f aca="false">SUM(S4:S90)</f>
-        <v>-9.09494701772928E-013</v>
+        <v>-6.82121026329696E-013</v>
       </c>
       <c r="T91" s="36" t="n">
         <f aca="false">SUM(T4:T90)</f>
@@ -38248,7 +38248,7 @@
       <c r="Y91" s="54"/>
       <c r="Z91" s="36" t="n">
         <f aca="false">SUM(Z4:Z90)</f>
-        <v>6.93489710101858E-011</v>
+        <v>6.9576344685629E-011</v>
       </c>
       <c r="AA91" s="54"/>
       <c r="AB91" s="36" t="n">
@@ -38286,7 +38286,7 @@
       <c r="AJ91" s="54"/>
       <c r="AK91" s="36" t="n">
         <f aca="false">SUM(AK4:AK90)</f>
-        <v>1.08684616861865E-010</v>
+        <v>1.07093001133762E-010</v>
       </c>
       <c r="AL91" s="54"/>
       <c r="AM91" s="36" t="n">
@@ -38324,7 +38324,7 @@
       <c r="AU91" s="54"/>
       <c r="AV91" s="36" t="n">
         <f aca="false">SUM(AV4:AV90)</f>
-        <v>1.41653799801134E-010</v>
+        <v>1.41881173476577E-010</v>
       </c>
       <c r="AW91" s="54"/>
       <c r="AX91" s="36" t="n">
@@ -38362,7 +38362,7 @@
       <c r="BF91" s="54"/>
       <c r="BG91" s="36" t="n">
         <f aca="false">SUM(BG4:BG90)</f>
-        <v>1.86901161214337E-010</v>
+        <v>1.88720150617883E-010</v>
       </c>
       <c r="BH91" s="54"/>
       <c r="BI91" s="36" t="n">
@@ -38400,7 +38400,7 @@
       <c r="BQ91" s="54"/>
       <c r="BR91" s="36" t="n">
         <f aca="false">SUM(BR4:BR90)</f>
-        <v>2.24190443987027E-010</v>
+        <v>2.22371454583481E-010</v>
       </c>
       <c r="BS91" s="54"/>
       <c r="BT91" s="36" t="n">
@@ -38451,7 +38451,7 @@
       </c>
       <c r="CG91" s="36" t="n">
         <f aca="false">SUM(CG4:CG90)</f>
-        <v>0</v>
+        <v>-6.82121026329696E-013</v>
       </c>
       <c r="CH91" s="36" t="n">
         <f aca="false">SUM(CH4:CH90)</f>
@@ -38476,7 +38476,7 @@
       <c r="CM91" s="54"/>
       <c r="CN91" s="36" t="n">
         <f aca="false">SUM(CN4:CN90)</f>
-        <v>2.86945578409359E-010</v>
+        <v>2.88764567812905E-010</v>
       </c>
       <c r="CO91" s="54"/>
       <c r="CP91" s="36" t="n">
@@ -38514,7 +38514,7 @@
       <c r="CX91" s="54"/>
       <c r="CY91" s="36" t="n">
         <f aca="false">SUM(CY4:CY90)</f>
-        <v>3.06954461848363E-010</v>
+        <v>3.10592440655455E-010</v>
       </c>
       <c r="CZ91" s="54"/>
       <c r="DA91" s="36" t="n">
@@ -38552,7 +38552,7 @@
       <c r="DI91" s="54"/>
       <c r="DJ91" s="36" t="n">
         <f aca="false">SUM(DJ4:DJ90)</f>
-        <v>3.09228198602796E-010</v>
+        <v>3.14685166813433E-010</v>
       </c>
       <c r="DK91" s="54"/>
       <c r="DL91" s="36" t="n">
@@ -38590,7 +38590,7 @@
       <c r="DT91" s="54"/>
       <c r="DU91" s="36" t="n">
         <f aca="false">SUM(DU4:DU90)</f>
-        <v>3.10365066980012E-010</v>
+        <v>3.17641024594195E-010</v>
       </c>
       <c r="DV91" s="54"/>
       <c r="DW91" s="36" t="n">
@@ -38628,7 +38628,7 @@
       <c r="EE91" s="54"/>
       <c r="EF91" s="36" t="n">
         <f aca="false">SUM(EF4:EF90)</f>
-        <v>3.15594661515206E-010</v>
+        <v>3.2287061912939E-010</v>
       </c>
       <c r="EG91" s="54"/>
       <c r="EH91" s="36" t="n">
@@ -38638,7 +38638,7 @@
       <c r="EI91" s="54"/>
       <c r="EJ91" s="36" t="n">
         <f aca="false">SUM(EJ4:EJ90)</f>
-        <v>3.17413650918752E-010</v>
+        <v>3.24689608532935E-010</v>
       </c>
       <c r="EK91" s="54"/>
     </row>
@@ -42655,7 +42655,7 @@
       </c>
       <c r="E16" s="115" t="n">
         <f aca="false">-SUM(TrialBalance!EJ28:EJ31)</f>
-        <v>12432.25</v>
+        <v>10832.25</v>
       </c>
       <c r="F16" s="115"/>
     </row>
@@ -42685,7 +42685,7 @@
       </c>
       <c r="E18" s="115" t="n">
         <f aca="false">-SUM(TrialBalance!EJ32:EJ34)</f>
-        <v>7535.78833333337</v>
+        <v>9135.78833333336</v>
       </c>
       <c r="F18" s="115"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -43143,7 +43143,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43976,7 +43976,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44518,7 +44518,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="635">
   <si>
     <t xml:space="preserve">Company Name (including Limited)</t>
   </si>
@@ -2264,12 +2264,6 @@
   </si>
   <si>
     <t xml:space="preserve">=</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costing over </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restricted to</t>
   </si>
   <si>
     <t xml:space="preserve">Marginal relief lower limit</t>
@@ -5275,7 +5269,7 @@
             <v>17328</v>
           </cell>
           <cell r="Y1">
-            <v>8500</v>
+            <v>8140</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
@@ -5420,7 +5414,7 @@
         </row>
         <row r="55">
           <cell r="R55">
-            <v>3000</v>
+            <v>3360</v>
           </cell>
         </row>
         <row r="55">
@@ -16988,18 +16982,10 @@
         <v>46327</v>
       </c>
       <c r="C11" s="451"/>
-      <c r="D11" s="451" t="s">
-        <v>625</v>
-      </c>
-      <c r="E11" s="468" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F11" s="451" t="s">
-        <v>626</v>
-      </c>
-      <c r="G11" s="468" t="n">
-        <v>3000</v>
-      </c>
+      <c r="D11" s="451"/>
+      <c r="E11" s="468"/>
+      <c r="F11" s="451"/>
+      <c r="G11" s="468"/>
       <c r="H11" s="451"/>
       <c r="I11" s="451"/>
       <c r="J11" s="451"/>
@@ -17032,7 +17018,7 @@
       <c r="G12" s="453"/>
       <c r="H12" s="451"/>
       <c r="I12" s="465" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="J12" s="451"/>
       <c r="K12" s="451"/>
@@ -17053,7 +17039,7 @@
       </c>
       <c r="C13" s="451"/>
       <c r="D13" s="458" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E13" s="458"/>
       <c r="F13" s="458"/>
@@ -17062,7 +17048,7 @@
       </c>
       <c r="H13" s="451"/>
       <c r="I13" s="465" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="J13" s="451"/>
       <c r="K13" s="451"/>
@@ -17088,17 +17074,17 @@
       <c r="G14" s="453"/>
       <c r="H14" s="451"/>
       <c r="I14" s="458" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="J14" s="458"/>
       <c r="K14" s="458"/>
       <c r="L14" s="456"/>
       <c r="M14" s="451"/>
       <c r="N14" s="453" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="O14" s="453" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="P14" s="451"/>
       <c r="Q14" s="451"/>
@@ -17111,7 +17097,7 @@
       </c>
       <c r="C15" s="451"/>
       <c r="D15" s="471" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E15" s="471"/>
       <c r="F15" s="471"/>
@@ -17146,7 +17132,7 @@
       </c>
       <c r="H16" s="451"/>
       <c r="I16" s="475" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="J16" s="475"/>
       <c r="K16" s="475"/>
@@ -17178,7 +17164,7 @@
       </c>
       <c r="H17" s="451"/>
       <c r="I17" s="475" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="J17" s="475"/>
       <c r="K17" s="475"/>
@@ -17236,7 +17222,7 @@
       </c>
       <c r="H19" s="451"/>
       <c r="I19" s="458" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="J19" s="458"/>
       <c r="K19" s="458"/>
@@ -17294,7 +17280,7 @@
       <c r="G21" s="453"/>
       <c r="H21" s="451"/>
       <c r="I21" s="458" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="J21" s="458"/>
       <c r="K21" s="458"/>
@@ -41374,7 +41360,7 @@
       <c r="M2" s="89"/>
       <c r="N2" s="89"/>
     </row>
-    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="92" t="s">
         <v>222</v>
       </c>
@@ -41404,7 +41390,7 @@
       <c r="M4" s="89"/>
       <c r="N4" s="89"/>
     </row>
-    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="97" t="n">
         <f aca="false">Admin!B8</f>
         <v>46295</v>
@@ -44948,7 +44934,7 @@
       <c r="H17" s="199"/>
       <c r="I17" s="200" t="n">
         <f aca="false">IF(K99&gt;0,K99,0)</f>
-        <v>3000</v>
+        <v>3360</v>
       </c>
       <c r="J17" s="178"/>
       <c r="K17" s="201" t="s">
@@ -44975,7 +44961,7 @@
       <c r="H18" s="205"/>
       <c r="I18" s="206" t="n">
         <f aca="false">IF(K102&lt;&gt;0,-K102,0)</f>
-        <v>8500</v>
+        <v>8140</v>
       </c>
       <c r="J18" s="178"/>
       <c r="K18" s="201" t="s">
@@ -46625,7 +46611,7 @@
       <c r="H97" s="179"/>
       <c r="I97" s="89" t="n">
         <f aca="false">IF([1]Schedule!$R$55&gt;0,[1]Schedule!$R$55," ")</f>
-        <v>3000</v>
+        <v>3360</v>
       </c>
       <c r="J97" s="178"/>
       <c r="K97" s="177"/>
@@ -46666,7 +46652,7 @@
       <c r="J99" s="178"/>
       <c r="K99" s="194" t="n">
         <f aca="false">SUM(I93:I98)</f>
-        <v>3000</v>
+        <v>3360</v>
       </c>
       <c r="L99" s="177"/>
     </row>
@@ -46695,7 +46681,7 @@
       <c r="H101" s="179"/>
       <c r="I101" s="178" t="n">
         <f aca="false">IF([1]Schedule!$W$1&gt;0,[1]Schedule!$Z$1-[1]Schedule!$Y$1," ")</f>
-        <v>-8500</v>
+        <v>-8140</v>
       </c>
       <c r="J101" s="178"/>
       <c r="K101" s="178"/>
@@ -46724,7 +46710,7 @@
       <c r="J102" s="178"/>
       <c r="K102" s="194" t="n">
         <f aca="false">SUM(I100:I101)</f>
-        <v>-8500</v>
+        <v>-8140</v>
       </c>
       <c r="L102" s="177"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -43129,7 +43129,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43962,7 +43962,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44504,7 +44504,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -43133,7 +43133,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43966,7 +43966,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44508,7 +44508,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -43133,7 +43133,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43966,7 +43966,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44508,7 +44508,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -43133,7 +43133,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43966,7 +43966,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44508,7 +44508,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="H119" s="159"/>
     </row>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -7315,7 +7315,7 @@
         </row>
         <row r="1">
           <cell r="X1">
-            <v>27575.2</v>
+            <v>27675.2</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -7324,7 +7324,7 @@
             <v>0</v>
           </cell>
           <cell r="AA1">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="AB1">
             <v>17000</v>
@@ -22191,7 +22191,7 @@
       <c r="AC22" s="36"/>
       <c r="AD22" s="36" t="n">
         <f aca="false">[4]Jan!$F$1-[4]Jan!$X$1</f>
-        <v>7624.8</v>
+        <v>7524.8</v>
       </c>
       <c r="AE22" s="36"/>
       <c r="AF22" s="36"/>
@@ -22201,7 +22201,7 @@
       <c r="AJ22" s="54"/>
       <c r="AK22" s="36" t="n">
         <f aca="false">SUM(Z22:AJ22)</f>
-        <v>83069.4</v>
+        <v>82969.4</v>
       </c>
       <c r="AL22" s="57"/>
       <c r="AM22" s="36"/>
@@ -22218,7 +22218,7 @@
       <c r="AU22" s="54"/>
       <c r="AV22" s="36" t="n">
         <f aca="false">SUM(AK22:AU22)</f>
-        <v>100404.2</v>
+        <v>100304.2</v>
       </c>
       <c r="AW22" s="57"/>
       <c r="AX22" s="36"/>
@@ -22235,7 +22235,7 @@
       <c r="BF22" s="54"/>
       <c r="BG22" s="36" t="n">
         <f aca="false">SUM(AV22:BF22)</f>
-        <v>112690.83</v>
+        <v>112590.83</v>
       </c>
       <c r="BH22" s="57"/>
       <c r="BI22" s="36"/>
@@ -22252,7 +22252,7 @@
       <c r="BQ22" s="54"/>
       <c r="BR22" s="36" t="n">
         <f aca="false">SUM(BG22:BQ22)</f>
-        <v>126217.63</v>
+        <v>126117.63</v>
       </c>
       <c r="BS22" s="57"/>
       <c r="BT22" s="36"/>
@@ -22269,7 +22269,7 @@
       <c r="CB22" s="54"/>
       <c r="CC22" s="36" t="n">
         <f aca="false">SUM(BR22:CB22)</f>
-        <v>119952.43</v>
+        <v>119852.43</v>
       </c>
       <c r="CD22" s="57"/>
       <c r="CE22" s="36"/>
@@ -22286,7 +22286,7 @@
       <c r="CM22" s="54"/>
       <c r="CN22" s="36" t="n">
         <f aca="false">SUM(CC22:CM22)</f>
-        <v>128565.73</v>
+        <v>128465.73</v>
       </c>
       <c r="CO22" s="57"/>
       <c r="CP22" s="36"/>
@@ -22303,7 +22303,7 @@
       <c r="CX22" s="54"/>
       <c r="CY22" s="36" t="n">
         <f aca="false">SUM(CN22:CX22)</f>
-        <v>148073.53</v>
+        <v>147973.53</v>
       </c>
       <c r="CZ22" s="57"/>
       <c r="DA22" s="36"/>
@@ -22320,7 +22320,7 @@
       <c r="DI22" s="54"/>
       <c r="DJ22" s="36" t="n">
         <f aca="false">SUM(CY22:DI22)</f>
-        <v>172888.33</v>
+        <v>172788.33</v>
       </c>
       <c r="DK22" s="57"/>
       <c r="DL22" s="36"/>
@@ -22337,7 +22337,7 @@
       <c r="DT22" s="54"/>
       <c r="DU22" s="36" t="n">
         <f aca="false">SUM(DJ22:DT22)</f>
-        <v>183605.63</v>
+        <v>183505.63</v>
       </c>
       <c r="DV22" s="57"/>
       <c r="DW22" s="36"/>
@@ -22354,13 +22354,13 @@
       <c r="EE22" s="54"/>
       <c r="EF22" s="36" t="n">
         <f aca="false">SUM(DU22:EE22)</f>
-        <v>181315.43</v>
+        <v>181215.43</v>
       </c>
       <c r="EG22" s="54"/>
       <c r="EI22" s="54"/>
       <c r="EJ22" s="36" t="n">
         <f aca="false">SUM(EF22:EH22)</f>
-        <v>181315.43</v>
+        <v>181215.43</v>
       </c>
       <c r="EK22" s="54"/>
     </row>
@@ -23102,7 +23102,7 @@
       <c r="AC26" s="36"/>
       <c r="AD26" s="36" t="n">
         <f aca="false">-[4]Jan!$G$1-[4]Jan!$H$1-[4]Jan!$I$1+[4]Jan!$Y$1+[4]Jan!$Z$1+[4]Jan!$AA$1</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE26" s="36" t="n">
         <f aca="false">-[5]Jan!$G$1-[5]Jan!$H$1-[5]Jan!$I$1+[5]Jan!$Y$1+[5]Jan!$Z$1+[5]Jan!$AA$1</f>
@@ -23121,7 +23121,7 @@
       <c r="AJ26" s="54"/>
       <c r="AK26" s="36" t="n">
         <f aca="false">SUM(Z26:AJ26)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AL26" s="57"/>
       <c r="AM26" s="36"/>
@@ -23147,7 +23147,7 @@
       <c r="AU26" s="54"/>
       <c r="AV26" s="36" t="n">
         <f aca="false">SUM(AK26:AU26)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AW26" s="57"/>
       <c r="AX26" s="36"/>
@@ -23173,7 +23173,7 @@
       <c r="BF26" s="54"/>
       <c r="BG26" s="36" t="n">
         <f aca="false">SUM(AV26:BF26)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="BH26" s="57"/>
       <c r="BI26" s="36"/>
@@ -23199,7 +23199,7 @@
       <c r="BQ26" s="54"/>
       <c r="BR26" s="36" t="n">
         <f aca="false">SUM(BG26:BQ26)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="BS26" s="57"/>
       <c r="BT26" s="36"/>
@@ -23225,7 +23225,7 @@
       <c r="CB26" s="54"/>
       <c r="CC26" s="36" t="n">
         <f aca="false">SUM(BR26:CB26)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="CD26" s="57"/>
       <c r="CE26" s="36"/>
@@ -23251,7 +23251,7 @@
       <c r="CM26" s="54"/>
       <c r="CN26" s="36" t="n">
         <f aca="false">SUM(CC26:CM26)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="CO26" s="57"/>
       <c r="CP26" s="36"/>
@@ -23277,7 +23277,7 @@
       <c r="CX26" s="54"/>
       <c r="CY26" s="36" t="n">
         <f aca="false">SUM(CN26:CX26)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="CZ26" s="57"/>
       <c r="DA26" s="36"/>
@@ -23303,7 +23303,7 @@
       <c r="DI26" s="54"/>
       <c r="DJ26" s="36" t="n">
         <f aca="false">SUM(CY26:DI26)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="DK26" s="57"/>
       <c r="DL26" s="36"/>
@@ -23329,7 +23329,7 @@
       <c r="DT26" s="54"/>
       <c r="DU26" s="36" t="n">
         <f aca="false">SUM(DJ26:DT26)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="DV26" s="57"/>
       <c r="DW26" s="36"/>
@@ -23355,13 +23355,13 @@
       <c r="EE26" s="54"/>
       <c r="EF26" s="36" t="n">
         <f aca="false">SUM(DU26:EE26)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="EG26" s="54"/>
       <c r="EI26" s="54"/>
       <c r="EJ26" s="36" t="n">
         <f aca="false">SUM(EF26:EH26)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="EK26" s="54"/>
     </row>
@@ -43133,7 +43133,7 @@
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43966,7 +43966,7 @@
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -44508,7 +44508,7 @@
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="H119" s="159"/>
     </row>
@@ -55636,9 +55636,9 @@
       <c r="Z177" s="339" t="s">
         <v>218</v>
       </c>
-      <c r="AA177" s="328" t="str">
-        <f aca="false">IF((CorporationTax!H15+CorporationTax!H17)&gt;0,CorporationTax!H15+CorporationTax!H17," ")</f>
-        <v> </v>
+      <c r="AA177" s="328" t="n">
+        <f aca="false">IF((CorporationTax!I15+CorporationTax!I17)&gt;0,CorporationTax!I15+CorporationTax!I17," ")</f>
+        <v>55860</v>
       </c>
       <c r="AB177" s="328"/>
       <c r="AC177" s="328"/>
@@ -55654,9 +55654,9 @@
       <c r="AK177" s="339" t="s">
         <v>218</v>
       </c>
-      <c r="AL177" s="328" t="str">
-        <f aca="false">IF(CorporationTax!H18&lt;&gt;0,CorporationTax!H18," ")</f>
-        <v> </v>
+      <c r="AL177" s="328" t="n">
+        <f aca="false">IF(CorporationTax!I18&lt;&gt;0,CorporationTax!I18," ")</f>
+        <v>8140</v>
       </c>
       <c r="AM177" s="328"/>
       <c r="AN177" s="328"/>
@@ -55747,7 +55747,7 @@
         <v>218</v>
       </c>
       <c r="AA179" s="328" t="str">
-        <f aca="false">IF(CorporationTax!H16&gt;0,CorporationTax!H16," ")</f>
+        <f aca="false">IF(CorporationTax!I16&gt;0,CorporationTax!I16," ")</f>
         <v> </v>
       </c>
       <c r="AB179" s="328"/>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -5445,7 +5445,7 @@
         </row>
         <row r="67">
           <cell r="B67">
-            <v>46006</v>
+            <v>46371</v>
           </cell>
           <cell r="C67" t="str">
             <v>Dell</v>
@@ -5463,7 +5463,7 @@
         </row>
         <row r="68">
           <cell r="B68">
-            <v>46023</v>
+            <v>46388</v>
           </cell>
           <cell r="C68" t="str">
             <v>Precision Tooling Supplies</v>
@@ -5481,7 +5481,7 @@
         </row>
         <row r="69">
           <cell r="B69">
-            <v>46068</v>
+            <v>46433</v>
           </cell>
           <cell r="C69" t="str">
             <v>IKEA</v>
@@ -5499,7 +5499,7 @@
         </row>
         <row r="70">
           <cell r="B70">
-            <v>46113</v>
+            <v>46478</v>
           </cell>
           <cell r="C70" t="str">
             <v>Precision Tooling Supplies</v>
@@ -5517,7 +5517,7 @@
         </row>
         <row r="71">
           <cell r="B71">
-            <v>46167</v>
+            <v>46532</v>
           </cell>
           <cell r="C71" t="str">
             <v>Ford</v>
@@ -45512,7 +45512,7 @@
     <row r="49" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="241" t="n">
         <f aca="false">IF([1]Schedule!$E$67&gt;0,[1]Schedule!$B$67," ")</f>
-        <v>46006</v>
+        <v>46371</v>
       </c>
       <c r="B49" s="87" t="str">
         <f aca="false">IF([1]Schedule!$E$67&gt;0,[1]Schedule!$C$67," ")</f>
@@ -45536,7 +45536,7 @@
     <row r="50" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="241" t="n">
         <f aca="false">IF([1]Schedule!$E$68&gt;0,[1]Schedule!$B$68," ")</f>
-        <v>46023</v>
+        <v>46388</v>
       </c>
       <c r="B50" s="87" t="str">
         <f aca="false">IF([1]Schedule!$E$68&gt;0,[1]Schedule!$C$68," ")</f>
@@ -45560,7 +45560,7 @@
     <row r="51" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="241" t="n">
         <f aca="false">IF([1]Schedule!$E$69&gt;0,[1]Schedule!$B$69," ")</f>
-        <v>46068</v>
+        <v>46433</v>
       </c>
       <c r="B51" s="87" t="str">
         <f aca="false">IF([1]Schedule!$E$69&gt;0,[1]Schedule!$C$69," ")</f>
@@ -45584,7 +45584,7 @@
     <row r="52" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="241" t="n">
         <f aca="false">IF([1]Schedule!$E$70&gt;0,[1]Schedule!$B$70," ")</f>
-        <v>46113</v>
+        <v>46478</v>
       </c>
       <c r="B52" s="87" t="str">
         <f aca="false">IF([1]Schedule!$E$70&gt;0,[1]Schedule!$C$70," ")</f>
@@ -45608,7 +45608,7 @@
     <row r="53" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="241" t="n">
         <f aca="false">IF([1]Schedule!$E$71&gt;0,[1]Schedule!$B$71," ")</f>
-        <v>46167</v>
+        <v>46532</v>
       </c>
       <c r="B53" s="87" t="str">
         <f aca="false">IF([1]Schedule!$E$71&gt;0,[1]Schedule!$C$71," ")</f>

--- a/examples/ltd-latest/Financialaccounts.xlsx
+++ b/examples/ltd-latest/Financialaccounts.xlsx
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="637">
   <si>
     <t xml:space="preserve">Company Name (including Limited)</t>
   </si>
@@ -401,6 +401,12 @@
   </si>
   <si>
     <t xml:space="preserve">Retained Profit (Loss) for the year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copyright (C) 2006-2026 DIY Accounting Limited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licensed under the PolyForm Internal Use License 1.0.0 with an additional grant for accountants. Free to use, source available: https://spreadsheets.diyaccounting.co.uk</t>
   </si>
   <si>
     <t xml:space="preserve">www.diyaccounting.co.uk</t>
@@ -12289,7 +12295,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R86"/>
+  <dimension ref="A1:R89"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="10.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="0.82"/>
@@ -13840,6 +13846,16 @@
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="1" t="s">
+        <v>101</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -13916,39 +13932,39 @@
     <row r="2" s="53" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="386"/>
       <c r="B2" s="387" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C2" s="388" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D2" s="388" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E2" s="388" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F2" s="388" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G2" s="388" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H2" s="388" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I2" s="388" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J2" s="47"/>
       <c r="K2" s="387" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L2" s="389"/>
     </row>
     <row r="3" s="53" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="386"/>
       <c r="B3" s="390" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C3" s="390"/>
       <c r="D3" s="51"/>
@@ -13997,7 +14013,7 @@
       </c>
       <c r="J4" s="54"/>
       <c r="K4" s="393" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L4" s="68"/>
     </row>
@@ -14151,7 +14167,7 @@
       </c>
       <c r="J8" s="54"/>
       <c r="K8" s="393" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="L8" s="68"/>
     </row>
@@ -14305,7 +14321,7 @@
       </c>
       <c r="J12" s="54"/>
       <c r="K12" s="393" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L12" s="68"/>
     </row>
@@ -14426,7 +14442,7 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="391"/>
       <c r="B16" s="394" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C16" s="394"/>
       <c r="D16" s="57"/>
@@ -14471,7 +14487,7 @@
       </c>
       <c r="J17" s="54"/>
       <c r="K17" s="393" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="L17" s="68"/>
     </row>
@@ -14935,7 +14951,7 @@
       <c r="F1" s="405"/>
       <c r="G1" s="405"/>
       <c r="H1" s="406" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="I1" s="406"/>
       <c r="J1" s="406"/>
@@ -14943,7 +14959,7 @@
       <c r="L1" s="406"/>
       <c r="M1" s="405"/>
       <c r="N1" s="406" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="O1" s="406"/>
       <c r="P1" s="406"/>
@@ -14951,7 +14967,7 @@
       <c r="R1" s="406"/>
       <c r="S1" s="405"/>
       <c r="T1" s="406" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="U1" s="406"/>
       <c r="V1" s="406"/>
@@ -14971,63 +14987,63 @@
     <row r="2" s="420" customFormat="true" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="410"/>
       <c r="B2" s="411" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C2" s="412"/>
       <c r="D2" s="413" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E2" s="414"/>
       <c r="F2" s="413" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G2" s="414"/>
       <c r="H2" s="415" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="I2" s="414"/>
       <c r="J2" s="413" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K2" s="414"/>
       <c r="L2" s="413" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M2" s="414"/>
       <c r="N2" s="415" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="O2" s="414"/>
       <c r="P2" s="413" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Q2" s="414"/>
       <c r="R2" s="413" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="S2" s="414"/>
       <c r="T2" s="415" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="U2" s="414"/>
       <c r="V2" s="413" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="W2" s="414"/>
       <c r="X2" s="416" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="Y2" s="417"/>
       <c r="Z2" s="413" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AA2" s="414"/>
       <c r="AB2" s="413" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AC2" s="418"/>
       <c r="AD2" s="419" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AE2" s="419"/>
       <c r="AF2" s="419"/>
@@ -15065,7 +15081,7 @@
       <c r="AB3" s="423"/>
       <c r="AC3" s="68"/>
       <c r="AD3" s="427" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AE3" s="427"/>
       <c r="AF3" s="427"/>
@@ -15075,7 +15091,7 @@
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="391"/>
       <c r="B4" s="428" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C4" s="428"/>
       <c r="D4" s="428"/>
@@ -15456,7 +15472,7 @@
       <c r="AB11" s="78"/>
       <c r="AC11" s="68"/>
       <c r="AD11" s="427" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AE11" s="427"/>
       <c r="AF11" s="427"/>
@@ -15686,7 +15702,7 @@
       <c r="AB15" s="78"/>
       <c r="AC15" s="68"/>
       <c r="AD15" s="427" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AE15" s="427"/>
       <c r="AF15" s="427"/>
@@ -15916,7 +15932,7 @@
       <c r="AB19" s="78"/>
       <c r="AC19" s="68"/>
       <c r="AD19" s="427" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AE19" s="427"/>
       <c r="AF19" s="427"/>
@@ -16146,7 +16162,7 @@
       <c r="AB23" s="78"/>
       <c r="AC23" s="68"/>
       <c r="AD23" s="427" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AE23" s="427"/>
       <c r="AF23" s="427"/>
@@ -16454,7 +16470,7 @@
       </c>
       <c r="AC28" s="68"/>
       <c r="AD28" s="427" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AE28" s="427"/>
       <c r="AF28" s="427"/>
@@ -16665,7 +16681,7 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="451"/>
       <c r="B1" s="452" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C1" s="451"/>
       <c r="D1" s="451"/>
@@ -16713,7 +16729,7 @@
       </c>
       <c r="C3" s="451"/>
       <c r="D3" s="458" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E3" s="458"/>
       <c r="F3" s="458"/>
@@ -16725,7 +16741,7 @@
       <c r="I3" s="451"/>
       <c r="J3" s="451"/>
       <c r="K3" s="460" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L3" s="460"/>
       <c r="M3" s="460"/>
@@ -16747,10 +16763,10 @@
       <c r="D4" s="451"/>
       <c r="E4" s="451"/>
       <c r="F4" s="453" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G4" s="453" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H4" s="451"/>
       <c r="I4" s="451"/>
@@ -16771,7 +16787,7 @@
       </c>
       <c r="C5" s="451"/>
       <c r="D5" s="451" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E5" s="451"/>
       <c r="F5" s="463" t="n">
@@ -16790,7 +16806,7 @@
       <c r="N5" s="451"/>
       <c r="O5" s="451"/>
       <c r="P5" s="451" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="Q5" s="453"/>
     </row>
@@ -16802,7 +16818,7 @@
       </c>
       <c r="C6" s="451"/>
       <c r="D6" s="451" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E6" s="451"/>
       <c r="F6" s="463" t="n">
@@ -16835,7 +16851,7 @@
         <v>19</v>
       </c>
       <c r="Q6" s="453" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16846,7 +16862,7 @@
       </c>
       <c r="C7" s="451"/>
       <c r="D7" s="451" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E7" s="451"/>
       <c r="F7" s="463" t="n">
@@ -16879,7 +16895,7 @@
         <v>19</v>
       </c>
       <c r="Q7" s="453" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16890,7 +16906,7 @@
       </c>
       <c r="C8" s="451"/>
       <c r="D8" s="451" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E8" s="451"/>
       <c r="F8" s="463" t="n">
@@ -16902,7 +16918,7 @@
       </c>
       <c r="H8" s="451"/>
       <c r="I8" s="465" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="J8" s="451"/>
       <c r="K8" s="451"/>
@@ -16914,7 +16930,7 @@
         <v>25</v>
       </c>
       <c r="Q8" s="453" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16930,16 +16946,16 @@
       <c r="G9" s="453"/>
       <c r="H9" s="451"/>
       <c r="I9" s="465" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="J9" s="451"/>
       <c r="K9" s="451"/>
       <c r="L9" s="468" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M9" s="451"/>
       <c r="N9" s="469" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="O9" s="470"/>
       <c r="P9" s="468" t="n">
@@ -16955,7 +16971,7 @@
       </c>
       <c r="C10" s="451"/>
       <c r="D10" s="471" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E10" s="471"/>
       <c r="F10" s="471"/>
@@ -16969,7 +16985,7 @@
         <v>46326</v>
       </c>
       <c r="M10" s="453" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N10" s="472" t="n">
         <f aca="false">B8</f>
@@ -16999,7 +17015,7 @@
         <v>46691</v>
       </c>
       <c r="M11" s="473" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N11" s="472" t="n">
         <f aca="false">B32</f>
@@ -17022,7 +17038,7 @@
       <c r="G12" s="453"/>
       <c r="H12" s="451"/>
       <c r="I12" s="465" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="J12" s="451"/>
       <c r="K12" s="451"/>
@@ -17043,16 +17059,16 @@
       </c>
       <c r="C13" s="451"/>
       <c r="D13" s="458" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E13" s="458"/>
       <c r="F13" s="458"/>
       <c r="G13" s="453" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H13" s="451"/>
       <c r="I13" s="465" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="J13" s="451"/>
       <c r="K13" s="451"/>
@@ -17078,17 +17094,17 @@
       <c r="G14" s="453"/>
       <c r="H14" s="451"/>
       <c r="I14" s="458" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="J14" s="458"/>
       <c r="K14" s="458"/>
       <c r="L14" s="456"/>
       <c r="M14" s="451"/>
       <c r="N14" s="453" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="O14" s="453" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="P14" s="451"/>
       <c r="Q14" s="451"/>
@@ -17101,7 +17117,7 @@
       </c>
       <c r="C15" s="451"/>
       <c r="D15" s="471" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E15" s="471"/>
       <c r="F15" s="471"/>
@@ -17136,7 +17152,7 @@
       </c>
       <c r="H16" s="451"/>
       <c r="I16" s="475" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="J16" s="475"/>
       <c r="K16" s="475"/>
@@ -17168,7 +17184,7 @@
       </c>
       <c r="H17" s="451"/>
       <c r="I17" s="475" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="J17" s="475"/>
       <c r="K17" s="475"/>
@@ -17191,7 +17207,7 @@
       </c>
       <c r="C18" s="451"/>
       <c r="D18" s="471" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E18" s="471"/>
       <c r="F18" s="471"/>
@@ -17226,7 +17242,7 @@
       </c>
       <c r="H19" s="451"/>
       <c r="I19" s="458" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="J19" s="458"/>
       <c r="K19" s="458"/>
@@ -17275,7 +17291,7 @@
       </c>
       <c r="C21" s="451"/>
       <c r="D21" s="22" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="481" t="n">
@@ -17284,7 +17300,7 @@
       <c r="G21" s="453"/>
       <c r="H21" s="451"/>
       <c r="I21" s="458" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="J21" s="458"/>
       <c r="K21" s="458"/>
@@ -17706,10 +17722,10 @@
     <row r="1" s="42" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="37"/>
       <c r="B1" s="38" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D1" s="40" t="n">
         <f aca="false">Admin!B9</f>
@@ -17921,7 +17937,7 @@
       </c>
       <c r="EG1" s="39"/>
       <c r="EH1" s="39" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="EI1" s="39"/>
       <c r="EJ1" s="40" t="n">
@@ -17933,365 +17949,365 @@
     <row r="2" s="46" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="43"/>
       <c r="B2" s="44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C2" s="39"/>
       <c r="D2" s="45" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E2" s="39"/>
       <c r="F2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="L2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N2" s="39"/>
       <c r="O2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P2" s="39"/>
       <c r="Q2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="R2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="S2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="T2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="U2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="V2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="W2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="X2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Y2" s="39"/>
       <c r="Z2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AA2" s="39"/>
       <c r="AB2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AC2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="AD2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AE2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AF2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AG2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="AH2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AI2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AJ2" s="39"/>
       <c r="AK2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AL2" s="39"/>
       <c r="AM2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AN2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="AO2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AP2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AQ2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AR2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="AS2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AT2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AU2" s="39"/>
       <c r="AV2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AW2" s="39"/>
       <c r="AX2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AY2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="AZ2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BA2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BB2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BC2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="BD2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BE2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BF2" s="39"/>
       <c r="BG2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BH2" s="39"/>
       <c r="BI2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BJ2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="BK2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BL2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BM2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BN2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="BO2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BP2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BQ2" s="39"/>
       <c r="BR2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BS2" s="39"/>
       <c r="BT2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BU2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="BV2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BW2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BX2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BY2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="BZ2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="CA2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="CB2" s="39"/>
       <c r="CC2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="CD2" s="39"/>
       <c r="CE2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="CF2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="CG2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="CH2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="CI2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="CJ2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="CK2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="CL2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="CM2" s="39"/>
       <c r="CN2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="CO2" s="39"/>
       <c r="CP2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="CQ2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="CR2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="CS2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="CT2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="CU2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="CV2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="CW2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="CX2" s="39"/>
       <c r="CY2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="CZ2" s="39"/>
       <c r="DA2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="DB2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="DC2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="DD2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="DE2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="DF2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="DG2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="DH2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="DI2" s="39"/>
       <c r="DJ2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="DK2" s="39"/>
       <c r="DL2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="DM2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="DN2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="DO2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="DP2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="DQ2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="DR2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="DS2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="DT2" s="39"/>
       <c r="DU2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="DV2" s="39"/>
       <c r="DW2" s="39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="DX2" s="39" t="s">
         <v>64</v>
       </c>
       <c r="DY2" s="39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="DZ2" s="39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="EA2" s="39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="EB2" s="39" t="s">
         <v>38</v>
       </c>
       <c r="EC2" s="39" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="ED2" s="39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="EE2" s="39"/>
       <c r="EF2" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="EG2" s="39"/>
       <c r="EH2" s="39"/>
       <c r="EI2" s="39"/>
       <c r="EJ2" s="45" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="EK2" s="39"/>
     </row>
@@ -18441,7 +18457,7 @@
     <row r="4" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="54"/>
       <c r="B4" s="55" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C4" s="56"/>
       <c r="Y4" s="54"/>
@@ -18577,7 +18593,7 @@
     <row r="5" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="54"/>
       <c r="B5" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C5" s="56"/>
       <c r="Y5" s="54"/>
@@ -18713,10 +18729,10 @@
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="54"/>
       <c r="B6" s="54" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D6" s="36" t="n">
         <f aca="false">OpenAccounts!G13</f>
@@ -18904,10 +18920,10 @@
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="54"/>
       <c r="B7" s="54" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D7" s="36" t="n">
         <f aca="false">OpenAccounts!H13</f>
@@ -19095,10 +19111,10 @@
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="54"/>
       <c r="B8" s="54" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D8" s="36" t="n">
         <f aca="false">OpenAccounts!I13</f>
@@ -19286,10 +19302,10 @@
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="54"/>
       <c r="B9" s="54" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D9" s="36" t="n">
         <f aca="false">OpenAccounts!J13</f>
@@ -19477,10 +19493,10 @@
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="54"/>
       <c r="B10" s="54" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D10" s="36" t="n">
         <f aca="false">OpenAccounts!K13</f>
@@ -19668,7 +19684,7 @@
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="54"/>
       <c r="B11" s="54" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C11" s="56"/>
       <c r="D11" s="36" t="n">
@@ -19894,7 +19910,7 @@
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="54"/>
       <c r="B12" s="54" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C12" s="56"/>
       <c r="D12" s="36" t="n">
@@ -20120,7 +20136,7 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="54"/>
       <c r="B13" s="54" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C13" s="56"/>
       <c r="D13" s="36" t="n">
@@ -20346,7 +20362,7 @@
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="54"/>
       <c r="B14" s="54" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C14" s="56"/>
       <c r="D14" s="36" t="n">
@@ -20572,7 +20588,7 @@
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="54"/>
       <c r="B15" s="54" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C15" s="56"/>
       <c r="D15" s="36" t="n">
@@ -20798,7 +20814,7 @@
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="54"/>
       <c r="B16" s="54" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C16" s="56"/>
       <c r="D16" s="36"/>
@@ -21020,10 +21036,10 @@
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="54"/>
       <c r="B17" s="54" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D17" s="36"/>
       <c r="E17" s="57"/>
@@ -21281,7 +21297,7 @@
     <row r="18" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="54"/>
       <c r="B18" s="55" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C18" s="56"/>
       <c r="Y18" s="54"/>
@@ -21417,7 +21433,7 @@
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="54"/>
       <c r="B19" s="54" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C19" s="56"/>
       <c r="D19" s="36" t="n">
@@ -21642,7 +21658,7 @@
         <v>34</v>
       </c>
       <c r="C20" s="56" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D20" s="36" t="n">
         <f aca="false">OpenAccounts!E16</f>
@@ -21700,7 +21716,7 @@
       </c>
       <c r="W20" s="36"/>
       <c r="X20" s="36" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Y20" s="54"/>
       <c r="Z20" s="36" t="n">
@@ -22008,7 +22024,7 @@
     <row r="21" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="54"/>
       <c r="B21" s="58" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C21" s="56"/>
       <c r="Y21" s="54"/>
@@ -22144,10 +22160,10 @@
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="54"/>
       <c r="B22" s="54" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C22" s="56" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D22" s="36" t="n">
         <f aca="false">OpenAccounts!G18</f>
@@ -22367,10 +22383,10 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="54"/>
       <c r="B23" s="54" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C23" s="56" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D23" s="36" t="n">
         <f aca="false">OpenAccounts!H18</f>
@@ -22593,7 +22609,7 @@
         <v>37</v>
       </c>
       <c r="C24" s="56" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D24" s="36" t="n">
         <f aca="false">OpenAccounts!I18</f>
@@ -22816,7 +22832,7 @@
         <v>38</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D25" s="36" t="n">
         <f aca="false">OpenAccounts!J18</f>
@@ -23040,7 +23056,7 @@
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="54"/>
       <c r="B26" s="54" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C26" s="56"/>
       <c r="D26" s="36" t="n">
@@ -23368,7 +23384,7 @@
     <row r="27" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="54"/>
       <c r="B27" s="55" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C27" s="56"/>
       <c r="Y27" s="54"/>
@@ -23507,7 +23523,7 @@
         <v>42</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D28" s="36" t="n">
         <f aca="false">-OpenAccounts!E20</f>
@@ -23875,7 +23891,7 @@
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="54"/>
       <c r="B29" s="54" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C29" s="56"/>
       <c r="D29" s="36" t="n">
@@ -24240,7 +24256,7 @@
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="54"/>
       <c r="B30" s="54" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C30" s="56"/>
       <c r="D30" s="36" t="n">
@@ -24461,10 +24477,10 @@
     <row r="31" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="54"/>
       <c r="B31" s="54" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D31" s="36" t="n">
         <f aca="false">-OpenAccounts!E23</f>
@@ -24796,10 +24812,10 @@
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="54"/>
       <c r="B32" s="54" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C32" s="56" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D32" s="36" t="n">
         <f aca="false">-OpenAccounts!I26</f>
@@ -25199,10 +25215,10 @@
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="54"/>
       <c r="B33" s="54" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D33" s="36" t="n">
         <f aca="false">-OpenAccounts!H26</f>
@@ -25602,10 +25618,10 @@
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="54"/>
       <c r="B34" s="54" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C34" s="56" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D34" s="36" t="n">
         <f aca="false">-OpenAccounts!G26</f>
@@ -25969,10 +25985,10 @@
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="54"/>
       <c r="B35" s="54" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D35" s="36" t="n">
         <f aca="false">-OpenAccounts!E24</f>
@@ -26307,7 +26323,7 @@
     <row r="36" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="54"/>
       <c r="B36" s="55" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C36" s="56"/>
       <c r="Y36" s="54"/>
@@ -26443,10 +26459,10 @@
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="54"/>
       <c r="B37" s="54" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C37" s="56" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D37" s="36" t="n">
         <f aca="false">OpenAccounts!E28</f>
@@ -26774,7 +26790,7 @@
     <row r="38" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="54"/>
       <c r="B38" s="55" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C38" s="56"/>
       <c r="Y38" s="54"/>
@@ -26913,7 +26929,7 @@
         <v>53</v>
       </c>
       <c r="C39" s="56" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D39" s="36" t="n">
         <f aca="false">-OpenAccounts!E30</f>
@@ -27241,10 +27257,10 @@
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="54"/>
       <c r="B40" s="54" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C40" s="56" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D40" s="36" t="n">
         <f aca="false">-OpenAccounts!E31</f>
@@ -27576,7 +27592,7 @@
     <row r="41" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="54"/>
       <c r="B41" s="55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C41" s="56"/>
       <c r="Y41" s="54"/>
@@ -27712,7 +27728,7 @@
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="54"/>
       <c r="B42" s="54" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C42" s="56"/>
       <c r="D42" s="36" t="n">
@@ -27901,7 +27917,7 @@
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="54"/>
       <c r="B43" s="54" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C43" s="56"/>
       <c r="D43" s="36" t="n">
@@ -28090,7 +28106,7 @@
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="54"/>
       <c r="B44" s="54" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C44" s="56"/>
       <c r="D44" s="36" t="n">
@@ -28409,7 +28425,7 @@
     <row r="46" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="54"/>
       <c r="B46" s="55" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C46" s="56"/>
       <c r="Y46" s="54"/>
@@ -28545,7 +28561,7 @@
     <row r="47" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="54"/>
       <c r="B47" s="54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C47" s="56"/>
       <c r="D47" s="57"/>
@@ -28733,7 +28749,7 @@
         <v>98</v>
       </c>
       <c r="C48" s="56" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D48" s="57"/>
       <c r="E48" s="57"/>
@@ -28918,7 +28934,7 @@
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="54"/>
       <c r="B49" s="54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C49" s="56"/>
       <c r="D49" s="57"/>
@@ -29238,7 +29254,7 @@
     <row r="51" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="54"/>
       <c r="B51" s="55" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C51" s="56"/>
       <c r="Y51" s="54"/>
@@ -29374,7 +29390,7 @@
     <row r="52" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="54"/>
       <c r="B52" s="55" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C52" s="56"/>
       <c r="Y52" s="54"/>
@@ -29510,10 +29526,10 @@
     <row r="53" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="54"/>
       <c r="B53" s="54" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C53" s="56" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D53" s="57"/>
       <c r="E53" s="57"/>
@@ -29730,10 +29746,10 @@
     <row r="54" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="54"/>
       <c r="B54" s="54" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C54" s="56" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D54" s="57"/>
       <c r="E54" s="57"/>
@@ -29950,10 +29966,10 @@
     <row r="55" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="54"/>
       <c r="B55" s="54" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C55" s="56" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D55" s="57"/>
       <c r="E55" s="57"/>
@@ -30173,7 +30189,7 @@
         <v>94</v>
       </c>
       <c r="C56" s="56" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D56" s="57"/>
       <c r="E56" s="57"/>
@@ -30390,10 +30406,10 @@
     <row r="57" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="54"/>
       <c r="B57" s="54" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C57" s="56" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D57" s="57"/>
       <c r="E57" s="57"/>
@@ -30610,10 +30626,10 @@
     <row r="58" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="54"/>
       <c r="B58" s="54" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C58" s="56" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D58" s="57"/>
       <c r="E58" s="57"/>
@@ -30942,7 +30958,7 @@
     <row r="59" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="54"/>
       <c r="B59" s="55" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C59" s="56"/>
       <c r="Y59" s="54"/>
@@ -31078,10 +31094,10 @@
     <row r="60" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="54"/>
       <c r="B60" s="54" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C60" s="56" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D60" s="57"/>
       <c r="E60" s="57"/>
@@ -31335,10 +31351,10 @@
     <row r="61" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="54"/>
       <c r="B61" s="54" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C61" s="56" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D61" s="57"/>
       <c r="E61" s="57"/>
@@ -31555,10 +31571,10 @@
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="54"/>
       <c r="B62" s="54" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C62" s="56" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D62" s="57"/>
       <c r="E62" s="57"/>
@@ -31775,7 +31791,7 @@
     <row r="63" s="57" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="54"/>
       <c r="B63" s="55" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C63" s="56"/>
       <c r="Y63" s="54"/>
@@ -31911,10 +31927,10 @@
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="54"/>
       <c r="B64" s="54" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C64" s="56" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D64" s="57"/>
       <c r="E64" s="57"/>
@@ -32131,10 +32147,10 @@
     <row r="65" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="54"/>
       <c r="B65" s="54" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C65" s="56" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D65" s="57"/>
       <c r="E65" s="57"/>
@@ -32354,7 +32370,7 @@
         <v>71</v>
       </c>
       <c r="C66" s="56" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D66" s="57"/>
       <c r="E66" s="57"/>
@@ -32607,7 +32623,7 @@
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="54"/>
       <c r="B67" s="54" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C67" s="56"/>
       <c r="D67" s="57"/>
@@ -32828,7 +32844,7 @@
         <v>73</v>
       </c>
       <c r="C68" s="56" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D68" s="57"/>
       <c r="E68" s="57"/>
@@ -33048,7 +33064,7 @@
         <v>74</v>
       </c>
       <c r="C69" s="56" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D69" s="57"/>
       <c r="E69" s="57"/>
@@ -33268,7 +33284,7 @@
         <v>75</v>
       </c>
       <c r="C70" s="56" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D70" s="57"/>
       <c r="E70" s="57"/>
@@ -33488,7 +33504,7 @@
         <v>76</v>
       </c>
       <c r="C71" s="56" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D71" s="57"/>
       <c r="E71" s="57"/>
@@ -33708,7 +33724,7 @@
         <v>77</v>
       </c>
       <c r="C72" s="56" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D72" s="57"/>
       <c r="E72" s="57"/>
@@ -33928,7 +33944,7 @@
         <v>78</v>
       </c>
       <c r="C73" s="56" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D73" s="57"/>
       <c r="E73" s="57"/>
@@ -34148,7 +34164,7 @@
         <v>79</v>
       </c>
       <c r="C74" s="56" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D74" s="57"/>
       <c r="E74" s="57"/>
@@ -34368,7 +34384,7 @@
         <v>80</v>
       </c>
       <c r="C75" s="56" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D75" s="57"/>
       <c r="E75" s="57"/>
@@ -34588,7 +34604,7 @@
         <v>81</v>
       </c>
       <c r="C76" s="56" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D76" s="57"/>
       <c r="E76" s="57"/>
@@ -34808,7 +34824,7 @@
         <v>82</v>
       </c>
       <c r="C77" s="56" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D77" s="57"/>
       <c r="E77" s="57"/>
@@ -35028,7 +35044,7 @@
         <v>83</v>
       </c>
       <c r="C78" s="56" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D78" s="57"/>
       <c r="E78" s="57"/>
@@ -35248,7 +35264,7 @@
         <v>84</v>
       </c>
       <c r="C79" s="56" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D79" s="57"/>
       <c r="E79" s="57"/>
@@ -35468,7 +35484,7 @@
         <v>85</v>
       </c>
       <c r="C80" s="56" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D80" s="57"/>
       <c r="E80" s="57"/>
@@ -35688,7 +35704,7 @@
         <v>86</v>
       </c>
       <c r="C81" s="56" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D81" s="57"/>
       <c r="E81" s="57"/>
@@ -35908,7 +35924,7 @@
         <v>87</v>
       </c>
       <c r="C82" s="56" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D82" s="57"/>
       <c r="E82" s="57"/>
@@ -36236,7 +36252,7 @@
         <v>88</v>
       </c>
       <c r="C83" s="56" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D83" s="57"/>
       <c r="E83" s="57"/>
@@ -36564,7 +36580,7 @@
         <v>89</v>
       </c>
       <c r="C84" s="56" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D84" s="57"/>
       <c r="E84" s="57"/>
@@ -36784,7 +36800,7 @@
         <v>90</v>
       </c>
       <c r="C85" s="56" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D85" s="57"/>
       <c r="E85" s="57"/>
@@ -37439,10 +37455,10 @@
     <row r="88" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="54"/>
       <c r="B88" s="54" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C88" s="56" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D88" s="57"/>
       <c r="E88" s="57"/>
@@ -37731,10 +37747,10 @@
     <row r="89" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="54"/>
       <c r="B89" s="54" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C89" s="56" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D89" s="57"/>
       <c r="E89" s="57"/>
@@ -38157,7 +38173,7 @@
     <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="54"/>
       <c r="B91" s="60" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C91" s="60"/>
       <c r="D91" s="36" t="n">
@@ -38885,10 +38901,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="62" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B1" s="63" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C1" s="64" t="n">
         <f aca="false">Admin!B10</f>
@@ -38963,49 +38979,49 @@
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="62"/>
       <c r="B3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N3" s="69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O3" s="68"/>
     </row>
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="70" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B4" s="71" t="n">
         <f aca="false">SUM(C4:N4)</f>
@@ -39063,7 +39079,7 @@
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="70" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B5" s="71" t="n">
         <f aca="false">SUM(C5:N5)</f>
@@ -39121,7 +39137,7 @@
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="70" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B6" s="71" t="n">
         <f aca="false">SUM(C6:N6)</f>
@@ -39488,7 +39504,7 @@
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="70" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B13" s="71" t="n">
         <f aca="false">SUM(C13:N13)</f>
@@ -39814,7 +39830,7 @@
     </row>
     <row r="20" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="70" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B20" s="71" t="n">
         <f aca="false">SUM(C20:N20)</f>
@@ -41165,7 +41181,7 @@
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="70" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B44" s="71" t="n">
         <f aca="false">SUM(C44:N44)</f>
@@ -41352,7 +41368,7 @@
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="90"/>
       <c r="C2" s="91" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D2" s="91"/>
       <c r="E2" s="90"/>
@@ -41366,7 +41382,7 @@
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="92" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D3" s="93" t="n">
         <f aca="false">Admin!B32</f>
@@ -41417,18 +41433,18 @@
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="99" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B6" s="99" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C6" s="100"/>
       <c r="D6" s="100"/>
       <c r="E6" s="99" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F6" s="99" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H6" s="89"/>
       <c r="I6" s="89"/>
@@ -41537,7 +41553,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="101" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D12" s="107" t="n">
         <f aca="false">Admin!B9</f>
@@ -41586,7 +41602,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="101" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D14" s="107" t="n">
         <f aca="false">D3</f>
@@ -42391,7 +42407,7 @@
     </row>
     <row r="54" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="110" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B54" s="104" t="n">
         <f aca="false">B51-B52</f>
@@ -42402,7 +42418,7 @@
       </c>
       <c r="D54" s="106"/>
       <c r="E54" s="110" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F54" s="104" t="n">
         <f aca="false">F51-F52</f>
@@ -42474,14 +42490,14 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="90"/>
       <c r="C1" s="111" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D1" s="111"/>
       <c r="E1" s="90"/>
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="112" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D2" s="113" t="n">
         <f aca="false">'PubP&amp;L'!D3</f>
@@ -42502,18 +42518,18 @@
     </row>
     <row r="4" s="114" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="99" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B4" s="99" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C4" s="88"/>
       <c r="D4" s="88"/>
       <c r="E4" s="99" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F4" s="99" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42594,7 +42610,7 @@
       </c>
       <c r="B12" s="115"/>
       <c r="C12" s="88" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E12" s="119" t="n">
         <f aca="false">IF(SUM(TrialBalance!EJ22:EJ24)&gt;0,SUM(TrialBalance!EJ22:EJ24)+TrialBalance!EJ25+TrialBalance!EJ26,TrialBalance!EJ25)</f>
@@ -42628,7 +42644,7 @@
       <c r="A15" s="115"/>
       <c r="B15" s="115"/>
       <c r="C15" s="117" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D15" s="117"/>
       <c r="E15" s="115"/>
@@ -42686,7 +42702,7 @@
       </c>
       <c r="B19" s="115"/>
       <c r="C19" s="88" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D19" s="88"/>
       <c r="E19" s="119" t="n">
@@ -42729,7 +42745,7 @@
         <v>42900</v>
       </c>
       <c r="C22" s="117" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D22" s="117"/>
       <c r="E22" s="118"/>
@@ -42755,7 +42771,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="117" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D24" s="117"/>
       <c r="E24" s="118"/>
@@ -42782,7 +42798,7 @@
         <v>225802</v>
       </c>
       <c r="C26" s="117" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D26" s="117"/>
       <c r="E26" s="118"/>
@@ -42834,7 +42850,7 @@
       </c>
       <c r="B30" s="118"/>
       <c r="C30" s="117" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D30" s="117"/>
       <c r="E30" s="115" t="n">
@@ -42869,18 +42885,18 @@
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="118" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B33" s="116" t="n">
         <f aca="false">B26-B31</f>
         <v>180802</v>
       </c>
       <c r="C33" s="117" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D33" s="117"/>
       <c r="E33" s="118" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F33" s="116" t="n">
         <f aca="false">F26-F31</f>
@@ -42912,7 +42928,7 @@
         <v>100</v>
       </c>
       <c r="C36" s="88" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E36" s="115"/>
       <c r="F36" s="115" t="n">
@@ -42959,18 +42975,18 @@
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="118" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B39" s="116" t="n">
         <f aca="false">SUM(B36:B38)</f>
         <v>180802</v>
       </c>
       <c r="C39" s="117" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D39" s="117"/>
       <c r="E39" s="118" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F39" s="116" t="n">
         <f aca="false">SUM(F36:F38)</f>
@@ -42980,21 +42996,21 @@
     </row>
     <row r="41" s="87" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="121" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B41" s="122" t="n">
         <f aca="false">D2</f>
         <v>46691</v>
       </c>
       <c r="C41" s="123" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D41" s="123"/>
       <c r="E41" s="123"/>
     </row>
     <row r="42" s="87" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="124" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B42" s="124"/>
       <c r="C42" s="124"/>
@@ -43003,7 +43019,7 @@
     </row>
     <row r="43" s="87" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="125" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B43" s="125"/>
       <c r="C43" s="125"/>
@@ -43012,7 +43028,7 @@
     </row>
     <row r="44" s="87" customFormat="true" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="124" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B44" s="124"/>
       <c r="C44" s="124"/>
@@ -43021,7 +43037,7 @@
     </row>
     <row r="45" s="87" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="124" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B45" s="124"/>
       <c r="C45" s="124"/>
@@ -43030,7 +43046,7 @@
     </row>
     <row r="46" s="87" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="124" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B46" s="124"/>
       <c r="C46" s="124"/>
@@ -43039,7 +43055,7 @@
     </row>
     <row r="47" s="87" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="124" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B47" s="124"/>
       <c r="C47" s="124"/>
@@ -43048,7 +43064,7 @@
     </row>
     <row r="48" s="87" customFormat="true" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="124" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B48" s="124"/>
       <c r="C48" s="124"/>
@@ -43057,7 +43073,7 @@
     </row>
     <row r="49" s="87" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="124" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B49" s="124"/>
       <c r="C49" s="124"/>
@@ -43066,7 +43082,7 @@
     </row>
     <row r="50" s="87" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="124" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B50" s="124"/>
       <c r="C50" s="124"/>
@@ -43075,7 +43091,7 @@
     </row>
     <row r="51" s="87" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="124" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B51" s="124"/>
       <c r="C51" s="124"/>
@@ -43084,7 +43100,7 @@
     </row>
     <row r="52" s="87" customFormat="true" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="126" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B52" s="126"/>
       <c r="C52" s="126"/>
@@ -43093,7 +43109,7 @@
     </row>
     <row r="53" s="87" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="124" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B53" s="124"/>
       <c r="C53" s="124"/>
@@ -43109,7 +43125,7 @@
     </row>
     <row r="55" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="129" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B55" s="129"/>
       <c r="C55" s="128"/>
@@ -43118,7 +43134,7 @@
     </row>
     <row r="56" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="129" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B56" s="129"/>
       <c r="C56" s="88" t="str">
@@ -43128,12 +43144,12 @@
     </row>
     <row r="57" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="129" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B57" s="129"/>
       <c r="C57" s="130" t="n">
         <f aca="true">TODAY()</f>
-        <v>46271</v>
+        <v>46274</v>
       </c>
       <c r="D57" s="130"/>
     </row>
@@ -43143,7 +43159,7 @@
     </row>
     <row r="59" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="129" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B59" s="129"/>
       <c r="C59" s="88" t="str">
@@ -43154,7 +43170,7 @@
     </row>
     <row r="60" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="129" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B60" s="129"/>
       <c r="C60" s="88" t="str">
@@ -43235,33 +43251,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="106" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="106" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" s="114" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="131"/>
       <c r="B4" s="132" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C4" s="132" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D4" s="132" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="132" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F4" s="132" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G4" s="132" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" s="114" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -43275,27 +43291,27 @@
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="131" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C6" s="131" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D6" s="131" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E6" s="131" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F6" s="131" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G6" s="131" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="106" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B7" s="131"/>
       <c r="C7" s="131"/>
@@ -43336,7 +43352,7 @@
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="101" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B9" s="108" t="n">
         <f aca="false">IF([1]Schedule!$E$64&gt;0,[1]Schedule!$E$64,0)</f>
@@ -43365,7 +43381,7 @@
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="101" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B10" s="108" t="n">
         <f aca="false">IF(([1]Schedule!$W$11+[1]Schedule!$W$64)&gt;0,[1]Schedule!$W$11+[1]Schedule!$W$64,0)</f>
@@ -43473,7 +43489,7 @@
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="101" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B15" s="108" t="n">
         <f aca="false">IF(([1]Schedule!$I$11+[1]Schedule!$I$64)&gt;0,[1]Schedule!$I$11+[1]Schedule!$I$64,0)</f>
@@ -43502,7 +43518,7 @@
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="101" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B16" s="108" t="n">
         <f aca="false">IF(([1]Schedule!$X$11+[1]Schedule!$X$64)&gt;0,[1]Schedule!$X$11+[1]Schedule!$X$64,0)</f>
@@ -43569,7 +43585,7 @@
     </row>
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="106" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B19" s="108"/>
       <c r="C19" s="108"/>
@@ -43610,17 +43626,17 @@
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="101" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="101" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="101" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43632,19 +43648,19 @@
         <v>0</v>
       </c>
       <c r="C27" s="89" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="101" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B28" s="135" t="n">
         <f aca="false">[1]Schedule!$H$13</f>
         <v>0.1</v>
       </c>
       <c r="C28" s="89" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43656,19 +43672,19 @@
         <v>0.2</v>
       </c>
       <c r="C29" s="89" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="101" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B30" s="135" t="n">
         <f aca="false">[1]Schedule!$H$32</f>
         <v>0.33</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D30" s="120"/>
     </row>
@@ -43681,17 +43697,17 @@
         <v>0.25</v>
       </c>
       <c r="C31" s="89" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="106" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="101" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D35" s="136" t="n">
         <f aca="false">TrialBalance!EJ66</f>
@@ -43701,12 +43717,12 @@
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="106" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="101" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B38" s="87"/>
       <c r="D38" s="137" t="n">
@@ -43722,12 +43738,12 @@
     </row>
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="106" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41" s="87" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="101" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B41" s="137" t="n">
         <f aca="false">'PubP&amp;L'!D3</f>
@@ -43795,7 +43811,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="140" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B20" s="140"/>
       <c r="C20" s="140"/>
@@ -43808,7 +43824,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="141" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B22" s="141"/>
       <c r="C22" s="141"/>
@@ -43876,7 +43892,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="144" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C50" s="145" t="str">
         <f aca="false">OpenAccounts!E4</f>
@@ -43910,28 +43926,28 @@
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D60" s="149" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E60" s="149"/>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F65" s="150" t="n">
         <f aca="false">'PubP&amp;L'!E5</f>
@@ -43941,17 +43957,17 @@
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D71" s="151" t="str">
         <f aca="false">OpenAccounts!E5</f>
@@ -43962,11 +43978,11 @@
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D74" s="152" t="n">
         <f aca="true">TODAY()</f>
-        <v>46271</v>
+        <v>46274</v>
       </c>
       <c r="E74" s="152"/>
       <c r="F74" s="152"/>
@@ -43987,7 +44003,7 @@
     </row>
     <row r="79" s="154" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="155" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
@@ -44002,7 +44018,7 @@
     </row>
     <row r="81" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="157" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B81" s="157"/>
       <c r="C81" s="157"/>
@@ -44015,7 +44031,7 @@
     </row>
     <row r="82" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="158" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B82" s="158"/>
       <c r="C82" s="159" t="n">
@@ -44054,7 +44070,7 @@
     </row>
     <row r="86" s="164" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="163" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B86" s="163"/>
       <c r="C86" s="163"/>
@@ -44067,7 +44083,7 @@
     </row>
     <row r="87" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="160" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B87" s="160"/>
       <c r="C87" s="160"/>
@@ -44077,7 +44093,7 @@
         <v>341283.333333333</v>
       </c>
       <c r="F87" s="166" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G87" s="166"/>
       <c r="H87" s="165" t="n">
@@ -44085,12 +44101,12 @@
         <v>0</v>
       </c>
       <c r="I87" s="144" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="88" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="160" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B88" s="160"/>
       <c r="C88" s="160"/>
@@ -44103,7 +44119,7 @@
     </row>
     <row r="89" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="167" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B89" s="167"/>
       <c r="C89" s="167"/>
@@ -44112,7 +44128,7 @@
         <v>0.944952873956146</v>
       </c>
       <c r="E89" s="169" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F89" s="169"/>
       <c r="G89" s="169"/>
@@ -44124,7 +44140,7 @@
     </row>
     <row r="90" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="160" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B90" s="160"/>
       <c r="C90" s="160"/>
@@ -44148,7 +44164,7 @@
     </row>
     <row r="92" s="164" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="163" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B92" s="163"/>
       <c r="C92" s="163"/>
@@ -44161,7 +44177,7 @@
     </row>
     <row r="93" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="160" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B93" s="160"/>
       <c r="C93" s="160"/>
@@ -44174,7 +44190,7 @@
     </row>
     <row r="94" s="144" customFormat="true" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="160" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B94" s="160"/>
       <c r="C94" s="160"/>
@@ -44183,7 +44199,7 @@
         <v>15000</v>
       </c>
       <c r="E94" s="170" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F94" s="170"/>
       <c r="G94" s="170"/>
@@ -44192,7 +44208,7 @@
     </row>
     <row r="95" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="167" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B95" s="167"/>
       <c r="C95" s="167"/>
@@ -44208,7 +44224,7 @@
     </row>
     <row r="96" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="167" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B96" s="167"/>
       <c r="C96" s="167"/>
@@ -44227,7 +44243,7 @@
       <c r="B97" s="172"/>
       <c r="C97" s="172"/>
       <c r="D97" s="147" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E97" s="147"/>
       <c r="F97" s="173" t="n">
@@ -44235,7 +44251,7 @@
         <v>60</v>
       </c>
       <c r="G97" s="174" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H97" s="159" t="n">
         <f aca="false">'PubP&amp;L'!E5</f>
@@ -44251,7 +44267,7 @@
       <c r="B98" s="172"/>
       <c r="C98" s="172"/>
       <c r="D98" s="147" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E98" s="147"/>
       <c r="F98" s="173" t="n">
@@ -44259,7 +44275,7 @@
         <v>25</v>
       </c>
       <c r="G98" s="174" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H98" s="159" t="n">
         <f aca="false">'PubP&amp;L'!E5</f>
@@ -44270,7 +44286,7 @@
     <row r="99" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="100" s="164" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="163" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B100" s="163"/>
       <c r="C100" s="163"/>
@@ -44283,7 +44299,7 @@
     </row>
     <row r="101" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="160" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B101" s="160"/>
       <c r="C101" s="160"/>
@@ -44296,7 +44312,7 @@
     </row>
     <row r="102" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="160" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B102" s="160"/>
       <c r="C102" s="160"/>
@@ -44309,7 +44325,7 @@
     </row>
     <row r="103" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="160" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B103" s="160"/>
       <c r="C103" s="160"/>
@@ -44322,7 +44338,7 @@
     </row>
     <row r="104" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="160" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B104" s="160"/>
       <c r="C104" s="160"/>
@@ -44346,7 +44362,7 @@
     </row>
     <row r="106" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="160" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B106" s="160"/>
       <c r="C106" s="160"/>
@@ -44359,7 +44375,7 @@
     </row>
     <row r="107" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="160" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B107" s="160"/>
       <c r="C107" s="160"/>
@@ -44372,7 +44388,7 @@
     </row>
     <row r="108" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="160" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B108" s="160"/>
       <c r="C108" s="160"/>
@@ -44385,7 +44401,7 @@
     </row>
     <row r="109" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="160" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B109" s="160"/>
       <c r="C109" s="160"/>
@@ -44398,7 +44414,7 @@
     </row>
     <row r="110" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="160" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B110" s="160"/>
       <c r="C110" s="160"/>
@@ -44422,7 +44438,7 @@
     </row>
     <row r="112" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="160" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B112" s="160"/>
       <c r="C112" s="160"/>
@@ -44435,7 +44451,7 @@
     </row>
     <row r="113" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="167" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B113" s="167"/>
       <c r="C113" s="167"/>
@@ -44451,7 +44467,7 @@
     </row>
     <row r="114" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="160" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B114" s="160"/>
       <c r="C114" s="160"/>
@@ -44464,7 +44480,7 @@
     </row>
     <row r="115" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="160" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B115" s="160"/>
       <c r="C115" s="160"/>
@@ -44491,7 +44507,7 @@
       <c r="B118" s="170"/>
       <c r="C118" s="170"/>
       <c r="D118" s="144" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="119" s="144" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44501,14 +44517,14 @@
       </c>
       <c r="C119" s="170"/>
       <c r="D119" s="144" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F119" s="144" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G119" s="159" t="n">
         <f aca="true">TODAY()</f>
-        <v>46271</v>
+        <v>46274</v>
       </c>
       <c r="H119" s="159"/>
     </row>
@@ -44640,7 +44656,7 @@
       <c r="C2" s="181"/>
       <c r="D2" s="181"/>
       <c r="E2" s="182" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F2" s="182"/>
       <c r="G2" s="182"/>
@@ -44648,7 +44664,7 @@
       <c r="I2" s="182"/>
       <c r="J2" s="183"/>
       <c r="K2" s="184" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L2" s="185"/>
     </row>
@@ -44662,11 +44678,11 @@
       <c r="G3" s="179"/>
       <c r="H3" s="179"/>
       <c r="I3" s="186" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J3" s="186"/>
       <c r="K3" s="186" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L3" s="177"/>
     </row>
@@ -44687,7 +44703,7 @@
     <row r="5" s="120" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="187"/>
       <c r="B5" s="188" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C5" s="188"/>
       <c r="D5" s="188"/>
@@ -44697,7 +44713,7 @@
       </c>
       <c r="F5" s="189"/>
       <c r="G5" s="190" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H5" s="189" t="n">
         <f aca="false">Admin!N7</f>
@@ -44729,7 +44745,7 @@
       <c r="A7" s="176"/>
       <c r="B7" s="177"/>
       <c r="C7" s="193" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D7" s="193"/>
       <c r="E7" s="193"/>
@@ -44748,7 +44764,7 @@
       <c r="A8" s="176"/>
       <c r="B8" s="177"/>
       <c r="C8" s="193" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D8" s="193"/>
       <c r="E8" s="193"/>
@@ -44781,7 +44797,7 @@
       <c r="A10" s="176"/>
       <c r="B10" s="195"/>
       <c r="C10" s="196" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D10" s="196"/>
       <c r="E10" s="196"/>
@@ -44813,7 +44829,7 @@
     <row r="12" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="187"/>
       <c r="B12" s="185" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C12" s="185"/>
       <c r="D12" s="185"/>
@@ -44846,7 +44862,7 @@
     <row r="14" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="187"/>
       <c r="B14" s="185" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C14" s="185"/>
       <c r="D14" s="185"/>
@@ -44862,7 +44878,7 @@
     <row r="15" s="120" customFormat="true" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="187"/>
       <c r="B15" s="197" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C15" s="197"/>
       <c r="D15" s="197"/>
@@ -44885,14 +44901,14 @@
       </c>
       <c r="J15" s="178"/>
       <c r="K15" s="201" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L15" s="202"/>
     </row>
     <row r="16" s="120" customFormat="true" ht="12.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="187"/>
       <c r="B16" s="193" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C16" s="193"/>
       <c r="D16" s="193"/>
@@ -44915,14 +44931,14 @@
       </c>
       <c r="J16" s="178"/>
       <c r="K16" s="201" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L16" s="202"/>
     </row>
     <row r="17" s="120" customFormat="true" ht="12.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="187"/>
       <c r="B17" s="193" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C17" s="193"/>
       <c r="D17" s="193"/>
@@ -44942,14 +44958,14 @@
       </c>
       <c r="J17" s="178"/>
       <c r="K17" s="201" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L17" s="202"/>
     </row>
     <row r="18" s="120" customFormat="true" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="187"/>
       <c r="B18" s="193" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C18" s="193"/>
       <c r="D18" s="193"/>
@@ -44969,7 +44985,7 @@
       </c>
       <c r="J18" s="178"/>
       <c r="K18" s="201" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L18" s="202"/>
     </row>
@@ -44991,7 +45007,7 @@
       <c r="A20" s="187"/>
       <c r="B20" s="195"/>
       <c r="C20" s="196" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D20" s="196"/>
       <c r="E20" s="196"/>
@@ -45023,7 +45039,7 @@
     <row r="22" s="120" customFormat="true" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="187"/>
       <c r="B22" s="207" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C22" s="207"/>
       <c r="D22" s="207"/>
@@ -45056,7 +45072,7 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="176"/>
       <c r="B24" s="211" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C24" s="177"/>
       <c r="D24" s="177"/>
@@ -45089,7 +45105,7 @@
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="176"/>
       <c r="B26" s="211" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C26" s="177"/>
       <c r="D26" s="177"/>
@@ -45122,7 +45138,7 @@
     <row r="28" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="187"/>
       <c r="B28" s="188" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C28" s="188"/>
       <c r="D28" s="188"/>
@@ -45171,29 +45187,29 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="180" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B31" s="217" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C31" s="218" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D31" s="218" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E31" s="218" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F31" s="219" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G31" s="219" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H31" s="219"/>
       <c r="I31" s="219" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J31" s="179"/>
       <c r="K31" s="178"/>
@@ -45306,7 +45322,7 @@
       </c>
       <c r="B35" s="214"/>
       <c r="C35" s="196" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D35" s="196"/>
       <c r="E35" s="196"/>
@@ -45339,7 +45355,7 @@
       <c r="A37" s="187"/>
       <c r="B37" s="185"/>
       <c r="C37" s="196" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D37" s="196"/>
       <c r="E37" s="196"/>
@@ -45372,7 +45388,7 @@
       <c r="A39" s="187"/>
       <c r="B39" s="230"/>
       <c r="C39" s="196" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D39" s="196"/>
       <c r="E39" s="196"/>
@@ -45420,7 +45436,7 @@
     <row r="44" s="120" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="187"/>
       <c r="B44" s="196" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C44" s="196"/>
       <c r="D44" s="185"/>
@@ -45440,12 +45456,12 @@
       <c r="D45" s="177"/>
       <c r="E45" s="177"/>
       <c r="F45" s="233" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G45" s="178"/>
       <c r="H45" s="179"/>
       <c r="I45" s="233" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J45" s="178"/>
       <c r="K45" s="178"/>
@@ -45453,10 +45469,10 @@
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="234" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B46" s="235" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C46" s="235"/>
       <c r="D46" s="177"/>
@@ -45476,12 +45492,12 @@
       <c r="D47" s="177"/>
       <c r="E47" s="223"/>
       <c r="F47" s="237" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G47" s="178"/>
       <c r="H47" s="179"/>
       <c r="I47" s="238" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J47" s="178"/>
       <c r="K47" s="178"/>
@@ -45490,7 +45506,7 @@
     <row r="48" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="187"/>
       <c r="B48" s="239" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C48" s="239"/>
       <c r="D48" s="240" t="n">
@@ -45704,7 +45720,7 @@
     <row r="57" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="222"/>
       <c r="B57" s="239" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C57" s="239"/>
       <c r="D57" s="240" t="n">
@@ -45845,7 +45861,7 @@
     </row>
     <row r="63" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="243" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B63" s="243"/>
       <c r="C63" s="243"/>
@@ -46060,7 +46076,7 @@
     <row r="72" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="187"/>
       <c r="B72" s="193" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C72" s="193"/>
       <c r="D72" s="240" t="n">
@@ -46216,7 +46232,7 @@
     <row r="79" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="187"/>
       <c r="B79" s="244" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C79" s="244"/>
       <c r="D79" s="222" t="n">
@@ -46265,12 +46281,12 @@
       <c r="D81" s="185"/>
       <c r="E81" s="185"/>
       <c r="F81" s="233" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G81" s="178"/>
       <c r="H81" s="179"/>
       <c r="I81" s="233" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J81" s="178"/>
       <c r="K81" s="178"/>
@@ -46279,7 +46295,7 @@
     <row r="82" s="120" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="185"/>
       <c r="B82" s="235" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C82" s="235"/>
       <c r="D82" s="185"/>
@@ -46299,12 +46315,12 @@
       <c r="D83" s="185"/>
       <c r="E83" s="223"/>
       <c r="F83" s="237" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G83" s="178"/>
       <c r="H83" s="179"/>
       <c r="I83" s="238" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J83" s="178"/>
       <c r="K83" s="178"/>
@@ -46312,10 +46328,10 @@
     </row>
     <row r="84" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="247" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B84" s="243" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C84" s="243"/>
       <c r="D84" s="248" t="n">
@@ -46471,7 +46487,7 @@
     <row r="91" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="176"/>
       <c r="B91" s="249" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C91" s="249"/>
       <c r="D91" s="250" t="n">
@@ -46483,7 +46499,7 @@
         <v>46691</v>
       </c>
       <c r="F91" s="251" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G91" s="251"/>
       <c r="H91" s="251"/>
@@ -46511,10 +46527,10 @@
     </row>
     <row r="93" s="120" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="252" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B93" s="196" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C93" s="196"/>
       <c r="D93" s="196"/>
@@ -46536,7 +46552,7 @@
     <row r="94" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="176"/>
       <c r="B94" s="255" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C94" s="255"/>
       <c r="D94" s="256" t="n">
@@ -46558,7 +46574,7 @@
     <row r="95" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="176"/>
       <c r="B95" s="255" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C95" s="255"/>
       <c r="D95" s="256" t="n">
@@ -46580,7 +46596,7 @@
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="176"/>
       <c r="B96" s="255" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C96" s="255"/>
       <c r="D96" s="256" t="n">
@@ -46602,7 +46618,7 @@
     <row r="97" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="180"/>
       <c r="B97" s="255" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C97" s="255"/>
       <c r="D97" s="256" t="n">
@@ -46638,7 +46654,7 @@
     <row r="99" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="208"/>
       <c r="B99" s="196" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C99" s="196"/>
       <c r="D99" s="196"/>
@@ -46693,10 +46709,10 @@
     </row>
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="247" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B102" s="196" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C102" s="196"/>
       <c r="D102" s="196"/>
@@ -46735,7 +46751,7 @@
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="208"/>
       <c r="B104" s="258" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C104" s="258"/>
       <c r="D104" s="258"/>
@@ -46872,7 +46888,7 @@
       <c r="D1" s="261"/>
       <c r="E1" s="261"/>
       <c r="F1" s="262" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G1" s="262"/>
       <c r="H1" s="262"/>
@@ -47001,7 +47017,7 @@
       <c r="AM3" s="265"/>
       <c r="AN3" s="265"/>
       <c r="AO3" s="266" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP3" s="266"/>
       <c r="AQ3" s="266"/>
@@ -47011,7 +47027,7 @@
       <c r="A4" s="264"/>
       <c r="B4" s="264"/>
       <c r="C4" s="267" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D4" s="267"/>
       <c r="E4" s="267"/>
@@ -47034,7 +47050,7 @@
       <c r="V4" s="264"/>
       <c r="W4" s="264"/>
       <c r="X4" s="268" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Y4" s="268"/>
       <c r="Z4" s="268"/>
@@ -47128,7 +47144,7 @@
       <c r="V6" s="264"/>
       <c r="W6" s="264"/>
       <c r="X6" s="269" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Y6" s="269"/>
       <c r="Z6" s="269"/>
@@ -47176,7 +47192,7 @@
       <c r="V7" s="264"/>
       <c r="W7" s="264"/>
       <c r="X7" s="270" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Y7" s="270"/>
       <c r="Z7" s="270"/>
@@ -47247,7 +47263,7 @@
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="271" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B9" s="271"/>
       <c r="C9" s="271"/>
@@ -47296,7 +47312,7 @@
     <row r="10" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="272"/>
       <c r="B10" s="272" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C10" s="272"/>
       <c r="D10" s="272"/>
@@ -47344,7 +47360,7 @@
     <row r="11" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="272"/>
       <c r="B11" s="272" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C11" s="272"/>
       <c r="D11" s="272"/>
@@ -47392,7 +47408,7 @@
     <row r="12" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="272"/>
       <c r="B12" s="272" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C12" s="272"/>
       <c r="D12" s="272"/>
@@ -47440,7 +47456,7 @@
     <row r="13" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="272"/>
       <c r="B13" s="272" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C13" s="272"/>
       <c r="D13" s="272"/>
@@ -47488,7 +47504,7 @@
     <row r="14" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="272"/>
       <c r="B14" s="272" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C14" s="272"/>
       <c r="D14" s="272"/>
@@ -47536,7 +47552,7 @@
     <row r="15" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="272"/>
       <c r="B15" s="272" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C15" s="272"/>
       <c r="D15" s="272"/>
@@ -47629,7 +47645,7 @@
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="273" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B17" s="273"/>
       <c r="C17" s="273"/>
@@ -47678,7 +47694,7 @@
     <row r="18" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="272"/>
       <c r="B18" s="274" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C18" s="274"/>
       <c r="D18" s="274"/>
@@ -47796,7 +47812,7 @@
       <c r="S20" s="276"/>
       <c r="T20" s="276"/>
       <c r="U20" s="276" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="V20" s="276"/>
       <c r="W20" s="276"/>
@@ -47815,7 +47831,7 @@
       <c r="AJ20" s="276"/>
       <c r="AK20" s="276"/>
       <c r="AL20" s="276" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AM20" s="276"/>
       <c r="AN20" s="276"/>
@@ -47885,7 +47901,7 @@
     <row r="22" s="120" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="276"/>
       <c r="B22" s="276" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C22" s="276"/>
       <c r="D22" s="276"/>
@@ -48225,7 +48241,7 @@
     </row>
     <row r="29" s="149" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="273" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B29" s="273"/>
       <c r="C29" s="273"/>
@@ -48320,7 +48336,7 @@
     <row r="31" s="120" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="276"/>
       <c r="B31" s="276" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C31" s="276"/>
       <c r="D31" s="276"/>
@@ -48346,7 +48362,7 @@
       <c r="X31" s="288"/>
       <c r="Y31" s="276"/>
       <c r="Z31" s="276" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AA31" s="276"/>
       <c r="AB31" s="276"/>
@@ -48370,7 +48386,7 @@
     <row r="32" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="272"/>
       <c r="B32" s="272" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C32" s="272"/>
       <c r="D32" s="272"/>
@@ -48383,7 +48399,7 @@
       <c r="K32" s="272"/>
       <c r="L32" s="272"/>
       <c r="M32" s="272" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N32" s="272"/>
       <c r="O32" s="272"/>
@@ -48398,7 +48414,7 @@
       <c r="X32" s="288"/>
       <c r="Y32" s="272"/>
       <c r="Z32" s="272" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA32" s="272"/>
       <c r="AB32" s="272"/>
@@ -48498,7 +48514,7 @@
       <c r="X34" s="288"/>
       <c r="Y34" s="272"/>
       <c r="Z34" s="272" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AA34" s="272"/>
       <c r="AB34" s="272"/>
@@ -48517,14 +48533,14 @@
       <c r="AO34" s="272"/>
       <c r="AP34" s="272"/>
       <c r="AQ34" s="291" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AR34" s="272"/>
     </row>
     <row r="35" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="272"/>
       <c r="B35" s="292" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C35" s="292"/>
       <c r="D35" s="292"/>
@@ -48596,7 +48612,7 @@
       <c r="X36" s="288"/>
       <c r="Y36" s="272"/>
       <c r="Z36" s="272" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AA36" s="272"/>
       <c r="AB36" s="272"/>
@@ -48620,7 +48636,7 @@
     <row r="37" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="272"/>
       <c r="B37" s="272" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C37" s="272"/>
       <c r="D37" s="272"/>
@@ -48714,7 +48730,7 @@
     <row r="39" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="272"/>
       <c r="B39" s="272" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C39" s="272"/>
       <c r="D39" s="272"/>
@@ -48740,7 +48756,7 @@
       <c r="X39" s="288"/>
       <c r="Y39" s="272"/>
       <c r="Z39" s="272" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AA39" s="272"/>
       <c r="AB39" s="272"/>
@@ -48788,7 +48804,7 @@
       <c r="X40" s="288"/>
       <c r="Y40" s="272"/>
       <c r="Z40" s="272" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AA40" s="272"/>
       <c r="AB40" s="272"/>
@@ -48812,7 +48828,7 @@
     <row r="41" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="272"/>
       <c r="B41" s="272" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C41" s="272"/>
       <c r="D41" s="272"/>
@@ -48860,7 +48876,7 @@
     <row r="42" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="272"/>
       <c r="B42" s="272" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C42" s="272"/>
       <c r="D42" s="272"/>
@@ -48954,7 +48970,7 @@
     <row r="44" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="272"/>
       <c r="B44" s="272" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C44" s="272"/>
       <c r="D44" s="272"/>
@@ -49048,7 +49064,7 @@
     <row r="46" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="272"/>
       <c r="B46" s="272" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C46" s="272"/>
       <c r="D46" s="272"/>
@@ -49166,7 +49182,7 @@
       <c r="X48" s="288"/>
       <c r="Y48" s="272"/>
       <c r="Z48" s="276" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA48" s="276"/>
       <c r="AB48" s="276"/>
@@ -49190,7 +49206,7 @@
     <row r="49" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="272"/>
       <c r="B49" s="276" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C49" s="276"/>
       <c r="D49" s="276"/>
@@ -49216,7 +49232,7 @@
       <c r="X49" s="288"/>
       <c r="Y49" s="272"/>
       <c r="Z49" s="292" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AA49" s="292"/>
       <c r="AB49" s="292"/>
@@ -49264,7 +49280,7 @@
       <c r="X50" s="288"/>
       <c r="Y50" s="272"/>
       <c r="Z50" s="292" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AA50" s="292"/>
       <c r="AB50" s="292"/>
@@ -49288,7 +49304,7 @@
     <row r="51" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="272"/>
       <c r="B51" s="272" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C51" s="272"/>
       <c r="D51" s="272"/>
@@ -49360,7 +49376,7 @@
       <c r="X52" s="288"/>
       <c r="Y52" s="272"/>
       <c r="Z52" s="272" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AA52" s="272"/>
       <c r="AB52" s="272"/>
@@ -49408,7 +49424,7 @@
       <c r="X53" s="288"/>
       <c r="Y53" s="272"/>
       <c r="Z53" s="272" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AA53" s="272"/>
       <c r="AB53" s="272"/>
@@ -49432,7 +49448,7 @@
     <row r="54" s="87" customFormat="true" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="272"/>
       <c r="B54" s="276" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C54" s="276"/>
       <c r="D54" s="276"/>
@@ -49504,7 +49520,7 @@
       <c r="X55" s="288"/>
       <c r="Y55" s="272"/>
       <c r="Z55" s="272" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AA55" s="272"/>
       <c r="AB55" s="272"/>
@@ -49528,7 +49544,7 @@
     <row r="56" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="272"/>
       <c r="B56" s="272" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C56" s="272"/>
       <c r="D56" s="272"/>
@@ -49554,7 +49570,7 @@
       <c r="X56" s="288"/>
       <c r="Y56" s="272"/>
       <c r="Z56" s="272" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AA56" s="272"/>
       <c r="AB56" s="272"/>
@@ -49624,7 +49640,7 @@
     <row r="58" s="87" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="272"/>
       <c r="B58" s="272" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C58" s="272"/>
       <c r="D58" s="272"/>
@@ -49650,7 +49666,7 @@
       <c r="X58" s="288"/>
       <c r="Y58" s="272"/>
       <c r="Z58" s="272" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AA58" s="272"/>
       <c r="AB58" s="272"/>
@@ -49698,7 +49714,7 @@
       <c r="X59" s="288"/>
       <c r="Y59" s="272"/>
       <c r="Z59" s="272" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AA59" s="272"/>
       <c r="AB59" s="272"/>
@@ -49813,7 +49829,7 @@
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="293" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B62" s="293"/>
       <c r="C62" s="293"/>
@@ -49861,7 +49877,7 @@
     </row>
     <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="294" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B63" s="294"/>
       <c r="C63" s="294"/>
@@ -49909,7 +49925,7 @@
     </row>
     <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="296" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B64" s="296"/>
       <c r="C64" s="296"/>
@@ -50009,7 +50025,7 @@
         <v>1</v>
       </c>
       <c r="C66" s="276" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D66" s="276"/>
       <c r="E66" s="276"/>
@@ -50046,7 +50062,7 @@
         <v>1</v>
       </c>
       <c r="AJ66" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AK66" s="300" t="n">
         <f aca="false">'PubP&amp;L'!F9</f>
@@ -50108,7 +50124,7 @@
     </row>
     <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="273" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B68" s="273"/>
       <c r="C68" s="273"/>
@@ -50206,7 +50222,7 @@
         <v>3</v>
       </c>
       <c r="C70" s="276" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D70" s="276"/>
       <c r="E70" s="276"/>
@@ -50232,7 +50248,7 @@
       </c>
       <c r="X70" s="301"/>
       <c r="Y70" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z70" s="302" t="n">
         <f aca="false">IF(CorporationTax!K22&gt;0,CorporationTax!K22," ")</f>
@@ -50309,7 +50325,7 @@
         <v>4</v>
       </c>
       <c r="C72" s="276" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D72" s="276"/>
       <c r="E72" s="276"/>
@@ -50335,7 +50351,7 @@
       </c>
       <c r="X72" s="301"/>
       <c r="Y72" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z72" s="302" t="str">
         <f aca="false">IF(OpenAccounts!Q5&gt;0,OpenAccounts!Q5," ")</f>
@@ -50395,7 +50411,7 @@
       <c r="AF73" s="272"/>
       <c r="AG73" s="272"/>
       <c r="AH73" s="303" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AI73" s="303"/>
       <c r="AJ73" s="303"/>
@@ -50414,7 +50430,7 @@
         <v>5</v>
       </c>
       <c r="C74" s="304" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D74" s="304"/>
       <c r="E74" s="304"/>
@@ -50450,7 +50466,7 @@
         <v>5</v>
       </c>
       <c r="AI74" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ74" s="302" t="n">
         <f aca="false">SUM(Z69:AF70)-SUM(Z72:AF73)</f>
@@ -50471,7 +50487,7 @@
         <v>6</v>
       </c>
       <c r="C75" s="276" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D75" s="276"/>
       <c r="E75" s="276"/>
@@ -50519,7 +50535,7 @@
       <c r="A76" s="272"/>
       <c r="B76" s="276"/>
       <c r="C76" s="304" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D76" s="304"/>
       <c r="E76" s="304"/>
@@ -50555,7 +50571,7 @@
         <v>6</v>
       </c>
       <c r="AI76" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ76" s="302" t="n">
         <f aca="false">IF(-TrialBalance!EJ58&gt;0,-TrialBalance!EJ58," ")</f>
@@ -50622,7 +50638,7 @@
         <v>11</v>
       </c>
       <c r="C78" s="276" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D78" s="276"/>
       <c r="E78" s="276"/>
@@ -50658,7 +50674,7 @@
         <v>11</v>
       </c>
       <c r="AI78" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ78" s="302"/>
       <c r="AK78" s="302"/>
@@ -50722,7 +50738,7 @@
         <v>12</v>
       </c>
       <c r="C80" s="276" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D80" s="276"/>
       <c r="E80" s="276"/>
@@ -50758,7 +50774,7 @@
         <v>14</v>
       </c>
       <c r="AI80" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ80" s="302"/>
       <c r="AK80" s="302"/>
@@ -50818,7 +50834,7 @@
     </row>
     <row r="82" s="87" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="307" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B82" s="307"/>
       <c r="C82" s="307"/>
@@ -50916,7 +50932,7 @@
         <v>16</v>
       </c>
       <c r="C84" s="276" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D84" s="276"/>
       <c r="E84" s="276"/>
@@ -50942,7 +50958,7 @@
       </c>
       <c r="X84" s="301"/>
       <c r="Y84" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z84" s="309"/>
       <c r="AA84" s="309"/>
@@ -51016,7 +51032,7 @@
         <v>17</v>
       </c>
       <c r="C86" s="276" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D86" s="276"/>
       <c r="E86" s="276"/>
@@ -51042,7 +51058,7 @@
       </c>
       <c r="X86" s="301"/>
       <c r="Y86" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z86" s="309"/>
       <c r="AA86" s="309"/>
@@ -51099,7 +51115,7 @@
       <c r="AF87" s="272"/>
       <c r="AG87" s="272"/>
       <c r="AH87" s="303" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AI87" s="303"/>
       <c r="AJ87" s="303"/>
@@ -51118,7 +51134,7 @@
         <v>18</v>
       </c>
       <c r="C88" s="310" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D88" s="310"/>
       <c r="E88" s="310"/>
@@ -51154,7 +51170,7 @@
         <v>18</v>
       </c>
       <c r="AI88" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ88" s="309"/>
       <c r="AK88" s="309"/>
@@ -51293,7 +51309,7 @@
       <c r="AF91" s="272"/>
       <c r="AG91" s="272"/>
       <c r="AH91" s="303" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AI91" s="303"/>
       <c r="AJ91" s="303"/>
@@ -51312,7 +51328,7 @@
         <v>21</v>
       </c>
       <c r="C92" s="312" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D92" s="312"/>
       <c r="E92" s="312"/>
@@ -51348,7 +51364,7 @@
         <v>21</v>
       </c>
       <c r="AI92" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ92" s="302" t="n">
         <f aca="false">IF(AJ74&gt;0,AJ74+SUM(AJ76:AJ80)+AJ88,0)</f>
@@ -51411,7 +51427,7 @@
     </row>
     <row r="94" s="87" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="307" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B94" s="307"/>
       <c r="C94" s="307"/>
@@ -51509,7 +51525,7 @@
         <v>24</v>
       </c>
       <c r="C96" s="276" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D96" s="276"/>
       <c r="E96" s="276"/>
@@ -51535,7 +51551,7 @@
       </c>
       <c r="X96" s="301"/>
       <c r="Y96" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z96" s="309"/>
       <c r="AA96" s="309"/>
@@ -51609,7 +51625,7 @@
         <v>30</v>
       </c>
       <c r="C98" s="276" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D98" s="276"/>
       <c r="E98" s="276"/>
@@ -51635,7 +51651,7 @@
       </c>
       <c r="X98" s="315"/>
       <c r="Y98" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z98" s="309"/>
       <c r="AA98" s="309"/>
@@ -51661,7 +51677,7 @@
       <c r="A99" s="272"/>
       <c r="B99" s="276"/>
       <c r="C99" s="276" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D99" s="276"/>
       <c r="E99" s="276"/>
@@ -51757,7 +51773,7 @@
         <v>31</v>
       </c>
       <c r="C101" s="292" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D101" s="292"/>
       <c r="E101" s="292"/>
@@ -51807,7 +51823,7 @@
       <c r="A102" s="272"/>
       <c r="B102" s="272"/>
       <c r="C102" s="292" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D102" s="292"/>
       <c r="E102" s="292"/>
@@ -51903,7 +51919,7 @@
         <v>32</v>
       </c>
       <c r="C104" s="276" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D104" s="276"/>
       <c r="E104" s="276"/>
@@ -51929,7 +51945,7 @@
       </c>
       <c r="X104" s="301"/>
       <c r="Y104" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z104" s="309"/>
       <c r="AA104" s="309"/>
@@ -52003,7 +52019,7 @@
         <v>35</v>
       </c>
       <c r="C106" s="276" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D106" s="276"/>
       <c r="E106" s="276"/>
@@ -52029,7 +52045,7 @@
       </c>
       <c r="X106" s="315"/>
       <c r="Y106" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z106" s="309"/>
       <c r="AA106" s="309"/>
@@ -52178,7 +52194,7 @@
       <c r="AF109" s="272"/>
       <c r="AG109" s="272"/>
       <c r="AH109" s="303" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AI109" s="303"/>
       <c r="AJ109" s="303"/>
@@ -52197,7 +52213,7 @@
         <v>37</v>
       </c>
       <c r="C110" s="319" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D110" s="319"/>
       <c r="E110" s="319"/>
@@ -52233,7 +52249,7 @@
         <v>37</v>
       </c>
       <c r="AI110" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ110" s="302" t="n">
         <f aca="false">AJ92-Z96-Z98-Z104-Z106</f>
@@ -52296,7 +52312,7 @@
     </row>
     <row r="112" s="87" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="307" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B112" s="307"/>
       <c r="C112" s="307"/>
@@ -52394,7 +52410,7 @@
         <v>38</v>
       </c>
       <c r="C114" s="276" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D114" s="276"/>
       <c r="E114" s="276"/>
@@ -52420,7 +52436,7 @@
       </c>
       <c r="X114" s="301"/>
       <c r="Y114" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z114" s="309"/>
       <c r="AA114" s="309"/>
@@ -52494,7 +52510,7 @@
         <v>39</v>
       </c>
       <c r="C116" s="276" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D116" s="276"/>
       <c r="E116" s="276"/>
@@ -52546,7 +52562,7 @@
       <c r="A117" s="272"/>
       <c r="B117" s="276"/>
       <c r="C117" s="276" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D117" s="276"/>
       <c r="E117" s="276"/>
@@ -52596,7 +52612,7 @@
         <v>40</v>
       </c>
       <c r="C118" s="276" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D118" s="276"/>
       <c r="E118" s="276"/>
@@ -52694,7 +52710,7 @@
         <v>41</v>
       </c>
       <c r="C120" s="276" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D120" s="276"/>
       <c r="E120" s="276"/>
@@ -52792,7 +52808,7 @@
         <v>42</v>
       </c>
       <c r="C122" s="292" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D122" s="272"/>
       <c r="E122" s="272"/>
@@ -52828,7 +52844,7 @@
         <v>42</v>
       </c>
       <c r="AI122" s="325" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AJ122" s="325"/>
       <c r="AK122" s="272"/>
@@ -52844,7 +52860,7 @@
       <c r="A123" s="272"/>
       <c r="B123" s="272"/>
       <c r="C123" s="326" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D123" s="327"/>
       <c r="E123" s="327"/>
@@ -52891,7 +52907,7 @@
     <row r="124" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="276"/>
       <c r="B124" s="276" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C124" s="276"/>
       <c r="D124" s="276"/>
@@ -52939,7 +52955,7 @@
     <row r="125" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="276"/>
       <c r="B125" s="276" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C125" s="276"/>
       <c r="D125" s="276"/>
@@ -52951,7 +52967,7 @@
       <c r="J125" s="276"/>
       <c r="K125" s="276"/>
       <c r="L125" s="276" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M125" s="276"/>
       <c r="N125" s="276"/>
@@ -52966,7 +52982,7 @@
       <c r="W125" s="276"/>
       <c r="X125" s="276"/>
       <c r="Y125" s="276" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z125" s="276"/>
       <c r="AA125" s="276"/>
@@ -52977,7 +52993,7 @@
       <c r="AF125" s="276"/>
       <c r="AG125" s="276"/>
       <c r="AH125" s="276" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AI125" s="276"/>
       <c r="AJ125" s="276"/>
@@ -53011,7 +53027,7 @@
         <v>44</v>
       </c>
       <c r="M126" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N126" s="328" t="n">
         <f aca="false">CorporationTax!F33</f>
@@ -53045,7 +53061,7 @@
         <v>46</v>
       </c>
       <c r="AI126" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ126" s="330" t="n">
         <f aca="false">CorporationTax!J33</f>
@@ -53058,7 +53074,7 @@
       <c r="AO126" s="330"/>
       <c r="AP126" s="330"/>
       <c r="AQ126" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AR126" s="272"/>
     </row>
@@ -53129,7 +53145,7 @@
         <v>54</v>
       </c>
       <c r="M128" s="299" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N128" s="328" t="n">
         <f aca="false">IF(CorporationTax!A34&gt;0,CorporationTax!F34," ")</f>
@@ -53163,7 +53179,7 @@
         <v>56</v>
       </c>
       <c r="AI128" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ128" s="330" t="n">
         <f aca="false">CorporationTax!J34</f>
@@ -53176,7 +53192,7 @@
       <c r="AO128" s="330"/>
       <c r="AP128" s="330"/>
       <c r="AQ128" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AR128" s="272"/>
     </row>
@@ -53261,7 +53277,7 @@
       <c r="AF130" s="272"/>
       <c r="AG130" s="272"/>
       <c r="AH130" s="303" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AI130" s="303"/>
       <c r="AJ130" s="303"/>
@@ -53316,7 +53332,7 @@
         <v>63</v>
       </c>
       <c r="AI131" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ131" s="330" t="n">
         <f aca="false">AJ126+AJ128</f>
@@ -53329,7 +53345,7 @@
       <c r="AO131" s="330"/>
       <c r="AP131" s="330"/>
       <c r="AQ131" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AR131" s="272"/>
     </row>
@@ -53385,7 +53401,7 @@
         <v>64</v>
       </c>
       <c r="C133" s="276" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D133" s="276"/>
       <c r="E133" s="276"/>
@@ -53409,7 +53425,7 @@
         <v>64</v>
       </c>
       <c r="W133" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="X133" s="333"/>
       <c r="Y133" s="330" t="n">
@@ -53422,7 +53438,7 @@
       <c r="AC133" s="330"/>
       <c r="AD133" s="333"/>
       <c r="AE133" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AF133" s="272"/>
       <c r="AG133" s="272"/>
@@ -53490,7 +53506,7 @@
         <v>65</v>
       </c>
       <c r="C135" s="276" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D135" s="276"/>
       <c r="E135" s="276"/>
@@ -53514,7 +53530,7 @@
         <v>65</v>
       </c>
       <c r="W135" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="X135" s="333"/>
       <c r="Y135" s="330" t="n">
@@ -53527,7 +53543,7 @@
       <c r="AC135" s="330"/>
       <c r="AD135" s="333"/>
       <c r="AE135" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AF135" s="272"/>
       <c r="AG135" s="272"/>
@@ -53595,7 +53611,7 @@
         <v>66</v>
       </c>
       <c r="C137" s="276" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D137" s="276"/>
       <c r="E137" s="276"/>
@@ -53626,7 +53642,7 @@
       <c r="Y137" s="334"/>
       <c r="Z137" s="334"/>
       <c r="AA137" s="331" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AB137" s="272"/>
       <c r="AC137" s="272"/>
@@ -53698,7 +53714,7 @@
         <v>67</v>
       </c>
       <c r="C139" s="276" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D139" s="276"/>
       <c r="E139" s="276"/>
@@ -53796,7 +53812,7 @@
         <v>68</v>
       </c>
       <c r="C141" s="276" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D141" s="276"/>
       <c r="E141" s="276"/>
@@ -53820,7 +53836,7 @@
         <v>68</v>
       </c>
       <c r="W141" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="X141" s="333"/>
       <c r="Y141" s="333"/>
@@ -53830,7 +53846,7 @@
       <c r="AC141" s="333"/>
       <c r="AD141" s="333"/>
       <c r="AE141" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AF141" s="272"/>
       <c r="AG141" s="272"/>
@@ -53898,7 +53914,7 @@
         <v>69</v>
       </c>
       <c r="C143" s="276" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D143" s="276"/>
       <c r="E143" s="276"/>
@@ -53922,7 +53938,7 @@
         <v>69</v>
       </c>
       <c r="W143" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="X143" s="333"/>
       <c r="Y143" s="333"/>
@@ -53932,7 +53948,7 @@
       <c r="AC143" s="333"/>
       <c r="AD143" s="333"/>
       <c r="AE143" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AF143" s="272"/>
       <c r="AG143" s="272"/>
@@ -53983,7 +53999,7 @@
       <c r="AF144" s="272"/>
       <c r="AG144" s="272"/>
       <c r="AH144" s="303" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AI144" s="303"/>
       <c r="AJ144" s="303"/>
@@ -54002,7 +54018,7 @@
         <v>70</v>
       </c>
       <c r="C145" s="335" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D145" s="335"/>
       <c r="E145" s="335"/>
@@ -54038,7 +54054,7 @@
         <v>70</v>
       </c>
       <c r="AI145" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ145" s="330" t="n">
         <f aca="false">Y135</f>
@@ -54051,7 +54067,7 @@
       <c r="AO145" s="330"/>
       <c r="AP145" s="330"/>
       <c r="AQ145" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AR145" s="272"/>
     </row>
@@ -54143,7 +54159,7 @@
       <c r="AM147" s="311"/>
       <c r="AN147" s="311"/>
       <c r="AO147" s="266" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AP147" s="266"/>
       <c r="AQ147" s="266"/>
@@ -54201,7 +54217,7 @@
         <v>79</v>
       </c>
       <c r="C149" s="276" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D149" s="276"/>
       <c r="E149" s="276"/>
@@ -54237,7 +54253,7 @@
       </c>
       <c r="AH149" s="315"/>
       <c r="AI149" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ149" s="333"/>
       <c r="AK149" s="333"/>
@@ -54247,7 +54263,7 @@
       <c r="AO149" s="333"/>
       <c r="AP149" s="333"/>
       <c r="AQ149" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AR149" s="272"/>
     </row>
@@ -54303,7 +54319,7 @@
         <v>80</v>
       </c>
       <c r="C151" s="292" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D151" s="292"/>
       <c r="E151" s="292"/>
@@ -54353,7 +54369,7 @@
       <c r="A152" s="272"/>
       <c r="B152" s="272"/>
       <c r="C152" s="292" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D152" s="292"/>
       <c r="E152" s="292"/>
@@ -54449,7 +54465,7 @@
         <v>84</v>
       </c>
       <c r="C154" s="276" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D154" s="276"/>
       <c r="E154" s="276"/>
@@ -54485,7 +54501,7 @@
         <v>84</v>
       </c>
       <c r="AI154" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ154" s="330" t="n">
         <f aca="false">IF(TrialBalance!EH35&gt;0,TrialBalance!EH35,0)</f>
@@ -54498,7 +54514,7 @@
       <c r="AO154" s="330"/>
       <c r="AP154" s="330"/>
       <c r="AQ154" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AR154" s="272"/>
     </row>
@@ -54554,7 +54570,7 @@
         <v>85</v>
       </c>
       <c r="C156" s="276" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D156" s="276"/>
       <c r="E156" s="276"/>
@@ -54590,7 +54606,7 @@
         <v>85</v>
       </c>
       <c r="AI156" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ156" s="333"/>
       <c r="AK156" s="333"/>
@@ -54600,7 +54616,7 @@
       <c r="AO156" s="333"/>
       <c r="AP156" s="333"/>
       <c r="AQ156" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AR156" s="272"/>
     </row>
@@ -54685,7 +54701,7 @@
       <c r="AF158" s="272"/>
       <c r="AG158" s="272"/>
       <c r="AH158" s="303" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AI158" s="303"/>
       <c r="AJ158" s="303"/>
@@ -54704,7 +54720,7 @@
         <v>86</v>
       </c>
       <c r="C159" s="336" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D159" s="336"/>
       <c r="E159" s="336"/>
@@ -54740,7 +54756,7 @@
         <v>86</v>
       </c>
       <c r="AI159" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ159" s="330" t="n">
         <f aca="false">IF(AJ145&gt;0,AJ145+AJ149-AJ154,0)</f>
@@ -54753,7 +54769,7 @@
       <c r="AO159" s="330"/>
       <c r="AP159" s="330"/>
       <c r="AQ159" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AR159" s="272"/>
     </row>
@@ -54805,7 +54821,7 @@
     </row>
     <row r="161" s="87" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="307" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B161" s="307"/>
       <c r="C161" s="307"/>
@@ -54903,7 +54919,7 @@
         <v>91</v>
       </c>
       <c r="C163" s="276" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D163" s="276"/>
       <c r="E163" s="276"/>
@@ -54939,7 +54955,7 @@
         <v>91</v>
       </c>
       <c r="AI163" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ163" s="330"/>
       <c r="AK163" s="330"/>
@@ -54949,7 +54965,7 @@
       <c r="AO163" s="330"/>
       <c r="AP163" s="330"/>
       <c r="AQ163" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AR163" s="272"/>
     </row>
@@ -55005,7 +55021,7 @@
         <v>92</v>
       </c>
       <c r="C165" s="337" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D165" s="337"/>
       <c r="E165" s="337"/>
@@ -55038,7 +55054,7 @@
       <c r="AF165" s="272"/>
       <c r="AG165" s="272"/>
       <c r="AH165" s="303" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AI165" s="303"/>
       <c r="AJ165" s="303"/>
@@ -55089,7 +55105,7 @@
         <v>92</v>
       </c>
       <c r="AI166" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ166" s="330" t="n">
         <f aca="false">IF(AJ159&gt;0,AJ159-AJ163,0)</f>
@@ -55102,7 +55118,7 @@
       <c r="AO166" s="330"/>
       <c r="AP166" s="330"/>
       <c r="AQ166" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AR166" s="272"/>
     </row>
@@ -55158,7 +55174,7 @@
         <v>93</v>
       </c>
       <c r="C168" s="276" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D168" s="276"/>
       <c r="E168" s="276"/>
@@ -55191,7 +55207,7 @@
       <c r="AF168" s="272"/>
       <c r="AG168" s="272"/>
       <c r="AH168" s="303" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AI168" s="303"/>
       <c r="AJ168" s="303"/>
@@ -55242,7 +55258,7 @@
         <v>93</v>
       </c>
       <c r="AI169" s="305" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AJ169" s="330" t="str">
         <f aca="false">IF(AJ163&gt;0,AJ163-AJ159," ")</f>
@@ -55255,7 +55271,7 @@
       <c r="AO169" s="330"/>
       <c r="AP169" s="330"/>
       <c r="AQ169" s="331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AR169" s="272"/>
     </row>
@@ -55307,7 +55323,7 @@
     </row>
     <row r="171" s="87" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="338" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B171" s="338"/>
       <c r="C171" s="338"/>
@@ -55355,7 +55371,7 @@
     </row>
     <row r="172" s="87" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="307" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B172" s="307"/>
       <c r="C172" s="307"/>
@@ -55471,7 +55487,7 @@
       <c r="U174" s="276"/>
       <c r="V174" s="276"/>
       <c r="W174" s="276" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="X174" s="276"/>
       <c r="Y174" s="276"/>
@@ -55485,7 +55501,7 @@
       <c r="AG174" s="276"/>
       <c r="AH174" s="276"/>
       <c r="AI174" s="276" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AJ174" s="276"/>
       <c r="AK174" s="276"/>
@@ -55500,7 +55516,7 @@
     <row r="175" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="272"/>
       <c r="B175" s="274" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C175" s="274"/>
       <c r="D175" s="274"/>
@@ -55508,7 +55524,7 @@
       <c r="F175" s="276"/>
       <c r="G175" s="276"/>
       <c r="H175" s="276" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I175" s="276"/>
       <c r="J175" s="276"/>
@@ -55530,7 +55546,7 @@
       <c r="X175" s="324"/>
       <c r="Y175" s="324"/>
       <c r="Z175" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AA175" s="340"/>
       <c r="AB175" s="340"/>
@@ -55545,7 +55561,7 @@
       </c>
       <c r="AJ175" s="324"/>
       <c r="AK175" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL175" s="341"/>
       <c r="AM175" s="341"/>
@@ -55604,7 +55620,7 @@
     <row r="177" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="272"/>
       <c r="B177" s="274" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C177" s="274"/>
       <c r="D177" s="274"/>
@@ -55612,7 +55628,7 @@
       <c r="F177" s="276"/>
       <c r="G177" s="276"/>
       <c r="H177" s="276" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I177" s="276"/>
       <c r="J177" s="276"/>
@@ -55634,7 +55650,7 @@
       <c r="X177" s="324"/>
       <c r="Y177" s="324"/>
       <c r="Z177" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AA177" s="328" t="n">
         <f aca="false">IF((CorporationTax!I15+CorporationTax!I17)&gt;0,CorporationTax!I15+CorporationTax!I17," ")</f>
@@ -55652,7 +55668,7 @@
       </c>
       <c r="AJ177" s="324"/>
       <c r="AK177" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL177" s="328" t="n">
         <f aca="false">IF(CorporationTax!I18&lt;&gt;0,CorporationTax!I18," ")</f>
@@ -55714,7 +55730,7 @@
     <row r="179" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="272"/>
       <c r="B179" s="274" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C179" s="274"/>
       <c r="D179" s="274"/>
@@ -55722,7 +55738,7 @@
       <c r="F179" s="276"/>
       <c r="G179" s="276"/>
       <c r="H179" s="276" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I179" s="276"/>
       <c r="J179" s="276"/>
@@ -55744,7 +55760,7 @@
       <c r="X179" s="324"/>
       <c r="Y179" s="324"/>
       <c r="Z179" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AA179" s="328" t="str">
         <f aca="false">IF(CorporationTax!I16&gt;0,CorporationTax!I16," ")</f>
@@ -55762,7 +55778,7 @@
       </c>
       <c r="AJ179" s="324"/>
       <c r="AK179" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL179" s="341"/>
       <c r="AM179" s="341"/>
@@ -55821,7 +55837,7 @@
     <row r="181" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="272"/>
       <c r="B181" s="274" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C181" s="274"/>
       <c r="D181" s="274"/>
@@ -55829,7 +55845,7 @@
       <c r="F181" s="276"/>
       <c r="G181" s="276"/>
       <c r="H181" s="276" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I181" s="276"/>
       <c r="J181" s="276"/>
@@ -55851,7 +55867,7 @@
       <c r="X181" s="324"/>
       <c r="Y181" s="324"/>
       <c r="Z181" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AA181" s="340"/>
       <c r="AB181" s="340"/>
@@ -55866,7 +55882,7 @@
       </c>
       <c r="AJ181" s="324"/>
       <c r="AK181" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL181" s="341"/>
       <c r="AM181" s="341"/>
@@ -55925,7 +55941,7 @@
     <row r="183" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="272"/>
       <c r="B183" s="274" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C183" s="274"/>
       <c r="D183" s="274"/>
@@ -55933,7 +55949,7 @@
       <c r="F183" s="276"/>
       <c r="G183" s="276"/>
       <c r="H183" s="276" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I183" s="276"/>
       <c r="J183" s="276"/>
@@ -55955,7 +55971,7 @@
       <c r="X183" s="324"/>
       <c r="Y183" s="324"/>
       <c r="Z183" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AA183" s="340"/>
       <c r="AB183" s="340"/>
@@ -55970,7 +55986,7 @@
       </c>
       <c r="AJ183" s="324"/>
       <c r="AK183" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL183" s="341"/>
       <c r="AM183" s="341"/>
@@ -56028,7 +56044,7 @@
     </row>
     <row r="185" s="87" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="307" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B185" s="307"/>
       <c r="C185" s="307"/>
@@ -56098,7 +56114,7 @@
       <c r="U186" s="276"/>
       <c r="V186" s="276"/>
       <c r="W186" s="276" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="X186" s="276"/>
       <c r="Y186" s="276"/>
@@ -56112,7 +56128,7 @@
       <c r="AG186" s="276"/>
       <c r="AH186" s="276"/>
       <c r="AI186" s="276" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AJ186" s="276"/>
       <c r="AK186" s="276"/>
@@ -56127,7 +56143,7 @@
     <row r="187" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="272"/>
       <c r="B187" s="274" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C187" s="274"/>
       <c r="D187" s="274"/>
@@ -56135,7 +56151,7 @@
       <c r="F187" s="276"/>
       <c r="G187" s="276"/>
       <c r="H187" s="276" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I187" s="276"/>
       <c r="J187" s="276"/>
@@ -56157,7 +56173,7 @@
       <c r="X187" s="324"/>
       <c r="Y187" s="324"/>
       <c r="Z187" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AA187" s="309"/>
       <c r="AB187" s="309"/>
@@ -56172,7 +56188,7 @@
       </c>
       <c r="AJ187" s="324"/>
       <c r="AK187" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL187" s="309"/>
       <c r="AM187" s="309"/>
@@ -56239,7 +56255,7 @@
       <c r="F189" s="272"/>
       <c r="G189" s="272"/>
       <c r="H189" s="292" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I189" s="292"/>
       <c r="J189" s="292"/>
@@ -56289,7 +56305,7 @@
       <c r="F190" s="272"/>
       <c r="G190" s="272"/>
       <c r="H190" s="292" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I190" s="292"/>
       <c r="J190" s="292"/>
@@ -56376,7 +56392,7 @@
     </row>
     <row r="192" s="87" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="307" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B192" s="307"/>
       <c r="C192" s="307"/>
@@ -56476,7 +56492,7 @@
       <c r="C194" s="345"/>
       <c r="D194" s="272"/>
       <c r="E194" s="276" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F194" s="272"/>
       <c r="G194" s="272"/>
@@ -56512,7 +56528,7 @@
       </c>
       <c r="AJ194" s="324"/>
       <c r="AK194" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL194" s="328" t="n">
         <f aca="false">IF(CorporationTax!F79&gt;0,CorporationTax!F79," ")</f>
@@ -56579,7 +56595,7 @@
       <c r="C196" s="346"/>
       <c r="D196" s="347"/>
       <c r="E196" s="348" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F196" s="272"/>
       <c r="G196" s="272"/>
@@ -56629,7 +56645,7 @@
       <c r="C197" s="346"/>
       <c r="D197" s="272"/>
       <c r="E197" s="349" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F197" s="272"/>
       <c r="G197" s="272"/>
@@ -56725,7 +56741,7 @@
       <c r="C199" s="345"/>
       <c r="D199" s="272"/>
       <c r="E199" s="276" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F199" s="272"/>
       <c r="G199" s="272"/>
@@ -56761,7 +56777,7 @@
       </c>
       <c r="AJ199" s="324"/>
       <c r="AK199" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL199" s="309"/>
       <c r="AM199" s="309"/>
@@ -56825,7 +56841,7 @@
       <c r="C201" s="345"/>
       <c r="D201" s="272"/>
       <c r="E201" s="276" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F201" s="272"/>
       <c r="G201" s="272"/>
@@ -56861,7 +56877,7 @@
       </c>
       <c r="AJ201" s="324"/>
       <c r="AK201" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL201" s="309"/>
       <c r="AM201" s="309"/>
@@ -56919,7 +56935,7 @@
     </row>
     <row r="203" s="87" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="338" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B203" s="338"/>
       <c r="C203" s="338"/>
@@ -57018,7 +57034,7 @@
       </c>
       <c r="C205" s="345"/>
       <c r="D205" s="276" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E205" s="276"/>
       <c r="F205" s="276"/>
@@ -57029,7 +57045,7 @@
       <c r="K205" s="272"/>
       <c r="L205" s="272"/>
       <c r="M205" s="350" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N205" s="350"/>
       <c r="O205" s="350"/>
@@ -57044,7 +57060,7 @@
       <c r="X205" s="350"/>
       <c r="Y205" s="272"/>
       <c r="Z205" s="276" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AA205" s="276"/>
       <c r="AB205" s="276"/>
@@ -57055,7 +57071,7 @@
       <c r="AG205" s="276"/>
       <c r="AH205" s="276"/>
       <c r="AI205" s="351" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AJ205" s="351"/>
       <c r="AK205" s="351"/>
@@ -57086,7 +57102,7 @@
       <c r="N206" s="324"/>
       <c r="O206" s="324"/>
       <c r="P206" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q206" s="328" t="str">
         <f aca="false">IF(Z72&gt;0,Z72," ")</f>
@@ -57101,7 +57117,7 @@
       <c r="X206" s="328"/>
       <c r="Y206" s="272"/>
       <c r="Z206" s="304" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AA206" s="304"/>
       <c r="AB206" s="304"/>
@@ -57116,7 +57132,7 @@
       </c>
       <c r="AJ206" s="324"/>
       <c r="AK206" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL206" s="309"/>
       <c r="AM206" s="309"/>
@@ -57179,7 +57195,7 @@
       </c>
       <c r="C208" s="345"/>
       <c r="D208" s="276" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E208" s="276"/>
       <c r="F208" s="276"/>
@@ -57190,7 +57206,7 @@
       <c r="K208" s="276"/>
       <c r="L208" s="276"/>
       <c r="M208" s="350" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N208" s="350"/>
       <c r="O208" s="350"/>
@@ -57205,7 +57221,7 @@
       <c r="X208" s="350"/>
       <c r="Y208" s="272"/>
       <c r="Z208" s="276" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AA208" s="347"/>
       <c r="AB208" s="276"/>
@@ -57216,7 +57232,7 @@
       <c r="AG208" s="276"/>
       <c r="AH208" s="276"/>
       <c r="AI208" s="351" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AJ208" s="351"/>
       <c r="AK208" s="351"/>
@@ -57233,7 +57249,7 @@
       <c r="B209" s="276"/>
       <c r="C209" s="276"/>
       <c r="D209" s="310" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E209" s="304"/>
       <c r="F209" s="304"/>
@@ -57249,7 +57265,7 @@
       <c r="N209" s="324"/>
       <c r="O209" s="324"/>
       <c r="P209" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q209" s="309"/>
       <c r="R209" s="309"/>
@@ -57274,7 +57290,7 @@
       </c>
       <c r="AJ209" s="324"/>
       <c r="AK209" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL209" s="309"/>
       <c r="AM209" s="309"/>
@@ -57289,7 +57305,7 @@
       <c r="B210" s="276"/>
       <c r="C210" s="276"/>
       <c r="D210" s="276" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E210" s="304"/>
       <c r="F210" s="304"/>
@@ -57385,7 +57401,7 @@
       </c>
       <c r="C212" s="345"/>
       <c r="D212" s="276" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E212" s="276"/>
       <c r="F212" s="276"/>
@@ -57396,7 +57412,7 @@
       <c r="K212" s="272"/>
       <c r="L212" s="272"/>
       <c r="M212" s="350" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N212" s="350"/>
       <c r="O212" s="350"/>
@@ -57411,7 +57427,7 @@
       <c r="X212" s="350"/>
       <c r="Y212" s="272"/>
       <c r="Z212" s="276" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AA212" s="347"/>
       <c r="AB212" s="276"/>
@@ -57422,7 +57438,7 @@
       <c r="AG212" s="276"/>
       <c r="AH212" s="276"/>
       <c r="AI212" s="351" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AJ212" s="351"/>
       <c r="AK212" s="351"/>
@@ -57439,7 +57455,7 @@
       <c r="B213" s="276"/>
       <c r="C213" s="276"/>
       <c r="D213" s="276" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E213" s="304"/>
       <c r="F213" s="304"/>
@@ -57455,7 +57471,7 @@
       <c r="N213" s="324"/>
       <c r="O213" s="324"/>
       <c r="P213" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q213" s="309"/>
       <c r="R213" s="309"/>
@@ -57480,7 +57496,7 @@
       </c>
       <c r="AJ213" s="324"/>
       <c r="AK213" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL213" s="309"/>
       <c r="AM213" s="309"/>
@@ -57543,7 +57559,7 @@
       </c>
       <c r="C215" s="345"/>
       <c r="D215" s="276" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E215" s="276"/>
       <c r="F215" s="276"/>
@@ -57554,7 +57570,7 @@
       <c r="K215" s="272"/>
       <c r="L215" s="272"/>
       <c r="M215" s="350" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N215" s="350"/>
       <c r="O215" s="350"/>
@@ -57569,7 +57585,7 @@
       <c r="X215" s="350"/>
       <c r="Y215" s="272"/>
       <c r="Z215" s="276" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AA215" s="347"/>
       <c r="AB215" s="276"/>
@@ -57580,7 +57596,7 @@
       <c r="AG215" s="276"/>
       <c r="AH215" s="276"/>
       <c r="AI215" s="351" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AJ215" s="351"/>
       <c r="AK215" s="351"/>
@@ -57611,7 +57627,7 @@
       <c r="N216" s="324"/>
       <c r="O216" s="324"/>
       <c r="P216" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q216" s="309"/>
       <c r="R216" s="309"/>
@@ -57623,7 +57639,7 @@
       <c r="X216" s="309"/>
       <c r="Y216" s="272"/>
       <c r="Z216" s="304" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AA216" s="304"/>
       <c r="AB216" s="304"/>
@@ -57638,7 +57654,7 @@
       </c>
       <c r="AJ216" s="324"/>
       <c r="AK216" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AL216" s="309"/>
       <c r="AM216" s="309"/>
@@ -57696,7 +57712,7 @@
     </row>
     <row r="218" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="352" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B218" s="352"/>
       <c r="C218" s="352"/>
@@ -57744,7 +57760,7 @@
     </row>
     <row r="219" s="87" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="294" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B219" s="294"/>
       <c r="C219" s="294"/>
@@ -57792,7 +57808,7 @@
     </row>
     <row r="220" s="87" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="353" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B220" s="353"/>
       <c r="C220" s="353"/>
@@ -57841,7 +57857,7 @@
     <row r="221" s="120" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="276"/>
       <c r="B221" s="276" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C221" s="276"/>
       <c r="D221" s="276"/>
@@ -57889,7 +57905,7 @@
     <row r="222" s="355" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="304"/>
       <c r="B222" s="304" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C222" s="304"/>
       <c r="D222" s="304"/>
@@ -57983,7 +57999,7 @@
     <row r="224" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="272"/>
       <c r="B224" s="276" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C224" s="276"/>
       <c r="D224" s="276"/>
@@ -58004,7 +58020,7 @@
       <c r="Q224" s="272"/>
       <c r="R224" s="272"/>
       <c r="S224" s="276" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="T224" s="272"/>
       <c r="U224" s="272"/>
@@ -58018,7 +58034,7 @@
       </c>
       <c r="AB224" s="324"/>
       <c r="AC224" s="339" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AD224" s="309"/>
       <c r="AE224" s="309"/>
@@ -58026,7 +58042,7 @@
       <c r="AG224" s="309"/>
       <c r="AH224" s="309"/>
       <c r="AI224" s="276" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AJ224" s="272"/>
       <c r="AK224" s="272"/>
@@ -58086,7 +58102,7 @@
     </row>
     <row r="226" s="87" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="307" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B226" s="307"/>
       <c r="C226" s="307"/>
@@ -58135,7 +58151,7 @@
     <row r="227" s="120" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="276"/>
       <c r="B227" s="276" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C227" s="276"/>
       <c r="D227" s="276"/>
@@ -58183,7 +58199,7 @@
     <row r="228" s="355" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="304"/>
       <c r="B228" s="304" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C228" s="304"/>
       <c r="D228" s="304"/>
@@ -58231,7 +58247,7 @@
     <row r="229" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="276"/>
       <c r="B229" s="276" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C229" s="276"/>
       <c r="D229" s="276"/>
@@ -58267,7 +58283,7 @@
       <c r="AH229" s="276"/>
       <c r="AI229" s="276"/>
       <c r="AJ229" s="276" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AK229" s="276"/>
       <c r="AL229" s="276"/>
@@ -58377,7 +58393,7 @@
     <row r="232" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="276"/>
       <c r="B232" s="276" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C232" s="276"/>
       <c r="D232" s="276"/>
@@ -58398,7 +58414,7 @@
       <c r="S232" s="276"/>
       <c r="T232" s="276"/>
       <c r="U232" s="276" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="V232" s="276"/>
       <c r="W232" s="276"/>
@@ -58523,7 +58539,7 @@
     <row r="235" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="276"/>
       <c r="B235" s="276" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C235" s="276"/>
       <c r="D235" s="276"/>
@@ -58664,7 +58680,7 @@
     </row>
     <row r="238" s="87" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="307" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B238" s="307"/>
       <c r="C238" s="307"/>
@@ -58713,7 +58729,7 @@
     <row r="239" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="276"/>
       <c r="B239" s="276" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C239" s="276"/>
       <c r="D239" s="276"/>
@@ -58761,7 +58777,7 @@
     <row r="240" s="363" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="321"/>
       <c r="B240" s="304" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C240" s="321"/>
       <c r="D240" s="321"/>
@@ -58903,7 +58919,7 @@
     <row r="243" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="272"/>
       <c r="B243" s="276" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C243" s="272"/>
       <c r="D243" s="272"/>
@@ -58999,7 +59015,7 @@
     <row r="245" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="272"/>
       <c r="B245" s="276" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C245" s="272"/>
       <c r="D245" s="272"/>
@@ -59095,7 +59111,7 @@
     <row r="247" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="272"/>
       <c r="B247" s="292" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C247" s="272"/>
       <c r="D247" s="272"/>
@@ -59331,7 +59347,7 @@
     <row r="252" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="276"/>
       <c r="B252" s="276" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C252" s="276"/>
       <c r="D252" s="276"/>
@@ -59427,7 +59443,7 @@
     <row r="254" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="276"/>
       <c r="B254" s="276" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C254" s="276"/>
       <c r="D254" s="276"/>
@@ -59521,7 +59537,7 @@
     <row r="256" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="276"/>
       <c r="B256" s="276" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C256" s="276"/>
       <c r="D256" s="276"/>
@@ -59709,7 +59725,7 @@
     <row r="260" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="272"/>
       <c r="B260" s="276" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C260" s="272"/>
       <c r="D260" s="272"/>
@@ -59850,7 +59866,7 @@
     </row>
     <row r="263" s="87" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="338" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B263" s="338"/>
       <c r="C263" s="338"/>
@@ -59899,7 +59915,7 @@
     <row r="264" s="149" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="374"/>
       <c r="B264" s="374" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C264" s="374"/>
       <c r="D264" s="374"/>
@@ -59947,7 +59963,7 @@
     <row r="265" s="375" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="318"/>
       <c r="B265" s="318" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C265" s="318"/>
       <c r="D265" s="318"/>
@@ -59995,7 +60011,7 @@
     <row r="266" s="149" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="374"/>
       <c r="B266" s="374" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C266" s="374"/>
       <c r="D266" s="374"/>
@@ -60043,7 +60059,7 @@
     <row r="267" s="149" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="374"/>
       <c r="B267" s="374" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C267" s="374"/>
       <c r="D267" s="374"/>
@@ -60091,7 +60107,7 @@
     <row r="268" s="376" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="312"/>
       <c r="B268" s="312" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C268" s="312"/>
       <c r="D268" s="312"/>
@@ -60139,7 +60155,7 @@
     <row r="269" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="276"/>
       <c r="B269" s="276" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C269" s="276"/>
       <c r="D269" s="276"/>
@@ -60325,7 +60341,7 @@
     <row r="273" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="272"/>
       <c r="B273" s="276" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C273" s="272"/>
       <c r="D273" s="272"/>
@@ -60356,7 +60372,7 @@
       <c r="AC273" s="272"/>
       <c r="AD273" s="272"/>
       <c r="AE273" s="276" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AF273" s="272"/>
       <c r="AG273" s="272"/>
@@ -60424,7 +60440,7 @@
     <row r="275" s="120" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="276"/>
       <c r="B275" s="276" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C275" s="276"/>
       <c r="D275" s="276"/>
@@ -60472,7 +60488,7 @@
     <row r="276" s="87" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="272"/>
       <c r="B276" s="378" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C276" s="378"/>
       <c r="D276" s="378"/>
